--- a/data/warn-scraper/cache/ca/warn_report1.xlsx
+++ b/data/warn-scraper/cache/ca/warn_report1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\WSB-CO\Communications Unit\Website Management\WARN (Worker Adjustment and Retraining Notification) Updates\2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1636375-9F01-49A7-9A58-E620E3FB49F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CED4AE8-C5B3-469D-9E3E-CC598074639B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="32550" yWindow="1635" windowWidth="21600" windowHeight="11430" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="713" uniqueCount="302">
   <si>
     <t>County/Parish</t>
   </si>
@@ -850,6 +850,141 @@
   </si>
   <si>
     <t>1424 Corporate Center Drive Suite 140 San Diego CA 92154</t>
+  </si>
+  <si>
+    <t>Yellow Corporation-Batavia St.</t>
+  </si>
+  <si>
+    <t>Yellow Corporation-Eckhoff</t>
+  </si>
+  <si>
+    <t>1535 E Pescadero Ave.  Tracy CA 95304</t>
+  </si>
+  <si>
+    <t>1700 Montague Expressway  San Jose CA 95131</t>
+  </si>
+  <si>
+    <t>11937 Regentview Ave  Downey CA 90241</t>
+  </si>
+  <si>
+    <t>155 E Channel Rd.  Benicia CA 94510</t>
+  </si>
+  <si>
+    <t>25555 Clawiter Road  Hayward CA 94545</t>
+  </si>
+  <si>
+    <t>4556 S Chestnut Ave  Fresno CA 93725</t>
+  </si>
+  <si>
+    <t>Humboldt County</t>
+  </si>
+  <si>
+    <t>1100 W Del Norte St  Eureka CA 95501</t>
+  </si>
+  <si>
+    <t>Imperial County</t>
+  </si>
+  <si>
+    <t>2451 Portico Blvd  Calexico CA 92231</t>
+  </si>
+  <si>
+    <t>4901 Lisa Marie Ct  Bakersfield CA 93313</t>
+  </si>
+  <si>
+    <t>11300 W Peoria  Sun Valley CA 91352</t>
+  </si>
+  <si>
+    <t>4700 South Eastern Avenue  Los Angeles CA 90040</t>
+  </si>
+  <si>
+    <t>9933 Beverly Blvd  Pico Rivera CA 90660</t>
+  </si>
+  <si>
+    <t>1130 South Reservoir Street  Pomona CA 91766</t>
+  </si>
+  <si>
+    <t>1110 South Reservoir St  Pomona CA 91766</t>
+  </si>
+  <si>
+    <t>Monterey County</t>
+  </si>
+  <si>
+    <t>1090 Terven Ave  Salinas CA 93901</t>
+  </si>
+  <si>
+    <t>270 Dutton Ave.  Santa Rosa CA 95407</t>
+  </si>
+  <si>
+    <t>1619 N Plaza Dr  Visalia CA 93291</t>
+  </si>
+  <si>
+    <t>Ventura County</t>
+  </si>
+  <si>
+    <t>2685 Sherwin Ave.  Ventura CA 93003</t>
+  </si>
+  <si>
+    <t>Yolo County</t>
+  </si>
+  <si>
+    <t>620 Harbor Blvd.  West Sacramento CA 95691</t>
+  </si>
+  <si>
+    <t>Cardinal Glass Industries, Inc.</t>
+  </si>
+  <si>
+    <t>1125 E Lanzit Ave  Los Angeles CA 90059</t>
+  </si>
+  <si>
+    <t>Peloton Interactive Inc.</t>
+  </si>
+  <si>
+    <t>4564 Redlands Avenue  Perris CA 92571</t>
+  </si>
+  <si>
+    <t>Tempo Automation Holdings, Inc.</t>
+  </si>
+  <si>
+    <t>2460 Alameda St  San Francisco CA 94103</t>
+  </si>
+  <si>
+    <t>SPT Microtechnologies USA, Inc.</t>
+  </si>
+  <si>
+    <t>5750 Hellyer Avenue, Suite 10  San Jose CA 95138</t>
+  </si>
+  <si>
+    <t>Corteva Agriscience LLC</t>
+  </si>
+  <si>
+    <t>901 Loveridge Road  Pittsburg CA 94565</t>
+  </si>
+  <si>
+    <t>Fish Market Restaurants, Inc.</t>
+  </si>
+  <si>
+    <t>3150 El Camino Real  Palo Alto CA 94306</t>
+  </si>
+  <si>
+    <t>1855 South Norfolk Street  San Mateo CA 94403</t>
+  </si>
+  <si>
+    <t>207 South Maple  South San Francisco CA 94080</t>
+  </si>
+  <si>
+    <t>FibroGen, Inc.</t>
+  </si>
+  <si>
+    <t>409 Illinois St  San Francisco CA 94158</t>
+  </si>
+  <si>
+    <t>Marin County</t>
+  </si>
+  <si>
+    <t>Vionic Consumer Care Operations</t>
+  </si>
+  <si>
+    <t>4040 Civic Center Drive, Suite 430  San Rafael CA 94903</t>
   </si>
 </sst>
 </file>
@@ -1459,13 +1594,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:H148"/>
+  <dimension ref="A1:H177"/>
   <sheetFormatPr defaultColWidth="46" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.5546875" customWidth="1"/>
-    <col min="3" max="3" width="9.6640625" customWidth="1"/>
-    <col min="4" max="4" width="9.5546875" customWidth="1"/>
+    <col min="2" max="3" width="9.88671875" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
     <col min="5" max="5" width="54.88671875" style="20" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.33203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.88671875" bestFit="1" customWidth="1"/>
@@ -4840,7 +4974,7 @@
         <v>45137</v>
       </c>
       <c r="E130" s="17" t="s">
-        <v>231</v>
+        <v>257</v>
       </c>
       <c r="F130" s="17" t="s">
         <v>15</v>
@@ -4866,7 +5000,7 @@
         <v>45137</v>
       </c>
       <c r="E131" s="19" t="s">
-        <v>231</v>
+        <v>258</v>
       </c>
       <c r="F131" s="19" t="s">
         <v>15</v>
@@ -5268,55 +5402,809 @@
         <v>256</v>
       </c>
     </row>
-    <row r="147" spans="1:8" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A147" s="3" t="s">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A147" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="B147" s="11">
+        <v>45139</v>
+      </c>
+      <c r="C147" s="11">
+        <v>45155</v>
+      </c>
+      <c r="D147" s="11">
+        <v>45137</v>
+      </c>
+      <c r="E147" s="19" t="s">
+        <v>231</v>
+      </c>
+      <c r="F147" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G147" s="14">
+        <v>257</v>
+      </c>
+      <c r="H147" s="15" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A148" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="B148" s="10">
+        <v>45139</v>
+      </c>
+      <c r="C148" s="10">
+        <v>45155</v>
+      </c>
+      <c r="D148" s="10">
+        <v>45137</v>
+      </c>
+      <c r="E148" s="17" t="s">
+        <v>231</v>
+      </c>
+      <c r="F148" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="G148" s="12">
+        <v>1</v>
+      </c>
+      <c r="H148" s="13" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A149" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="B149" s="11">
+        <v>45139</v>
+      </c>
+      <c r="C149" s="11">
+        <v>45155</v>
+      </c>
+      <c r="D149" s="11">
+        <v>45137</v>
+      </c>
+      <c r="E149" s="19" t="s">
+        <v>231</v>
+      </c>
+      <c r="F149" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G149" s="14">
+        <v>120</v>
+      </c>
+      <c r="H149" s="15" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A150" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="B150" s="10">
+        <v>45139</v>
+      </c>
+      <c r="C150" s="10">
+        <v>45155</v>
+      </c>
+      <c r="D150" s="10">
+        <v>45137</v>
+      </c>
+      <c r="E150" s="17" t="s">
+        <v>231</v>
+      </c>
+      <c r="F150" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="G150" s="12">
+        <v>1</v>
+      </c>
+      <c r="H150" s="13" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A151" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="B151" s="11">
+        <v>45139</v>
+      </c>
+      <c r="C151" s="11">
+        <v>45156</v>
+      </c>
+      <c r="D151" s="11">
+        <v>45137</v>
+      </c>
+      <c r="E151" s="19" t="s">
+        <v>231</v>
+      </c>
+      <c r="F151" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G151" s="14">
+        <v>99</v>
+      </c>
+      <c r="H151" s="15" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A152" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B152" s="10">
+        <v>45139</v>
+      </c>
+      <c r="C152" s="10">
+        <v>45156</v>
+      </c>
+      <c r="D152" s="10">
+        <v>45137</v>
+      </c>
+      <c r="E152" s="17" t="s">
+        <v>231</v>
+      </c>
+      <c r="F152" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="G152" s="12">
+        <v>66</v>
+      </c>
+      <c r="H152" s="13" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A153" s="18" t="s">
+        <v>265</v>
+      </c>
+      <c r="B153" s="11">
+        <v>45139</v>
+      </c>
+      <c r="C153" s="11">
+        <v>45156</v>
+      </c>
+      <c r="D153" s="11">
+        <v>45137</v>
+      </c>
+      <c r="E153" s="19" t="s">
+        <v>231</v>
+      </c>
+      <c r="F153" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G153" s="14">
+        <v>4</v>
+      </c>
+      <c r="H153" s="15" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A154" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="B154" s="10">
+        <v>45139</v>
+      </c>
+      <c r="C154" s="10">
+        <v>45156</v>
+      </c>
+      <c r="D154" s="10">
+        <v>45137</v>
+      </c>
+      <c r="E154" s="17" t="s">
+        <v>231</v>
+      </c>
+      <c r="F154" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="G154" s="12">
+        <v>15</v>
+      </c>
+      <c r="H154" s="13" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A155" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="B155" s="11">
+        <v>45139</v>
+      </c>
+      <c r="C155" s="11">
+        <v>45156</v>
+      </c>
+      <c r="D155" s="11">
+        <v>45137</v>
+      </c>
+      <c r="E155" s="19" t="s">
+        <v>231</v>
+      </c>
+      <c r="F155" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G155" s="14">
+        <v>27</v>
+      </c>
+      <c r="H155" s="15" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A156" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="B156" s="10">
+        <v>45139</v>
+      </c>
+      <c r="C156" s="10">
+        <v>45156</v>
+      </c>
+      <c r="D156" s="10">
+        <v>45137</v>
+      </c>
+      <c r="E156" s="17" t="s">
+        <v>231</v>
+      </c>
+      <c r="F156" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="G156" s="12">
+        <v>102</v>
+      </c>
+      <c r="H156" s="13" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A157" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="B157" s="11">
+        <v>45139</v>
+      </c>
+      <c r="C157" s="11">
+        <v>45156</v>
+      </c>
+      <c r="D157" s="11">
+        <v>45137</v>
+      </c>
+      <c r="E157" s="19" t="s">
+        <v>231</v>
+      </c>
+      <c r="F157" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G157" s="14">
+        <v>2</v>
+      </c>
+      <c r="H157" s="15" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A158" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="B158" s="10">
+        <v>45139</v>
+      </c>
+      <c r="C158" s="10">
+        <v>45156</v>
+      </c>
+      <c r="D158" s="10">
+        <v>45137</v>
+      </c>
+      <c r="E158" s="17" t="s">
+        <v>231</v>
+      </c>
+      <c r="F158" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="G158" s="12">
+        <v>169</v>
+      </c>
+      <c r="H158" s="13" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A159" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="B159" s="11">
+        <v>45139</v>
+      </c>
+      <c r="C159" s="11">
+        <v>45156</v>
+      </c>
+      <c r="D159" s="11">
+        <v>45137</v>
+      </c>
+      <c r="E159" s="19" t="s">
+        <v>231</v>
+      </c>
+      <c r="F159" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G159" s="14">
+        <v>70</v>
+      </c>
+      <c r="H159" s="15" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A160" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="B160" s="10">
+        <v>45139</v>
+      </c>
+      <c r="C160" s="10">
+        <v>45156</v>
+      </c>
+      <c r="D160" s="10">
+        <v>45137</v>
+      </c>
+      <c r="E160" s="17" t="s">
+        <v>231</v>
+      </c>
+      <c r="F160" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="G160" s="12">
+        <v>22</v>
+      </c>
+      <c r="H160" s="13" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A161" s="18" t="s">
+        <v>275</v>
+      </c>
+      <c r="B161" s="11">
+        <v>45139</v>
+      </c>
+      <c r="C161" s="11">
+        <v>45156</v>
+      </c>
+      <c r="D161" s="11">
+        <v>45137</v>
+      </c>
+      <c r="E161" s="19" t="s">
+        <v>231</v>
+      </c>
+      <c r="F161" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G161" s="14">
+        <v>4</v>
+      </c>
+      <c r="H161" s="15" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A162" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="B162" s="10">
+        <v>45139</v>
+      </c>
+      <c r="C162" s="10">
+        <v>45156</v>
+      </c>
+      <c r="D162" s="10">
+        <v>45137</v>
+      </c>
+      <c r="E162" s="17" t="s">
+        <v>231</v>
+      </c>
+      <c r="F162" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="G162" s="12">
         <v>29</v>
       </c>
-      <c r="B147" s="4" t="s">
+      <c r="H162" s="13" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A163" s="18" t="s">
+        <v>172</v>
+      </c>
+      <c r="B163" s="11">
+        <v>45139</v>
+      </c>
+      <c r="C163" s="11">
+        <v>45156</v>
+      </c>
+      <c r="D163" s="11">
+        <v>45137</v>
+      </c>
+      <c r="E163" s="19" t="s">
+        <v>231</v>
+      </c>
+      <c r="F163" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G163" s="14">
+        <v>23</v>
+      </c>
+      <c r="H163" s="15" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A164" s="16" t="s">
+        <v>279</v>
+      </c>
+      <c r="B164" s="10">
+        <v>45139</v>
+      </c>
+      <c r="C164" s="10">
+        <v>45156</v>
+      </c>
+      <c r="D164" s="10">
+        <v>45137</v>
+      </c>
+      <c r="E164" s="17" t="s">
+        <v>231</v>
+      </c>
+      <c r="F164" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="G164" s="12">
+        <v>23</v>
+      </c>
+      <c r="H164" s="13" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A165" s="18" t="s">
+        <v>281</v>
+      </c>
+      <c r="B165" s="11">
+        <v>45139</v>
+      </c>
+      <c r="C165" s="11">
+        <v>45156</v>
+      </c>
+      <c r="D165" s="11">
+        <v>45137</v>
+      </c>
+      <c r="E165" s="19" t="s">
+        <v>231</v>
+      </c>
+      <c r="F165" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G165" s="14">
+        <v>58</v>
+      </c>
+      <c r="H165" s="15" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A166" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="B166" s="10">
+        <v>45117</v>
+      </c>
+      <c r="C166" s="10">
+        <v>45159</v>
+      </c>
+      <c r="D166" s="10">
+        <v>45179</v>
+      </c>
+      <c r="E166" s="17" t="s">
+        <v>283</v>
+      </c>
+      <c r="F166" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="G166" s="12">
+        <v>29</v>
+      </c>
+      <c r="H166" s="13" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A167" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B167" s="11">
+        <v>45119</v>
+      </c>
+      <c r="C167" s="11">
+        <v>45159</v>
+      </c>
+      <c r="D167" s="11">
+        <v>45184</v>
+      </c>
+      <c r="E167" s="19" t="s">
+        <v>285</v>
+      </c>
+      <c r="F167" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G167" s="14">
         <v>21</v>
       </c>
-      <c r="C147" s="4" t="s">
+      <c r="H167" s="15" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A168" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="B168" s="10">
+        <v>45121</v>
+      </c>
+      <c r="C168" s="10">
+        <v>45159</v>
+      </c>
+      <c r="D168" s="10">
+        <v>45121</v>
+      </c>
+      <c r="E168" s="17" t="s">
+        <v>287</v>
+      </c>
+      <c r="F168" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="G168" s="12">
+        <v>58</v>
+      </c>
+      <c r="H168" s="13" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A169" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="B169" s="11">
+        <v>45139</v>
+      </c>
+      <c r="C169" s="11">
+        <v>45159</v>
+      </c>
+      <c r="D169" s="11">
+        <v>45250</v>
+      </c>
+      <c r="E169" s="19" t="s">
+        <v>289</v>
+      </c>
+      <c r="F169" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="G169" s="14">
+        <v>67</v>
+      </c>
+      <c r="H169" s="15" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A170" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B170" s="10">
+        <v>45124</v>
+      </c>
+      <c r="C170" s="10">
+        <v>45161</v>
+      </c>
+      <c r="D170" s="10">
+        <v>45226</v>
+      </c>
+      <c r="E170" s="17" t="s">
+        <v>291</v>
+      </c>
+      <c r="F170" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G170" s="12">
+        <v>31</v>
+      </c>
+      <c r="H170" s="13" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A171" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="B171" s="11">
+        <v>45121</v>
+      </c>
+      <c r="C171" s="11">
+        <v>45161</v>
+      </c>
+      <c r="D171" s="11">
+        <v>45183</v>
+      </c>
+      <c r="E171" s="19" t="s">
+        <v>293</v>
+      </c>
+      <c r="F171" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G171" s="14">
+        <v>49</v>
+      </c>
+      <c r="H171" s="15" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A172" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="B172" s="10">
+        <v>45121</v>
+      </c>
+      <c r="C172" s="10">
+        <v>45161</v>
+      </c>
+      <c r="D172" s="10">
+        <v>45183</v>
+      </c>
+      <c r="E172" s="17" t="s">
+        <v>293</v>
+      </c>
+      <c r="F172" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="G172" s="12">
+        <v>85</v>
+      </c>
+      <c r="H172" s="13" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A173" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="B173" s="11">
+        <v>45121</v>
+      </c>
+      <c r="C173" s="11">
+        <v>45161</v>
+      </c>
+      <c r="D173" s="11">
+        <v>45183</v>
+      </c>
+      <c r="E173" s="19" t="s">
+        <v>293</v>
+      </c>
+      <c r="F173" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G173" s="14">
+        <v>6</v>
+      </c>
+      <c r="H173" s="15" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A174" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="B174" s="10">
+        <v>45124</v>
+      </c>
+      <c r="C174" s="10">
+        <v>45161</v>
+      </c>
+      <c r="D174" s="10">
+        <v>45184</v>
+      </c>
+      <c r="E174" s="17" t="s">
+        <v>297</v>
+      </c>
+      <c r="F174" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G174" s="12">
+        <v>104</v>
+      </c>
+      <c r="H174" s="13" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A175" s="18" t="s">
+        <v>299</v>
+      </c>
+      <c r="B175" s="11">
+        <v>45126</v>
+      </c>
+      <c r="C175" s="11">
+        <v>45161</v>
+      </c>
+      <c r="D175" s="11">
+        <v>45186</v>
+      </c>
+      <c r="E175" s="19" t="s">
+        <v>300</v>
+      </c>
+      <c r="F175" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G175" s="14">
+        <v>6</v>
+      </c>
+      <c r="H175" s="15" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A176" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B176" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C176" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D147" s="4" t="s">
+      <c r="D176" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E147" s="4" t="s">
+      <c r="E176" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="F147" s="4" t="s">
+      <c r="F176" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="G147" s="4" t="s">
+      <c r="G176" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="H147" s="5" t="s">
+      <c r="H176" s="5" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A148" s="6" t="s">
+    <row r="177" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A177" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B148" s="7">
-        <v>7955</v>
-      </c>
-      <c r="C148" s="7">
-        <v>87</v>
-      </c>
-      <c r="D148" s="7">
-        <v>2</v>
-      </c>
-      <c r="E148" s="7">
+      <c r="B177" s="7">
+        <v>9503</v>
+      </c>
+      <c r="C177" s="7">
+        <v>89</v>
+      </c>
+      <c r="D177" s="7">
+        <v>3</v>
+      </c>
+      <c r="E177" s="7">
         <v>0</v>
       </c>
-      <c r="F148" s="7">
-        <v>55</v>
-      </c>
-      <c r="G148" s="7">
+      <c r="F177" s="7">
+        <v>81</v>
+      </c>
+      <c r="G177" s="7">
         <v>1</v>
       </c>
-      <c r="H148" s="8">
+      <c r="H177" s="8">
         <v>0</v>
       </c>
     </row>

--- a/data/warn-scraper/cache/ca/warn_report1.xlsx
+++ b/data/warn-scraper/cache/ca/warn_report1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\WSB-CO\Communications Unit\Website Management\WARN (Worker Adjustment and Retraining Notification) Updates\2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CED4AE8-C5B3-469D-9E3E-CC598074639B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECEB01EC-EE2F-4435-8557-1AAAAAEA88C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="32550" yWindow="1635" windowWidth="21600" windowHeight="11430" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="713" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="733" uniqueCount="311">
   <si>
     <t>County/Parish</t>
   </si>
@@ -985,6 +985,33 @@
   </si>
   <si>
     <t>4040 Civic Center Drive, Suite 430  San Rafael CA 94903</t>
+  </si>
+  <si>
+    <t>Accenture</t>
+  </si>
+  <si>
+    <t>34750 Campus Drive  Fremont CA 94555</t>
+  </si>
+  <si>
+    <t>34800 Campus Drive  Fremont CA 94555</t>
+  </si>
+  <si>
+    <t>Intense Lighting, LLC</t>
+  </si>
+  <si>
+    <t>3340 E. La Palma Avenue  Anaheim CA 92806</t>
+  </si>
+  <si>
+    <t>Blowfish</t>
+  </si>
+  <si>
+    <t>6063 Bristol Parkway  Culver City CA 90230</t>
+  </si>
+  <si>
+    <t>Charles River Laboratories, Inc.</t>
+  </si>
+  <si>
+    <t>225 Gateway Boulevard, Suite 200  South San Francisco CA 94080</t>
   </si>
 </sst>
 </file>
@@ -1594,19 +1621,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:H177"/>
+  <dimension ref="A1:H182"/>
   <sheetFormatPr defaultColWidth="46" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="9.88671875" customWidth="1"/>
-    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="4" max="4" width="9.88671875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="54.88671875" style="20" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.33203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="44.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="49" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" s="1" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -5991,7 +6018,7 @@
         <v>289</v>
       </c>
       <c r="F169" s="19" t="s">
-        <v>17</v>
+        <v>100</v>
       </c>
       <c r="G169" s="14">
         <v>67</v>
@@ -6156,55 +6183,185 @@
         <v>301</v>
       </c>
     </row>
-    <row r="176" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A176" s="3" t="s">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A176" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="B176" s="10">
+        <v>45128</v>
+      </c>
+      <c r="C176" s="10">
+        <v>45166</v>
+      </c>
+      <c r="D176" s="10">
+        <v>45240</v>
+      </c>
+      <c r="E176" s="17" t="s">
+        <v>302</v>
+      </c>
+      <c r="F176" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="G176" s="12">
+        <v>100</v>
+      </c>
+      <c r="H176" s="13" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A177" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="B177" s="11">
+        <v>45128</v>
+      </c>
+      <c r="C177" s="11">
+        <v>45166</v>
+      </c>
+      <c r="D177" s="11">
+        <v>45240</v>
+      </c>
+      <c r="E177" s="19" t="s">
+        <v>302</v>
+      </c>
+      <c r="F177" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G177" s="14">
+        <v>140</v>
+      </c>
+      <c r="H177" s="15" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A178" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="B178" s="10">
+        <v>45131</v>
+      </c>
+      <c r="C178" s="10">
+        <v>45166</v>
+      </c>
+      <c r="D178" s="10">
+        <v>45198</v>
+      </c>
+      <c r="E178" s="17" t="s">
+        <v>305</v>
+      </c>
+      <c r="F178" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="G178" s="12">
+        <v>90</v>
+      </c>
+      <c r="H178" s="13" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A179" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="B179" s="11">
+        <v>45125</v>
+      </c>
+      <c r="C179" s="11">
+        <v>45166</v>
+      </c>
+      <c r="D179" s="11">
+        <v>45184</v>
+      </c>
+      <c r="E179" s="19" t="s">
+        <v>307</v>
+      </c>
+      <c r="F179" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G179" s="14">
+        <v>20</v>
+      </c>
+      <c r="H179" s="15" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A180" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="B180" s="10">
+        <v>45126</v>
+      </c>
+      <c r="C180" s="10">
+        <v>45166</v>
+      </c>
+      <c r="D180" s="10">
+        <v>45188</v>
+      </c>
+      <c r="E180" s="17" t="s">
+        <v>309</v>
+      </c>
+      <c r="F180" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="G180" s="12">
+        <v>55</v>
+      </c>
+      <c r="H180" s="13" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A181" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B176" s="4" t="s">
+      <c r="B181" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C176" s="4" t="s">
+      <c r="C181" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D176" s="4" t="s">
+      <c r="D181" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E176" s="4" t="s">
+      <c r="E181" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="F176" s="4" t="s">
+      <c r="F181" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="G176" s="4" t="s">
+      <c r="G181" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="H176" s="5" t="s">
+      <c r="H181" s="5" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A177" s="6" t="s">
+    <row r="182" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A182" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B177" s="7">
-        <v>9503</v>
-      </c>
-      <c r="C177" s="7">
+      <c r="B182" s="7">
+        <v>9908</v>
+      </c>
+      <c r="C182" s="7">
         <v>89</v>
       </c>
-      <c r="D177" s="7">
-        <v>3</v>
-      </c>
-      <c r="E177" s="7">
+      <c r="D182" s="7">
+        <v>2</v>
+      </c>
+      <c r="E182" s="7">
         <v>0</v>
       </c>
-      <c r="F177" s="7">
-        <v>81</v>
-      </c>
-      <c r="G177" s="7">
-        <v>1</v>
-      </c>
-      <c r="H177" s="8">
+      <c r="F182" s="7">
+        <v>86</v>
+      </c>
+      <c r="G182" s="7">
+        <v>2</v>
+      </c>
+      <c r="H182" s="8">
         <v>0</v>
       </c>
     </row>
@@ -6212,4 +6369,145 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="204" verticalDpi="192" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Unknown Document Type" ma:contentTypeID="0x010104" ma:contentTypeVersion="0" ma:contentTypeDescription="" ma:contentTypeScope="" ma:versionID="05d83ceaa0bbd2e3bc716e6e66bd857a">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b3d69fe45253d5ff147bb69036b756a7">
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all/>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type" ma:readOnly="true"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="3" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{400E7170-80D4-4C48-A568-27FD03FB56DB}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F06FF2FE-7F4B-48F7-AA53-77B138CFCB36}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{36E059A5-9524-4245-B2CB-4E04A6998050}"/>
 </file>
--- a/data/warn-scraper/cache/ca/warn_report1.xlsx
+++ b/data/warn-scraper/cache/ca/warn_report1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\WSB-CO\Communications Unit\Website Management\WARN (Worker Adjustment and Retraining Notification) Updates\2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECEB01EC-EE2F-4435-8557-1AAAAAEA88C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A4FD36D-9E71-4DB9-92A2-776FE75C337B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32550" yWindow="1635" windowWidth="21600" windowHeight="11430" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
+    <workbookView xWindow="29895" yWindow="1230" windowWidth="21600" windowHeight="11430" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="733" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="785" uniqueCount="330">
   <si>
     <t>County/Parish</t>
   </si>
@@ -1012,6 +1012,63 @@
   </si>
   <si>
     <t>225 Gateway Boulevard, Suite 200  South San Francisco CA 94080</t>
+  </si>
+  <si>
+    <t>Gemological Institute of America, Inc. (GIA)</t>
+  </si>
+  <si>
+    <t>5345 Armada Drive  Carlsbad CA 92008</t>
+  </si>
+  <si>
+    <t>Petco Animal Supplies Stores</t>
+  </si>
+  <si>
+    <t>10850 Via Frontera  San Diego CA 92127</t>
+  </si>
+  <si>
+    <t>Codexis, Inc.</t>
+  </si>
+  <si>
+    <t>200 Penobscot Drive  Redwood City CA 94063</t>
+  </si>
+  <si>
+    <t>825 Industrial Road  San Carlos CA 94070</t>
+  </si>
+  <si>
+    <t>CSL Vifor</t>
+  </si>
+  <si>
+    <t>200 Cardinal Way  Redwood City CA 94063</t>
+  </si>
+  <si>
+    <t>Headway Technologies Inc.</t>
+  </si>
+  <si>
+    <t>682 South Hillview Dr.  Milpitas CA 95035</t>
+  </si>
+  <si>
+    <t>497 South Hillview Dr.  Milpitas CA 95035</t>
+  </si>
+  <si>
+    <t>550 South Hillview Drive  Milpitas CA 95035</t>
+  </si>
+  <si>
+    <t>463 South Milpitas Blvd  Milpitas CA 95035</t>
+  </si>
+  <si>
+    <t>595 Yosemite Drive  Milpitas CA 95035</t>
+  </si>
+  <si>
+    <t>Langmuir Systems, LLC</t>
+  </si>
+  <si>
+    <t>11106 Moreno Ave Buildings 4 5 6  Lakeside CA 92040</t>
+  </si>
+  <si>
+    <t>Pizza Antica Mill Valley</t>
+  </si>
+  <si>
+    <t>800 Redwood Hwy #705  Mill Valley CA 94941</t>
   </si>
 </sst>
 </file>
@@ -1621,7 +1678,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:H182"/>
+  <dimension ref="A1:H195"/>
   <sheetFormatPr defaultColWidth="46" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.33203125" bestFit="1" customWidth="1"/>
@@ -1633,7 +1690,7 @@
     <col min="8" max="8" width="49" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" s="1" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -6313,55 +6370,393 @@
         <v>310</v>
       </c>
     </row>
-    <row r="181" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A181" s="3" t="s">
+    <row r="181" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A181" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="B181" s="11">
+        <v>45131</v>
+      </c>
+      <c r="C181" s="11">
+        <v>45167</v>
+      </c>
+      <c r="D181" s="11">
+        <v>45191</v>
+      </c>
+      <c r="E181" s="19" t="s">
+        <v>311</v>
+      </c>
+      <c r="F181" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G181" s="14">
+        <v>151</v>
+      </c>
+      <c r="H181" s="15" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A182" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="B182" s="10">
+        <v>45131</v>
+      </c>
+      <c r="C182" s="10">
+        <v>45167</v>
+      </c>
+      <c r="D182" s="10">
+        <v>45135</v>
+      </c>
+      <c r="E182" s="17" t="s">
+        <v>313</v>
+      </c>
+      <c r="F182" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G182" s="12">
+        <v>47</v>
+      </c>
+      <c r="H182" s="13" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A183" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="B183" s="11">
+        <v>45131</v>
+      </c>
+      <c r="C183" s="11">
+        <v>45167</v>
+      </c>
+      <c r="D183" s="11">
+        <v>45226</v>
+      </c>
+      <c r="E183" s="19" t="s">
+        <v>313</v>
+      </c>
+      <c r="F183" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G183" s="14">
+        <v>9</v>
+      </c>
+      <c r="H183" s="15" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A184" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="B184" s="10">
+        <v>45127</v>
+      </c>
+      <c r="C184" s="10">
+        <v>45168</v>
+      </c>
+      <c r="D184" s="10">
+        <v>45199</v>
+      </c>
+      <c r="E184" s="17" t="s">
+        <v>315</v>
+      </c>
+      <c r="F184" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G184" s="12">
+        <v>28</v>
+      </c>
+      <c r="H184" s="13" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A185" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="B185" s="11">
+        <v>45127</v>
+      </c>
+      <c r="C185" s="11">
+        <v>45168</v>
+      </c>
+      <c r="D185" s="11">
+        <v>45199</v>
+      </c>
+      <c r="E185" s="19" t="s">
+        <v>315</v>
+      </c>
+      <c r="F185" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G185" s="14">
+        <v>31</v>
+      </c>
+      <c r="H185" s="15" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A186" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="B186" s="10">
+        <v>45159</v>
+      </c>
+      <c r="C186" s="10">
+        <v>45168</v>
+      </c>
+      <c r="D186" s="10">
+        <v>45224</v>
+      </c>
+      <c r="E186" s="17" t="s">
+        <v>318</v>
+      </c>
+      <c r="F186" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G186" s="12">
+        <v>85</v>
+      </c>
+      <c r="H186" s="13" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A187" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="B187" s="11">
+        <v>45127</v>
+      </c>
+      <c r="C187" s="11">
+        <v>45168</v>
+      </c>
+      <c r="D187" s="11">
+        <v>45191</v>
+      </c>
+      <c r="E187" s="19" t="s">
+        <v>320</v>
+      </c>
+      <c r="F187" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G187" s="14">
+        <v>2</v>
+      </c>
+      <c r="H187" s="15" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A188" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="B188" s="10">
+        <v>45127</v>
+      </c>
+      <c r="C188" s="10">
+        <v>45168</v>
+      </c>
+      <c r="D188" s="10">
+        <v>45191</v>
+      </c>
+      <c r="E188" s="17" t="s">
+        <v>320</v>
+      </c>
+      <c r="F188" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G188" s="12">
+        <v>59</v>
+      </c>
+      <c r="H188" s="13" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="189" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A189" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="B189" s="11">
+        <v>45127</v>
+      </c>
+      <c r="C189" s="11">
+        <v>45168</v>
+      </c>
+      <c r="D189" s="11">
+        <v>45191</v>
+      </c>
+      <c r="E189" s="19" t="s">
+        <v>320</v>
+      </c>
+      <c r="F189" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G189" s="14">
+        <v>2</v>
+      </c>
+      <c r="H189" s="15" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A190" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="B190" s="10">
+        <v>45127</v>
+      </c>
+      <c r="C190" s="10">
+        <v>45168</v>
+      </c>
+      <c r="D190" s="10">
+        <v>45191</v>
+      </c>
+      <c r="E190" s="17" t="s">
+        <v>320</v>
+      </c>
+      <c r="F190" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G190" s="12">
+        <v>24</v>
+      </c>
+      <c r="H190" s="13" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="191" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A191" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="B191" s="11">
+        <v>45127</v>
+      </c>
+      <c r="C191" s="11">
+        <v>45168</v>
+      </c>
+      <c r="D191" s="11">
+        <v>45191</v>
+      </c>
+      <c r="E191" s="19" t="s">
+        <v>320</v>
+      </c>
+      <c r="F191" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G191" s="14">
+        <v>3</v>
+      </c>
+      <c r="H191" s="15" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A192" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="B192" s="10">
+        <v>45133</v>
+      </c>
+      <c r="C192" s="10">
+        <v>45168</v>
+      </c>
+      <c r="D192" s="10">
+        <v>45199</v>
+      </c>
+      <c r="E192" s="17" t="s">
+        <v>326</v>
+      </c>
+      <c r="F192" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="G192" s="12">
+        <v>16</v>
+      </c>
+      <c r="H192" s="13" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A193" s="18" t="s">
+        <v>299</v>
+      </c>
+      <c r="B193" s="11">
+        <v>45133</v>
+      </c>
+      <c r="C193" s="11">
+        <v>45168</v>
+      </c>
+      <c r="D193" s="11">
+        <v>45191</v>
+      </c>
+      <c r="E193" s="19" t="s">
+        <v>328</v>
+      </c>
+      <c r="F193" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G193" s="14">
+        <v>43</v>
+      </c>
+      <c r="H193" s="15" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A194" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B181" s="4" t="s">
+      <c r="B194" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C181" s="4" t="s">
+      <c r="C194" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D181" s="4" t="s">
+      <c r="D194" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E181" s="4" t="s">
+      <c r="E194" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="F181" s="4" t="s">
+      <c r="F194" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="G181" s="4" t="s">
+      <c r="G194" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="H181" s="5" t="s">
+      <c r="H194" s="5" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A182" s="6" t="s">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A195" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B182" s="7">
-        <v>9908</v>
-      </c>
-      <c r="C182" s="7">
-        <v>89</v>
-      </c>
-      <c r="D182" s="7">
+      <c r="B195" s="7">
+        <v>10408</v>
+      </c>
+      <c r="C195" s="7">
+        <v>100</v>
+      </c>
+      <c r="D195" s="7">
         <v>2</v>
       </c>
-      <c r="E182" s="7">
+      <c r="E195" s="7">
         <v>0</v>
       </c>
-      <c r="F182" s="7">
-        <v>86</v>
-      </c>
-      <c r="G182" s="7">
+      <c r="F195" s="7">
+        <v>88</v>
+      </c>
+      <c r="G195" s="7">
         <v>2</v>
       </c>
-      <c r="H182" s="8">
+      <c r="H195" s="8">
         <v>0</v>
       </c>
     </row>
@@ -6501,13 +6896,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{400E7170-80D4-4C48-A568-27FD03FB56DB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{37DAEFFE-2516-4BA9-8EF3-4546F3550B69}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F06FF2FE-7F4B-48F7-AA53-77B138CFCB36}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24B95492-2BE7-4244-8E63-AC25B1B4B114}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{36E059A5-9524-4245-B2CB-4E04A6998050}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{743DEB1B-F207-49D5-8C91-A5E6CD647815}"/>
 </file>
--- a/data/warn-scraper/cache/ca/warn_report1.xlsx
+++ b/data/warn-scraper/cache/ca/warn_report1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\WSB-CO\Communications Unit\Website Management\WARN (Worker Adjustment and Retraining Notification) Updates\2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A4FD36D-9E71-4DB9-92A2-776FE75C337B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF8AE2F3-DDD9-4A29-BD38-69CE3E46E4CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="29895" yWindow="1230" windowWidth="21600" windowHeight="11430" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="785" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="801" uniqueCount="338">
   <si>
     <t>County/Parish</t>
   </si>
@@ -1069,6 +1069,30 @@
   </si>
   <si>
     <t>800 Redwood Hwy #705  Mill Valley CA 94941</t>
+  </si>
+  <si>
+    <t>Alstom Mass Transit Corp.</t>
+  </si>
+  <si>
+    <t>1461 Loveridge Rd.  Pittsburg CA 94565</t>
+  </si>
+  <si>
+    <t>Point Digital Finance, Inc.</t>
+  </si>
+  <si>
+    <t>444 High St.  Palo Alto CA 94301</t>
+  </si>
+  <si>
+    <t>SP+ Corporation at Hollywood Burbank Airport</t>
+  </si>
+  <si>
+    <t>2627 Hollywood Way  Burbank CA 91506</t>
+  </si>
+  <si>
+    <t>Tri-City Medical Center</t>
+  </si>
+  <si>
+    <t>4002 Vista Way  Oceanside CA 92056</t>
   </si>
 </sst>
 </file>
@@ -1678,7 +1702,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:H195"/>
+  <dimension ref="A1:H199"/>
   <sheetFormatPr defaultColWidth="46" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.33203125" bestFit="1" customWidth="1"/>
@@ -1690,7 +1714,7 @@
     <col min="8" max="8" width="49" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" s="1" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -6708,55 +6732,159 @@
         <v>329</v>
       </c>
     </row>
-    <row r="194" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A194" s="3" t="s">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A194" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B194" s="10">
+        <v>45134</v>
+      </c>
+      <c r="C194" s="10">
+        <v>45169</v>
+      </c>
+      <c r="D194" s="10">
+        <v>45197</v>
+      </c>
+      <c r="E194" s="17" t="s">
+        <v>330</v>
+      </c>
+      <c r="F194" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="G194" s="12">
+        <v>41</v>
+      </c>
+      <c r="H194" s="13" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A195" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="B195" s="11">
+        <v>45134</v>
+      </c>
+      <c r="C195" s="11">
+        <v>45169</v>
+      </c>
+      <c r="D195" s="11">
+        <v>45135</v>
+      </c>
+      <c r="E195" s="19" t="s">
+        <v>332</v>
+      </c>
+      <c r="F195" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G195" s="14">
+        <v>61</v>
+      </c>
+      <c r="H195" s="15" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A196" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="B196" s="10">
+        <v>45134</v>
+      </c>
+      <c r="C196" s="10">
+        <v>45169</v>
+      </c>
+      <c r="D196" s="10">
+        <v>45199</v>
+      </c>
+      <c r="E196" s="17" t="s">
+        <v>334</v>
+      </c>
+      <c r="F196" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="G196" s="12">
+        <v>84</v>
+      </c>
+      <c r="H196" s="13" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A197" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="B197" s="11">
+        <v>45138</v>
+      </c>
+      <c r="C197" s="11">
+        <v>45170</v>
+      </c>
+      <c r="D197" s="11">
+        <v>45199</v>
+      </c>
+      <c r="E197" s="19" t="s">
+        <v>336</v>
+      </c>
+      <c r="F197" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G197" s="14">
+        <v>96</v>
+      </c>
+      <c r="H197" s="15" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A198" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B194" s="4" t="s">
+      <c r="B198" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C194" s="4" t="s">
+      <c r="C198" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D194" s="4" t="s">
+      <c r="D198" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E194" s="4" t="s">
+      <c r="E198" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="F194" s="4" t="s">
+      <c r="F198" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="G194" s="4" t="s">
+      <c r="G198" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="H194" s="5" t="s">
+      <c r="H198" s="5" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A195" s="6" t="s">
+    <row r="199" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A199" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B195" s="7">
-        <v>10408</v>
-      </c>
-      <c r="C195" s="7">
-        <v>100</v>
-      </c>
-      <c r="D195" s="7">
+      <c r="B199" s="7">
+        <v>10690</v>
+      </c>
+      <c r="C199" s="7">
+        <v>102</v>
+      </c>
+      <c r="D199" s="7">
         <v>2</v>
       </c>
-      <c r="E195" s="7">
+      <c r="E199" s="7">
         <v>0</v>
       </c>
-      <c r="F195" s="7">
-        <v>88</v>
-      </c>
-      <c r="G195" s="7">
+      <c r="F199" s="7">
+        <v>90</v>
+      </c>
+      <c r="G199" s="7">
         <v>2</v>
       </c>
-      <c r="H195" s="8">
+      <c r="H199" s="8">
         <v>0</v>
       </c>
     </row>
@@ -6896,13 +7024,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{37DAEFFE-2516-4BA9-8EF3-4546F3550B69}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0F09A8C0-E365-4AD8-8961-1F7F5D36A416}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24B95492-2BE7-4244-8E63-AC25B1B4B114}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0A9048EA-A18E-4F43-AA47-F2899FB879BD}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{743DEB1B-F207-49D5-8C91-A5E6CD647815}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B0B53D9E-C0A7-4E3B-9A67-B096899B6DF0}"/>
 </file>
--- a/data/warn-scraper/cache/ca/warn_report1.xlsx
+++ b/data/warn-scraper/cache/ca/warn_report1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jochoa2\Desktop\Conditional Approvals\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jochoa2\Documents\Web Testing\DAT VR Results\RID1547-WARN_Report1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA798565-1607-4B19-AABA-1A82BD4F401A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59E0E291-61AF-4899-924B-632A0ED84E0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
   <sheets>
     <sheet name="Index" sheetId="3" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="823" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="851" uniqueCount="363">
   <si>
     <t>County/Parish</t>
   </si>
@@ -1122,41 +1122,6 @@
   </si>
   <si>
     <t>990 West 190th Street  Torrance CA 90502</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">WARN REPORT - </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>07/01/23 to 09/06/23</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="16"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A detailed WARN summary by county and filtered according to received date. Table Spans cells A2 through H202.</t>
-    </r>
   </si>
   <si>
     <r>
@@ -1185,6 +1150,80 @@
   <si>
     <t>This worksheet contains 3 sheets. The introductory page, WARN Report Summary, and Detailed WARN Report. The second sheet provides an overview of the report according to layoff/closure types and related quantitative data. The third sheet displays a detailed summary report of affected companies by county. This Daily WARN Report is updated every Tuesday and Thursday. Hyperlinks to the other 2 sheets can be found below in cell A3-A4.</t>
   </si>
+  <si>
+    <t>Visalia Citrus Packing Group, Inc.</t>
+  </si>
+  <si>
+    <t>12143 Avenue 456 Orange Cove Packing Facility Orange Cove CA 93646</t>
+  </si>
+  <si>
+    <t>Dabico Airport Solutions, Inc.</t>
+  </si>
+  <si>
+    <t>5665 Corporate Avenue  Cypress CA 90630</t>
+  </si>
+  <si>
+    <t>19743 Avenue 344 Woodlake Packing Facility Woodlake CA 93286</t>
+  </si>
+  <si>
+    <t>Mercy Medical Transportation, Inc.</t>
+  </si>
+  <si>
+    <t>1338 D Street  Ramona CA 92065</t>
+  </si>
+  <si>
+    <t>Planet Labs PBC</t>
+  </si>
+  <si>
+    <t>645 Harrison Street, 4th Floor  San Francisco CA 94107</t>
+  </si>
+  <si>
+    <t>Johns Manville</t>
+  </si>
+  <si>
+    <t>5916 County Road 49  Willows CA 95988</t>
+  </si>
+  <si>
+    <t>ContextLogic Inc.</t>
+  </si>
+  <si>
+    <t>One Sansome Street, 33rd Floor  San Francisco CA 94104</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">WARN REPORT - </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>07/01/23 to 09/11/23</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A detailed WARN summary by county and filtered according to received date. Table Spans cells A2 through H209.</t>
+    </r>
+  </si>
 </sst>
 </file>
 
@@ -1206,12 +1245,6 @@
     <font>
       <b/>
       <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="8"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -1279,6 +1312,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -1398,71 +1437,71 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="3"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="3"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1486,13 +1525,12 @@
         <sz val="8"/>
         <color rgb="FF000000"/>
         <name val="Arial"/>
-        <family val="2"/>
         <scheme val="none"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFF0F0F0"/>
+          <bgColor rgb="FFF0F0F0"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -1527,14 +1565,13 @@
         <sz val="8"/>
         <color rgb="FF000000"/>
         <name val="Arial"/>
-        <family val="2"/>
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="165" formatCode="[$-10436]#,##0;\(#,##0\)"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFF0F0F0"/>
+          <bgColor rgb="FFF0F0F0"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -1569,13 +1606,12 @@
         <sz val="8"/>
         <color rgb="FF000000"/>
         <name val="Arial"/>
-        <family val="2"/>
         <scheme val="none"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFF0F0F0"/>
+          <bgColor rgb="FFF0F0F0"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -1610,13 +1646,12 @@
         <sz val="8"/>
         <color rgb="FF000000"/>
         <name val="Arial"/>
-        <family val="2"/>
         <scheme val="none"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFF0F0F0"/>
+          <bgColor rgb="FFF0F0F0"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -1651,14 +1686,13 @@
         <sz val="8"/>
         <color rgb="FF000000"/>
         <name val="Arial"/>
-        <family val="2"/>
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="164" formatCode="[$-10409]mm/dd/yyyy"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFF0F0F0"/>
+          <bgColor rgb="FFF0F0F0"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -1693,14 +1727,13 @@
         <sz val="8"/>
         <color rgb="FF000000"/>
         <name val="Arial"/>
-        <family val="2"/>
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="164" formatCode="[$-10409]mm/dd/yyyy"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFF0F0F0"/>
+          <bgColor rgb="FFF0F0F0"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -1735,14 +1768,13 @@
         <sz val="8"/>
         <color rgb="FF000000"/>
         <name val="Arial"/>
-        <family val="2"/>
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="164" formatCode="[$-10409]mm/dd/yyyy"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFF0F0F0"/>
+          <bgColor rgb="FFF0F0F0"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -1777,13 +1809,12 @@
         <sz val="8"/>
         <color rgb="FF000000"/>
         <name val="Arial"/>
-        <family val="2"/>
         <scheme val="none"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFF0F0F0"/>
+          <bgColor rgb="FFF0F0F0"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -1975,8 +2006,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:H202" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
-  <autoFilter ref="A2:H202" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:H209" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
+  <autoFilter ref="A2:H209" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -2304,22 +2335,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="105" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
-        <v>349</v>
+      <c r="A1" s="2" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="21" x14ac:dyDescent="0.35">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="9" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="10" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="10" t="s">
         <v>154</v>
       </c>
     </row>
@@ -2342,83 +2373,83 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
-        <v>348</v>
+      <c r="A1" s="2" t="s">
+        <v>347</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="5" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="B3" s="16">
+      <c r="B3" s="6">
         <f>SUM('Detailed WARN Report '!G:G)</f>
-        <v>10799</v>
+        <v>11238</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="16">
+      <c r="B4" s="6">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Permanent")</f>
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="16">
+      <c r="B5" s="6">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Temporary")</f>
         <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="16">
+      <c r="B6" s="6">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Not Identified")</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="16">
+      <c r="B7" s="6">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Permanent")</f>
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="16">
+      <c r="B8" s="6">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Temporary")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="16">
+      <c r="B9" s="6">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Not Identified")</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="11" type="noConversion"/>
+  <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
@@ -2428,5251 +2459,5433 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:H202"/>
+  <dimension ref="A1:H209"/>
   <sheetFormatPr defaultColWidth="46" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="4" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="54.85546875" style="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="54.85546875" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="49" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="52.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="117" x14ac:dyDescent="0.25">
-      <c r="A1" s="18" t="s">
-        <v>347</v>
-      </c>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-    </row>
-    <row r="2" spans="1:8" s="1" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="21" t="s">
+      <c r="A1" s="8" t="s">
+        <v>362</v>
+      </c>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+    </row>
+    <row r="2" spans="1:8" s="1" customFormat="1" ht="24.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="21" t="s">
+      <c r="D2" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E2" s="21" t="s">
+      <c r="E2" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="21" t="s">
+      <c r="F2" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="21" t="s">
+      <c r="G2" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="22" t="s">
+      <c r="H2" s="12" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="14">
         <v>45041</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="14">
         <v>45110</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="14">
         <v>45171</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="F3" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" s="4">
+      <c r="F3" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="16">
         <v>29</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="17" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="19">
         <v>45041</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="19">
         <v>45110</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="19">
         <v>45171</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="F4" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4" s="6">
+      <c r="F4" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="21">
         <v>31</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="22" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="14">
         <v>45041</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="14">
         <v>45110</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="14">
         <v>45171</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="F5" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" s="4">
+      <c r="F5" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="16">
         <v>47</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="H5" s="17" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="19">
         <v>45041</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="19">
         <v>45110</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="19">
         <v>45171</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="F6" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G6" s="6">
+      <c r="F6" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="21">
         <v>29</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="22" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="14">
         <v>45041</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="14">
         <v>45110</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="14">
         <v>45171</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E7" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="F7" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G7" s="4">
+      <c r="F7" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7" s="16">
         <v>35</v>
       </c>
-      <c r="H7" s="5" t="s">
+      <c r="H7" s="17" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="19">
         <v>45041</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="19">
         <v>45110</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="19">
         <v>45171</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="E8" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="F8" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G8" s="6">
+      <c r="F8" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" s="21">
         <v>35</v>
       </c>
-      <c r="H8" s="7" t="s">
+      <c r="H8" s="22" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" s="14">
         <v>45041</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="14">
         <v>45112</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="14">
         <v>45171</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="E9" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="F9" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G9" s="4">
+      <c r="F9" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G9" s="16">
         <v>27</v>
       </c>
-      <c r="H9" s="5" t="s">
+      <c r="H9" s="17" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10" s="19">
         <v>45084</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="19">
         <v>45112</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="19">
         <v>45145</v>
       </c>
-      <c r="E10" s="11" t="s">
+      <c r="E10" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="F10" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G10" s="6">
+      <c r="F10" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10" s="21">
         <v>1</v>
       </c>
-      <c r="H10" s="7" t="s">
+      <c r="H10" s="22" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="14">
         <v>45041</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11" s="14">
         <v>45112</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11" s="14">
         <v>45171</v>
       </c>
-      <c r="E11" s="9" t="s">
+      <c r="E11" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="F11" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G11" s="4">
+      <c r="F11" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G11" s="16">
         <v>18</v>
       </c>
-      <c r="H11" s="5" t="s">
+      <c r="H11" s="17" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B12" s="19">
         <v>45041</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="19">
         <v>45112</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="19">
         <v>45171</v>
       </c>
-      <c r="E12" s="11" t="s">
+      <c r="E12" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="F12" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G12" s="6">
+      <c r="F12" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G12" s="21">
         <v>27</v>
       </c>
-      <c r="H12" s="7" t="s">
+      <c r="H12" s="22" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13" s="14">
         <v>45041</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="14">
         <v>45112</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="14">
         <v>45171</v>
       </c>
-      <c r="E13" s="9" t="s">
+      <c r="E13" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="F13" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G13" s="4">
+      <c r="F13" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G13" s="16">
         <v>34</v>
       </c>
-      <c r="H13" s="5" t="s">
+      <c r="H13" s="17" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="10" t="s">
+      <c r="A14" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B14" s="19">
         <v>45041</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="19">
         <v>45112</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="19">
         <v>45171</v>
       </c>
-      <c r="E14" s="11" t="s">
+      <c r="E14" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="F14" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G14" s="6">
+      <c r="F14" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G14" s="21">
         <v>46</v>
       </c>
-      <c r="H14" s="7" t="s">
+      <c r="H14" s="22" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B15" s="14">
         <v>45041</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C15" s="14">
         <v>45112</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D15" s="14">
         <v>45171</v>
       </c>
-      <c r="E15" s="9" t="s">
+      <c r="E15" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="F15" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G15" s="4">
+      <c r="F15" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G15" s="16">
         <v>38</v>
       </c>
-      <c r="H15" s="5" t="s">
+      <c r="H15" s="17" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="B16" s="3">
+      <c r="B16" s="19">
         <v>45041</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16" s="19">
         <v>45112</v>
       </c>
-      <c r="D16" s="3">
+      <c r="D16" s="19">
         <v>45171</v>
       </c>
-      <c r="E16" s="11" t="s">
+      <c r="E16" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="F16" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G16" s="6">
+      <c r="F16" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G16" s="21">
         <v>40</v>
       </c>
-      <c r="H16" s="7" t="s">
+      <c r="H16" s="22" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B17" s="14">
         <v>45084</v>
       </c>
-      <c r="C17" s="2">
+      <c r="C17" s="14">
         <v>45112</v>
       </c>
-      <c r="D17" s="2">
+      <c r="D17" s="14">
         <v>45145</v>
       </c>
-      <c r="E17" s="9" t="s">
+      <c r="E17" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="F17" s="9" t="s">
+      <c r="F17" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="G17" s="4">
+      <c r="G17" s="16">
         <v>75</v>
       </c>
-      <c r="H17" s="5" t="s">
+      <c r="H17" s="17" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="10" t="s">
+      <c r="A18" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="B18" s="3">
+      <c r="B18" s="19">
         <v>45084</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" s="19">
         <v>45113</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="19">
         <v>45142</v>
       </c>
-      <c r="E18" s="11" t="s">
+      <c r="E18" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="F18" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G18" s="6">
+      <c r="F18" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G18" s="21">
         <v>68</v>
       </c>
-      <c r="H18" s="7" t="s">
+      <c r="H18" s="22" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="B19" s="2">
+      <c r="B19" s="14">
         <v>45083</v>
       </c>
-      <c r="C19" s="2">
+      <c r="C19" s="14">
         <v>45113</v>
       </c>
-      <c r="D19" s="2">
+      <c r="D19" s="14">
         <v>45083</v>
       </c>
-      <c r="E19" s="9" t="s">
+      <c r="E19" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="F19" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G19" s="4">
+      <c r="F19" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G19" s="16">
         <v>60</v>
       </c>
-      <c r="H19" s="5" t="s">
+      <c r="H19" s="17" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="10" t="s">
+      <c r="A20" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="B20" s="3">
+      <c r="B20" s="19">
         <v>45084</v>
       </c>
-      <c r="C20" s="3">
+      <c r="C20" s="19">
         <v>45113</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="19">
         <v>45152</v>
       </c>
-      <c r="E20" s="11" t="s">
+      <c r="E20" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="F20" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G20" s="6">
+      <c r="F20" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G20" s="21">
         <v>57</v>
       </c>
-      <c r="H20" s="7" t="s">
+      <c r="H20" s="22" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="B21" s="2">
+      <c r="B21" s="14">
         <v>45084</v>
       </c>
-      <c r="C21" s="2">
+      <c r="C21" s="14">
         <v>45113</v>
       </c>
-      <c r="D21" s="2">
+      <c r="D21" s="14">
         <v>45152</v>
       </c>
-      <c r="E21" s="9" t="s">
+      <c r="E21" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="F21" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G21" s="4">
-        <v>15</v>
-      </c>
-      <c r="H21" s="5" t="s">
+      <c r="F21" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G21" s="16">
+        <v>15</v>
+      </c>
+      <c r="H21" s="17" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="10" t="s">
+      <c r="A22" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="B22" s="3">
+      <c r="B22" s="19">
         <v>45086</v>
       </c>
-      <c r="C22" s="3">
+      <c r="C22" s="19">
         <v>45114</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="19">
         <v>45153</v>
       </c>
-      <c r="E22" s="11" t="s">
+      <c r="E22" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="F22" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G22" s="6">
+      <c r="F22" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G22" s="21">
         <v>69</v>
       </c>
-      <c r="H22" s="7" t="s">
+      <c r="H22" s="22" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="B23" s="2">
+      <c r="B23" s="14">
         <v>45082</v>
       </c>
-      <c r="C23" s="2">
+      <c r="C23" s="14">
         <v>45114</v>
       </c>
-      <c r="D23" s="2">
+      <c r="D23" s="14">
         <v>45142</v>
       </c>
-      <c r="E23" s="9" t="s">
+      <c r="E23" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="F23" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G23" s="4">
+      <c r="F23" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G23" s="16">
         <v>2</v>
       </c>
-      <c r="H23" s="5" t="s">
+      <c r="H23" s="17" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="10" t="s">
+      <c r="A24" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="B24" s="3">
+      <c r="B24" s="19">
         <v>45114</v>
       </c>
-      <c r="C24" s="3">
+      <c r="C24" s="19">
         <v>45117</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24" s="19">
         <v>45177</v>
       </c>
-      <c r="E24" s="11" t="s">
+      <c r="E24" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="F24" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G24" s="6">
+      <c r="F24" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G24" s="21">
         <v>4</v>
       </c>
-      <c r="H24" s="7" t="s">
+      <c r="H24" s="22" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="B25" s="2">
+      <c r="B25" s="14">
         <v>45089</v>
       </c>
-      <c r="C25" s="2">
+      <c r="C25" s="14">
         <v>45117</v>
       </c>
-      <c r="D25" s="2">
+      <c r="D25" s="14">
         <v>45150</v>
       </c>
-      <c r="E25" s="9" t="s">
+      <c r="E25" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="F25" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G25" s="4">
+      <c r="F25" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G25" s="16">
         <v>107</v>
       </c>
-      <c r="H25" s="5" t="s">
+      <c r="H25" s="17" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="10" t="s">
+      <c r="A26" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="B26" s="3">
+      <c r="B26" s="19">
         <v>45084</v>
       </c>
-      <c r="C26" s="3">
+      <c r="C26" s="19">
         <v>45117</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="19">
         <v>45085</v>
       </c>
-      <c r="E26" s="11" t="s">
+      <c r="E26" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="F26" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G26" s="6">
+      <c r="F26" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G26" s="21">
         <v>79</v>
       </c>
-      <c r="H26" s="7" t="s">
+      <c r="H26" s="22" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="8" t="s">
+      <c r="A27" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="B27" s="2">
+      <c r="B27" s="14">
         <v>45090</v>
       </c>
-      <c r="C27" s="2">
+      <c r="C27" s="14">
         <v>45117</v>
       </c>
-      <c r="D27" s="2">
+      <c r="D27" s="14">
         <v>45107</v>
       </c>
-      <c r="E27" s="9" t="s">
+      <c r="E27" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="F27" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G27" s="4">
+      <c r="F27" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G27" s="16">
         <v>6</v>
       </c>
-      <c r="H27" s="5" t="s">
+      <c r="H27" s="17" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="10" t="s">
+      <c r="A28" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="B28" s="3">
+      <c r="B28" s="19">
         <v>45089</v>
       </c>
-      <c r="C28" s="3">
+      <c r="C28" s="19">
         <v>45117</v>
       </c>
-      <c r="D28" s="3">
+      <c r="D28" s="19">
         <v>45136</v>
       </c>
-      <c r="E28" s="11" t="s">
+      <c r="E28" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="F28" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G28" s="6">
+      <c r="F28" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G28" s="21">
         <v>5</v>
       </c>
-      <c r="H28" s="7" t="s">
+      <c r="H28" s="22" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="8" t="s">
+      <c r="A29" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="B29" s="2">
+      <c r="B29" s="14">
         <v>45082</v>
       </c>
-      <c r="C29" s="2">
+      <c r="C29" s="14">
         <v>45118</v>
       </c>
-      <c r="D29" s="2">
+      <c r="D29" s="14">
         <v>45077</v>
       </c>
-      <c r="E29" s="9" t="s">
+      <c r="E29" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="F29" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G29" s="4">
+      <c r="F29" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G29" s="16">
         <v>78</v>
       </c>
-      <c r="H29" s="5" t="s">
+      <c r="H29" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="10" t="s">
+      <c r="A30" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="B30" s="3">
+      <c r="B30" s="19">
         <v>45092</v>
       </c>
-      <c r="C30" s="3">
+      <c r="C30" s="19">
         <v>45118</v>
       </c>
-      <c r="D30" s="3">
+      <c r="D30" s="19">
         <v>45170</v>
       </c>
-      <c r="E30" s="11" t="s">
+      <c r="E30" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="F30" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G30" s="6">
+      <c r="F30" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G30" s="21">
         <v>3</v>
       </c>
-      <c r="H30" s="7" t="s">
+      <c r="H30" s="22" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="8" t="s">
+      <c r="A31" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="B31" s="2">
+      <c r="B31" s="14">
         <v>45092</v>
       </c>
-      <c r="C31" s="2">
+      <c r="C31" s="14">
         <v>45118</v>
       </c>
-      <c r="D31" s="2">
+      <c r="D31" s="14">
         <v>45261</v>
       </c>
-      <c r="E31" s="9" t="s">
+      <c r="E31" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="F31" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G31" s="4">
+      <c r="F31" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G31" s="16">
         <v>3</v>
       </c>
-      <c r="H31" s="5" t="s">
+      <c r="H31" s="17" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="10" t="s">
+      <c r="A32" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="B32" s="3">
+      <c r="B32" s="19">
         <v>45092</v>
       </c>
-      <c r="C32" s="3">
+      <c r="C32" s="19">
         <v>45118</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="19">
         <v>45291</v>
       </c>
-      <c r="E32" s="11" t="s">
+      <c r="E32" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="F32" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G32" s="6">
+      <c r="F32" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G32" s="21">
         <v>2</v>
       </c>
-      <c r="H32" s="7" t="s">
+      <c r="H32" s="22" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="8" t="s">
+      <c r="A33" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="B33" s="2">
+      <c r="B33" s="14">
         <v>45092</v>
       </c>
-      <c r="C33" s="2">
+      <c r="C33" s="14">
         <v>45118</v>
       </c>
-      <c r="D33" s="2">
+      <c r="D33" s="14">
         <v>45153</v>
       </c>
-      <c r="E33" s="9" t="s">
+      <c r="E33" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="F33" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G33" s="4">
+      <c r="F33" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G33" s="16">
         <v>98</v>
       </c>
-      <c r="H33" s="5" t="s">
+      <c r="H33" s="17" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="10" t="s">
+      <c r="A34" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="B34" s="3">
+      <c r="B34" s="19">
         <v>45092</v>
       </c>
-      <c r="C34" s="3">
+      <c r="C34" s="19">
         <v>45118</v>
       </c>
-      <c r="D34" s="3">
+      <c r="D34" s="19">
         <v>45154</v>
       </c>
-      <c r="E34" s="11" t="s">
+      <c r="E34" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="F34" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G34" s="6">
+      <c r="F34" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G34" s="21">
         <v>90</v>
       </c>
-      <c r="H34" s="7" t="s">
+      <c r="H34" s="22" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="8" t="s">
+      <c r="A35" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="B35" s="2">
+      <c r="B35" s="14">
         <v>45093</v>
       </c>
-      <c r="C35" s="2">
+      <c r="C35" s="14">
         <v>45118</v>
       </c>
-      <c r="D35" s="2">
+      <c r="D35" s="14">
         <v>45154</v>
       </c>
-      <c r="E35" s="9" t="s">
+      <c r="E35" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="F35" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G35" s="4">
+      <c r="F35" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G35" s="16">
         <v>49</v>
       </c>
-      <c r="H35" s="5" t="s">
+      <c r="H35" s="17" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="10" t="s">
+      <c r="A36" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="B36" s="3">
+      <c r="B36" s="19">
         <v>45093</v>
       </c>
-      <c r="C36" s="3">
+      <c r="C36" s="19">
         <v>45118</v>
       </c>
-      <c r="D36" s="3">
+      <c r="D36" s="19">
         <v>45223</v>
       </c>
-      <c r="E36" s="11" t="s">
+      <c r="E36" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="F36" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G36" s="6">
+      <c r="F36" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G36" s="21">
         <v>21</v>
       </c>
-      <c r="H36" s="7" t="s">
+      <c r="H36" s="22" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="8" t="s">
+      <c r="A37" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="B37" s="2">
+      <c r="B37" s="14">
         <v>45090</v>
       </c>
-      <c r="C37" s="2">
+      <c r="C37" s="14">
         <v>45119</v>
       </c>
-      <c r="D37" s="2">
+      <c r="D37" s="14">
         <v>45153</v>
       </c>
-      <c r="E37" s="9" t="s">
+      <c r="E37" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="F37" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G37" s="4">
+      <c r="F37" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G37" s="16">
         <v>13</v>
       </c>
-      <c r="H37" s="5" t="s">
+      <c r="H37" s="17" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="10" t="s">
+      <c r="A38" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="B38" s="3">
+      <c r="B38" s="19">
         <v>45090</v>
       </c>
-      <c r="C38" s="3">
+      <c r="C38" s="19">
         <v>45119</v>
       </c>
-      <c r="D38" s="3">
+      <c r="D38" s="19">
         <v>45151</v>
       </c>
-      <c r="E38" s="11" t="s">
+      <c r="E38" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="F38" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G38" s="6">
+      <c r="F38" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G38" s="21">
         <v>185</v>
       </c>
-      <c r="H38" s="7" t="s">
+      <c r="H38" s="22" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="8" t="s">
+      <c r="A39" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="B39" s="2">
+      <c r="B39" s="14">
         <v>45098</v>
       </c>
-      <c r="C39" s="2">
+      <c r="C39" s="14">
         <v>45120</v>
       </c>
-      <c r="D39" s="2">
+      <c r="D39" s="14">
         <v>45128</v>
       </c>
-      <c r="E39" s="9" t="s">
+      <c r="E39" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="F39" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G39" s="4">
+      <c r="F39" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G39" s="16">
         <v>1</v>
       </c>
-      <c r="H39" s="5" t="s">
+      <c r="H39" s="17" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="10" t="s">
+      <c r="A40" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="B40" s="3">
+      <c r="B40" s="19">
         <v>45106</v>
       </c>
-      <c r="C40" s="3">
+      <c r="C40" s="19">
         <v>45120</v>
       </c>
-      <c r="D40" s="3">
+      <c r="D40" s="19">
         <v>45170</v>
       </c>
-      <c r="E40" s="11" t="s">
+      <c r="E40" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="F40" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G40" s="6">
+      <c r="F40" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G40" s="21">
         <v>23</v>
       </c>
-      <c r="H40" s="7" t="s">
+      <c r="H40" s="22" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="8" t="s">
+      <c r="A41" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="B41" s="2">
+      <c r="B41" s="14">
         <v>45098</v>
       </c>
-      <c r="C41" s="2">
+      <c r="C41" s="14">
         <v>45120</v>
       </c>
-      <c r="D41" s="2">
+      <c r="D41" s="14">
         <v>45128</v>
       </c>
-      <c r="E41" s="9" t="s">
+      <c r="E41" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="F41" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G41" s="4">
+      <c r="F41" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G41" s="16">
         <v>71</v>
       </c>
-      <c r="H41" s="5" t="s">
+      <c r="H41" s="17" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="10" t="s">
+      <c r="A42" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="B42" s="3">
+      <c r="B42" s="19">
         <v>45096</v>
       </c>
-      <c r="C42" s="3">
+      <c r="C42" s="19">
         <v>45120</v>
       </c>
-      <c r="D42" s="3">
+      <c r="D42" s="19">
         <v>45157</v>
       </c>
-      <c r="E42" s="11" t="s">
+      <c r="E42" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="F42" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G42" s="6">
+      <c r="F42" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G42" s="21">
         <v>63</v>
       </c>
-      <c r="H42" s="7" t="s">
+      <c r="H42" s="22" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="8" t="s">
+      <c r="A43" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="B43" s="2">
+      <c r="B43" s="14">
         <v>45098</v>
       </c>
-      <c r="C43" s="2">
+      <c r="C43" s="14">
         <v>45120</v>
       </c>
-      <c r="D43" s="2">
+      <c r="D43" s="14">
         <v>45128</v>
       </c>
-      <c r="E43" s="9" t="s">
+      <c r="E43" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="F43" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G43" s="4">
+      <c r="F43" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G43" s="16">
         <v>64</v>
       </c>
-      <c r="H43" s="5" t="s">
+      <c r="H43" s="17" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="10" t="s">
+      <c r="A44" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="B44" s="3">
+      <c r="B44" s="19">
         <v>45098</v>
       </c>
-      <c r="C44" s="3">
+      <c r="C44" s="19">
         <v>45120</v>
       </c>
-      <c r="D44" s="3">
+      <c r="D44" s="19">
         <v>45128</v>
       </c>
-      <c r="E44" s="11" t="s">
+      <c r="E44" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="F44" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G44" s="6">
+      <c r="F44" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G44" s="21">
         <v>14</v>
       </c>
-      <c r="H44" s="7" t="s">
+      <c r="H44" s="22" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="8" t="s">
+      <c r="A45" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="B45" s="2">
+      <c r="B45" s="14">
         <v>45093</v>
       </c>
-      <c r="C45" s="2">
+      <c r="C45" s="14">
         <v>45120</v>
       </c>
-      <c r="D45" s="2">
+      <c r="D45" s="14">
         <v>45163</v>
       </c>
-      <c r="E45" s="9" t="s">
+      <c r="E45" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="F45" s="9" t="s">
+      <c r="F45" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="G45" s="4">
+      <c r="G45" s="16">
         <v>53</v>
       </c>
-      <c r="H45" s="5" t="s">
+      <c r="H45" s="17" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="10" t="s">
+      <c r="A46" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="B46" s="3">
+      <c r="B46" s="19">
         <v>45089</v>
       </c>
-      <c r="C46" s="3">
+      <c r="C46" s="19">
         <v>45124</v>
       </c>
-      <c r="D46" s="3">
+      <c r="D46" s="19">
         <v>45149</v>
       </c>
-      <c r="E46" s="11" t="s">
+      <c r="E46" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="F46" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G46" s="6">
+      <c r="F46" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G46" s="21">
         <v>52</v>
       </c>
-      <c r="H46" s="7" t="s">
+      <c r="H46" s="22" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" s="8" t="s">
+      <c r="A47" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="B47" s="2">
+      <c r="B47" s="14">
         <v>45077</v>
       </c>
-      <c r="C47" s="2">
+      <c r="C47" s="14">
         <v>45124</v>
       </c>
-      <c r="D47" s="2">
+      <c r="D47" s="14">
         <v>45077</v>
       </c>
-      <c r="E47" s="9" t="s">
+      <c r="E47" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F47" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G47" s="4">
+      <c r="F47" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G47" s="16">
         <v>2</v>
       </c>
-      <c r="H47" s="5" t="s">
+      <c r="H47" s="17" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="10" t="s">
+      <c r="A48" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="B48" s="3">
+      <c r="B48" s="19">
         <v>45085</v>
       </c>
-      <c r="C48" s="3">
+      <c r="C48" s="19">
         <v>45124</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D48" s="19">
         <v>45142</v>
       </c>
-      <c r="E48" s="11" t="s">
+      <c r="E48" s="20" t="s">
         <v>105</v>
       </c>
-      <c r="F48" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G48" s="6">
+      <c r="F48" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G48" s="21">
         <v>68</v>
       </c>
-      <c r="H48" s="7" t="s">
+      <c r="H48" s="22" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="8" t="s">
+      <c r="A49" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="B49" s="2">
+      <c r="B49" s="14">
         <v>45090</v>
       </c>
-      <c r="C49" s="2">
+      <c r="C49" s="14">
         <v>45124</v>
       </c>
-      <c r="D49" s="2">
+      <c r="D49" s="14">
         <v>45170</v>
       </c>
-      <c r="E49" s="9" t="s">
+      <c r="E49" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="F49" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G49" s="4">
+      <c r="F49" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G49" s="16">
         <v>4</v>
       </c>
-      <c r="H49" s="5" t="s">
+      <c r="H49" s="17" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="10" t="s">
+      <c r="A50" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="B50" s="3">
+      <c r="B50" s="19">
         <v>45077</v>
       </c>
-      <c r="C50" s="3">
+      <c r="C50" s="19">
         <v>45124</v>
       </c>
-      <c r="D50" s="3">
+      <c r="D50" s="19">
         <v>45077</v>
       </c>
-      <c r="E50" s="11" t="s">
+      <c r="E50" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="F50" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G50" s="6">
+      <c r="F50" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G50" s="21">
         <v>31</v>
       </c>
-      <c r="H50" s="7" t="s">
+      <c r="H50" s="22" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="8" t="s">
+      <c r="A51" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="B51" s="2">
+      <c r="B51" s="14">
         <v>45077</v>
       </c>
-      <c r="C51" s="2">
+      <c r="C51" s="14">
         <v>45124</v>
       </c>
-      <c r="D51" s="2">
+      <c r="D51" s="14">
         <v>45077</v>
       </c>
-      <c r="E51" s="9" t="s">
+      <c r="E51" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F51" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G51" s="4">
+      <c r="F51" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G51" s="16">
         <v>1</v>
       </c>
-      <c r="H51" s="5" t="s">
+      <c r="H51" s="17" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="10" t="s">
+      <c r="A52" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="B52" s="3">
+      <c r="B52" s="19">
         <v>45097</v>
       </c>
-      <c r="C52" s="3">
+      <c r="C52" s="19">
         <v>45126</v>
       </c>
-      <c r="D52" s="3">
+      <c r="D52" s="19">
         <v>45159</v>
       </c>
-      <c r="E52" s="11" t="s">
+      <c r="E52" s="20" t="s">
         <v>111</v>
       </c>
-      <c r="F52" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G52" s="6">
+      <c r="F52" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G52" s="21">
         <v>96</v>
       </c>
-      <c r="H52" s="7" t="s">
+      <c r="H52" s="22" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" s="8" t="s">
+      <c r="A53" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="B53" s="2">
+      <c r="B53" s="14">
         <v>45097</v>
       </c>
-      <c r="C53" s="2">
+      <c r="C53" s="14">
         <v>45126</v>
       </c>
-      <c r="D53" s="2">
+      <c r="D53" s="14">
         <v>45159</v>
       </c>
-      <c r="E53" s="9" t="s">
+      <c r="E53" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="F53" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G53" s="4">
+      <c r="F53" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G53" s="16">
         <v>99</v>
       </c>
-      <c r="H53" s="5" t="s">
+      <c r="H53" s="17" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="10" t="s">
+      <c r="A54" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="B54" s="3">
+      <c r="B54" s="19">
         <v>45119</v>
       </c>
-      <c r="C54" s="3">
+      <c r="C54" s="19">
         <v>45126</v>
       </c>
-      <c r="D54" s="3">
+      <c r="D54" s="19">
         <v>45139</v>
       </c>
-      <c r="E54" s="11" t="s">
+      <c r="E54" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="F54" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G54" s="6">
+      <c r="F54" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G54" s="21">
         <v>55</v>
       </c>
-      <c r="H54" s="7" t="s">
+      <c r="H54" s="22" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" s="8" t="s">
+      <c r="A55" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="B55" s="2">
+      <c r="B55" s="14">
         <v>45097</v>
       </c>
-      <c r="C55" s="2">
+      <c r="C55" s="14">
         <v>45127</v>
       </c>
-      <c r="D55" s="2">
+      <c r="D55" s="14">
         <v>45107</v>
       </c>
-      <c r="E55" s="9" t="s">
+      <c r="E55" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="F55" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G55" s="4">
+      <c r="F55" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G55" s="16">
         <v>3</v>
       </c>
-      <c r="H55" s="5" t="s">
+      <c r="H55" s="17" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" s="10" t="s">
+      <c r="A56" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="B56" s="3">
+      <c r="B56" s="19">
         <v>45085</v>
       </c>
-      <c r="C56" s="3">
+      <c r="C56" s="19">
         <v>45127</v>
       </c>
-      <c r="D56" s="3">
+      <c r="D56" s="19">
         <v>45169</v>
       </c>
-      <c r="E56" s="11" t="s">
+      <c r="E56" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="F56" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G56" s="6">
+      <c r="F56" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G56" s="21">
         <v>136</v>
       </c>
-      <c r="H56" s="7" t="s">
+      <c r="H56" s="22" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="8" t="s">
+      <c r="A57" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="B57" s="2">
+      <c r="B57" s="14">
         <v>45098</v>
       </c>
-      <c r="C57" s="2">
+      <c r="C57" s="14">
         <v>45127</v>
       </c>
-      <c r="D57" s="2">
+      <c r="D57" s="14">
         <v>45105</v>
       </c>
-      <c r="E57" s="9" t="s">
+      <c r="E57" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="F57" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G57" s="4">
+      <c r="F57" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G57" s="16">
         <v>14</v>
       </c>
-      <c r="H57" s="5" t="s">
+      <c r="H57" s="17" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" s="10" t="s">
+      <c r="A58" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="B58" s="3">
+      <c r="B58" s="19">
         <v>45098</v>
       </c>
-      <c r="C58" s="3">
+      <c r="C58" s="19">
         <v>45127</v>
       </c>
-      <c r="D58" s="3">
+      <c r="D58" s="19">
         <v>45128</v>
       </c>
-      <c r="E58" s="11" t="s">
+      <c r="E58" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="F58" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G58" s="6">
+      <c r="F58" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G58" s="21">
         <v>1</v>
       </c>
-      <c r="H58" s="7" t="s">
+      <c r="H58" s="22" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="8" t="s">
+      <c r="A59" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="B59" s="2">
+      <c r="B59" s="14">
         <v>45098</v>
       </c>
-      <c r="C59" s="2">
+      <c r="C59" s="14">
         <v>45127</v>
       </c>
-      <c r="D59" s="2">
+      <c r="D59" s="14">
         <v>45159</v>
       </c>
-      <c r="E59" s="9" t="s">
+      <c r="E59" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="F59" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G59" s="4">
+      <c r="F59" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G59" s="16">
         <v>100</v>
       </c>
-      <c r="H59" s="5" t="s">
+      <c r="H59" s="17" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="10" t="s">
+      <c r="A60" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="B60" s="3">
+      <c r="B60" s="19">
         <v>45098</v>
       </c>
-      <c r="C60" s="3">
+      <c r="C60" s="19">
         <v>45127</v>
       </c>
-      <c r="D60" s="3">
+      <c r="D60" s="19">
         <v>45190</v>
       </c>
-      <c r="E60" s="11" t="s">
+      <c r="E60" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="F60" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G60" s="6">
+      <c r="F60" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G60" s="21">
         <v>2</v>
       </c>
-      <c r="H60" s="7" t="s">
+      <c r="H60" s="22" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="8" t="s">
+      <c r="A61" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="B61" s="2">
+      <c r="B61" s="14">
         <v>45098</v>
       </c>
-      <c r="C61" s="2">
+      <c r="C61" s="14">
         <v>45127</v>
       </c>
-      <c r="D61" s="2">
+      <c r="D61" s="14">
         <v>45209</v>
       </c>
-      <c r="E61" s="9" t="s">
+      <c r="E61" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="F61" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G61" s="4">
+      <c r="F61" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G61" s="16">
         <v>2</v>
       </c>
-      <c r="H61" s="5" t="s">
+      <c r="H61" s="17" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" s="10" t="s">
+      <c r="A62" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="B62" s="3">
+      <c r="B62" s="19">
         <v>45098</v>
       </c>
-      <c r="C62" s="3">
+      <c r="C62" s="19">
         <v>45131</v>
       </c>
-      <c r="D62" s="3">
+      <c r="D62" s="19">
         <v>45086</v>
       </c>
-      <c r="E62" s="11" t="s">
+      <c r="E62" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="F62" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G62" s="6">
+      <c r="F62" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G62" s="21">
         <v>102</v>
       </c>
-      <c r="H62" s="7" t="s">
+      <c r="H62" s="22" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" s="8" t="s">
+      <c r="A63" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="B63" s="2">
+      <c r="B63" s="14">
         <v>45098</v>
       </c>
-      <c r="C63" s="2">
+      <c r="C63" s="14">
         <v>45131</v>
       </c>
-      <c r="D63" s="2">
+      <c r="D63" s="14">
         <v>45086</v>
       </c>
-      <c r="E63" s="9" t="s">
+      <c r="E63" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="F63" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G63" s="4">
+      <c r="F63" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G63" s="16">
         <v>13</v>
       </c>
-      <c r="H63" s="5" t="s">
+      <c r="H63" s="17" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" s="10" t="s">
+      <c r="A64" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="B64" s="3">
+      <c r="B64" s="19">
         <v>45098</v>
       </c>
-      <c r="C64" s="3">
+      <c r="C64" s="19">
         <v>45131</v>
       </c>
-      <c r="D64" s="3">
+      <c r="D64" s="19">
         <v>45086</v>
       </c>
-      <c r="E64" s="11" t="s">
+      <c r="E64" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="F64" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G64" s="6">
+      <c r="F64" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G64" s="21">
         <v>72</v>
       </c>
-      <c r="H64" s="7" t="s">
+      <c r="H64" s="22" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" s="8" t="s">
+      <c r="A65" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="B65" s="2">
+      <c r="B65" s="14">
         <v>45118</v>
       </c>
-      <c r="C65" s="2">
+      <c r="C65" s="14">
         <v>45131</v>
       </c>
-      <c r="D65" s="2">
+      <c r="D65" s="14">
         <v>45118</v>
       </c>
-      <c r="E65" s="9" t="s">
+      <c r="E65" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="F65" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G65" s="4">
+      <c r="F65" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G65" s="16">
         <v>32</v>
       </c>
-      <c r="H65" s="5" t="s">
+      <c r="H65" s="17" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" s="10" t="s">
+      <c r="A66" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="B66" s="3">
+      <c r="B66" s="19">
         <v>45118</v>
       </c>
-      <c r="C66" s="3">
+      <c r="C66" s="19">
         <v>45131</v>
       </c>
-      <c r="D66" s="3">
+      <c r="D66" s="19">
         <v>45118</v>
       </c>
-      <c r="E66" s="11" t="s">
+      <c r="E66" s="20" t="s">
         <v>126</v>
       </c>
-      <c r="F66" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G66" s="6">
+      <c r="F66" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G66" s="21">
         <v>10</v>
       </c>
-      <c r="H66" s="7" t="s">
+      <c r="H66" s="22" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" s="8" t="s">
+      <c r="A67" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="B67" s="2">
+      <c r="B67" s="14">
         <v>45118</v>
       </c>
-      <c r="C67" s="2">
+      <c r="C67" s="14">
         <v>45131</v>
       </c>
-      <c r="D67" s="2">
+      <c r="D67" s="14">
         <v>45118</v>
       </c>
-      <c r="E67" s="9" t="s">
+      <c r="E67" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="F67" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G67" s="4">
+      <c r="F67" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G67" s="16">
         <v>1</v>
       </c>
-      <c r="H67" s="5" t="s">
+      <c r="H67" s="17" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" s="10" t="s">
+      <c r="A68" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="B68" s="3">
+      <c r="B68" s="19">
         <v>45118</v>
       </c>
-      <c r="C68" s="3">
+      <c r="C68" s="19">
         <v>45131</v>
       </c>
-      <c r="D68" s="3">
+      <c r="D68" s="19">
         <v>45118</v>
       </c>
-      <c r="E68" s="11" t="s">
+      <c r="E68" s="20" t="s">
         <v>126</v>
       </c>
-      <c r="F68" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G68" s="6">
+      <c r="F68" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G68" s="21">
         <v>8</v>
       </c>
-      <c r="H68" s="7" t="s">
+      <c r="H68" s="22" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" s="8" t="s">
+      <c r="A69" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="B69" s="2">
+      <c r="B69" s="14">
         <v>45084</v>
       </c>
-      <c r="C69" s="2">
+      <c r="C69" s="14">
         <v>45132</v>
       </c>
-      <c r="D69" s="2">
+      <c r="D69" s="14">
         <v>45144</v>
       </c>
-      <c r="E69" s="9" t="s">
+      <c r="E69" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="F69" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G69" s="4">
+      <c r="F69" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G69" s="16">
         <v>54</v>
       </c>
-      <c r="H69" s="5" t="s">
+      <c r="H69" s="17" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A70" s="10" t="s">
+      <c r="A70" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="B70" s="3">
+      <c r="B70" s="19">
         <v>45084</v>
       </c>
-      <c r="C70" s="3">
+      <c r="C70" s="19">
         <v>45132</v>
       </c>
-      <c r="D70" s="3">
+      <c r="D70" s="19">
         <v>45144</v>
       </c>
-      <c r="E70" s="11" t="s">
+      <c r="E70" s="20" t="s">
         <v>133</v>
       </c>
-      <c r="F70" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G70" s="6">
+      <c r="F70" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G70" s="21">
         <v>35</v>
       </c>
-      <c r="H70" s="7" t="s">
+      <c r="H70" s="22" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A71" s="8" t="s">
+      <c r="A71" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="B71" s="2">
+      <c r="B71" s="14">
         <v>45065</v>
       </c>
-      <c r="C71" s="2">
+      <c r="C71" s="14">
         <v>45132</v>
       </c>
-      <c r="D71" s="2">
+      <c r="D71" s="14">
         <v>45137</v>
       </c>
-      <c r="E71" s="9" t="s">
+      <c r="E71" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="F71" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G71" s="4">
+      <c r="F71" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G71" s="16">
         <v>32</v>
       </c>
-      <c r="H71" s="5" t="s">
+      <c r="H71" s="17" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" s="10" t="s">
+      <c r="A72" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="B72" s="3">
+      <c r="B72" s="19">
         <v>45044</v>
       </c>
-      <c r="C72" s="3">
+      <c r="C72" s="19">
         <v>45132</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="19">
         <v>45107</v>
       </c>
-      <c r="E72" s="11" t="s">
+      <c r="E72" s="20" t="s">
         <v>138</v>
       </c>
-      <c r="F72" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G72" s="6">
+      <c r="F72" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G72" s="21">
         <v>88</v>
       </c>
-      <c r="H72" s="7" t="s">
+      <c r="H72" s="22" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" s="8" t="s">
+      <c r="A73" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="B73" s="2">
+      <c r="B73" s="14">
         <v>45068</v>
       </c>
-      <c r="C73" s="2">
+      <c r="C73" s="14">
         <v>45132</v>
       </c>
-      <c r="D73" s="2">
+      <c r="D73" s="14">
         <v>45137</v>
       </c>
-      <c r="E73" s="9" t="s">
+      <c r="E73" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="F73" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G73" s="4">
+      <c r="F73" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G73" s="16">
         <v>73</v>
       </c>
-      <c r="H73" s="5" t="s">
+      <c r="H73" s="17" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" s="10" t="s">
+      <c r="A74" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="B74" s="3">
+      <c r="B74" s="19">
         <v>45099</v>
       </c>
-      <c r="C74" s="3">
+      <c r="C74" s="19">
         <v>45133</v>
       </c>
-      <c r="D74" s="3">
+      <c r="D74" s="19">
         <v>45160</v>
       </c>
-      <c r="E74" s="11" t="s">
+      <c r="E74" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="F74" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G74" s="6">
+      <c r="F74" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G74" s="21">
         <v>85</v>
       </c>
-      <c r="H74" s="7" t="s">
+      <c r="H74" s="22" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A75" s="8" t="s">
+      <c r="A75" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="B75" s="2">
+      <c r="B75" s="14">
         <v>45099</v>
       </c>
-      <c r="C75" s="2">
+      <c r="C75" s="14">
         <v>45133</v>
       </c>
-      <c r="D75" s="2">
+      <c r="D75" s="14">
         <v>45160</v>
       </c>
-      <c r="E75" s="9" t="s">
+      <c r="E75" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="F75" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G75" s="4">
+      <c r="F75" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G75" s="16">
         <v>28</v>
       </c>
-      <c r="H75" s="5" t="s">
+      <c r="H75" s="17" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A76" s="10" t="s">
+      <c r="A76" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="B76" s="3">
+      <c r="B76" s="19">
         <v>45098</v>
       </c>
-      <c r="C76" s="3">
+      <c r="C76" s="19">
         <v>45133</v>
       </c>
-      <c r="D76" s="3">
+      <c r="D76" s="19">
         <v>45154</v>
       </c>
-      <c r="E76" s="11" t="s">
+      <c r="E76" s="20" t="s">
         <v>144</v>
       </c>
-      <c r="F76" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G76" s="6">
+      <c r="F76" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G76" s="21">
         <v>65</v>
       </c>
-      <c r="H76" s="7" t="s">
+      <c r="H76" s="22" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A77" s="8" t="s">
+      <c r="A77" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="B77" s="2">
+      <c r="B77" s="14">
         <v>45103</v>
       </c>
-      <c r="C77" s="2">
+      <c r="C77" s="14">
         <v>45133</v>
       </c>
-      <c r="D77" s="2">
+      <c r="D77" s="14">
         <v>45163</v>
       </c>
-      <c r="E77" s="9" t="s">
+      <c r="E77" s="15" t="s">
         <v>146</v>
       </c>
-      <c r="F77" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G77" s="4">
+      <c r="F77" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G77" s="16">
         <v>65</v>
       </c>
-      <c r="H77" s="5" t="s">
+      <c r="H77" s="17" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" s="10" t="s">
+      <c r="A78" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="B78" s="3">
+      <c r="B78" s="19">
         <v>45098</v>
       </c>
-      <c r="C78" s="3">
+      <c r="C78" s="19">
         <v>45133</v>
       </c>
-      <c r="D78" s="3">
+      <c r="D78" s="19">
         <v>45152</v>
       </c>
-      <c r="E78" s="11" t="s">
+      <c r="E78" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="F78" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G78" s="6">
+      <c r="F78" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G78" s="21">
         <v>79</v>
       </c>
-      <c r="H78" s="7" t="s">
+      <c r="H78" s="22" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" s="8" t="s">
+      <c r="A79" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="B79" s="2">
+      <c r="B79" s="14">
         <v>45100</v>
       </c>
-      <c r="C79" s="2">
+      <c r="C79" s="14">
         <v>45133</v>
       </c>
-      <c r="D79" s="2">
+      <c r="D79" s="14">
         <v>45161</v>
       </c>
-      <c r="E79" s="9" t="s">
+      <c r="E79" s="15" t="s">
         <v>150</v>
       </c>
-      <c r="F79" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G79" s="4">
+      <c r="F79" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G79" s="16">
         <v>109</v>
       </c>
-      <c r="H79" s="5" t="s">
+      <c r="H79" s="17" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A80" s="10" t="s">
+      <c r="A80" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="B80" s="3">
+      <c r="B80" s="19">
         <v>45105</v>
       </c>
-      <c r="C80" s="3">
+      <c r="C80" s="19">
         <v>45134</v>
       </c>
-      <c r="D80" s="3">
+      <c r="D80" s="19">
         <v>45170</v>
       </c>
-      <c r="E80" s="11" t="s">
+      <c r="E80" s="20" t="s">
         <v>156</v>
       </c>
-      <c r="F80" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G80" s="6">
+      <c r="F80" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G80" s="21">
         <v>102</v>
       </c>
-      <c r="H80" s="7" t="s">
+      <c r="H80" s="22" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A81" s="8" t="s">
+      <c r="A81" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="B81" s="2">
+      <c r="B81" s="14">
         <v>45106</v>
       </c>
-      <c r="C81" s="2">
+      <c r="C81" s="14">
         <v>45134</v>
       </c>
-      <c r="D81" s="2">
+      <c r="D81" s="14">
         <v>45110</v>
       </c>
-      <c r="E81" s="9" t="s">
+      <c r="E81" s="15" t="s">
         <v>158</v>
       </c>
-      <c r="F81" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G81" s="4">
+      <c r="F81" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G81" s="16">
         <v>158</v>
       </c>
-      <c r="H81" s="5" t="s">
+      <c r="H81" s="17" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A82" s="10" t="s">
+      <c r="A82" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="B82" s="3">
+      <c r="B82" s="19">
         <v>45105</v>
       </c>
-      <c r="C82" s="3">
+      <c r="C82" s="19">
         <v>45134</v>
       </c>
-      <c r="D82" s="3">
+      <c r="D82" s="19">
         <v>45169</v>
       </c>
-      <c r="E82" s="11" t="s">
+      <c r="E82" s="20" t="s">
         <v>160</v>
       </c>
-      <c r="F82" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G82" s="6">
+      <c r="F82" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G82" s="21">
         <v>43</v>
       </c>
-      <c r="H82" s="7" t="s">
+      <c r="H82" s="22" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A83" s="8" t="s">
+      <c r="A83" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="B83" s="2">
+      <c r="B83" s="14">
         <v>45105</v>
       </c>
-      <c r="C83" s="2">
+      <c r="C83" s="14">
         <v>45134</v>
       </c>
-      <c r="D83" s="2">
+      <c r="D83" s="14">
         <v>45226</v>
       </c>
-      <c r="E83" s="9" t="s">
+      <c r="E83" s="15" t="s">
         <v>160</v>
       </c>
-      <c r="F83" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G83" s="4">
+      <c r="F83" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G83" s="16">
         <v>10</v>
       </c>
-      <c r="H83" s="5" t="s">
+      <c r="H83" s="17" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A84" s="10" t="s">
+      <c r="A84" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="B84" s="3">
+      <c r="B84" s="19">
         <v>45104</v>
       </c>
-      <c r="C84" s="3">
+      <c r="C84" s="19">
         <v>45134</v>
       </c>
-      <c r="D84" s="3">
+      <c r="D84" s="19">
         <v>45135</v>
       </c>
-      <c r="E84" s="11" t="s">
+      <c r="E84" s="20" t="s">
         <v>162</v>
       </c>
-      <c r="F84" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G84" s="6">
+      <c r="F84" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G84" s="21">
         <v>48</v>
       </c>
-      <c r="H84" s="7" t="s">
+      <c r="H84" s="22" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A85" s="8" t="s">
+      <c r="A85" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="B85" s="2">
+      <c r="B85" s="14">
         <v>45105</v>
       </c>
-      <c r="C85" s="2">
+      <c r="C85" s="14">
         <v>45134</v>
       </c>
-      <c r="D85" s="2">
+      <c r="D85" s="14">
         <v>45136</v>
       </c>
-      <c r="E85" s="9" t="s">
+      <c r="E85" s="15" t="s">
         <v>164</v>
       </c>
-      <c r="F85" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G85" s="4">
+      <c r="F85" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G85" s="16">
         <v>5</v>
       </c>
-      <c r="H85" s="5" t="s">
+      <c r="H85" s="17" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A86" s="10" t="s">
+      <c r="A86" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="B86" s="3">
+      <c r="B86" s="19">
         <v>45106</v>
       </c>
-      <c r="C86" s="3">
+      <c r="C86" s="19">
         <v>45134</v>
       </c>
-      <c r="D86" s="3">
+      <c r="D86" s="19">
         <v>45110</v>
       </c>
-      <c r="E86" s="11" t="s">
+      <c r="E86" s="20" t="s">
         <v>166</v>
       </c>
-      <c r="F86" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G86" s="6">
+      <c r="F86" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G86" s="21">
         <v>19</v>
       </c>
-      <c r="H86" s="7" t="s">
+      <c r="H86" s="22" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A87" s="8" t="s">
+      <c r="A87" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="B87" s="2">
+      <c r="B87" s="14">
         <v>45106</v>
       </c>
-      <c r="C87" s="2">
+      <c r="C87" s="14">
         <v>45135</v>
       </c>
-      <c r="D87" s="2">
+      <c r="D87" s="14">
         <v>45169</v>
       </c>
-      <c r="E87" s="9" t="s">
+      <c r="E87" s="15" t="s">
         <v>168</v>
       </c>
-      <c r="F87" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G87" s="4">
+      <c r="F87" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G87" s="16">
         <v>80</v>
       </c>
-      <c r="H87" s="5" t="s">
+      <c r="H87" s="17" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A88" s="10" t="s">
+      <c r="A88" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="B88" s="3">
+      <c r="B88" s="19">
         <v>45106</v>
       </c>
-      <c r="C88" s="3">
+      <c r="C88" s="19">
         <v>45135</v>
       </c>
-      <c r="D88" s="3">
+      <c r="D88" s="19">
         <v>45199</v>
       </c>
-      <c r="E88" s="11" t="s">
+      <c r="E88" s="20" t="s">
         <v>170</v>
       </c>
-      <c r="F88" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G88" s="6">
+      <c r="F88" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G88" s="21">
         <v>9</v>
       </c>
-      <c r="H88" s="7" t="s">
+      <c r="H88" s="22" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A89" s="8" t="s">
+      <c r="A89" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="B89" s="2">
+      <c r="B89" s="14">
         <v>45099</v>
       </c>
-      <c r="C89" s="2">
+      <c r="C89" s="14">
         <v>45138</v>
       </c>
-      <c r="D89" s="2">
+      <c r="D89" s="14">
         <v>45160</v>
       </c>
-      <c r="E89" s="9" t="s">
+      <c r="E89" s="15" t="s">
         <v>172</v>
       </c>
-      <c r="F89" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G89" s="4">
+      <c r="F89" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G89" s="16">
         <v>38</v>
       </c>
-      <c r="H89" s="5" t="s">
+      <c r="H89" s="17" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A90" s="10" t="s">
+      <c r="A90" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="B90" s="3">
+      <c r="B90" s="19">
         <v>45099</v>
       </c>
-      <c r="C90" s="3">
+      <c r="C90" s="19">
         <v>45138</v>
       </c>
-      <c r="D90" s="3">
+      <c r="D90" s="19">
         <v>45160</v>
       </c>
-      <c r="E90" s="11" t="s">
+      <c r="E90" s="20" t="s">
         <v>172</v>
       </c>
-      <c r="F90" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G90" s="6">
+      <c r="F90" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G90" s="21">
         <v>64</v>
       </c>
-      <c r="H90" s="7" t="s">
+      <c r="H90" s="22" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A91" s="8" t="s">
+      <c r="A91" s="13" t="s">
         <v>175</v>
       </c>
-      <c r="B91" s="2">
+      <c r="B91" s="14">
         <v>45100</v>
       </c>
-      <c r="C91" s="2">
+      <c r="C91" s="14">
         <v>45139</v>
       </c>
-      <c r="D91" s="2">
+      <c r="D91" s="14">
         <v>45170</v>
       </c>
-      <c r="E91" s="9" t="s">
+      <c r="E91" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="F91" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G91" s="4">
+      <c r="F91" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G91" s="16">
         <v>93</v>
       </c>
-      <c r="H91" s="5" t="s">
+      <c r="H91" s="17" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A92" s="10" t="s">
+      <c r="A92" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="B92" s="3">
+      <c r="B92" s="19">
         <v>45106</v>
       </c>
-      <c r="C92" s="3">
+      <c r="C92" s="19">
         <v>45140</v>
       </c>
-      <c r="D92" s="3">
+      <c r="D92" s="19">
         <v>45165</v>
       </c>
-      <c r="E92" s="11" t="s">
+      <c r="E92" s="20" t="s">
         <v>172</v>
       </c>
-      <c r="F92" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G92" s="6">
+      <c r="F92" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G92" s="21">
         <v>66</v>
       </c>
-      <c r="H92" s="7" t="s">
+      <c r="H92" s="22" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A93" s="8" t="s">
+      <c r="A93" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="B93" s="2">
+      <c r="B93" s="14">
         <v>45106</v>
       </c>
-      <c r="C93" s="2">
+      <c r="C93" s="14">
         <v>45140</v>
       </c>
-      <c r="D93" s="2">
+      <c r="D93" s="14">
         <v>45165</v>
       </c>
-      <c r="E93" s="9" t="s">
+      <c r="E93" s="15" t="s">
         <v>172</v>
       </c>
-      <c r="F93" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G93" s="4">
+      <c r="F93" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G93" s="16">
         <v>5</v>
       </c>
-      <c r="H93" s="5" t="s">
+      <c r="H93" s="17" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A94" s="10" t="s">
+      <c r="A94" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="B94" s="3">
+      <c r="B94" s="19">
         <v>45106</v>
       </c>
-      <c r="C94" s="3">
+      <c r="C94" s="19">
         <v>45140</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="19">
         <v>45165</v>
       </c>
-      <c r="E94" s="11" t="s">
+      <c r="E94" s="20" t="s">
         <v>172</v>
       </c>
-      <c r="F94" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G94" s="6">
+      <c r="F94" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G94" s="21">
         <v>27</v>
       </c>
-      <c r="H94" s="7" t="s">
+      <c r="H94" s="22" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A95" s="8" t="s">
+      <c r="A95" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="B95" s="2">
+      <c r="B95" s="14">
         <v>45099</v>
       </c>
-      <c r="C95" s="2">
+      <c r="C95" s="14">
         <v>45140</v>
       </c>
-      <c r="D95" s="2">
+      <c r="D95" s="14">
         <v>45160</v>
       </c>
-      <c r="E95" s="9" t="s">
+      <c r="E95" s="15" t="s">
         <v>172</v>
       </c>
-      <c r="F95" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G95" s="4">
+      <c r="F95" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G95" s="16">
         <v>6</v>
       </c>
-      <c r="H95" s="5" t="s">
+      <c r="H95" s="17" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A96" s="10" t="s">
+      <c r="A96" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="B96" s="3">
+      <c r="B96" s="19">
         <v>45099</v>
       </c>
-      <c r="C96" s="3">
+      <c r="C96" s="19">
         <v>45140</v>
       </c>
-      <c r="D96" s="3">
+      <c r="D96" s="19">
         <v>45160</v>
       </c>
-      <c r="E96" s="11" t="s">
+      <c r="E96" s="20" t="s">
         <v>172</v>
       </c>
-      <c r="F96" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G96" s="6">
+      <c r="F96" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G96" s="21">
         <v>2</v>
       </c>
-      <c r="H96" s="7" t="s">
+      <c r="H96" s="22" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A97" s="8" t="s">
+      <c r="A97" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="B97" s="2">
+      <c r="B97" s="14">
         <v>45099</v>
       </c>
-      <c r="C97" s="2">
+      <c r="C97" s="14">
         <v>45140</v>
       </c>
-      <c r="D97" s="2">
+      <c r="D97" s="14">
         <v>45159</v>
       </c>
-      <c r="E97" s="9" t="s">
+      <c r="E97" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="F97" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G97" s="4">
+      <c r="F97" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G97" s="16">
         <v>99</v>
       </c>
-      <c r="H97" s="5" t="s">
+      <c r="H97" s="17" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A98" s="10" t="s">
+      <c r="A98" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="B98" s="3">
+      <c r="B98" s="19">
         <v>45092</v>
       </c>
-      <c r="C98" s="3">
+      <c r="C98" s="19">
         <v>45140</v>
       </c>
-      <c r="D98" s="3">
+      <c r="D98" s="19">
         <v>45107</v>
       </c>
-      <c r="E98" s="11" t="s">
+      <c r="E98" s="20" t="s">
         <v>185</v>
       </c>
-      <c r="F98" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G98" s="6">
+      <c r="F98" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G98" s="21">
         <v>14</v>
       </c>
-      <c r="H98" s="7" t="s">
+      <c r="H98" s="22" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A99" s="8" t="s">
+      <c r="A99" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="B99" s="2">
+      <c r="B99" s="14">
         <v>45106</v>
       </c>
-      <c r="C99" s="2">
+      <c r="C99" s="14">
         <v>45141</v>
       </c>
-      <c r="D99" s="2">
+      <c r="D99" s="14">
         <v>45166</v>
       </c>
-      <c r="E99" s="9" t="s">
+      <c r="E99" s="15" t="s">
         <v>187</v>
       </c>
-      <c r="F99" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G99" s="4">
+      <c r="F99" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G99" s="16">
         <v>20</v>
       </c>
-      <c r="H99" s="5" t="s">
+      <c r="H99" s="17" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A100" s="10" t="s">
+      <c r="A100" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="B100" s="3">
+      <c r="B100" s="19">
         <v>45107</v>
       </c>
-      <c r="C100" s="3">
+      <c r="C100" s="19">
         <v>45141</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="19">
         <v>45107</v>
       </c>
-      <c r="E100" s="11" t="s">
+      <c r="E100" s="20" t="s">
         <v>189</v>
       </c>
-      <c r="F100" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G100" s="6">
+      <c r="F100" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G100" s="21">
         <v>54</v>
       </c>
-      <c r="H100" s="7" t="s">
+      <c r="H100" s="22" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A101" s="8" t="s">
+      <c r="A101" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="B101" s="2">
+      <c r="B101" s="14">
         <v>45106</v>
       </c>
-      <c r="C101" s="2">
+      <c r="C101" s="14">
         <v>45141</v>
       </c>
-      <c r="D101" s="2">
+      <c r="D101" s="14">
         <v>45166</v>
       </c>
-      <c r="E101" s="9" t="s">
+      <c r="E101" s="15" t="s">
         <v>191</v>
       </c>
-      <c r="F101" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G101" s="4">
+      <c r="F101" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G101" s="16">
         <v>1</v>
       </c>
-      <c r="H101" s="5" t="s">
+      <c r="H101" s="17" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A102" s="10" t="s">
+      <c r="A102" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="B102" s="3">
+      <c r="B102" s="19">
         <v>45106</v>
       </c>
-      <c r="C102" s="3">
+      <c r="C102" s="19">
         <v>45141</v>
       </c>
-      <c r="D102" s="3">
+      <c r="D102" s="19">
         <v>45166</v>
       </c>
-      <c r="E102" s="11" t="s">
+      <c r="E102" s="20" t="s">
         <v>193</v>
       </c>
-      <c r="F102" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G102" s="6">
+      <c r="F102" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G102" s="21">
         <v>97</v>
       </c>
-      <c r="H102" s="7" t="s">
+      <c r="H102" s="22" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A103" s="8" t="s">
+      <c r="A103" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="B103" s="2">
+      <c r="B103" s="14">
         <v>45106</v>
       </c>
-      <c r="C103" s="2">
+      <c r="C103" s="14">
         <v>45141</v>
       </c>
-      <c r="D103" s="2">
+      <c r="D103" s="14">
         <v>45166</v>
       </c>
-      <c r="E103" s="9" t="s">
+      <c r="E103" s="15" t="s">
         <v>195</v>
       </c>
-      <c r="F103" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G103" s="4">
+      <c r="F103" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G103" s="16">
         <v>1</v>
       </c>
-      <c r="H103" s="5" t="s">
+      <c r="H103" s="17" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A104" s="10" t="s">
+      <c r="A104" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="B104" s="3">
+      <c r="B104" s="19">
         <v>45106</v>
       </c>
-      <c r="C104" s="3">
+      <c r="C104" s="19">
         <v>45141</v>
       </c>
-      <c r="D104" s="3">
+      <c r="D104" s="19">
         <v>45166</v>
       </c>
-      <c r="E104" s="11" t="s">
+      <c r="E104" s="20" t="s">
         <v>197</v>
       </c>
-      <c r="F104" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G104" s="6">
+      <c r="F104" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G104" s="21">
         <v>46</v>
       </c>
-      <c r="H104" s="7" t="s">
+      <c r="H104" s="22" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A105" s="8" t="s">
+      <c r="A105" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="B105" s="2">
+      <c r="B105" s="14">
         <v>45106</v>
       </c>
-      <c r="C105" s="2">
+      <c r="C105" s="14">
         <v>45141</v>
       </c>
-      <c r="D105" s="2">
+      <c r="D105" s="14">
         <v>45166</v>
       </c>
-      <c r="E105" s="9" t="s">
+      <c r="E105" s="15" t="s">
         <v>199</v>
       </c>
-      <c r="F105" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G105" s="4">
+      <c r="F105" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G105" s="16">
         <v>36</v>
       </c>
-      <c r="H105" s="5" t="s">
+      <c r="H105" s="17" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A106" s="10" t="s">
+      <c r="A106" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="B106" s="3">
+      <c r="B106" s="19">
         <v>45106</v>
       </c>
-      <c r="C106" s="3">
+      <c r="C106" s="19">
         <v>45141</v>
       </c>
-      <c r="D106" s="3">
+      <c r="D106" s="19">
         <v>45166</v>
       </c>
-      <c r="E106" s="11" t="s">
+      <c r="E106" s="20" t="s">
         <v>201</v>
       </c>
-      <c r="F106" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G106" s="6">
+      <c r="F106" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G106" s="21">
         <v>17</v>
       </c>
-      <c r="H106" s="7" t="s">
+      <c r="H106" s="22" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A107" s="8" t="s">
+      <c r="A107" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="B107" s="2">
+      <c r="B107" s="14">
         <v>45106</v>
       </c>
-      <c r="C107" s="2">
+      <c r="C107" s="14">
         <v>45141</v>
       </c>
-      <c r="D107" s="2">
+      <c r="D107" s="14">
         <v>45166</v>
       </c>
-      <c r="E107" s="9" t="s">
+      <c r="E107" s="15" t="s">
         <v>203</v>
       </c>
-      <c r="F107" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G107" s="4">
-        <v>16</v>
-      </c>
-      <c r="H107" s="5" t="s">
+      <c r="F107" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G107" s="16">
+        <v>16</v>
+      </c>
+      <c r="H107" s="17" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A108" s="10" t="s">
+      <c r="A108" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="B108" s="3">
+      <c r="B108" s="19">
         <v>45105</v>
       </c>
-      <c r="C108" s="3">
+      <c r="C108" s="19">
         <v>45142</v>
       </c>
-      <c r="D108" s="3">
+      <c r="D108" s="19">
         <v>45108</v>
       </c>
-      <c r="E108" s="11" t="s">
+      <c r="E108" s="20" t="s">
         <v>205</v>
       </c>
-      <c r="F108" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G108" s="6">
+      <c r="F108" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G108" s="21">
         <v>107</v>
       </c>
-      <c r="H108" s="7" t="s">
+      <c r="H108" s="22" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A109" s="8" t="s">
+      <c r="A109" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="B109" s="2">
+      <c r="B109" s="14">
         <v>45105</v>
       </c>
-      <c r="C109" s="2">
+      <c r="C109" s="14">
         <v>45142</v>
       </c>
-      <c r="D109" s="2">
+      <c r="D109" s="14">
         <v>45108</v>
       </c>
-      <c r="E109" s="9" t="s">
+      <c r="E109" s="15" t="s">
         <v>205</v>
       </c>
-      <c r="F109" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G109" s="4">
+      <c r="F109" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G109" s="16">
         <v>57</v>
       </c>
-      <c r="H109" s="5" t="s">
+      <c r="H109" s="17" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A110" s="10" t="s">
+      <c r="A110" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B110" s="3">
+      <c r="B110" s="19">
         <v>45110</v>
       </c>
-      <c r="C110" s="3">
+      <c r="C110" s="19">
         <v>45145</v>
       </c>
-      <c r="D110" s="3">
+      <c r="D110" s="19">
         <v>45173</v>
       </c>
-      <c r="E110" s="11" t="s">
+      <c r="E110" s="20" t="s">
         <v>208</v>
       </c>
-      <c r="F110" s="11" t="s">
+      <c r="F110" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="G110" s="6">
+      <c r="G110" s="21">
         <v>111</v>
       </c>
-      <c r="H110" s="7" t="s">
+      <c r="H110" s="22" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A111" s="8" t="s">
+      <c r="A111" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="B111" s="2">
+      <c r="B111" s="14">
         <v>45110</v>
       </c>
-      <c r="C111" s="2">
+      <c r="C111" s="14">
         <v>45145</v>
       </c>
-      <c r="D111" s="2">
+      <c r="D111" s="14">
         <v>45172</v>
       </c>
-      <c r="E111" s="9" t="s">
+      <c r="E111" s="15" t="s">
         <v>210</v>
       </c>
-      <c r="F111" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G111" s="4">
+      <c r="F111" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G111" s="16">
         <v>61</v>
       </c>
-      <c r="H111" s="5" t="s">
+      <c r="H111" s="17" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A112" s="10" t="s">
+      <c r="A112" s="18" t="s">
         <v>212</v>
       </c>
-      <c r="B112" s="3">
+      <c r="B112" s="19">
         <v>45104</v>
       </c>
-      <c r="C112" s="3">
+      <c r="C112" s="19">
         <v>45145</v>
       </c>
-      <c r="D112" s="3">
+      <c r="D112" s="19">
         <v>45169</v>
       </c>
-      <c r="E112" s="11" t="s">
+      <c r="E112" s="20" t="s">
         <v>213</v>
       </c>
-      <c r="F112" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G112" s="6">
+      <c r="F112" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G112" s="21">
         <v>137</v>
       </c>
-      <c r="H112" s="7" t="s">
+      <c r="H112" s="22" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A113" s="8" t="s">
+      <c r="A113" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="B113" s="2">
+      <c r="B113" s="14">
         <v>45113</v>
       </c>
-      <c r="C113" s="2">
+      <c r="C113" s="14">
         <v>45146</v>
       </c>
-      <c r="D113" s="2">
+      <c r="D113" s="14">
         <v>45173</v>
       </c>
-      <c r="E113" s="9" t="s">
+      <c r="E113" s="15" t="s">
         <v>215</v>
       </c>
-      <c r="F113" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G113" s="4">
+      <c r="F113" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G113" s="16">
         <v>63</v>
       </c>
-      <c r="H113" s="5" t="s">
+      <c r="H113" s="17" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A114" s="10" t="s">
+      <c r="A114" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="B114" s="3">
+      <c r="B114" s="19">
         <v>45113</v>
       </c>
-      <c r="C114" s="3">
+      <c r="C114" s="19">
         <v>45147</v>
       </c>
-      <c r="D114" s="3">
+      <c r="D114" s="19">
         <v>45173</v>
       </c>
-      <c r="E114" s="11" t="s">
+      <c r="E114" s="20" t="s">
         <v>217</v>
       </c>
-      <c r="F114" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G114" s="6">
+      <c r="F114" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G114" s="21">
         <v>75</v>
       </c>
-      <c r="H114" s="7" t="s">
+      <c r="H114" s="22" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A115" s="8" t="s">
+      <c r="A115" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="B115" s="2">
+      <c r="B115" s="14">
         <v>45113</v>
       </c>
-      <c r="C115" s="2">
+      <c r="C115" s="14">
         <v>45147</v>
       </c>
-      <c r="D115" s="2">
+      <c r="D115" s="14">
         <v>45107</v>
       </c>
-      <c r="E115" s="9" t="s">
+      <c r="E115" s="15" t="s">
         <v>219</v>
       </c>
-      <c r="F115" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G115" s="4">
+      <c r="F115" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G115" s="16">
         <v>3</v>
       </c>
-      <c r="H115" s="5" t="s">
+      <c r="H115" s="17" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A116" s="10" t="s">
+      <c r="A116" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="B116" s="3">
+      <c r="B116" s="19">
         <v>45116</v>
       </c>
-      <c r="C116" s="3">
+      <c r="C116" s="19">
         <v>45147</v>
       </c>
-      <c r="D116" s="3">
+      <c r="D116" s="19">
         <v>45163</v>
       </c>
-      <c r="E116" s="11" t="s">
+      <c r="E116" s="20" t="s">
         <v>221</v>
       </c>
-      <c r="F116" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G116" s="6">
+      <c r="F116" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G116" s="21">
         <v>111</v>
       </c>
-      <c r="H116" s="7" t="s">
+      <c r="H116" s="22" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A117" s="8" t="s">
+      <c r="A117" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="B117" s="2">
+      <c r="B117" s="14">
         <v>45106</v>
       </c>
-      <c r="C117" s="2">
+      <c r="C117" s="14">
         <v>45147</v>
       </c>
-      <c r="D117" s="2">
+      <c r="D117" s="14">
         <v>45199</v>
       </c>
-      <c r="E117" s="9" t="s">
+      <c r="E117" s="15" t="s">
         <v>223</v>
       </c>
-      <c r="F117" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G117" s="4">
+      <c r="F117" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G117" s="16">
         <v>164</v>
       </c>
-      <c r="H117" s="5" t="s">
+      <c r="H117" s="17" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A118" s="10" t="s">
+      <c r="A118" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="B118" s="3">
+      <c r="B118" s="19">
         <v>45117</v>
       </c>
-      <c r="C118" s="3">
+      <c r="C118" s="19">
         <v>45148</v>
       </c>
-      <c r="D118" s="3">
+      <c r="D118" s="19">
         <v>45184</v>
       </c>
-      <c r="E118" s="11" t="s">
+      <c r="E118" s="20" t="s">
         <v>225</v>
       </c>
-      <c r="F118" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G118" s="6">
+      <c r="F118" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G118" s="21">
         <v>203</v>
       </c>
-      <c r="H118" s="7" t="s">
+      <c r="H118" s="22" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A119" s="8" t="s">
+      <c r="A119" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="B119" s="2">
+      <c r="B119" s="14">
         <v>45119</v>
       </c>
-      <c r="C119" s="2">
+      <c r="C119" s="14">
         <v>45148</v>
       </c>
-      <c r="D119" s="2">
+      <c r="D119" s="14">
         <v>45187</v>
       </c>
-      <c r="E119" s="9" t="s">
+      <c r="E119" s="15" t="s">
         <v>227</v>
       </c>
-      <c r="F119" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G119" s="4">
+      <c r="F119" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G119" s="16">
         <v>74</v>
       </c>
-      <c r="H119" s="5" t="s">
+      <c r="H119" s="17" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A120" s="10" t="s">
+      <c r="A120" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="B120" s="3">
+      <c r="B120" s="19">
         <v>45117</v>
       </c>
-      <c r="C120" s="3">
+      <c r="C120" s="19">
         <v>45148</v>
       </c>
-      <c r="D120" s="3">
+      <c r="D120" s="19">
         <v>45177</v>
       </c>
-      <c r="E120" s="11" t="s">
+      <c r="E120" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="F120" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G120" s="6">
+      <c r="F120" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G120" s="21">
         <v>40</v>
       </c>
-      <c r="H120" s="7" t="s">
+      <c r="H120" s="22" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A121" s="8" t="s">
+      <c r="A121" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="B121" s="2">
+      <c r="B121" s="14">
         <v>45117</v>
       </c>
-      <c r="C121" s="2">
+      <c r="C121" s="14">
         <v>45148</v>
       </c>
-      <c r="D121" s="2">
+      <c r="D121" s="14">
         <v>45184</v>
       </c>
-      <c r="E121" s="9" t="s">
+      <c r="E121" s="15" t="s">
         <v>225</v>
       </c>
-      <c r="F121" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G121" s="4">
+      <c r="F121" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G121" s="16">
         <v>45</v>
       </c>
-      <c r="H121" s="5" t="s">
+      <c r="H121" s="17" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A122" s="10" t="s">
+      <c r="A122" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B122" s="3">
+      <c r="B122" s="19">
         <v>45106</v>
       </c>
-      <c r="C122" s="3">
+      <c r="C122" s="19">
         <v>45152</v>
       </c>
-      <c r="D122" s="3">
+      <c r="D122" s="19">
         <v>45169</v>
       </c>
-      <c r="E122" s="11" t="s">
+      <c r="E122" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="F122" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G122" s="6">
+      <c r="F122" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G122" s="21">
         <v>89</v>
       </c>
-      <c r="H122" s="7" t="s">
+      <c r="H122" s="22" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A123" s="8" t="s">
+      <c r="A123" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="B123" s="2">
+      <c r="B123" s="14">
         <v>45106</v>
       </c>
-      <c r="C123" s="2">
+      <c r="C123" s="14">
         <v>45152</v>
       </c>
-      <c r="D123" s="2">
+      <c r="D123" s="14">
         <v>45169</v>
       </c>
-      <c r="E123" s="9" t="s">
+      <c r="E123" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="F123" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G123" s="4">
+      <c r="F123" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G123" s="16">
         <v>51</v>
       </c>
-      <c r="H123" s="5" t="s">
+      <c r="H123" s="17" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A124" s="10" t="s">
+      <c r="A124" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="B124" s="3">
+      <c r="B124" s="19">
         <v>45120</v>
       </c>
-      <c r="C124" s="3">
+      <c r="C124" s="19">
         <v>45153</v>
       </c>
-      <c r="D124" s="3">
+      <c r="D124" s="19">
         <v>45152</v>
       </c>
-      <c r="E124" s="11" t="s">
+      <c r="E124" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="F124" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G124" s="6">
+      <c r="F124" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G124" s="21">
         <v>3</v>
       </c>
-      <c r="H124" s="7" t="s">
+      <c r="H124" s="22" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A125" s="8" t="s">
+      <c r="A125" s="13" t="s">
         <v>233</v>
       </c>
-      <c r="B125" s="2">
+      <c r="B125" s="14">
         <v>45139</v>
       </c>
-      <c r="C125" s="2">
+      <c r="C125" s="14">
         <v>45153</v>
       </c>
-      <c r="D125" s="2">
+      <c r="D125" s="14">
         <v>45137</v>
       </c>
-      <c r="E125" s="9" t="s">
+      <c r="E125" s="15" t="s">
         <v>234</v>
       </c>
-      <c r="F125" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G125" s="4">
+      <c r="F125" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G125" s="16">
         <v>48</v>
       </c>
-      <c r="H125" s="5" t="s">
+      <c r="H125" s="17" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A126" s="10" t="s">
+      <c r="A126" s="18" t="s">
         <v>236</v>
       </c>
-      <c r="B126" s="3">
+      <c r="B126" s="19">
         <v>45139</v>
       </c>
-      <c r="C126" s="3">
+      <c r="C126" s="19">
         <v>45153</v>
       </c>
-      <c r="D126" s="3">
+      <c r="D126" s="19">
         <v>45137</v>
       </c>
-      <c r="E126" s="11" t="s">
+      <c r="E126" s="20" t="s">
         <v>234</v>
       </c>
-      <c r="F126" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G126" s="6">
+      <c r="F126" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G126" s="21">
         <v>2</v>
       </c>
-      <c r="H126" s="7" t="s">
+      <c r="H126" s="22" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A127" s="8" t="s">
+      <c r="A127" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="B127" s="2">
+      <c r="B127" s="14">
         <v>45139</v>
       </c>
-      <c r="C127" s="2">
+      <c r="C127" s="14">
         <v>45153</v>
       </c>
-      <c r="D127" s="2">
+      <c r="D127" s="14">
         <v>45137</v>
       </c>
-      <c r="E127" s="9" t="s">
+      <c r="E127" s="15" t="s">
         <v>234</v>
       </c>
-      <c r="F127" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G127" s="4">
+      <c r="F127" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G127" s="16">
         <v>30</v>
       </c>
-      <c r="H127" s="5" t="s">
+      <c r="H127" s="17" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A128" s="10" t="s">
+      <c r="A128" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="B128" s="3">
+      <c r="B128" s="19">
         <v>45120</v>
       </c>
-      <c r="C128" s="3">
+      <c r="C128" s="19">
         <v>45153</v>
       </c>
-      <c r="D128" s="3">
+      <c r="D128" s="19">
         <v>45152</v>
       </c>
-      <c r="E128" s="11" t="s">
+      <c r="E128" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="F128" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G128" s="6">
+      <c r="F128" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G128" s="21">
         <v>14</v>
       </c>
-      <c r="H128" s="7" t="s">
+      <c r="H128" s="22" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A129" s="8" t="s">
+      <c r="A129" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="B129" s="2">
+      <c r="B129" s="14">
         <v>45121</v>
       </c>
-      <c r="C129" s="2">
+      <c r="C129" s="14">
         <v>45153</v>
       </c>
-      <c r="D129" s="2">
+      <c r="D129" s="14">
         <v>45184</v>
       </c>
-      <c r="E129" s="9" t="s">
+      <c r="E129" s="15" t="s">
         <v>240</v>
       </c>
-      <c r="F129" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G129" s="4">
+      <c r="F129" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G129" s="16">
         <v>34</v>
       </c>
-      <c r="H129" s="5" t="s">
+      <c r="H129" s="17" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A130" s="10" t="s">
+      <c r="A130" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="B130" s="3">
+      <c r="B130" s="19">
         <v>45139</v>
       </c>
-      <c r="C130" s="3">
+      <c r="C130" s="19">
         <v>45153</v>
       </c>
-      <c r="D130" s="3">
+      <c r="D130" s="19">
         <v>45137</v>
       </c>
-      <c r="E130" s="11" t="s">
+      <c r="E130" s="20" t="s">
         <v>234</v>
       </c>
-      <c r="F130" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G130" s="6">
+      <c r="F130" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G130" s="21">
         <v>39</v>
       </c>
-      <c r="H130" s="7" t="s">
+      <c r="H130" s="22" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A131" s="8" t="s">
+      <c r="A131" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="B131" s="2">
+      <c r="B131" s="14">
         <v>45139</v>
       </c>
-      <c r="C131" s="2">
+      <c r="C131" s="14">
         <v>45153</v>
       </c>
-      <c r="D131" s="2">
+      <c r="D131" s="14">
         <v>45137</v>
       </c>
-      <c r="E131" s="9" t="s">
+      <c r="E131" s="15" t="s">
         <v>243</v>
       </c>
-      <c r="F131" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G131" s="4">
+      <c r="F131" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G131" s="16">
         <v>83</v>
       </c>
-      <c r="H131" s="5" t="s">
+      <c r="H131" s="17" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A132" s="10" t="s">
+      <c r="A132" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="B132" s="3">
+      <c r="B132" s="19">
         <v>45139</v>
       </c>
-      <c r="C132" s="3">
+      <c r="C132" s="19">
         <v>45153</v>
       </c>
-      <c r="D132" s="3">
+      <c r="D132" s="19">
         <v>45137</v>
       </c>
-      <c r="E132" s="11" t="s">
+      <c r="E132" s="20" t="s">
         <v>245</v>
       </c>
-      <c r="F132" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G132" s="6">
+      <c r="F132" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G132" s="21">
         <v>94</v>
       </c>
-      <c r="H132" s="7" t="s">
+      <c r="H132" s="22" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A133" s="8" t="s">
+      <c r="A133" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="B133" s="2">
+      <c r="B133" s="14">
         <v>45139</v>
       </c>
-      <c r="C133" s="2">
+      <c r="C133" s="14">
         <v>45153</v>
       </c>
-      <c r="D133" s="2">
+      <c r="D133" s="14">
         <v>45137</v>
       </c>
-      <c r="E133" s="9" t="s">
+      <c r="E133" s="15" t="s">
         <v>234</v>
       </c>
-      <c r="F133" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G133" s="4">
+      <c r="F133" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G133" s="16">
         <v>60</v>
       </c>
-      <c r="H133" s="5" t="s">
+      <c r="H133" s="17" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A134" s="10" t="s">
+      <c r="A134" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="B134" s="3">
+      <c r="B134" s="19">
         <v>45139</v>
       </c>
-      <c r="C134" s="3">
+      <c r="C134" s="19">
         <v>45153</v>
       </c>
-      <c r="D134" s="3">
+      <c r="D134" s="19">
         <v>45137</v>
       </c>
-      <c r="E134" s="11" t="s">
+      <c r="E134" s="20" t="s">
         <v>234</v>
       </c>
-      <c r="F134" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G134" s="6">
-        <v>15</v>
-      </c>
-      <c r="H134" s="7" t="s">
+      <c r="F134" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G134" s="21">
+        <v>15</v>
+      </c>
+      <c r="H134" s="22" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A135" s="8" t="s">
+      <c r="A135" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="B135" s="2">
+      <c r="B135" s="14">
         <v>45139</v>
       </c>
-      <c r="C135" s="2">
+      <c r="C135" s="14">
         <v>45153</v>
       </c>
-      <c r="D135" s="2">
+      <c r="D135" s="14">
         <v>45137</v>
       </c>
-      <c r="E135" s="9" t="s">
+      <c r="E135" s="15" t="s">
         <v>234</v>
       </c>
-      <c r="F135" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G135" s="4">
+      <c r="F135" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G135" s="16">
         <v>709</v>
       </c>
-      <c r="H135" s="5" t="s">
+      <c r="H135" s="17" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A136" s="10" t="s">
+      <c r="A136" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="B136" s="3">
+      <c r="B136" s="19">
         <v>45139</v>
       </c>
-      <c r="C136" s="3">
+      <c r="C136" s="19">
         <v>45153</v>
       </c>
-      <c r="D136" s="3">
+      <c r="D136" s="19">
         <v>45137</v>
       </c>
-      <c r="E136" s="11" t="s">
+      <c r="E136" s="20" t="s">
         <v>234</v>
       </c>
-      <c r="F136" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G136" s="6">
+      <c r="F136" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G136" s="21">
         <v>240</v>
       </c>
-      <c r="H136" s="7" t="s">
+      <c r="H136" s="22" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A137" s="8" t="s">
+      <c r="A137" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="B137" s="2">
+      <c r="B137" s="14">
         <v>45120</v>
       </c>
-      <c r="C137" s="2">
+      <c r="C137" s="14">
         <v>45153</v>
       </c>
-      <c r="D137" s="2">
+      <c r="D137" s="14">
         <v>45152</v>
       </c>
-      <c r="E137" s="9" t="s">
+      <c r="E137" s="15" t="s">
         <v>251</v>
       </c>
-      <c r="F137" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G137" s="4">
+      <c r="F137" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G137" s="16">
         <v>75</v>
       </c>
-      <c r="H137" s="5" t="s">
+      <c r="H137" s="17" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A138" s="10" t="s">
+      <c r="A138" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="B138" s="3">
+      <c r="B138" s="19">
         <v>45120</v>
       </c>
-      <c r="C138" s="3">
+      <c r="C138" s="19">
         <v>45153</v>
       </c>
-      <c r="D138" s="3">
+      <c r="D138" s="19">
         <v>45152</v>
       </c>
-      <c r="E138" s="11" t="s">
+      <c r="E138" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="F138" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G138" s="6">
+      <c r="F138" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G138" s="21">
         <v>76</v>
       </c>
-      <c r="H138" s="7" t="s">
+      <c r="H138" s="22" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A139" s="8" t="s">
+      <c r="A139" s="13" t="s">
         <v>252</v>
       </c>
-      <c r="B139" s="2">
+      <c r="B139" s="14">
         <v>45139</v>
       </c>
-      <c r="C139" s="2">
+      <c r="C139" s="14">
         <v>45153</v>
       </c>
-      <c r="D139" s="2">
+      <c r="D139" s="14">
         <v>45137</v>
       </c>
-      <c r="E139" s="9" t="s">
+      <c r="E139" s="15" t="s">
         <v>234</v>
       </c>
-      <c r="F139" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G139" s="4">
+      <c r="F139" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G139" s="16">
         <v>11</v>
       </c>
-      <c r="H139" s="5" t="s">
+      <c r="H139" s="17" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A140" s="10" t="s">
+      <c r="A140" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="B140" s="3">
+      <c r="B140" s="19">
         <v>45139</v>
       </c>
-      <c r="C140" s="3">
+      <c r="C140" s="19">
         <v>45153</v>
       </c>
-      <c r="D140" s="3">
+      <c r="D140" s="19">
         <v>45137</v>
       </c>
-      <c r="E140" s="11" t="s">
+      <c r="E140" s="20" t="s">
         <v>234</v>
       </c>
-      <c r="F140" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G140" s="6">
+      <c r="F140" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G140" s="21">
         <v>145</v>
       </c>
-      <c r="H140" s="7" t="s">
+      <c r="H140" s="22" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A141" s="8" t="s">
+      <c r="A141" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="B141" s="2">
+      <c r="B141" s="14">
         <v>45106</v>
       </c>
-      <c r="C141" s="2">
+      <c r="C141" s="14">
         <v>45154</v>
       </c>
-      <c r="D141" s="2">
+      <c r="D141" s="14">
         <v>45169</v>
       </c>
-      <c r="E141" s="9" t="s">
+      <c r="E141" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="F141" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G141" s="4">
+      <c r="F141" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G141" s="16">
         <v>67</v>
       </c>
-      <c r="H141" s="5" t="s">
+      <c r="H141" s="17" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A142" s="10" t="s">
+      <c r="A142" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="B142" s="3">
+      <c r="B142" s="19">
         <v>45106</v>
       </c>
-      <c r="C142" s="3">
+      <c r="C142" s="19">
         <v>45154</v>
       </c>
-      <c r="D142" s="3">
+      <c r="D142" s="19">
         <v>45169</v>
       </c>
-      <c r="E142" s="11" t="s">
+      <c r="E142" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="F142" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G142" s="6">
+      <c r="F142" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G142" s="21">
         <v>5</v>
       </c>
-      <c r="H142" s="7" t="s">
+      <c r="H142" s="22" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A143" s="8" t="s">
+      <c r="A143" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="B143" s="2">
+      <c r="B143" s="14">
         <v>45106</v>
       </c>
-      <c r="C143" s="2">
+      <c r="C143" s="14">
         <v>45154</v>
       </c>
-      <c r="D143" s="2">
+      <c r="D143" s="14">
         <v>45169</v>
       </c>
-      <c r="E143" s="9" t="s">
+      <c r="E143" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="F143" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G143" s="4">
+      <c r="F143" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G143" s="16">
         <v>98</v>
       </c>
-      <c r="H143" s="5" t="s">
+      <c r="H143" s="17" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A144" s="10" t="s">
+      <c r="A144" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="B144" s="3">
+      <c r="B144" s="19">
         <v>45106</v>
       </c>
-      <c r="C144" s="3">
+      <c r="C144" s="19">
         <v>45154</v>
       </c>
-      <c r="D144" s="3">
+      <c r="D144" s="19">
         <v>45169</v>
       </c>
-      <c r="E144" s="11" t="s">
+      <c r="E144" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="F144" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G144" s="6">
+      <c r="F144" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G144" s="21">
         <v>5</v>
       </c>
-      <c r="H144" s="7" t="s">
+      <c r="H144" s="22" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A145" s="8" t="s">
+      <c r="A145" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="B145" s="2">
+      <c r="B145" s="14">
         <v>45139</v>
       </c>
-      <c r="C145" s="2">
+      <c r="C145" s="14">
         <v>45154</v>
       </c>
-      <c r="D145" s="2">
+      <c r="D145" s="14">
         <v>45137</v>
       </c>
-      <c r="E145" s="9" t="s">
+      <c r="E145" s="15" t="s">
         <v>234</v>
       </c>
-      <c r="F145" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G145" s="4">
+      <c r="F145" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G145" s="16">
         <v>58</v>
       </c>
-      <c r="H145" s="5" t="s">
+      <c r="H145" s="17" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A146" s="10" t="s">
+      <c r="A146" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="B146" s="3">
+      <c r="B146" s="19">
         <v>45139</v>
       </c>
-      <c r="C146" s="3">
+      <c r="C146" s="19">
         <v>45154</v>
       </c>
-      <c r="D146" s="3">
+      <c r="D146" s="19">
         <v>45137</v>
       </c>
-      <c r="E146" s="11" t="s">
+      <c r="E146" s="20" t="s">
         <v>234</v>
       </c>
-      <c r="F146" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G146" s="6">
+      <c r="F146" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G146" s="21">
         <v>43</v>
       </c>
-      <c r="H146" s="7" t="s">
+      <c r="H146" s="22" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A147" s="8" t="s">
+      <c r="A147" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="B147" s="2">
+      <c r="B147" s="14">
         <v>45139</v>
       </c>
-      <c r="C147" s="2">
+      <c r="C147" s="14">
         <v>45154</v>
       </c>
-      <c r="D147" s="2">
+      <c r="D147" s="14">
         <v>45137</v>
       </c>
-      <c r="E147" s="9" t="s">
+      <c r="E147" s="15" t="s">
         <v>234</v>
       </c>
-      <c r="F147" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G147" s="4">
+      <c r="F147" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G147" s="16">
         <v>2</v>
       </c>
-      <c r="H147" s="5" t="s">
+      <c r="H147" s="17" t="s">
         <v>261</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A148" s="10" t="s">
+      <c r="A148" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="B148" s="3">
+      <c r="B148" s="19">
         <v>45139</v>
       </c>
-      <c r="C148" s="3">
+      <c r="C148" s="19">
         <v>45155</v>
       </c>
-      <c r="D148" s="3">
+      <c r="D148" s="19">
         <v>45137</v>
       </c>
-      <c r="E148" s="11" t="s">
+      <c r="E148" s="20" t="s">
         <v>234</v>
       </c>
-      <c r="F148" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G148" s="6">
+      <c r="F148" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G148" s="21">
         <v>257</v>
       </c>
-      <c r="H148" s="7" t="s">
+      <c r="H148" s="22" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A149" s="8" t="s">
+      <c r="A149" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="B149" s="2">
+      <c r="B149" s="14">
         <v>45139</v>
       </c>
-      <c r="C149" s="2">
+      <c r="C149" s="14">
         <v>45155</v>
       </c>
-      <c r="D149" s="2">
+      <c r="D149" s="14">
         <v>45137</v>
       </c>
-      <c r="E149" s="9" t="s">
+      <c r="E149" s="15" t="s">
         <v>234</v>
       </c>
-      <c r="F149" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G149" s="4">
+      <c r="F149" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G149" s="16">
         <v>1</v>
       </c>
-      <c r="H149" s="5" t="s">
+      <c r="H149" s="17" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A150" s="10" t="s">
+      <c r="A150" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="B150" s="3">
+      <c r="B150" s="19">
         <v>45139</v>
       </c>
-      <c r="C150" s="3">
+      <c r="C150" s="19">
         <v>45155</v>
       </c>
-      <c r="D150" s="3">
+      <c r="D150" s="19">
         <v>45137</v>
       </c>
-      <c r="E150" s="11" t="s">
+      <c r="E150" s="20" t="s">
         <v>234</v>
       </c>
-      <c r="F150" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G150" s="6">
+      <c r="F150" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G150" s="21">
         <v>120</v>
       </c>
-      <c r="H150" s="7" t="s">
+      <c r="H150" s="22" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A151" s="8" t="s">
+      <c r="A151" s="13" t="s">
         <v>212</v>
       </c>
-      <c r="B151" s="2">
+      <c r="B151" s="14">
         <v>45139</v>
       </c>
-      <c r="C151" s="2">
+      <c r="C151" s="14">
         <v>45155</v>
       </c>
-      <c r="D151" s="2">
+      <c r="D151" s="14">
         <v>45137</v>
       </c>
-      <c r="E151" s="9" t="s">
+      <c r="E151" s="15" t="s">
         <v>234</v>
       </c>
-      <c r="F151" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G151" s="4">
+      <c r="F151" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G151" s="16">
         <v>1</v>
       </c>
-      <c r="H151" s="5" t="s">
+      <c r="H151" s="17" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A152" s="10" t="s">
+      <c r="A152" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="B152" s="3">
+      <c r="B152" s="19">
         <v>45139</v>
       </c>
-      <c r="C152" s="3">
+      <c r="C152" s="19">
         <v>45156</v>
       </c>
-      <c r="D152" s="3">
+      <c r="D152" s="19">
         <v>45137</v>
       </c>
-      <c r="E152" s="11" t="s">
+      <c r="E152" s="20" t="s">
         <v>234</v>
       </c>
-      <c r="F152" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G152" s="6">
+      <c r="F152" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G152" s="21">
         <v>99</v>
       </c>
-      <c r="H152" s="7" t="s">
+      <c r="H152" s="22" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A153" s="8" t="s">
+      <c r="A153" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="B153" s="2">
+      <c r="B153" s="14">
         <v>45139</v>
       </c>
-      <c r="C153" s="2">
+      <c r="C153" s="14">
         <v>45156</v>
       </c>
-      <c r="D153" s="2">
+      <c r="D153" s="14">
         <v>45137</v>
       </c>
-      <c r="E153" s="9" t="s">
+      <c r="E153" s="15" t="s">
         <v>234</v>
       </c>
-      <c r="F153" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G153" s="4">
+      <c r="F153" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G153" s="16">
         <v>66</v>
       </c>
-      <c r="H153" s="5" t="s">
+      <c r="H153" s="17" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A154" s="10" t="s">
+      <c r="A154" s="18" t="s">
         <v>268</v>
       </c>
-      <c r="B154" s="3">
+      <c r="B154" s="19">
         <v>45139</v>
       </c>
-      <c r="C154" s="3">
+      <c r="C154" s="19">
         <v>45156</v>
       </c>
-      <c r="D154" s="3">
+      <c r="D154" s="19">
         <v>45137</v>
       </c>
-      <c r="E154" s="11" t="s">
+      <c r="E154" s="20" t="s">
         <v>234</v>
       </c>
-      <c r="F154" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G154" s="6">
+      <c r="F154" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G154" s="21">
         <v>4</v>
       </c>
-      <c r="H154" s="7" t="s">
+      <c r="H154" s="22" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A155" s="8" t="s">
+      <c r="A155" s="13" t="s">
         <v>270</v>
       </c>
-      <c r="B155" s="2">
+      <c r="B155" s="14">
         <v>45139</v>
       </c>
-      <c r="C155" s="2">
+      <c r="C155" s="14">
         <v>45156</v>
       </c>
-      <c r="D155" s="2">
+      <c r="D155" s="14">
         <v>45137</v>
       </c>
-      <c r="E155" s="9" t="s">
+      <c r="E155" s="15" t="s">
         <v>234</v>
       </c>
-      <c r="F155" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G155" s="4">
-        <v>15</v>
-      </c>
-      <c r="H155" s="5" t="s">
+      <c r="F155" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G155" s="16">
+        <v>15</v>
+      </c>
+      <c r="H155" s="17" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A156" s="10" t="s">
+      <c r="A156" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="B156" s="3">
+      <c r="B156" s="19">
         <v>45139</v>
       </c>
-      <c r="C156" s="3">
+      <c r="C156" s="19">
         <v>45156</v>
       </c>
-      <c r="D156" s="3">
+      <c r="D156" s="19">
         <v>45137</v>
       </c>
-      <c r="E156" s="11" t="s">
+      <c r="E156" s="20" t="s">
         <v>234</v>
       </c>
-      <c r="F156" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G156" s="6">
+      <c r="F156" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G156" s="21">
         <v>27</v>
       </c>
-      <c r="H156" s="7" t="s">
+      <c r="H156" s="22" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A157" s="8" t="s">
+      <c r="A157" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="B157" s="2">
+      <c r="B157" s="14">
         <v>45139</v>
       </c>
-      <c r="C157" s="2">
+      <c r="C157" s="14">
         <v>45156</v>
       </c>
-      <c r="D157" s="2">
+      <c r="D157" s="14">
         <v>45137</v>
       </c>
-      <c r="E157" s="9" t="s">
+      <c r="E157" s="15" t="s">
         <v>234</v>
       </c>
-      <c r="F157" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G157" s="4">
+      <c r="F157" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G157" s="16">
         <v>102</v>
       </c>
-      <c r="H157" s="5" t="s">
+      <c r="H157" s="17" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A158" s="10" t="s">
+      <c r="A158" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="B158" s="3">
+      <c r="B158" s="19">
         <v>45139</v>
       </c>
-      <c r="C158" s="3">
+      <c r="C158" s="19">
         <v>45156</v>
       </c>
-      <c r="D158" s="3">
+      <c r="D158" s="19">
         <v>45137</v>
       </c>
-      <c r="E158" s="11" t="s">
+      <c r="E158" s="20" t="s">
         <v>234</v>
       </c>
-      <c r="F158" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G158" s="6">
+      <c r="F158" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G158" s="21">
         <v>2</v>
       </c>
-      <c r="H158" s="7" t="s">
+      <c r="H158" s="22" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A159" s="8" t="s">
+      <c r="A159" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="B159" s="2">
+      <c r="B159" s="14">
         <v>45139</v>
       </c>
-      <c r="C159" s="2">
+      <c r="C159" s="14">
         <v>45156</v>
       </c>
-      <c r="D159" s="2">
+      <c r="D159" s="14">
         <v>45137</v>
       </c>
-      <c r="E159" s="9" t="s">
+      <c r="E159" s="15" t="s">
         <v>234</v>
       </c>
-      <c r="F159" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G159" s="4">
+      <c r="F159" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G159" s="16">
         <v>169</v>
       </c>
-      <c r="H159" s="5" t="s">
+      <c r="H159" s="17" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A160" s="10" t="s">
+      <c r="A160" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="B160" s="3">
+      <c r="B160" s="19">
         <v>45139</v>
       </c>
-      <c r="C160" s="3">
+      <c r="C160" s="19">
         <v>45156</v>
       </c>
-      <c r="D160" s="3">
+      <c r="D160" s="19">
         <v>45137</v>
       </c>
-      <c r="E160" s="11" t="s">
+      <c r="E160" s="20" t="s">
         <v>234</v>
       </c>
-      <c r="F160" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G160" s="6">
+      <c r="F160" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G160" s="21">
         <v>70</v>
       </c>
-      <c r="H160" s="7" t="s">
+      <c r="H160" s="22" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A161" s="8" t="s">
+      <c r="A161" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="B161" s="2">
+      <c r="B161" s="14">
         <v>45139</v>
       </c>
-      <c r="C161" s="2">
+      <c r="C161" s="14">
         <v>45156</v>
       </c>
-      <c r="D161" s="2">
+      <c r="D161" s="14">
         <v>45137</v>
       </c>
-      <c r="E161" s="9" t="s">
+      <c r="E161" s="15" t="s">
         <v>234</v>
       </c>
-      <c r="F161" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G161" s="4">
+      <c r="F161" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G161" s="16">
         <v>22</v>
       </c>
-      <c r="H161" s="5" t="s">
+      <c r="H161" s="17" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A162" s="10" t="s">
+      <c r="A162" s="18" t="s">
         <v>278</v>
       </c>
-      <c r="B162" s="3">
+      <c r="B162" s="19">
         <v>45139</v>
       </c>
-      <c r="C162" s="3">
+      <c r="C162" s="19">
         <v>45156</v>
       </c>
-      <c r="D162" s="3">
+      <c r="D162" s="19">
         <v>45137</v>
       </c>
-      <c r="E162" s="11" t="s">
+      <c r="E162" s="20" t="s">
         <v>234</v>
       </c>
-      <c r="F162" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G162" s="6">
+      <c r="F162" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G162" s="21">
         <v>4</v>
       </c>
-      <c r="H162" s="7" t="s">
+      <c r="H162" s="22" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A163" s="8" t="s">
+      <c r="A163" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="B163" s="2">
+      <c r="B163" s="14">
         <v>45139</v>
       </c>
-      <c r="C163" s="2">
+      <c r="C163" s="14">
         <v>45156</v>
       </c>
-      <c r="D163" s="2">
+      <c r="D163" s="14">
         <v>45137</v>
       </c>
-      <c r="E163" s="9" t="s">
+      <c r="E163" s="15" t="s">
         <v>234</v>
       </c>
-      <c r="F163" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G163" s="4">
+      <c r="F163" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G163" s="16">
         <v>29</v>
       </c>
-      <c r="H163" s="5" t="s">
+      <c r="H163" s="17" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A164" s="10" t="s">
+      <c r="A164" s="18" t="s">
         <v>175</v>
       </c>
-      <c r="B164" s="3">
+      <c r="B164" s="19">
         <v>45139</v>
       </c>
-      <c r="C164" s="3">
+      <c r="C164" s="19">
         <v>45156</v>
       </c>
-      <c r="D164" s="3">
+      <c r="D164" s="19">
         <v>45137</v>
       </c>
-      <c r="E164" s="11" t="s">
+      <c r="E164" s="20" t="s">
         <v>234</v>
       </c>
-      <c r="F164" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G164" s="6">
+      <c r="F164" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G164" s="21">
         <v>23</v>
       </c>
-      <c r="H164" s="7" t="s">
+      <c r="H164" s="22" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A165" s="8" t="s">
+      <c r="A165" s="13" t="s">
         <v>282</v>
       </c>
-      <c r="B165" s="2">
+      <c r="B165" s="14">
         <v>45139</v>
       </c>
-      <c r="C165" s="2">
+      <c r="C165" s="14">
         <v>45156</v>
       </c>
-      <c r="D165" s="2">
+      <c r="D165" s="14">
         <v>45137</v>
       </c>
-      <c r="E165" s="9" t="s">
+      <c r="E165" s="15" t="s">
         <v>234</v>
       </c>
-      <c r="F165" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G165" s="4">
+      <c r="F165" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G165" s="16">
         <v>23</v>
       </c>
-      <c r="H165" s="5" t="s">
+      <c r="H165" s="17" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A166" s="10" t="s">
+      <c r="A166" s="18" t="s">
         <v>284</v>
       </c>
-      <c r="B166" s="3">
+      <c r="B166" s="19">
         <v>45139</v>
       </c>
-      <c r="C166" s="3">
+      <c r="C166" s="19">
         <v>45156</v>
       </c>
-      <c r="D166" s="3">
+      <c r="D166" s="19">
         <v>45137</v>
       </c>
-      <c r="E166" s="11" t="s">
+      <c r="E166" s="20" t="s">
         <v>234</v>
       </c>
-      <c r="F166" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G166" s="6">
+      <c r="F166" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G166" s="21">
         <v>58</v>
       </c>
-      <c r="H166" s="7" t="s">
+      <c r="H166" s="22" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A167" s="8" t="s">
+      <c r="A167" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="B167" s="2">
+      <c r="B167" s="14">
         <v>45117</v>
       </c>
-      <c r="C167" s="2">
+      <c r="C167" s="14">
         <v>45159</v>
       </c>
-      <c r="D167" s="2">
+      <c r="D167" s="14">
         <v>45179</v>
       </c>
-      <c r="E167" s="9" t="s">
+      <c r="E167" s="15" t="s">
         <v>286</v>
       </c>
-      <c r="F167" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G167" s="4">
+      <c r="F167" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G167" s="16">
         <v>29</v>
       </c>
-      <c r="H167" s="5" t="s">
+      <c r="H167" s="17" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A168" s="10" t="s">
+      <c r="A168" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="B168" s="3">
+      <c r="B168" s="19">
         <v>45119</v>
       </c>
-      <c r="C168" s="3">
+      <c r="C168" s="19">
         <v>45159</v>
       </c>
-      <c r="D168" s="3">
+      <c r="D168" s="19">
         <v>45184</v>
       </c>
-      <c r="E168" s="11" t="s">
+      <c r="E168" s="20" t="s">
         <v>288</v>
       </c>
-      <c r="F168" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G168" s="6">
+      <c r="F168" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G168" s="21">
         <v>21</v>
       </c>
-      <c r="H168" s="7" t="s">
+      <c r="H168" s="22" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A169" s="8" t="s">
+      <c r="A169" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="B169" s="2">
+      <c r="B169" s="14">
         <v>45121</v>
       </c>
-      <c r="C169" s="2">
+      <c r="C169" s="14">
         <v>45159</v>
       </c>
-      <c r="D169" s="2">
+      <c r="D169" s="14">
         <v>45121</v>
       </c>
-      <c r="E169" s="9" t="s">
+      <c r="E169" s="15" t="s">
         <v>290</v>
       </c>
-      <c r="F169" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G169" s="4">
+      <c r="F169" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G169" s="16">
         <v>58</v>
       </c>
-      <c r="H169" s="5" t="s">
+      <c r="H169" s="17" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A170" s="10" t="s">
+      <c r="A170" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="B170" s="3">
+      <c r="B170" s="19">
         <v>45139</v>
       </c>
-      <c r="C170" s="3">
+      <c r="C170" s="19">
         <v>45159</v>
       </c>
-      <c r="D170" s="3">
+      <c r="D170" s="19">
         <v>45250</v>
       </c>
-      <c r="E170" s="11" t="s">
+      <c r="E170" s="20" t="s">
         <v>292</v>
       </c>
-      <c r="F170" s="11" t="s">
+      <c r="F170" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="G170" s="6">
+      <c r="G170" s="21">
         <v>67</v>
       </c>
-      <c r="H170" s="7" t="s">
+      <c r="H170" s="22" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A171" s="8" t="s">
+      <c r="A171" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="B171" s="2">
+      <c r="B171" s="14">
         <v>45124</v>
       </c>
-      <c r="C171" s="2">
+      <c r="C171" s="14">
         <v>45161</v>
       </c>
-      <c r="D171" s="2">
+      <c r="D171" s="14">
         <v>45226</v>
       </c>
-      <c r="E171" s="9" t="s">
+      <c r="E171" s="15" t="s">
         <v>294</v>
       </c>
-      <c r="F171" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G171" s="4">
+      <c r="F171" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G171" s="16">
         <v>31</v>
       </c>
-      <c r="H171" s="5" t="s">
+      <c r="H171" s="17" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A172" s="10" t="s">
+      <c r="A172" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="B172" s="3">
+      <c r="B172" s="19">
         <v>45121</v>
       </c>
-      <c r="C172" s="3">
+      <c r="C172" s="19">
         <v>45161</v>
       </c>
-      <c r="D172" s="3">
+      <c r="D172" s="19">
         <v>45183</v>
       </c>
-      <c r="E172" s="11" t="s">
+      <c r="E172" s="20" t="s">
         <v>296</v>
       </c>
-      <c r="F172" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G172" s="6">
+      <c r="F172" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G172" s="21">
         <v>49</v>
       </c>
-      <c r="H172" s="7" t="s">
+      <c r="H172" s="22" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A173" s="8" t="s">
+      <c r="A173" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="B173" s="2">
+      <c r="B173" s="14">
         <v>45121</v>
       </c>
-      <c r="C173" s="2">
+      <c r="C173" s="14">
         <v>45161</v>
       </c>
-      <c r="D173" s="2">
+      <c r="D173" s="14">
         <v>45183</v>
       </c>
-      <c r="E173" s="9" t="s">
+      <c r="E173" s="15" t="s">
         <v>296</v>
       </c>
-      <c r="F173" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G173" s="4">
+      <c r="F173" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G173" s="16">
         <v>85</v>
       </c>
-      <c r="H173" s="5" t="s">
+      <c r="H173" s="17" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A174" s="10" t="s">
+      <c r="A174" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="B174" s="3">
+      <c r="B174" s="19">
         <v>45121</v>
       </c>
-      <c r="C174" s="3">
+      <c r="C174" s="19">
         <v>45161</v>
       </c>
-      <c r="D174" s="3">
+      <c r="D174" s="19">
         <v>45183</v>
       </c>
-      <c r="E174" s="11" t="s">
+      <c r="E174" s="20" t="s">
         <v>296</v>
       </c>
-      <c r="F174" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G174" s="6">
+      <c r="F174" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G174" s="21">
         <v>6</v>
       </c>
-      <c r="H174" s="7" t="s">
+      <c r="H174" s="22" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A175" s="8" t="s">
+      <c r="A175" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="B175" s="2">
+      <c r="B175" s="14">
         <v>45124</v>
       </c>
-      <c r="C175" s="2">
+      <c r="C175" s="14">
         <v>45161</v>
       </c>
-      <c r="D175" s="2">
+      <c r="D175" s="14">
         <v>45184</v>
       </c>
-      <c r="E175" s="9" t="s">
+      <c r="E175" s="15" t="s">
         <v>300</v>
       </c>
-      <c r="F175" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G175" s="4">
+      <c r="F175" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G175" s="16">
         <v>104</v>
       </c>
-      <c r="H175" s="5" t="s">
+      <c r="H175" s="17" t="s">
         <v>301</v>
       </c>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A176" s="10" t="s">
+      <c r="A176" s="18" t="s">
         <v>302</v>
       </c>
-      <c r="B176" s="3">
+      <c r="B176" s="19">
         <v>45126</v>
       </c>
-      <c r="C176" s="3">
+      <c r="C176" s="19">
         <v>45161</v>
       </c>
-      <c r="D176" s="3">
+      <c r="D176" s="19">
         <v>45186</v>
       </c>
-      <c r="E176" s="11" t="s">
+      <c r="E176" s="20" t="s">
         <v>303</v>
       </c>
-      <c r="F176" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G176" s="6">
+      <c r="F176" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G176" s="21">
         <v>6</v>
       </c>
-      <c r="H176" s="7" t="s">
+      <c r="H176" s="22" t="s">
         <v>304</v>
       </c>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A177" s="8" t="s">
+      <c r="A177" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="B177" s="2">
+      <c r="B177" s="14">
         <v>45128</v>
       </c>
-      <c r="C177" s="2">
+      <c r="C177" s="14">
         <v>45166</v>
       </c>
-      <c r="D177" s="2">
+      <c r="D177" s="14">
         <v>45240</v>
       </c>
-      <c r="E177" s="9" t="s">
+      <c r="E177" s="15" t="s">
         <v>305</v>
       </c>
-      <c r="F177" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G177" s="4">
+      <c r="F177" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G177" s="16">
         <v>100</v>
       </c>
-      <c r="H177" s="5" t="s">
+      <c r="H177" s="17" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A178" s="10" t="s">
+      <c r="A178" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="B178" s="3">
+      <c r="B178" s="19">
         <v>45128</v>
       </c>
-      <c r="C178" s="3">
+      <c r="C178" s="19">
         <v>45166</v>
       </c>
-      <c r="D178" s="3">
+      <c r="D178" s="19">
         <v>45240</v>
       </c>
-      <c r="E178" s="11" t="s">
+      <c r="E178" s="20" t="s">
         <v>305</v>
       </c>
-      <c r="F178" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G178" s="6">
+      <c r="F178" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G178" s="21">
         <v>140</v>
       </c>
-      <c r="H178" s="7" t="s">
+      <c r="H178" s="22" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A179" s="8" t="s">
+      <c r="A179" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="B179" s="2">
+      <c r="B179" s="14">
         <v>45131</v>
       </c>
-      <c r="C179" s="2">
+      <c r="C179" s="14">
         <v>45166</v>
       </c>
-      <c r="D179" s="2">
+      <c r="D179" s="14">
         <v>45198</v>
       </c>
-      <c r="E179" s="9" t="s">
+      <c r="E179" s="15" t="s">
         <v>308</v>
       </c>
-      <c r="F179" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G179" s="4">
+      <c r="F179" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G179" s="16">
         <v>90</v>
       </c>
-      <c r="H179" s="5" t="s">
+      <c r="H179" s="17" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A180" s="10" t="s">
+      <c r="A180" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="B180" s="3">
+      <c r="B180" s="19">
         <v>45125</v>
       </c>
-      <c r="C180" s="3">
+      <c r="C180" s="19">
         <v>45166</v>
       </c>
-      <c r="D180" s="3">
+      <c r="D180" s="19">
         <v>45184</v>
       </c>
-      <c r="E180" s="11" t="s">
+      <c r="E180" s="20" t="s">
         <v>310</v>
       </c>
-      <c r="F180" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G180" s="6">
+      <c r="F180" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G180" s="21">
         <v>20</v>
       </c>
-      <c r="H180" s="7" t="s">
+      <c r="H180" s="22" t="s">
         <v>311</v>
       </c>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A181" s="8" t="s">
+      <c r="A181" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="B181" s="2">
+      <c r="B181" s="14">
         <v>45126</v>
       </c>
-      <c r="C181" s="2">
+      <c r="C181" s="14">
         <v>45166</v>
       </c>
-      <c r="D181" s="2">
+      <c r="D181" s="14">
         <v>45188</v>
       </c>
-      <c r="E181" s="9" t="s">
+      <c r="E181" s="15" t="s">
         <v>312</v>
       </c>
-      <c r="F181" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G181" s="4">
+      <c r="F181" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G181" s="16">
         <v>55</v>
       </c>
-      <c r="H181" s="5" t="s">
+      <c r="H181" s="17" t="s">
         <v>313</v>
       </c>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A182" s="10" t="s">
+      <c r="A182" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="B182" s="3">
+      <c r="B182" s="19">
         <v>45131</v>
       </c>
-      <c r="C182" s="3">
+      <c r="C182" s="19">
         <v>45167</v>
       </c>
-      <c r="D182" s="3">
+      <c r="D182" s="19">
         <v>45191</v>
       </c>
-      <c r="E182" s="11" t="s">
+      <c r="E182" s="20" t="s">
         <v>314</v>
       </c>
-      <c r="F182" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G182" s="6">
+      <c r="F182" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G182" s="21">
         <v>151</v>
       </c>
-      <c r="H182" s="7" t="s">
+      <c r="H182" s="22" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A183" s="8" t="s">
+      <c r="A183" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="B183" s="2">
+      <c r="B183" s="14">
         <v>45131</v>
       </c>
-      <c r="C183" s="2">
+      <c r="C183" s="14">
         <v>45167</v>
       </c>
-      <c r="D183" s="2">
+      <c r="D183" s="14">
         <v>45135</v>
       </c>
-      <c r="E183" s="9" t="s">
+      <c r="E183" s="15" t="s">
         <v>316</v>
       </c>
-      <c r="F183" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G183" s="4">
+      <c r="F183" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G183" s="16">
         <v>47</v>
       </c>
-      <c r="H183" s="5" t="s">
+      <c r="H183" s="17" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A184" s="10" t="s">
+      <c r="A184" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="B184" s="3">
+      <c r="B184" s="19">
         <v>45131</v>
       </c>
-      <c r="C184" s="3">
+      <c r="C184" s="19">
         <v>45167</v>
       </c>
-      <c r="D184" s="3">
+      <c r="D184" s="19">
         <v>45226</v>
       </c>
-      <c r="E184" s="11" t="s">
+      <c r="E184" s="20" t="s">
         <v>316</v>
       </c>
-      <c r="F184" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G184" s="6">
+      <c r="F184" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G184" s="21">
         <v>9</v>
       </c>
-      <c r="H184" s="7" t="s">
+      <c r="H184" s="22" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A185" s="8" t="s">
+      <c r="A185" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="B185" s="2">
+      <c r="B185" s="14">
         <v>45127</v>
       </c>
-      <c r="C185" s="2">
+      <c r="C185" s="14">
         <v>45168</v>
       </c>
-      <c r="D185" s="2">
+      <c r="D185" s="14">
         <v>45199</v>
       </c>
-      <c r="E185" s="9" t="s">
+      <c r="E185" s="15" t="s">
         <v>318</v>
       </c>
-      <c r="F185" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G185" s="4">
+      <c r="F185" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G185" s="16">
         <v>28</v>
       </c>
-      <c r="H185" s="5" t="s">
+      <c r="H185" s="17" t="s">
         <v>319</v>
       </c>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A186" s="10" t="s">
+      <c r="A186" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="B186" s="3">
+      <c r="B186" s="19">
         <v>45127</v>
       </c>
-      <c r="C186" s="3">
+      <c r="C186" s="19">
         <v>45168</v>
       </c>
-      <c r="D186" s="3">
+      <c r="D186" s="19">
         <v>45199</v>
       </c>
-      <c r="E186" s="11" t="s">
+      <c r="E186" s="20" t="s">
         <v>318</v>
       </c>
-      <c r="F186" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G186" s="6">
+      <c r="F186" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G186" s="21">
         <v>31</v>
       </c>
-      <c r="H186" s="7" t="s">
+      <c r="H186" s="22" t="s">
         <v>320</v>
       </c>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A187" s="8" t="s">
+      <c r="A187" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="B187" s="2">
+      <c r="B187" s="14">
         <v>45159</v>
       </c>
-      <c r="C187" s="2">
+      <c r="C187" s="14">
         <v>45168</v>
       </c>
-      <c r="D187" s="2">
+      <c r="D187" s="14">
         <v>45224</v>
       </c>
-      <c r="E187" s="9" t="s">
+      <c r="E187" s="15" t="s">
         <v>321</v>
       </c>
-      <c r="F187" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G187" s="4">
+      <c r="F187" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G187" s="16">
         <v>85</v>
       </c>
-      <c r="H187" s="5" t="s">
+      <c r="H187" s="17" t="s">
         <v>322</v>
       </c>
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A188" s="10" t="s">
+      <c r="A188" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="B188" s="3">
+      <c r="B188" s="19">
         <v>45127</v>
       </c>
-      <c r="C188" s="3">
+      <c r="C188" s="19">
         <v>45168</v>
       </c>
-      <c r="D188" s="3">
+      <c r="D188" s="19">
         <v>45191</v>
       </c>
-      <c r="E188" s="11" t="s">
+      <c r="E188" s="20" t="s">
         <v>323</v>
       </c>
-      <c r="F188" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G188" s="6">
+      <c r="F188" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G188" s="21">
         <v>2</v>
       </c>
-      <c r="H188" s="7" t="s">
+      <c r="H188" s="22" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A189" s="8" t="s">
+      <c r="A189" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="B189" s="2">
+      <c r="B189" s="14">
         <v>45127</v>
       </c>
-      <c r="C189" s="2">
+      <c r="C189" s="14">
         <v>45168</v>
       </c>
-      <c r="D189" s="2">
+      <c r="D189" s="14">
         <v>45191</v>
       </c>
-      <c r="E189" s="9" t="s">
+      <c r="E189" s="15" t="s">
         <v>323</v>
       </c>
-      <c r="F189" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G189" s="4">
+      <c r="F189" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G189" s="16">
         <v>59</v>
       </c>
-      <c r="H189" s="5" t="s">
+      <c r="H189" s="17" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A190" s="10" t="s">
+      <c r="A190" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="B190" s="3">
+      <c r="B190" s="19">
         <v>45127</v>
       </c>
-      <c r="C190" s="3">
+      <c r="C190" s="19">
         <v>45168</v>
       </c>
-      <c r="D190" s="3">
+      <c r="D190" s="19">
         <v>45191</v>
       </c>
-      <c r="E190" s="11" t="s">
+      <c r="E190" s="20" t="s">
         <v>323</v>
       </c>
-      <c r="F190" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G190" s="6">
+      <c r="F190" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G190" s="21">
         <v>2</v>
       </c>
-      <c r="H190" s="7" t="s">
+      <c r="H190" s="22" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A191" s="8" t="s">
+      <c r="A191" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="B191" s="2">
+      <c r="B191" s="14">
         <v>45127</v>
       </c>
-      <c r="C191" s="2">
+      <c r="C191" s="14">
         <v>45168</v>
       </c>
-      <c r="D191" s="2">
+      <c r="D191" s="14">
         <v>45191</v>
       </c>
-      <c r="E191" s="9" t="s">
+      <c r="E191" s="15" t="s">
         <v>323</v>
       </c>
-      <c r="F191" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G191" s="4">
+      <c r="F191" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G191" s="16">
         <v>24</v>
       </c>
-      <c r="H191" s="5" t="s">
+      <c r="H191" s="17" t="s">
         <v>327</v>
       </c>
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A192" s="10" t="s">
+      <c r="A192" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="B192" s="3">
+      <c r="B192" s="19">
         <v>45127</v>
       </c>
-      <c r="C192" s="3">
+      <c r="C192" s="19">
         <v>45168</v>
       </c>
-      <c r="D192" s="3">
+      <c r="D192" s="19">
         <v>45191</v>
       </c>
-      <c r="E192" s="11" t="s">
+      <c r="E192" s="20" t="s">
         <v>323</v>
       </c>
-      <c r="F192" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G192" s="6">
+      <c r="F192" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G192" s="21">
         <v>3</v>
       </c>
-      <c r="H192" s="7" t="s">
+      <c r="H192" s="22" t="s">
         <v>328</v>
       </c>
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A193" s="8" t="s">
+      <c r="A193" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="B193" s="2">
+      <c r="B193" s="14">
         <v>45133</v>
       </c>
-      <c r="C193" s="2">
+      <c r="C193" s="14">
         <v>45168</v>
       </c>
-      <c r="D193" s="2">
+      <c r="D193" s="14">
         <v>45199</v>
       </c>
-      <c r="E193" s="9" t="s">
+      <c r="E193" s="15" t="s">
         <v>329</v>
       </c>
-      <c r="F193" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G193" s="4">
-        <v>16</v>
-      </c>
-      <c r="H193" s="5" t="s">
+      <c r="F193" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G193" s="16">
+        <v>16</v>
+      </c>
+      <c r="H193" s="17" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A194" s="10" t="s">
+      <c r="A194" s="18" t="s">
         <v>302</v>
       </c>
-      <c r="B194" s="3">
+      <c r="B194" s="19">
         <v>45133</v>
       </c>
-      <c r="C194" s="3">
+      <c r="C194" s="19">
         <v>45168</v>
       </c>
-      <c r="D194" s="3">
+      <c r="D194" s="19">
         <v>45191</v>
       </c>
-      <c r="E194" s="11" t="s">
+      <c r="E194" s="20" t="s">
         <v>331</v>
       </c>
-      <c r="F194" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G194" s="6">
+      <c r="F194" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G194" s="21">
         <v>43</v>
       </c>
-      <c r="H194" s="7" t="s">
+      <c r="H194" s="22" t="s">
         <v>332</v>
       </c>
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A195" s="8" t="s">
+      <c r="A195" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="B195" s="2">
+      <c r="B195" s="14">
         <v>45134</v>
       </c>
-      <c r="C195" s="2">
+      <c r="C195" s="14">
         <v>45169</v>
       </c>
-      <c r="D195" s="2">
+      <c r="D195" s="14">
         <v>45197</v>
       </c>
-      <c r="E195" s="9" t="s">
+      <c r="E195" s="15" t="s">
         <v>333</v>
       </c>
-      <c r="F195" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G195" s="4">
+      <c r="F195" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G195" s="16">
         <v>41</v>
       </c>
-      <c r="H195" s="5" t="s">
+      <c r="H195" s="17" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A196" s="10" t="s">
+      <c r="A196" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="B196" s="3">
+      <c r="B196" s="19">
         <v>45134</v>
       </c>
-      <c r="C196" s="3">
+      <c r="C196" s="19">
         <v>45169</v>
       </c>
-      <c r="D196" s="3">
+      <c r="D196" s="19">
         <v>45135</v>
       </c>
-      <c r="E196" s="11" t="s">
+      <c r="E196" s="20" t="s">
         <v>335</v>
       </c>
-      <c r="F196" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G196" s="6">
+      <c r="F196" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G196" s="21">
         <v>61</v>
       </c>
-      <c r="H196" s="7" t="s">
+      <c r="H196" s="22" t="s">
         <v>336</v>
       </c>
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A197" s="8" t="s">
+      <c r="A197" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="B197" s="2">
+      <c r="B197" s="14">
         <v>45134</v>
       </c>
-      <c r="C197" s="2">
+      <c r="C197" s="14">
         <v>45169</v>
       </c>
-      <c r="D197" s="2">
+      <c r="D197" s="14">
         <v>45199</v>
       </c>
-      <c r="E197" s="9" t="s">
+      <c r="E197" s="15" t="s">
         <v>337</v>
       </c>
-      <c r="F197" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G197" s="4">
+      <c r="F197" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G197" s="16">
         <v>84</v>
       </c>
-      <c r="H197" s="5" t="s">
+      <c r="H197" s="17" t="s">
         <v>338</v>
       </c>
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A198" s="10" t="s">
+      <c r="A198" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="B198" s="3">
+      <c r="B198" s="19">
         <v>45138</v>
       </c>
-      <c r="C198" s="3">
+      <c r="C198" s="19">
         <v>45170</v>
       </c>
-      <c r="D198" s="3">
+      <c r="D198" s="19">
         <v>45199</v>
       </c>
-      <c r="E198" s="11" t="s">
+      <c r="E198" s="20" t="s">
         <v>339</v>
       </c>
-      <c r="F198" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G198" s="6">
+      <c r="F198" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G198" s="21">
         <v>96</v>
       </c>
-      <c r="H198" s="7" t="s">
+      <c r="H198" s="22" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A199" s="8" t="s">
+      <c r="A199" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="B199" s="2">
+      <c r="B199" s="14">
         <v>45135</v>
       </c>
-      <c r="C199" s="2">
+      <c r="C199" s="14">
         <v>45175</v>
       </c>
-      <c r="D199" s="2">
+      <c r="D199" s="14">
         <v>45198</v>
       </c>
-      <c r="E199" s="9" t="s">
+      <c r="E199" s="15" t="s">
         <v>341</v>
       </c>
-      <c r="F199" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G199" s="4">
+      <c r="F199" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G199" s="16">
         <v>12</v>
       </c>
-      <c r="H199" s="5" t="s">
+      <c r="H199" s="17" t="s">
         <v>342</v>
       </c>
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A200" s="10" t="s">
+      <c r="A200" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="B200" s="3">
+      <c r="B200" s="19">
         <v>45134</v>
       </c>
-      <c r="C200" s="3">
+      <c r="C200" s="19">
         <v>45175</v>
       </c>
-      <c r="D200" s="3">
+      <c r="D200" s="19">
         <v>45198</v>
       </c>
-      <c r="E200" s="11" t="s">
+      <c r="E200" s="20" t="s">
         <v>343</v>
       </c>
-      <c r="F200" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G200" s="6">
+      <c r="F200" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G200" s="21">
         <v>12</v>
       </c>
-      <c r="H200" s="7" t="s">
+      <c r="H200" s="22" t="s">
         <v>344</v>
       </c>
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A201" s="8" t="s">
+      <c r="A201" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="B201" s="2">
+      <c r="B201" s="14">
         <v>45135</v>
       </c>
-      <c r="C201" s="2">
+      <c r="C201" s="14">
         <v>45175</v>
       </c>
-      <c r="D201" s="2">
+      <c r="D201" s="14">
         <v>45198</v>
       </c>
-      <c r="E201" s="9" t="s">
+      <c r="E201" s="15" t="s">
         <v>341</v>
       </c>
-      <c r="F201" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G201" s="4">
+      <c r="F201" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G201" s="16">
         <v>26</v>
       </c>
-      <c r="H201" s="5" t="s">
+      <c r="H201" s="17" t="s">
         <v>345</v>
       </c>
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A202" s="10" t="s">
+      <c r="A202" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="B202" s="3">
+      <c r="B202" s="19">
         <v>45135</v>
       </c>
-      <c r="C202" s="3">
+      <c r="C202" s="19">
         <v>45175</v>
       </c>
-      <c r="D202" s="3">
+      <c r="D202" s="19">
         <v>45198</v>
       </c>
-      <c r="E202" s="11" t="s">
+      <c r="E202" s="20" t="s">
         <v>341</v>
       </c>
-      <c r="F202" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G202" s="6">
+      <c r="F202" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G202" s="21">
         <v>59</v>
       </c>
-      <c r="H202" s="7" t="s">
+      <c r="H202" s="22" t="s">
         <v>346</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A203" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B203" s="14">
+        <v>45134</v>
+      </c>
+      <c r="C203" s="14">
+        <v>45176</v>
+      </c>
+      <c r="D203" s="14">
+        <v>45199</v>
+      </c>
+      <c r="E203" s="15" t="s">
+        <v>349</v>
+      </c>
+      <c r="F203" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G203" s="16">
+        <v>34</v>
+      </c>
+      <c r="H203" s="17" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A204" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="B204" s="19">
+        <v>45107</v>
+      </c>
+      <c r="C204" s="19">
+        <v>45176</v>
+      </c>
+      <c r="D204" s="19">
+        <v>45170</v>
+      </c>
+      <c r="E204" s="20" t="s">
+        <v>351</v>
+      </c>
+      <c r="F204" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G204" s="21">
+        <v>25</v>
+      </c>
+      <c r="H204" s="22" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="205" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A205" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="B205" s="14">
+        <v>45134</v>
+      </c>
+      <c r="C205" s="14">
+        <v>45176</v>
+      </c>
+      <c r="D205" s="14">
+        <v>45199</v>
+      </c>
+      <c r="E205" s="15" t="s">
+        <v>349</v>
+      </c>
+      <c r="F205" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G205" s="16">
+        <v>31</v>
+      </c>
+      <c r="H205" s="17" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A206" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="B206" s="19">
+        <v>45139</v>
+      </c>
+      <c r="C206" s="19">
+        <v>45177</v>
+      </c>
+      <c r="D206" s="19">
+        <v>45199</v>
+      </c>
+      <c r="E206" s="20" t="s">
+        <v>354</v>
+      </c>
+      <c r="F206" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G206" s="21">
+        <v>58</v>
+      </c>
+      <c r="H206" s="22" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A207" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="B207" s="14">
+        <v>45139</v>
+      </c>
+      <c r="C207" s="14">
+        <v>45177</v>
+      </c>
+      <c r="D207" s="14">
+        <v>45201</v>
+      </c>
+      <c r="E207" s="15" t="s">
+        <v>356</v>
+      </c>
+      <c r="F207" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G207" s="16">
+        <v>85</v>
+      </c>
+      <c r="H207" s="17" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A208" s="18" t="s">
+        <v>236</v>
+      </c>
+      <c r="B208" s="19">
+        <v>45128</v>
+      </c>
+      <c r="C208" s="19">
+        <v>45180</v>
+      </c>
+      <c r="D208" s="19">
+        <v>45194</v>
+      </c>
+      <c r="E208" s="20" t="s">
+        <v>358</v>
+      </c>
+      <c r="F208" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="G208" s="21">
+        <v>54</v>
+      </c>
+      <c r="H208" s="22" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A209" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="B209" s="14">
+        <v>45139</v>
+      </c>
+      <c r="C209" s="14">
+        <v>45180</v>
+      </c>
+      <c r="D209" s="14">
+        <v>45199</v>
+      </c>
+      <c r="E209" s="15" t="s">
+        <v>360</v>
+      </c>
+      <c r="F209" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G209" s="16">
+        <v>152</v>
+      </c>
+      <c r="H209" s="17" t="s">
+        <v>361</v>
       </c>
     </row>
   </sheetData>
@@ -7685,6 +7898,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -7693,7 +7912,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Unknown Document Type" ma:contentTypeID="0x010104" ma:contentTypeVersion="0" ma:contentTypeDescription="" ma:contentTypeScope="" ma:versionID="05d83ceaa0bbd2e3bc716e6e66bd857a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b3d69fe45253d5ff147bb69036b756a7">
     <xsd:element name="properties">
@@ -7807,22 +8026,25 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A7B30132-FE9F-42B5-80C0-84081E76EB11}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BD6915D8-292A-4C72-84B0-36610D772FCD}">
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FD0AB034-9D49-434D-B66A-864CC083AA06}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47E0AC38-C849-489B-B8A8-2905A6DC5595}">
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84F1102D-7CFD-420C-84AE-7A62FA48FE59}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
@@ -7835,13 +8057,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2BC2501-B538-4C33-94E3-119E21104840}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data/warn-scraper/cache/ca/warn_report1.xlsx
+++ b/data/warn-scraper/cache/ca/warn_report1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jochoa2\Documents\Web Testing\DAT VR Results\RID1547-WARN_Report1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jochoa2\Desktop\Conditional Approvals\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59E0E291-61AF-4899-924B-632A0ED84E0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79497DDC-D4BF-4552-80EE-47C5F4E53320}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
+    <workbookView xWindow="14310" yWindow="-16320" windowWidth="29040" windowHeight="15840" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
   <sheets>
     <sheet name="Index" sheetId="3" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="851" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="875" uniqueCount="374">
   <si>
     <t>County/Parish</t>
   </si>
@@ -1190,6 +1190,39 @@
     <t>One Sansome Street, 33rd Floor  San Francisco CA 94104</t>
   </si>
   <si>
+    <t>Sunrun Inc.</t>
+  </si>
+  <si>
+    <t>12830 Romandel Avenue  Santa Fe Springs CA 90670</t>
+  </si>
+  <si>
+    <t>Cisco Systems, Inc.</t>
+  </si>
+  <si>
+    <t>560 McCarthy Blvd.  Milpitas CA 95035</t>
+  </si>
+  <si>
+    <t>170 West Tasman Drive  San Jose CA 95134</t>
+  </si>
+  <si>
+    <t>Company 3/Method Inc</t>
+  </si>
+  <si>
+    <t>San Luis Obispo County</t>
+  </si>
+  <si>
+    <t>Beyond Hello CA, LLC</t>
+  </si>
+  <si>
+    <t>923 Huber Street  Grover Beach CA 93433</t>
+  </si>
+  <si>
+    <t>ATI Restoration, LLC</t>
+  </si>
+  <si>
+    <t>3242 Airway Drive  Santa Rosa CA 95403</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">WARN REPORT - </t>
     </r>
@@ -1201,7 +1234,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>07/01/23 to 09/11/23</t>
+      <t>07/01/23 to 09/13/23</t>
     </r>
     <r>
       <rPr>
@@ -1221,7 +1254,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>A detailed WARN summary by county and filtered according to received date. Table Spans cells A2 through H209.</t>
+      <t>A detailed WARN summary by county and filtered according to received date. Table Spans cells A2 through H215.</t>
     </r>
   </si>
 </sst>
@@ -1317,7 +1350,6 @@
       <sz val="8"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -1529,8 +1561,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF0F0F0"/>
-          <bgColor rgb="FFF0F0F0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -1570,8 +1602,8 @@
       <numFmt numFmtId="165" formatCode="[$-10436]#,##0;\(#,##0\)"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF0F0F0"/>
-          <bgColor rgb="FFF0F0F0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -1610,8 +1642,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF0F0F0"/>
-          <bgColor rgb="FFF0F0F0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -1650,8 +1682,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF0F0F0"/>
-          <bgColor rgb="FFF0F0F0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -1691,8 +1723,8 @@
       <numFmt numFmtId="164" formatCode="[$-10409]mm/dd/yyyy"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF0F0F0"/>
-          <bgColor rgb="FFF0F0F0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -1732,8 +1764,8 @@
       <numFmt numFmtId="164" formatCode="[$-10409]mm/dd/yyyy"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF0F0F0"/>
-          <bgColor rgb="FFF0F0F0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -1773,8 +1805,8 @@
       <numFmt numFmtId="164" formatCode="[$-10409]mm/dd/yyyy"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF0F0F0"/>
-          <bgColor rgb="FFF0F0F0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -1813,8 +1845,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF0F0F0"/>
-          <bgColor rgb="FFF0F0F0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -2006,8 +2038,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:H209" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
-  <autoFilter ref="A2:H209" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:H215" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
+  <autoFilter ref="A2:H215" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -2391,7 +2423,7 @@
       </c>
       <c r="B3" s="6">
         <f>SUM('Detailed WARN Report '!G:G)</f>
-        <v>11238</v>
+        <v>11680</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -2400,7 +2432,7 @@
       </c>
       <c r="B4" s="6">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Permanent")</f>
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -2409,7 +2441,7 @@
       </c>
       <c r="B5" s="6">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Temporary")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -2427,7 +2459,7 @@
       </c>
       <c r="B7" s="6">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Permanent")</f>
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -2459,8 +2491,8 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:H209"/>
-  <sheetFormatPr defaultColWidth="46" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H215"/>
+  <sheetFormatPr defaultColWidth="26" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="4" width="8.7109375" bestFit="1" customWidth="1"/>
@@ -2472,7 +2504,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="117" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>362</v>
+        <v>373</v>
       </c>
       <c r="D1" s="7"/>
       <c r="E1" s="7"/>
@@ -7886,6 +7918,162 @@
       </c>
       <c r="H209" s="17" t="s">
         <v>361</v>
+      </c>
+    </row>
+    <row r="210" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A210" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="B210" s="19">
+        <v>45140</v>
+      </c>
+      <c r="C210" s="19">
+        <v>45181</v>
+      </c>
+      <c r="D210" s="19">
+        <v>45201</v>
+      </c>
+      <c r="E210" s="20" t="s">
+        <v>362</v>
+      </c>
+      <c r="F210" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G210" s="21">
+        <v>53</v>
+      </c>
+      <c r="H210" s="22" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A211" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B211" s="14">
+        <v>45124</v>
+      </c>
+      <c r="C211" s="14">
+        <v>45181</v>
+      </c>
+      <c r="D211" s="14">
+        <v>45215</v>
+      </c>
+      <c r="E211" s="15" t="s">
+        <v>364</v>
+      </c>
+      <c r="F211" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G211" s="16">
+        <v>123</v>
+      </c>
+      <c r="H211" s="17" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A212" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="B212" s="19">
+        <v>45124</v>
+      </c>
+      <c r="C212" s="19">
+        <v>45181</v>
+      </c>
+      <c r="D212" s="19">
+        <v>45215</v>
+      </c>
+      <c r="E212" s="20" t="s">
+        <v>364</v>
+      </c>
+      <c r="F212" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G212" s="21">
+        <v>227</v>
+      </c>
+      <c r="H212" s="22" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A213" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B213" s="14">
+        <v>45142</v>
+      </c>
+      <c r="C213" s="14">
+        <v>45182</v>
+      </c>
+      <c r="D213" s="14">
+        <v>45200</v>
+      </c>
+      <c r="E213" s="15" t="s">
+        <v>367</v>
+      </c>
+      <c r="F213" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="G213" s="16">
+        <v>19</v>
+      </c>
+      <c r="H213" s="17" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A214" s="18" t="s">
+        <v>368</v>
+      </c>
+      <c r="B214" s="19">
+        <v>45142</v>
+      </c>
+      <c r="C214" s="19">
+        <v>45182</v>
+      </c>
+      <c r="D214" s="19">
+        <v>45177</v>
+      </c>
+      <c r="E214" s="20" t="s">
+        <v>369</v>
+      </c>
+      <c r="F214" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G214" s="21">
+        <v>2</v>
+      </c>
+      <c r="H214" s="22" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A215" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="B215" s="14">
+        <v>45141</v>
+      </c>
+      <c r="C215" s="14">
+        <v>45182</v>
+      </c>
+      <c r="D215" s="14">
+        <v>45205</v>
+      </c>
+      <c r="E215" s="15" t="s">
+        <v>371</v>
+      </c>
+      <c r="F215" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G215" s="16">
+        <v>18</v>
+      </c>
+      <c r="H215" s="17" t="s">
+        <v>372</v>
       </c>
     </row>
   </sheetData>
@@ -8027,7 +8215,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A7B30132-FE9F-42B5-80C0-84081E76EB11}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AC06125-8442-4191-9EC7-BDA92AB0B9AD}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
@@ -8036,7 +8224,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FD0AB034-9D49-434D-B66A-864CC083AA06}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F17506A-DCE7-4082-BC3D-89E34E0EA76B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
@@ -8044,7 +8232,7 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84F1102D-7CFD-420C-84AE-7A62FA48FE59}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E8A2E801-96BC-43E9-A765-2CE49A3B3E09}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>

--- a/data/warn-scraper/cache/ca/warn_report1.xlsx
+++ b/data/warn-scraper/cache/ca/warn_report1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jochoa2\Desktop\Conditional Approvals\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79497DDC-D4BF-4552-80EE-47C5F4E53320}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{713F8B14-6760-4F80-9A4D-4A031D8361D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14310" yWindow="-16320" windowWidth="29040" windowHeight="15840" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="875" uniqueCount="374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="927" uniqueCount="392">
   <si>
     <t>County/Parish</t>
   </si>
@@ -1223,6 +1223,60 @@
     <t>3242 Airway Drive  Santa Rosa CA 95403</t>
   </si>
   <si>
+    <t>Rodan &amp; Fields, LLC</t>
+  </si>
+  <si>
+    <t>3001 Bishop Drive Suite 450  San Ramon CA 94583</t>
+  </si>
+  <si>
+    <t>1172 W. National Dr. Suite 50  Sacramento CA 95834</t>
+  </si>
+  <si>
+    <t>L3 Technologies, Inc., a wholly owned subsidiary of L3Harris Technologies</t>
+  </si>
+  <si>
+    <t>2436 Town Garden Rd.  Carlsbad CA 92009</t>
+  </si>
+  <si>
+    <t>dnata US Inflight Caterin</t>
+  </si>
+  <si>
+    <t>291 Coral Circle  El Segundo CA 90245</t>
+  </si>
+  <si>
+    <t>dnata US Inflight Catering</t>
+  </si>
+  <si>
+    <t>J.B. Hunt Transport, Inc.</t>
+  </si>
+  <si>
+    <t>5699 Las Positas Rd  Livermore CA 94551</t>
+  </si>
+  <si>
+    <t>Ericsson Inc.</t>
+  </si>
+  <si>
+    <t>3200 El Camino Real #180  Irvine CA 92602</t>
+  </si>
+  <si>
+    <t>4119 S. Market Ct., Bldg. A, Suite 20  Sacramento CA 95834</t>
+  </si>
+  <si>
+    <t>5885 Hollis St., STE 100  Emeryville CA 94608</t>
+  </si>
+  <si>
+    <t>URS Midwest, Inc dba United Road Services</t>
+  </si>
+  <si>
+    <t>741 Arcturus Avenue  Bakersfield CA 93303</t>
+  </si>
+  <si>
+    <t>Joy Signal Technology</t>
+  </si>
+  <si>
+    <t>1020 Marauder St  Chico CA 95973</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">WARN REPORT - </t>
     </r>
@@ -1234,7 +1288,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>07/01/23 to 09/13/23</t>
+      <t>07/01/23 to 09/18/23</t>
     </r>
     <r>
       <rPr>
@@ -1254,7 +1308,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>A detailed WARN summary by county and filtered according to received date. Table Spans cells A2 through H215.</t>
+      <t>A detailed WARN summary by county and filtered according to received date. Table Spans cells A2 through H228.</t>
     </r>
   </si>
 </sst>
@@ -1350,6 +1404,7 @@
       <sz val="8"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -2038,8 +2093,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:H215" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
-  <autoFilter ref="A2:H215" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:H228" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
+  <autoFilter ref="A2:H228" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -2423,7 +2478,7 @@
       </c>
       <c r="B3" s="6">
         <f>SUM('Detailed WARN Report '!G:G)</f>
-        <v>11680</v>
+        <v>12507</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -2432,7 +2487,7 @@
       </c>
       <c r="B4" s="6">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Permanent")</f>
-        <v>111</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -2459,7 +2514,7 @@
       </c>
       <c r="B7" s="6">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Permanent")</f>
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -2491,7 +2546,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:H215"/>
+  <dimension ref="A1:H228"/>
   <sheetFormatPr defaultColWidth="26" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.85546875" bestFit="1" customWidth="1"/>
@@ -2504,7 +2559,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="117" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>373</v>
+        <v>391</v>
       </c>
       <c r="D1" s="7"/>
       <c r="E1" s="7"/>
@@ -2512,7 +2567,7 @@
       <c r="G1" s="7"/>
       <c r="H1" s="7"/>
     </row>
-    <row r="2" spans="1:8" s="1" customFormat="1" ht="24.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" s="1" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
         <v>0</v>
       </c>
@@ -8074,6 +8129,344 @@
       </c>
       <c r="H215" s="17" t="s">
         <v>372</v>
+      </c>
+    </row>
+    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A216" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="B216" s="19">
+        <v>45153</v>
+      </c>
+      <c r="C216" s="19">
+        <v>45183</v>
+      </c>
+      <c r="D216" s="19">
+        <v>45213</v>
+      </c>
+      <c r="E216" s="20" t="s">
+        <v>373</v>
+      </c>
+      <c r="F216" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G216" s="21">
+        <v>76</v>
+      </c>
+      <c r="H216" s="22" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A217" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="B217" s="14">
+        <v>45145</v>
+      </c>
+      <c r="C217" s="14">
+        <v>45183</v>
+      </c>
+      <c r="D217" s="14">
+        <v>45175</v>
+      </c>
+      <c r="E217" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="F217" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G217" s="16">
+        <v>1</v>
+      </c>
+      <c r="H217" s="17" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A218" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="B218" s="19">
+        <v>45140</v>
+      </c>
+      <c r="C218" s="19">
+        <v>45183</v>
+      </c>
+      <c r="D218" s="19">
+        <v>45201</v>
+      </c>
+      <c r="E218" s="20" t="s">
+        <v>362</v>
+      </c>
+      <c r="F218" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G218" s="21">
+        <v>50</v>
+      </c>
+      <c r="H218" s="22" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A219" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="B219" s="14">
+        <v>45147</v>
+      </c>
+      <c r="C219" s="14">
+        <v>45183</v>
+      </c>
+      <c r="D219" s="14">
+        <v>45247</v>
+      </c>
+      <c r="E219" s="15" t="s">
+        <v>376</v>
+      </c>
+      <c r="F219" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G219" s="16">
+        <v>134</v>
+      </c>
+      <c r="H219" s="17" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="220" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A220" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="B220" s="19">
+        <v>45149</v>
+      </c>
+      <c r="C220" s="19">
+        <v>45183</v>
+      </c>
+      <c r="D220" s="19">
+        <v>45209</v>
+      </c>
+      <c r="E220" s="20" t="s">
+        <v>378</v>
+      </c>
+      <c r="F220" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G220" s="21">
+        <v>73</v>
+      </c>
+      <c r="H220" s="22" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="221" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A221" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B221" s="14">
+        <v>45149</v>
+      </c>
+      <c r="C221" s="14">
+        <v>45183</v>
+      </c>
+      <c r="D221" s="14">
+        <v>45240</v>
+      </c>
+      <c r="E221" s="15" t="s">
+        <v>380</v>
+      </c>
+      <c r="F221" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G221" s="16">
+        <v>1</v>
+      </c>
+      <c r="H221" s="17" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="222" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A222" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="B222" s="19">
+        <v>45149</v>
+      </c>
+      <c r="C222" s="19">
+        <v>45183</v>
+      </c>
+      <c r="D222" s="19">
+        <v>45247</v>
+      </c>
+      <c r="E222" s="20" t="s">
+        <v>378</v>
+      </c>
+      <c r="F222" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G222" s="21">
+        <v>2</v>
+      </c>
+      <c r="H222" s="22" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="223" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A223" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="B223" s="14">
+        <v>45142</v>
+      </c>
+      <c r="C223" s="14">
+        <v>45184</v>
+      </c>
+      <c r="D223" s="14">
+        <v>45202</v>
+      </c>
+      <c r="E223" s="15" t="s">
+        <v>381</v>
+      </c>
+      <c r="F223" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G223" s="16">
+        <v>127</v>
+      </c>
+      <c r="H223" s="17" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="224" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A224" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="B224" s="19">
+        <v>45135</v>
+      </c>
+      <c r="C224" s="19">
+        <v>45184</v>
+      </c>
+      <c r="D224" s="19">
+        <v>45198</v>
+      </c>
+      <c r="E224" s="20" t="s">
+        <v>383</v>
+      </c>
+      <c r="F224" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G224" s="21">
+        <v>76</v>
+      </c>
+      <c r="H224" s="22" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="225" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A225" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B225" s="14">
+        <v>45135</v>
+      </c>
+      <c r="C225" s="14">
+        <v>45184</v>
+      </c>
+      <c r="D225" s="14">
+        <v>45198</v>
+      </c>
+      <c r="E225" s="15" t="s">
+        <v>383</v>
+      </c>
+      <c r="F225" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G225" s="16">
+        <v>94</v>
+      </c>
+      <c r="H225" s="17" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="226" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A226" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="B226" s="19">
+        <v>45145</v>
+      </c>
+      <c r="C226" s="19">
+        <v>45187</v>
+      </c>
+      <c r="D226" s="19">
+        <v>45146</v>
+      </c>
+      <c r="E226" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="F226" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G226" s="21">
+        <v>62</v>
+      </c>
+      <c r="H226" s="22" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="227" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A227" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B227" s="14">
+        <v>45147</v>
+      </c>
+      <c r="C227" s="14">
+        <v>45187</v>
+      </c>
+      <c r="D227" s="14">
+        <v>45212</v>
+      </c>
+      <c r="E227" s="15" t="s">
+        <v>387</v>
+      </c>
+      <c r="F227" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G227" s="16">
+        <v>4</v>
+      </c>
+      <c r="H227" s="17" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="228" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A228" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="B228" s="19">
+        <v>45180</v>
+      </c>
+      <c r="C228" s="19">
+        <v>45187</v>
+      </c>
+      <c r="D228" s="19">
+        <v>45149</v>
+      </c>
+      <c r="E228" s="20" t="s">
+        <v>389</v>
+      </c>
+      <c r="F228" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G228" s="21">
+        <v>127</v>
+      </c>
+      <c r="H228" s="22" t="s">
+        <v>390</v>
       </c>
     </row>
   </sheetData>
@@ -8215,16 +8608,22 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AC06125-8442-4191-9EC7-BDA92AB0B9AD}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F899729A-C84F-4370-85D4-EC206100DD6E}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F17506A-DCE7-4082-BC3D-89E34E0EA76B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{549E0B6C-9FDE-4527-97EE-B343EAB00909}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
@@ -8232,7 +8631,7 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E8A2E801-96BC-43E9-A765-2CE49A3B3E09}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{79360BBE-A6BD-4738-9B60-059BA3E6954D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>

--- a/data/warn-scraper/cache/ca/warn_report1.xlsx
+++ b/data/warn-scraper/cache/ca/warn_report1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25601"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24931"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jochoa2\Desktop\Conditional Approvals\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\WSB-CO\Communications Unit\Website Management\WARN (Worker Adjustment and Retraining Notification) Updates\2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{713F8B14-6760-4F80-9A4D-4A031D8361D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{145B4A5F-4AC5-4A45-A7F0-BF43D33F62C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14310" yWindow="-16320" windowWidth="29040" windowHeight="15840" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
+    <workbookView xWindow="29895" yWindow="1230" windowWidth="21600" windowHeight="11430" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
   <sheets>
     <sheet name="Index" sheetId="3" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="927" uniqueCount="392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="931" uniqueCount="394">
   <si>
     <t>County/Parish</t>
   </si>
@@ -1275,6 +1275,12 @@
   </si>
   <si>
     <t>1020 Marauder St  Chico CA 95973</t>
+  </si>
+  <si>
+    <t>ImmunityBio, Inc.</t>
+  </si>
+  <si>
+    <t>2040 E. Mariposa Avenue  El Segundo CA 90245</t>
   </si>
   <si>
     <r>
@@ -1308,7 +1314,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>A detailed WARN summary by county and filtered according to received date. Table Spans cells A2 through H228.</t>
+      <t>A detailed WARN summary by county and filtered according to received date. Table Spans cells A2 through H229.</t>
     </r>
   </si>
 </sst>
@@ -1404,7 +1410,6 @@
       <sz val="8"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -1616,8 +1621,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFF0F0F0"/>
+          <bgColor rgb="FFF0F0F0"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -1657,8 +1662,8 @@
       <numFmt numFmtId="165" formatCode="[$-10436]#,##0;\(#,##0\)"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFF0F0F0"/>
+          <bgColor rgb="FFF0F0F0"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -1697,8 +1702,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFF0F0F0"/>
+          <bgColor rgb="FFF0F0F0"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -1737,8 +1742,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFF0F0F0"/>
+          <bgColor rgb="FFF0F0F0"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -1778,8 +1783,8 @@
       <numFmt numFmtId="164" formatCode="[$-10409]mm/dd/yyyy"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFF0F0F0"/>
+          <bgColor rgb="FFF0F0F0"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -1819,8 +1824,8 @@
       <numFmt numFmtId="164" formatCode="[$-10409]mm/dd/yyyy"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFF0F0F0"/>
+          <bgColor rgb="FFF0F0F0"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -1860,8 +1865,8 @@
       <numFmt numFmtId="164" formatCode="[$-10409]mm/dd/yyyy"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFF0F0F0"/>
+          <bgColor rgb="FFF0F0F0"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -1900,8 +1905,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFF0F0F0"/>
+          <bgColor rgb="FFF0F0F0"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -2093,8 +2098,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:H228" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
-  <autoFilter ref="A2:H228" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:H229" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
+  <autoFilter ref="A2:H229" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -2416,27 +2421,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D341DFFF-02D2-4572-95F5-BB3221952133}">
   <dimension ref="A1:A4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="66.140625" customWidth="1"/>
+    <col min="1" max="1" width="66.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="105" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="21" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:1" ht="21" x14ac:dyDescent="0.4">
       <c r="A2" s="9" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
         <v>154</v>
       </c>
@@ -2453,18 +2458,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1832896D-8AFB-4FFC-957E-910308F3BC0C}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29" customWidth="1"/>
-    <col min="2" max="2" width="12.42578125" customWidth="1"/>
+    <col min="2" max="2" width="12.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="75.599999999999994" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>28</v>
       </c>
@@ -2472,25 +2477,25 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>152</v>
       </c>
       <c r="B3" s="6">
         <f>SUM('Detailed WARN Report '!G:G)</f>
-        <v>12507</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>12555</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>21</v>
       </c>
       <c r="B4" s="6">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Permanent")</f>
-        <v>120</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>22</v>
       </c>
@@ -2499,7 +2504,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>23</v>
       </c>
@@ -2508,7 +2513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>24</v>
       </c>
@@ -2517,7 +2522,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>25</v>
       </c>
@@ -2526,7 +2531,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>26</v>
       </c>
@@ -2546,20 +2551,20 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:H228"/>
-  <sheetFormatPr defaultColWidth="26" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H229"/>
+  <sheetFormatPr defaultColWidth="26" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="25.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="54.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="52.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="54.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="52.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="117" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="99.6" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="D1" s="7"/>
       <c r="E1" s="7"/>
@@ -2567,7 +2572,7 @@
       <c r="G1" s="7"/>
       <c r="H1" s="7"/>
     </row>
-    <row r="2" spans="1:8" s="1" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" s="1" customFormat="1" ht="24.6" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
         <v>0</v>
       </c>
@@ -2593,7 +2598,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
         <v>14</v>
       </c>
@@ -2619,7 +2624,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="18" t="s">
         <v>13</v>
       </c>
@@ -2645,7 +2650,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
         <v>12</v>
       </c>
@@ -2671,7 +2676,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="18" t="s">
         <v>6</v>
       </c>
@@ -2697,7 +2702,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
         <v>6</v>
       </c>
@@ -2723,7 +2728,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="18" t="s">
         <v>5</v>
       </c>
@@ -2749,7 +2754,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="13" t="s">
         <v>8</v>
       </c>
@@ -2775,7 +2780,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="18" t="s">
         <v>5</v>
       </c>
@@ -2801,7 +2806,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="13" t="s">
         <v>39</v>
       </c>
@@ -2827,7 +2832,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="18" t="s">
         <v>11</v>
       </c>
@@ -2853,7 +2858,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="13" t="s">
         <v>11</v>
       </c>
@@ -2879,7 +2884,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="18" t="s">
         <v>9</v>
       </c>
@@ -2905,7 +2910,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="13" t="s">
         <v>7</v>
       </c>
@@ -2931,7 +2936,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="18" t="s">
         <v>10</v>
       </c>
@@ -2957,7 +2962,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="13" t="s">
         <v>10</v>
       </c>
@@ -2983,7 +2988,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="18" t="s">
         <v>5</v>
       </c>
@@ -3009,7 +3014,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="13" t="s">
         <v>52</v>
       </c>
@@ -3035,7 +3040,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="18" t="s">
         <v>5</v>
       </c>
@@ -3061,7 +3066,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="13" t="s">
         <v>5</v>
       </c>
@@ -3087,7 +3092,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="18" t="s">
         <v>13</v>
       </c>
@@ -3113,7 +3118,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="13" t="s">
         <v>7</v>
       </c>
@@ -3139,7 +3144,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="18" t="s">
         <v>5</v>
       </c>
@@ -3165,7 +3170,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="13" t="s">
         <v>5</v>
       </c>
@@ -3191,7 +3196,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="18" t="s">
         <v>63</v>
       </c>
@@ -3217,7 +3222,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="13" t="s">
         <v>66</v>
       </c>
@@ -3243,7 +3248,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="18" t="s">
         <v>6</v>
       </c>
@@ -3269,7 +3274,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="13" t="s">
         <v>7</v>
       </c>
@@ -3295,7 +3300,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="18" t="s">
         <v>11</v>
       </c>
@@ -3321,7 +3326,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="13" t="s">
         <v>11</v>
       </c>
@@ -3347,7 +3352,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="18" t="s">
         <v>11</v>
       </c>
@@ -3373,7 +3378,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="13" t="s">
         <v>9</v>
       </c>
@@ -3399,7 +3404,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="18" t="s">
         <v>76</v>
       </c>
@@ -3425,7 +3430,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="13" t="s">
         <v>79</v>
       </c>
@@ -3451,7 +3456,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="18" t="s">
         <v>79</v>
       </c>
@@ -3477,7 +3482,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="13" t="s">
         <v>66</v>
       </c>
@@ -3503,7 +3508,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="18" t="s">
         <v>6</v>
       </c>
@@ -3529,7 +3534,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="13" t="s">
         <v>86</v>
       </c>
@@ -3555,7 +3560,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="18" t="s">
         <v>63</v>
       </c>
@@ -3581,7 +3586,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="13" t="s">
         <v>63</v>
       </c>
@@ -3607,7 +3612,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="18" t="s">
         <v>76</v>
       </c>
@@ -3633,7 +3638,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="13" t="s">
         <v>6</v>
       </c>
@@ -3659,7 +3664,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="18" t="s">
         <v>6</v>
       </c>
@@ -3685,7 +3690,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="13" t="s">
         <v>97</v>
       </c>
@@ -3711,7 +3716,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="18" t="s">
         <v>86</v>
       </c>
@@ -3737,7 +3742,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="13" t="s">
         <v>13</v>
       </c>
@@ -3763,7 +3768,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="18" t="s">
         <v>5</v>
       </c>
@@ -3789,7 +3794,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="13" t="s">
         <v>63</v>
       </c>
@@ -3815,7 +3820,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" s="18" t="s">
         <v>52</v>
       </c>
@@ -3841,7 +3846,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" s="13" t="s">
         <v>52</v>
       </c>
@@ -3867,7 +3872,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" s="18" t="s">
         <v>12</v>
       </c>
@@ -3893,7 +3898,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" s="13" t="s">
         <v>6</v>
       </c>
@@ -3919,7 +3924,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" s="18" t="s">
         <v>52</v>
       </c>
@@ -3945,7 +3950,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" s="13" t="s">
         <v>5</v>
       </c>
@@ -3971,7 +3976,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" s="18" t="s">
         <v>76</v>
       </c>
@@ -3997,7 +4002,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" s="13" t="s">
         <v>52</v>
       </c>
@@ -4023,7 +4028,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" s="18" t="s">
         <v>52</v>
       </c>
@@ -4049,7 +4054,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" s="13" t="s">
         <v>52</v>
       </c>
@@ -4075,7 +4080,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" s="18" t="s">
         <v>52</v>
       </c>
@@ -4101,7 +4106,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" s="13" t="s">
         <v>52</v>
       </c>
@@ -4127,7 +4132,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" s="18" t="s">
         <v>7</v>
       </c>
@@ -4153,7 +4158,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" s="13" t="s">
         <v>7</v>
       </c>
@@ -4179,7 +4184,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" s="18" t="s">
         <v>52</v>
       </c>
@@ -4205,7 +4210,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" s="13" t="s">
         <v>52</v>
       </c>
@@ -4231,7 +4236,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" s="18" t="s">
         <v>52</v>
       </c>
@@ -4257,7 +4262,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" s="13" t="s">
         <v>52</v>
       </c>
@@ -4283,7 +4288,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" s="18" t="s">
         <v>52</v>
       </c>
@@ -4309,7 +4314,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" s="13" t="s">
         <v>86</v>
       </c>
@@ -4335,7 +4340,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" s="18" t="s">
         <v>86</v>
       </c>
@@ -4361,7 +4366,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" s="13" t="s">
         <v>135</v>
       </c>
@@ -4387,7 +4392,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" s="18" t="s">
         <v>5</v>
       </c>
@@ -4413,7 +4418,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" s="13" t="s">
         <v>6</v>
       </c>
@@ -4439,7 +4444,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" s="18" t="s">
         <v>86</v>
       </c>
@@ -4465,7 +4470,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" s="13" t="s">
         <v>86</v>
       </c>
@@ -4491,7 +4496,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" s="18" t="s">
         <v>86</v>
       </c>
@@ -4517,7 +4522,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" s="13" t="s">
         <v>86</v>
       </c>
@@ -4543,7 +4548,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" s="18" t="s">
         <v>5</v>
       </c>
@@ -4569,7 +4574,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" s="13" t="s">
         <v>66</v>
       </c>
@@ -4595,7 +4600,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" s="18" t="s">
         <v>66</v>
       </c>
@@ -4621,7 +4626,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" s="13" t="s">
         <v>5</v>
       </c>
@@ -4647,7 +4652,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" s="18" t="s">
         <v>5</v>
       </c>
@@ -4673,7 +4678,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" s="13" t="s">
         <v>5</v>
       </c>
@@ -4699,7 +4704,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" s="18" t="s">
         <v>63</v>
       </c>
@@ -4725,7 +4730,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" s="13" t="s">
         <v>6</v>
       </c>
@@ -4751,7 +4756,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" s="18" t="s">
         <v>52</v>
       </c>
@@ -4777,7 +4782,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" s="13" t="s">
         <v>86</v>
       </c>
@@ -4803,7 +4808,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" s="18" t="s">
         <v>6</v>
       </c>
@@ -4829,7 +4834,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" s="13" t="s">
         <v>86</v>
       </c>
@@ -4855,7 +4860,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" s="18" t="s">
         <v>63</v>
       </c>
@@ -4881,7 +4886,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" s="13" t="s">
         <v>175</v>
       </c>
@@ -4907,7 +4912,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" s="18" t="s">
         <v>6</v>
       </c>
@@ -4933,7 +4938,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" s="13" t="s">
         <v>6</v>
       </c>
@@ -4959,7 +4964,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" s="18" t="s">
         <v>6</v>
       </c>
@@ -4985,7 +4990,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" s="13" t="s">
         <v>6</v>
       </c>
@@ -5011,7 +5016,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" s="18" t="s">
         <v>6</v>
       </c>
@@ -5037,7 +5042,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" s="13" t="s">
         <v>6</v>
       </c>
@@ -5063,7 +5068,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" s="18" t="s">
         <v>97</v>
       </c>
@@ -5089,7 +5094,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" s="13" t="s">
         <v>5</v>
       </c>
@@ -5115,7 +5120,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" s="18" t="s">
         <v>7</v>
       </c>
@@ -5141,7 +5146,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" s="13" t="s">
         <v>5</v>
       </c>
@@ -5167,7 +5172,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" s="18" t="s">
         <v>5</v>
       </c>
@@ -5193,7 +5198,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" s="13" t="s">
         <v>5</v>
       </c>
@@ -5219,7 +5224,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104" s="18" t="s">
         <v>5</v>
       </c>
@@ -5245,7 +5250,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105" s="13" t="s">
         <v>5</v>
       </c>
@@ -5271,7 +5276,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" s="18" t="s">
         <v>5</v>
       </c>
@@ -5297,7 +5302,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107" s="13" t="s">
         <v>5</v>
       </c>
@@ -5323,7 +5328,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" s="18" t="s">
         <v>5</v>
       </c>
@@ -5349,7 +5354,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109" s="13" t="s">
         <v>52</v>
       </c>
@@ -5375,7 +5380,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110" s="18" t="s">
         <v>9</v>
       </c>
@@ -5401,7 +5406,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A111" s="13" t="s">
         <v>76</v>
       </c>
@@ -5427,7 +5432,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112" s="18" t="s">
         <v>212</v>
       </c>
@@ -5453,7 +5458,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A113" s="13" t="s">
         <v>52</v>
       </c>
@@ -5479,7 +5484,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114" s="18" t="s">
         <v>86</v>
       </c>
@@ -5505,7 +5510,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A115" s="13" t="s">
         <v>5</v>
       </c>
@@ -5531,7 +5536,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116" s="18" t="s">
         <v>5</v>
       </c>
@@ -5557,7 +5562,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A117" s="13" t="s">
         <v>76</v>
       </c>
@@ -5583,7 +5588,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118" s="18" t="s">
         <v>14</v>
       </c>
@@ -5609,7 +5614,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119" s="13" t="s">
         <v>5</v>
       </c>
@@ -5635,7 +5640,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120" s="18" t="s">
         <v>7</v>
       </c>
@@ -5661,7 +5666,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A121" s="13" t="s">
         <v>52</v>
       </c>
@@ -5687,7 +5692,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A122" s="18" t="s">
         <v>9</v>
       </c>
@@ -5713,7 +5718,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A123" s="13" t="s">
         <v>7</v>
       </c>
@@ -5739,7 +5744,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A124" s="18" t="s">
         <v>86</v>
       </c>
@@ -5765,7 +5770,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A125" s="13" t="s">
         <v>233</v>
       </c>
@@ -5791,7 +5796,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A126" s="18" t="s">
         <v>236</v>
       </c>
@@ -5817,7 +5822,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A127" s="13" t="s">
         <v>63</v>
       </c>
@@ -5843,7 +5848,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A128" s="18" t="s">
         <v>63</v>
       </c>
@@ -5869,7 +5874,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A129" s="13" t="s">
         <v>63</v>
       </c>
@@ -5895,7 +5900,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A130" s="18" t="s">
         <v>7</v>
       </c>
@@ -5921,7 +5926,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A131" s="13" t="s">
         <v>66</v>
       </c>
@@ -5947,7 +5952,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A132" s="18" t="s">
         <v>66</v>
       </c>
@@ -5973,7 +5978,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A133" s="13" t="s">
         <v>9</v>
       </c>
@@ -5999,7 +6004,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A134" s="18" t="s">
         <v>76</v>
       </c>
@@ -6025,7 +6030,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A135" s="13" t="s">
         <v>76</v>
       </c>
@@ -6051,7 +6056,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A136" s="18" t="s">
         <v>76</v>
       </c>
@@ -6077,7 +6082,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A137" s="13" t="s">
         <v>6</v>
       </c>
@@ -6103,7 +6108,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A138" s="18" t="s">
         <v>6</v>
       </c>
@@ -6129,7 +6134,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A139" s="13" t="s">
         <v>252</v>
       </c>
@@ -6155,7 +6160,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A140" s="18" t="s">
         <v>5</v>
       </c>
@@ -6181,7 +6186,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A141" s="13" t="s">
         <v>7</v>
       </c>
@@ -6207,7 +6212,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A142" s="18" t="s">
         <v>7</v>
       </c>
@@ -6233,7 +6238,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A143" s="13" t="s">
         <v>7</v>
       </c>
@@ -6259,7 +6264,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A144" s="18" t="s">
         <v>7</v>
       </c>
@@ -6285,7 +6290,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A145" s="13" t="s">
         <v>6</v>
       </c>
@@ -6311,7 +6316,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A146" s="18" t="s">
         <v>6</v>
       </c>
@@ -6337,7 +6342,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A147" s="13" t="s">
         <v>6</v>
       </c>
@@ -6363,7 +6368,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A148" s="18" t="s">
         <v>97</v>
       </c>
@@ -6389,7 +6394,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A149" s="13" t="s">
         <v>7</v>
       </c>
@@ -6415,7 +6420,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A150" s="18" t="s">
         <v>5</v>
       </c>
@@ -6441,7 +6446,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A151" s="13" t="s">
         <v>212</v>
       </c>
@@ -6467,7 +6472,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A152" s="18" t="s">
         <v>86</v>
       </c>
@@ -6493,7 +6498,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A153" s="13" t="s">
         <v>13</v>
       </c>
@@ -6519,7 +6524,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A154" s="18" t="s">
         <v>268</v>
       </c>
@@ -6545,7 +6550,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A155" s="13" t="s">
         <v>270</v>
       </c>
@@ -6571,7 +6576,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A156" s="18" t="s">
         <v>8</v>
       </c>
@@ -6597,7 +6602,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A157" s="13" t="s">
         <v>5</v>
       </c>
@@ -6623,7 +6628,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A158" s="18" t="s">
         <v>5</v>
       </c>
@@ -6649,7 +6654,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A159" s="13" t="s">
         <v>5</v>
       </c>
@@ -6675,7 +6680,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A160" s="18" t="s">
         <v>5</v>
       </c>
@@ -6701,7 +6706,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A161" s="13" t="s">
         <v>5</v>
       </c>
@@ -6727,7 +6732,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A162" s="18" t="s">
         <v>278</v>
       </c>
@@ -6753,7 +6758,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A163" s="13" t="s">
         <v>79</v>
       </c>
@@ -6779,7 +6784,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A164" s="18" t="s">
         <v>175</v>
       </c>
@@ -6805,7 +6810,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A165" s="13" t="s">
         <v>282</v>
       </c>
@@ -6831,7 +6836,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A166" s="18" t="s">
         <v>284</v>
       </c>
@@ -6857,7 +6862,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A167" s="13" t="s">
         <v>5</v>
       </c>
@@ -6883,7 +6888,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A168" s="18" t="s">
         <v>11</v>
       </c>
@@ -6909,7 +6914,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A169" s="13" t="s">
         <v>52</v>
       </c>
@@ -6935,7 +6940,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A170" s="18" t="s">
         <v>7</v>
       </c>
@@ -6961,7 +6966,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A171" s="13" t="s">
         <v>14</v>
       </c>
@@ -6987,7 +6992,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A172" s="18" t="s">
         <v>7</v>
       </c>
@@ -7013,7 +7018,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A173" s="13" t="s">
         <v>7</v>
       </c>
@@ -7039,7 +7044,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A174" s="18" t="s">
         <v>7</v>
       </c>
@@ -7065,7 +7070,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A175" s="13" t="s">
         <v>52</v>
       </c>
@@ -7091,7 +7096,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A176" s="18" t="s">
         <v>302</v>
       </c>
@@ -7117,7 +7122,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A177" s="13" t="s">
         <v>86</v>
       </c>
@@ -7143,7 +7148,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A178" s="18" t="s">
         <v>86</v>
       </c>
@@ -7169,7 +7174,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A179" s="13" t="s">
         <v>66</v>
       </c>
@@ -7195,7 +7200,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A180" s="18" t="s">
         <v>5</v>
       </c>
@@ -7221,7 +7226,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A181" s="13" t="s">
         <v>63</v>
       </c>
@@ -7247,7 +7252,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A182" s="18" t="s">
         <v>6</v>
       </c>
@@ -7273,7 +7278,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A183" s="13" t="s">
         <v>6</v>
       </c>
@@ -7299,7 +7304,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A184" s="18" t="s">
         <v>6</v>
       </c>
@@ -7325,7 +7330,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A185" s="13" t="s">
         <v>63</v>
       </c>
@@ -7351,7 +7356,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A186" s="18" t="s">
         <v>63</v>
       </c>
@@ -7377,7 +7382,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A187" s="13" t="s">
         <v>63</v>
       </c>
@@ -7403,7 +7408,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A188" s="18" t="s">
         <v>7</v>
       </c>
@@ -7429,7 +7434,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A189" s="13" t="s">
         <v>7</v>
       </c>
@@ -7455,7 +7460,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A190" s="18" t="s">
         <v>7</v>
       </c>
@@ -7481,7 +7486,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A191" s="13" t="s">
         <v>7</v>
       </c>
@@ -7507,7 +7512,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A192" s="18" t="s">
         <v>7</v>
       </c>
@@ -7533,7 +7538,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A193" s="13" t="s">
         <v>6</v>
       </c>
@@ -7559,7 +7564,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A194" s="18" t="s">
         <v>302</v>
       </c>
@@ -7585,7 +7590,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A195" s="13" t="s">
         <v>14</v>
       </c>
@@ -7611,7 +7616,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A196" s="18" t="s">
         <v>7</v>
       </c>
@@ -7637,7 +7642,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A197" s="13" t="s">
         <v>5</v>
       </c>
@@ -7663,7 +7668,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A198" s="18" t="s">
         <v>6</v>
       </c>
@@ -7689,7 +7694,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A199" s="13" t="s">
         <v>5</v>
       </c>
@@ -7715,7 +7720,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A200" s="18" t="s">
         <v>5</v>
       </c>
@@ -7741,7 +7746,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A201" s="13" t="s">
         <v>5</v>
       </c>
@@ -7767,7 +7772,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A202" s="18" t="s">
         <v>5</v>
       </c>
@@ -7793,7 +7798,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A203" s="13" t="s">
         <v>13</v>
       </c>
@@ -7819,7 +7824,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A204" s="18" t="s">
         <v>66</v>
       </c>
@@ -7845,7 +7850,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A205" s="13" t="s">
         <v>175</v>
       </c>
@@ -7871,7 +7876,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A206" s="18" t="s">
         <v>6</v>
       </c>
@@ -7897,7 +7902,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A207" s="13" t="s">
         <v>52</v>
       </c>
@@ -7923,7 +7928,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A208" s="18" t="s">
         <v>236</v>
       </c>
@@ -7949,7 +7954,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A209" s="13" t="s">
         <v>52</v>
       </c>
@@ -7975,7 +7980,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A210" s="18" t="s">
         <v>5</v>
       </c>
@@ -8001,7 +8006,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A211" s="13" t="s">
         <v>7</v>
       </c>
@@ -8027,7 +8032,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A212" s="18" t="s">
         <v>7</v>
       </c>
@@ -8053,7 +8058,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A213" s="13" t="s">
         <v>5</v>
       </c>
@@ -8079,7 +8084,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A214" s="18" t="s">
         <v>368</v>
       </c>
@@ -8105,7 +8110,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A215" s="13" t="s">
         <v>79</v>
       </c>
@@ -8131,7 +8136,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A216" s="18" t="s">
         <v>14</v>
       </c>
@@ -8157,7 +8162,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A217" s="13" t="s">
         <v>63</v>
       </c>
@@ -8183,7 +8188,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A218" s="18" t="s">
         <v>9</v>
       </c>
@@ -8209,7 +8214,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A219" s="13" t="s">
         <v>6</v>
       </c>
@@ -8235,7 +8240,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A220" s="18" t="s">
         <v>5</v>
       </c>
@@ -8261,7 +8266,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A221" s="13" t="s">
         <v>5</v>
       </c>
@@ -8287,7 +8292,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A222" s="18" t="s">
         <v>5</v>
       </c>
@@ -8313,7 +8318,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A223" s="13" t="s">
         <v>86</v>
       </c>
@@ -8339,7 +8344,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A224" s="18" t="s">
         <v>66</v>
       </c>
@@ -8365,7 +8370,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="225" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A225" s="13" t="s">
         <v>9</v>
       </c>
@@ -8391,7 +8396,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="226" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A226" s="18" t="s">
         <v>86</v>
       </c>
@@ -8417,7 +8422,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="227" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A227" s="13" t="s">
         <v>8</v>
       </c>
@@ -8443,7 +8448,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="228" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A228" s="18" t="s">
         <v>39</v>
       </c>
@@ -8467,6 +8472,32 @@
       </c>
       <c r="H228" s="22" t="s">
         <v>390</v>
+      </c>
+    </row>
+    <row r="229" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A229" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B229" s="14">
+        <v>45156</v>
+      </c>
+      <c r="C229" s="14">
+        <v>45188</v>
+      </c>
+      <c r="D229" s="14">
+        <v>45216</v>
+      </c>
+      <c r="E229" s="15" t="s">
+        <v>391</v>
+      </c>
+      <c r="F229" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G229" s="16">
+        <v>48</v>
+      </c>
+      <c r="H229" s="17" t="s">
+        <v>392</v>
       </c>
     </row>
   </sheetData>
@@ -8479,21 +8510,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Unknown Document Type" ma:contentTypeID="0x010104" ma:contentTypeVersion="0" ma:contentTypeDescription="" ma:contentTypeScope="" ma:versionID="05d83ceaa0bbd2e3bc716e6e66bd857a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b3d69fe45253d5ff147bb69036b756a7">
     <xsd:element name="properties">
@@ -8607,41 +8623,29 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F899729A-C84F-4370-85D4-EC206100DD6E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F5AB9ED-5A1C-47B2-83C2-F768FFC81423}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{549E0B6C-9FDE-4527-97EE-B343EAB00909}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EE2358EB-C708-41B4-9E09-C6E77F256BA5}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{79360BBE-A6BD-4738-9B60-059BA3E6954D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E742885-4A58-4ED2-8394-56012BBEE4E6}"/>
 </file>
--- a/data/warn-scraper/cache/ca/warn_report1.xlsx
+++ b/data/warn-scraper/cache/ca/warn_report1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\WSB-CO\Communications Unit\Website Management\WARN (Worker Adjustment and Retraining Notification) Updates\2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{145B4A5F-4AC5-4A45-A7F0-BF43D33F62C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C059C3D-9E75-43F0-AC76-11C7665B8AAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="29895" yWindow="1230" windowWidth="21600" windowHeight="11430" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="931" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1035" uniqueCount="432">
   <si>
     <t>County/Parish</t>
   </si>
@@ -1283,6 +1283,120 @@
     <t>2040 E. Mariposa Avenue  El Segundo CA 90245</t>
   </si>
   <si>
+    <t>Morrison Healthcare at Adventist Health Bakersfield</t>
+  </si>
+  <si>
+    <t>2615 Chester Ave.  Bakersfield CA 93301</t>
+  </si>
+  <si>
+    <t>U.S. Bank</t>
+  </si>
+  <si>
+    <t>1221 Broadway  Oakland CA 94612</t>
+  </si>
+  <si>
+    <t>9865 Town Centre Drive  San Diego CA 92121</t>
+  </si>
+  <si>
+    <t>U. S. Bank</t>
+  </si>
+  <si>
+    <t>9885 Town Centre Drive  San Diego CA 92121</t>
+  </si>
+  <si>
+    <t>Certified Freight Logistics, Inc.</t>
+  </si>
+  <si>
+    <t>1483 W Anderson St  Stockton CA 95206</t>
+  </si>
+  <si>
+    <t>Wolfspeed, Inc.</t>
+  </si>
+  <si>
+    <t>18275 Serene Dr.  Morgan Hill CA 95037</t>
+  </si>
+  <si>
+    <t>1344 White Ct.  Santa Maria CA 93458</t>
+  </si>
+  <si>
+    <t>Universal Protection Service, LP dba Allied Universal Security Services</t>
+  </si>
+  <si>
+    <t>1 Meta Way  Menlo Park CA 94025</t>
+  </si>
+  <si>
+    <t>180 Jefferson Drive  Menlo Park CA 94025</t>
+  </si>
+  <si>
+    <t>1 Hacker Way  Menlo Park CA 94025</t>
+  </si>
+  <si>
+    <t>100 Independence Drive  Menlo Park CA 94025</t>
+  </si>
+  <si>
+    <t>MV Transportation, Inc.</t>
+  </si>
+  <si>
+    <t>2801 N Hollywood Way  Burbank CA 91504</t>
+  </si>
+  <si>
+    <t>REACH Medical Holdings</t>
+  </si>
+  <si>
+    <t>5005 Marsh Drive  Concord CA 94520</t>
+  </si>
+  <si>
+    <t>407 Mathew Street  Santa Clara CA 95050</t>
+  </si>
+  <si>
+    <t>Clari Inc.</t>
+  </si>
+  <si>
+    <t>1154 Sonora Court  Sunnyvale CA 94086</t>
+  </si>
+  <si>
+    <t>36610 Sky Canyon Drive, Hangar 51  Murrieta CA 92563</t>
+  </si>
+  <si>
+    <t>9918 Hibert Street  San Diego CA 92131</t>
+  </si>
+  <si>
+    <t>BlackLine Systems, Inc.</t>
+  </si>
+  <si>
+    <t>4301 Hacienda Drive, 5th Floor  Pleasanton CA 94588</t>
+  </si>
+  <si>
+    <t>The Vons Companies Inc.</t>
+  </si>
+  <si>
+    <t>1129 S. Fair Oaks Avenue  South Pasadena CA 91030</t>
+  </si>
+  <si>
+    <t>21300 Victory Blvd 12th Floor  Woodland Hills CA 91367</t>
+  </si>
+  <si>
+    <t>Burke Williams</t>
+  </si>
+  <si>
+    <t>27741 Crown Valley Pkwy., Suite 211  Mission Viejo CA 92691</t>
+  </si>
+  <si>
+    <t>KeHE Distributors, Inc.</t>
+  </si>
+  <si>
+    <t>16081 Fern Avenue  Chino CA 91708</t>
+  </si>
+  <si>
+    <t>Natural Alternatives International</t>
+  </si>
+  <si>
+    <t>5928 Farnsworth Court  Carlsbad CA 92008</t>
+  </si>
+  <si>
+    <t>1211 &amp; 1215 Park Center Drive  Vista CA 92081</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">WARN REPORT - </t>
     </r>
@@ -1294,7 +1408,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>07/01/23 to 09/18/23</t>
+      <t>07/01/23 to 09/27/23</t>
     </r>
     <r>
       <rPr>
@@ -1314,7 +1428,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>A detailed WARN summary by county and filtered according to received date. Table Spans cells A2 through H229.</t>
+      <t>A detailed WARN summary by county and filtered according to received date. Table Spans cells A2 through H255.</t>
     </r>
   </si>
 </sst>
@@ -1621,8 +1735,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF0F0F0"/>
-          <bgColor rgb="FFF0F0F0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -1662,8 +1776,8 @@
       <numFmt numFmtId="165" formatCode="[$-10436]#,##0;\(#,##0\)"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF0F0F0"/>
-          <bgColor rgb="FFF0F0F0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -1702,8 +1816,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF0F0F0"/>
-          <bgColor rgb="FFF0F0F0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -1742,8 +1856,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF0F0F0"/>
-          <bgColor rgb="FFF0F0F0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -1783,8 +1897,8 @@
       <numFmt numFmtId="164" formatCode="[$-10409]mm/dd/yyyy"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF0F0F0"/>
-          <bgColor rgb="FFF0F0F0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -1824,8 +1938,8 @@
       <numFmt numFmtId="164" formatCode="[$-10409]mm/dd/yyyy"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF0F0F0"/>
-          <bgColor rgb="FFF0F0F0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -1865,8 +1979,8 @@
       <numFmt numFmtId="164" formatCode="[$-10409]mm/dd/yyyy"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF0F0F0"/>
-          <bgColor rgb="FFF0F0F0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -1905,8 +2019,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF0F0F0"/>
-          <bgColor rgb="FFF0F0F0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -2098,8 +2212,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:H229" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
-  <autoFilter ref="A2:H229" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:H255" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
+  <autoFilter ref="A2:H255" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -2483,7 +2597,7 @@
       </c>
       <c r="B3" s="6">
         <f>SUM('Detailed WARN Report '!G:G)</f>
-        <v>12555</v>
+        <v>13900</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -2492,7 +2606,7 @@
       </c>
       <c r="B4" s="6">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Permanent")</f>
-        <v>121</v>
+        <v>138</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -2519,7 +2633,7 @@
       </c>
       <c r="B7" s="6">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Permanent")</f>
-        <v>100</v>
+        <v>106</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -2528,7 +2642,7 @@
       </c>
       <c r="B8" s="6">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Temporary")</f>
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
@@ -2551,7 +2665,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:H229"/>
+  <dimension ref="A1:H255"/>
   <sheetFormatPr defaultColWidth="26" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.88671875" bestFit="1" customWidth="1"/>
@@ -2564,7 +2678,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="99.6" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
-        <v>393</v>
+        <v>431</v>
       </c>
       <c r="D1" s="7"/>
       <c r="E1" s="7"/>
@@ -2572,7 +2686,7 @@
       <c r="G1" s="7"/>
       <c r="H1" s="7"/>
     </row>
-    <row r="2" spans="1:8" s="1" customFormat="1" ht="24.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
         <v>0</v>
       </c>
@@ -8498,6 +8612,682 @@
       </c>
       <c r="H229" s="17" t="s">
         <v>392</v>
+      </c>
+    </row>
+    <row r="230" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A230" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="B230" s="19">
+        <v>45163</v>
+      </c>
+      <c r="C230" s="19">
+        <v>45190</v>
+      </c>
+      <c r="D230" s="19">
+        <v>45227</v>
+      </c>
+      <c r="E230" s="20" t="s">
+        <v>393</v>
+      </c>
+      <c r="F230" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G230" s="21">
+        <v>74</v>
+      </c>
+      <c r="H230" s="22" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="231" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A231" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="B231" s="14">
+        <v>45112</v>
+      </c>
+      <c r="C231" s="14">
+        <v>45190</v>
+      </c>
+      <c r="D231" s="14">
+        <v>45177</v>
+      </c>
+      <c r="E231" s="15" t="s">
+        <v>395</v>
+      </c>
+      <c r="F231" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G231" s="16">
+        <v>57</v>
+      </c>
+      <c r="H231" s="17" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="232" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A232" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="B232" s="19">
+        <v>45112</v>
+      </c>
+      <c r="C232" s="19">
+        <v>45190</v>
+      </c>
+      <c r="D232" s="19">
+        <v>45177</v>
+      </c>
+      <c r="E232" s="20" t="s">
+        <v>395</v>
+      </c>
+      <c r="F232" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G232" s="21">
+        <v>68</v>
+      </c>
+      <c r="H232" s="22" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="233" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A233" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="B233" s="14">
+        <v>45112</v>
+      </c>
+      <c r="C233" s="14">
+        <v>45190</v>
+      </c>
+      <c r="D233" s="14">
+        <v>45177</v>
+      </c>
+      <c r="E233" s="15" t="s">
+        <v>398</v>
+      </c>
+      <c r="F233" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G233" s="16">
+        <v>1</v>
+      </c>
+      <c r="H233" s="17" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="234" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A234" s="18" t="s">
+        <v>97</v>
+      </c>
+      <c r="B234" s="19">
+        <v>45160</v>
+      </c>
+      <c r="C234" s="19">
+        <v>45190</v>
+      </c>
+      <c r="D234" s="19">
+        <v>45220</v>
+      </c>
+      <c r="E234" s="20" t="s">
+        <v>400</v>
+      </c>
+      <c r="F234" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G234" s="21">
+        <v>4</v>
+      </c>
+      <c r="H234" s="22" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="235" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A235" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B235" s="14">
+        <v>45160</v>
+      </c>
+      <c r="C235" s="14">
+        <v>45190</v>
+      </c>
+      <c r="D235" s="14">
+        <v>45219</v>
+      </c>
+      <c r="E235" s="15" t="s">
+        <v>402</v>
+      </c>
+      <c r="F235" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G235" s="16">
+        <v>50</v>
+      </c>
+      <c r="H235" s="17" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="236" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A236" s="18" t="s">
+        <v>252</v>
+      </c>
+      <c r="B236" s="19">
+        <v>45160</v>
+      </c>
+      <c r="C236" s="19">
+        <v>45190</v>
+      </c>
+      <c r="D236" s="19">
+        <v>45220</v>
+      </c>
+      <c r="E236" s="20" t="s">
+        <v>400</v>
+      </c>
+      <c r="F236" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G236" s="21">
+        <v>150</v>
+      </c>
+      <c r="H236" s="22" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="237" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A237" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="B237" s="14">
+        <v>45134</v>
+      </c>
+      <c r="C237" s="14">
+        <v>45191</v>
+      </c>
+      <c r="D237" s="14">
+        <v>45170</v>
+      </c>
+      <c r="E237" s="15" t="s">
+        <v>405</v>
+      </c>
+      <c r="F237" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G237" s="16">
+        <v>9</v>
+      </c>
+      <c r="H237" s="17" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="238" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A238" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="B238" s="19">
+        <v>45134</v>
+      </c>
+      <c r="C238" s="19">
+        <v>45191</v>
+      </c>
+      <c r="D238" s="19">
+        <v>45170</v>
+      </c>
+      <c r="E238" s="20" t="s">
+        <v>405</v>
+      </c>
+      <c r="F238" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G238" s="21">
+        <v>13</v>
+      </c>
+      <c r="H238" s="22" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="239" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A239" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="B239" s="14">
+        <v>45134</v>
+      </c>
+      <c r="C239" s="14">
+        <v>45191</v>
+      </c>
+      <c r="D239" s="14">
+        <v>45170</v>
+      </c>
+      <c r="E239" s="15" t="s">
+        <v>405</v>
+      </c>
+      <c r="F239" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G239" s="16">
+        <v>3</v>
+      </c>
+      <c r="H239" s="17" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="240" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A240" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="B240" s="19">
+        <v>45134</v>
+      </c>
+      <c r="C240" s="19">
+        <v>45191</v>
+      </c>
+      <c r="D240" s="19">
+        <v>45170</v>
+      </c>
+      <c r="E240" s="20" t="s">
+        <v>405</v>
+      </c>
+      <c r="F240" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G240" s="21">
+        <v>12</v>
+      </c>
+      <c r="H240" s="22" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="241" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A241" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B241" s="14">
+        <v>45141</v>
+      </c>
+      <c r="C241" s="14">
+        <v>45191</v>
+      </c>
+      <c r="D241" s="14">
+        <v>45199</v>
+      </c>
+      <c r="E241" s="15" t="s">
+        <v>410</v>
+      </c>
+      <c r="F241" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G241" s="16">
+        <v>20</v>
+      </c>
+      <c r="H241" s="17" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="242" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A242" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="B242" s="19">
+        <v>45136</v>
+      </c>
+      <c r="C242" s="19">
+        <v>45194</v>
+      </c>
+      <c r="D242" s="19">
+        <v>45199</v>
+      </c>
+      <c r="E242" s="20" t="s">
+        <v>412</v>
+      </c>
+      <c r="F242" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G242" s="21">
+        <v>10</v>
+      </c>
+      <c r="H242" s="22" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="243" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A243" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B243" s="14">
+        <v>45149</v>
+      </c>
+      <c r="C243" s="14">
+        <v>45194</v>
+      </c>
+      <c r="D243" s="14">
+        <v>45215</v>
+      </c>
+      <c r="E243" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="F243" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G243" s="16">
+        <v>240</v>
+      </c>
+      <c r="H243" s="17" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="244" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A244" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="B244" s="19">
+        <v>45152</v>
+      </c>
+      <c r="C244" s="19">
+        <v>45194</v>
+      </c>
+      <c r="D244" s="19">
+        <v>45214</v>
+      </c>
+      <c r="E244" s="20" t="s">
+        <v>415</v>
+      </c>
+      <c r="F244" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G244" s="21">
+        <v>139</v>
+      </c>
+      <c r="H244" s="22" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="245" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A245" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B245" s="14">
+        <v>45136</v>
+      </c>
+      <c r="C245" s="14">
+        <v>45194</v>
+      </c>
+      <c r="D245" s="14">
+        <v>45199</v>
+      </c>
+      <c r="E245" s="15" t="s">
+        <v>412</v>
+      </c>
+      <c r="F245" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G245" s="16">
+        <v>13</v>
+      </c>
+      <c r="H245" s="17" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="246" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A246" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="B246" s="19">
+        <v>45160</v>
+      </c>
+      <c r="C246" s="19">
+        <v>45195</v>
+      </c>
+      <c r="D246" s="19">
+        <v>45205</v>
+      </c>
+      <c r="E246" s="20" t="s">
+        <v>395</v>
+      </c>
+      <c r="F246" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G246" s="21">
+        <v>54</v>
+      </c>
+      <c r="H246" s="22" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="247" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A247" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="B247" s="14">
+        <v>45161</v>
+      </c>
+      <c r="C247" s="14">
+        <v>45196</v>
+      </c>
+      <c r="D247" s="14">
+        <v>45221</v>
+      </c>
+      <c r="E247" s="15" t="s">
+        <v>419</v>
+      </c>
+      <c r="F247" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G247" s="16">
+        <v>21</v>
+      </c>
+      <c r="H247" s="17" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="248" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A248" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="B248" s="19">
+        <v>45153</v>
+      </c>
+      <c r="C248" s="19">
+        <v>45196</v>
+      </c>
+      <c r="D248" s="19">
+        <v>45185</v>
+      </c>
+      <c r="E248" s="20" t="s">
+        <v>421</v>
+      </c>
+      <c r="F248" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G248" s="21">
+        <v>53</v>
+      </c>
+      <c r="H248" s="22" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="249" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A249" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B249" s="14">
+        <v>45161</v>
+      </c>
+      <c r="C249" s="14">
+        <v>45196</v>
+      </c>
+      <c r="D249" s="14">
+        <v>45221</v>
+      </c>
+      <c r="E249" s="15" t="s">
+        <v>419</v>
+      </c>
+      <c r="F249" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G249" s="16">
+        <v>95</v>
+      </c>
+      <c r="H249" s="17" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="250" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A250" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="B250" s="19">
+        <v>45155</v>
+      </c>
+      <c r="C250" s="19">
+        <v>45196</v>
+      </c>
+      <c r="D250" s="19">
+        <v>45215</v>
+      </c>
+      <c r="E250" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="F250" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G250" s="21">
+        <v>2</v>
+      </c>
+      <c r="H250" s="22" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="251" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A251" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="B251" s="14">
+        <v>45189</v>
+      </c>
+      <c r="C251" s="14">
+        <v>45196</v>
+      </c>
+      <c r="D251" s="14">
+        <v>45250</v>
+      </c>
+      <c r="E251" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="F251" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G251" s="16">
+        <v>1</v>
+      </c>
+      <c r="H251" s="17" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="252" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A252" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="B252" s="19">
+        <v>45156</v>
+      </c>
+      <c r="C252" s="19">
+        <v>45196</v>
+      </c>
+      <c r="D252" s="19">
+        <v>45150</v>
+      </c>
+      <c r="E252" s="20" t="s">
+        <v>424</v>
+      </c>
+      <c r="F252" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="G252" s="21">
+        <v>110</v>
+      </c>
+      <c r="H252" s="22" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="253" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A253" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="B253" s="14">
+        <v>45161</v>
+      </c>
+      <c r="C253" s="14">
+        <v>45196</v>
+      </c>
+      <c r="D253" s="14">
+        <v>45233</v>
+      </c>
+      <c r="E253" s="15" t="s">
+        <v>426</v>
+      </c>
+      <c r="F253" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G253" s="16">
+        <v>80</v>
+      </c>
+      <c r="H253" s="17" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="254" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A254" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="B254" s="19">
+        <v>45154</v>
+      </c>
+      <c r="C254" s="19">
+        <v>45196</v>
+      </c>
+      <c r="D254" s="19">
+        <v>45200</v>
+      </c>
+      <c r="E254" s="20" t="s">
+        <v>428</v>
+      </c>
+      <c r="F254" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="G254" s="21">
+        <v>44</v>
+      </c>
+      <c r="H254" s="22" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="255" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A255" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="B255" s="14">
+        <v>45154</v>
+      </c>
+      <c r="C255" s="14">
+        <v>45196</v>
+      </c>
+      <c r="D255" s="14">
+        <v>45200</v>
+      </c>
+      <c r="E255" s="15" t="s">
+        <v>428</v>
+      </c>
+      <c r="F255" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="G255" s="16">
+        <v>22</v>
+      </c>
+      <c r="H255" s="17" t="s">
+        <v>430</v>
       </c>
     </row>
   </sheetData>
@@ -8639,13 +9429,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F5AB9ED-5A1C-47B2-83C2-F768FFC81423}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9043B263-9323-43AE-A469-90F10B3677EB}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EE2358EB-C708-41B4-9E09-C6E77F256BA5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3BA8219-99D3-470D-9DE4-E21C87C0BD92}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E742885-4A58-4ED2-8394-56012BBEE4E6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5932A20B-F538-4D97-9BE1-0551A842EE0A}"/>
 </file>
--- a/data/warn-scraper/cache/ca/warn_report1.xlsx
+++ b/data/warn-scraper/cache/ca/warn_report1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\WSB-CO\Communications Unit\Website Management\WARN (Worker Adjustment and Retraining Notification) Updates\2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C059C3D-9E75-43F0-AC76-11C7665B8AAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F73AAD66-ABBA-43E7-8F7E-DCBB58A0015C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="29895" yWindow="1230" windowWidth="21600" windowHeight="11430" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1035" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1147" uniqueCount="469">
   <si>
     <t>County/Parish</t>
   </si>
@@ -1397,6 +1397,117 @@
     <t>1211 &amp; 1215 Park Center Drive  Vista CA 92081</t>
   </si>
   <si>
+    <t>Farmers Insurance Exchange</t>
+  </si>
+  <si>
+    <t>6301 Owensmouth Avenue  Woodland Hills CA 91367</t>
+  </si>
+  <si>
+    <t>6303 Owensmouth Avenue  Woodland Hills CA 91367</t>
+  </si>
+  <si>
+    <t>Farmers Group, Inc.</t>
+  </si>
+  <si>
+    <t>DazPak Flexible Packaging</t>
+  </si>
+  <si>
+    <t>17032 Armstrong Ave.  Irvine CA 92614</t>
+  </si>
+  <si>
+    <t>Legacy Supply Chain Services II</t>
+  </si>
+  <si>
+    <t>4155 Wineville Road  Jurupa Valley CA 91752</t>
+  </si>
+  <si>
+    <t>17825 Indian Street  Moreno Valley CA 92551</t>
+  </si>
+  <si>
+    <t>Juul Labs, Inc.</t>
+  </si>
+  <si>
+    <t>947 Illinois Street Units 108 and 1000 San Francisco CA 94107</t>
+  </si>
+  <si>
+    <t>2475 3rd Street Units 205, 244, 256, 264, 270, 271 San Francisco CA 94107</t>
+  </si>
+  <si>
+    <t>2325-2699 3rd Street Units 601 and 605 San Francisco CA 94107</t>
+  </si>
+  <si>
+    <t>Del Friscos Grille</t>
+  </si>
+  <si>
+    <t>1551 Ocean Avenue, Suite 105  Santa Monica CA 90401</t>
+  </si>
+  <si>
+    <t>Kraft Heinz Foods Company</t>
+  </si>
+  <si>
+    <t>2450 White Road  Irvine CA 92614</t>
+  </si>
+  <si>
+    <t>Splash Cafe, Inc. dba Splash Cafe Artisan Bakery</t>
+  </si>
+  <si>
+    <t>1491 Monterey Street  San Luis Obispo CA 93401</t>
+  </si>
+  <si>
+    <t>PLI Holdings, Inc.</t>
+  </si>
+  <si>
+    <t>111 North Baldwin Park Boulevard  City of Industry CA 91746</t>
+  </si>
+  <si>
+    <t>6420 E. Pacific Coast Hwy.  Long Beach CA 90803</t>
+  </si>
+  <si>
+    <t>FUJIFILM Irvine Scientific, Inc.</t>
+  </si>
+  <si>
+    <t>17112 Armstrong Ave.  Irvine CA 92614</t>
+  </si>
+  <si>
+    <t>Kings Garden, Inc.</t>
+  </si>
+  <si>
+    <t>19533 McLane St.  Palm Springs CA 92262</t>
+  </si>
+  <si>
+    <t>3535 N Anza Road  Palm Springs CA 92262</t>
+  </si>
+  <si>
+    <t>3585 Del Sol  Palm Springs CA 92262</t>
+  </si>
+  <si>
+    <t>63795 19th Ave  Palm Springs CA 92262</t>
+  </si>
+  <si>
+    <t>2511 Daimler St  Santa Ana CA 92705</t>
+  </si>
+  <si>
+    <t>2601 Daimler St  Santa Ana CA 92705</t>
+  </si>
+  <si>
+    <t>1700 Carnegie Ave  Santa Ana CA 92705</t>
+  </si>
+  <si>
+    <t>1800 Carnegie Ave  Santa Ana CA 92705</t>
+  </si>
+  <si>
+    <t>1880 E St. Andrew Pl  Santa Ana CA 92705</t>
+  </si>
+  <si>
+    <t>1830 E Warner Ave  Santa Ana CA 92705</t>
+  </si>
+  <si>
+    <t>Sonoco</t>
+  </si>
+  <si>
+    <t>1030 North Anderson Road  Exeter CA 93221</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">WARN REPORT - </t>
     </r>
@@ -1408,7 +1519,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>07/01/23 to 09/27/23</t>
+      <t>07/01/23 to 10/02/23</t>
     </r>
     <r>
       <rPr>
@@ -1428,7 +1539,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>A detailed WARN summary by county and filtered according to received date. Table Spans cells A2 through H255.</t>
+      <t>A detailed WARN summary by county and filtered according to received date. Table Spans cells A2 through H283.</t>
     </r>
   </si>
 </sst>
@@ -2212,8 +2323,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:H255" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
-  <autoFilter ref="A2:H255" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:H283" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
+  <autoFilter ref="A2:H283" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -2597,7 +2708,7 @@
       </c>
       <c r="B3" s="6">
         <f>SUM('Detailed WARN Report '!G:G)</f>
-        <v>13900</v>
+        <v>15240</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -2606,7 +2717,7 @@
       </c>
       <c r="B4" s="6">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Permanent")</f>
-        <v>138</v>
+        <v>157</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -2633,7 +2744,7 @@
       </c>
       <c r="B7" s="6">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Permanent")</f>
-        <v>106</v>
+        <v>115</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -2665,7 +2776,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:H255"/>
+  <dimension ref="A1:H283"/>
   <sheetFormatPr defaultColWidth="26" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.88671875" bestFit="1" customWidth="1"/>
@@ -2673,12 +2784,12 @@
     <col min="5" max="5" width="54.88671875" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.33203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="52.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="55" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="99.6" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
-        <v>431</v>
+        <v>468</v>
       </c>
       <c r="D1" s="7"/>
       <c r="E1" s="7"/>
@@ -2686,7 +2797,7 @@
       <c r="G1" s="7"/>
       <c r="H1" s="7"/>
     </row>
-    <row r="2" spans="1:8" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" s="1" customFormat="1" ht="24.6" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
         <v>0</v>
       </c>
@@ -9288,6 +9399,734 @@
       </c>
       <c r="H255" s="17" t="s">
         <v>430</v>
+      </c>
+    </row>
+    <row r="256" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A256" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="B256" s="19">
+        <v>45166</v>
+      </c>
+      <c r="C256" s="19">
+        <v>45197</v>
+      </c>
+      <c r="D256" s="19">
+        <v>45230</v>
+      </c>
+      <c r="E256" s="20" t="s">
+        <v>431</v>
+      </c>
+      <c r="F256" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G256" s="21">
+        <v>136</v>
+      </c>
+      <c r="H256" s="22" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="257" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A257" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B257" s="14">
+        <v>45166</v>
+      </c>
+      <c r="C257" s="14">
+        <v>45197</v>
+      </c>
+      <c r="D257" s="14">
+        <v>45230</v>
+      </c>
+      <c r="E257" s="15" t="s">
+        <v>431</v>
+      </c>
+      <c r="F257" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G257" s="16">
+        <v>2</v>
+      </c>
+      <c r="H257" s="17" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="258" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A258" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="B258" s="19">
+        <v>45166</v>
+      </c>
+      <c r="C258" s="19">
+        <v>45197</v>
+      </c>
+      <c r="D258" s="19">
+        <v>45230</v>
+      </c>
+      <c r="E258" s="20" t="s">
+        <v>434</v>
+      </c>
+      <c r="F258" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G258" s="21">
+        <v>68</v>
+      </c>
+      <c r="H258" s="22" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="259" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A259" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B259" s="14">
+        <v>45166</v>
+      </c>
+      <c r="C259" s="14">
+        <v>45197</v>
+      </c>
+      <c r="D259" s="14">
+        <v>45230</v>
+      </c>
+      <c r="E259" s="15" t="s">
+        <v>434</v>
+      </c>
+      <c r="F259" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G259" s="16">
+        <v>163</v>
+      </c>
+      <c r="H259" s="17" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="260" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A260" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="B260" s="19">
+        <v>45152</v>
+      </c>
+      <c r="C260" s="19">
+        <v>45197</v>
+      </c>
+      <c r="D260" s="19">
+        <v>45214</v>
+      </c>
+      <c r="E260" s="20" t="s">
+        <v>435</v>
+      </c>
+      <c r="F260" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G260" s="21">
+        <v>19</v>
+      </c>
+      <c r="H260" s="22" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="261" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A261" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B261" s="14">
+        <v>45166</v>
+      </c>
+      <c r="C261" s="14">
+        <v>45197</v>
+      </c>
+      <c r="D261" s="14">
+        <v>45228</v>
+      </c>
+      <c r="E261" s="15" t="s">
+        <v>437</v>
+      </c>
+      <c r="F261" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G261" s="16">
+        <v>39</v>
+      </c>
+      <c r="H261" s="17" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="262" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A262" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B262" s="19">
+        <v>45166</v>
+      </c>
+      <c r="C262" s="19">
+        <v>45197</v>
+      </c>
+      <c r="D262" s="19">
+        <v>45228</v>
+      </c>
+      <c r="E262" s="20" t="s">
+        <v>437</v>
+      </c>
+      <c r="F262" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G262" s="21">
+        <v>14</v>
+      </c>
+      <c r="H262" s="22" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="263" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A263" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B263" s="14">
+        <v>45163</v>
+      </c>
+      <c r="C263" s="14">
+        <v>45197</v>
+      </c>
+      <c r="D263" s="14">
+        <v>45214</v>
+      </c>
+      <c r="E263" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="F263" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G263" s="16">
+        <v>58</v>
+      </c>
+      <c r="H263" s="17" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="264" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A264" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B264" s="19">
+        <v>45162</v>
+      </c>
+      <c r="C264" s="19">
+        <v>45197</v>
+      </c>
+      <c r="D264" s="19">
+        <v>45177</v>
+      </c>
+      <c r="E264" s="20" t="s">
+        <v>440</v>
+      </c>
+      <c r="F264" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G264" s="21">
+        <v>20</v>
+      </c>
+      <c r="H264" s="22" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="265" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A265" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="B265" s="14">
+        <v>45162</v>
+      </c>
+      <c r="C265" s="14">
+        <v>45197</v>
+      </c>
+      <c r="D265" s="14">
+        <v>45177</v>
+      </c>
+      <c r="E265" s="15" t="s">
+        <v>440</v>
+      </c>
+      <c r="F265" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G265" s="16">
+        <v>20</v>
+      </c>
+      <c r="H265" s="17" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="266" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A266" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B266" s="19">
+        <v>45162</v>
+      </c>
+      <c r="C266" s="19">
+        <v>45197</v>
+      </c>
+      <c r="D266" s="19">
+        <v>45177</v>
+      </c>
+      <c r="E266" s="20" t="s">
+        <v>440</v>
+      </c>
+      <c r="F266" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G266" s="21">
+        <v>20</v>
+      </c>
+      <c r="H266" s="22" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="267" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A267" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B267" s="14">
+        <v>45168</v>
+      </c>
+      <c r="C267" s="14">
+        <v>45198</v>
+      </c>
+      <c r="D267" s="14">
+        <v>45230</v>
+      </c>
+      <c r="E267" s="15" t="s">
+        <v>444</v>
+      </c>
+      <c r="F267" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G267" s="16">
+        <v>53</v>
+      </c>
+      <c r="H267" s="17" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="268" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A268" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="B268" s="19">
+        <v>45169</v>
+      </c>
+      <c r="C268" s="19">
+        <v>45198</v>
+      </c>
+      <c r="D268" s="19">
+        <v>45230</v>
+      </c>
+      <c r="E268" s="20" t="s">
+        <v>446</v>
+      </c>
+      <c r="F268" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G268" s="21">
+        <v>60</v>
+      </c>
+      <c r="H268" s="22" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="269" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A269" s="13" t="s">
+        <v>368</v>
+      </c>
+      <c r="B269" s="14">
+        <v>45167</v>
+      </c>
+      <c r="C269" s="14">
+        <v>45198</v>
+      </c>
+      <c r="D269" s="14">
+        <v>45230</v>
+      </c>
+      <c r="E269" s="15" t="s">
+        <v>448</v>
+      </c>
+      <c r="F269" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G269" s="16">
+        <v>29</v>
+      </c>
+      <c r="H269" s="17" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="270" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A270" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="B270" s="19">
+        <v>45170</v>
+      </c>
+      <c r="C270" s="19">
+        <v>45201</v>
+      </c>
+      <c r="D270" s="19">
+        <v>45244</v>
+      </c>
+      <c r="E270" s="20" t="s">
+        <v>450</v>
+      </c>
+      <c r="F270" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G270" s="21">
+        <v>217</v>
+      </c>
+      <c r="H270" s="22" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="271" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A271" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B271" s="14">
+        <v>45169</v>
+      </c>
+      <c r="C271" s="14">
+        <v>45201</v>
+      </c>
+      <c r="D271" s="14">
+        <v>45231</v>
+      </c>
+      <c r="E271" s="15" t="s">
+        <v>288</v>
+      </c>
+      <c r="F271" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G271" s="16">
+        <v>3</v>
+      </c>
+      <c r="H271" s="17" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="272" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A272" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="B272" s="19">
+        <v>45140</v>
+      </c>
+      <c r="C272" s="19">
+        <v>45201</v>
+      </c>
+      <c r="D272" s="19">
+        <v>45205</v>
+      </c>
+      <c r="E272" s="20" t="s">
+        <v>453</v>
+      </c>
+      <c r="F272" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G272" s="21">
+        <v>6</v>
+      </c>
+      <c r="H272" s="22" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="273" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A273" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B273" s="14">
+        <v>45147</v>
+      </c>
+      <c r="C273" s="14">
+        <v>45201</v>
+      </c>
+      <c r="D273" s="14">
+        <v>45205</v>
+      </c>
+      <c r="E273" s="15" t="s">
+        <v>455</v>
+      </c>
+      <c r="F273" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G273" s="16">
+        <v>59</v>
+      </c>
+      <c r="H273" s="17" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="274" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A274" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B274" s="19">
+        <v>45147</v>
+      </c>
+      <c r="C274" s="19">
+        <v>45201</v>
+      </c>
+      <c r="D274" s="19">
+        <v>45205</v>
+      </c>
+      <c r="E274" s="20" t="s">
+        <v>455</v>
+      </c>
+      <c r="F274" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G274" s="21">
+        <v>4</v>
+      </c>
+      <c r="H274" s="22" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="275" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A275" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B275" s="14">
+        <v>45147</v>
+      </c>
+      <c r="C275" s="14">
+        <v>45201</v>
+      </c>
+      <c r="D275" s="14">
+        <v>45205</v>
+      </c>
+      <c r="E275" s="15" t="s">
+        <v>455</v>
+      </c>
+      <c r="F275" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G275" s="16">
+        <v>3</v>
+      </c>
+      <c r="H275" s="17" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="276" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A276" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B276" s="19">
+        <v>45147</v>
+      </c>
+      <c r="C276" s="19">
+        <v>45201</v>
+      </c>
+      <c r="D276" s="19">
+        <v>45205</v>
+      </c>
+      <c r="E276" s="20" t="s">
+        <v>455</v>
+      </c>
+      <c r="F276" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G276" s="21">
+        <v>4</v>
+      </c>
+      <c r="H276" s="22" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="277" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A277" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="B277" s="14">
+        <v>45140</v>
+      </c>
+      <c r="C277" s="14">
+        <v>45201</v>
+      </c>
+      <c r="D277" s="14">
+        <v>45205</v>
+      </c>
+      <c r="E277" s="15" t="s">
+        <v>453</v>
+      </c>
+      <c r="F277" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G277" s="16">
+        <v>18</v>
+      </c>
+      <c r="H277" s="17" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="278" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A278" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="B278" s="19">
+        <v>45140</v>
+      </c>
+      <c r="C278" s="19">
+        <v>45201</v>
+      </c>
+      <c r="D278" s="19">
+        <v>45205</v>
+      </c>
+      <c r="E278" s="20" t="s">
+        <v>453</v>
+      </c>
+      <c r="F278" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G278" s="21">
+        <v>1</v>
+      </c>
+      <c r="H278" s="22" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="279" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A279" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="B279" s="14">
+        <v>45140</v>
+      </c>
+      <c r="C279" s="14">
+        <v>45201</v>
+      </c>
+      <c r="D279" s="14">
+        <v>45205</v>
+      </c>
+      <c r="E279" s="15" t="s">
+        <v>453</v>
+      </c>
+      <c r="F279" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G279" s="16">
+        <v>7</v>
+      </c>
+      <c r="H279" s="17" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="280" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A280" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="B280" s="19">
+        <v>45140</v>
+      </c>
+      <c r="C280" s="19">
+        <v>45201</v>
+      </c>
+      <c r="D280" s="19">
+        <v>45205</v>
+      </c>
+      <c r="E280" s="20" t="s">
+        <v>453</v>
+      </c>
+      <c r="F280" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G280" s="21">
+        <v>2</v>
+      </c>
+      <c r="H280" s="22" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="281" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A281" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="B281" s="14">
+        <v>45140</v>
+      </c>
+      <c r="C281" s="14">
+        <v>45201</v>
+      </c>
+      <c r="D281" s="14">
+        <v>45205</v>
+      </c>
+      <c r="E281" s="15" t="s">
+        <v>453</v>
+      </c>
+      <c r="F281" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G281" s="16">
+        <v>11</v>
+      </c>
+      <c r="H281" s="17" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="282" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A282" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="B282" s="19">
+        <v>45140</v>
+      </c>
+      <c r="C282" s="19">
+        <v>45201</v>
+      </c>
+      <c r="D282" s="19">
+        <v>45205</v>
+      </c>
+      <c r="E282" s="20" t="s">
+        <v>453</v>
+      </c>
+      <c r="F282" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G282" s="21">
+        <v>12</v>
+      </c>
+      <c r="H282" s="22" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="283" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A283" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="B283" s="14">
+        <v>45170</v>
+      </c>
+      <c r="C283" s="14">
+        <v>45201</v>
+      </c>
+      <c r="D283" s="14">
+        <v>45231</v>
+      </c>
+      <c r="E283" s="15" t="s">
+        <v>466</v>
+      </c>
+      <c r="F283" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G283" s="16">
+        <v>292</v>
+      </c>
+      <c r="H283" s="17" t="s">
+        <v>467</v>
       </c>
     </row>
   </sheetData>
@@ -9429,13 +10268,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9043B263-9323-43AE-A469-90F10B3677EB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F594D079-1D81-4918-A813-548FE0BD6918}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3BA8219-99D3-470D-9DE4-E21C87C0BD92}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8AA973C8-1F75-4744-8955-4159BDE7D63D}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5932A20B-F538-4D97-9BE1-0551A842EE0A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE31A677-60B7-46F0-90C7-4F72848EFE0E}"/>
 </file>
--- a/data/warn-scraper/cache/ca/warn_report1.xlsx
+++ b/data/warn-scraper/cache/ca/warn_report1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\WSB-CO\Communications Unit\Website Management\WARN (Worker Adjustment and Retraining Notification) Updates\2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F73AAD66-ABBA-43E7-8F7E-DCBB58A0015C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7DF38DB-9310-4869-9BD5-BCB4144BC38C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="29895" yWindow="1230" windowWidth="21600" windowHeight="11430" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1147" uniqueCount="469">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1267" uniqueCount="509">
   <si>
     <t>County/Parish</t>
   </si>
@@ -1508,6 +1508,126 @@
     <t>1030 North Anderson Road  Exeter CA 93221</t>
   </si>
   <si>
+    <t>Kaiser Foundation Hospitals</t>
+  </si>
+  <si>
+    <t>5810 Owens Dr.  Pleasanton CA 94588</t>
+  </si>
+  <si>
+    <t>99 S. Oakland Ave.  Pasadena CA 91101</t>
+  </si>
+  <si>
+    <t>Kaiser Foundation Hospitals - Pasadena</t>
+  </si>
+  <si>
+    <t>74 N. Pasadena Ave.  Pasadena CA 91103</t>
+  </si>
+  <si>
+    <t>Kaiser Foundation Hospitals-Walnut</t>
+  </si>
+  <si>
+    <t>393 E. Walnut St.  Pasadena CA 91188</t>
+  </si>
+  <si>
+    <t>Kaiser Foundation Hospitals-Los Robles</t>
+  </si>
+  <si>
+    <t>199 S. Los Robles Ave.  Pasadena CA 91101</t>
+  </si>
+  <si>
+    <t>Boardriders Wholesale, LLC</t>
+  </si>
+  <si>
+    <t>1000 Universal City Plaza #196  Universal City CA 91608</t>
+  </si>
+  <si>
+    <t>Kaiser Foundation Hospitals - Ordway Building</t>
+  </si>
+  <si>
+    <t>1 Kaiser Plaza-Ordway Building  Oakland CA 94612</t>
+  </si>
+  <si>
+    <t>1950 Franklin St.  Oakland CA 94612</t>
+  </si>
+  <si>
+    <t>Kaiser Foundation Hospitals - Harrison</t>
+  </si>
+  <si>
+    <t>1800 Harrison St.  Oakland CA 94612</t>
+  </si>
+  <si>
+    <t>5600 Argosy Circle Suite 100  Huntington Beach CA 92649</t>
+  </si>
+  <si>
+    <t>960 W 16th St.  Costa Mesa CA 92627</t>
+  </si>
+  <si>
+    <t>1310 Cantu-Galleano Ranch Rd.  Mira Loma CA 91752</t>
+  </si>
+  <si>
+    <t>10740 4th St.  Rancho Cucamonga CA 91730</t>
+  </si>
+  <si>
+    <t>Coronado Brewing Company, Inc.</t>
+  </si>
+  <si>
+    <t>875 Seacoast Dr.  Imperial Beach CA 91932</t>
+  </si>
+  <si>
+    <t>8954 Rio San Diego Dr.  San Diego CA 92108</t>
+  </si>
+  <si>
+    <t>3100 Thornton Ave.  Burbank CA 91504</t>
+  </si>
+  <si>
+    <t>California Resources Corporation</t>
+  </si>
+  <si>
+    <t>9600 Ming Avenue  Bakersfield CA 93311</t>
+  </si>
+  <si>
+    <t>5300 District Boulevard  Bakersfield CA 93313</t>
+  </si>
+  <si>
+    <t>9522 Oil Field Road  Bakersfield CA 93308</t>
+  </si>
+  <si>
+    <t>11450 Elk Hills Road  Tupman CA 93276</t>
+  </si>
+  <si>
+    <t>4809 Elk Hills Road  Tupman CA 93276</t>
+  </si>
+  <si>
+    <t>25761 Hwy 119  Taft CA 93268</t>
+  </si>
+  <si>
+    <t>16223 S. Granite Road  Bakersfield CA 93308</t>
+  </si>
+  <si>
+    <t>30565 Merced Avenue  Shafter CA 93263</t>
+  </si>
+  <si>
+    <t>Jensen Enterprises Inc. dba Jensen Precast</t>
+  </si>
+  <si>
+    <t>5400 Raley Boulevard  Sacramento CA 95838</t>
+  </si>
+  <si>
+    <t>Foundation for California Community Colleges</t>
+  </si>
+  <si>
+    <t>1102 Q Street, Suite 4800  Sacramento CA 95811</t>
+  </si>
+  <si>
+    <t>AppFolio, Inc.</t>
+  </si>
+  <si>
+    <t>8620 Spectrum Center Blvd., 11th Floor  San Diego CA 92123</t>
+  </si>
+  <si>
+    <t>70 Castilian Drive  Goleta CA 93117</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">WARN REPORT - </t>
     </r>
@@ -1519,7 +1639,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>07/01/23 to 10/02/23</t>
+      <t>07/01/23 to 10/04/23</t>
     </r>
     <r>
       <rPr>
@@ -1539,7 +1659,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>A detailed WARN summary by county and filtered according to received date. Table Spans cells A2 through H283.</t>
+      <t>A detailed WARN summary by county and filtered according to received date. Table Spans cells A2 through H313.</t>
     </r>
   </si>
 </sst>
@@ -2323,8 +2443,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:H283" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
-  <autoFilter ref="A2:H283" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:H313" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
+  <autoFilter ref="A2:H313" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -2708,7 +2828,7 @@
       </c>
       <c r="B3" s="6">
         <f>SUM('Detailed WARN Report '!G:G)</f>
-        <v>15240</v>
+        <v>15871</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -2717,7 +2837,7 @@
       </c>
       <c r="B4" s="6">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Permanent")</f>
-        <v>157</v>
+        <v>185</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -2744,7 +2864,7 @@
       </c>
       <c r="B7" s="6">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Permanent")</f>
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -2776,7 +2896,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:H283"/>
+  <dimension ref="A1:H313"/>
   <sheetFormatPr defaultColWidth="26" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.88671875" bestFit="1" customWidth="1"/>
@@ -2789,7 +2909,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="99.6" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
-        <v>468</v>
+        <v>508</v>
       </c>
       <c r="D1" s="7"/>
       <c r="E1" s="7"/>
@@ -10127,6 +10247,786 @@
       </c>
       <c r="H283" s="17" t="s">
         <v>467</v>
+      </c>
+    </row>
+    <row r="284" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A284" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="B284" s="19">
+        <v>45181</v>
+      </c>
+      <c r="C284" s="19">
+        <v>45202</v>
+      </c>
+      <c r="D284" s="19">
+        <v>45240</v>
+      </c>
+      <c r="E284" s="20" t="s">
+        <v>468</v>
+      </c>
+      <c r="F284" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G284" s="21">
+        <v>21</v>
+      </c>
+      <c r="H284" s="22" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="285" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A285" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B285" s="14">
+        <v>45181</v>
+      </c>
+      <c r="C285" s="14">
+        <v>45202</v>
+      </c>
+      <c r="D285" s="14">
+        <v>45240</v>
+      </c>
+      <c r="E285" s="15" t="s">
+        <v>468</v>
+      </c>
+      <c r="F285" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G285" s="16">
+        <v>8</v>
+      </c>
+      <c r="H285" s="17" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="286" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A286" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="B286" s="19">
+        <v>45181</v>
+      </c>
+      <c r="C286" s="19">
+        <v>45202</v>
+      </c>
+      <c r="D286" s="19">
+        <v>45240</v>
+      </c>
+      <c r="E286" s="20" t="s">
+        <v>471</v>
+      </c>
+      <c r="F286" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G286" s="21">
+        <v>1</v>
+      </c>
+      <c r="H286" s="22" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="287" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A287" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B287" s="14">
+        <v>45181</v>
+      </c>
+      <c r="C287" s="14">
+        <v>45202</v>
+      </c>
+      <c r="D287" s="14">
+        <v>45240</v>
+      </c>
+      <c r="E287" s="15" t="s">
+        <v>473</v>
+      </c>
+      <c r="F287" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G287" s="16">
+        <v>8</v>
+      </c>
+      <c r="H287" s="17" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="288" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A288" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="B288" s="19">
+        <v>45181</v>
+      </c>
+      <c r="C288" s="19">
+        <v>45202</v>
+      </c>
+      <c r="D288" s="19">
+        <v>45240</v>
+      </c>
+      <c r="E288" s="20" t="s">
+        <v>475</v>
+      </c>
+      <c r="F288" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G288" s="21">
+        <v>1</v>
+      </c>
+      <c r="H288" s="22" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="289" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A289" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B289" s="14">
+        <v>45170</v>
+      </c>
+      <c r="C289" s="14">
+        <v>45202</v>
+      </c>
+      <c r="D289" s="14">
+        <v>45170</v>
+      </c>
+      <c r="E289" s="15" t="s">
+        <v>477</v>
+      </c>
+      <c r="F289" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G289" s="16">
+        <v>1</v>
+      </c>
+      <c r="H289" s="17" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="290" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A290" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="B290" s="19">
+        <v>45181</v>
+      </c>
+      <c r="C290" s="19">
+        <v>45202</v>
+      </c>
+      <c r="D290" s="19">
+        <v>45240</v>
+      </c>
+      <c r="E290" s="20" t="s">
+        <v>479</v>
+      </c>
+      <c r="F290" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G290" s="21">
+        <v>2</v>
+      </c>
+      <c r="H290" s="22" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="291" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A291" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="B291" s="14">
+        <v>45181</v>
+      </c>
+      <c r="C291" s="14">
+        <v>45202</v>
+      </c>
+      <c r="D291" s="14">
+        <v>45240</v>
+      </c>
+      <c r="E291" s="15" t="s">
+        <v>468</v>
+      </c>
+      <c r="F291" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G291" s="16">
+        <v>1</v>
+      </c>
+      <c r="H291" s="17" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="292" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A292" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="B292" s="19">
+        <v>45181</v>
+      </c>
+      <c r="C292" s="19">
+        <v>45202</v>
+      </c>
+      <c r="D292" s="19">
+        <v>45240</v>
+      </c>
+      <c r="E292" s="20" t="s">
+        <v>482</v>
+      </c>
+      <c r="F292" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G292" s="21">
+        <v>4</v>
+      </c>
+      <c r="H292" s="22" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="293" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A293" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="B293" s="14">
+        <v>45170</v>
+      </c>
+      <c r="C293" s="14">
+        <v>45202</v>
+      </c>
+      <c r="D293" s="14">
+        <v>45170</v>
+      </c>
+      <c r="E293" s="15" t="s">
+        <v>477</v>
+      </c>
+      <c r="F293" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G293" s="16">
+        <v>57</v>
+      </c>
+      <c r="H293" s="17" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="294" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A294" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="B294" s="19">
+        <v>45170</v>
+      </c>
+      <c r="C294" s="19">
+        <v>45202</v>
+      </c>
+      <c r="D294" s="19">
+        <v>45183</v>
+      </c>
+      <c r="E294" s="20" t="s">
+        <v>477</v>
+      </c>
+      <c r="F294" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G294" s="21">
+        <v>3</v>
+      </c>
+      <c r="H294" s="22" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="295" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A295" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="B295" s="14">
+        <v>45170</v>
+      </c>
+      <c r="C295" s="14">
+        <v>45202</v>
+      </c>
+      <c r="D295" s="14">
+        <v>45212</v>
+      </c>
+      <c r="E295" s="15" t="s">
+        <v>477</v>
+      </c>
+      <c r="F295" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G295" s="16">
+        <v>12</v>
+      </c>
+      <c r="H295" s="17" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="296" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A296" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="B296" s="19">
+        <v>45170</v>
+      </c>
+      <c r="C296" s="19">
+        <v>45202</v>
+      </c>
+      <c r="D296" s="19">
+        <v>45170</v>
+      </c>
+      <c r="E296" s="20" t="s">
+        <v>477</v>
+      </c>
+      <c r="F296" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G296" s="21">
+        <v>10</v>
+      </c>
+      <c r="H296" s="22" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="297" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A297" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B297" s="14">
+        <v>45170</v>
+      </c>
+      <c r="C297" s="14">
+        <v>45202</v>
+      </c>
+      <c r="D297" s="14">
+        <v>45170</v>
+      </c>
+      <c r="E297" s="15" t="s">
+        <v>477</v>
+      </c>
+      <c r="F297" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G297" s="16">
+        <v>1</v>
+      </c>
+      <c r="H297" s="17" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="298" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A298" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="B298" s="19">
+        <v>45181</v>
+      </c>
+      <c r="C298" s="19">
+        <v>45202</v>
+      </c>
+      <c r="D298" s="19">
+        <v>45240</v>
+      </c>
+      <c r="E298" s="20" t="s">
+        <v>468</v>
+      </c>
+      <c r="F298" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G298" s="21">
+        <v>1</v>
+      </c>
+      <c r="H298" s="22" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="299" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A299" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="B299" s="14">
+        <v>45177</v>
+      </c>
+      <c r="C299" s="14">
+        <v>45202</v>
+      </c>
+      <c r="D299" s="14">
+        <v>45237</v>
+      </c>
+      <c r="E299" s="15" t="s">
+        <v>488</v>
+      </c>
+      <c r="F299" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G299" s="16">
+        <v>27</v>
+      </c>
+      <c r="H299" s="17" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="300" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A300" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="B300" s="19">
+        <v>45181</v>
+      </c>
+      <c r="C300" s="19">
+        <v>45202</v>
+      </c>
+      <c r="D300" s="19">
+        <v>45240</v>
+      </c>
+      <c r="E300" s="20" t="s">
+        <v>468</v>
+      </c>
+      <c r="F300" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G300" s="21">
+        <v>1</v>
+      </c>
+      <c r="H300" s="22" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="301" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A301" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B301" s="14">
+        <v>45181</v>
+      </c>
+      <c r="C301" s="14">
+        <v>45202</v>
+      </c>
+      <c r="D301" s="14">
+        <v>45240</v>
+      </c>
+      <c r="E301" s="15" t="s">
+        <v>468</v>
+      </c>
+      <c r="F301" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G301" s="16">
+        <v>1</v>
+      </c>
+      <c r="H301" s="17" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="302" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A302" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="B302" s="19">
+        <v>45166</v>
+      </c>
+      <c r="C302" s="19">
+        <v>45203</v>
+      </c>
+      <c r="D302" s="19">
+        <v>45166</v>
+      </c>
+      <c r="E302" s="20" t="s">
+        <v>492</v>
+      </c>
+      <c r="F302" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G302" s="21">
+        <v>26</v>
+      </c>
+      <c r="H302" s="22" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="303" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A303" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B303" s="14">
+        <v>45166</v>
+      </c>
+      <c r="C303" s="14">
+        <v>45203</v>
+      </c>
+      <c r="D303" s="14">
+        <v>45166</v>
+      </c>
+      <c r="E303" s="15" t="s">
+        <v>492</v>
+      </c>
+      <c r="F303" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G303" s="16">
+        <v>1</v>
+      </c>
+      <c r="H303" s="17" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="304" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A304" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="B304" s="19">
+        <v>45166</v>
+      </c>
+      <c r="C304" s="19">
+        <v>45203</v>
+      </c>
+      <c r="D304" s="19">
+        <v>45166</v>
+      </c>
+      <c r="E304" s="20" t="s">
+        <v>492</v>
+      </c>
+      <c r="F304" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G304" s="21">
+        <v>4</v>
+      </c>
+      <c r="H304" s="22" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="305" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A305" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B305" s="14">
+        <v>45166</v>
+      </c>
+      <c r="C305" s="14">
+        <v>45203</v>
+      </c>
+      <c r="D305" s="14">
+        <v>45166</v>
+      </c>
+      <c r="E305" s="15" t="s">
+        <v>492</v>
+      </c>
+      <c r="F305" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G305" s="16">
+        <v>1</v>
+      </c>
+      <c r="H305" s="17" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="306" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A306" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="B306" s="19">
+        <v>45166</v>
+      </c>
+      <c r="C306" s="19">
+        <v>45203</v>
+      </c>
+      <c r="D306" s="19">
+        <v>45166</v>
+      </c>
+      <c r="E306" s="20" t="s">
+        <v>492</v>
+      </c>
+      <c r="F306" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G306" s="21">
+        <v>25</v>
+      </c>
+      <c r="H306" s="22" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="307" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A307" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B307" s="14">
+        <v>45166</v>
+      </c>
+      <c r="C307" s="14">
+        <v>45203</v>
+      </c>
+      <c r="D307" s="14">
+        <v>45166</v>
+      </c>
+      <c r="E307" s="15" t="s">
+        <v>492</v>
+      </c>
+      <c r="F307" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G307" s="16">
+        <v>2</v>
+      </c>
+      <c r="H307" s="17" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="308" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A308" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="B308" s="19">
+        <v>45166</v>
+      </c>
+      <c r="C308" s="19">
+        <v>45203</v>
+      </c>
+      <c r="D308" s="19">
+        <v>45166</v>
+      </c>
+      <c r="E308" s="20" t="s">
+        <v>492</v>
+      </c>
+      <c r="F308" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G308" s="21">
+        <v>1</v>
+      </c>
+      <c r="H308" s="22" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="309" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A309" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B309" s="14">
+        <v>45166</v>
+      </c>
+      <c r="C309" s="14">
+        <v>45203</v>
+      </c>
+      <c r="D309" s="14">
+        <v>45166</v>
+      </c>
+      <c r="E309" s="15" t="s">
+        <v>492</v>
+      </c>
+      <c r="F309" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G309" s="16">
+        <v>1</v>
+      </c>
+      <c r="H309" s="17" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="310" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A310" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="B310" s="19">
+        <v>45170</v>
+      </c>
+      <c r="C310" s="19">
+        <v>45203</v>
+      </c>
+      <c r="D310" s="19">
+        <v>45291</v>
+      </c>
+      <c r="E310" s="20" t="s">
+        <v>501</v>
+      </c>
+      <c r="F310" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G310" s="21">
+        <v>40</v>
+      </c>
+      <c r="H310" s="22" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="311" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A311" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B311" s="14">
+        <v>45198</v>
+      </c>
+      <c r="C311" s="14">
+        <v>45203</v>
+      </c>
+      <c r="D311" s="14">
+        <v>45198</v>
+      </c>
+      <c r="E311" s="15" t="s">
+        <v>503</v>
+      </c>
+      <c r="F311" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G311" s="16">
+        <v>259</v>
+      </c>
+      <c r="H311" s="17" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="312" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A312" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="B312" s="19">
+        <v>45155</v>
+      </c>
+      <c r="C312" s="19">
+        <v>45203</v>
+      </c>
+      <c r="D312" s="19">
+        <v>45215</v>
+      </c>
+      <c r="E312" s="20" t="s">
+        <v>505</v>
+      </c>
+      <c r="F312" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G312" s="21">
+        <v>13</v>
+      </c>
+      <c r="H312" s="22" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="313" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A313" s="13" t="s">
+        <v>252</v>
+      </c>
+      <c r="B313" s="14">
+        <v>45155</v>
+      </c>
+      <c r="C313" s="14">
+        <v>45203</v>
+      </c>
+      <c r="D313" s="14">
+        <v>45215</v>
+      </c>
+      <c r="E313" s="15" t="s">
+        <v>505</v>
+      </c>
+      <c r="F313" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G313" s="16">
+        <v>98</v>
+      </c>
+      <c r="H313" s="17" t="s">
+        <v>507</v>
       </c>
     </row>
   </sheetData>
@@ -10268,13 +11168,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F594D079-1D81-4918-A813-548FE0BD6918}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EE7B66AD-1D30-4BAF-A751-586ADFCB74D6}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8AA973C8-1F75-4744-8955-4159BDE7D63D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D213AFB6-BFE6-45C6-90F8-B1BA09264667}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE31A677-60B7-46F0-90C7-4F72848EFE0E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69DA0557-31F4-4C1A-A6A8-C372EC9FC153}"/>
 </file>
--- a/data/warn-scraper/cache/ca/warn_report1.xlsx
+++ b/data/warn-scraper/cache/ca/warn_report1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\WSB-CO\Communications Unit\Website Management\WARN (Worker Adjustment and Retraining Notification) Updates\2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7DF38DB-9310-4869-9BD5-BCB4144BC38C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9124B997-875B-444F-84AD-DB9BF5D9F0E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="29895" yWindow="1230" windowWidth="21600" windowHeight="11430" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1267" uniqueCount="509">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1327" uniqueCount="520">
   <si>
     <t>County/Parish</t>
   </si>
@@ -1427,15 +1427,6 @@
     <t>Juul Labs, Inc.</t>
   </si>
   <si>
-    <t>947 Illinois Street Units 108 and 1000 San Francisco CA 94107</t>
-  </si>
-  <si>
-    <t>2475 3rd Street Units 205, 244, 256, 264, 270, 271 San Francisco CA 94107</t>
-  </si>
-  <si>
-    <t>2325-2699 3rd Street Units 601 and 605 San Francisco CA 94107</t>
-  </si>
-  <si>
     <t>Del Friscos Grille</t>
   </si>
   <si>
@@ -1626,6 +1617,48 @@
   </si>
   <si>
     <t>70 Castilian Drive  Goleta CA 93117</t>
+  </si>
+  <si>
+    <t>947 Illinois Street Unit 108 San Francisco CA 94107</t>
+  </si>
+  <si>
+    <t>Juul Labs, Inc. - 270</t>
+  </si>
+  <si>
+    <t>2475 3rd Street Unit 270 San Francisco CA 94107</t>
+  </si>
+  <si>
+    <t>JUUL Labs</t>
+  </si>
+  <si>
+    <t>947 Illinois Street, Unit 108  San Francisco CA 94107</t>
+  </si>
+  <si>
+    <t>JUUL Labs - 270</t>
+  </si>
+  <si>
+    <t>Juul Labs - 270</t>
+  </si>
+  <si>
+    <t>JUUl Labs - 270</t>
+  </si>
+  <si>
+    <t>2475 3rd Street Unit 270 San Fransisco CA 94107</t>
+  </si>
+  <si>
+    <t>JUUL Labs - 271</t>
+  </si>
+  <si>
+    <t>2475 3rd Street Unit 271 San Francisco CA 94107</t>
+  </si>
+  <si>
+    <t>West Coast Industries, Inc.</t>
+  </si>
+  <si>
+    <t>2779 E. El Presidio Street  Carson CA 90810</t>
+  </si>
+  <si>
+    <t>2779 E. El Presidio St.  Carson CA 90810</t>
   </si>
   <si>
     <r>
@@ -1639,7 +1672,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>07/01/23 to 10/04/23</t>
+      <t>07/01/23 to 10/09/23</t>
     </r>
     <r>
       <rPr>
@@ -1659,7 +1692,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>A detailed WARN summary by county and filtered according to received date. Table Spans cells A2 through H313.</t>
+      <t>A detailed WARN summary by county and filtered according to received date. Table Spans cells A2 through H328.</t>
     </r>
   </si>
 </sst>
@@ -2443,8 +2476,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:H313" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
-  <autoFilter ref="A2:H313" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:H328" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
+  <autoFilter ref="A2:H328" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -2828,7 +2861,7 @@
       </c>
       <c r="B3" s="6">
         <f>SUM('Detailed WARN Report '!G:G)</f>
-        <v>15871</v>
+        <v>15928</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -2837,7 +2870,7 @@
       </c>
       <c r="B4" s="6">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Permanent")</f>
-        <v>185</v>
+        <v>198</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -2864,7 +2897,7 @@
       </c>
       <c r="B7" s="6">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Permanent")</f>
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -2896,7 +2929,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:H313"/>
+  <dimension ref="A1:H328"/>
   <sheetFormatPr defaultColWidth="26" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.88671875" bestFit="1" customWidth="1"/>
@@ -2904,12 +2937,12 @@
     <col min="5" max="5" width="54.88671875" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.33203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="55" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="52.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="99.6" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
-        <v>508</v>
+        <v>519</v>
       </c>
       <c r="D1" s="7"/>
       <c r="E1" s="7"/>
@@ -2917,7 +2950,7 @@
       <c r="G1" s="7"/>
       <c r="H1" s="7"/>
     </row>
-    <row r="2" spans="1:8" s="1" customFormat="1" ht="24.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" s="1" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
         <v>0</v>
       </c>
@@ -8882,7 +8915,7 @@
         <v>45190</v>
       </c>
       <c r="D231" s="14">
-        <v>45177</v>
+        <v>45107</v>
       </c>
       <c r="E231" s="15" t="s">
         <v>395</v>
@@ -8891,7 +8924,7 @@
         <v>16</v>
       </c>
       <c r="G231" s="16">
-        <v>57</v>
+        <v>30</v>
       </c>
       <c r="H231" s="17" t="s">
         <v>396</v>
@@ -8899,7 +8932,7 @@
     </row>
     <row r="232" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A232" s="18" t="s">
-        <v>6</v>
+        <v>86</v>
       </c>
       <c r="B232" s="19">
         <v>45112</v>
@@ -8908,7 +8941,7 @@
         <v>45190</v>
       </c>
       <c r="D232" s="19">
-        <v>45177</v>
+        <v>45135</v>
       </c>
       <c r="E232" s="20" t="s">
         <v>395</v>
@@ -8917,15 +8950,15 @@
         <v>16</v>
       </c>
       <c r="G232" s="21">
-        <v>68</v>
+        <v>4</v>
       </c>
       <c r="H232" s="22" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="233" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A233" s="13" t="s">
-        <v>6</v>
+        <v>86</v>
       </c>
       <c r="B233" s="14">
         <v>45112</v>
@@ -8937,73 +8970,73 @@
         <v>45177</v>
       </c>
       <c r="E233" s="15" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="F233" s="15" t="s">
         <v>16</v>
       </c>
       <c r="G233" s="16">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="H233" s="17" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="234" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A234" s="18" t="s">
-        <v>97</v>
+        <v>6</v>
       </c>
       <c r="B234" s="19">
-        <v>45160</v>
+        <v>45112</v>
       </c>
       <c r="C234" s="19">
         <v>45190</v>
       </c>
       <c r="D234" s="19">
-        <v>45220</v>
+        <v>45177</v>
       </c>
       <c r="E234" s="20" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F234" s="20" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G234" s="21">
-        <v>4</v>
+        <v>68</v>
       </c>
       <c r="H234" s="22" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
     </row>
     <row r="235" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A235" s="13" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B235" s="14">
-        <v>45160</v>
+        <v>45112</v>
       </c>
       <c r="C235" s="14">
         <v>45190</v>
       </c>
       <c r="D235" s="14">
-        <v>45219</v>
+        <v>45177</v>
       </c>
       <c r="E235" s="15" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="F235" s="15" t="s">
         <v>16</v>
       </c>
       <c r="G235" s="16">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="H235" s="17" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
     </row>
     <row r="236" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A236" s="18" t="s">
-        <v>252</v>
+        <v>97</v>
       </c>
       <c r="B236" s="19">
         <v>45160</v>
@@ -9021,62 +9054,62 @@
         <v>15</v>
       </c>
       <c r="G236" s="21">
-        <v>150</v>
+        <v>4</v>
       </c>
       <c r="H236" s="22" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
     </row>
     <row r="237" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A237" s="13" t="s">
-        <v>63</v>
+        <v>7</v>
       </c>
       <c r="B237" s="14">
-        <v>45134</v>
+        <v>45160</v>
       </c>
       <c r="C237" s="14">
-        <v>45191</v>
+        <v>45190</v>
       </c>
       <c r="D237" s="14">
-        <v>45170</v>
+        <v>45219</v>
       </c>
       <c r="E237" s="15" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="F237" s="15" t="s">
         <v>16</v>
       </c>
       <c r="G237" s="16">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="H237" s="17" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="238" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A238" s="18" t="s">
-        <v>63</v>
+        <v>252</v>
       </c>
       <c r="B238" s="19">
-        <v>45134</v>
+        <v>45160</v>
       </c>
       <c r="C238" s="19">
-        <v>45191</v>
+        <v>45190</v>
       </c>
       <c r="D238" s="19">
-        <v>45170</v>
+        <v>45220</v>
       </c>
       <c r="E238" s="20" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="F238" s="20" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G238" s="21">
-        <v>13</v>
+        <v>150</v>
       </c>
       <c r="H238" s="22" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
     </row>
     <row r="239" spans="1:8" x14ac:dyDescent="0.3">
@@ -9099,10 +9132,10 @@
         <v>16</v>
       </c>
       <c r="G239" s="16">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H239" s="17" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="240" spans="1:8" x14ac:dyDescent="0.3">
@@ -9125,535 +9158,535 @@
         <v>16</v>
       </c>
       <c r="G240" s="21">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H240" s="22" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="241" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A241" s="13" t="s">
-        <v>5</v>
+        <v>63</v>
       </c>
       <c r="B241" s="14">
-        <v>45141</v>
+        <v>45134</v>
       </c>
       <c r="C241" s="14">
         <v>45191</v>
       </c>
       <c r="D241" s="14">
-        <v>45199</v>
+        <v>45170</v>
       </c>
       <c r="E241" s="15" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="F241" s="15" t="s">
         <v>16</v>
       </c>
       <c r="G241" s="16">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="H241" s="17" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
     </row>
     <row r="242" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A242" s="18" t="s">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="B242" s="19">
-        <v>45136</v>
+        <v>45134</v>
       </c>
       <c r="C242" s="19">
-        <v>45194</v>
+        <v>45191</v>
       </c>
       <c r="D242" s="19">
-        <v>45199</v>
+        <v>45170</v>
       </c>
       <c r="E242" s="20" t="s">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="F242" s="20" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G242" s="21">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H242" s="22" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
     </row>
     <row r="243" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A243" s="13" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B243" s="14">
-        <v>45149</v>
+        <v>45141</v>
       </c>
       <c r="C243" s="14">
-        <v>45194</v>
+        <v>45191</v>
       </c>
       <c r="D243" s="14">
-        <v>45215</v>
+        <v>45199</v>
       </c>
       <c r="E243" s="15" t="s">
-        <v>156</v>
+        <v>410</v>
       </c>
       <c r="F243" s="15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G243" s="16">
-        <v>240</v>
+        <v>20</v>
       </c>
       <c r="H243" s="17" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="244" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A244" s="18" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B244" s="19">
-        <v>45152</v>
+        <v>45136</v>
       </c>
       <c r="C244" s="19">
         <v>45194</v>
       </c>
       <c r="D244" s="19">
-        <v>45214</v>
+        <v>45199</v>
       </c>
       <c r="E244" s="20" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="F244" s="20" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G244" s="21">
-        <v>139</v>
+        <v>10</v>
       </c>
       <c r="H244" s="22" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
     </row>
     <row r="245" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A245" s="13" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B245" s="14">
-        <v>45136</v>
+        <v>45149</v>
       </c>
       <c r="C245" s="14">
         <v>45194</v>
       </c>
       <c r="D245" s="14">
-        <v>45199</v>
+        <v>45215</v>
       </c>
       <c r="E245" s="15" t="s">
-        <v>412</v>
+        <v>156</v>
       </c>
       <c r="F245" s="15" t="s">
         <v>15</v>
       </c>
       <c r="G245" s="16">
-        <v>13</v>
+        <v>240</v>
       </c>
       <c r="H245" s="17" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
     </row>
     <row r="246" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A246" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B246" s="19">
-        <v>45160</v>
+        <v>45152</v>
       </c>
       <c r="C246" s="19">
-        <v>45195</v>
+        <v>45194</v>
       </c>
       <c r="D246" s="19">
-        <v>45205</v>
+        <v>45214</v>
       </c>
       <c r="E246" s="20" t="s">
-        <v>395</v>
+        <v>415</v>
       </c>
       <c r="F246" s="20" t="s">
         <v>16</v>
       </c>
       <c r="G246" s="21">
-        <v>54</v>
+        <v>139</v>
       </c>
       <c r="H246" s="22" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="247" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A247" s="13" t="s">
-        <v>86</v>
+        <v>11</v>
       </c>
       <c r="B247" s="14">
-        <v>45161</v>
+        <v>45136</v>
       </c>
       <c r="C247" s="14">
-        <v>45196</v>
+        <v>45194</v>
       </c>
       <c r="D247" s="14">
-        <v>45221</v>
+        <v>45199</v>
       </c>
       <c r="E247" s="15" t="s">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="F247" s="15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G247" s="16">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="H247" s="17" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="248" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A248" s="18" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B248" s="19">
-        <v>45153</v>
+        <v>45160</v>
       </c>
       <c r="C248" s="19">
-        <v>45196</v>
+        <v>45195</v>
       </c>
       <c r="D248" s="19">
-        <v>45185</v>
+        <v>45177</v>
       </c>
       <c r="E248" s="20" t="s">
-        <v>421</v>
+        <v>395</v>
       </c>
       <c r="F248" s="20" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G248" s="21">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="H248" s="22" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
     </row>
     <row r="249" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A249" s="13" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B249" s="14">
-        <v>45161</v>
+        <v>45160</v>
       </c>
       <c r="C249" s="14">
-        <v>45196</v>
+        <v>45195</v>
       </c>
       <c r="D249" s="14">
-        <v>45221</v>
+        <v>45198</v>
       </c>
       <c r="E249" s="15" t="s">
-        <v>419</v>
+        <v>395</v>
       </c>
       <c r="F249" s="15" t="s">
         <v>16</v>
       </c>
       <c r="G249" s="16">
-        <v>95</v>
+        <v>11</v>
       </c>
       <c r="H249" s="17" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
     </row>
     <row r="250" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A250" s="18" t="s">
-        <v>63</v>
+        <v>6</v>
       </c>
       <c r="B250" s="19">
-        <v>45155</v>
+        <v>45160</v>
       </c>
       <c r="C250" s="19">
-        <v>45196</v>
+        <v>45195</v>
       </c>
       <c r="D250" s="19">
-        <v>45215</v>
+        <v>45191</v>
       </c>
       <c r="E250" s="20" t="s">
-        <v>89</v>
+        <v>395</v>
       </c>
       <c r="F250" s="20" t="s">
         <v>16</v>
       </c>
       <c r="G250" s="21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H250" s="22" t="s">
-        <v>90</v>
+        <v>418</v>
       </c>
     </row>
     <row r="251" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A251" s="13" t="s">
-        <v>63</v>
+        <v>6</v>
       </c>
       <c r="B251" s="14">
-        <v>45189</v>
+        <v>45160</v>
       </c>
       <c r="C251" s="14">
-        <v>45196</v>
+        <v>45195</v>
       </c>
       <c r="D251" s="14">
-        <v>45250</v>
+        <v>45205</v>
       </c>
       <c r="E251" s="15" t="s">
-        <v>89</v>
+        <v>395</v>
       </c>
       <c r="F251" s="15" t="s">
         <v>16</v>
       </c>
       <c r="G251" s="16">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H251" s="17" t="s">
-        <v>90</v>
+        <v>418</v>
       </c>
     </row>
     <row r="252" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A252" s="18" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="B252" s="19">
-        <v>45156</v>
+        <v>45161</v>
       </c>
       <c r="C252" s="19">
         <v>45196</v>
       </c>
       <c r="D252" s="19">
-        <v>45150</v>
+        <v>45221</v>
       </c>
       <c r="E252" s="20" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="F252" s="20" t="s">
-        <v>99</v>
+        <v>16</v>
       </c>
       <c r="G252" s="21">
-        <v>110</v>
+        <v>21</v>
       </c>
       <c r="H252" s="22" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
     </row>
     <row r="253" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A253" s="13" t="s">
-        <v>76</v>
+        <v>5</v>
       </c>
       <c r="B253" s="14">
-        <v>45161</v>
+        <v>45153</v>
       </c>
       <c r="C253" s="14">
         <v>45196</v>
       </c>
       <c r="D253" s="14">
-        <v>45233</v>
+        <v>45185</v>
       </c>
       <c r="E253" s="15" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="F253" s="15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G253" s="16">
-        <v>80</v>
+        <v>53</v>
       </c>
       <c r="H253" s="17" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
     </row>
     <row r="254" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A254" s="18" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B254" s="19">
-        <v>45154</v>
+        <v>45161</v>
       </c>
       <c r="C254" s="19">
         <v>45196</v>
       </c>
       <c r="D254" s="19">
-        <v>45200</v>
+        <v>45221</v>
       </c>
       <c r="E254" s="20" t="s">
-        <v>428</v>
+        <v>419</v>
       </c>
       <c r="F254" s="20" t="s">
-        <v>99</v>
+        <v>16</v>
       </c>
       <c r="G254" s="21">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="H254" s="22" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
     </row>
     <row r="255" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A255" s="13" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="B255" s="14">
-        <v>45154</v>
+        <v>45155</v>
       </c>
       <c r="C255" s="14">
         <v>45196</v>
       </c>
       <c r="D255" s="14">
-        <v>45200</v>
+        <v>45215</v>
       </c>
       <c r="E255" s="15" t="s">
-        <v>428</v>
+        <v>89</v>
       </c>
       <c r="F255" s="15" t="s">
-        <v>99</v>
+        <v>16</v>
       </c>
       <c r="G255" s="16">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="H255" s="17" t="s">
-        <v>430</v>
+        <v>90</v>
       </c>
     </row>
     <row r="256" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A256" s="18" t="s">
-        <v>5</v>
+        <v>63</v>
       </c>
       <c r="B256" s="19">
-        <v>45166</v>
+        <v>45189</v>
       </c>
       <c r="C256" s="19">
-        <v>45197</v>
+        <v>45196</v>
       </c>
       <c r="D256" s="19">
-        <v>45230</v>
+        <v>45250</v>
       </c>
       <c r="E256" s="20" t="s">
-        <v>431</v>
+        <v>89</v>
       </c>
       <c r="F256" s="20" t="s">
         <v>16</v>
       </c>
       <c r="G256" s="21">
-        <v>136</v>
+        <v>1</v>
       </c>
       <c r="H256" s="22" t="s">
-        <v>432</v>
+        <v>90</v>
       </c>
     </row>
     <row r="257" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A257" s="13" t="s">
-        <v>5</v>
+        <v>66</v>
       </c>
       <c r="B257" s="14">
-        <v>45166</v>
+        <v>45156</v>
       </c>
       <c r="C257" s="14">
-        <v>45197</v>
+        <v>45196</v>
       </c>
       <c r="D257" s="14">
-        <v>45230</v>
+        <v>45150</v>
       </c>
       <c r="E257" s="15" t="s">
-        <v>431</v>
+        <v>424</v>
       </c>
       <c r="F257" s="15" t="s">
-        <v>16</v>
+        <v>99</v>
       </c>
       <c r="G257" s="16">
-        <v>2</v>
+        <v>110</v>
       </c>
       <c r="H257" s="17" t="s">
-        <v>433</v>
+        <v>425</v>
       </c>
     </row>
     <row r="258" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A258" s="18" t="s">
-        <v>5</v>
+        <v>76</v>
       </c>
       <c r="B258" s="19">
-        <v>45166</v>
+        <v>45161</v>
       </c>
       <c r="C258" s="19">
-        <v>45197</v>
+        <v>45196</v>
       </c>
       <c r="D258" s="19">
-        <v>45230</v>
+        <v>45233</v>
       </c>
       <c r="E258" s="20" t="s">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="F258" s="20" t="s">
         <v>16</v>
       </c>
       <c r="G258" s="21">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="H258" s="22" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
     </row>
     <row r="259" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A259" s="13" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B259" s="14">
-        <v>45166</v>
+        <v>45154</v>
       </c>
       <c r="C259" s="14">
-        <v>45197</v>
+        <v>45196</v>
       </c>
       <c r="D259" s="14">
-        <v>45230</v>
+        <v>45200</v>
       </c>
       <c r="E259" s="15" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="F259" s="15" t="s">
-        <v>16</v>
+        <v>99</v>
       </c>
       <c r="G259" s="16">
-        <v>163</v>
+        <v>44</v>
       </c>
       <c r="H259" s="17" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
     </row>
     <row r="260" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A260" s="18" t="s">
-        <v>66</v>
+        <v>6</v>
       </c>
       <c r="B260" s="19">
-        <v>45152</v>
+        <v>45154</v>
       </c>
       <c r="C260" s="19">
-        <v>45197</v>
+        <v>45196</v>
       </c>
       <c r="D260" s="19">
-        <v>45214</v>
+        <v>45200</v>
       </c>
       <c r="E260" s="20" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="F260" s="20" t="s">
-        <v>15</v>
+        <v>99</v>
       </c>
       <c r="G260" s="21">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H260" s="22" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
     </row>
     <row r="261" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A261" s="13" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B261" s="14">
         <v>45166</v>
@@ -9662,24 +9695,24 @@
         <v>45197</v>
       </c>
       <c r="D261" s="14">
-        <v>45228</v>
+        <v>45230</v>
       </c>
       <c r="E261" s="15" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="F261" s="15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G261" s="16">
-        <v>39</v>
+        <v>136</v>
       </c>
       <c r="H261" s="17" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
     </row>
     <row r="262" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A262" s="18" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B262" s="19">
         <v>45166</v>
@@ -9688,487 +9721,487 @@
         <v>45197</v>
       </c>
       <c r="D262" s="19">
-        <v>45228</v>
+        <v>45230</v>
       </c>
       <c r="E262" s="20" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="F262" s="20" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G262" s="21">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="H262" s="22" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
     </row>
     <row r="263" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A263" s="13" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B263" s="14">
-        <v>45163</v>
+        <v>45166</v>
       </c>
       <c r="C263" s="14">
         <v>45197</v>
       </c>
       <c r="D263" s="14">
-        <v>45214</v>
+        <v>45230</v>
       </c>
       <c r="E263" s="15" t="s">
-        <v>51</v>
+        <v>434</v>
       </c>
       <c r="F263" s="15" t="s">
         <v>16</v>
       </c>
       <c r="G263" s="16">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="H263" s="17" t="s">
-        <v>230</v>
+        <v>432</v>
       </c>
     </row>
     <row r="264" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A264" s="18" t="s">
-        <v>52</v>
+        <v>5</v>
       </c>
       <c r="B264" s="19">
-        <v>45162</v>
+        <v>45166</v>
       </c>
       <c r="C264" s="19">
         <v>45197</v>
       </c>
       <c r="D264" s="19">
-        <v>45177</v>
+        <v>45230</v>
       </c>
       <c r="E264" s="20" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="F264" s="20" t="s">
         <v>16</v>
       </c>
       <c r="G264" s="21">
-        <v>20</v>
+        <v>163</v>
       </c>
       <c r="H264" s="22" t="s">
-        <v>441</v>
+        <v>433</v>
       </c>
     </row>
     <row r="265" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A265" s="13" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="B265" s="14">
-        <v>45162</v>
+        <v>45152</v>
       </c>
       <c r="C265" s="14">
         <v>45197</v>
       </c>
       <c r="D265" s="14">
-        <v>45177</v>
+        <v>45214</v>
       </c>
       <c r="E265" s="15" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="F265" s="15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G265" s="16">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H265" s="17" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
     </row>
     <row r="266" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A266" s="18" t="s">
-        <v>52</v>
+        <v>11</v>
       </c>
       <c r="B266" s="19">
-        <v>45162</v>
+        <v>45166</v>
       </c>
       <c r="C266" s="19">
         <v>45197</v>
       </c>
       <c r="D266" s="19">
-        <v>45177</v>
+        <v>45228</v>
       </c>
       <c r="E266" s="20" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="F266" s="20" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G266" s="21">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="H266" s="22" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
     </row>
     <row r="267" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A267" s="13" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B267" s="14">
-        <v>45168</v>
+        <v>45166</v>
       </c>
       <c r="C267" s="14">
-        <v>45198</v>
+        <v>45197</v>
       </c>
       <c r="D267" s="14">
-        <v>45230</v>
+        <v>45228</v>
       </c>
       <c r="E267" s="15" t="s">
-        <v>444</v>
+        <v>437</v>
       </c>
       <c r="F267" s="15" t="s">
         <v>15</v>
       </c>
       <c r="G267" s="16">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="H267" s="17" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
     </row>
     <row r="268" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A268" s="18" t="s">
-        <v>66</v>
+        <v>9</v>
       </c>
       <c r="B268" s="19">
-        <v>45169</v>
+        <v>45163</v>
       </c>
       <c r="C268" s="19">
-        <v>45198</v>
+        <v>45197</v>
       </c>
       <c r="D268" s="19">
-        <v>45230</v>
+        <v>45214</v>
       </c>
       <c r="E268" s="20" t="s">
-        <v>446</v>
+        <v>51</v>
       </c>
       <c r="F268" s="20" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G268" s="21">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H268" s="22" t="s">
-        <v>447</v>
+        <v>230</v>
       </c>
     </row>
     <row r="269" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A269" s="13" t="s">
-        <v>368</v>
+        <v>52</v>
       </c>
       <c r="B269" s="14">
-        <v>45167</v>
+        <v>45162</v>
       </c>
       <c r="C269" s="14">
-        <v>45198</v>
+        <v>45197</v>
       </c>
       <c r="D269" s="14">
-        <v>45230</v>
+        <v>45177</v>
       </c>
       <c r="E269" s="15" t="s">
-        <v>448</v>
+        <v>440</v>
       </c>
       <c r="F269" s="15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G269" s="16">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="H269" s="17" t="s">
-        <v>449</v>
+        <v>505</v>
       </c>
     </row>
     <row r="270" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A270" s="18" t="s">
-        <v>5</v>
+        <v>52</v>
       </c>
       <c r="B270" s="19">
-        <v>45170</v>
+        <v>45162</v>
       </c>
       <c r="C270" s="19">
-        <v>45201</v>
+        <v>45197</v>
       </c>
       <c r="D270" s="19">
-        <v>45244</v>
+        <v>45177</v>
       </c>
       <c r="E270" s="20" t="s">
-        <v>450</v>
+        <v>506</v>
       </c>
       <c r="F270" s="20" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G270" s="21">
-        <v>217</v>
+        <v>26</v>
       </c>
       <c r="H270" s="22" t="s">
-        <v>451</v>
+        <v>507</v>
       </c>
     </row>
     <row r="271" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A271" s="13" t="s">
-        <v>5</v>
+        <v>52</v>
       </c>
       <c r="B271" s="14">
-        <v>45169</v>
+        <v>45162</v>
       </c>
       <c r="C271" s="14">
-        <v>45201</v>
+        <v>45197</v>
       </c>
       <c r="D271" s="14">
-        <v>45231</v>
+        <v>45214</v>
       </c>
       <c r="E271" s="15" t="s">
-        <v>288</v>
+        <v>508</v>
       </c>
       <c r="F271" s="15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G271" s="16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H271" s="17" t="s">
-        <v>452</v>
+        <v>509</v>
       </c>
     </row>
     <row r="272" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A272" s="18" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="B272" s="19">
-        <v>45140</v>
+        <v>45162</v>
       </c>
       <c r="C272" s="19">
-        <v>45201</v>
+        <v>45197</v>
       </c>
       <c r="D272" s="19">
-        <v>45205</v>
+        <v>45199</v>
       </c>
       <c r="E272" s="20" t="s">
-        <v>453</v>
+        <v>510</v>
       </c>
       <c r="F272" s="20" t="s">
         <v>16</v>
       </c>
       <c r="G272" s="21">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H272" s="22" t="s">
-        <v>454</v>
+        <v>507</v>
       </c>
     </row>
     <row r="273" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A273" s="13" t="s">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="B273" s="14">
-        <v>45147</v>
+        <v>45162</v>
       </c>
       <c r="C273" s="14">
-        <v>45201</v>
+        <v>45197</v>
       </c>
       <c r="D273" s="14">
-        <v>45205</v>
+        <v>45260</v>
       </c>
       <c r="E273" s="15" t="s">
-        <v>455</v>
+        <v>511</v>
       </c>
       <c r="F273" s="15" t="s">
         <v>16</v>
       </c>
       <c r="G273" s="16">
-        <v>59</v>
+        <v>5</v>
       </c>
       <c r="H273" s="17" t="s">
-        <v>456</v>
+        <v>507</v>
       </c>
     </row>
     <row r="274" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A274" s="18" t="s">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="B274" s="19">
-        <v>45147</v>
+        <v>45162</v>
       </c>
       <c r="C274" s="19">
-        <v>45201</v>
+        <v>45197</v>
       </c>
       <c r="D274" s="19">
-        <v>45205</v>
+        <v>45291</v>
       </c>
       <c r="E274" s="20" t="s">
-        <v>455</v>
+        <v>512</v>
       </c>
       <c r="F274" s="20" t="s">
         <v>16</v>
       </c>
       <c r="G274" s="21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H274" s="22" t="s">
-        <v>457</v>
+        <v>507</v>
       </c>
     </row>
     <row r="275" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A275" s="13" t="s">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="B275" s="14">
-        <v>45147</v>
+        <v>45162</v>
       </c>
       <c r="C275" s="14">
-        <v>45201</v>
+        <v>45197</v>
       </c>
       <c r="D275" s="14">
-        <v>45205</v>
+        <v>45275</v>
       </c>
       <c r="E275" s="15" t="s">
-        <v>455</v>
+        <v>512</v>
       </c>
       <c r="F275" s="15" t="s">
         <v>16</v>
       </c>
       <c r="G275" s="16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H275" s="17" t="s">
-        <v>458</v>
+        <v>513</v>
       </c>
     </row>
     <row r="276" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A276" s="18" t="s">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="B276" s="19">
-        <v>45147</v>
+        <v>45162</v>
       </c>
       <c r="C276" s="19">
-        <v>45201</v>
+        <v>45197</v>
       </c>
       <c r="D276" s="19">
-        <v>45205</v>
+        <v>45230</v>
       </c>
       <c r="E276" s="20" t="s">
-        <v>455</v>
+        <v>510</v>
       </c>
       <c r="F276" s="20" t="s">
         <v>16</v>
       </c>
       <c r="G276" s="21">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H276" s="22" t="s">
-        <v>459</v>
+        <v>507</v>
       </c>
     </row>
     <row r="277" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A277" s="13" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="B277" s="14">
-        <v>45140</v>
+        <v>45162</v>
       </c>
       <c r="C277" s="14">
-        <v>45201</v>
+        <v>45197</v>
       </c>
       <c r="D277" s="14">
-        <v>45205</v>
+        <v>45177</v>
       </c>
       <c r="E277" s="15" t="s">
-        <v>453</v>
+        <v>514</v>
       </c>
       <c r="F277" s="15" t="s">
         <v>16</v>
       </c>
       <c r="G277" s="16">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H277" s="17" t="s">
-        <v>460</v>
+        <v>515</v>
       </c>
     </row>
     <row r="278" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A278" s="18" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="B278" s="19">
-        <v>45140</v>
+        <v>45162</v>
       </c>
       <c r="C278" s="19">
-        <v>45201</v>
+        <v>45197</v>
       </c>
       <c r="D278" s="19">
-        <v>45205</v>
+        <v>45214</v>
       </c>
       <c r="E278" s="20" t="s">
-        <v>453</v>
+        <v>514</v>
       </c>
       <c r="F278" s="20" t="s">
         <v>16</v>
       </c>
       <c r="G278" s="21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H278" s="22" t="s">
-        <v>461</v>
+        <v>515</v>
       </c>
     </row>
     <row r="279" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A279" s="13" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="B279" s="14">
-        <v>45140</v>
+        <v>45162</v>
       </c>
       <c r="C279" s="14">
-        <v>45201</v>
+        <v>45197</v>
       </c>
       <c r="D279" s="14">
-        <v>45205</v>
+        <v>45261</v>
       </c>
       <c r="E279" s="15" t="s">
-        <v>453</v>
+        <v>514</v>
       </c>
       <c r="F279" s="15" t="s">
         <v>16</v>
       </c>
       <c r="G279" s="16">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H279" s="17" t="s">
-        <v>462</v>
+        <v>515</v>
       </c>
     </row>
     <row r="280" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A280" s="18" t="s">
-        <v>66</v>
+        <v>5</v>
       </c>
       <c r="B280" s="19">
-        <v>45140</v>
+        <v>45168</v>
       </c>
       <c r="C280" s="19">
-        <v>45201</v>
+        <v>45198</v>
       </c>
       <c r="D280" s="19">
-        <v>45205</v>
+        <v>45230</v>
       </c>
       <c r="E280" s="20" t="s">
-        <v>453</v>
+        <v>441</v>
       </c>
       <c r="F280" s="20" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G280" s="21">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="H280" s="22" t="s">
-        <v>463</v>
+        <v>442</v>
       </c>
     </row>
     <row r="281" spans="1:8" x14ac:dyDescent="0.3">
@@ -10176,56 +10209,56 @@
         <v>66</v>
       </c>
       <c r="B281" s="14">
-        <v>45140</v>
+        <v>45169</v>
       </c>
       <c r="C281" s="14">
-        <v>45201</v>
+        <v>45198</v>
       </c>
       <c r="D281" s="14">
-        <v>45205</v>
+        <v>45230</v>
       </c>
       <c r="E281" s="15" t="s">
-        <v>453</v>
+        <v>443</v>
       </c>
       <c r="F281" s="15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G281" s="16">
-        <v>11</v>
+        <v>60</v>
       </c>
       <c r="H281" s="17" t="s">
-        <v>464</v>
+        <v>444</v>
       </c>
     </row>
     <row r="282" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A282" s="18" t="s">
-        <v>66</v>
+        <v>368</v>
       </c>
       <c r="B282" s="19">
-        <v>45140</v>
+        <v>45167</v>
       </c>
       <c r="C282" s="19">
-        <v>45201</v>
+        <v>45198</v>
       </c>
       <c r="D282" s="19">
-        <v>45205</v>
+        <v>45230</v>
       </c>
       <c r="E282" s="20" t="s">
-        <v>453</v>
+        <v>445</v>
       </c>
       <c r="F282" s="20" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G282" s="21">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="H282" s="22" t="s">
-        <v>465</v>
+        <v>446</v>
       </c>
     </row>
     <row r="283" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A283" s="13" t="s">
-        <v>175</v>
+        <v>5</v>
       </c>
       <c r="B283" s="14">
         <v>45170</v>
@@ -10234,218 +10267,218 @@
         <v>45201</v>
       </c>
       <c r="D283" s="14">
-        <v>45231</v>
+        <v>45244</v>
       </c>
       <c r="E283" s="15" t="s">
-        <v>466</v>
+        <v>447</v>
       </c>
       <c r="F283" s="15" t="s">
         <v>15</v>
       </c>
       <c r="G283" s="16">
-        <v>292</v>
+        <v>217</v>
       </c>
       <c r="H283" s="17" t="s">
-        <v>467</v>
+        <v>448</v>
       </c>
     </row>
     <row r="284" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A284" s="18" t="s">
-        <v>86</v>
+        <v>5</v>
       </c>
       <c r="B284" s="19">
-        <v>45181</v>
+        <v>45169</v>
       </c>
       <c r="C284" s="19">
-        <v>45202</v>
+        <v>45201</v>
       </c>
       <c r="D284" s="19">
-        <v>45240</v>
+        <v>45231</v>
       </c>
       <c r="E284" s="20" t="s">
-        <v>468</v>
+        <v>288</v>
       </c>
       <c r="F284" s="20" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G284" s="21">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="H284" s="22" t="s">
-        <v>469</v>
+        <v>449</v>
       </c>
     </row>
     <row r="285" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A285" s="13" t="s">
-        <v>5</v>
+        <v>66</v>
       </c>
       <c r="B285" s="14">
-        <v>45181</v>
+        <v>45140</v>
       </c>
       <c r="C285" s="14">
-        <v>45202</v>
+        <v>45201</v>
       </c>
       <c r="D285" s="14">
-        <v>45240</v>
+        <v>45205</v>
       </c>
       <c r="E285" s="15" t="s">
-        <v>468</v>
+        <v>450</v>
       </c>
       <c r="F285" s="15" t="s">
         <v>16</v>
       </c>
       <c r="G285" s="16">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H285" s="17" t="s">
-        <v>470</v>
+        <v>451</v>
       </c>
     </row>
     <row r="286" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A286" s="18" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B286" s="19">
-        <v>45181</v>
+        <v>45147</v>
       </c>
       <c r="C286" s="19">
-        <v>45202</v>
+        <v>45201</v>
       </c>
       <c r="D286" s="19">
-        <v>45240</v>
+        <v>45205</v>
       </c>
       <c r="E286" s="20" t="s">
-        <v>471</v>
+        <v>452</v>
       </c>
       <c r="F286" s="20" t="s">
         <v>16</v>
       </c>
       <c r="G286" s="21">
-        <v>1</v>
+        <v>59</v>
       </c>
       <c r="H286" s="22" t="s">
-        <v>472</v>
+        <v>453</v>
       </c>
     </row>
     <row r="287" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A287" s="13" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B287" s="14">
-        <v>45181</v>
+        <v>45147</v>
       </c>
       <c r="C287" s="14">
-        <v>45202</v>
+        <v>45201</v>
       </c>
       <c r="D287" s="14">
-        <v>45240</v>
+        <v>45205</v>
       </c>
       <c r="E287" s="15" t="s">
-        <v>473</v>
+        <v>452</v>
       </c>
       <c r="F287" s="15" t="s">
         <v>16</v>
       </c>
       <c r="G287" s="16">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H287" s="17" t="s">
-        <v>474</v>
+        <v>454</v>
       </c>
     </row>
     <row r="288" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A288" s="18" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B288" s="19">
-        <v>45181</v>
+        <v>45147</v>
       </c>
       <c r="C288" s="19">
-        <v>45202</v>
+        <v>45201</v>
       </c>
       <c r="D288" s="19">
-        <v>45240</v>
+        <v>45205</v>
       </c>
       <c r="E288" s="20" t="s">
-        <v>475</v>
+        <v>452</v>
       </c>
       <c r="F288" s="20" t="s">
         <v>16</v>
       </c>
       <c r="G288" s="21">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H288" s="22" t="s">
-        <v>476</v>
+        <v>455</v>
       </c>
     </row>
     <row r="289" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A289" s="13" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B289" s="14">
-        <v>45170</v>
+        <v>45147</v>
       </c>
       <c r="C289" s="14">
-        <v>45202</v>
+        <v>45201</v>
       </c>
       <c r="D289" s="14">
-        <v>45170</v>
+        <v>45205</v>
       </c>
       <c r="E289" s="15" t="s">
-        <v>477</v>
+        <v>452</v>
       </c>
       <c r="F289" s="15" t="s">
         <v>16</v>
       </c>
       <c r="G289" s="16">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H289" s="17" t="s">
-        <v>478</v>
+        <v>456</v>
       </c>
     </row>
     <row r="290" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A290" s="18" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="B290" s="19">
-        <v>45181</v>
+        <v>45140</v>
       </c>
       <c r="C290" s="19">
-        <v>45202</v>
+        <v>45201</v>
       </c>
       <c r="D290" s="19">
-        <v>45240</v>
+        <v>45205</v>
       </c>
       <c r="E290" s="20" t="s">
-        <v>479</v>
+        <v>450</v>
       </c>
       <c r="F290" s="20" t="s">
         <v>16</v>
       </c>
       <c r="G290" s="21">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="H290" s="22" t="s">
-        <v>480</v>
+        <v>457</v>
       </c>
     </row>
     <row r="291" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A291" s="13" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="B291" s="14">
-        <v>45181</v>
+        <v>45140</v>
       </c>
       <c r="C291" s="14">
-        <v>45202</v>
+        <v>45201</v>
       </c>
       <c r="D291" s="14">
-        <v>45240</v>
+        <v>45205</v>
       </c>
       <c r="E291" s="15" t="s">
-        <v>468</v>
+        <v>450</v>
       </c>
       <c r="F291" s="15" t="s">
         <v>16</v>
@@ -10454,33 +10487,33 @@
         <v>1</v>
       </c>
       <c r="H291" s="17" t="s">
-        <v>481</v>
+        <v>458</v>
       </c>
     </row>
     <row r="292" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A292" s="18" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="B292" s="19">
-        <v>45181</v>
+        <v>45140</v>
       </c>
       <c r="C292" s="19">
-        <v>45202</v>
+        <v>45201</v>
       </c>
       <c r="D292" s="19">
-        <v>45240</v>
+        <v>45205</v>
       </c>
       <c r="E292" s="20" t="s">
-        <v>482</v>
+        <v>450</v>
       </c>
       <c r="F292" s="20" t="s">
         <v>16</v>
       </c>
       <c r="G292" s="21">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H292" s="22" t="s">
-        <v>483</v>
+        <v>459</v>
       </c>
     </row>
     <row r="293" spans="1:8" x14ac:dyDescent="0.3">
@@ -10488,25 +10521,25 @@
         <v>66</v>
       </c>
       <c r="B293" s="14">
-        <v>45170</v>
+        <v>45140</v>
       </c>
       <c r="C293" s="14">
-        <v>45202</v>
+        <v>45201</v>
       </c>
       <c r="D293" s="14">
-        <v>45170</v>
+        <v>45205</v>
       </c>
       <c r="E293" s="15" t="s">
-        <v>477</v>
+        <v>450</v>
       </c>
       <c r="F293" s="15" t="s">
         <v>16</v>
       </c>
       <c r="G293" s="16">
-        <v>57</v>
+        <v>2</v>
       </c>
       <c r="H293" s="17" t="s">
-        <v>484</v>
+        <v>460</v>
       </c>
     </row>
     <row r="294" spans="1:8" x14ac:dyDescent="0.3">
@@ -10514,25 +10547,25 @@
         <v>66</v>
       </c>
       <c r="B294" s="19">
-        <v>45170</v>
+        <v>45140</v>
       </c>
       <c r="C294" s="19">
-        <v>45202</v>
+        <v>45201</v>
       </c>
       <c r="D294" s="19">
-        <v>45183</v>
+        <v>45205</v>
       </c>
       <c r="E294" s="20" t="s">
-        <v>477</v>
+        <v>450</v>
       </c>
       <c r="F294" s="20" t="s">
         <v>16</v>
       </c>
       <c r="G294" s="21">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="H294" s="22" t="s">
-        <v>484</v>
+        <v>461</v>
       </c>
     </row>
     <row r="295" spans="1:8" x14ac:dyDescent="0.3">
@@ -10540,16 +10573,16 @@
         <v>66</v>
       </c>
       <c r="B295" s="14">
-        <v>45170</v>
+        <v>45140</v>
       </c>
       <c r="C295" s="14">
-        <v>45202</v>
+        <v>45201</v>
       </c>
       <c r="D295" s="14">
-        <v>45212</v>
+        <v>45205</v>
       </c>
       <c r="E295" s="15" t="s">
-        <v>477</v>
+        <v>450</v>
       </c>
       <c r="F295" s="15" t="s">
         <v>16</v>
@@ -10558,64 +10591,64 @@
         <v>12</v>
       </c>
       <c r="H295" s="17" t="s">
-        <v>484</v>
+        <v>462</v>
       </c>
     </row>
     <row r="296" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A296" s="18" t="s">
-        <v>66</v>
+        <v>175</v>
       </c>
       <c r="B296" s="19">
         <v>45170</v>
       </c>
       <c r="C296" s="19">
-        <v>45202</v>
+        <v>45201</v>
       </c>
       <c r="D296" s="19">
-        <v>45170</v>
+        <v>45231</v>
       </c>
       <c r="E296" s="20" t="s">
-        <v>477</v>
+        <v>463</v>
       </c>
       <c r="F296" s="20" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G296" s="21">
-        <v>10</v>
+        <v>292</v>
       </c>
       <c r="H296" s="22" t="s">
-        <v>485</v>
+        <v>464</v>
       </c>
     </row>
     <row r="297" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A297" s="13" t="s">
-        <v>11</v>
+        <v>86</v>
       </c>
       <c r="B297" s="14">
-        <v>45170</v>
+        <v>45181</v>
       </c>
       <c r="C297" s="14">
         <v>45202</v>
       </c>
       <c r="D297" s="14">
-        <v>45170</v>
+        <v>45240</v>
       </c>
       <c r="E297" s="15" t="s">
-        <v>477</v>
+        <v>465</v>
       </c>
       <c r="F297" s="15" t="s">
         <v>16</v>
       </c>
       <c r="G297" s="16">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="H297" s="17" t="s">
-        <v>486</v>
+        <v>466</v>
       </c>
     </row>
     <row r="298" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A298" s="18" t="s">
-        <v>76</v>
+        <v>5</v>
       </c>
       <c r="B298" s="19">
         <v>45181</v>
@@ -10627,47 +10660,47 @@
         <v>45240</v>
       </c>
       <c r="E298" s="20" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="F298" s="20" t="s">
         <v>16</v>
       </c>
       <c r="G298" s="21">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H298" s="22" t="s">
-        <v>487</v>
+        <v>467</v>
       </c>
     </row>
     <row r="299" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A299" s="13" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B299" s="14">
-        <v>45177</v>
+        <v>45181</v>
       </c>
       <c r="C299" s="14">
         <v>45202</v>
       </c>
       <c r="D299" s="14">
-        <v>45237</v>
+        <v>45240</v>
       </c>
       <c r="E299" s="15" t="s">
-        <v>488</v>
+        <v>468</v>
       </c>
       <c r="F299" s="15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G299" s="16">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="H299" s="17" t="s">
-        <v>489</v>
+        <v>469</v>
       </c>
     </row>
     <row r="300" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A300" s="18" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B300" s="19">
         <v>45181</v>
@@ -10679,16 +10712,16 @@
         <v>45240</v>
       </c>
       <c r="E300" s="20" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="F300" s="20" t="s">
         <v>16</v>
       </c>
       <c r="G300" s="21">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H300" s="22" t="s">
-        <v>490</v>
+        <v>471</v>
       </c>
     </row>
     <row r="301" spans="1:8" x14ac:dyDescent="0.3">
@@ -10705,7 +10738,7 @@
         <v>45240</v>
       </c>
       <c r="E301" s="15" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="F301" s="15" t="s">
         <v>16</v>
@@ -10714,267 +10747,267 @@
         <v>1</v>
       </c>
       <c r="H301" s="17" t="s">
-        <v>491</v>
+        <v>473</v>
       </c>
     </row>
     <row r="302" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A302" s="18" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B302" s="19">
-        <v>45166</v>
+        <v>45170</v>
       </c>
       <c r="C302" s="19">
-        <v>45203</v>
+        <v>45202</v>
       </c>
       <c r="D302" s="19">
-        <v>45166</v>
+        <v>45170</v>
       </c>
       <c r="E302" s="20" t="s">
-        <v>492</v>
+        <v>474</v>
       </c>
       <c r="F302" s="20" t="s">
         <v>16</v>
       </c>
       <c r="G302" s="21">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="H302" s="22" t="s">
-        <v>493</v>
+        <v>475</v>
       </c>
     </row>
     <row r="303" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A303" s="13" t="s">
-        <v>8</v>
+        <v>86</v>
       </c>
       <c r="B303" s="14">
-        <v>45166</v>
+        <v>45181</v>
       </c>
       <c r="C303" s="14">
-        <v>45203</v>
+        <v>45202</v>
       </c>
       <c r="D303" s="14">
-        <v>45166</v>
+        <v>45240</v>
       </c>
       <c r="E303" s="15" t="s">
-        <v>492</v>
+        <v>476</v>
       </c>
       <c r="F303" s="15" t="s">
         <v>16</v>
       </c>
       <c r="G303" s="16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H303" s="17" t="s">
-        <v>494</v>
+        <v>477</v>
       </c>
     </row>
     <row r="304" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A304" s="18" t="s">
-        <v>8</v>
+        <v>86</v>
       </c>
       <c r="B304" s="19">
-        <v>45166</v>
+        <v>45181</v>
       </c>
       <c r="C304" s="19">
-        <v>45203</v>
+        <v>45202</v>
       </c>
       <c r="D304" s="19">
-        <v>45166</v>
+        <v>45240</v>
       </c>
       <c r="E304" s="20" t="s">
-        <v>492</v>
+        <v>465</v>
       </c>
       <c r="F304" s="20" t="s">
         <v>16</v>
       </c>
       <c r="G304" s="21">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H304" s="22" t="s">
-        <v>495</v>
+        <v>478</v>
       </c>
     </row>
     <row r="305" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A305" s="13" t="s">
-        <v>8</v>
+        <v>86</v>
       </c>
       <c r="B305" s="14">
-        <v>45166</v>
+        <v>45181</v>
       </c>
       <c r="C305" s="14">
-        <v>45203</v>
+        <v>45202</v>
       </c>
       <c r="D305" s="14">
-        <v>45166</v>
+        <v>45240</v>
       </c>
       <c r="E305" s="15" t="s">
-        <v>492</v>
+        <v>479</v>
       </c>
       <c r="F305" s="15" t="s">
         <v>16</v>
       </c>
       <c r="G305" s="16">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H305" s="17" t="s">
-        <v>496</v>
+        <v>480</v>
       </c>
     </row>
     <row r="306" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A306" s="18" t="s">
-        <v>8</v>
+        <v>66</v>
       </c>
       <c r="B306" s="19">
-        <v>45166</v>
+        <v>45170</v>
       </c>
       <c r="C306" s="19">
-        <v>45203</v>
+        <v>45202</v>
       </c>
       <c r="D306" s="19">
-        <v>45166</v>
+        <v>45170</v>
       </c>
       <c r="E306" s="20" t="s">
-        <v>492</v>
+        <v>474</v>
       </c>
       <c r="F306" s="20" t="s">
         <v>16</v>
       </c>
       <c r="G306" s="21">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="H306" s="22" t="s">
-        <v>497</v>
+        <v>481</v>
       </c>
     </row>
     <row r="307" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A307" s="13" t="s">
-        <v>8</v>
+        <v>66</v>
       </c>
       <c r="B307" s="14">
-        <v>45166</v>
+        <v>45170</v>
       </c>
       <c r="C307" s="14">
-        <v>45203</v>
+        <v>45202</v>
       </c>
       <c r="D307" s="14">
-        <v>45166</v>
+        <v>45183</v>
       </c>
       <c r="E307" s="15" t="s">
-        <v>492</v>
+        <v>474</v>
       </c>
       <c r="F307" s="15" t="s">
         <v>16</v>
       </c>
       <c r="G307" s="16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H307" s="17" t="s">
-        <v>498</v>
+        <v>481</v>
       </c>
     </row>
     <row r="308" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A308" s="18" t="s">
-        <v>8</v>
+        <v>66</v>
       </c>
       <c r="B308" s="19">
-        <v>45166</v>
+        <v>45170</v>
       </c>
       <c r="C308" s="19">
-        <v>45203</v>
+        <v>45202</v>
       </c>
       <c r="D308" s="19">
-        <v>45166</v>
+        <v>45212</v>
       </c>
       <c r="E308" s="20" t="s">
-        <v>492</v>
+        <v>474</v>
       </c>
       <c r="F308" s="20" t="s">
         <v>16</v>
       </c>
       <c r="G308" s="21">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H308" s="22" t="s">
-        <v>499</v>
+        <v>481</v>
       </c>
     </row>
     <row r="309" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A309" s="13" t="s">
-        <v>8</v>
+        <v>66</v>
       </c>
       <c r="B309" s="14">
-        <v>45166</v>
+        <v>45170</v>
       </c>
       <c r="C309" s="14">
-        <v>45203</v>
+        <v>45202</v>
       </c>
       <c r="D309" s="14">
-        <v>45166</v>
+        <v>45170</v>
       </c>
       <c r="E309" s="15" t="s">
-        <v>492</v>
+        <v>474</v>
       </c>
       <c r="F309" s="15" t="s">
         <v>16</v>
       </c>
       <c r="G309" s="16">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H309" s="17" t="s">
-        <v>500</v>
+        <v>482</v>
       </c>
     </row>
     <row r="310" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A310" s="18" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B310" s="19">
         <v>45170</v>
       </c>
       <c r="C310" s="19">
-        <v>45203</v>
+        <v>45202</v>
       </c>
       <c r="D310" s="19">
-        <v>45291</v>
+        <v>45170</v>
       </c>
       <c r="E310" s="20" t="s">
-        <v>501</v>
+        <v>474</v>
       </c>
       <c r="F310" s="20" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G310" s="21">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="H310" s="22" t="s">
-        <v>502</v>
+        <v>483</v>
       </c>
     </row>
     <row r="311" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A311" s="13" t="s">
-        <v>9</v>
+        <v>76</v>
       </c>
       <c r="B311" s="14">
-        <v>45198</v>
+        <v>45181</v>
       </c>
       <c r="C311" s="14">
-        <v>45203</v>
+        <v>45202</v>
       </c>
       <c r="D311" s="14">
-        <v>45198</v>
+        <v>45240</v>
       </c>
       <c r="E311" s="15" t="s">
-        <v>503</v>
+        <v>465</v>
       </c>
       <c r="F311" s="15" t="s">
         <v>16</v>
       </c>
       <c r="G311" s="16">
-        <v>259</v>
+        <v>1</v>
       </c>
       <c r="H311" s="17" t="s">
-        <v>504</v>
+        <v>484</v>
       </c>
     </row>
     <row r="312" spans="1:8" x14ac:dyDescent="0.3">
@@ -10982,51 +11015,441 @@
         <v>6</v>
       </c>
       <c r="B312" s="19">
-        <v>45155</v>
+        <v>45177</v>
       </c>
       <c r="C312" s="19">
-        <v>45203</v>
+        <v>45202</v>
       </c>
       <c r="D312" s="19">
-        <v>45215</v>
+        <v>45237</v>
       </c>
       <c r="E312" s="20" t="s">
-        <v>505</v>
+        <v>485</v>
       </c>
       <c r="F312" s="20" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G312" s="21">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="H312" s="22" t="s">
-        <v>506</v>
+        <v>486</v>
       </c>
     </row>
     <row r="313" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A313" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="B313" s="14">
+        <v>45181</v>
+      </c>
+      <c r="C313" s="14">
+        <v>45202</v>
+      </c>
+      <c r="D313" s="14">
+        <v>45240</v>
+      </c>
+      <c r="E313" s="15" t="s">
+        <v>465</v>
+      </c>
+      <c r="F313" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G313" s="16">
+        <v>1</v>
+      </c>
+      <c r="H313" s="17" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="314" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A314" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="B314" s="19">
+        <v>45181</v>
+      </c>
+      <c r="C314" s="19">
+        <v>45202</v>
+      </c>
+      <c r="D314" s="19">
+        <v>45240</v>
+      </c>
+      <c r="E314" s="20" t="s">
+        <v>465</v>
+      </c>
+      <c r="F314" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G314" s="21">
+        <v>1</v>
+      </c>
+      <c r="H314" s="22" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="315" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A315" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B315" s="14">
+        <v>45166</v>
+      </c>
+      <c r="C315" s="14">
+        <v>45203</v>
+      </c>
+      <c r="D315" s="14">
+        <v>45166</v>
+      </c>
+      <c r="E315" s="15" t="s">
+        <v>489</v>
+      </c>
+      <c r="F315" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G315" s="16">
+        <v>26</v>
+      </c>
+      <c r="H315" s="17" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="316" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A316" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="B316" s="19">
+        <v>45166</v>
+      </c>
+      <c r="C316" s="19">
+        <v>45203</v>
+      </c>
+      <c r="D316" s="19">
+        <v>45166</v>
+      </c>
+      <c r="E316" s="20" t="s">
+        <v>489</v>
+      </c>
+      <c r="F316" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G316" s="21">
+        <v>1</v>
+      </c>
+      <c r="H316" s="22" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="317" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A317" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B317" s="14">
+        <v>45166</v>
+      </c>
+      <c r="C317" s="14">
+        <v>45203</v>
+      </c>
+      <c r="D317" s="14">
+        <v>45166</v>
+      </c>
+      <c r="E317" s="15" t="s">
+        <v>489</v>
+      </c>
+      <c r="F317" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G317" s="16">
+        <v>4</v>
+      </c>
+      <c r="H317" s="17" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="318" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A318" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="B318" s="19">
+        <v>45166</v>
+      </c>
+      <c r="C318" s="19">
+        <v>45203</v>
+      </c>
+      <c r="D318" s="19">
+        <v>45166</v>
+      </c>
+      <c r="E318" s="20" t="s">
+        <v>489</v>
+      </c>
+      <c r="F318" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G318" s="21">
+        <v>1</v>
+      </c>
+      <c r="H318" s="22" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="319" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A319" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B319" s="14">
+        <v>45166</v>
+      </c>
+      <c r="C319" s="14">
+        <v>45203</v>
+      </c>
+      <c r="D319" s="14">
+        <v>45166</v>
+      </c>
+      <c r="E319" s="15" t="s">
+        <v>489</v>
+      </c>
+      <c r="F319" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G319" s="16">
+        <v>25</v>
+      </c>
+      <c r="H319" s="17" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="320" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A320" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="B320" s="19">
+        <v>45166</v>
+      </c>
+      <c r="C320" s="19">
+        <v>45203</v>
+      </c>
+      <c r="D320" s="19">
+        <v>45166</v>
+      </c>
+      <c r="E320" s="20" t="s">
+        <v>489</v>
+      </c>
+      <c r="F320" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G320" s="21">
+        <v>2</v>
+      </c>
+      <c r="H320" s="22" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="321" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A321" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B321" s="14">
+        <v>45166</v>
+      </c>
+      <c r="C321" s="14">
+        <v>45203</v>
+      </c>
+      <c r="D321" s="14">
+        <v>45166</v>
+      </c>
+      <c r="E321" s="15" t="s">
+        <v>489</v>
+      </c>
+      <c r="F321" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G321" s="16">
+        <v>1</v>
+      </c>
+      <c r="H321" s="17" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="322" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A322" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="B322" s="19">
+        <v>45166</v>
+      </c>
+      <c r="C322" s="19">
+        <v>45203</v>
+      </c>
+      <c r="D322" s="19">
+        <v>45166</v>
+      </c>
+      <c r="E322" s="20" t="s">
+        <v>489</v>
+      </c>
+      <c r="F322" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G322" s="21">
+        <v>1</v>
+      </c>
+      <c r="H322" s="22" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="323" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A323" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B323" s="14">
+        <v>45170</v>
+      </c>
+      <c r="C323" s="14">
+        <v>45203</v>
+      </c>
+      <c r="D323" s="14">
+        <v>45291</v>
+      </c>
+      <c r="E323" s="15" t="s">
+        <v>498</v>
+      </c>
+      <c r="F323" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G323" s="16">
+        <v>40</v>
+      </c>
+      <c r="H323" s="17" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="324" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A324" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="B324" s="19">
+        <v>45198</v>
+      </c>
+      <c r="C324" s="19">
+        <v>45203</v>
+      </c>
+      <c r="D324" s="19">
+        <v>45198</v>
+      </c>
+      <c r="E324" s="20" t="s">
+        <v>500</v>
+      </c>
+      <c r="F324" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G324" s="21">
+        <v>259</v>
+      </c>
+      <c r="H324" s="22" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="325" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A325" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="B325" s="14">
+        <v>45155</v>
+      </c>
+      <c r="C325" s="14">
+        <v>45203</v>
+      </c>
+      <c r="D325" s="14">
+        <v>45215</v>
+      </c>
+      <c r="E325" s="15" t="s">
+        <v>502</v>
+      </c>
+      <c r="F325" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G325" s="16">
+        <v>13</v>
+      </c>
+      <c r="H325" s="17" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="326" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A326" s="18" t="s">
         <v>252</v>
       </c>
-      <c r="B313" s="14">
+      <c r="B326" s="19">
         <v>45155</v>
       </c>
-      <c r="C313" s="14">
+      <c r="C326" s="19">
         <v>45203</v>
       </c>
-      <c r="D313" s="14">
+      <c r="D326" s="19">
         <v>45215</v>
       </c>
-      <c r="E313" s="15" t="s">
-        <v>505</v>
-      </c>
-      <c r="F313" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="G313" s="16">
+      <c r="E326" s="20" t="s">
+        <v>502</v>
+      </c>
+      <c r="F326" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G326" s="21">
         <v>98</v>
       </c>
-      <c r="H313" s="17" t="s">
-        <v>507</v>
+      <c r="H326" s="22" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="327" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A327" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B327" s="14">
+        <v>45174</v>
+      </c>
+      <c r="C327" s="14">
+        <v>45204</v>
+      </c>
+      <c r="D327" s="14">
+        <v>45234</v>
+      </c>
+      <c r="E327" s="15" t="s">
+        <v>516</v>
+      </c>
+      <c r="F327" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G327" s="16">
+        <v>53</v>
+      </c>
+      <c r="H327" s="17" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="328" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A328" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="B328" s="19">
+        <v>45174</v>
+      </c>
+      <c r="C328" s="19">
+        <v>45204</v>
+      </c>
+      <c r="D328" s="19">
+        <v>45260</v>
+      </c>
+      <c r="E328" s="20" t="s">
+        <v>516</v>
+      </c>
+      <c r="F328" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G328" s="21">
+        <v>4</v>
+      </c>
+      <c r="H328" s="22" t="s">
+        <v>518</v>
       </c>
     </row>
   </sheetData>
@@ -11168,13 +11591,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EE7B66AD-1D30-4BAF-A751-586ADFCB74D6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C06C59DD-BA72-4539-8251-9A8329B0FC1D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D213AFB6-BFE6-45C6-90F8-B1BA09264667}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7FBFE211-0C34-433D-9B33-99A7F9097B46}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69DA0557-31F4-4C1A-A6A8-C372EC9FC153}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0246515F-3E8A-4DEB-BEE7-4506A2B6AD32}"/>
 </file>
--- a/data/warn-scraper/cache/ca/warn_report1.xlsx
+++ b/data/warn-scraper/cache/ca/warn_report1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\WSB-CO\Communications Unit\Website Management\WARN (Worker Adjustment and Retraining Notification) Updates\2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9124B997-875B-444F-84AD-DB9BF5D9F0E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C61627DE-A2FA-4509-AF3F-85FE62B7F0D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="29895" yWindow="1230" windowWidth="21600" windowHeight="11430" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1327" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1339" uniqueCount="526">
   <si>
     <t>County/Parish</t>
   </si>
@@ -1661,6 +1661,24 @@
     <t>2779 E. El Presidio St.  Carson CA 90810</t>
   </si>
   <si>
+    <t>Astra Space Operations, LLC</t>
+  </si>
+  <si>
+    <t>1900 Skyhawk  Alameda CA 94501</t>
+  </si>
+  <si>
+    <t>Newark Group, Inc.</t>
+  </si>
+  <si>
+    <t>525 Mathew Street  Santa Clara CA 95050</t>
+  </si>
+  <si>
+    <t>ChargePoint, Inc.</t>
+  </si>
+  <si>
+    <t>240 E. Hacienda Avenue  Campbell CA 95008</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">WARN REPORT - </t>
     </r>
@@ -1672,7 +1690,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>07/01/23 to 10/09/23</t>
+      <t>07/01/23 to 10/11/23</t>
     </r>
     <r>
       <rPr>
@@ -1692,7 +1710,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>A detailed WARN summary by county and filtered according to received date. Table Spans cells A2 through H328.</t>
+      <t>A detailed WARN summary by county and filtered according to received date. Table Spans cells A2 through H331.</t>
     </r>
   </si>
 </sst>
@@ -1999,8 +2017,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFF0F0F0"/>
+          <bgColor rgb="FFF0F0F0"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -2040,8 +2058,8 @@
       <numFmt numFmtId="165" formatCode="[$-10436]#,##0;\(#,##0\)"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFF0F0F0"/>
+          <bgColor rgb="FFF0F0F0"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -2080,8 +2098,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFF0F0F0"/>
+          <bgColor rgb="FFF0F0F0"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -2120,8 +2138,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFF0F0F0"/>
+          <bgColor rgb="FFF0F0F0"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -2161,8 +2179,8 @@
       <numFmt numFmtId="164" formatCode="[$-10409]mm/dd/yyyy"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFF0F0F0"/>
+          <bgColor rgb="FFF0F0F0"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -2202,8 +2220,8 @@
       <numFmt numFmtId="164" formatCode="[$-10409]mm/dd/yyyy"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFF0F0F0"/>
+          <bgColor rgb="FFF0F0F0"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -2243,8 +2261,8 @@
       <numFmt numFmtId="164" formatCode="[$-10409]mm/dd/yyyy"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFF0F0F0"/>
+          <bgColor rgb="FFF0F0F0"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -2283,8 +2301,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFF0F0F0"/>
+          <bgColor rgb="FFF0F0F0"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -2476,8 +2494,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:H328" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
-  <autoFilter ref="A2:H328" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:H331" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
+  <autoFilter ref="A2:H331" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -2861,7 +2879,7 @@
       </c>
       <c r="B3" s="6">
         <f>SUM('Detailed WARN Report '!G:G)</f>
-        <v>15928</v>
+        <v>16139</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -2870,7 +2888,7 @@
       </c>
       <c r="B4" s="6">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Permanent")</f>
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -2897,7 +2915,7 @@
       </c>
       <c r="B7" s="6">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Permanent")</f>
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -2929,20 +2947,20 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:H328"/>
+  <dimension ref="A1:H331"/>
   <sheetFormatPr defaultColWidth="26" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.88671875" bestFit="1" customWidth="1"/>
     <col min="2" max="4" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="54.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="62.44140625" style="2" customWidth="1"/>
     <col min="6" max="6" width="14.33203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="52.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="63.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="99.6" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="D1" s="7"/>
       <c r="E1" s="7"/>
@@ -2950,7 +2968,7 @@
       <c r="G1" s="7"/>
       <c r="H1" s="7"/>
     </row>
-    <row r="2" spans="1:8" s="1" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" s="1" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
         <v>0</v>
       </c>
@@ -11450,6 +11468,84 @@
       </c>
       <c r="H328" s="22" t="s">
         <v>518</v>
+      </c>
+    </row>
+    <row r="329" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A329" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="B329" s="14">
+        <v>45145</v>
+      </c>
+      <c r="C329" s="14">
+        <v>45210</v>
+      </c>
+      <c r="D329" s="14">
+        <v>45202</v>
+      </c>
+      <c r="E329" s="15" t="s">
+        <v>519</v>
+      </c>
+      <c r="F329" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G329" s="16">
+        <v>58</v>
+      </c>
+      <c r="H329" s="17" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="330" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A330" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="B330" s="19">
+        <v>45175</v>
+      </c>
+      <c r="C330" s="19">
+        <v>45210</v>
+      </c>
+      <c r="D330" s="19">
+        <v>45245</v>
+      </c>
+      <c r="E330" s="20" t="s">
+        <v>521</v>
+      </c>
+      <c r="F330" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G330" s="21">
+        <v>74</v>
+      </c>
+      <c r="H330" s="22" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="331" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A331" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B331" s="14">
+        <v>45175</v>
+      </c>
+      <c r="C331" s="14">
+        <v>45210</v>
+      </c>
+      <c r="D331" s="14">
+        <v>45236</v>
+      </c>
+      <c r="E331" s="15" t="s">
+        <v>523</v>
+      </c>
+      <c r="F331" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G331" s="16">
+        <v>79</v>
+      </c>
+      <c r="H331" s="17" t="s">
+        <v>524</v>
       </c>
     </row>
   </sheetData>
@@ -11591,13 +11687,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C06C59DD-BA72-4539-8251-9A8329B0FC1D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{61F2A46D-3115-416C-B004-AA8BFCB59A27}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7FBFE211-0C34-433D-9B33-99A7F9097B46}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9AF08510-8FE0-46F1-BD9B-66F2943EBCF0}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0246515F-3E8A-4DEB-BEE7-4506A2B6AD32}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FE57D973-3294-4168-A7D2-38AD12F7189B}"/>
 </file>
--- a/data/warn-scraper/cache/ca/warn_report1.xlsx
+++ b/data/warn-scraper/cache/ca/warn_report1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\WSB-CO\Communications Unit\Website Management\WARN (Worker Adjustment and Retraining Notification) Updates\2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ACDA53E8-D7E5-4D4D-9293-3747A3225DB6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A42E3C1C-6FBC-454B-9527-9C185A042B60}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="29895" yWindow="1230" windowWidth="21600" windowHeight="11430" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1439" uniqueCount="552">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1647" uniqueCount="612">
   <si>
     <t>This worksheet contains 3 sheets. The introductory page, WARN Report Summary, and Detailed WARN Report. The second sheet provides an overview of the report according to layoff/closure types and related quantitative data. The third sheet displays a detailed summary report of affected companies by county. This Daily WARN Report is updated every Tuesday and Thursday. Hyperlinks to the other 2 sheets can be found below in cell A3-A4.</t>
   </si>
@@ -103,7 +103,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>07/01/23 to 10/16/23</t>
+      <t>07/01/23 to 10/18/23</t>
     </r>
     <r>
       <rPr>
@@ -123,7 +123,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>A detailed WARN summary by county and filtered according to received date. Table Spans cells A2 through H356.</t>
+      <t>A detailed WARN summary by county and filtered according to received date. Table Spans cells A2 through H408.</t>
     </r>
   </si>
   <si>
@@ -1427,9 +1427,15 @@
     <t>6301 Owensmouth Avenue  Woodland Hills CA 91367</t>
   </si>
   <si>
+    <t>Farmers Insurance Exchange - 6303</t>
+  </si>
+  <si>
     <t>6303 Owensmouth Avenue  Woodland Hills CA 91367</t>
   </si>
   <si>
+    <t>Farmers Group, Inc. - 6301</t>
+  </si>
+  <si>
     <t>Farmers Group, Inc.</t>
   </si>
   <si>
@@ -1779,6 +1785,180 @@
   </si>
   <si>
     <t>8900 Venice Boulevard Unit 109  Culver City CA 90232</t>
+  </si>
+  <si>
+    <t>4507 N. Selland Avenue  Fresno CA 93725</t>
+  </si>
+  <si>
+    <t>Sunrun Inc. - Angus</t>
+  </si>
+  <si>
+    <t>2965 S. Angus Avenue  Fresno CA 93725</t>
+  </si>
+  <si>
+    <t>LEER Group</t>
+  </si>
+  <si>
+    <t>1686 E. Beamer Street  Woodland CA 95776</t>
+  </si>
+  <si>
+    <t>1242 E. Beamer Street  Woodland CA 95776</t>
+  </si>
+  <si>
+    <t>4507 N. Selland Ave.  Fresno CA 93725</t>
+  </si>
+  <si>
+    <t>Noble House Home Furnishing LLC Superior HQ</t>
+  </si>
+  <si>
+    <t>21325 Superior St.  Chatsworth CA 91311</t>
+  </si>
+  <si>
+    <t>Noble House Home Furnishings LLC GDF Outlet</t>
+  </si>
+  <si>
+    <t>9200 DeSoto Ave.  Chatsworth CA 91311</t>
+  </si>
+  <si>
+    <t>Noble House Home Furnishings - 7901 Deering</t>
+  </si>
+  <si>
+    <t>7901 Deering Ave.  Canoga Park CA 91304</t>
+  </si>
+  <si>
+    <t>Noble House Home Furnishings LLC</t>
+  </si>
+  <si>
+    <t>1714 S. Anderson Ave.  Compton CA 90220</t>
+  </si>
+  <si>
+    <t>Nobel House Home Furnishings LLC</t>
+  </si>
+  <si>
+    <t>4388 Shirley Ave.  El Monte CA 91731</t>
+  </si>
+  <si>
+    <t>12830 romandel Ave.  Santa Fe Springs CA 90670</t>
+  </si>
+  <si>
+    <t>38940 Trade Center Drive  Palmdale CA 93551</t>
+  </si>
+  <si>
+    <t>2010 E Carson St  Long Beach CA 90807</t>
+  </si>
+  <si>
+    <t>3559 E South St  Long Beach CA 90805</t>
+  </si>
+  <si>
+    <t>555 E Ocean Blvd #110  Long Beach CA 90802</t>
+  </si>
+  <si>
+    <t>Matheson Flight Extenders, Inc.</t>
+  </si>
+  <si>
+    <t>2400 E. Artesia Blvd.  Long Beach CA 90805</t>
+  </si>
+  <si>
+    <t>2712 Augustine Drive Suite 120  Santa Clara CA 95054</t>
+  </si>
+  <si>
+    <t>10028 Adams Ave  Huntington Beach CA 92646</t>
+  </si>
+  <si>
+    <t>10165 Valley View St  Cypress CA 90630</t>
+  </si>
+  <si>
+    <t>1031 Avenida Pico #103  San Clemente CA 92673</t>
+  </si>
+  <si>
+    <t>1040 W Imperial Hwy Suite D  La Habra CA 90631</t>
+  </si>
+  <si>
+    <t>20635 Yorba Linda Blvd  Yorba Linda CA 92886</t>
+  </si>
+  <si>
+    <t>2415 East Imperial Hwy  Brea CA 92821</t>
+  </si>
+  <si>
+    <t>705 E Birch Street Suite P  Brea CA 92821</t>
+  </si>
+  <si>
+    <t>14443 Culver Drive Suite 14443-A  Irvine CA 92604</t>
+  </si>
+  <si>
+    <t>31845 Temecula Pkwy  Temecula CA 92592</t>
+  </si>
+  <si>
+    <t>3195 Harbor Blvd  Costa Mesa CA 92626</t>
+  </si>
+  <si>
+    <t>3955 Bedford Canyon Rd Ste 103  Corona CA 92883</t>
+  </si>
+  <si>
+    <t>40461 Murrieta Hot Springs Rd.  Murrieta CA 92563</t>
+  </si>
+  <si>
+    <t>44-419 Town Center Way Ste E  Palm Desert CA 92260</t>
+  </si>
+  <si>
+    <t>78-965 Hwy 111  La Quinta CA 92253</t>
+  </si>
+  <si>
+    <t>82-151 Ave 42 #100  Indio CA 92203</t>
+  </si>
+  <si>
+    <t>1201 E Bidwell St  Folsom CA 95630</t>
+  </si>
+  <si>
+    <t>Noble House Home Furnishings LLc</t>
+  </si>
+  <si>
+    <t>3655 E. Philadelphia St.  Ontario CA 91761</t>
+  </si>
+  <si>
+    <t>11971 Central Ave  Chino CA 91710</t>
+  </si>
+  <si>
+    <t>125 Research Drive Suite B  Redlands CA 92374</t>
+  </si>
+  <si>
+    <t>1855 S Centre City Pkwy Suite 1885B  Escondido CA 92025</t>
+  </si>
+  <si>
+    <t>1390 Market St Ste 109  San Francisco CA 94102</t>
+  </si>
+  <si>
+    <t>Divvy Homes Inc.</t>
+  </si>
+  <si>
+    <t>300 Montgomery Street, Suite 350  San Francisco CA 94104</t>
+  </si>
+  <si>
+    <t>1551 stimson St. Unit 4  Stockton CA 95206</t>
+  </si>
+  <si>
+    <t>1760 South Bascom Ave Suite 140  Campbell CA 95008</t>
+  </si>
+  <si>
+    <t>1421 W MacArthur Blvd #E  Santa Ana CA 92704</t>
+  </si>
+  <si>
+    <t>13299 E South St  Cerritos CA 90703</t>
+  </si>
+  <si>
+    <t>784 Admiral Callaghan Lane Suite 784  Vallejo CA 94591</t>
+  </si>
+  <si>
+    <t>415 N Pacific Coast Hwy Suite 101  Redondo Beach CA 90277</t>
+  </si>
+  <si>
+    <t>2944 Tapo Canyon Rd #A  Simi Valley CA 93063</t>
+  </si>
+  <si>
+    <t>132 Vintage Way Suite F5  Novato CA 94945</t>
+  </si>
+  <si>
+    <t>411 3rd St  San Rafael CA 94901</t>
   </si>
 </sst>
 </file>
@@ -2083,8 +2263,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFF0F0F0"/>
+          <bgColor rgb="FFF0F0F0"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -2124,8 +2304,8 @@
       <numFmt numFmtId="165" formatCode="[$-10436]#,##0;\(#,##0\)"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFF0F0F0"/>
+          <bgColor rgb="FFF0F0F0"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -2164,8 +2344,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFF0F0F0"/>
+          <bgColor rgb="FFF0F0F0"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -2204,8 +2384,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFF0F0F0"/>
+          <bgColor rgb="FFF0F0F0"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -2245,8 +2425,8 @@
       <numFmt numFmtId="164" formatCode="[$-10409]mm/dd/yyyy"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFF0F0F0"/>
+          <bgColor rgb="FFF0F0F0"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -2286,8 +2466,8 @@
       <numFmt numFmtId="164" formatCode="[$-10409]mm/dd/yyyy"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFF0F0F0"/>
+          <bgColor rgb="FFF0F0F0"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -2327,8 +2507,8 @@
       <numFmt numFmtId="164" formatCode="[$-10409]mm/dd/yyyy"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFF0F0F0"/>
+          <bgColor rgb="FFF0F0F0"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -2367,8 +2547,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFF0F0F0"/>
+          <bgColor rgb="FFF0F0F0"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -2560,8 +2740,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:H356" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="9" tableBorderDxfId="10" totalsRowBorderDxfId="8">
-  <autoFilter ref="A2:H356" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:H408" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="9" tableBorderDxfId="10" totalsRowBorderDxfId="8">
+  <autoFilter ref="A2:H408" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -2945,7 +3125,7 @@
       </c>
       <c r="B3" s="5">
         <f>SUM('Detailed WARN Report '!G:G)</f>
-        <v>16425</v>
+        <v>17503</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -2954,7 +3134,7 @@
       </c>
       <c r="B4" s="5">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Permanent")</f>
-        <v>223</v>
+        <v>265</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -2981,7 +3161,7 @@
       </c>
       <c r="B7" s="5">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Permanent")</f>
-        <v>121</v>
+        <v>131</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -3013,7 +3193,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:H356"/>
+  <dimension ref="A1:H408"/>
   <sheetFormatPr defaultColWidth="26" defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="25.85546875" bestFit="1" customWidth="1"/>
@@ -9779,7 +9959,7 @@
         <v>45197</v>
       </c>
       <c r="D261" s="13">
-        <v>45230</v>
+        <v>45229</v>
       </c>
       <c r="E261" s="14" t="s">
         <v>432</v>
@@ -9788,7 +9968,7 @@
         <v>25</v>
       </c>
       <c r="G261" s="15">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="H261" s="16" t="s">
         <v>433</v>
@@ -9805,10 +9985,10 @@
         <v>45197</v>
       </c>
       <c r="D262" s="18">
-        <v>45230</v>
+        <v>45229</v>
       </c>
       <c r="E262" s="19" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="F262" s="19" t="s">
         <v>25</v>
@@ -9817,7 +9997,7 @@
         <v>2</v>
       </c>
       <c r="H262" s="21" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="263" spans="1:8">
@@ -9831,16 +10011,16 @@
         <v>45197</v>
       </c>
       <c r="D263" s="13">
-        <v>45230</v>
+        <v>45229</v>
       </c>
       <c r="E263" s="14" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F263" s="14" t="s">
         <v>25</v>
       </c>
       <c r="G263" s="15">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="H263" s="16" t="s">
         <v>433</v>
@@ -9857,50 +10037,50 @@
         <v>45197</v>
       </c>
       <c r="D264" s="18">
-        <v>45230</v>
+        <v>45229</v>
       </c>
       <c r="E264" s="19" t="s">
+        <v>437</v>
+      </c>
+      <c r="F264" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="G264" s="20">
+        <v>135</v>
+      </c>
+      <c r="H264" s="21" t="s">
         <v>435</v>
-      </c>
-      <c r="F264" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="G264" s="20">
-        <v>163</v>
-      </c>
-      <c r="H264" s="21" t="s">
-        <v>434</v>
       </c>
     </row>
     <row r="265" spans="1:8">
       <c r="A265" s="12" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="B265" s="13">
-        <v>45152</v>
+        <v>45166</v>
       </c>
       <c r="C265" s="13">
         <v>45197</v>
       </c>
       <c r="D265" s="13">
-        <v>45214</v>
+        <v>45257</v>
       </c>
       <c r="E265" s="14" t="s">
         <v>436</v>
       </c>
       <c r="F265" s="14" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="G265" s="15">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="H265" s="16" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
     </row>
     <row r="266" spans="1:8">
       <c r="A266" s="17" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B266" s="18">
         <v>45166</v>
@@ -9909,24 +10089,24 @@
         <v>45197</v>
       </c>
       <c r="D266" s="18">
-        <v>45228</v>
+        <v>45258</v>
       </c>
       <c r="E266" s="19" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="F266" s="19" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="G266" s="20">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="H266" s="21" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
     </row>
     <row r="267" spans="1:8">
       <c r="A267" s="12" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B267" s="13">
         <v>45166</v>
@@ -9935,149 +10115,149 @@
         <v>45197</v>
       </c>
       <c r="D267" s="13">
-        <v>45228</v>
+        <v>45286</v>
       </c>
       <c r="E267" s="14" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="F267" s="14" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="G267" s="15">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="H267" s="16" t="s">
-        <v>440</v>
+        <v>433</v>
       </c>
     </row>
     <row r="268" spans="1:8">
       <c r="A268" s="17" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="B268" s="18">
-        <v>45163</v>
+        <v>45166</v>
       </c>
       <c r="C268" s="18">
         <v>45197</v>
       </c>
       <c r="D268" s="18">
-        <v>45214</v>
+        <v>45247</v>
       </c>
       <c r="E268" s="19" t="s">
-        <v>77</v>
+        <v>437</v>
       </c>
       <c r="F268" s="19" t="s">
         <v>25</v>
       </c>
       <c r="G268" s="20">
-        <v>58</v>
+        <v>1</v>
       </c>
       <c r="H268" s="21" t="s">
-        <v>233</v>
+        <v>435</v>
       </c>
     </row>
     <row r="269" spans="1:8">
       <c r="A269" s="12" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="B269" s="13">
-        <v>45162</v>
+        <v>45152</v>
       </c>
       <c r="C269" s="13">
         <v>45197</v>
       </c>
       <c r="D269" s="13">
-        <v>45177</v>
+        <v>45214</v>
       </c>
       <c r="E269" s="14" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="F269" s="14" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="G269" s="15">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="H269" s="16" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
     </row>
     <row r="270" spans="1:8">
       <c r="A270" s="17" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="B270" s="18">
-        <v>45162</v>
+        <v>45166</v>
       </c>
       <c r="C270" s="18">
         <v>45197</v>
       </c>
       <c r="D270" s="18">
-        <v>45177</v>
+        <v>45228</v>
       </c>
       <c r="E270" s="19" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F270" s="19" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="G270" s="20">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="H270" s="21" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
     </row>
     <row r="271" spans="1:8">
       <c r="A271" s="12" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="B271" s="13">
-        <v>45162</v>
+        <v>45166</v>
       </c>
       <c r="C271" s="13">
         <v>45197</v>
       </c>
       <c r="D271" s="13">
-        <v>45214</v>
+        <v>45228</v>
       </c>
       <c r="E271" s="14" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="F271" s="14" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="G271" s="15">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="H271" s="16" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
     </row>
     <row r="272" spans="1:8">
       <c r="A272" s="17" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="B272" s="18">
-        <v>45162</v>
+        <v>45163</v>
       </c>
       <c r="C272" s="18">
         <v>45197</v>
       </c>
       <c r="D272" s="18">
-        <v>45199</v>
+        <v>45214</v>
       </c>
       <c r="E272" s="19" t="s">
-        <v>447</v>
+        <v>77</v>
       </c>
       <c r="F272" s="19" t="s">
         <v>25</v>
       </c>
       <c r="G272" s="20">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="H272" s="21" t="s">
-        <v>444</v>
+        <v>233</v>
       </c>
     </row>
     <row r="273" spans="1:8">
@@ -10091,10 +10271,10 @@
         <v>45197</v>
       </c>
       <c r="D273" s="13">
-        <v>45260</v>
+        <v>45177</v>
       </c>
       <c r="E273" s="14" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="F273" s="14" t="s">
         <v>25</v>
@@ -10117,19 +10297,19 @@
         <v>45197</v>
       </c>
       <c r="D274" s="18">
-        <v>45291</v>
+        <v>45177</v>
       </c>
       <c r="E274" s="19" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="F274" s="19" t="s">
         <v>25</v>
       </c>
       <c r="G274" s="20">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="H274" s="21" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="275" spans="1:8">
@@ -10143,10 +10323,10 @@
         <v>45197</v>
       </c>
       <c r="D275" s="13">
-        <v>45275</v>
+        <v>45214</v>
       </c>
       <c r="E275" s="14" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="F275" s="14" t="s">
         <v>25</v>
@@ -10155,7 +10335,7 @@
         <v>1</v>
       </c>
       <c r="H275" s="16" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="276" spans="1:8">
@@ -10169,19 +10349,19 @@
         <v>45197</v>
       </c>
       <c r="D276" s="18">
-        <v>45230</v>
+        <v>45199</v>
       </c>
       <c r="E276" s="19" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="F276" s="19" t="s">
         <v>25</v>
       </c>
       <c r="G276" s="20">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H276" s="21" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="277" spans="1:8">
@@ -10195,19 +10375,19 @@
         <v>45197</v>
       </c>
       <c r="D277" s="13">
-        <v>45177</v>
+        <v>45260</v>
       </c>
       <c r="E277" s="14" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="F277" s="14" t="s">
         <v>25</v>
       </c>
       <c r="G277" s="15">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="H277" s="16" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
     </row>
     <row r="278" spans="1:8">
@@ -10221,7 +10401,7 @@
         <v>45197</v>
       </c>
       <c r="D278" s="18">
-        <v>45214</v>
+        <v>45291</v>
       </c>
       <c r="E278" s="19" t="s">
         <v>451</v>
@@ -10230,10 +10410,10 @@
         <v>25</v>
       </c>
       <c r="G278" s="20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H278" s="21" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
     </row>
     <row r="279" spans="1:8">
@@ -10247,7 +10427,7 @@
         <v>45197</v>
       </c>
       <c r="D279" s="13">
-        <v>45261</v>
+        <v>45275</v>
       </c>
       <c r="E279" s="14" t="s">
         <v>451</v>
@@ -10264,106 +10444,106 @@
     </row>
     <row r="280" spans="1:8">
       <c r="A280" s="17" t="s">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="B280" s="18">
-        <v>45168</v>
+        <v>45162</v>
       </c>
       <c r="C280" s="18">
-        <v>45198</v>
+        <v>45197</v>
       </c>
       <c r="D280" s="18">
         <v>45230</v>
       </c>
       <c r="E280" s="19" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="F280" s="19" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="G280" s="20">
-        <v>53</v>
+        <v>1</v>
       </c>
       <c r="H280" s="21" t="s">
-        <v>454</v>
+        <v>446</v>
       </c>
     </row>
     <row r="281" spans="1:8">
       <c r="A281" s="12" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="B281" s="13">
-        <v>45169</v>
+        <v>45162</v>
       </c>
       <c r="C281" s="13">
-        <v>45198</v>
+        <v>45197</v>
       </c>
       <c r="D281" s="13">
-        <v>45230</v>
+        <v>45177</v>
       </c>
       <c r="E281" s="14" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="F281" s="14" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="G281" s="15">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="H281" s="16" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="282" spans="1:8">
       <c r="A282" s="17" t="s">
-        <v>369</v>
+        <v>58</v>
       </c>
       <c r="B282" s="18">
-        <v>45167</v>
+        <v>45162</v>
       </c>
       <c r="C282" s="18">
-        <v>45198</v>
+        <v>45197</v>
       </c>
       <c r="D282" s="18">
-        <v>45230</v>
+        <v>45214</v>
       </c>
       <c r="E282" s="19" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="F282" s="19" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="G282" s="20">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="H282" s="21" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
     </row>
     <row r="283" spans="1:8">
       <c r="A283" s="12" t="s">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="B283" s="13">
-        <v>45170</v>
+        <v>45162</v>
       </c>
       <c r="C283" s="13">
-        <v>45201</v>
+        <v>45197</v>
       </c>
       <c r="D283" s="13">
-        <v>45244</v>
+        <v>45261</v>
       </c>
       <c r="E283" s="14" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="F283" s="14" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="G283" s="15">
-        <v>217</v>
+        <v>1</v>
       </c>
       <c r="H283" s="16" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
     </row>
     <row r="284" spans="1:8">
@@ -10371,25 +10551,25 @@
         <v>34</v>
       </c>
       <c r="B284" s="18">
-        <v>45169</v>
+        <v>45168</v>
       </c>
       <c r="C284" s="18">
-        <v>45201</v>
+        <v>45198</v>
       </c>
       <c r="D284" s="18">
-        <v>45231</v>
+        <v>45230</v>
       </c>
       <c r="E284" s="19" t="s">
-        <v>291</v>
+        <v>455</v>
       </c>
       <c r="F284" s="19" t="s">
         <v>39</v>
       </c>
       <c r="G284" s="20">
-        <v>3</v>
+        <v>53</v>
       </c>
       <c r="H284" s="21" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
     </row>
     <row r="285" spans="1:8">
@@ -10397,111 +10577,111 @@
         <v>72</v>
       </c>
       <c r="B285" s="13">
-        <v>45140</v>
+        <v>45169</v>
       </c>
       <c r="C285" s="13">
-        <v>45201</v>
+        <v>45198</v>
       </c>
       <c r="D285" s="13">
-        <v>45205</v>
+        <v>45230</v>
       </c>
       <c r="E285" s="14" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="F285" s="14" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="G285" s="15">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="H285" s="16" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
     </row>
     <row r="286" spans="1:8">
       <c r="A286" s="17" t="s">
-        <v>44</v>
+        <v>369</v>
       </c>
       <c r="B286" s="18">
-        <v>45147</v>
+        <v>45167</v>
       </c>
       <c r="C286" s="18">
-        <v>45201</v>
+        <v>45198</v>
       </c>
       <c r="D286" s="18">
-        <v>45205</v>
+        <v>45230</v>
       </c>
       <c r="E286" s="19" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="F286" s="19" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="G286" s="20">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="H286" s="21" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
     </row>
     <row r="287" spans="1:8">
       <c r="A287" s="12" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B287" s="13">
-        <v>45147</v>
+        <v>45170</v>
       </c>
       <c r="C287" s="13">
         <v>45201</v>
       </c>
       <c r="D287" s="13">
-        <v>45205</v>
+        <v>45244</v>
       </c>
       <c r="E287" s="14" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="F287" s="14" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="G287" s="15">
-        <v>4</v>
+        <v>217</v>
       </c>
       <c r="H287" s="16" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
     </row>
     <row r="288" spans="1:8">
       <c r="A288" s="17" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B288" s="18">
-        <v>45147</v>
+        <v>45169</v>
       </c>
       <c r="C288" s="18">
         <v>45201</v>
       </c>
       <c r="D288" s="18">
-        <v>45205</v>
+        <v>45231</v>
       </c>
       <c r="E288" s="19" t="s">
-        <v>464</v>
+        <v>291</v>
       </c>
       <c r="F288" s="19" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="G288" s="20">
         <v>3</v>
       </c>
       <c r="H288" s="21" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
     </row>
     <row r="289" spans="1:8">
       <c r="A289" s="12" t="s">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="B289" s="13">
-        <v>45147</v>
+        <v>45140</v>
       </c>
       <c r="C289" s="13">
         <v>45201</v>
@@ -10516,18 +10696,18 @@
         <v>25</v>
       </c>
       <c r="G289" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H289" s="16" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
     </row>
     <row r="290" spans="1:8">
       <c r="A290" s="17" t="s">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="B290" s="18">
-        <v>45140</v>
+        <v>45147</v>
       </c>
       <c r="C290" s="18">
         <v>45201</v>
@@ -10536,24 +10716,24 @@
         <v>45205</v>
       </c>
       <c r="E290" s="19" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="F290" s="19" t="s">
         <v>25</v>
       </c>
       <c r="G290" s="20">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="H290" s="21" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="291" spans="1:8">
       <c r="A291" s="12" t="s">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="B291" s="13">
-        <v>45140</v>
+        <v>45147</v>
       </c>
       <c r="C291" s="13">
         <v>45201</v>
@@ -10562,24 +10742,24 @@
         <v>45205</v>
       </c>
       <c r="E291" s="14" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="F291" s="14" t="s">
         <v>25</v>
       </c>
       <c r="G291" s="15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H291" s="16" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="292" spans="1:8">
       <c r="A292" s="17" t="s">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="B292" s="18">
-        <v>45140</v>
+        <v>45147</v>
       </c>
       <c r="C292" s="18">
         <v>45201</v>
@@ -10588,24 +10768,24 @@
         <v>45205</v>
       </c>
       <c r="E292" s="19" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="F292" s="19" t="s">
         <v>25</v>
       </c>
       <c r="G292" s="20">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H292" s="21" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="293" spans="1:8">
       <c r="A293" s="12" t="s">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="B293" s="13">
-        <v>45140</v>
+        <v>45147</v>
       </c>
       <c r="C293" s="13">
         <v>45201</v>
@@ -10614,16 +10794,16 @@
         <v>45205</v>
       </c>
       <c r="E293" s="14" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="F293" s="14" t="s">
         <v>25</v>
       </c>
       <c r="G293" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H293" s="16" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="294" spans="1:8">
@@ -10640,16 +10820,16 @@
         <v>45205</v>
       </c>
       <c r="E294" s="19" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="F294" s="19" t="s">
         <v>25</v>
       </c>
       <c r="G294" s="20">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="H294" s="21" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="295" spans="1:8">
@@ -10666,151 +10846,151 @@
         <v>45205</v>
       </c>
       <c r="E295" s="14" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="F295" s="14" t="s">
         <v>25</v>
       </c>
       <c r="G295" s="15">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="H295" s="16" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="296" spans="1:8">
       <c r="A296" s="17" t="s">
-        <v>178</v>
+        <v>72</v>
       </c>
       <c r="B296" s="18">
-        <v>45170</v>
+        <v>45140</v>
       </c>
       <c r="C296" s="18">
         <v>45201</v>
       </c>
       <c r="D296" s="18">
-        <v>45231</v>
+        <v>45205</v>
       </c>
       <c r="E296" s="19" t="s">
-        <v>475</v>
+        <v>464</v>
       </c>
       <c r="F296" s="19" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="G296" s="20">
-        <v>292</v>
+        <v>7</v>
       </c>
       <c r="H296" s="21" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
     </row>
     <row r="297" spans="1:8">
       <c r="A297" s="12" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="B297" s="13">
-        <v>45181</v>
+        <v>45140</v>
       </c>
       <c r="C297" s="13">
-        <v>45202</v>
+        <v>45201</v>
       </c>
       <c r="D297" s="13">
-        <v>45240</v>
+        <v>45205</v>
       </c>
       <c r="E297" s="14" t="s">
-        <v>477</v>
+        <v>464</v>
       </c>
       <c r="F297" s="14" t="s">
         <v>25</v>
       </c>
       <c r="G297" s="15">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="H297" s="16" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
     </row>
     <row r="298" spans="1:8">
       <c r="A298" s="17" t="s">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="B298" s="18">
-        <v>45181</v>
+        <v>45140</v>
       </c>
       <c r="C298" s="18">
-        <v>45202</v>
+        <v>45201</v>
       </c>
       <c r="D298" s="18">
-        <v>45240</v>
+        <v>45205</v>
       </c>
       <c r="E298" s="19" t="s">
-        <v>477</v>
+        <v>464</v>
       </c>
       <c r="F298" s="19" t="s">
         <v>25</v>
       </c>
       <c r="G298" s="20">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H298" s="21" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
     </row>
     <row r="299" spans="1:8">
       <c r="A299" s="12" t="s">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="B299" s="13">
-        <v>45181</v>
+        <v>45140</v>
       </c>
       <c r="C299" s="13">
-        <v>45202</v>
+        <v>45201</v>
       </c>
       <c r="D299" s="13">
-        <v>45240</v>
+        <v>45205</v>
       </c>
       <c r="E299" s="14" t="s">
-        <v>480</v>
+        <v>464</v>
       </c>
       <c r="F299" s="14" t="s">
         <v>25</v>
       </c>
       <c r="G299" s="15">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H299" s="16" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
     </row>
     <row r="300" spans="1:8">
       <c r="A300" s="17" t="s">
-        <v>34</v>
+        <v>178</v>
       </c>
       <c r="B300" s="18">
-        <v>45181</v>
+        <v>45170</v>
       </c>
       <c r="C300" s="18">
-        <v>45202</v>
+        <v>45201</v>
       </c>
       <c r="D300" s="18">
-        <v>45240</v>
+        <v>45231</v>
       </c>
       <c r="E300" s="19" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="F300" s="19" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="G300" s="20">
-        <v>8</v>
+        <v>292</v>
       </c>
       <c r="H300" s="21" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
     </row>
     <row r="301" spans="1:8">
       <c r="A301" s="12" t="s">
-        <v>34</v>
+        <v>93</v>
       </c>
       <c r="B301" s="13">
         <v>45181</v>
@@ -10822,16 +11002,16 @@
         <v>45240</v>
       </c>
       <c r="E301" s="14" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="F301" s="14" t="s">
         <v>25</v>
       </c>
       <c r="G301" s="15">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="H301" s="16" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
     </row>
     <row r="302" spans="1:8">
@@ -10839,30 +11019,30 @@
         <v>34</v>
       </c>
       <c r="B302" s="18">
-        <v>45170</v>
+        <v>45181</v>
       </c>
       <c r="C302" s="18">
         <v>45202</v>
       </c>
       <c r="D302" s="18">
-        <v>45170</v>
+        <v>45240</v>
       </c>
       <c r="E302" s="19" t="s">
-        <v>486</v>
+        <v>479</v>
       </c>
       <c r="F302" s="19" t="s">
         <v>25</v>
       </c>
       <c r="G302" s="20">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H302" s="21" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
     </row>
     <row r="303" spans="1:8">
       <c r="A303" s="12" t="s">
-        <v>93</v>
+        <v>34</v>
       </c>
       <c r="B303" s="13">
         <v>45181</v>
@@ -10874,21 +11054,21 @@
         <v>45240</v>
       </c>
       <c r="E303" s="14" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="F303" s="14" t="s">
         <v>25</v>
       </c>
       <c r="G303" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H303" s="16" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
     </row>
     <row r="304" spans="1:8">
       <c r="A304" s="17" t="s">
-        <v>93</v>
+        <v>34</v>
       </c>
       <c r="B304" s="18">
         <v>45181</v>
@@ -10900,21 +11080,21 @@
         <v>45240</v>
       </c>
       <c r="E304" s="19" t="s">
-        <v>477</v>
+        <v>484</v>
       </c>
       <c r="F304" s="19" t="s">
         <v>25</v>
       </c>
       <c r="G304" s="20">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H304" s="21" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
     </row>
     <row r="305" spans="1:8">
       <c r="A305" s="12" t="s">
-        <v>93</v>
+        <v>34</v>
       </c>
       <c r="B305" s="13">
         <v>45181</v>
@@ -10926,21 +11106,21 @@
         <v>45240</v>
       </c>
       <c r="E305" s="14" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="F305" s="14" t="s">
         <v>25</v>
       </c>
       <c r="G305" s="15">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H305" s="16" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
     </row>
     <row r="306" spans="1:8">
       <c r="A306" s="17" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="B306" s="18">
         <v>45170</v>
@@ -10952,91 +11132,91 @@
         <v>45170</v>
       </c>
       <c r="E306" s="19" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="F306" s="19" t="s">
         <v>25</v>
       </c>
       <c r="G306" s="20">
-        <v>57</v>
+        <v>1</v>
       </c>
       <c r="H306" s="21" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
     </row>
     <row r="307" spans="1:8">
       <c r="A307" s="12" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="B307" s="13">
-        <v>45170</v>
+        <v>45181</v>
       </c>
       <c r="C307" s="13">
         <v>45202</v>
       </c>
       <c r="D307" s="13">
-        <v>45183</v>
+        <v>45240</v>
       </c>
       <c r="E307" s="14" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="F307" s="14" t="s">
         <v>25</v>
       </c>
       <c r="G307" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H307" s="16" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="308" spans="1:8">
       <c r="A308" s="17" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="B308" s="18">
-        <v>45170</v>
+        <v>45181</v>
       </c>
       <c r="C308" s="18">
         <v>45202</v>
       </c>
       <c r="D308" s="18">
-        <v>45212</v>
+        <v>45240</v>
       </c>
       <c r="E308" s="19" t="s">
-        <v>486</v>
+        <v>479</v>
       </c>
       <c r="F308" s="19" t="s">
         <v>25</v>
       </c>
       <c r="G308" s="20">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="H308" s="21" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="309" spans="1:8">
       <c r="A309" s="12" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="B309" s="13">
-        <v>45170</v>
+        <v>45181</v>
       </c>
       <c r="C309" s="13">
         <v>45202</v>
       </c>
       <c r="D309" s="13">
-        <v>45170</v>
+        <v>45240</v>
       </c>
       <c r="E309" s="14" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="F309" s="14" t="s">
         <v>25</v>
       </c>
       <c r="G309" s="15">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H309" s="16" t="s">
         <v>494</v>
@@ -11044,7 +11224,7 @@
     </row>
     <row r="310" spans="1:8">
       <c r="A310" s="17" t="s">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="B310" s="18">
         <v>45170</v>
@@ -11056,13 +11236,13 @@
         <v>45170</v>
       </c>
       <c r="E310" s="19" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="F310" s="19" t="s">
         <v>25</v>
       </c>
       <c r="G310" s="20">
-        <v>1</v>
+        <v>57</v>
       </c>
       <c r="H310" s="21" t="s">
         <v>495</v>
@@ -11070,97 +11250,97 @@
     </row>
     <row r="311" spans="1:8">
       <c r="A311" s="12" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="B311" s="13">
-        <v>45181</v>
+        <v>45170</v>
       </c>
       <c r="C311" s="13">
         <v>45202</v>
       </c>
       <c r="D311" s="13">
-        <v>45240</v>
+        <v>45183</v>
       </c>
       <c r="E311" s="14" t="s">
-        <v>477</v>
+        <v>488</v>
       </c>
       <c r="F311" s="14" t="s">
         <v>25</v>
       </c>
       <c r="G311" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H311" s="16" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="312" spans="1:8">
       <c r="A312" s="17" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
       <c r="B312" s="18">
-        <v>45177</v>
+        <v>45170</v>
       </c>
       <c r="C312" s="18">
         <v>45202</v>
       </c>
       <c r="D312" s="18">
-        <v>45237</v>
+        <v>45212</v>
       </c>
       <c r="E312" s="19" t="s">
-        <v>497</v>
+        <v>488</v>
       </c>
       <c r="F312" s="19" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="G312" s="20">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="H312" s="21" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
     </row>
     <row r="313" spans="1:8">
       <c r="A313" s="12" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
       <c r="B313" s="13">
-        <v>45181</v>
+        <v>45170</v>
       </c>
       <c r="C313" s="13">
         <v>45202</v>
       </c>
       <c r="D313" s="13">
-        <v>45240</v>
+        <v>45170</v>
       </c>
       <c r="E313" s="14" t="s">
-        <v>477</v>
+        <v>488</v>
       </c>
       <c r="F313" s="14" t="s">
         <v>25</v>
       </c>
       <c r="G313" s="15">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H313" s="16" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
     </row>
     <row r="314" spans="1:8">
       <c r="A314" s="17" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="B314" s="18">
-        <v>45181</v>
+        <v>45170</v>
       </c>
       <c r="C314" s="18">
         <v>45202</v>
       </c>
       <c r="D314" s="18">
-        <v>45240</v>
+        <v>45170</v>
       </c>
       <c r="E314" s="19" t="s">
-        <v>477</v>
+        <v>488</v>
       </c>
       <c r="F314" s="19" t="s">
         <v>25</v>
@@ -11169,102 +11349,102 @@
         <v>1</v>
       </c>
       <c r="H314" s="21" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
     </row>
     <row r="315" spans="1:8">
       <c r="A315" s="12" t="s">
-        <v>36</v>
+        <v>83</v>
       </c>
       <c r="B315" s="13">
-        <v>45166</v>
+        <v>45181</v>
       </c>
       <c r="C315" s="13">
-        <v>45203</v>
+        <v>45202</v>
       </c>
       <c r="D315" s="13">
-        <v>45166</v>
+        <v>45240</v>
       </c>
       <c r="E315" s="14" t="s">
-        <v>501</v>
+        <v>479</v>
       </c>
       <c r="F315" s="14" t="s">
         <v>25</v>
       </c>
       <c r="G315" s="15">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="H315" s="16" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
     </row>
     <row r="316" spans="1:8">
       <c r="A316" s="17" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B316" s="18">
-        <v>45166</v>
+        <v>45177</v>
       </c>
       <c r="C316" s="18">
-        <v>45203</v>
+        <v>45202</v>
       </c>
       <c r="D316" s="18">
-        <v>45166</v>
+        <v>45237</v>
       </c>
       <c r="E316" s="19" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="F316" s="19" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="G316" s="20">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="H316" s="21" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
     </row>
     <row r="317" spans="1:8">
       <c r="A317" s="12" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B317" s="13">
-        <v>45166</v>
+        <v>45181</v>
       </c>
       <c r="C317" s="13">
-        <v>45203</v>
+        <v>45202</v>
       </c>
       <c r="D317" s="13">
-        <v>45166</v>
+        <v>45240</v>
       </c>
       <c r="E317" s="14" t="s">
+        <v>479</v>
+      </c>
+      <c r="F317" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G317" s="15">
+        <v>1</v>
+      </c>
+      <c r="H317" s="16" t="s">
         <v>501</v>
-      </c>
-      <c r="F317" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="G317" s="15">
-        <v>4</v>
-      </c>
-      <c r="H317" s="16" t="s">
-        <v>504</v>
       </c>
     </row>
     <row r="318" spans="1:8">
       <c r="A318" s="17" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B318" s="18">
-        <v>45166</v>
+        <v>45181</v>
       </c>
       <c r="C318" s="18">
-        <v>45203</v>
+        <v>45202</v>
       </c>
       <c r="D318" s="18">
-        <v>45166</v>
+        <v>45240</v>
       </c>
       <c r="E318" s="19" t="s">
-        <v>501</v>
+        <v>479</v>
       </c>
       <c r="F318" s="19" t="s">
         <v>25</v>
@@ -11273,7 +11453,7 @@
         <v>1</v>
       </c>
       <c r="H318" s="21" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
     </row>
     <row r="319" spans="1:8">
@@ -11290,16 +11470,16 @@
         <v>45166</v>
       </c>
       <c r="E319" s="14" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="F319" s="14" t="s">
         <v>25</v>
       </c>
       <c r="G319" s="15">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H319" s="16" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="320" spans="1:8">
@@ -11316,16 +11496,16 @@
         <v>45166</v>
       </c>
       <c r="E320" s="19" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="F320" s="19" t="s">
         <v>25</v>
       </c>
       <c r="G320" s="20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H320" s="21" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="321" spans="1:8">
@@ -11342,16 +11522,16 @@
         <v>45166</v>
       </c>
       <c r="E321" s="14" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="F321" s="14" t="s">
         <v>25</v>
       </c>
       <c r="G321" s="15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H321" s="16" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
     </row>
     <row r="322" spans="1:8">
@@ -11368,7 +11548,7 @@
         <v>45166</v>
       </c>
       <c r="E322" s="19" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="F322" s="19" t="s">
         <v>25</v>
@@ -11377,267 +11557,267 @@
         <v>1</v>
       </c>
       <c r="H322" s="21" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="323" spans="1:8">
       <c r="A323" s="12" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="B323" s="13">
-        <v>45170</v>
+        <v>45166</v>
       </c>
       <c r="C323" s="13">
         <v>45203</v>
       </c>
       <c r="D323" s="13">
-        <v>45291</v>
+        <v>45166</v>
       </c>
       <c r="E323" s="14" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="F323" s="14" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="G323" s="15">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="H323" s="16" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
     </row>
     <row r="324" spans="1:8">
       <c r="A324" s="17" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="B324" s="18">
-        <v>45198</v>
+        <v>45166</v>
       </c>
       <c r="C324" s="18">
         <v>45203</v>
       </c>
       <c r="D324" s="18">
-        <v>45198</v>
+        <v>45166</v>
       </c>
       <c r="E324" s="19" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="F324" s="19" t="s">
         <v>25</v>
       </c>
       <c r="G324" s="20">
-        <v>259</v>
+        <v>2</v>
       </c>
       <c r="H324" s="21" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
     </row>
     <row r="325" spans="1:8">
       <c r="A325" s="12" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="B325" s="13">
-        <v>45155</v>
+        <v>45166</v>
       </c>
       <c r="C325" s="13">
         <v>45203</v>
       </c>
       <c r="D325" s="13">
-        <v>45215</v>
+        <v>45166</v>
       </c>
       <c r="E325" s="14" t="s">
-        <v>514</v>
+        <v>503</v>
       </c>
       <c r="F325" s="14" t="s">
         <v>25</v>
       </c>
       <c r="G325" s="15">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="H325" s="16" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
     </row>
     <row r="326" spans="1:8">
       <c r="A326" s="17" t="s">
-        <v>255</v>
+        <v>36</v>
       </c>
       <c r="B326" s="18">
-        <v>45155</v>
+        <v>45166</v>
       </c>
       <c r="C326" s="18">
         <v>45203</v>
       </c>
       <c r="D326" s="18">
-        <v>45215</v>
+        <v>45166</v>
       </c>
       <c r="E326" s="19" t="s">
-        <v>514</v>
+        <v>503</v>
       </c>
       <c r="F326" s="19" t="s">
         <v>25</v>
       </c>
       <c r="G326" s="20">
-        <v>98</v>
+        <v>1</v>
       </c>
       <c r="H326" s="21" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
     </row>
     <row r="327" spans="1:8">
       <c r="A327" s="12" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="B327" s="13">
-        <v>45174</v>
+        <v>45170</v>
       </c>
       <c r="C327" s="13">
-        <v>45204</v>
+        <v>45203</v>
       </c>
       <c r="D327" s="13">
-        <v>45234</v>
+        <v>45291</v>
       </c>
       <c r="E327" s="14" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="F327" s="14" t="s">
         <v>39</v>
       </c>
       <c r="G327" s="15">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="H327" s="16" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
     </row>
     <row r="328" spans="1:8">
       <c r="A328" s="17" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="B328" s="18">
-        <v>45174</v>
+        <v>45198</v>
       </c>
       <c r="C328" s="18">
-        <v>45204</v>
+        <v>45203</v>
       </c>
       <c r="D328" s="18">
-        <v>45260</v>
+        <v>45198</v>
       </c>
       <c r="E328" s="19" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="F328" s="19" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="G328" s="20">
-        <v>4</v>
+        <v>259</v>
       </c>
       <c r="H328" s="21" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
     </row>
     <row r="329" spans="1:8">
       <c r="A329" s="12" t="s">
-        <v>93</v>
+        <v>31</v>
       </c>
       <c r="B329" s="13">
-        <v>45145</v>
+        <v>45155</v>
       </c>
       <c r="C329" s="13">
-        <v>45210</v>
+        <v>45203</v>
       </c>
       <c r="D329" s="13">
-        <v>45202</v>
+        <v>45215</v>
       </c>
       <c r="E329" s="14" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="F329" s="14" t="s">
         <v>25</v>
       </c>
       <c r="G329" s="15">
-        <v>58</v>
+        <v>13</v>
       </c>
       <c r="H329" s="16" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
     </row>
     <row r="330" spans="1:8">
       <c r="A330" s="17" t="s">
-        <v>49</v>
+        <v>255</v>
       </c>
       <c r="B330" s="18">
-        <v>45175</v>
+        <v>45155</v>
       </c>
       <c r="C330" s="18">
-        <v>45210</v>
+        <v>45203</v>
       </c>
       <c r="D330" s="18">
-        <v>45245</v>
+        <v>45215</v>
       </c>
       <c r="E330" s="19" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="F330" s="19" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="G330" s="20">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="H330" s="21" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
     </row>
     <row r="331" spans="1:8">
       <c r="A331" s="12" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="B331" s="13">
-        <v>45175</v>
+        <v>45174</v>
       </c>
       <c r="C331" s="13">
-        <v>45210</v>
+        <v>45204</v>
       </c>
       <c r="D331" s="13">
-        <v>45236</v>
+        <v>45234</v>
       </c>
       <c r="E331" s="14" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="F331" s="14" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="G331" s="15">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="H331" s="16" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
     </row>
     <row r="332" spans="1:8">
       <c r="A332" s="17" t="s">
-        <v>93</v>
+        <v>34</v>
       </c>
       <c r="B332" s="18">
-        <v>45175</v>
+        <v>45174</v>
       </c>
       <c r="C332" s="18">
-        <v>45212</v>
+        <v>45204</v>
       </c>
       <c r="D332" s="18">
-        <v>45231</v>
+        <v>45260</v>
       </c>
       <c r="E332" s="19" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="F332" s="19" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="G332" s="20">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H332" s="21" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
     </row>
     <row r="333" spans="1:8">
@@ -11645,25 +11825,25 @@
         <v>93</v>
       </c>
       <c r="B333" s="13">
-        <v>45180</v>
+        <v>45145</v>
       </c>
       <c r="C333" s="13">
-        <v>45212</v>
+        <v>45210</v>
       </c>
       <c r="D333" s="13">
-        <v>45240</v>
+        <v>45202</v>
       </c>
       <c r="E333" s="14" t="s">
-        <v>105</v>
+        <v>522</v>
       </c>
       <c r="F333" s="14" t="s">
         <v>25</v>
       </c>
       <c r="G333" s="15">
-        <v>140</v>
+        <v>58</v>
       </c>
       <c r="H333" s="16" t="s">
-        <v>150</v>
+        <v>523</v>
       </c>
     </row>
     <row r="334" spans="1:8">
@@ -11674,48 +11854,48 @@
         <v>45175</v>
       </c>
       <c r="C334" s="18">
-        <v>45212</v>
+        <v>45210</v>
       </c>
       <c r="D334" s="18">
-        <v>45233</v>
+        <v>45245</v>
       </c>
       <c r="E334" s="19" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="F334" s="19" t="s">
         <v>39</v>
       </c>
       <c r="G334" s="20">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="H334" s="21" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
     </row>
     <row r="335" spans="1:8">
       <c r="A335" s="12" t="s">
-        <v>104</v>
+        <v>49</v>
       </c>
       <c r="B335" s="13">
-        <v>45188</v>
+        <v>45175</v>
       </c>
       <c r="C335" s="13">
-        <v>45212</v>
+        <v>45210</v>
       </c>
       <c r="D335" s="13">
-        <v>45285</v>
+        <v>45236</v>
       </c>
       <c r="E335" s="14" t="s">
-        <v>105</v>
+        <v>526</v>
       </c>
       <c r="F335" s="14" t="s">
-        <v>106</v>
+        <v>25</v>
       </c>
       <c r="G335" s="15">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="H335" s="16" t="s">
-        <v>107</v>
+        <v>527</v>
       </c>
     </row>
     <row r="336" spans="1:8">
@@ -11723,25 +11903,25 @@
         <v>93</v>
       </c>
       <c r="B336" s="18">
-        <v>45148</v>
+        <v>45175</v>
       </c>
       <c r="C336" s="18">
-        <v>45215</v>
+        <v>45212</v>
       </c>
       <c r="D336" s="18">
-        <v>45208</v>
+        <v>45231</v>
       </c>
       <c r="E336" s="19" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="F336" s="19" t="s">
         <v>25</v>
       </c>
       <c r="G336" s="20">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H336" s="21" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
     </row>
     <row r="337" spans="1:8">
@@ -11749,77 +11929,77 @@
         <v>93</v>
       </c>
       <c r="B337" s="13">
-        <v>45148</v>
+        <v>45180</v>
       </c>
       <c r="C337" s="13">
-        <v>45215</v>
+        <v>45212</v>
       </c>
       <c r="D337" s="13">
-        <v>45208</v>
+        <v>45240</v>
       </c>
       <c r="E337" s="14" t="s">
-        <v>530</v>
+        <v>105</v>
       </c>
       <c r="F337" s="14" t="s">
         <v>25</v>
       </c>
       <c r="G337" s="15">
-        <v>1</v>
+        <v>140</v>
       </c>
       <c r="H337" s="16" t="s">
-        <v>532</v>
+        <v>150</v>
       </c>
     </row>
     <row r="338" spans="1:8">
       <c r="A338" s="17" t="s">
-        <v>93</v>
+        <v>49</v>
       </c>
       <c r="B338" s="18">
-        <v>45148</v>
+        <v>45175</v>
       </c>
       <c r="C338" s="18">
-        <v>45215</v>
+        <v>45212</v>
       </c>
       <c r="D338" s="18">
-        <v>45208</v>
+        <v>45233</v>
       </c>
       <c r="E338" s="19" t="s">
         <v>530</v>
       </c>
       <c r="F338" s="19" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="G338" s="20">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="H338" s="21" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
     </row>
     <row r="339" spans="1:8">
       <c r="A339" s="12" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="B339" s="13">
-        <v>45148</v>
+        <v>45188</v>
       </c>
       <c r="C339" s="13">
-        <v>45215</v>
+        <v>45212</v>
       </c>
       <c r="D339" s="13">
-        <v>45208</v>
+        <v>45285</v>
       </c>
       <c r="E339" s="14" t="s">
-        <v>530</v>
+        <v>105</v>
       </c>
       <c r="F339" s="14" t="s">
-        <v>25</v>
+        <v>106</v>
       </c>
       <c r="G339" s="15">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="H339" s="16" t="s">
-        <v>534</v>
+        <v>107</v>
       </c>
     </row>
     <row r="340" spans="1:8">
@@ -11836,7 +12016,7 @@
         <v>45208</v>
       </c>
       <c r="E340" s="19" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="F340" s="19" t="s">
         <v>25</v>
@@ -11845,12 +12025,12 @@
         <v>1</v>
       </c>
       <c r="H340" s="21" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
     </row>
     <row r="341" spans="1:8">
       <c r="A341" s="12" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="B341" s="13">
         <v>45148</v>
@@ -11862,7 +12042,7 @@
         <v>45208</v>
       </c>
       <c r="E341" s="14" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="F341" s="14" t="s">
         <v>25</v>
@@ -11871,12 +12051,12 @@
         <v>1</v>
       </c>
       <c r="H341" s="16" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
     </row>
     <row r="342" spans="1:8">
       <c r="A342" s="17" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="B342" s="18">
         <v>45148</v>
@@ -11888,21 +12068,21 @@
         <v>45208</v>
       </c>
       <c r="E342" s="19" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="F342" s="19" t="s">
         <v>25</v>
       </c>
       <c r="G342" s="20">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H342" s="21" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
     </row>
     <row r="343" spans="1:8">
       <c r="A343" s="12" t="s">
-        <v>23</v>
+        <v>93</v>
       </c>
       <c r="B343" s="13">
         <v>45148</v>
@@ -11914,7 +12094,7 @@
         <v>45208</v>
       </c>
       <c r="E343" s="14" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="F343" s="14" t="s">
         <v>25</v>
@@ -11923,12 +12103,12 @@
         <v>1</v>
       </c>
       <c r="H343" s="16" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
     </row>
     <row r="344" spans="1:8">
       <c r="A344" s="17" t="s">
-        <v>23</v>
+        <v>93</v>
       </c>
       <c r="B344" s="18">
         <v>45148</v>
@@ -11940,7 +12120,7 @@
         <v>45208</v>
       </c>
       <c r="E344" s="19" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="F344" s="19" t="s">
         <v>25</v>
@@ -11949,12 +12129,12 @@
         <v>1</v>
       </c>
       <c r="H344" s="21" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
     </row>
     <row r="345" spans="1:8">
       <c r="A345" s="12" t="s">
-        <v>23</v>
+        <v>72</v>
       </c>
       <c r="B345" s="13">
         <v>45148</v>
@@ -11966,21 +12146,21 @@
         <v>45208</v>
       </c>
       <c r="E345" s="14" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="F345" s="14" t="s">
         <v>25</v>
       </c>
       <c r="G345" s="15">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H345" s="16" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
     </row>
     <row r="346" spans="1:8">
       <c r="A346" s="17" t="s">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="B346" s="18">
         <v>45148</v>
@@ -11992,7 +12172,7 @@
         <v>45208</v>
       </c>
       <c r="E346" s="19" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="F346" s="19" t="s">
         <v>25</v>
@@ -12001,12 +12181,12 @@
         <v>4</v>
       </c>
       <c r="H346" s="21" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
     <row r="347" spans="1:8">
       <c r="A347" s="12" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B347" s="13">
         <v>45148</v>
@@ -12018,21 +12198,21 @@
         <v>45208</v>
       </c>
       <c r="E347" s="14" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="F347" s="14" t="s">
         <v>25</v>
       </c>
       <c r="G347" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H347" s="16" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
     </row>
     <row r="348" spans="1:8">
       <c r="A348" s="17" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="B348" s="18">
         <v>45148</v>
@@ -12044,7 +12224,7 @@
         <v>45208</v>
       </c>
       <c r="E348" s="19" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="F348" s="19" t="s">
         <v>25</v>
@@ -12053,12 +12233,12 @@
         <v>1</v>
       </c>
       <c r="H348" s="21" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
     </row>
     <row r="349" spans="1:8">
       <c r="A349" s="12" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="B349" s="13">
         <v>45148</v>
@@ -12070,16 +12250,16 @@
         <v>45208</v>
       </c>
       <c r="E349" s="14" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="F349" s="14" t="s">
         <v>25</v>
       </c>
       <c r="G349" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H349" s="16" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="350" spans="1:8">
@@ -12096,7 +12276,7 @@
         <v>45208</v>
       </c>
       <c r="E350" s="19" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="F350" s="19" t="s">
         <v>25</v>
@@ -12105,12 +12285,12 @@
         <v>4</v>
       </c>
       <c r="H350" s="21" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
     </row>
     <row r="351" spans="1:8">
       <c r="A351" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B351" s="13">
         <v>45148</v>
@@ -12122,7 +12302,7 @@
         <v>45208</v>
       </c>
       <c r="E351" s="14" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="F351" s="14" t="s">
         <v>25</v>
@@ -12131,7 +12311,7 @@
         <v>2</v>
       </c>
       <c r="H351" s="16" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
     </row>
     <row r="352" spans="1:8">
@@ -12148,7 +12328,7 @@
         <v>45208</v>
       </c>
       <c r="E352" s="19" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="F352" s="19" t="s">
         <v>25</v>
@@ -12157,7 +12337,7 @@
         <v>1</v>
       </c>
       <c r="H352" s="21" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
     </row>
     <row r="353" spans="1:8">
@@ -12174,16 +12354,16 @@
         <v>45208</v>
       </c>
       <c r="E353" s="14" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="F353" s="14" t="s">
         <v>25</v>
       </c>
       <c r="G353" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H353" s="16" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
     </row>
     <row r="354" spans="1:8">
@@ -12200,16 +12380,16 @@
         <v>45208</v>
       </c>
       <c r="E354" s="19" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="F354" s="19" t="s">
         <v>25</v>
       </c>
       <c r="G354" s="20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H354" s="21" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
     </row>
     <row r="355" spans="1:8">
@@ -12226,16 +12406,16 @@
         <v>45208</v>
       </c>
       <c r="E355" s="14" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="F355" s="14" t="s">
         <v>25</v>
       </c>
       <c r="G355" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H355" s="16" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
     </row>
     <row r="356" spans="1:8">
@@ -12252,16 +12432,1368 @@
         <v>45208</v>
       </c>
       <c r="E356" s="19" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="F356" s="19" t="s">
         <v>25</v>
       </c>
       <c r="G356" s="20">
+        <v>1</v>
+      </c>
+      <c r="H356" s="21" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="357" spans="1:8">
+      <c r="A357" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B357" s="13">
+        <v>45148</v>
+      </c>
+      <c r="C357" s="13">
+        <v>45215</v>
+      </c>
+      <c r="D357" s="13">
+        <v>45208</v>
+      </c>
+      <c r="E357" s="14" t="s">
+        <v>532</v>
+      </c>
+      <c r="F357" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G357" s="15">
+        <v>3</v>
+      </c>
+      <c r="H357" s="16" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="358" spans="1:8">
+      <c r="A358" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B358" s="18">
+        <v>45148</v>
+      </c>
+      <c r="C358" s="18">
+        <v>45215</v>
+      </c>
+      <c r="D358" s="18">
+        <v>45208</v>
+      </c>
+      <c r="E358" s="19" t="s">
+        <v>532</v>
+      </c>
+      <c r="F358" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="G358" s="20">
+        <v>3</v>
+      </c>
+      <c r="H358" s="21" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="359" spans="1:8">
+      <c r="A359" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B359" s="13">
+        <v>45148</v>
+      </c>
+      <c r="C359" s="13">
+        <v>45215</v>
+      </c>
+      <c r="D359" s="13">
+        <v>45208</v>
+      </c>
+      <c r="E359" s="14" t="s">
+        <v>532</v>
+      </c>
+      <c r="F359" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G359" s="15">
+        <v>3</v>
+      </c>
+      <c r="H359" s="16" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="360" spans="1:8">
+      <c r="A360" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B360" s="18">
+        <v>45148</v>
+      </c>
+      <c r="C360" s="18">
+        <v>45215</v>
+      </c>
+      <c r="D360" s="18">
+        <v>45208</v>
+      </c>
+      <c r="E360" s="19" t="s">
+        <v>532</v>
+      </c>
+      <c r="F360" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="G360" s="20">
         <v>5</v>
       </c>
-      <c r="H356" s="21" t="s">
-        <v>551</v>
+      <c r="H360" s="21" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="361" spans="1:8">
+      <c r="A361" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B361" s="13">
+        <v>45140</v>
+      </c>
+      <c r="C361" s="13">
+        <v>45216</v>
+      </c>
+      <c r="D361" s="13">
+        <v>45201</v>
+      </c>
+      <c r="E361" s="14" t="s">
+        <v>363</v>
+      </c>
+      <c r="F361" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G361" s="15">
+        <v>31</v>
+      </c>
+      <c r="H361" s="16" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="362" spans="1:8">
+      <c r="A362" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="B362" s="18">
+        <v>45140</v>
+      </c>
+      <c r="C362" s="18">
+        <v>45216</v>
+      </c>
+      <c r="D362" s="18">
+        <v>45201</v>
+      </c>
+      <c r="E362" s="19" t="s">
+        <v>555</v>
+      </c>
+      <c r="F362" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="G362" s="20">
+        <v>22</v>
+      </c>
+      <c r="H362" s="21" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="363" spans="1:8">
+      <c r="A363" s="12" t="s">
+        <v>287</v>
+      </c>
+      <c r="B363" s="13">
+        <v>45181</v>
+      </c>
+      <c r="C363" s="13">
+        <v>45216</v>
+      </c>
+      <c r="D363" s="13">
+        <v>45241</v>
+      </c>
+      <c r="E363" s="14" t="s">
+        <v>557</v>
+      </c>
+      <c r="F363" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="G363" s="15">
+        <v>1</v>
+      </c>
+      <c r="H363" s="16" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="364" spans="1:8">
+      <c r="A364" s="17" t="s">
+        <v>287</v>
+      </c>
+      <c r="B364" s="18">
+        <v>45181</v>
+      </c>
+      <c r="C364" s="18">
+        <v>45216</v>
+      </c>
+      <c r="D364" s="18">
+        <v>45241</v>
+      </c>
+      <c r="E364" s="19" t="s">
+        <v>557</v>
+      </c>
+      <c r="F364" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="G364" s="20">
+        <v>215</v>
+      </c>
+      <c r="H364" s="21" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="365" spans="1:8">
+      <c r="A365" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B365" s="13">
+        <v>45181</v>
+      </c>
+      <c r="C365" s="13">
+        <v>45217</v>
+      </c>
+      <c r="D365" s="13">
+        <v>45243</v>
+      </c>
+      <c r="E365" s="14" t="s">
+        <v>363</v>
+      </c>
+      <c r="F365" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G365" s="15">
+        <v>1</v>
+      </c>
+      <c r="H365" s="16" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="366" spans="1:8">
+      <c r="A366" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B366" s="18">
+        <v>45180</v>
+      </c>
+      <c r="C366" s="18">
+        <v>45217</v>
+      </c>
+      <c r="D366" s="18">
+        <v>45230</v>
+      </c>
+      <c r="E366" s="19" t="s">
+        <v>561</v>
+      </c>
+      <c r="F366" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="G366" s="20">
+        <v>100</v>
+      </c>
+      <c r="H366" s="21" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="367" spans="1:8">
+      <c r="A367" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B367" s="13">
+        <v>45180</v>
+      </c>
+      <c r="C367" s="13">
+        <v>45217</v>
+      </c>
+      <c r="D367" s="13">
+        <v>45230</v>
+      </c>
+      <c r="E367" s="14" t="s">
+        <v>563</v>
+      </c>
+      <c r="F367" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="G367" s="15">
+        <v>7</v>
+      </c>
+      <c r="H367" s="16" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="368" spans="1:8">
+      <c r="A368" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B368" s="18">
+        <v>45180</v>
+      </c>
+      <c r="C368" s="18">
+        <v>45217</v>
+      </c>
+      <c r="D368" s="18">
+        <v>45230</v>
+      </c>
+      <c r="E368" s="19" t="s">
+        <v>565</v>
+      </c>
+      <c r="F368" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="G368" s="20">
+        <v>9</v>
+      </c>
+      <c r="H368" s="21" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="369" spans="1:8">
+      <c r="A369" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B369" s="13">
+        <v>45180</v>
+      </c>
+      <c r="C369" s="13">
+        <v>45217</v>
+      </c>
+      <c r="D369" s="13">
+        <v>45230</v>
+      </c>
+      <c r="E369" s="14" t="s">
+        <v>567</v>
+      </c>
+      <c r="F369" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="G369" s="15">
+        <v>27</v>
+      </c>
+      <c r="H369" s="16" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="370" spans="1:8">
+      <c r="A370" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B370" s="18">
+        <v>45180</v>
+      </c>
+      <c r="C370" s="18">
+        <v>45217</v>
+      </c>
+      <c r="D370" s="18">
+        <v>45230</v>
+      </c>
+      <c r="E370" s="19" t="s">
+        <v>569</v>
+      </c>
+      <c r="F370" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="G370" s="20">
+        <v>44</v>
+      </c>
+      <c r="H370" s="21" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="371" spans="1:8">
+      <c r="A371" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B371" s="13">
+        <v>45181</v>
+      </c>
+      <c r="C371" s="13">
+        <v>45217</v>
+      </c>
+      <c r="D371" s="13">
+        <v>45243</v>
+      </c>
+      <c r="E371" s="14" t="s">
+        <v>363</v>
+      </c>
+      <c r="F371" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G371" s="15">
+        <v>3</v>
+      </c>
+      <c r="H371" s="16" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="372" spans="1:8">
+      <c r="A372" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B372" s="18">
+        <v>45181</v>
+      </c>
+      <c r="C372" s="18">
+        <v>45217</v>
+      </c>
+      <c r="D372" s="18">
+        <v>45243</v>
+      </c>
+      <c r="E372" s="19" t="s">
+        <v>363</v>
+      </c>
+      <c r="F372" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="G372" s="20">
+        <v>24</v>
+      </c>
+      <c r="H372" s="21" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="373" spans="1:8">
+      <c r="A373" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B373" s="13">
+        <v>45148</v>
+      </c>
+      <c r="C373" s="13">
+        <v>45217</v>
+      </c>
+      <c r="D373" s="13">
+        <v>45208</v>
+      </c>
+      <c r="E373" s="14" t="s">
+        <v>532</v>
+      </c>
+      <c r="F373" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G373" s="15">
+        <v>3</v>
+      </c>
+      <c r="H373" s="16" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="374" spans="1:8">
+      <c r="A374" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B374" s="18">
+        <v>45148</v>
+      </c>
+      <c r="C374" s="18">
+        <v>45217</v>
+      </c>
+      <c r="D374" s="18">
+        <v>45208</v>
+      </c>
+      <c r="E374" s="19" t="s">
+        <v>532</v>
+      </c>
+      <c r="F374" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="G374" s="20">
+        <v>3</v>
+      </c>
+      <c r="H374" s="21" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="375" spans="1:8">
+      <c r="A375" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B375" s="13">
+        <v>45148</v>
+      </c>
+      <c r="C375" s="13">
+        <v>45217</v>
+      </c>
+      <c r="D375" s="13">
+        <v>45208</v>
+      </c>
+      <c r="E375" s="14" t="s">
+        <v>532</v>
+      </c>
+      <c r="F375" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G375" s="15">
+        <v>3</v>
+      </c>
+      <c r="H375" s="16" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="376" spans="1:8">
+      <c r="A376" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B376" s="18">
+        <v>45183</v>
+      </c>
+      <c r="C376" s="18">
+        <v>45217</v>
+      </c>
+      <c r="D376" s="18">
+        <v>45243</v>
+      </c>
+      <c r="E376" s="19" t="s">
+        <v>576</v>
+      </c>
+      <c r="F376" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="G376" s="20">
+        <v>257</v>
+      </c>
+      <c r="H376" s="21" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="377" spans="1:8">
+      <c r="A377" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="B377" s="13">
+        <v>45148</v>
+      </c>
+      <c r="C377" s="13">
+        <v>45217</v>
+      </c>
+      <c r="D377" s="13">
+        <v>45208</v>
+      </c>
+      <c r="E377" s="14" t="s">
+        <v>532</v>
+      </c>
+      <c r="F377" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G377" s="15">
+        <v>2</v>
+      </c>
+      <c r="H377" s="16" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="378" spans="1:8">
+      <c r="A378" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="B378" s="18">
+        <v>45148</v>
+      </c>
+      <c r="C378" s="18">
+        <v>45217</v>
+      </c>
+      <c r="D378" s="18">
+        <v>45208</v>
+      </c>
+      <c r="E378" s="19" t="s">
+        <v>532</v>
+      </c>
+      <c r="F378" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="G378" s="20">
+        <v>8</v>
+      </c>
+      <c r="H378" s="21" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="379" spans="1:8">
+      <c r="A379" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="B379" s="13">
+        <v>45148</v>
+      </c>
+      <c r="C379" s="13">
+        <v>45217</v>
+      </c>
+      <c r="D379" s="13">
+        <v>45208</v>
+      </c>
+      <c r="E379" s="14" t="s">
+        <v>532</v>
+      </c>
+      <c r="F379" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G379" s="15">
+        <v>3</v>
+      </c>
+      <c r="H379" s="16" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="380" spans="1:8">
+      <c r="A380" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="B380" s="18">
+        <v>45148</v>
+      </c>
+      <c r="C380" s="18">
+        <v>45217</v>
+      </c>
+      <c r="D380" s="18">
+        <v>45208</v>
+      </c>
+      <c r="E380" s="19" t="s">
+        <v>532</v>
+      </c>
+      <c r="F380" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="G380" s="20">
+        <v>4</v>
+      </c>
+      <c r="H380" s="21" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="381" spans="1:8">
+      <c r="A381" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="B381" s="13">
+        <v>45148</v>
+      </c>
+      <c r="C381" s="13">
+        <v>45217</v>
+      </c>
+      <c r="D381" s="13">
+        <v>45208</v>
+      </c>
+      <c r="E381" s="14" t="s">
+        <v>532</v>
+      </c>
+      <c r="F381" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G381" s="15">
+        <v>2</v>
+      </c>
+      <c r="H381" s="16" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="382" spans="1:8">
+      <c r="A382" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="B382" s="18">
+        <v>45148</v>
+      </c>
+      <c r="C382" s="18">
+        <v>45217</v>
+      </c>
+      <c r="D382" s="18">
+        <v>45208</v>
+      </c>
+      <c r="E382" s="19" t="s">
+        <v>532</v>
+      </c>
+      <c r="F382" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="G382" s="20">
+        <v>12</v>
+      </c>
+      <c r="H382" s="21" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="383" spans="1:8">
+      <c r="A383" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="B383" s="13">
+        <v>45148</v>
+      </c>
+      <c r="C383" s="13">
+        <v>45217</v>
+      </c>
+      <c r="D383" s="13">
+        <v>45208</v>
+      </c>
+      <c r="E383" s="14" t="s">
+        <v>532</v>
+      </c>
+      <c r="F383" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G383" s="15">
+        <v>9</v>
+      </c>
+      <c r="H383" s="16" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="384" spans="1:8">
+      <c r="A384" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="B384" s="18">
+        <v>45148</v>
+      </c>
+      <c r="C384" s="18">
+        <v>45217</v>
+      </c>
+      <c r="D384" s="18">
+        <v>45208</v>
+      </c>
+      <c r="E384" s="19" t="s">
+        <v>532</v>
+      </c>
+      <c r="F384" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="G384" s="20">
+        <v>9</v>
+      </c>
+      <c r="H384" s="21" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="385" spans="1:8">
+      <c r="A385" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="B385" s="13">
+        <v>45148</v>
+      </c>
+      <c r="C385" s="13">
+        <v>45217</v>
+      </c>
+      <c r="D385" s="13">
+        <v>45208</v>
+      </c>
+      <c r="E385" s="14" t="s">
+        <v>532</v>
+      </c>
+      <c r="F385" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G385" s="15">
+        <v>2</v>
+      </c>
+      <c r="H385" s="16" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="386" spans="1:8">
+      <c r="A386" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="B386" s="18">
+        <v>45148</v>
+      </c>
+      <c r="C386" s="18">
+        <v>45217</v>
+      </c>
+      <c r="D386" s="18">
+        <v>45208</v>
+      </c>
+      <c r="E386" s="19" t="s">
+        <v>532</v>
+      </c>
+      <c r="F386" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="G386" s="20">
+        <v>2</v>
+      </c>
+      <c r="H386" s="21" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="387" spans="1:8">
+      <c r="A387" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B387" s="13">
+        <v>45148</v>
+      </c>
+      <c r="C387" s="13">
+        <v>45217</v>
+      </c>
+      <c r="D387" s="13">
+        <v>45208</v>
+      </c>
+      <c r="E387" s="14" t="s">
+        <v>532</v>
+      </c>
+      <c r="F387" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G387" s="15">
+        <v>2</v>
+      </c>
+      <c r="H387" s="16" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="388" spans="1:8">
+      <c r="A388" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="B388" s="18">
+        <v>45148</v>
+      </c>
+      <c r="C388" s="18">
+        <v>45217</v>
+      </c>
+      <c r="D388" s="18">
+        <v>45208</v>
+      </c>
+      <c r="E388" s="19" t="s">
+        <v>532</v>
+      </c>
+      <c r="F388" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="G388" s="20">
+        <v>2</v>
+      </c>
+      <c r="H388" s="21" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="389" spans="1:8">
+      <c r="A389" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B389" s="13">
+        <v>45148</v>
+      </c>
+      <c r="C389" s="13">
+        <v>45217</v>
+      </c>
+      <c r="D389" s="13">
+        <v>45208</v>
+      </c>
+      <c r="E389" s="14" t="s">
+        <v>532</v>
+      </c>
+      <c r="F389" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G389" s="15">
+        <v>3</v>
+      </c>
+      <c r="H389" s="16" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="390" spans="1:8">
+      <c r="A390" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="B390" s="18">
+        <v>45148</v>
+      </c>
+      <c r="C390" s="18">
+        <v>45217</v>
+      </c>
+      <c r="D390" s="18">
+        <v>45208</v>
+      </c>
+      <c r="E390" s="19" t="s">
+        <v>532</v>
+      </c>
+      <c r="F390" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="G390" s="20">
+        <v>1</v>
+      </c>
+      <c r="H390" s="21" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="391" spans="1:8">
+      <c r="A391" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B391" s="13">
+        <v>45148</v>
+      </c>
+      <c r="C391" s="13">
+        <v>45217</v>
+      </c>
+      <c r="D391" s="13">
+        <v>45208</v>
+      </c>
+      <c r="E391" s="14" t="s">
+        <v>532</v>
+      </c>
+      <c r="F391" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G391" s="15">
+        <v>2</v>
+      </c>
+      <c r="H391" s="16" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="392" spans="1:8">
+      <c r="A392" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="B392" s="18">
+        <v>45148</v>
+      </c>
+      <c r="C392" s="18">
+        <v>45217</v>
+      </c>
+      <c r="D392" s="18">
+        <v>45208</v>
+      </c>
+      <c r="E392" s="19" t="s">
+        <v>532</v>
+      </c>
+      <c r="F392" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="G392" s="20">
+        <v>1</v>
+      </c>
+      <c r="H392" s="21" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="393" spans="1:8">
+      <c r="A393" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="B393" s="13">
+        <v>45148</v>
+      </c>
+      <c r="C393" s="13">
+        <v>45217</v>
+      </c>
+      <c r="D393" s="13">
+        <v>45208</v>
+      </c>
+      <c r="E393" s="14" t="s">
+        <v>532</v>
+      </c>
+      <c r="F393" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G393" s="15">
+        <v>3</v>
+      </c>
+      <c r="H393" s="16" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="394" spans="1:8">
+      <c r="A394" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="B394" s="18">
+        <v>45180</v>
+      </c>
+      <c r="C394" s="18">
+        <v>45217</v>
+      </c>
+      <c r="D394" s="18">
+        <v>45230</v>
+      </c>
+      <c r="E394" s="19" t="s">
+        <v>595</v>
+      </c>
+      <c r="F394" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="G394" s="20">
+        <v>61</v>
+      </c>
+      <c r="H394" s="21" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="395" spans="1:8">
+      <c r="A395" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="B395" s="13">
+        <v>45148</v>
+      </c>
+      <c r="C395" s="13">
+        <v>45217</v>
+      </c>
+      <c r="D395" s="13">
+        <v>45208</v>
+      </c>
+      <c r="E395" s="14" t="s">
+        <v>532</v>
+      </c>
+      <c r="F395" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G395" s="15">
+        <v>5</v>
+      </c>
+      <c r="H395" s="16" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="396" spans="1:8">
+      <c r="A396" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="B396" s="18">
+        <v>45181</v>
+      </c>
+      <c r="C396" s="18">
+        <v>45217</v>
+      </c>
+      <c r="D396" s="18">
+        <v>45243</v>
+      </c>
+      <c r="E396" s="19" t="s">
+        <v>363</v>
+      </c>
+      <c r="F396" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="G396" s="20">
+        <v>39</v>
+      </c>
+      <c r="H396" s="21" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="397" spans="1:8">
+      <c r="A397" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B397" s="13">
+        <v>45148</v>
+      </c>
+      <c r="C397" s="13">
+        <v>45217</v>
+      </c>
+      <c r="D397" s="13">
+        <v>45208</v>
+      </c>
+      <c r="E397" s="14" t="s">
+        <v>532</v>
+      </c>
+      <c r="F397" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G397" s="15">
+        <v>11</v>
+      </c>
+      <c r="H397" s="16" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="398" spans="1:8">
+      <c r="A398" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="B398" s="18">
+        <v>45148</v>
+      </c>
+      <c r="C398" s="18">
+        <v>45217</v>
+      </c>
+      <c r="D398" s="18">
+        <v>45208</v>
+      </c>
+      <c r="E398" s="19" t="s">
+        <v>532</v>
+      </c>
+      <c r="F398" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="G398" s="20">
+        <v>6</v>
+      </c>
+      <c r="H398" s="21" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="399" spans="1:8">
+      <c r="A399" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="B399" s="13">
+        <v>45176</v>
+      </c>
+      <c r="C399" s="13">
+        <v>45217</v>
+      </c>
+      <c r="D399" s="13">
+        <v>45237</v>
+      </c>
+      <c r="E399" s="14" t="s">
+        <v>601</v>
+      </c>
+      <c r="F399" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G399" s="15">
+        <v>95</v>
+      </c>
+      <c r="H399" s="16" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="400" spans="1:8">
+      <c r="A400" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="B400" s="18">
+        <v>45181</v>
+      </c>
+      <c r="C400" s="18">
+        <v>45217</v>
+      </c>
+      <c r="D400" s="18">
+        <v>45243</v>
+      </c>
+      <c r="E400" s="19" t="s">
+        <v>363</v>
+      </c>
+      <c r="F400" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="G400" s="20">
+        <v>31</v>
+      </c>
+      <c r="H400" s="21" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="401" spans="1:8">
+      <c r="A401" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="B401" s="13">
+        <v>45148</v>
+      </c>
+      <c r="C401" s="13">
+        <v>45217</v>
+      </c>
+      <c r="D401" s="13">
+        <v>45208</v>
+      </c>
+      <c r="E401" s="14" t="s">
+        <v>532</v>
+      </c>
+      <c r="F401" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G401" s="15">
+        <v>18</v>
+      </c>
+      <c r="H401" s="16" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="402" spans="1:8">
+      <c r="A402" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="B402" s="18">
+        <v>45148</v>
+      </c>
+      <c r="C402" s="18">
+        <v>45217</v>
+      </c>
+      <c r="D402" s="18">
+        <v>45208</v>
+      </c>
+      <c r="E402" s="19" t="s">
+        <v>532</v>
+      </c>
+      <c r="F402" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="G402" s="20">
+        <v>2</v>
+      </c>
+      <c r="H402" s="21" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="403" spans="1:8">
+      <c r="A403" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B403" s="13">
+        <v>45148</v>
+      </c>
+      <c r="C403" s="13">
+        <v>45217</v>
+      </c>
+      <c r="D403" s="13">
+        <v>45208</v>
+      </c>
+      <c r="E403" s="14" t="s">
+        <v>532</v>
+      </c>
+      <c r="F403" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G403" s="15">
+        <v>3</v>
+      </c>
+      <c r="H403" s="16" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="404" spans="1:8">
+      <c r="A404" s="17" t="s">
+        <v>215</v>
+      </c>
+      <c r="B404" s="18">
+        <v>45148</v>
+      </c>
+      <c r="C404" s="18">
+        <v>45217</v>
+      </c>
+      <c r="D404" s="18">
+        <v>45208</v>
+      </c>
+      <c r="E404" s="19" t="s">
+        <v>532</v>
+      </c>
+      <c r="F404" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="G404" s="20">
+        <v>12</v>
+      </c>
+      <c r="H404" s="21" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="405" spans="1:8">
+      <c r="A405" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B405" s="13">
+        <v>45148</v>
+      </c>
+      <c r="C405" s="13">
+        <v>45217</v>
+      </c>
+      <c r="D405" s="13">
+        <v>45208</v>
+      </c>
+      <c r="E405" s="14" t="s">
+        <v>532</v>
+      </c>
+      <c r="F405" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G405" s="15">
+        <v>1</v>
+      </c>
+      <c r="H405" s="16" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="406" spans="1:8">
+      <c r="A406" s="17" t="s">
+        <v>285</v>
+      </c>
+      <c r="B406" s="18">
+        <v>45148</v>
+      </c>
+      <c r="C406" s="18">
+        <v>45217</v>
+      </c>
+      <c r="D406" s="18">
+        <v>45208</v>
+      </c>
+      <c r="E406" s="19" t="s">
+        <v>532</v>
+      </c>
+      <c r="F406" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="G406" s="20">
+        <v>10</v>
+      </c>
+      <c r="H406" s="21" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="407" spans="1:8">
+      <c r="A407" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="B407" s="13">
+        <v>45148</v>
+      </c>
+      <c r="C407" s="13">
+        <v>45217</v>
+      </c>
+      <c r="D407" s="13">
+        <v>45208</v>
+      </c>
+      <c r="E407" s="14" t="s">
+        <v>532</v>
+      </c>
+      <c r="F407" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G407" s="15">
+        <v>2</v>
+      </c>
+      <c r="H407" s="16" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="408" spans="1:8">
+      <c r="A408" s="17" t="s">
+        <v>305</v>
+      </c>
+      <c r="B408" s="18">
+        <v>45148</v>
+      </c>
+      <c r="C408" s="18">
+        <v>45217</v>
+      </c>
+      <c r="D408" s="18">
+        <v>45208</v>
+      </c>
+      <c r="E408" s="19" t="s">
+        <v>532</v>
+      </c>
+      <c r="F408" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="G408" s="20">
+        <v>3</v>
+      </c>
+      <c r="H408" s="21" t="s">
+        <v>611</v>
       </c>
     </row>
   </sheetData>
@@ -12403,13 +13935,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1243B619-7504-40D8-9063-D2630197E4F3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0547CBF0-1BAF-4A60-A761-FFE25F3D6445}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C7975F10-3C2E-4620-9D1B-9D0C1B53DD7C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1143DF19-6DE9-4999-9184-AE0DB370768D}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8058A2E8-9B7B-485B-BC8F-D2C84FE9DB03}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED512A25-1FBF-419B-AB02-EB74E9A5CFFE}"/>
 </file>
--- a/data/warn-scraper/cache/ca/warn_report1.xlsx
+++ b/data/warn-scraper/cache/ca/warn_report1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\WSB-CO\Communications Unit\Website Management\WARN (Worker Adjustment and Retraining Notification) Updates\2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A42E3C1C-6FBC-454B-9527-9C185A042B60}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{99CB9904-488B-4205-9325-7024921D333A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="29895" yWindow="1230" windowWidth="21600" windowHeight="11430" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1647" uniqueCount="612">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1723" uniqueCount="645">
   <si>
     <t>This worksheet contains 3 sheets. The introductory page, WARN Report Summary, and Detailed WARN Report. The second sheet provides an overview of the report according to layoff/closure types and related quantitative data. The third sheet displays a detailed summary report of affected companies by county. This Daily WARN Report is updated every Tuesday and Thursday. Hyperlinks to the other 2 sheets can be found below in cell A3-A4.</t>
   </si>
@@ -103,7 +103,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>07/01/23 to 10/18/23</t>
+      <t>07/01/23 to 10/23/23</t>
     </r>
     <r>
       <rPr>
@@ -123,7 +123,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>A detailed WARN summary by county and filtered according to received date. Table Spans cells A2 through H408.</t>
+      <t>A detailed WARN summary by county and filtered according to received date. Table Spans cells A2 through H427.</t>
     </r>
   </si>
   <si>
@@ -1802,6 +1802,9 @@
     <t>1686 E. Beamer Street  Woodland CA 95776</t>
   </si>
   <si>
+    <t>LEER Group - 1242</t>
+  </si>
+  <si>
     <t>1242 E. Beamer Street  Woodland CA 95776</t>
   </si>
   <si>
@@ -1959,6 +1962,102 @@
   </si>
   <si>
     <t>411 3rd St  San Rafael CA 94901</t>
+  </si>
+  <si>
+    <t>Bamboo Group Operations LLC dba Bamboo Sushi</t>
+  </si>
+  <si>
+    <t>2855 Stevens Creek Blvd.  Santa Clara CA 95050</t>
+  </si>
+  <si>
+    <t>B. Braun Medical Inc.</t>
+  </si>
+  <si>
+    <t>2525 McGaw Avenue  Irvine CA 92614</t>
+  </si>
+  <si>
+    <t>Container Connection</t>
+  </si>
+  <si>
+    <t>14575 Innovation Dr.  Riverside CA 92508</t>
+  </si>
+  <si>
+    <t>Formagrid Inc. dba Airtable</t>
+  </si>
+  <si>
+    <t>799 Market Street, 8th Floor  San Francisco CA 94103</t>
+  </si>
+  <si>
+    <t>Pacific Coast Sightseeing Tours &amp; Charters, Inc.</t>
+  </si>
+  <si>
+    <t>2001 S. Manchester Avenue  Anaheim CA 92802</t>
+  </si>
+  <si>
+    <t>Federal Express Corporation</t>
+  </si>
+  <si>
+    <t>7401 World Way West  Los Angeles CA 90045</t>
+  </si>
+  <si>
+    <t>Niagara Bottling LLC</t>
+  </si>
+  <si>
+    <t>1440 Bridgegate Drive  Diamond Bar CA 91765</t>
+  </si>
+  <si>
+    <t>Shaw Industries Group Inc. Plant WG</t>
+  </si>
+  <si>
+    <t>15305 Valley View Drive  Santa Fe Springs CA 90670</t>
+  </si>
+  <si>
+    <t>Phillips Tool &amp; Die, Inc. dba Busy Bee Tooling</t>
+  </si>
+  <si>
+    <t>1620 Marigold Place  Ontario CA 91761</t>
+  </si>
+  <si>
+    <t>Bloom Energy Corporation</t>
+  </si>
+  <si>
+    <t>44408 Pacific Commons  Fremont CA 94538</t>
+  </si>
+  <si>
+    <t>44370 Christy Street  Fremont CA 94538</t>
+  </si>
+  <si>
+    <t>City National Bank</t>
+  </si>
+  <si>
+    <t>555 S. Flower Street  Los Angeles CA 90071</t>
+  </si>
+  <si>
+    <t>350 S. Grand Ave  Los Angeles CA 90071</t>
+  </si>
+  <si>
+    <t>1801 W. Olympic Boulevard  Los Angeles CA 90006</t>
+  </si>
+  <si>
+    <t>Cacique Foods, LLC</t>
+  </si>
+  <si>
+    <t>14940 Proctor Ave  City of Industry CA 91746</t>
+  </si>
+  <si>
+    <t>5303 Rivergrade Rd  Irwindale CA 91706</t>
+  </si>
+  <si>
+    <t>1252 Orleans Drive  Sunnyvale CA 94089</t>
+  </si>
+  <si>
+    <t>Cummins Meritor</t>
+  </si>
+  <si>
+    <t>2415 Auto Parkway  Escondido CA 92029</t>
+  </si>
+  <si>
+    <t>2057 Aldergrove Ave.  Escondido CA 92029</t>
   </si>
 </sst>
 </file>
@@ -2740,8 +2839,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:H408" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="9" tableBorderDxfId="10" totalsRowBorderDxfId="8">
-  <autoFilter ref="A2:H408" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:H427" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="9" tableBorderDxfId="10" totalsRowBorderDxfId="8">
+  <autoFilter ref="A2:H427" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -3125,7 +3224,7 @@
       </c>
       <c r="B3" s="5">
         <f>SUM('Detailed WARN Report '!G:G)</f>
-        <v>17503</v>
+        <v>18951</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -3134,7 +3233,7 @@
       </c>
       <c r="B4" s="5">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Permanent")</f>
-        <v>265</v>
+        <v>278</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -3161,7 +3260,7 @@
       </c>
       <c r="B7" s="5">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Permanent")</f>
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -3193,7 +3292,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:H408"/>
+  <dimension ref="A1:H427"/>
   <sheetFormatPr defaultColWidth="26" defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="25.85546875" bestFit="1" customWidth="1"/>
@@ -12611,7 +12710,7 @@
         <v>45216</v>
       </c>
       <c r="D363" s="13">
-        <v>45241</v>
+        <v>45243</v>
       </c>
       <c r="E363" s="14" t="s">
         <v>557</v>
@@ -12620,7 +12719,7 @@
         <v>39</v>
       </c>
       <c r="G363" s="15">
-        <v>1</v>
+        <v>122</v>
       </c>
       <c r="H363" s="16" t="s">
         <v>558</v>
@@ -12637,19 +12736,19 @@
         <v>45216</v>
       </c>
       <c r="D364" s="18">
-        <v>45241</v>
+        <v>45243</v>
       </c>
       <c r="E364" s="19" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="F364" s="19" t="s">
         <v>39</v>
       </c>
       <c r="G364" s="20">
-        <v>215</v>
+        <v>27</v>
       </c>
       <c r="H364" s="21" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="365" spans="1:8">
@@ -12675,7 +12774,7 @@
         <v>1</v>
       </c>
       <c r="H365" s="16" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="366" spans="1:8">
@@ -12692,7 +12791,7 @@
         <v>45230</v>
       </c>
       <c r="E366" s="19" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="F366" s="19" t="s">
         <v>39</v>
@@ -12701,7 +12800,7 @@
         <v>100</v>
       </c>
       <c r="H366" s="21" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="367" spans="1:8">
@@ -12718,7 +12817,7 @@
         <v>45230</v>
       </c>
       <c r="E367" s="14" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="F367" s="14" t="s">
         <v>39</v>
@@ -12727,7 +12826,7 @@
         <v>7</v>
       </c>
       <c r="H367" s="16" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="368" spans="1:8">
@@ -12744,7 +12843,7 @@
         <v>45230</v>
       </c>
       <c r="E368" s="19" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="F368" s="19" t="s">
         <v>39</v>
@@ -12753,7 +12852,7 @@
         <v>9</v>
       </c>
       <c r="H368" s="21" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="369" spans="1:8">
@@ -12770,7 +12869,7 @@
         <v>45230</v>
       </c>
       <c r="E369" s="14" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F369" s="14" t="s">
         <v>39</v>
@@ -12779,7 +12878,7 @@
         <v>27</v>
       </c>
       <c r="H369" s="16" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="370" spans="1:8">
@@ -12796,7 +12895,7 @@
         <v>45230</v>
       </c>
       <c r="E370" s="19" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="F370" s="19" t="s">
         <v>39</v>
@@ -12805,7 +12904,7 @@
         <v>44</v>
       </c>
       <c r="H370" s="21" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="371" spans="1:8">
@@ -12831,7 +12930,7 @@
         <v>3</v>
       </c>
       <c r="H371" s="16" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="372" spans="1:8">
@@ -12857,7 +12956,7 @@
         <v>24</v>
       </c>
       <c r="H372" s="21" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="373" spans="1:8">
@@ -12883,7 +12982,7 @@
         <v>3</v>
       </c>
       <c r="H373" s="16" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="374" spans="1:8">
@@ -12909,7 +13008,7 @@
         <v>3</v>
       </c>
       <c r="H374" s="21" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="375" spans="1:8">
@@ -12935,7 +13034,7 @@
         <v>3</v>
       </c>
       <c r="H375" s="16" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="376" spans="1:8">
@@ -12952,7 +13051,7 @@
         <v>45243</v>
       </c>
       <c r="E376" s="19" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="F376" s="19" t="s">
         <v>39</v>
@@ -12961,7 +13060,7 @@
         <v>257</v>
       </c>
       <c r="H376" s="21" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="377" spans="1:8">
@@ -12987,7 +13086,7 @@
         <v>2</v>
       </c>
       <c r="H377" s="16" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="378" spans="1:8">
@@ -13013,7 +13112,7 @@
         <v>8</v>
       </c>
       <c r="H378" s="21" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="379" spans="1:8">
@@ -13039,7 +13138,7 @@
         <v>3</v>
       </c>
       <c r="H379" s="16" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="380" spans="1:8">
@@ -13065,7 +13164,7 @@
         <v>4</v>
       </c>
       <c r="H380" s="21" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="381" spans="1:8">
@@ -13091,7 +13190,7 @@
         <v>2</v>
       </c>
       <c r="H381" s="16" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="382" spans="1:8">
@@ -13117,7 +13216,7 @@
         <v>12</v>
       </c>
       <c r="H382" s="21" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="383" spans="1:8">
@@ -13143,7 +13242,7 @@
         <v>9</v>
       </c>
       <c r="H383" s="16" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="384" spans="1:8">
@@ -13169,7 +13268,7 @@
         <v>9</v>
       </c>
       <c r="H384" s="21" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="385" spans="1:8">
@@ -13195,7 +13294,7 @@
         <v>2</v>
       </c>
       <c r="H385" s="16" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="386" spans="1:8">
@@ -13221,7 +13320,7 @@
         <v>2</v>
       </c>
       <c r="H386" s="21" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="387" spans="1:8">
@@ -13247,7 +13346,7 @@
         <v>2</v>
       </c>
       <c r="H387" s="16" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="388" spans="1:8">
@@ -13273,7 +13372,7 @@
         <v>2</v>
       </c>
       <c r="H388" s="21" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="389" spans="1:8">
@@ -13299,7 +13398,7 @@
         <v>3</v>
       </c>
       <c r="H389" s="16" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="390" spans="1:8">
@@ -13325,7 +13424,7 @@
         <v>1</v>
       </c>
       <c r="H390" s="21" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="391" spans="1:8">
@@ -13351,7 +13450,7 @@
         <v>2</v>
       </c>
       <c r="H391" s="16" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="392" spans="1:8">
@@ -13377,7 +13476,7 @@
         <v>1</v>
       </c>
       <c r="H392" s="21" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="393" spans="1:8">
@@ -13403,7 +13502,7 @@
         <v>3</v>
       </c>
       <c r="H393" s="16" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="394" spans="1:8">
@@ -13420,7 +13519,7 @@
         <v>45230</v>
       </c>
       <c r="E394" s="19" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="F394" s="19" t="s">
         <v>39</v>
@@ -13429,7 +13528,7 @@
         <v>61</v>
       </c>
       <c r="H394" s="21" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="395" spans="1:8">
@@ -13455,7 +13554,7 @@
         <v>5</v>
       </c>
       <c r="H395" s="16" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="396" spans="1:8">
@@ -13481,7 +13580,7 @@
         <v>39</v>
       </c>
       <c r="H396" s="21" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="397" spans="1:8">
@@ -13507,7 +13606,7 @@
         <v>11</v>
       </c>
       <c r="H397" s="16" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="398" spans="1:8">
@@ -13533,7 +13632,7 @@
         <v>6</v>
       </c>
       <c r="H398" s="21" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="399" spans="1:8">
@@ -13550,7 +13649,7 @@
         <v>45237</v>
       </c>
       <c r="E399" s="14" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="F399" s="14" t="s">
         <v>25</v>
@@ -13559,7 +13658,7 @@
         <v>95</v>
       </c>
       <c r="H399" s="16" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="400" spans="1:8">
@@ -13585,7 +13684,7 @@
         <v>31</v>
       </c>
       <c r="H400" s="21" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="401" spans="1:8">
@@ -13611,7 +13710,7 @@
         <v>18</v>
       </c>
       <c r="H401" s="16" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="402" spans="1:8">
@@ -13637,7 +13736,7 @@
         <v>2</v>
       </c>
       <c r="H402" s="21" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="403" spans="1:8">
@@ -13663,7 +13762,7 @@
         <v>3</v>
       </c>
       <c r="H403" s="16" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="404" spans="1:8">
@@ -13689,7 +13788,7 @@
         <v>12</v>
       </c>
       <c r="H404" s="21" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="405" spans="1:8">
@@ -13715,7 +13814,7 @@
         <v>1</v>
       </c>
       <c r="H405" s="16" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="406" spans="1:8">
@@ -13741,7 +13840,7 @@
         <v>10</v>
       </c>
       <c r="H406" s="21" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="407" spans="1:8">
@@ -13767,7 +13866,7 @@
         <v>2</v>
       </c>
       <c r="H407" s="16" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="408" spans="1:8">
@@ -13793,7 +13892,501 @@
         <v>3</v>
       </c>
       <c r="H408" s="21" t="s">
-        <v>611</v>
+        <v>612</v>
+      </c>
+    </row>
+    <row r="409" spans="1:8">
+      <c r="A409" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="B409" s="13">
+        <v>45183</v>
+      </c>
+      <c r="C409" s="13">
+        <v>45218</v>
+      </c>
+      <c r="D409" s="13">
+        <v>45243</v>
+      </c>
+      <c r="E409" s="14" t="s">
+        <v>613</v>
+      </c>
+      <c r="F409" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="G409" s="15">
+        <v>49</v>
+      </c>
+      <c r="H409" s="16" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="410" spans="1:8">
+      <c r="A410" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="B410" s="18">
+        <v>45183</v>
+      </c>
+      <c r="C410" s="18">
+        <v>45218</v>
+      </c>
+      <c r="D410" s="18">
+        <v>45243</v>
+      </c>
+      <c r="E410" s="19" t="s">
+        <v>615</v>
+      </c>
+      <c r="F410" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="G410" s="20">
+        <v>70</v>
+      </c>
+      <c r="H410" s="21" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="411" spans="1:8">
+      <c r="A411" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B411" s="13">
+        <v>45183</v>
+      </c>
+      <c r="C411" s="13">
+        <v>45218</v>
+      </c>
+      <c r="D411" s="13">
+        <v>45252</v>
+      </c>
+      <c r="E411" s="14" t="s">
+        <v>617</v>
+      </c>
+      <c r="F411" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G411" s="15">
+        <v>64</v>
+      </c>
+      <c r="H411" s="16" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="412" spans="1:8">
+      <c r="A412" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="B412" s="18">
+        <v>45183</v>
+      </c>
+      <c r="C412" s="18">
+        <v>45218</v>
+      </c>
+      <c r="D412" s="18">
+        <v>45184</v>
+      </c>
+      <c r="E412" s="19" t="s">
+        <v>619</v>
+      </c>
+      <c r="F412" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="G412" s="20">
+        <v>99</v>
+      </c>
+      <c r="H412" s="21" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="413" spans="1:8">
+      <c r="A413" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="B413" s="13">
+        <v>45183</v>
+      </c>
+      <c r="C413" s="13">
+        <v>45219</v>
+      </c>
+      <c r="D413" s="13">
+        <v>45243</v>
+      </c>
+      <c r="E413" s="14" t="s">
+        <v>621</v>
+      </c>
+      <c r="F413" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G413" s="15">
+        <v>68</v>
+      </c>
+      <c r="H413" s="16" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="414" spans="1:8">
+      <c r="A414" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B414" s="18">
+        <v>45184</v>
+      </c>
+      <c r="C414" s="18">
+        <v>45219</v>
+      </c>
+      <c r="D414" s="18">
+        <v>45245</v>
+      </c>
+      <c r="E414" s="19" t="s">
+        <v>623</v>
+      </c>
+      <c r="F414" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="G414" s="20">
+        <v>405</v>
+      </c>
+      <c r="H414" s="21" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="415" spans="1:8">
+      <c r="A415" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B415" s="13">
+        <v>45184</v>
+      </c>
+      <c r="C415" s="13">
+        <v>45219</v>
+      </c>
+      <c r="D415" s="13">
+        <v>45245</v>
+      </c>
+      <c r="E415" s="14" t="s">
+        <v>625</v>
+      </c>
+      <c r="F415" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G415" s="15">
+        <v>111</v>
+      </c>
+      <c r="H415" s="16" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="416" spans="1:8">
+      <c r="A416" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B416" s="18">
+        <v>45188</v>
+      </c>
+      <c r="C416" s="18">
+        <v>45219</v>
+      </c>
+      <c r="D416" s="18">
+        <v>45250</v>
+      </c>
+      <c r="E416" s="19" t="s">
+        <v>627</v>
+      </c>
+      <c r="F416" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="G416" s="20">
+        <v>283</v>
+      </c>
+      <c r="H416" s="21" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="417" spans="1:8">
+      <c r="A417" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="B417" s="13">
+        <v>45183</v>
+      </c>
+      <c r="C417" s="13">
+        <v>45219</v>
+      </c>
+      <c r="D417" s="13">
+        <v>45272</v>
+      </c>
+      <c r="E417" s="14" t="s">
+        <v>629</v>
+      </c>
+      <c r="F417" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="G417" s="15">
+        <v>7</v>
+      </c>
+      <c r="H417" s="16" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="418" spans="1:8">
+      <c r="A418" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="B418" s="18">
+        <v>45185</v>
+      </c>
+      <c r="C418" s="18">
+        <v>45222</v>
+      </c>
+      <c r="D418" s="18">
+        <v>45185</v>
+      </c>
+      <c r="E418" s="19" t="s">
+        <v>631</v>
+      </c>
+      <c r="F418" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="G418" s="20">
+        <v>34</v>
+      </c>
+      <c r="H418" s="21" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="419" spans="1:8">
+      <c r="A419" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="B419" s="13">
+        <v>45185</v>
+      </c>
+      <c r="C419" s="13">
+        <v>45222</v>
+      </c>
+      <c r="D419" s="13">
+        <v>45185</v>
+      </c>
+      <c r="E419" s="14" t="s">
+        <v>631</v>
+      </c>
+      <c r="F419" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G419" s="15">
+        <v>1</v>
+      </c>
+      <c r="H419" s="16" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="420" spans="1:8">
+      <c r="A420" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B420" s="18">
+        <v>45182</v>
+      </c>
+      <c r="C420" s="18">
+        <v>45222</v>
+      </c>
+      <c r="D420" s="18">
+        <v>45245</v>
+      </c>
+      <c r="E420" s="19" t="s">
+        <v>634</v>
+      </c>
+      <c r="F420" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="G420" s="20">
+        <v>34</v>
+      </c>
+      <c r="H420" s="21" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="421" spans="1:8">
+      <c r="A421" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B421" s="13">
+        <v>45182</v>
+      </c>
+      <c r="C421" s="13">
+        <v>45222</v>
+      </c>
+      <c r="D421" s="13">
+        <v>45245</v>
+      </c>
+      <c r="E421" s="14" t="s">
+        <v>634</v>
+      </c>
+      <c r="F421" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G421" s="15">
+        <v>35</v>
+      </c>
+      <c r="H421" s="16" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="422" spans="1:8">
+      <c r="A422" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B422" s="18">
+        <v>45182</v>
+      </c>
+      <c r="C422" s="18">
+        <v>45222</v>
+      </c>
+      <c r="D422" s="18">
+        <v>45245</v>
+      </c>
+      <c r="E422" s="19" t="s">
+        <v>634</v>
+      </c>
+      <c r="F422" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="G422" s="20">
+        <v>2</v>
+      </c>
+      <c r="H422" s="21" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="423" spans="1:8">
+      <c r="A423" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B423" s="13">
+        <v>45188</v>
+      </c>
+      <c r="C423" s="13">
+        <v>45222</v>
+      </c>
+      <c r="D423" s="13">
+        <v>45188</v>
+      </c>
+      <c r="E423" s="14" t="s">
+        <v>638</v>
+      </c>
+      <c r="F423" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="G423" s="15">
+        <v>203</v>
+      </c>
+      <c r="H423" s="16" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="424" spans="1:8">
+      <c r="A424" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B424" s="18">
+        <v>45188</v>
+      </c>
+      <c r="C424" s="18">
+        <v>45222</v>
+      </c>
+      <c r="D424" s="18">
+        <v>45188</v>
+      </c>
+      <c r="E424" s="19" t="s">
+        <v>638</v>
+      </c>
+      <c r="F424" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="G424" s="20">
+        <v>22</v>
+      </c>
+      <c r="H424" s="21" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="425" spans="1:8">
+      <c r="A425" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="B425" s="13">
+        <v>45185</v>
+      </c>
+      <c r="C425" s="13">
+        <v>45222</v>
+      </c>
+      <c r="D425" s="13">
+        <v>45185</v>
+      </c>
+      <c r="E425" s="14" t="s">
+        <v>631</v>
+      </c>
+      <c r="F425" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G425" s="15">
+        <v>12</v>
+      </c>
+      <c r="H425" s="16" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="426" spans="1:8">
+      <c r="A426" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="B426" s="18">
+        <v>45187</v>
+      </c>
+      <c r="C426" s="18">
+        <v>45222</v>
+      </c>
+      <c r="D426" s="18">
+        <v>45291</v>
+      </c>
+      <c r="E426" s="19" t="s">
+        <v>642</v>
+      </c>
+      <c r="F426" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="G426" s="20">
+        <v>15</v>
+      </c>
+      <c r="H426" s="21" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="427" spans="1:8">
+      <c r="A427" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B427" s="13">
+        <v>45187</v>
+      </c>
+      <c r="C427" s="13">
+        <v>45222</v>
+      </c>
+      <c r="D427" s="13">
+        <v>45291</v>
+      </c>
+      <c r="E427" s="14" t="s">
+        <v>642</v>
+      </c>
+      <c r="F427" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G427" s="15">
+        <v>1</v>
+      </c>
+      <c r="H427" s="16" t="s">
+        <v>644</v>
       </c>
     </row>
   </sheetData>
@@ -13935,13 +14528,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0547CBF0-1BAF-4A60-A761-FFE25F3D6445}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8F751C9A-4FC5-4BDE-9771-AFF63B1DFAF0}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1143DF19-6DE9-4999-9184-AE0DB370768D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CEAE9BB4-D8CA-4C9E-95C8-28B6416561DA}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED512A25-1FBF-419B-AB02-EB74E9A5CFFE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08C5908A-5D9D-4671-90EB-2446192B044F}"/>
 </file>
--- a/data/warn-scraper/cache/ca/warn_report1.xlsx
+++ b/data/warn-scraper/cache/ca/warn_report1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\WSB-CO\Communications Unit\Website Management\WARN (Worker Adjustment and Retraining Notification) Updates\2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{99CB9904-488B-4205-9325-7024921D333A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7C80454A-EF11-4149-A910-6FC18ACA8D66}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="29895" yWindow="1230" windowWidth="21600" windowHeight="11430" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1723" uniqueCount="645">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1775" uniqueCount="660">
   <si>
     <t>This worksheet contains 3 sheets. The introductory page, WARN Report Summary, and Detailed WARN Report. The second sheet provides an overview of the report according to layoff/closure types and related quantitative data. The third sheet displays a detailed summary report of affected companies by county. This Daily WARN Report is updated every Tuesday and Thursday. Hyperlinks to the other 2 sheets can be found below in cell A3-A4.</t>
   </si>
@@ -103,7 +103,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>07/01/23 to 10/23/23</t>
+      <t>07/01/23 to 10/25/23</t>
     </r>
     <r>
       <rPr>
@@ -123,7 +123,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>A detailed WARN summary by county and filtered according to received date. Table Spans cells A2 through H427.</t>
+      <t>A detailed WARN summary by county and filtered according to received date. Table Spans cells A2 through H440.</t>
     </r>
   </si>
   <si>
@@ -2058,6 +2058,51 @@
   </si>
   <si>
     <t>2057 Aldergrove Ave.  Escondido CA 92029</t>
+  </si>
+  <si>
+    <t>1245 Broadway Plaza, Space C34  Walnut Creek CA 94596</t>
+  </si>
+  <si>
+    <t>Dryer's Grand Ice Cream</t>
+  </si>
+  <si>
+    <t>7901 District Blvd.  Bakersfield CA 93313</t>
+  </si>
+  <si>
+    <t>7901 District Blvd  Bakersfield CA 93313</t>
+  </si>
+  <si>
+    <t>Jabil, Inc.</t>
+  </si>
+  <si>
+    <t>26211 Enterprise Way  Lake Forest CA 92630</t>
+  </si>
+  <si>
+    <t>Roku, Inc.</t>
+  </si>
+  <si>
+    <t>1173 Coleman Ave.  San Jose CA 95110</t>
+  </si>
+  <si>
+    <t>Dreyer's Grand Ice Cream</t>
+  </si>
+  <si>
+    <t>970 E. Continental  Tulare CA 93274</t>
+  </si>
+  <si>
+    <t>BMO Bank N.A. successor in interest to Bank of the West</t>
+  </si>
+  <si>
+    <t>Distribution Alternatives, Inc.</t>
+  </si>
+  <si>
+    <t>1979 Renaissance Parkway  Rialto CA 92376</t>
+  </si>
+  <si>
+    <t>30 Great Oaks Boulevard  San Jose CA 95119</t>
+  </si>
+  <si>
+    <t>6375 San Ignacio Avenue  San Jose CA 95119</t>
   </si>
 </sst>
 </file>
@@ -2362,8 +2407,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF0F0F0"/>
-          <bgColor rgb="FFF0F0F0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -2403,8 +2448,8 @@
       <numFmt numFmtId="165" formatCode="[$-10436]#,##0;\(#,##0\)"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF0F0F0"/>
-          <bgColor rgb="FFF0F0F0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -2443,8 +2488,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF0F0F0"/>
-          <bgColor rgb="FFF0F0F0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -2483,8 +2528,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF0F0F0"/>
-          <bgColor rgb="FFF0F0F0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -2524,8 +2569,8 @@
       <numFmt numFmtId="164" formatCode="[$-10409]mm/dd/yyyy"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF0F0F0"/>
-          <bgColor rgb="FFF0F0F0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -2565,8 +2610,8 @@
       <numFmt numFmtId="164" formatCode="[$-10409]mm/dd/yyyy"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF0F0F0"/>
-          <bgColor rgb="FFF0F0F0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -2606,8 +2651,8 @@
       <numFmt numFmtId="164" formatCode="[$-10409]mm/dd/yyyy"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF0F0F0"/>
-          <bgColor rgb="FFF0F0F0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -2646,8 +2691,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF0F0F0"/>
-          <bgColor rgb="FFF0F0F0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -2839,8 +2884,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:H427" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="9" tableBorderDxfId="10" totalsRowBorderDxfId="8">
-  <autoFilter ref="A2:H427" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:H440" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="9" tableBorderDxfId="10" totalsRowBorderDxfId="8">
+  <autoFilter ref="A2:H440" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -3224,7 +3269,7 @@
       </c>
       <c r="B3" s="5">
         <f>SUM('Detailed WARN Report '!G:G)</f>
-        <v>18951</v>
+        <v>22819</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -3233,7 +3278,7 @@
       </c>
       <c r="B4" s="5">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Permanent")</f>
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -3242,7 +3287,7 @@
       </c>
       <c r="B5" s="5">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Temporary")</f>
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -3260,7 +3305,7 @@
       </c>
       <c r="B7" s="5">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Permanent")</f>
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -3269,7 +3314,7 @@
       </c>
       <c r="B8" s="5">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Temporary")</f>
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -3292,7 +3337,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:H427"/>
+  <dimension ref="A1:H440"/>
   <sheetFormatPr defaultColWidth="26" defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="25.85546875" bestFit="1" customWidth="1"/>
@@ -14389,6 +14434,344 @@
         <v>644</v>
       </c>
     </row>
+    <row r="428" spans="1:8">
+      <c r="A428" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="B428" s="18">
+        <v>45190</v>
+      </c>
+      <c r="C428" s="18">
+        <v>45223</v>
+      </c>
+      <c r="D428" s="18">
+        <v>45283</v>
+      </c>
+      <c r="E428" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="F428" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="G428" s="20">
+        <v>138</v>
+      </c>
+      <c r="H428" s="21" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="429" spans="1:8">
+      <c r="A429" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B429" s="13">
+        <v>45190</v>
+      </c>
+      <c r="C429" s="13">
+        <v>45223</v>
+      </c>
+      <c r="D429" s="13">
+        <v>45323</v>
+      </c>
+      <c r="E429" s="14" t="s">
+        <v>291</v>
+      </c>
+      <c r="F429" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="G429" s="15">
+        <v>6</v>
+      </c>
+      <c r="H429" s="16" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="430" spans="1:8">
+      <c r="A430" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="B430" s="18">
+        <v>45189</v>
+      </c>
+      <c r="C430" s="18">
+        <v>45223</v>
+      </c>
+      <c r="D430" s="18">
+        <v>45249</v>
+      </c>
+      <c r="E430" s="19" t="s">
+        <v>646</v>
+      </c>
+      <c r="F430" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="G430" s="20">
+        <v>1015</v>
+      </c>
+      <c r="H430" s="21" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="431" spans="1:8">
+      <c r="A431" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="B431" s="13">
+        <v>45189</v>
+      </c>
+      <c r="C431" s="13">
+        <v>45223</v>
+      </c>
+      <c r="D431" s="13">
+        <v>45275</v>
+      </c>
+      <c r="E431" s="14" t="s">
+        <v>646</v>
+      </c>
+      <c r="F431" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="G431" s="15">
+        <v>1015</v>
+      </c>
+      <c r="H431" s="16" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="432" spans="1:8">
+      <c r="A432" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="B432" s="18">
+        <v>45190</v>
+      </c>
+      <c r="C432" s="18">
+        <v>45223</v>
+      </c>
+      <c r="D432" s="18">
+        <v>45285</v>
+      </c>
+      <c r="E432" s="19" t="s">
+        <v>649</v>
+      </c>
+      <c r="F432" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="G432" s="20">
+        <v>69</v>
+      </c>
+      <c r="H432" s="21" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="433" spans="1:8">
+      <c r="A433" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="B433" s="13">
+        <v>45190</v>
+      </c>
+      <c r="C433" s="13">
+        <v>45223</v>
+      </c>
+      <c r="D433" s="13">
+        <v>45250</v>
+      </c>
+      <c r="E433" s="14" t="s">
+        <v>651</v>
+      </c>
+      <c r="F433" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G433" s="15">
+        <v>136</v>
+      </c>
+      <c r="H433" s="16" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="434" spans="1:8">
+      <c r="A434" s="17" t="s">
+        <v>178</v>
+      </c>
+      <c r="B434" s="18">
+        <v>45189</v>
+      </c>
+      <c r="C434" s="18">
+        <v>45223</v>
+      </c>
+      <c r="D434" s="18">
+        <v>45250</v>
+      </c>
+      <c r="E434" s="19" t="s">
+        <v>653</v>
+      </c>
+      <c r="F434" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="G434" s="20">
+        <v>306</v>
+      </c>
+      <c r="H434" s="21" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="435" spans="1:8">
+      <c r="A435" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="B435" s="13">
+        <v>45189</v>
+      </c>
+      <c r="C435" s="13">
+        <v>45223</v>
+      </c>
+      <c r="D435" s="13">
+        <v>45271</v>
+      </c>
+      <c r="E435" s="14" t="s">
+        <v>646</v>
+      </c>
+      <c r="F435" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="G435" s="15">
+        <v>306</v>
+      </c>
+      <c r="H435" s="16" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="436" spans="1:8">
+      <c r="A436" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B436" s="18">
+        <v>45188</v>
+      </c>
+      <c r="C436" s="18">
+        <v>45224</v>
+      </c>
+      <c r="D436" s="18">
+        <v>45268</v>
+      </c>
+      <c r="E436" s="19" t="s">
+        <v>655</v>
+      </c>
+      <c r="F436" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="G436" s="20">
+        <v>200</v>
+      </c>
+      <c r="H436" s="21" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="437" spans="1:8">
+      <c r="A437" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="B437" s="13">
+        <v>45189</v>
+      </c>
+      <c r="C437" s="13">
+        <v>45224</v>
+      </c>
+      <c r="D437" s="13">
+        <v>45250</v>
+      </c>
+      <c r="E437" s="14" t="s">
+        <v>656</v>
+      </c>
+      <c r="F437" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="G437" s="15">
+        <v>15</v>
+      </c>
+      <c r="H437" s="16" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="438" spans="1:8">
+      <c r="A438" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="B438" s="18">
+        <v>45188</v>
+      </c>
+      <c r="C438" s="18">
+        <v>45224</v>
+      </c>
+      <c r="D438" s="18">
+        <v>45268</v>
+      </c>
+      <c r="E438" s="19" t="s">
+        <v>655</v>
+      </c>
+      <c r="F438" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="G438" s="20">
+        <v>28</v>
+      </c>
+      <c r="H438" s="21" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="439" spans="1:8">
+      <c r="A439" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="B439" s="13">
+        <v>45190</v>
+      </c>
+      <c r="C439" s="13">
+        <v>45224</v>
+      </c>
+      <c r="D439" s="13">
+        <v>45285</v>
+      </c>
+      <c r="E439" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="F439" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="G439" s="15">
+        <v>550</v>
+      </c>
+      <c r="H439" s="16" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="440" spans="1:8">
+      <c r="A440" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="B440" s="18">
+        <v>45190</v>
+      </c>
+      <c r="C440" s="18">
+        <v>45224</v>
+      </c>
+      <c r="D440" s="18">
+        <v>45285</v>
+      </c>
+      <c r="E440" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="F440" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="G440" s="20">
+        <v>84</v>
+      </c>
+      <c r="H440" s="21" t="s">
+        <v>659</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="204" verticalDpi="192" r:id="rId1"/>
@@ -14399,21 +14782,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Unknown Document Type" ma:contentTypeID="0x010104" ma:contentTypeVersion="0" ma:contentTypeDescription="" ma:contentTypeScope="" ma:versionID="05d83ceaa0bbd2e3bc716e6e66bd857a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b3d69fe45253d5ff147bb69036b756a7">
     <xsd:element name="properties">
@@ -14527,14 +14895,29 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8F751C9A-4FC5-4BDE-9771-AFF63B1DFAF0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{87D6B202-3E9E-4EA9-962B-300F97594113}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CEAE9BB4-D8CA-4C9E-95C8-28B6416561DA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3DB660E6-0B52-405E-B4A3-081794E50287}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08C5908A-5D9D-4671-90EB-2446192B044F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{165F0DDD-7BCE-4EDD-BB6E-87FAA2B80802}"/>
 </file>
--- a/data/warn-scraper/cache/ca/warn_report1.xlsx
+++ b/data/warn-scraper/cache/ca/warn_report1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\WSB-CO\Communications Unit\Website Management\WARN (Worker Adjustment and Retraining Notification) Updates\2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF0BDA80-55FD-4D80-B931-8D710729DDBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C76FFED1-DF39-4B26-82E2-428F55AF13B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29430" yWindow="2130" windowWidth="21600" windowHeight="11430" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
+    <workbookView xWindow="624" yWindow="684" windowWidth="21600" windowHeight="11436" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
   <sheets>
     <sheet name="Index" sheetId="3" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2103" uniqueCount="764">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2171" uniqueCount="793">
   <si>
     <t>County/Parish</t>
   </si>
@@ -2393,6 +2393,93 @@
     <t>105 E Street  Vallejo CA 94592</t>
   </si>
   <si>
+    <t>5885 Hollis St. Suite 100  Emeryville CA 94608</t>
+  </si>
+  <si>
+    <t>MaxLite, Inc.</t>
+  </si>
+  <si>
+    <t>1148 Ocean Circle  Anaheim CA 92806</t>
+  </si>
+  <si>
+    <t>First Financial Credit Union</t>
+  </si>
+  <si>
+    <t>5115 Wilshire Blvd, Unit F  Los Angeles CA 90036</t>
+  </si>
+  <si>
+    <t>Mexi-Grill, LLC dba Javier's Newport Beach</t>
+  </si>
+  <si>
+    <t>7832 E. Coast Hwy Crystal Cove Promenade Newport Beach CA 92657</t>
+  </si>
+  <si>
+    <t>ResMEd Inc.</t>
+  </si>
+  <si>
+    <t>9001 Spectrum Center Blvd  San Diego CA 92123</t>
+  </si>
+  <si>
+    <t>Baxalta US, Inc.</t>
+  </si>
+  <si>
+    <t>4501 Colorado Blvd.  Los Angeles CA 90039</t>
+  </si>
+  <si>
+    <t>15903 Strathern Street  Van Nuys CA 91406</t>
+  </si>
+  <si>
+    <t>Capital One Financial</t>
+  </si>
+  <si>
+    <t>20 Pacifica Suite 550  Irvine CA 92618</t>
+  </si>
+  <si>
+    <t>Becton, Dickinson and Company</t>
+  </si>
+  <si>
+    <t>3750 Torrey View Ct.  San Diego CA 92130</t>
+  </si>
+  <si>
+    <t>Sunrise Growers Inc.</t>
+  </si>
+  <si>
+    <t>808 East Third Street  Oxnard CA 93030</t>
+  </si>
+  <si>
+    <t>WMBE Payrolling Inc. dba TCWGlobal</t>
+  </si>
+  <si>
+    <t>5885 Hollis St, Suite 100  Emeryville CA 94608</t>
+  </si>
+  <si>
+    <t>Surefox North America Inc</t>
+  </si>
+  <si>
+    <t>1685 Plymouth Street  Mountain View CA 94043</t>
+  </si>
+  <si>
+    <t>2000 North Shoreline Blvd  Mountain View CA 94043</t>
+  </si>
+  <si>
+    <t>100 Bay View Drive #100  Mountain View CA 94043</t>
+  </si>
+  <si>
+    <t>Arden Hills Country Club, Inc</t>
+  </si>
+  <si>
+    <t>1220 Arden Hills Lane  Sacramento CA 95864</t>
+  </si>
+  <si>
+    <t>Santa Cruz County</t>
+  </si>
+  <si>
+    <t>Kitayama Brothers Inc.</t>
+  </si>
+  <si>
+    <t>481 San Andreas Road  Watsonville CA 95076</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">WARN REPORT - </t>
     </r>
@@ -2404,7 +2491,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>07/01/23 to 11/15/23</t>
+      <t>07/01/23 to 11/20/23</t>
     </r>
     <r>
       <rPr>
@@ -2424,7 +2511,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>A detailed WARN summary by county and filtered according to received date. Table Spans cells A2 through H522.</t>
+      <t>A detailed WARN summary by county and filtered according to received date. Table Spans cells A2 through H539.</t>
     </r>
   </si>
 </sst>
@@ -3207,8 +3294,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:H522" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
-  <autoFilter ref="A2:H522" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:H539" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
+  <autoFilter ref="A2:H539" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -3592,7 +3679,7 @@
       </c>
       <c r="B3" s="5">
         <f>SUM('Detailed WARN Report '!G:G)</f>
-        <v>26780</v>
+        <v>28211</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -3601,7 +3688,7 @@
       </c>
       <c r="B4" s="5">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Permanent")</f>
-        <v>340</v>
+        <v>347</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -3628,7 +3715,7 @@
       </c>
       <c r="B7" s="5">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Permanent")</f>
-        <v>160</v>
+        <v>169</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -3637,7 +3724,7 @@
       </c>
       <c r="B8" s="5">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Temporary")</f>
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
@@ -3660,7 +3747,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:H522"/>
+  <dimension ref="A1:H539"/>
   <sheetFormatPr defaultColWidth="26" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.88671875" bestFit="1" customWidth="1"/>
@@ -3673,7 +3760,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="99.6" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
-        <v>763</v>
+        <v>792</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -17225,6 +17312,448 @@
       </c>
       <c r="H522" s="21" t="s">
         <v>759</v>
+      </c>
+    </row>
+    <row r="523" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A523" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="B523" s="13">
+        <v>45217</v>
+      </c>
+      <c r="C523" s="13">
+        <v>45246</v>
+      </c>
+      <c r="D523" s="13">
+        <v>45278</v>
+      </c>
+      <c r="E523" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="F523" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G523" s="17">
+        <v>112</v>
+      </c>
+      <c r="H523" s="18" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="524" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A524" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="B524" s="15">
+        <v>45224</v>
+      </c>
+      <c r="C524" s="15">
+        <v>45246</v>
+      </c>
+      <c r="D524" s="15">
+        <v>45291</v>
+      </c>
+      <c r="E524" s="19" t="s">
+        <v>764</v>
+      </c>
+      <c r="F524" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G524" s="20">
+        <v>4</v>
+      </c>
+      <c r="H524" s="21" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="525" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A525" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B525" s="13">
+        <v>45223</v>
+      </c>
+      <c r="C525" s="13">
+        <v>45246</v>
+      </c>
+      <c r="D525" s="13">
+        <v>45289</v>
+      </c>
+      <c r="E525" s="16" t="s">
+        <v>766</v>
+      </c>
+      <c r="F525" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G525" s="17">
+        <v>3</v>
+      </c>
+      <c r="H525" s="18" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="526" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A526" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="B526" s="15">
+        <v>45215</v>
+      </c>
+      <c r="C526" s="15">
+        <v>45246</v>
+      </c>
+      <c r="D526" s="15">
+        <v>45293</v>
+      </c>
+      <c r="E526" s="19" t="s">
+        <v>768</v>
+      </c>
+      <c r="F526" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="G526" s="20">
+        <v>239</v>
+      </c>
+      <c r="H526" s="21" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="527" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A527" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B527" s="13">
+        <v>45224</v>
+      </c>
+      <c r="C527" s="13">
+        <v>45246</v>
+      </c>
+      <c r="D527" s="13">
+        <v>45261</v>
+      </c>
+      <c r="E527" s="16" t="s">
+        <v>770</v>
+      </c>
+      <c r="F527" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G527" s="17">
+        <v>364</v>
+      </c>
+      <c r="H527" s="18" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="528" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A528" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="B528" s="15">
+        <v>45216</v>
+      </c>
+      <c r="C528" s="15">
+        <v>45247</v>
+      </c>
+      <c r="D528" s="15">
+        <v>45382</v>
+      </c>
+      <c r="E528" s="19" t="s">
+        <v>772</v>
+      </c>
+      <c r="F528" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G528" s="20">
+        <v>14</v>
+      </c>
+      <c r="H528" s="21" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="529" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A529" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B529" s="13">
+        <v>45216</v>
+      </c>
+      <c r="C529" s="13">
+        <v>45247</v>
+      </c>
+      <c r="D529" s="13">
+        <v>45382</v>
+      </c>
+      <c r="E529" s="16" t="s">
+        <v>772</v>
+      </c>
+      <c r="F529" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G529" s="17">
+        <v>1</v>
+      </c>
+      <c r="H529" s="18" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="530" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A530" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="B530" s="15">
+        <v>45229</v>
+      </c>
+      <c r="C530" s="15">
+        <v>45247</v>
+      </c>
+      <c r="D530" s="15">
+        <v>45296</v>
+      </c>
+      <c r="E530" s="19" t="s">
+        <v>775</v>
+      </c>
+      <c r="F530" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G530" s="20">
+        <v>49</v>
+      </c>
+      <c r="H530" s="21" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="531" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A531" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B531" s="13">
+        <v>45216</v>
+      </c>
+      <c r="C531" s="13">
+        <v>45247</v>
+      </c>
+      <c r="D531" s="13">
+        <v>45277</v>
+      </c>
+      <c r="E531" s="16" t="s">
+        <v>777</v>
+      </c>
+      <c r="F531" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G531" s="17">
+        <v>48</v>
+      </c>
+      <c r="H531" s="18" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="532" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A532" s="14" t="s">
+        <v>282</v>
+      </c>
+      <c r="B532" s="15">
+        <v>45229</v>
+      </c>
+      <c r="C532" s="15">
+        <v>45247</v>
+      </c>
+      <c r="D532" s="15">
+        <v>45290</v>
+      </c>
+      <c r="E532" s="19" t="s">
+        <v>779</v>
+      </c>
+      <c r="F532" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G532" s="20">
+        <v>34</v>
+      </c>
+      <c r="H532" s="21" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="533" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A533" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="B533" s="13">
+        <v>45217</v>
+      </c>
+      <c r="C533" s="13">
+        <v>45250</v>
+      </c>
+      <c r="D533" s="13">
+        <v>45278</v>
+      </c>
+      <c r="E533" s="16" t="s">
+        <v>781</v>
+      </c>
+      <c r="F533" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G533" s="17">
+        <v>88</v>
+      </c>
+      <c r="H533" s="18" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="534" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A534" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="B534" s="15">
+        <v>45215</v>
+      </c>
+      <c r="C534" s="15">
+        <v>45250</v>
+      </c>
+      <c r="D534" s="15">
+        <v>45278</v>
+      </c>
+      <c r="E534" s="19" t="s">
+        <v>783</v>
+      </c>
+      <c r="F534" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G534" s="20">
+        <v>126</v>
+      </c>
+      <c r="H534" s="21" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="535" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A535" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B535" s="13">
+        <v>45215</v>
+      </c>
+      <c r="C535" s="13">
+        <v>45250</v>
+      </c>
+      <c r="D535" s="13">
+        <v>45278</v>
+      </c>
+      <c r="E535" s="16" t="s">
+        <v>783</v>
+      </c>
+      <c r="F535" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G535" s="17">
+        <v>193</v>
+      </c>
+      <c r="H535" s="18" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="536" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A536" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="B536" s="15">
+        <v>45215</v>
+      </c>
+      <c r="C536" s="15">
+        <v>45250</v>
+      </c>
+      <c r="D536" s="15">
+        <v>45278</v>
+      </c>
+      <c r="E536" s="19" t="s">
+        <v>783</v>
+      </c>
+      <c r="F536" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G536" s="20">
+        <v>57</v>
+      </c>
+      <c r="H536" s="21" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="537" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A537" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B537" s="13">
+        <v>45215</v>
+      </c>
+      <c r="C537" s="13">
+        <v>45250</v>
+      </c>
+      <c r="D537" s="13">
+        <v>45278</v>
+      </c>
+      <c r="E537" s="16" t="s">
+        <v>783</v>
+      </c>
+      <c r="F537" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G537" s="17">
+        <v>10</v>
+      </c>
+      <c r="H537" s="18" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="538" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A538" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="B538" s="15">
+        <v>45212</v>
+      </c>
+      <c r="C538" s="15">
+        <v>45250</v>
+      </c>
+      <c r="D538" s="15">
+        <v>45291</v>
+      </c>
+      <c r="E538" s="19" t="s">
+        <v>787</v>
+      </c>
+      <c r="F538" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G538" s="20">
+        <v>33</v>
+      </c>
+      <c r="H538" s="21" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="539" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A539" s="12" t="s">
+        <v>789</v>
+      </c>
+      <c r="B539" s="13">
+        <v>45222</v>
+      </c>
+      <c r="C539" s="13">
+        <v>45250</v>
+      </c>
+      <c r="D539" s="13">
+        <v>45283</v>
+      </c>
+      <c r="E539" s="16" t="s">
+        <v>790</v>
+      </c>
+      <c r="F539" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G539" s="17">
+        <v>56</v>
+      </c>
+      <c r="H539" s="18" t="s">
+        <v>791</v>
       </c>
     </row>
   </sheetData>
@@ -17366,13 +17895,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF8DE23A-3CF1-486C-8A22-1A60FA39EAEC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5D2E18AF-8891-42F5-B11E-A6D79B6A0815}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E0CF02DC-F0FE-453F-AB8E-21EAAE0E23E8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EA3627E-1E86-4EFA-AE81-A8B9025F1AE8}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A6493A2-2D1E-4F25-829D-E3D4DF36FD56}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{32E73414-ED92-4F93-B076-33A65B6F81A4}"/>
 </file>
--- a/data/warn-scraper/cache/ca/warn_report1.xlsx
+++ b/data/warn-scraper/cache/ca/warn_report1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\WSB-CO\Communications Unit\Website Management\WARN (Worker Adjustment and Retraining Notification) Updates\2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C76FFED1-DF39-4B26-82E2-428F55AF13B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5005354B-1F8F-403C-A9E3-041FD40956A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="624" yWindow="684" windowWidth="21600" windowHeight="11436" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2171" uniqueCount="793">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2223" uniqueCount="811">
   <si>
     <t>County/Parish</t>
   </si>
@@ -2480,6 +2480,60 @@
     <t>481 San Andreas Road  Watsonville CA 95076</t>
   </si>
   <si>
+    <t>Exabeam, Inc.</t>
+  </si>
+  <si>
+    <t>1051 E. Hillsdale Blvd., Fourth Floor  San Mateo CA 94404</t>
+  </si>
+  <si>
+    <t>Qualcomm Incorporated</t>
+  </si>
+  <si>
+    <t>3195 Kifer Road  Santa Clara CA 95051</t>
+  </si>
+  <si>
+    <t>3135 Kifer Road  Santa Clara CA 95051</t>
+  </si>
+  <si>
+    <t>3150 Central Expressway  Santa Clara CA 95051</t>
+  </si>
+  <si>
+    <t>3165 Kifer Road  Santa Clara CA 95051</t>
+  </si>
+  <si>
+    <t>3105 Kifer Road  Santa Clara CA 95051</t>
+  </si>
+  <si>
+    <t>3090 Oakmead Village Drive  Santa Clara CA 95051</t>
+  </si>
+  <si>
+    <t>5775 Morehouse Drive  San Diego CA 92121</t>
+  </si>
+  <si>
+    <t>Fashion Institute of Design &amp; Merchandising FIDM</t>
+  </si>
+  <si>
+    <t>919 South Grand Avenue  Los Angeles CA 90015</t>
+  </si>
+  <si>
+    <t>Momentum for Health</t>
+  </si>
+  <si>
+    <t>2115 The Alameda  San Jose CA 95126</t>
+  </si>
+  <si>
+    <t>185 Martinvale Lane  San Jose CA 95119</t>
+  </si>
+  <si>
+    <t>2001 The Alameda  San Jose CA 95126</t>
+  </si>
+  <si>
+    <t>Ojai Valley Inn</t>
+  </si>
+  <si>
+    <t>905 Country Club Road  Ojai CA 93023</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">WARN REPORT - </t>
     </r>
@@ -2491,7 +2545,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>07/01/23 to 11/20/23</t>
+      <t>07/01/23 to 11/27/23</t>
     </r>
     <r>
       <rPr>
@@ -2511,7 +2565,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>A detailed WARN summary by county and filtered according to received date. Table Spans cells A2 through H539.</t>
+      <t>A detailed WARN summary by county and filtered according to received date. Table Spans cells A2 through H552.</t>
     </r>
   </si>
 </sst>
@@ -2817,8 +2871,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF0F0F0"/>
-          <bgColor rgb="FFF0F0F0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -2858,8 +2912,8 @@
       <numFmt numFmtId="165" formatCode="[$-10436]#,##0;\(#,##0\)"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF0F0F0"/>
-          <bgColor rgb="FFF0F0F0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -2898,8 +2952,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF0F0F0"/>
-          <bgColor rgb="FFF0F0F0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -2938,8 +2992,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF0F0F0"/>
-          <bgColor rgb="FFF0F0F0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -2979,8 +3033,8 @@
       <numFmt numFmtId="164" formatCode="[$-10409]mm/dd/yyyy"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF0F0F0"/>
-          <bgColor rgb="FFF0F0F0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -3020,8 +3074,8 @@
       <numFmt numFmtId="164" formatCode="[$-10409]mm/dd/yyyy"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF0F0F0"/>
-          <bgColor rgb="FFF0F0F0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -3061,8 +3115,8 @@
       <numFmt numFmtId="164" formatCode="[$-10409]mm/dd/yyyy"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF0F0F0"/>
-          <bgColor rgb="FFF0F0F0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -3101,8 +3155,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF0F0F0"/>
-          <bgColor rgb="FFF0F0F0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -3294,8 +3348,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:H539" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
-  <autoFilter ref="A2:H539" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:H552" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
+  <autoFilter ref="A2:H552" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -3679,7 +3733,7 @@
       </c>
       <c r="B3" s="5">
         <f>SUM('Detailed WARN Report '!G:G)</f>
-        <v>28211</v>
+        <v>30841</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -3688,7 +3742,7 @@
       </c>
       <c r="B4" s="5">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Permanent")</f>
-        <v>347</v>
+        <v>356</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -3715,7 +3769,7 @@
       </c>
       <c r="B7" s="5">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Permanent")</f>
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -3724,7 +3778,7 @@
       </c>
       <c r="B8" s="5">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Temporary")</f>
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
@@ -3747,7 +3801,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:H539"/>
+  <dimension ref="A1:H552"/>
   <sheetFormatPr defaultColWidth="26" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.88671875" bestFit="1" customWidth="1"/>
@@ -3760,7 +3814,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="99.6" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
-        <v>792</v>
+        <v>810</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -17754,6 +17808,344 @@
       </c>
       <c r="H539" s="18" t="s">
         <v>791</v>
+      </c>
+    </row>
+    <row r="540" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A540" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="B540" s="15">
+        <v>45224</v>
+      </c>
+      <c r="C540" s="15">
+        <v>45252</v>
+      </c>
+      <c r="D540" s="15">
+        <v>45292</v>
+      </c>
+      <c r="E540" s="19" t="s">
+        <v>792</v>
+      </c>
+      <c r="F540" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G540" s="20">
+        <v>94</v>
+      </c>
+      <c r="H540" s="21" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="541" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A541" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B541" s="13">
+        <v>45210</v>
+      </c>
+      <c r="C541" s="13">
+        <v>45252</v>
+      </c>
+      <c r="D541" s="13">
+        <v>45273</v>
+      </c>
+      <c r="E541" s="16" t="s">
+        <v>794</v>
+      </c>
+      <c r="F541" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G541" s="17">
+        <v>189</v>
+      </c>
+      <c r="H541" s="18" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="542" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A542" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="B542" s="15">
+        <v>45210</v>
+      </c>
+      <c r="C542" s="15">
+        <v>45252</v>
+      </c>
+      <c r="D542" s="15">
+        <v>45273</v>
+      </c>
+      <c r="E542" s="19" t="s">
+        <v>794</v>
+      </c>
+      <c r="F542" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G542" s="20">
+        <v>1</v>
+      </c>
+      <c r="H542" s="21" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="543" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A543" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B543" s="13">
+        <v>45210</v>
+      </c>
+      <c r="C543" s="13">
+        <v>45252</v>
+      </c>
+      <c r="D543" s="13">
+        <v>45273</v>
+      </c>
+      <c r="E543" s="16" t="s">
+        <v>794</v>
+      </c>
+      <c r="F543" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G543" s="17">
+        <v>1</v>
+      </c>
+      <c r="H543" s="18" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="544" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A544" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="B544" s="15">
+        <v>45210</v>
+      </c>
+      <c r="C544" s="15">
+        <v>45252</v>
+      </c>
+      <c r="D544" s="15">
+        <v>45273</v>
+      </c>
+      <c r="E544" s="19" t="s">
+        <v>794</v>
+      </c>
+      <c r="F544" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G544" s="20">
+        <v>1</v>
+      </c>
+      <c r="H544" s="21" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="545" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A545" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B545" s="13">
+        <v>45210</v>
+      </c>
+      <c r="C545" s="13">
+        <v>45252</v>
+      </c>
+      <c r="D545" s="13">
+        <v>45273</v>
+      </c>
+      <c r="E545" s="16" t="s">
+        <v>794</v>
+      </c>
+      <c r="F545" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G545" s="17">
+        <v>1</v>
+      </c>
+      <c r="H545" s="18" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="546" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A546" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="B546" s="15">
+        <v>45210</v>
+      </c>
+      <c r="C546" s="15">
+        <v>45252</v>
+      </c>
+      <c r="D546" s="15">
+        <v>45273</v>
+      </c>
+      <c r="E546" s="19" t="s">
+        <v>794</v>
+      </c>
+      <c r="F546" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G546" s="20">
+        <v>1</v>
+      </c>
+      <c r="H546" s="21" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="547" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A547" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B547" s="13">
+        <v>45210</v>
+      </c>
+      <c r="C547" s="13">
+        <v>45252</v>
+      </c>
+      <c r="D547" s="13">
+        <v>45273</v>
+      </c>
+      <c r="E547" s="16" t="s">
+        <v>794</v>
+      </c>
+      <c r="F547" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G547" s="17">
+        <v>1064</v>
+      </c>
+      <c r="H547" s="18" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="548" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A548" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="B548" s="15">
+        <v>45225</v>
+      </c>
+      <c r="C548" s="15">
+        <v>45257</v>
+      </c>
+      <c r="D548" s="15">
+        <v>45290</v>
+      </c>
+      <c r="E548" s="19" t="s">
+        <v>802</v>
+      </c>
+      <c r="F548" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G548" s="20">
+        <v>322</v>
+      </c>
+      <c r="H548" s="21" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="549" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A549" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B549" s="13">
+        <v>45226</v>
+      </c>
+      <c r="C549" s="13">
+        <v>45257</v>
+      </c>
+      <c r="D549" s="13">
+        <v>45291</v>
+      </c>
+      <c r="E549" s="16" t="s">
+        <v>804</v>
+      </c>
+      <c r="F549" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G549" s="17">
+        <v>84</v>
+      </c>
+      <c r="H549" s="18" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="550" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A550" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="B550" s="15">
+        <v>45226</v>
+      </c>
+      <c r="C550" s="15">
+        <v>45257</v>
+      </c>
+      <c r="D550" s="15">
+        <v>45291</v>
+      </c>
+      <c r="E550" s="19" t="s">
+        <v>804</v>
+      </c>
+      <c r="F550" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G550" s="20">
+        <v>1</v>
+      </c>
+      <c r="H550" s="21" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="551" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A551" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B551" s="13">
+        <v>45226</v>
+      </c>
+      <c r="C551" s="13">
+        <v>45257</v>
+      </c>
+      <c r="D551" s="13">
+        <v>45291</v>
+      </c>
+      <c r="E551" s="16" t="s">
+        <v>804</v>
+      </c>
+      <c r="F551" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G551" s="17">
+        <v>1</v>
+      </c>
+      <c r="H551" s="18" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="552" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A552" s="14" t="s">
+        <v>282</v>
+      </c>
+      <c r="B552" s="15">
+        <v>45217</v>
+      </c>
+      <c r="C552" s="15">
+        <v>45257</v>
+      </c>
+      <c r="D552" s="15">
+        <v>45293</v>
+      </c>
+      <c r="E552" s="19" t="s">
+        <v>808</v>
+      </c>
+      <c r="F552" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="G552" s="20">
+        <v>870</v>
+      </c>
+      <c r="H552" s="21" t="s">
+        <v>809</v>
       </c>
     </row>
   </sheetData>
@@ -17895,13 +18287,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5D2E18AF-8891-42F5-B11E-A6D79B6A0815}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8017DCF6-A00C-45A5-8B80-D567C3BC7D8C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EA3627E-1E86-4EFA-AE81-A8B9025F1AE8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{11BA3045-0346-4BA5-A87A-6CC80678F99C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{32E73414-ED92-4F93-B076-33A65B6F81A4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91F5C132-AF4B-4AC9-B206-5D6BBA916D8D}"/>
 </file>
--- a/data/warn-scraper/cache/ca/warn_report1.xlsx
+++ b/data/warn-scraper/cache/ca/warn_report1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\WSB-CO\Communications Unit\Website Management\WARN (Worker Adjustment and Retraining Notification) Updates\2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5005354B-1F8F-403C-A9E3-041FD40956A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9014203-69F7-4E88-8A79-FCA9B2FA3C97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="624" yWindow="684" windowWidth="21600" windowHeight="11436" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2223" uniqueCount="811">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2271" uniqueCount="826">
   <si>
     <t>County/Parish</t>
   </si>
@@ -2534,6 +2534,51 @@
     <t>905 Country Club Road  Ojai CA 93023</t>
   </si>
   <si>
+    <t>Family YMCA of the Desert at Palm Desert Aquatic Center</t>
+  </si>
+  <si>
+    <t>Layoff Not known at this time</t>
+  </si>
+  <si>
+    <t>73751 Magnesia Falls Dr.  Palm Desert CA 92260</t>
+  </si>
+  <si>
+    <t>Locanabio, Inc.</t>
+  </si>
+  <si>
+    <t>3545 John Hopkins Court Suite 200  San Diego CA 92121</t>
+  </si>
+  <si>
+    <t>The Hotel del Coronado</t>
+  </si>
+  <si>
+    <t>1500 Orange Ave.  Coronado CA 92118</t>
+  </si>
+  <si>
+    <t>Miyoko's PBC</t>
+  </si>
+  <si>
+    <t>2086 Marina Avenue  Petaluma CA 94954</t>
+  </si>
+  <si>
+    <t>Elevance Health, Inc.</t>
+  </si>
+  <si>
+    <t>21215 Burbank Blvd.  Woodland Hills CA 91367</t>
+  </si>
+  <si>
+    <t>St. John of God Health Care Services</t>
+  </si>
+  <si>
+    <t>13333 Palmdale Road  Victorville CA 92392</t>
+  </si>
+  <si>
+    <t>Alvarado Hospital, LLC dba Alvarado Hospital Medical Center</t>
+  </si>
+  <si>
+    <t>6655 Alvarado Road  San Diego CA 92120</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">WARN REPORT - </t>
     </r>
@@ -2545,7 +2590,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>07/01/23 to 11/27/23</t>
+      <t>07/01/23 to 11/29/23</t>
     </r>
     <r>
       <rPr>
@@ -2565,7 +2610,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>A detailed WARN summary by county and filtered according to received date. Table Spans cells A2 through H552.</t>
+      <t>A detailed WARN summary by county and filtered according to received date. Table Spans cells A2 through H564.</t>
     </r>
   </si>
 </sst>
@@ -2871,8 +2916,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFF0F0F0"/>
+          <bgColor rgb="FFF0F0F0"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -2912,8 +2957,8 @@
       <numFmt numFmtId="165" formatCode="[$-10436]#,##0;\(#,##0\)"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFF0F0F0"/>
+          <bgColor rgb="FFF0F0F0"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -2952,8 +2997,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFF0F0F0"/>
+          <bgColor rgb="FFF0F0F0"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -2992,8 +3037,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFF0F0F0"/>
+          <bgColor rgb="FFF0F0F0"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -3033,8 +3078,8 @@
       <numFmt numFmtId="164" formatCode="[$-10409]mm/dd/yyyy"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFF0F0F0"/>
+          <bgColor rgb="FFF0F0F0"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -3074,8 +3119,8 @@
       <numFmt numFmtId="164" formatCode="[$-10409]mm/dd/yyyy"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFF0F0F0"/>
+          <bgColor rgb="FFF0F0F0"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -3115,8 +3160,8 @@
       <numFmt numFmtId="164" formatCode="[$-10409]mm/dd/yyyy"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFF0F0F0"/>
+          <bgColor rgb="FFF0F0F0"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -3155,8 +3200,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFF0F0F0"/>
+          <bgColor rgb="FFF0F0F0"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -3348,8 +3393,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:H552" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
-  <autoFilter ref="A2:H552" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:H564" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
+  <autoFilter ref="A2:H564" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -3733,7 +3778,7 @@
       </c>
       <c r="B3" s="5">
         <f>SUM('Detailed WARN Report '!G:G)</f>
-        <v>30841</v>
+        <v>32308</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -3742,7 +3787,7 @@
       </c>
       <c r="B4" s="5">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Permanent")</f>
-        <v>356</v>
+        <v>361</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -3751,7 +3796,7 @@
       </c>
       <c r="B5" s="5">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Temporary")</f>
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
@@ -3769,7 +3814,7 @@
       </c>
       <c r="B7" s="5">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Permanent")</f>
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -3801,20 +3846,20 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:H552"/>
+  <dimension ref="A1:H564"/>
   <sheetFormatPr defaultColWidth="26" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.88671875" bestFit="1" customWidth="1"/>
     <col min="2" max="4" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="62.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="54.88671875" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.33203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="63.5546875" customWidth="1"/>
+    <col min="8" max="8" width="58.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="99.6" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
-        <v>810</v>
+        <v>825</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -18146,6 +18191,318 @@
       </c>
       <c r="H552" s="21" t="s">
         <v>809</v>
+      </c>
+    </row>
+    <row r="553" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A553" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B553" s="13">
+        <v>45231</v>
+      </c>
+      <c r="C553" s="13">
+        <v>45258</v>
+      </c>
+      <c r="D553" s="13">
+        <v>45291</v>
+      </c>
+      <c r="E553" s="16" t="s">
+        <v>810</v>
+      </c>
+      <c r="F553" s="16" t="s">
+        <v>811</v>
+      </c>
+      <c r="G553" s="17">
+        <v>85</v>
+      </c>
+      <c r="H553" s="18" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="554" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A554" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B554" s="15">
+        <v>45231</v>
+      </c>
+      <c r="C554" s="15">
+        <v>45258</v>
+      </c>
+      <c r="D554" s="15">
+        <v>45291</v>
+      </c>
+      <c r="E554" s="19" t="s">
+        <v>813</v>
+      </c>
+      <c r="F554" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G554" s="20">
+        <v>58</v>
+      </c>
+      <c r="H554" s="21" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="555" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A555" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B555" s="13">
+        <v>45231</v>
+      </c>
+      <c r="C555" s="13">
+        <v>45258</v>
+      </c>
+      <c r="D555" s="13">
+        <v>45295</v>
+      </c>
+      <c r="E555" s="16" t="s">
+        <v>815</v>
+      </c>
+      <c r="F555" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="G555" s="17">
+        <v>10</v>
+      </c>
+      <c r="H555" s="18" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="556" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A556" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B556" s="15">
+        <v>45231</v>
+      </c>
+      <c r="C556" s="15">
+        <v>45258</v>
+      </c>
+      <c r="D556" s="15">
+        <v>45296</v>
+      </c>
+      <c r="E556" s="19" t="s">
+        <v>815</v>
+      </c>
+      <c r="F556" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="G556" s="20">
+        <v>82</v>
+      </c>
+      <c r="H556" s="21" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="557" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A557" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B557" s="13">
+        <v>45231</v>
+      </c>
+      <c r="C557" s="13">
+        <v>45258</v>
+      </c>
+      <c r="D557" s="13">
+        <v>45298</v>
+      </c>
+      <c r="E557" s="16" t="s">
+        <v>815</v>
+      </c>
+      <c r="F557" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="G557" s="17">
+        <v>43</v>
+      </c>
+      <c r="H557" s="18" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="558" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A558" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B558" s="15">
+        <v>45231</v>
+      </c>
+      <c r="C558" s="15">
+        <v>45258</v>
+      </c>
+      <c r="D558" s="15">
+        <v>45302</v>
+      </c>
+      <c r="E558" s="19" t="s">
+        <v>815</v>
+      </c>
+      <c r="F558" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="G558" s="20">
+        <v>6</v>
+      </c>
+      <c r="H558" s="21" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="559" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A559" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B559" s="13">
+        <v>45231</v>
+      </c>
+      <c r="C559" s="13">
+        <v>45258</v>
+      </c>
+      <c r="D559" s="13">
+        <v>45313</v>
+      </c>
+      <c r="E559" s="16" t="s">
+        <v>815</v>
+      </c>
+      <c r="F559" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="G559" s="17">
+        <v>56</v>
+      </c>
+      <c r="H559" s="18" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="560" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A560" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="B560" s="15">
+        <v>45231</v>
+      </c>
+      <c r="C560" s="15">
+        <v>45258</v>
+      </c>
+      <c r="D560" s="15">
+        <v>45295</v>
+      </c>
+      <c r="E560" s="19" t="s">
+        <v>817</v>
+      </c>
+      <c r="F560" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G560" s="20">
+        <v>33</v>
+      </c>
+      <c r="H560" s="21" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="561" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A561" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B561" s="13">
+        <v>45229</v>
+      </c>
+      <c r="C561" s="13">
+        <v>45259</v>
+      </c>
+      <c r="D561" s="13">
+        <v>45380</v>
+      </c>
+      <c r="E561" s="16" t="s">
+        <v>819</v>
+      </c>
+      <c r="F561" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G561" s="17">
+        <v>87</v>
+      </c>
+      <c r="H561" s="18" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="562" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A562" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="B562" s="15">
+        <v>45224</v>
+      </c>
+      <c r="C562" s="15">
+        <v>45259</v>
+      </c>
+      <c r="D562" s="15">
+        <v>45289</v>
+      </c>
+      <c r="E562" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="F562" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G562" s="20">
+        <v>172</v>
+      </c>
+      <c r="H562" s="21" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="563" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A563" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="B563" s="13">
+        <v>45229</v>
+      </c>
+      <c r="C563" s="13">
+        <v>45259</v>
+      </c>
+      <c r="D563" s="13">
+        <v>45291</v>
+      </c>
+      <c r="E563" s="16" t="s">
+        <v>821</v>
+      </c>
+      <c r="F563" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G563" s="17">
+        <v>27</v>
+      </c>
+      <c r="H563" s="18" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="564" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A564" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B564" s="15">
+        <v>45210</v>
+      </c>
+      <c r="C564" s="15">
+        <v>45259</v>
+      </c>
+      <c r="D564" s="15">
+        <v>45291</v>
+      </c>
+      <c r="E564" s="19" t="s">
+        <v>823</v>
+      </c>
+      <c r="F564" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G564" s="20">
+        <v>808</v>
+      </c>
+      <c r="H564" s="21" t="s">
+        <v>824</v>
       </c>
     </row>
   </sheetData>
@@ -18287,13 +18644,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8017DCF6-A00C-45A5-8B80-D567C3BC7D8C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97F3F67B-1AC3-4EBA-A159-3ABD22C40C37}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{11BA3045-0346-4BA5-A87A-6CC80678F99C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F883A3B5-A1C5-4A52-9EC4-BEE926CAA65B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91F5C132-AF4B-4AC9-B206-5D6BBA916D8D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{75774455-C0FB-438C-BE4F-E3AE10870C57}"/>
 </file>
--- a/data/warn-scraper/cache/ca/warn_report1.xlsx
+++ b/data/warn-scraper/cache/ca/warn_report1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\WSB-CO\Communications Unit\Website Management\WARN (Worker Adjustment and Retraining Notification) Updates\2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9014203-69F7-4E88-8A79-FCA9B2FA3C97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{250C4250-AE91-4AB8-8FC3-6AA50D2CA08A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="624" yWindow="684" windowWidth="21600" windowHeight="11436" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2271" uniqueCount="826">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2375" uniqueCount="847">
   <si>
     <t>County/Parish</t>
   </si>
@@ -2579,6 +2579,69 @@
     <t>6655 Alvarado Road  San Diego CA 92120</t>
   </si>
   <si>
+    <t>John Muir Health (JMH)</t>
+  </si>
+  <si>
+    <t>2298 Pike Court  Concord CA 94520</t>
+  </si>
+  <si>
+    <t>Command Security Service LP at Google/Bayview</t>
+  </si>
+  <si>
+    <t>100 Bay View Drive  Mountain View CA 94043</t>
+  </si>
+  <si>
+    <t>Becton, Dickinson, and Company</t>
+  </si>
+  <si>
+    <t>3750 Torrey View Court  San Diego CA 92130</t>
+  </si>
+  <si>
+    <t>Becton, Dickinson, and Company - Pacific</t>
+  </si>
+  <si>
+    <t>10020 Pacific Mesa Blvd.  San Diego CA 92121</t>
+  </si>
+  <si>
+    <t>Cygnus Home Service, LLC dba Yelloh</t>
+  </si>
+  <si>
+    <t>320 Old Yard Drive  Bakersfield CA 93307</t>
+  </si>
+  <si>
+    <t>Vertical Supply Group</t>
+  </si>
+  <si>
+    <t>12519 Putman Street  Whittier CA 90602</t>
+  </si>
+  <si>
+    <t>Yelloh</t>
+  </si>
+  <si>
+    <t>16 Bellarmine Court  Chico CA 95928</t>
+  </si>
+  <si>
+    <t>19813 Hirsch Court  Anderson CA 96007</t>
+  </si>
+  <si>
+    <t>351 North Orange Street  Riverside CA 92501</t>
+  </si>
+  <si>
+    <t>999 Kent Street  Elk Grove CA 95624</t>
+  </si>
+  <si>
+    <t>575 Industrial Park Drive  Manteca CA 95337</t>
+  </si>
+  <si>
+    <t>440 East Todd Road  Santa Rosa CA 95407</t>
+  </si>
+  <si>
+    <t>San Diego Imaging Management, Inc.</t>
+  </si>
+  <si>
+    <t>8745 Aero Drive, Suite 200  San Diego CA 92123</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">WARN REPORT - </t>
     </r>
@@ -2590,7 +2653,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>07/01/23 to 11/29/23</t>
+      <t>07/01/23 to 12/04/23</t>
     </r>
     <r>
       <rPr>
@@ -2610,7 +2673,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>A detailed WARN summary by county and filtered according to received date. Table Spans cells A2 through H564.</t>
+      <t>A detailed WARN summary by county and filtered according to received date. Table Spans cells A2 through H590.</t>
     </r>
   </si>
 </sst>
@@ -3393,8 +3456,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:H564" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
-  <autoFilter ref="A2:H564" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:H590" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
+  <autoFilter ref="A2:H590" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -3778,7 +3841,7 @@
       </c>
       <c r="B3" s="5">
         <f>SUM('Detailed WARN Report '!G:G)</f>
-        <v>32308</v>
+        <v>32921</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -3787,7 +3850,7 @@
       </c>
       <c r="B4" s="5">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Permanent")</f>
-        <v>361</v>
+        <v>378</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -3796,7 +3859,7 @@
       </c>
       <c r="B5" s="5">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Temporary")</f>
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
@@ -3814,7 +3877,7 @@
       </c>
       <c r="B7" s="5">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Permanent")</f>
-        <v>173</v>
+        <v>181</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -3846,20 +3909,20 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:H564"/>
+  <dimension ref="A1:H590"/>
   <sheetFormatPr defaultColWidth="26" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.88671875" bestFit="1" customWidth="1"/>
     <col min="2" max="4" width="8.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="54.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.5546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.88671875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="58.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="99.6" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
-        <v>825</v>
+        <v>846</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -3867,7 +3930,7 @@
       <c r="G1" s="6"/>
       <c r="H1" s="6"/>
     </row>
-    <row r="2" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="24.6" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
         <v>0</v>
       </c>
@@ -12458,7 +12521,7 @@
         <v>45203</v>
       </c>
       <c r="D332" s="15">
-        <v>45198</v>
+        <v>45289</v>
       </c>
       <c r="E332" s="19" t="s">
         <v>499</v>
@@ -12467,7 +12530,7 @@
         <v>16</v>
       </c>
       <c r="G332" s="20">
-        <v>259</v>
+        <v>298</v>
       </c>
       <c r="H332" s="21" t="s">
         <v>500</v>
@@ -18193,7 +18256,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="553" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A553" s="12" t="s">
         <v>11</v>
       </c>
@@ -18503,6 +18566,682 @@
       </c>
       <c r="H564" s="21" t="s">
         <v>824</v>
+      </c>
+    </row>
+    <row r="565" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A565" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B565" s="13">
+        <v>45223</v>
+      </c>
+      <c r="C565" s="13">
+        <v>45260</v>
+      </c>
+      <c r="D565" s="13">
+        <v>45289</v>
+      </c>
+      <c r="E565" s="16" t="s">
+        <v>825</v>
+      </c>
+      <c r="F565" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G565" s="17">
+        <v>164</v>
+      </c>
+      <c r="H565" s="18" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="566" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A566" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="B566" s="15">
+        <v>45233</v>
+      </c>
+      <c r="C566" s="15">
+        <v>45260</v>
+      </c>
+      <c r="D566" s="15">
+        <v>45279</v>
+      </c>
+      <c r="E566" s="19" t="s">
+        <v>827</v>
+      </c>
+      <c r="F566" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G566" s="20">
+        <v>33</v>
+      </c>
+      <c r="H566" s="21" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="567" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A567" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B567" s="13">
+        <v>45203</v>
+      </c>
+      <c r="C567" s="13">
+        <v>45260</v>
+      </c>
+      <c r="D567" s="13">
+        <v>45210</v>
+      </c>
+      <c r="E567" s="16" t="s">
+        <v>829</v>
+      </c>
+      <c r="F567" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G567" s="17">
+        <v>38</v>
+      </c>
+      <c r="H567" s="18" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="568" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A568" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B568" s="15">
+        <v>45203</v>
+      </c>
+      <c r="C568" s="15">
+        <v>45260</v>
+      </c>
+      <c r="D568" s="15">
+        <v>45210</v>
+      </c>
+      <c r="E568" s="19" t="s">
+        <v>831</v>
+      </c>
+      <c r="F568" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G568" s="20">
+        <v>27</v>
+      </c>
+      <c r="H568" s="21" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="569" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A569" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B569" s="13">
+        <v>45203</v>
+      </c>
+      <c r="C569" s="13">
+        <v>45260</v>
+      </c>
+      <c r="D569" s="13">
+        <v>45212</v>
+      </c>
+      <c r="E569" s="16" t="s">
+        <v>829</v>
+      </c>
+      <c r="F569" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G569" s="17">
+        <v>3</v>
+      </c>
+      <c r="H569" s="18" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="570" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A570" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B570" s="15">
+        <v>45203</v>
+      </c>
+      <c r="C570" s="15">
+        <v>45260</v>
+      </c>
+      <c r="D570" s="15">
+        <v>45215</v>
+      </c>
+      <c r="E570" s="19" t="s">
+        <v>829</v>
+      </c>
+      <c r="F570" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G570" s="20">
+        <v>1</v>
+      </c>
+      <c r="H570" s="21" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="571" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A571" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B571" s="13">
+        <v>45203</v>
+      </c>
+      <c r="C571" s="13">
+        <v>45260</v>
+      </c>
+      <c r="D571" s="13">
+        <v>45226</v>
+      </c>
+      <c r="E571" s="16" t="s">
+        <v>829</v>
+      </c>
+      <c r="F571" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G571" s="17">
+        <v>2</v>
+      </c>
+      <c r="H571" s="18" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="572" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A572" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B572" s="15">
+        <v>45203</v>
+      </c>
+      <c r="C572" s="15">
+        <v>45260</v>
+      </c>
+      <c r="D572" s="15">
+        <v>45229</v>
+      </c>
+      <c r="E572" s="19" t="s">
+        <v>829</v>
+      </c>
+      <c r="F572" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G572" s="20">
+        <v>26</v>
+      </c>
+      <c r="H572" s="21" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="573" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A573" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B573" s="13">
+        <v>45203</v>
+      </c>
+      <c r="C573" s="13">
+        <v>45260</v>
+      </c>
+      <c r="D573" s="13">
+        <v>45230</v>
+      </c>
+      <c r="E573" s="16" t="s">
+        <v>829</v>
+      </c>
+      <c r="F573" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G573" s="17">
+        <v>1</v>
+      </c>
+      <c r="H573" s="18" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="574" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A574" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B574" s="15">
+        <v>45203</v>
+      </c>
+      <c r="C574" s="15">
+        <v>45260</v>
+      </c>
+      <c r="D574" s="15">
+        <v>45232</v>
+      </c>
+      <c r="E574" s="19" t="s">
+        <v>829</v>
+      </c>
+      <c r="F574" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G574" s="20">
+        <v>1</v>
+      </c>
+      <c r="H574" s="21" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="575" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A575" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B575" s="13">
+        <v>45203</v>
+      </c>
+      <c r="C575" s="13">
+        <v>45260</v>
+      </c>
+      <c r="D575" s="13">
+        <v>45213</v>
+      </c>
+      <c r="E575" s="16" t="s">
+        <v>829</v>
+      </c>
+      <c r="F575" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G575" s="17">
+        <v>4</v>
+      </c>
+      <c r="H575" s="18" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="576" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A576" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B576" s="15">
+        <v>45203</v>
+      </c>
+      <c r="C576" s="15">
+        <v>45260</v>
+      </c>
+      <c r="D576" s="15">
+        <v>45222</v>
+      </c>
+      <c r="E576" s="19" t="s">
+        <v>829</v>
+      </c>
+      <c r="F576" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G576" s="20">
+        <v>1</v>
+      </c>
+      <c r="H576" s="21" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="577" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A577" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B577" s="13">
+        <v>45203</v>
+      </c>
+      <c r="C577" s="13">
+        <v>45260</v>
+      </c>
+      <c r="D577" s="13">
+        <v>45231</v>
+      </c>
+      <c r="E577" s="16" t="s">
+        <v>829</v>
+      </c>
+      <c r="F577" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G577" s="17">
+        <v>1</v>
+      </c>
+      <c r="H577" s="18" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="578" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A578" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B578" s="15">
+        <v>45224</v>
+      </c>
+      <c r="C578" s="15">
+        <v>45260</v>
+      </c>
+      <c r="D578" s="15">
+        <v>45285</v>
+      </c>
+      <c r="E578" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="F578" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="G578" s="20">
+        <v>86</v>
+      </c>
+      <c r="H578" s="21" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="579" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A579" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B579" s="13">
+        <v>45208</v>
+      </c>
+      <c r="C579" s="13">
+        <v>45261</v>
+      </c>
+      <c r="D579" s="13">
+        <v>45219</v>
+      </c>
+      <c r="E579" s="16" t="s">
+        <v>833</v>
+      </c>
+      <c r="F579" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G579" s="17">
+        <v>13</v>
+      </c>
+      <c r="H579" s="18" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="580" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A580" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="B580" s="15">
+        <v>45229</v>
+      </c>
+      <c r="C580" s="15">
+        <v>45261</v>
+      </c>
+      <c r="D580" s="15">
+        <v>45291</v>
+      </c>
+      <c r="E580" s="19" t="s">
+        <v>835</v>
+      </c>
+      <c r="F580" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G580" s="20">
+        <v>7</v>
+      </c>
+      <c r="H580" s="21" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="581" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A581" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="B581" s="13">
+        <v>45208</v>
+      </c>
+      <c r="C581" s="13">
+        <v>45261</v>
+      </c>
+      <c r="D581" s="13">
+        <v>45219</v>
+      </c>
+      <c r="E581" s="16" t="s">
+        <v>837</v>
+      </c>
+      <c r="F581" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G581" s="17">
+        <v>7</v>
+      </c>
+      <c r="H581" s="18" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="582" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A582" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="B582" s="15">
+        <v>45208</v>
+      </c>
+      <c r="C582" s="15">
+        <v>45261</v>
+      </c>
+      <c r="D582" s="15">
+        <v>45219</v>
+      </c>
+      <c r="E582" s="19" t="s">
+        <v>837</v>
+      </c>
+      <c r="F582" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G582" s="20">
+        <v>11</v>
+      </c>
+      <c r="H582" s="21" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="583" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A583" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B583" s="13">
+        <v>45208</v>
+      </c>
+      <c r="C583" s="13">
+        <v>45261</v>
+      </c>
+      <c r="D583" s="13">
+        <v>45219</v>
+      </c>
+      <c r="E583" s="16" t="s">
+        <v>833</v>
+      </c>
+      <c r="F583" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G583" s="17">
+        <v>3</v>
+      </c>
+      <c r="H583" s="18" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="584" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A584" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="B584" s="15">
+        <v>45208</v>
+      </c>
+      <c r="C584" s="15">
+        <v>45261</v>
+      </c>
+      <c r="D584" s="15">
+        <v>45219</v>
+      </c>
+      <c r="E584" s="19" t="s">
+        <v>833</v>
+      </c>
+      <c r="F584" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G584" s="20">
+        <v>7</v>
+      </c>
+      <c r="H584" s="21" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="585" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A585" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="B585" s="13">
+        <v>45208</v>
+      </c>
+      <c r="C585" s="13">
+        <v>45261</v>
+      </c>
+      <c r="D585" s="13">
+        <v>45219</v>
+      </c>
+      <c r="E585" s="16" t="s">
+        <v>833</v>
+      </c>
+      <c r="F585" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G585" s="17">
+        <v>16</v>
+      </c>
+      <c r="H585" s="18" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="586" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A586" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="B586" s="15">
+        <v>45208</v>
+      </c>
+      <c r="C586" s="15">
+        <v>45261</v>
+      </c>
+      <c r="D586" s="15">
+        <v>45219</v>
+      </c>
+      <c r="E586" s="19" t="s">
+        <v>833</v>
+      </c>
+      <c r="F586" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G586" s="20">
+        <v>9</v>
+      </c>
+      <c r="H586" s="21" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="587" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A587" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="B587" s="13">
+        <v>45227</v>
+      </c>
+      <c r="C587" s="13">
+        <v>45264</v>
+      </c>
+      <c r="D587" s="13">
+        <v>45227</v>
+      </c>
+      <c r="E587" s="16" t="s">
+        <v>629</v>
+      </c>
+      <c r="F587" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G587" s="17">
+        <v>47</v>
+      </c>
+      <c r="H587" s="18" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="588" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A588" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="B588" s="15">
+        <v>45227</v>
+      </c>
+      <c r="C588" s="15">
+        <v>45264</v>
+      </c>
+      <c r="D588" s="15">
+        <v>45227</v>
+      </c>
+      <c r="E588" s="19" t="s">
+        <v>629</v>
+      </c>
+      <c r="F588" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G588" s="20">
+        <v>1</v>
+      </c>
+      <c r="H588" s="21" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="589" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A589" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B589" s="13">
+        <v>45227</v>
+      </c>
+      <c r="C589" s="13">
+        <v>45264</v>
+      </c>
+      <c r="D589" s="13">
+        <v>45227</v>
+      </c>
+      <c r="E589" s="16" t="s">
+        <v>629</v>
+      </c>
+      <c r="F589" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G589" s="17">
+        <v>13</v>
+      </c>
+      <c r="H589" s="18" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="590" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A590" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B590" s="15">
+        <v>45230</v>
+      </c>
+      <c r="C590" s="15">
+        <v>45264</v>
+      </c>
+      <c r="D590" s="15">
+        <v>45291</v>
+      </c>
+      <c r="E590" s="19" t="s">
+        <v>844</v>
+      </c>
+      <c r="F590" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G590" s="20">
+        <v>52</v>
+      </c>
+      <c r="H590" s="21" t="s">
+        <v>845</v>
       </c>
     </row>
   </sheetData>
@@ -18644,13 +19383,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97F3F67B-1AC3-4EBA-A159-3ABD22C40C37}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{779A0347-8082-49F5-895C-C33AB7010852}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F883A3B5-A1C5-4A52-9EC4-BEE926CAA65B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50ACF8EA-8D23-48CA-B56D-FE193F5286FF}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{75774455-C0FB-438C-BE4F-E3AE10870C57}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{21D28A8F-6DC0-4B06-B775-7F83DFD4E794}"/>
 </file>
--- a/data/warn-scraper/cache/ca/warn_report1.xlsx
+++ b/data/warn-scraper/cache/ca/warn_report1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\WSB-CO\Communications Unit\Website Management\WARN (Worker Adjustment and Retraining Notification) Updates\2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{250C4250-AE91-4AB8-8FC3-6AA50D2CA08A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{623A32BD-6433-421C-B552-A8B155A8E09B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="624" yWindow="684" windowWidth="21600" windowHeight="11436" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2375" uniqueCount="847">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2423" uniqueCount="866">
   <si>
     <t>County/Parish</t>
   </si>
@@ -2642,6 +2642,63 @@
     <t>8745 Aero Drive, Suite 200  San Diego CA 92123</t>
   </si>
   <si>
+    <t>Parker Hannifin Corporation</t>
+  </si>
+  <si>
+    <t>5650 Steward Avenue  Fremont CA 94538</t>
+  </si>
+  <si>
+    <t>PWLC I, Inc.</t>
+  </si>
+  <si>
+    <t>24351 Via Albeniz  Mission Viejo CA 92692</t>
+  </si>
+  <si>
+    <t>Viasat, Inc.</t>
+  </si>
+  <si>
+    <t>6155 El Camino Real  Carlsbad CA 92009</t>
+  </si>
+  <si>
+    <t>Amazon</t>
+  </si>
+  <si>
+    <t>188 Spear St. 2nd Floor  San Francisco CA 94105</t>
+  </si>
+  <si>
+    <t>333 W. San Carlos St. Unit 1700  San Jose CA 95110</t>
+  </si>
+  <si>
+    <t>889 Americana Way  Glendale CA 91210</t>
+  </si>
+  <si>
+    <t>Informatica LLC</t>
+  </si>
+  <si>
+    <t>2100 Seaport Blvd.  Redwood City CA 94063</t>
+  </si>
+  <si>
+    <t>Sangamo Therapeutics, Inc.</t>
+  </si>
+  <si>
+    <t>7000 Marina Blvd  Brisbane CA 94005</t>
+  </si>
+  <si>
+    <t>501 Canal Blvd  Brisbane CA 94005</t>
+  </si>
+  <si>
+    <t>34521 Golden Lantern Stret  Dana Point CA 92629</t>
+  </si>
+  <si>
+    <t>6699 Alvarado Road, STE 2309  San Diego CA 921120</t>
+  </si>
+  <si>
+    <t>Faire Wholesale, Inc.</t>
+  </si>
+  <si>
+    <t>100 Potrero Avenue  San Francisco CA 94103</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">WARN REPORT - </t>
     </r>
@@ -2653,7 +2710,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>07/01/23 to 12/04/23</t>
+      <t>07/01/23 to 12/06/23</t>
     </r>
     <r>
       <rPr>
@@ -2673,7 +2730,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>A detailed WARN summary by county and filtered according to received date. Table Spans cells A2 through H590.</t>
+      <t>A detailed WARN summary by county and filtered according to received date. Table Spans cells A2 through H602.</t>
     </r>
   </si>
 </sst>
@@ -3456,8 +3513,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:H590" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
-  <autoFilter ref="A2:H590" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:H602" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
+  <autoFilter ref="A2:H602" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -3841,7 +3898,7 @@
       </c>
       <c r="B3" s="5">
         <f>SUM('Detailed WARN Report '!G:G)</f>
-        <v>32921</v>
+        <v>33705</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -3850,7 +3907,7 @@
       </c>
       <c r="B4" s="5">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Permanent")</f>
-        <v>378</v>
+        <v>385</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -3867,8 +3924,7 @@
         <v>23</v>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Not Identified")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
@@ -3877,7 +3933,7 @@
       </c>
       <c r="B7" s="5">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Permanent")</f>
-        <v>181</v>
+        <v>186</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -3909,7 +3965,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:H590"/>
+  <dimension ref="A1:H602"/>
   <sheetFormatPr defaultColWidth="26" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.88671875" bestFit="1" customWidth="1"/>
@@ -3922,7 +3978,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="99.6" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
-        <v>846</v>
+        <v>865</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -3930,7 +3986,7 @@
       <c r="G1" s="6"/>
       <c r="H1" s="6"/>
     </row>
-    <row r="2" spans="1:8" ht="24.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
         <v>0</v>
       </c>
@@ -19242,6 +19298,318 @@
       </c>
       <c r="H590" s="21" t="s">
         <v>845</v>
+      </c>
+    </row>
+    <row r="591" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A591" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="B591" s="13">
+        <v>45232</v>
+      </c>
+      <c r="C591" s="13">
+        <v>45265</v>
+      </c>
+      <c r="D591" s="13">
+        <v>45408</v>
+      </c>
+      <c r="E591" s="16" t="s">
+        <v>846</v>
+      </c>
+      <c r="F591" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G591" s="17">
+        <v>4</v>
+      </c>
+      <c r="H591" s="18" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="592" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A592" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="B592" s="15">
+        <v>45229</v>
+      </c>
+      <c r="C592" s="15">
+        <v>45265</v>
+      </c>
+      <c r="D592" s="15">
+        <v>45289</v>
+      </c>
+      <c r="E592" s="19" t="s">
+        <v>848</v>
+      </c>
+      <c r="F592" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G592" s="20">
+        <v>60</v>
+      </c>
+      <c r="H592" s="21" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="593" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A593" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B593" s="13">
+        <v>45231</v>
+      </c>
+      <c r="C593" s="13">
+        <v>45265</v>
+      </c>
+      <c r="D593" s="13">
+        <v>45293</v>
+      </c>
+      <c r="E593" s="16" t="s">
+        <v>850</v>
+      </c>
+      <c r="F593" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G593" s="17">
+        <v>228</v>
+      </c>
+      <c r="H593" s="18" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="594" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A594" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="B594" s="15">
+        <v>45232</v>
+      </c>
+      <c r="C594" s="15">
+        <v>45265</v>
+      </c>
+      <c r="D594" s="15">
+        <v>45307</v>
+      </c>
+      <c r="E594" s="19" t="s">
+        <v>852</v>
+      </c>
+      <c r="F594" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G594" s="20">
+        <v>57</v>
+      </c>
+      <c r="H594" s="21" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="595" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A595" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B595" s="13">
+        <v>45231</v>
+      </c>
+      <c r="C595" s="13">
+        <v>45265</v>
+      </c>
+      <c r="D595" s="13">
+        <v>45293</v>
+      </c>
+      <c r="E595" s="16" t="s">
+        <v>850</v>
+      </c>
+      <c r="F595" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G595" s="17">
+        <v>11</v>
+      </c>
+      <c r="H595" s="18" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="596" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A596" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="B596" s="15">
+        <v>45232</v>
+      </c>
+      <c r="C596" s="15">
+        <v>45265</v>
+      </c>
+      <c r="D596" s="15">
+        <v>45293</v>
+      </c>
+      <c r="E596" s="19" t="s">
+        <v>852</v>
+      </c>
+      <c r="F596" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G596" s="20">
+        <v>114</v>
+      </c>
+      <c r="H596" s="21" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="597" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A597" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="B597" s="13">
+        <v>45231</v>
+      </c>
+      <c r="C597" s="13">
+        <v>45266</v>
+      </c>
+      <c r="D597" s="13">
+        <v>45291</v>
+      </c>
+      <c r="E597" s="16" t="s">
+        <v>856</v>
+      </c>
+      <c r="F597" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G597" s="17">
+        <v>90</v>
+      </c>
+      <c r="H597" s="18" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="598" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A598" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="B598" s="15">
+        <v>45231</v>
+      </c>
+      <c r="C598" s="15">
+        <v>45266</v>
+      </c>
+      <c r="D598" s="15">
+        <v>45293</v>
+      </c>
+      <c r="E598" s="19" t="s">
+        <v>858</v>
+      </c>
+      <c r="F598" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G598" s="20">
+        <v>65</v>
+      </c>
+      <c r="H598" s="21" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="599" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A599" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="B599" s="13">
+        <v>45231</v>
+      </c>
+      <c r="C599" s="13">
+        <v>45266</v>
+      </c>
+      <c r="D599" s="13">
+        <v>45293</v>
+      </c>
+      <c r="E599" s="16" t="s">
+        <v>858</v>
+      </c>
+      <c r="F599" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G599" s="17">
+        <v>37</v>
+      </c>
+      <c r="H599" s="18" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="600" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A600" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="B600" s="15">
+        <v>45236</v>
+      </c>
+      <c r="C600" s="15">
+        <v>45266</v>
+      </c>
+      <c r="D600" s="15">
+        <v>45296</v>
+      </c>
+      <c r="E600" s="19" t="s">
+        <v>658</v>
+      </c>
+      <c r="F600" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G600" s="20">
+        <v>42</v>
+      </c>
+      <c r="H600" s="21" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="601" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A601" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B601" s="13">
+        <v>45231</v>
+      </c>
+      <c r="C601" s="13">
+        <v>45266</v>
+      </c>
+      <c r="D601" s="13">
+        <v>45291</v>
+      </c>
+      <c r="E601" s="16" t="s">
+        <v>823</v>
+      </c>
+      <c r="F601" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G601" s="17">
+        <v>6</v>
+      </c>
+      <c r="H601" s="18" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="602" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A602" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="B602" s="15">
+        <v>45230</v>
+      </c>
+      <c r="C602" s="15">
+        <v>45266</v>
+      </c>
+      <c r="D602" s="15">
+        <v>45231</v>
+      </c>
+      <c r="E602" s="19" t="s">
+        <v>863</v>
+      </c>
+      <c r="F602" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G602" s="20">
+        <v>70</v>
+      </c>
+      <c r="H602" s="21" t="s">
+        <v>864</v>
       </c>
     </row>
   </sheetData>
@@ -19383,13 +19751,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{779A0347-8082-49F5-895C-C33AB7010852}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A163450D-64D5-4CD4-B3F8-AB34544890D5}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50ACF8EA-8D23-48CA-B56D-FE193F5286FF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBF41D6E-4406-4F06-974E-F55B0CCD2036}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{21D28A8F-6DC0-4B06-B775-7F83DFD4E794}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{450AC859-7E74-4964-ABF1-BB6E6F1960B9}"/>
 </file>
--- a/data/warn-scraper/cache/ca/warn_report1.xlsx
+++ b/data/warn-scraper/cache/ca/warn_report1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\WSB-CO\Communications Unit\Website Management\WARN (Worker Adjustment and Retraining Notification) Updates\2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{623A32BD-6433-421C-B552-A8B155A8E09B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDD01F9D-5173-4EAB-B400-BF1A68D9C3DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="624" yWindow="684" windowWidth="21600" windowHeight="11436" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2423" uniqueCount="866">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2495" uniqueCount="888">
   <si>
     <t>County/Parish</t>
   </si>
@@ -2699,6 +2699,72 @@
     <t>100 Potrero Avenue  San Francisco CA 94103</t>
   </si>
   <si>
+    <t>Organic Milling - Allen Facility</t>
+  </si>
+  <si>
+    <t>505 W. Allen Ave.  San Dimas CA 91773</t>
+  </si>
+  <si>
+    <t>Organic Milling - Acacia Facility</t>
+  </si>
+  <si>
+    <t>305 S. Acacia St.  San Dimas CA 91773</t>
+  </si>
+  <si>
+    <t>Daiso Distribution Center</t>
+  </si>
+  <si>
+    <t>16400 Trojan Way  La Mirada CA 90638</t>
+  </si>
+  <si>
+    <t>Flex LTD</t>
+  </si>
+  <si>
+    <t>847 Gibraltar Drive  Milpitas CA 95035</t>
+  </si>
+  <si>
+    <t>Nextdoor, Inc.</t>
+  </si>
+  <si>
+    <t>420 Taylor St.  San Francisco CA 94102</t>
+  </si>
+  <si>
+    <t>ForgeRock, Inc.</t>
+  </si>
+  <si>
+    <t>201 Mission St. Suite 2900  San Francisco CA 94105</t>
+  </si>
+  <si>
+    <t>Charles Schwab &amp; Co., Inc.</t>
+  </si>
+  <si>
+    <t>211 Main Street  San Francisco CA 94105</t>
+  </si>
+  <si>
+    <t>Pac-12 Enterprises, LLC</t>
+  </si>
+  <si>
+    <t>12647 Alcosta Boulevard, 5th Floor  San Ramon CA 94583</t>
+  </si>
+  <si>
+    <t>St James Infirmary</t>
+  </si>
+  <si>
+    <t>1087-1089 Mission St  San Francisco CA 94103</t>
+  </si>
+  <si>
+    <t>Analog Devices, Inc.</t>
+  </si>
+  <si>
+    <t>90 Rio Robles  San Jose CA 95134</t>
+  </si>
+  <si>
+    <t>130 Rio Robles  San Jose CA 95134</t>
+  </si>
+  <si>
+    <t>160 Rio Robles  San Jose CA 95134</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">WARN REPORT - </t>
     </r>
@@ -2710,7 +2776,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>07/01/23 to 12/06/23</t>
+      <t>07/01/23 to 12/11/23</t>
     </r>
     <r>
       <rPr>
@@ -2730,7 +2796,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>A detailed WARN summary by county and filtered according to received date. Table Spans cells A2 through H602.</t>
+      <t>A detailed WARN summary by county and filtered according to received date. Table Spans cells A2 through H620.</t>
     </r>
   </si>
 </sst>
@@ -3513,8 +3579,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:H602" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
-  <autoFilter ref="A2:H602" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:H620" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
+  <autoFilter ref="A2:H620" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -3898,7 +3964,7 @@
       </c>
       <c r="B3" s="5">
         <f>SUM('Detailed WARN Report '!G:G)</f>
-        <v>33705</v>
+        <v>34504</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -3907,7 +3973,7 @@
       </c>
       <c r="B4" s="5">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Permanent")</f>
-        <v>385</v>
+        <v>401</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -3933,7 +3999,7 @@
       </c>
       <c r="B7" s="5">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Permanent")</f>
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -3965,7 +4031,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:H602"/>
+  <dimension ref="A1:H620"/>
   <sheetFormatPr defaultColWidth="26" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.88671875" bestFit="1" customWidth="1"/>
@@ -3978,7 +4044,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="99.6" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
-        <v>865</v>
+        <v>887</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -19610,6 +19676,474 @@
       </c>
       <c r="H602" s="21" t="s">
         <v>864</v>
+      </c>
+    </row>
+    <row r="603" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A603" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B603" s="13">
+        <v>45231</v>
+      </c>
+      <c r="C603" s="13">
+        <v>45267</v>
+      </c>
+      <c r="D603" s="13">
+        <v>45231</v>
+      </c>
+      <c r="E603" s="16" t="s">
+        <v>865</v>
+      </c>
+      <c r="F603" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G603" s="17">
+        <v>7</v>
+      </c>
+      <c r="H603" s="18" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="604" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A604" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="B604" s="15">
+        <v>45231</v>
+      </c>
+      <c r="C604" s="15">
+        <v>45267</v>
+      </c>
+      <c r="D604" s="15">
+        <v>45231</v>
+      </c>
+      <c r="E604" s="19" t="s">
+        <v>867</v>
+      </c>
+      <c r="F604" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G604" s="20">
+        <v>1</v>
+      </c>
+      <c r="H604" s="21" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="605" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A605" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B605" s="13">
+        <v>45232</v>
+      </c>
+      <c r="C605" s="13">
+        <v>45267</v>
+      </c>
+      <c r="D605" s="13">
+        <v>45338</v>
+      </c>
+      <c r="E605" s="16" t="s">
+        <v>869</v>
+      </c>
+      <c r="F605" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G605" s="17">
+        <v>74</v>
+      </c>
+      <c r="H605" s="18" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="606" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A606" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="B606" s="15">
+        <v>45237</v>
+      </c>
+      <c r="C606" s="15">
+        <v>45267</v>
+      </c>
+      <c r="D606" s="15">
+        <v>45297</v>
+      </c>
+      <c r="E606" s="19" t="s">
+        <v>871</v>
+      </c>
+      <c r="F606" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G606" s="20">
+        <v>31</v>
+      </c>
+      <c r="H606" s="21" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="607" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A607" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="B607" s="13">
+        <v>45237</v>
+      </c>
+      <c r="C607" s="13">
+        <v>45267</v>
+      </c>
+      <c r="D607" s="13">
+        <v>45239</v>
+      </c>
+      <c r="E607" s="16" t="s">
+        <v>873</v>
+      </c>
+      <c r="F607" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G607" s="17">
+        <v>99</v>
+      </c>
+      <c r="H607" s="18" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="608" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A608" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="B608" s="15">
+        <v>45237</v>
+      </c>
+      <c r="C608" s="15">
+        <v>45267</v>
+      </c>
+      <c r="D608" s="15">
+        <v>45212</v>
+      </c>
+      <c r="E608" s="19" t="s">
+        <v>875</v>
+      </c>
+      <c r="F608" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G608" s="20">
+        <v>1</v>
+      </c>
+      <c r="H608" s="21" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="609" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A609" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="B609" s="13">
+        <v>45237</v>
+      </c>
+      <c r="C609" s="13">
+        <v>45267</v>
+      </c>
+      <c r="D609" s="13">
+        <v>45298</v>
+      </c>
+      <c r="E609" s="16" t="s">
+        <v>875</v>
+      </c>
+      <c r="F609" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G609" s="17">
+        <v>1</v>
+      </c>
+      <c r="H609" s="18" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="610" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A610" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="B610" s="15">
+        <v>45237</v>
+      </c>
+      <c r="C610" s="15">
+        <v>45267</v>
+      </c>
+      <c r="D610" s="15">
+        <v>45322</v>
+      </c>
+      <c r="E610" s="19" t="s">
+        <v>875</v>
+      </c>
+      <c r="F610" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G610" s="20">
+        <v>1</v>
+      </c>
+      <c r="H610" s="21" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="611" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A611" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="B611" s="13">
+        <v>45237</v>
+      </c>
+      <c r="C611" s="13">
+        <v>45267</v>
+      </c>
+      <c r="D611" s="13">
+        <v>45323</v>
+      </c>
+      <c r="E611" s="16" t="s">
+        <v>875</v>
+      </c>
+      <c r="F611" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G611" s="17">
+        <v>1</v>
+      </c>
+      <c r="H611" s="18" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="612" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A612" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="B612" s="15">
+        <v>45237</v>
+      </c>
+      <c r="C612" s="15">
+        <v>45267</v>
+      </c>
+      <c r="D612" s="15">
+        <v>45351</v>
+      </c>
+      <c r="E612" s="19" t="s">
+        <v>875</v>
+      </c>
+      <c r="F612" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G612" s="20">
+        <v>1</v>
+      </c>
+      <c r="H612" s="21" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="613" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A613" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="B613" s="13">
+        <v>45237</v>
+      </c>
+      <c r="C613" s="13">
+        <v>45267</v>
+      </c>
+      <c r="D613" s="13">
+        <v>45382</v>
+      </c>
+      <c r="E613" s="16" t="s">
+        <v>875</v>
+      </c>
+      <c r="F613" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G613" s="17">
+        <v>1</v>
+      </c>
+      <c r="H613" s="18" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="614" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A614" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="B614" s="15">
+        <v>45237</v>
+      </c>
+      <c r="C614" s="15">
+        <v>45267</v>
+      </c>
+      <c r="D614" s="15">
+        <v>45473</v>
+      </c>
+      <c r="E614" s="19" t="s">
+        <v>875</v>
+      </c>
+      <c r="F614" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G614" s="20">
+        <v>103</v>
+      </c>
+      <c r="H614" s="21" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="615" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A615" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="B615" s="13">
+        <v>45236</v>
+      </c>
+      <c r="C615" s="13">
+        <v>45267</v>
+      </c>
+      <c r="D615" s="13">
+        <v>45296</v>
+      </c>
+      <c r="E615" s="16" t="s">
+        <v>877</v>
+      </c>
+      <c r="F615" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G615" s="17">
+        <v>155</v>
+      </c>
+      <c r="H615" s="18" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="616" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A616" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B616" s="15">
+        <v>45233</v>
+      </c>
+      <c r="C616" s="15">
+        <v>45271</v>
+      </c>
+      <c r="D616" s="15">
+        <v>45296</v>
+      </c>
+      <c r="E616" s="19" t="s">
+        <v>879</v>
+      </c>
+      <c r="F616" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G616" s="20">
+        <v>141</v>
+      </c>
+      <c r="H616" s="21" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="617" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A617" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="B617" s="13">
+        <v>45232</v>
+      </c>
+      <c r="C617" s="13">
+        <v>45271</v>
+      </c>
+      <c r="D617" s="13">
+        <v>45292</v>
+      </c>
+      <c r="E617" s="16" t="s">
+        <v>881</v>
+      </c>
+      <c r="F617" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G617" s="17">
+        <v>71</v>
+      </c>
+      <c r="H617" s="18" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="618" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A618" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="B618" s="15">
+        <v>45233</v>
+      </c>
+      <c r="C618" s="15">
+        <v>45271</v>
+      </c>
+      <c r="D618" s="15">
+        <v>45303</v>
+      </c>
+      <c r="E618" s="19" t="s">
+        <v>883</v>
+      </c>
+      <c r="F618" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G618" s="20">
+        <v>109</v>
+      </c>
+      <c r="H618" s="21" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="619" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A619" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B619" s="13">
+        <v>45233</v>
+      </c>
+      <c r="C619" s="13">
+        <v>45271</v>
+      </c>
+      <c r="D619" s="13">
+        <v>45303</v>
+      </c>
+      <c r="E619" s="16" t="s">
+        <v>883</v>
+      </c>
+      <c r="F619" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G619" s="17">
+        <v>1</v>
+      </c>
+      <c r="H619" s="18" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="620" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A620" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="B620" s="15">
+        <v>45233</v>
+      </c>
+      <c r="C620" s="15">
+        <v>45271</v>
+      </c>
+      <c r="D620" s="15">
+        <v>45303</v>
+      </c>
+      <c r="E620" s="19" t="s">
+        <v>883</v>
+      </c>
+      <c r="F620" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G620" s="20">
+        <v>1</v>
+      </c>
+      <c r="H620" s="21" t="s">
+        <v>886</v>
       </c>
     </row>
   </sheetData>
@@ -19751,13 +20285,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A163450D-64D5-4CD4-B3F8-AB34544890D5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E84E538-2F65-477F-A3F2-10935D6DF2BF}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBF41D6E-4406-4F06-974E-F55B0CCD2036}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9562333A-43BC-4B9E-922A-54ACFAF29DD0}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{450AC859-7E74-4964-ABF1-BB6E6F1960B9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2835DBA7-FD3A-4C05-B23F-0F51300F44EF}"/>
 </file>
--- a/data/warn-scraper/cache/ca/warn_report1.xlsx
+++ b/data/warn-scraper/cache/ca/warn_report1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\WSB-CO\Communications Unit\Website Management\WARN (Worker Adjustment and Retraining Notification) Updates\2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDD01F9D-5173-4EAB-B400-BF1A68D9C3DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{527ECFE3-28DC-4821-A55A-0B3EFED1C9E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="624" yWindow="684" windowWidth="21600" windowHeight="11436" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2495" uniqueCount="888">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2619" uniqueCount="925">
   <si>
     <t>County/Parish</t>
   </si>
@@ -2765,6 +2765,117 @@
     <t>160 Rio Robles  San Jose CA 95134</t>
   </si>
   <si>
+    <t>Kaiser Foundation Hospitals - Fair Oaks</t>
+  </si>
+  <si>
+    <t>75 N. Fair Oaks Ave.  Pasadena CA 91103</t>
+  </si>
+  <si>
+    <t>25825 Vermont Ave.  Harbor City CA 90710</t>
+  </si>
+  <si>
+    <t>4900 Rivergrade Rd. Ste.C-110  Baldwin Park CA 91706</t>
+  </si>
+  <si>
+    <t>1200 El Camino Real  South San Francisco CA 94080</t>
+  </si>
+  <si>
+    <t>Kaiser Foundation Hospitals - Lakeside</t>
+  </si>
+  <si>
+    <t>300 Lakeside Dr.  Oakland CA 94612</t>
+  </si>
+  <si>
+    <t>Kaiser Foundation Hospitals - One</t>
+  </si>
+  <si>
+    <t>One Kaiser Plaza  Oakland CA 94612</t>
+  </si>
+  <si>
+    <t>1840 California Ave.  Corona CA 92881</t>
+  </si>
+  <si>
+    <t>12254 Bellflower Blvd.  Downey CA 90242</t>
+  </si>
+  <si>
+    <t>3100 Thornton AVe.  Burbank CA 91504</t>
+  </si>
+  <si>
+    <t>25 N. Via Monte  Walnut Creek CA 94598</t>
+  </si>
+  <si>
+    <t>Oracle America, Inc. at Adventist Health</t>
+  </si>
+  <si>
+    <t>One Adventist Health Way  Roseville CA 95661</t>
+  </si>
+  <si>
+    <t>Rico Corp. dba D' Addario Woodwinds</t>
+  </si>
+  <si>
+    <t>Kaiser Foundation Hospitals - Arrow</t>
+  </si>
+  <si>
+    <t>10850 Arrow Rte.  Rancho Cucamonga CA 91730</t>
+  </si>
+  <si>
+    <t>Global Expedited Transportation, Inc.</t>
+  </si>
+  <si>
+    <t>10370 Commerce Center Dr. Suite B210  Rancho Cucamonga CA 91730</t>
+  </si>
+  <si>
+    <t>Kaiser Foundation Hospitals - Canyon</t>
+  </si>
+  <si>
+    <t>3840 Murphy Canyon Rd.  San Diego CA 92123</t>
+  </si>
+  <si>
+    <t>Kaiser Foundation Hospitals - Mission</t>
+  </si>
+  <si>
+    <t>10990 S.D. Mission Rd.  San Diego CA 92108</t>
+  </si>
+  <si>
+    <t>Kaiser Foundation Hospitals - Rio</t>
+  </si>
+  <si>
+    <t>Acutus Medical, Inc.</t>
+  </si>
+  <si>
+    <t>2210 Faraday Avenue Suite 100  Carlsbad CA 92008</t>
+  </si>
+  <si>
+    <t>2210 Faraday Avenue, Suite 100  Carlsbad CA 92008</t>
+  </si>
+  <si>
+    <t>Splunk Inc.</t>
+  </si>
+  <si>
+    <t>250 Brannan Street  San Francisco CA 94107</t>
+  </si>
+  <si>
+    <t>500 Santana Row  San Jose CA 95128</t>
+  </si>
+  <si>
+    <t>122 East Brokaw Road  San Jose CA 95112</t>
+  </si>
+  <si>
+    <t>The Apothecarium</t>
+  </si>
+  <si>
+    <t>1850 41st Avenue  Capitola CA 95010</t>
+  </si>
+  <si>
+    <t>Atara Biotherapeutics</t>
+  </si>
+  <si>
+    <t>2380 Conejo Spectrum Street #200  Thousand Oaks CA 91320</t>
+  </si>
+  <si>
+    <t>1280 Rancho Conejo Blvd.  Thousand Oaks CA 91320</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">WARN REPORT - </t>
     </r>
@@ -2776,7 +2887,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>07/01/23 to 12/11/23</t>
+      <t>07/01/23 to 12/13/23</t>
     </r>
     <r>
       <rPr>
@@ -2796,7 +2907,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>A detailed WARN summary by county and filtered according to received date. Table Spans cells A2 through H620.</t>
+      <t>A detailed WARN summary by county and filtered according to received date. Table Spans cells A2 through H651.</t>
     </r>
   </si>
 </sst>
@@ -3579,8 +3690,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:H620" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
-  <autoFilter ref="A2:H620" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:H651" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
+  <autoFilter ref="A2:H651" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -3964,7 +4075,7 @@
       </c>
       <c r="B3" s="5">
         <f>SUM('Detailed WARN Report '!G:G)</f>
-        <v>34504</v>
+        <v>35524</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -3973,7 +4084,7 @@
       </c>
       <c r="B4" s="5">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Permanent")</f>
-        <v>401</v>
+        <v>428</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -3982,7 +4093,7 @@
       </c>
       <c r="B5" s="5">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Temporary")</f>
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
@@ -3999,7 +4110,7 @@
       </c>
       <c r="B7" s="5">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Permanent")</f>
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -4031,7 +4142,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:H620"/>
+  <dimension ref="A1:H651"/>
   <sheetFormatPr defaultColWidth="26" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.88671875" bestFit="1" customWidth="1"/>
@@ -4044,7 +4155,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="99.6" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
-        <v>887</v>
+        <v>924</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -4052,7 +4163,7 @@
       <c r="G1" s="6"/>
       <c r="H1" s="6"/>
     </row>
-    <row r="2" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
         <v>0</v>
       </c>
@@ -15633,7 +15744,7 @@
         <v>45225</v>
       </c>
       <c r="D447" s="13">
-        <v>45257</v>
+        <v>45280</v>
       </c>
       <c r="E447" s="16" t="s">
         <v>662</v>
@@ -20144,6 +20255,812 @@
       </c>
       <c r="H620" s="21" t="s">
         <v>886</v>
+      </c>
+    </row>
+    <row r="621" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A621" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B621" s="13">
+        <v>45236</v>
+      </c>
+      <c r="C621" s="13">
+        <v>45272</v>
+      </c>
+      <c r="D621" s="13">
+        <v>45295</v>
+      </c>
+      <c r="E621" s="16" t="s">
+        <v>464</v>
+      </c>
+      <c r="F621" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G621" s="17">
+        <v>26</v>
+      </c>
+      <c r="H621" s="18" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="622" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A622" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="B622" s="15">
+        <v>45236</v>
+      </c>
+      <c r="C622" s="15">
+        <v>45272</v>
+      </c>
+      <c r="D622" s="15">
+        <v>45295</v>
+      </c>
+      <c r="E622" s="19" t="s">
+        <v>467</v>
+      </c>
+      <c r="F622" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G622" s="20">
+        <v>22</v>
+      </c>
+      <c r="H622" s="21" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="623" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A623" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B623" s="13">
+        <v>45236</v>
+      </c>
+      <c r="C623" s="13">
+        <v>45272</v>
+      </c>
+      <c r="D623" s="13">
+        <v>45295</v>
+      </c>
+      <c r="E623" s="16" t="s">
+        <v>887</v>
+      </c>
+      <c r="F623" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G623" s="17">
+        <v>2</v>
+      </c>
+      <c r="H623" s="18" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="624" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A624" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="B624" s="15">
+        <v>45236</v>
+      </c>
+      <c r="C624" s="15">
+        <v>45272</v>
+      </c>
+      <c r="D624" s="15">
+        <v>45295</v>
+      </c>
+      <c r="E624" s="19" t="s">
+        <v>464</v>
+      </c>
+      <c r="F624" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G624" s="20">
+        <v>1</v>
+      </c>
+      <c r="H624" s="21" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="625" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A625" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B625" s="13">
+        <v>45236</v>
+      </c>
+      <c r="C625" s="13">
+        <v>45272</v>
+      </c>
+      <c r="D625" s="13">
+        <v>45295</v>
+      </c>
+      <c r="E625" s="16" t="s">
+        <v>464</v>
+      </c>
+      <c r="F625" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G625" s="17">
+        <v>1</v>
+      </c>
+      <c r="H625" s="18" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="626" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A626" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="B626" s="15">
+        <v>45236</v>
+      </c>
+      <c r="C626" s="15">
+        <v>45272</v>
+      </c>
+      <c r="D626" s="15">
+        <v>45295</v>
+      </c>
+      <c r="E626" s="19" t="s">
+        <v>464</v>
+      </c>
+      <c r="F626" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G626" s="20">
+        <v>1</v>
+      </c>
+      <c r="H626" s="21" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="627" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A627" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="B627" s="13">
+        <v>45236</v>
+      </c>
+      <c r="C627" s="13">
+        <v>45272</v>
+      </c>
+      <c r="D627" s="13">
+        <v>45295</v>
+      </c>
+      <c r="E627" s="16" t="s">
+        <v>892</v>
+      </c>
+      <c r="F627" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G627" s="17">
+        <v>4</v>
+      </c>
+      <c r="H627" s="18" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="628" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A628" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="B628" s="15">
+        <v>45236</v>
+      </c>
+      <c r="C628" s="15">
+        <v>45272</v>
+      </c>
+      <c r="D628" s="15">
+        <v>45295</v>
+      </c>
+      <c r="E628" s="19" t="s">
+        <v>478</v>
+      </c>
+      <c r="F628" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G628" s="20">
+        <v>6</v>
+      </c>
+      <c r="H628" s="21" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="629" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A629" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="B629" s="13">
+        <v>45236</v>
+      </c>
+      <c r="C629" s="13">
+        <v>45272</v>
+      </c>
+      <c r="D629" s="13">
+        <v>45295</v>
+      </c>
+      <c r="E629" s="16" t="s">
+        <v>894</v>
+      </c>
+      <c r="F629" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G629" s="17">
+        <v>2</v>
+      </c>
+      <c r="H629" s="18" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="630" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A630" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B630" s="15">
+        <v>45236</v>
+      </c>
+      <c r="C630" s="15">
+        <v>45272</v>
+      </c>
+      <c r="D630" s="15">
+        <v>45295</v>
+      </c>
+      <c r="E630" s="19" t="s">
+        <v>464</v>
+      </c>
+      <c r="F630" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G630" s="20">
+        <v>4</v>
+      </c>
+      <c r="H630" s="21" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="631" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A631" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B631" s="13">
+        <v>45233</v>
+      </c>
+      <c r="C631" s="13">
+        <v>45272</v>
+      </c>
+      <c r="D631" s="13">
+        <v>45291</v>
+      </c>
+      <c r="E631" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="F631" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G631" s="17">
+        <v>235</v>
+      </c>
+      <c r="H631" s="18" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="632" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A632" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="B632" s="15">
+        <v>45236</v>
+      </c>
+      <c r="C632" s="15">
+        <v>45272</v>
+      </c>
+      <c r="D632" s="15">
+        <v>45295</v>
+      </c>
+      <c r="E632" s="19" t="s">
+        <v>464</v>
+      </c>
+      <c r="F632" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G632" s="20">
+        <v>1</v>
+      </c>
+      <c r="H632" s="21" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="633" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A633" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B633" s="13">
+        <v>45236</v>
+      </c>
+      <c r="C633" s="13">
+        <v>45272</v>
+      </c>
+      <c r="D633" s="13">
+        <v>45295</v>
+      </c>
+      <c r="E633" s="16" t="s">
+        <v>464</v>
+      </c>
+      <c r="F633" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G633" s="17">
+        <v>20</v>
+      </c>
+      <c r="H633" s="18" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="634" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A634" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="B634" s="15">
+        <v>45236</v>
+      </c>
+      <c r="C634" s="15">
+        <v>45273</v>
+      </c>
+      <c r="D634" s="15">
+        <v>45295</v>
+      </c>
+      <c r="E634" s="19" t="s">
+        <v>464</v>
+      </c>
+      <c r="F634" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G634" s="20">
+        <v>41</v>
+      </c>
+      <c r="H634" s="21" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="635" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A635" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B635" s="13">
+        <v>45236</v>
+      </c>
+      <c r="C635" s="13">
+        <v>45273</v>
+      </c>
+      <c r="D635" s="13">
+        <v>45295</v>
+      </c>
+      <c r="E635" s="16" t="s">
+        <v>464</v>
+      </c>
+      <c r="F635" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="G635" s="17">
+        <v>1</v>
+      </c>
+      <c r="H635" s="18" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="636" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A636" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B636" s="15">
+        <v>45243</v>
+      </c>
+      <c r="C636" s="15">
+        <v>45273</v>
+      </c>
+      <c r="D636" s="15">
+        <v>45303</v>
+      </c>
+      <c r="E636" s="19" t="s">
+        <v>900</v>
+      </c>
+      <c r="F636" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G636" s="20">
+        <v>65</v>
+      </c>
+      <c r="H636" s="21" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="637" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A637" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B637" s="13">
+        <v>45236</v>
+      </c>
+      <c r="C637" s="13">
+        <v>45273</v>
+      </c>
+      <c r="D637" s="13">
+        <v>45310</v>
+      </c>
+      <c r="E637" s="16" t="s">
+        <v>902</v>
+      </c>
+      <c r="F637" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G637" s="17">
+        <v>26</v>
+      </c>
+      <c r="H637" s="18" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="638" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A638" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="B638" s="15">
+        <v>45236</v>
+      </c>
+      <c r="C638" s="15">
+        <v>45273</v>
+      </c>
+      <c r="D638" s="15">
+        <v>45295</v>
+      </c>
+      <c r="E638" s="19" t="s">
+        <v>464</v>
+      </c>
+      <c r="F638" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G638" s="20">
+        <v>6</v>
+      </c>
+      <c r="H638" s="21" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="639" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A639" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="B639" s="13">
+        <v>45236</v>
+      </c>
+      <c r="C639" s="13">
+        <v>45273</v>
+      </c>
+      <c r="D639" s="13">
+        <v>45295</v>
+      </c>
+      <c r="E639" s="16" t="s">
+        <v>903</v>
+      </c>
+      <c r="F639" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G639" s="17">
+        <v>1</v>
+      </c>
+      <c r="H639" s="18" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="640" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A640" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="B640" s="15">
+        <v>45238</v>
+      </c>
+      <c r="C640" s="15">
+        <v>45273</v>
+      </c>
+      <c r="D640" s="15">
+        <v>45306</v>
+      </c>
+      <c r="E640" s="19" t="s">
+        <v>905</v>
+      </c>
+      <c r="F640" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G640" s="20">
+        <v>51</v>
+      </c>
+      <c r="H640" s="21" t="s">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="641" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A641" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B641" s="13">
+        <v>45236</v>
+      </c>
+      <c r="C641" s="13">
+        <v>45273</v>
+      </c>
+      <c r="D641" s="13">
+        <v>45295</v>
+      </c>
+      <c r="E641" s="16" t="s">
+        <v>907</v>
+      </c>
+      <c r="F641" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G641" s="17">
+        <v>8</v>
+      </c>
+      <c r="H641" s="18" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="642" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A642" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B642" s="15">
+        <v>45236</v>
+      </c>
+      <c r="C642" s="15">
+        <v>45273</v>
+      </c>
+      <c r="D642" s="15">
+        <v>45295</v>
+      </c>
+      <c r="E642" s="19" t="s">
+        <v>909</v>
+      </c>
+      <c r="F642" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G642" s="20">
+        <v>1</v>
+      </c>
+      <c r="H642" s="21" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="643" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A643" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B643" s="13">
+        <v>45236</v>
+      </c>
+      <c r="C643" s="13">
+        <v>45273</v>
+      </c>
+      <c r="D643" s="13">
+        <v>45295</v>
+      </c>
+      <c r="E643" s="16" t="s">
+        <v>911</v>
+      </c>
+      <c r="F643" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G643" s="17">
+        <v>5</v>
+      </c>
+      <c r="H643" s="18" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="644" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A644" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B644" s="15">
+        <v>45238</v>
+      </c>
+      <c r="C644" s="15">
+        <v>45273</v>
+      </c>
+      <c r="D644" s="15">
+        <v>45298</v>
+      </c>
+      <c r="E644" s="19" t="s">
+        <v>912</v>
+      </c>
+      <c r="F644" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G644" s="20">
+        <v>140</v>
+      </c>
+      <c r="H644" s="21" t="s">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="645" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A645" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B645" s="13">
+        <v>45238</v>
+      </c>
+      <c r="C645" s="13">
+        <v>45273</v>
+      </c>
+      <c r="D645" s="13">
+        <v>45328</v>
+      </c>
+      <c r="E645" s="16" t="s">
+        <v>912</v>
+      </c>
+      <c r="F645" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G645" s="17">
+        <v>7</v>
+      </c>
+      <c r="H645" s="18" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="646" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A646" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="B646" s="15">
+        <v>45231</v>
+      </c>
+      <c r="C646" s="15">
+        <v>45273</v>
+      </c>
+      <c r="D646" s="15">
+        <v>45278</v>
+      </c>
+      <c r="E646" s="19" t="s">
+        <v>915</v>
+      </c>
+      <c r="F646" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G646" s="20">
+        <v>44</v>
+      </c>
+      <c r="H646" s="21" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="647" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A647" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B647" s="13">
+        <v>45231</v>
+      </c>
+      <c r="C647" s="13">
+        <v>45273</v>
+      </c>
+      <c r="D647" s="13">
+        <v>45278</v>
+      </c>
+      <c r="E647" s="16" t="s">
+        <v>915</v>
+      </c>
+      <c r="F647" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G647" s="17">
+        <v>132</v>
+      </c>
+      <c r="H647" s="18" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="648" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A648" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="B648" s="15">
+        <v>45239</v>
+      </c>
+      <c r="C648" s="15">
+        <v>45273</v>
+      </c>
+      <c r="D648" s="15">
+        <v>45299</v>
+      </c>
+      <c r="E648" s="19" t="s">
+        <v>305</v>
+      </c>
+      <c r="F648" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G648" s="20">
+        <v>87</v>
+      </c>
+      <c r="H648" s="21" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="649" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A649" s="12" t="s">
+        <v>789</v>
+      </c>
+      <c r="B649" s="13">
+        <v>45243</v>
+      </c>
+      <c r="C649" s="13">
+        <v>45273</v>
+      </c>
+      <c r="D649" s="13">
+        <v>45303</v>
+      </c>
+      <c r="E649" s="16" t="s">
+        <v>919</v>
+      </c>
+      <c r="F649" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G649" s="17">
+        <v>7</v>
+      </c>
+      <c r="H649" s="18" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="650" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A650" s="14" t="s">
+        <v>282</v>
+      </c>
+      <c r="B650" s="15">
+        <v>45231</v>
+      </c>
+      <c r="C650" s="15">
+        <v>45273</v>
+      </c>
+      <c r="D650" s="15">
+        <v>45291</v>
+      </c>
+      <c r="E650" s="19" t="s">
+        <v>921</v>
+      </c>
+      <c r="F650" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G650" s="20">
+        <v>72</v>
+      </c>
+      <c r="H650" s="21" t="s">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="651" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A651" s="12" t="s">
+        <v>282</v>
+      </c>
+      <c r="B651" s="13">
+        <v>45231</v>
+      </c>
+      <c r="C651" s="13">
+        <v>45273</v>
+      </c>
+      <c r="D651" s="13">
+        <v>45291</v>
+      </c>
+      <c r="E651" s="16" t="s">
+        <v>921</v>
+      </c>
+      <c r="F651" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G651" s="17">
+        <v>1</v>
+      </c>
+      <c r="H651" s="18" t="s">
+        <v>923</v>
       </c>
     </row>
   </sheetData>
@@ -20285,13 +21202,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E84E538-2F65-477F-A3F2-10935D6DF2BF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ACBADEC5-19FA-4C96-BDB7-7E865E63669C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9562333A-43BC-4B9E-922A-54ACFAF29DD0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6C6D04E-1A93-400F-B2C0-35619BAB5383}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2835DBA7-FD3A-4C05-B23F-0F51300F44EF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FE0E8F8F-B4D9-4546-8D3B-F512BDDDF4A5}"/>
 </file>
--- a/data/warn-scraper/cache/ca/warn_report1.xlsx
+++ b/data/warn-scraper/cache/ca/warn_report1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26626"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\WSB-CO\Communications Unit\Website Management\WARN (Worker Adjustment and Retraining Notification) Updates\2023\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BVang\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{527ECFE3-28DC-4821-A55A-0B3EFED1C9E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C49BA018-AE1D-4AF2-ADEA-272DDCD68F87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="624" yWindow="684" windowWidth="21600" windowHeight="11436" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
   <sheets>
     <sheet name="Index" sheetId="3" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2619" uniqueCount="925">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2751" uniqueCount="950">
   <si>
     <t>County/Parish</t>
   </si>
@@ -2876,6 +2876,81 @@
     <t>1280 Rancho Conejo Blvd.  Thousand Oaks CA 91320</t>
   </si>
   <si>
+    <t>Hyperloop One</t>
+  </si>
+  <si>
+    <t>777 S. Alameda St. Suite 400  Los Angeles CA 90021</t>
+  </si>
+  <si>
+    <t>Merced County</t>
+  </si>
+  <si>
+    <t>TVT Trucking, Inc. and FTU Labor Contractors</t>
+  </si>
+  <si>
+    <t>8480 Church Street  Gilroy CA 95341</t>
+  </si>
+  <si>
+    <t>Marvell Semiconductor, Inc.</t>
+  </si>
+  <si>
+    <t>5488 Marvell Lane  Santa Clara CA 95054</t>
+  </si>
+  <si>
+    <t>15485 Sand Canyon Ave.  Irvine CA 92618</t>
+  </si>
+  <si>
+    <t>AHMC San Gabriel Valley Medical Center LP dba San Gabriel Valley Medical Center</t>
+  </si>
+  <si>
+    <t>438 West Las Tunas Drive  San Gabriel CA 91776</t>
+  </si>
+  <si>
+    <t>TriLink Biotechnologies, LLC and Maravai Intermediate Holdings, LLC</t>
+  </si>
+  <si>
+    <t>10770 Wateridge Cir.  San Diego CA 92121</t>
+  </si>
+  <si>
+    <t>5717 Pacific Center Blvd.  San Diego CA 92121</t>
+  </si>
+  <si>
+    <t>10240 Flanders Ct.  San Diego CA 92121</t>
+  </si>
+  <si>
+    <t>10247 Flanders Ct.  San Diego CA 92121</t>
+  </si>
+  <si>
+    <t>Virgin Galactic, LLC</t>
+  </si>
+  <si>
+    <t>16555 Spaceship Landing Way  Mojave CA 93501</t>
+  </si>
+  <si>
+    <t>1223 Sabovich Street  Mojave CA 93501</t>
+  </si>
+  <si>
+    <t>1682 Sabovich Street, Suite #B  Mojave CA 93501</t>
+  </si>
+  <si>
+    <t>1246 Barnes Street  Mojave CA 93501</t>
+  </si>
+  <si>
+    <t>2250 Mission College Boulevard  Santa Clara CA 95054</t>
+  </si>
+  <si>
+    <t>Agilent Technologies, Inc.</t>
+  </si>
+  <si>
+    <t>5301 Stevens Creek Blvd.  Santa Clara CA 95051</t>
+  </si>
+  <si>
+    <t>Owens-Brockway Glass Container, Inc.</t>
+  </si>
+  <si>
+    <t>14700 W. Schulte Road  Tracy CA 95377</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">WARN REPORT - </t>
     </r>
@@ -2887,7 +2962,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>07/01/23 to 12/13/23</t>
+      <t>07/01/23 to 12/18/23</t>
     </r>
     <r>
       <rPr>
@@ -2907,7 +2982,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>A detailed WARN summary by county and filtered according to received date. Table Spans cells A2 through H651.</t>
+      <t>A detailed WARN summary by county and filtered according to received date. Table Spans cells A2 through H684.</t>
     </r>
   </si>
 </sst>
@@ -3213,8 +3288,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF0F0F0"/>
-          <bgColor rgb="FFF0F0F0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -3254,8 +3329,8 @@
       <numFmt numFmtId="165" formatCode="[$-10436]#,##0;\(#,##0\)"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF0F0F0"/>
-          <bgColor rgb="FFF0F0F0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -3294,8 +3369,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF0F0F0"/>
-          <bgColor rgb="FFF0F0F0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -3334,8 +3409,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF0F0F0"/>
-          <bgColor rgb="FFF0F0F0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -3375,8 +3450,8 @@
       <numFmt numFmtId="164" formatCode="[$-10409]mm/dd/yyyy"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF0F0F0"/>
-          <bgColor rgb="FFF0F0F0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -3416,8 +3491,8 @@
       <numFmt numFmtId="164" formatCode="[$-10409]mm/dd/yyyy"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF0F0F0"/>
-          <bgColor rgb="FFF0F0F0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -3457,8 +3532,8 @@
       <numFmt numFmtId="164" formatCode="[$-10409]mm/dd/yyyy"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF0F0F0"/>
-          <bgColor rgb="FFF0F0F0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -3497,8 +3572,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF0F0F0"/>
-          <bgColor rgb="FFF0F0F0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -3690,8 +3765,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:H651" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
-  <autoFilter ref="A2:H651" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:H684" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
+  <autoFilter ref="A2:H684" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -4013,27 +4088,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D341DFFF-02D2-4572-95F5-BB3221952133}">
   <dimension ref="A1:A4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="66.109375" customWidth="1"/>
+    <col min="1" max="1" width="66.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" ht="105" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="21" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:1" ht="21" x14ac:dyDescent="0.35">
       <c r="A2" s="8" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>154</v>
       </c>
@@ -4050,18 +4125,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1832896D-8AFB-4FFC-957E-910308F3BC0C}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29" customWidth="1"/>
-    <col min="2" max="2" width="12.44140625" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="75.599999999999994" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>28</v>
       </c>
@@ -4069,34 +4144,34 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>152</v>
       </c>
       <c r="B3" s="5">
         <f>SUM('Detailed WARN Report '!G:G)</f>
-        <v>35524</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+        <v>36205</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B4" s="5">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Permanent")</f>
-        <v>428</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B5" s="5">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Temporary")</f>
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>23</v>
       </c>
@@ -4104,16 +4179,16 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B7" s="5">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Permanent")</f>
-        <v>191</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>25</v>
       </c>
@@ -4122,7 +4197,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>26</v>
       </c>
@@ -4142,20 +4217,20 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:H651"/>
-  <sheetFormatPr defaultColWidth="26" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:H684"/>
+  <sheetFormatPr defaultColWidth="26" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="54.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="58.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="59.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="58.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="99.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="117" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>924</v>
+        <v>949</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -4163,7 +4238,7 @@
       <c r="G1" s="6"/>
       <c r="H1" s="6"/>
     </row>
-    <row r="2" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
         <v>0</v>
       </c>
@@ -4189,7 +4264,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
         <v>14</v>
       </c>
@@ -4215,7 +4290,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
         <v>13</v>
       </c>
@@ -4241,7 +4316,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
         <v>12</v>
       </c>
@@ -4267,7 +4342,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
         <v>6</v>
       </c>
@@ -4293,7 +4368,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
         <v>6</v>
       </c>
@@ -4319,7 +4394,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
         <v>5</v>
       </c>
@@ -4345,7 +4420,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
         <v>8</v>
       </c>
@@ -4371,7 +4446,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
         <v>5</v>
       </c>
@@ -4397,7 +4472,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
         <v>39</v>
       </c>
@@ -4423,7 +4498,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
         <v>11</v>
       </c>
@@ -4449,7 +4524,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
         <v>11</v>
       </c>
@@ -4475,7 +4550,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
         <v>9</v>
       </c>
@@ -4501,7 +4576,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
         <v>7</v>
       </c>
@@ -4527,7 +4602,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
         <v>10</v>
       </c>
@@ -4553,7 +4628,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
         <v>10</v>
       </c>
@@ -4579,7 +4654,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
         <v>5</v>
       </c>
@@ -4605,7 +4680,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
         <v>52</v>
       </c>
@@ -4631,7 +4706,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
         <v>5</v>
       </c>
@@ -4657,7 +4732,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
         <v>5</v>
       </c>
@@ -4683,7 +4758,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
         <v>13</v>
       </c>
@@ -4709,7 +4784,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
         <v>7</v>
       </c>
@@ -4735,7 +4810,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
         <v>5</v>
       </c>
@@ -4761,7 +4836,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
         <v>5</v>
       </c>
@@ -4787,7 +4862,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
         <v>63</v>
       </c>
@@ -4813,7 +4888,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="s">
         <v>66</v>
       </c>
@@ -4839,7 +4914,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="14" t="s">
         <v>6</v>
       </c>
@@ -4865,7 +4940,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
         <v>7</v>
       </c>
@@ -4891,7 +4966,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="14" t="s">
         <v>11</v>
       </c>
@@ -4917,7 +4992,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
         <v>11</v>
       </c>
@@ -4943,7 +5018,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="14" t="s">
         <v>11</v>
       </c>
@@ -4969,7 +5044,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="12" t="s">
         <v>9</v>
       </c>
@@ -4995,7 +5070,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="14" t="s">
         <v>76</v>
       </c>
@@ -5021,7 +5096,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="12" t="s">
         <v>79</v>
       </c>
@@ -5047,7 +5122,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="14" t="s">
         <v>79</v>
       </c>
@@ -5073,7 +5148,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
         <v>66</v>
       </c>
@@ -5099,7 +5174,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="14" t="s">
         <v>6</v>
       </c>
@@ -5125,7 +5200,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="12" t="s">
         <v>86</v>
       </c>
@@ -5151,7 +5226,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="14" t="s">
         <v>63</v>
       </c>
@@ -5177,7 +5252,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="12" t="s">
         <v>63</v>
       </c>
@@ -5203,7 +5278,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="14" t="s">
         <v>76</v>
       </c>
@@ -5229,7 +5304,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="12" t="s">
         <v>6</v>
       </c>
@@ -5255,7 +5330,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="14" t="s">
         <v>6</v>
       </c>
@@ -5281,7 +5356,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="12" t="s">
         <v>97</v>
       </c>
@@ -5307,7 +5382,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="14" t="s">
         <v>86</v>
       </c>
@@ -5333,7 +5408,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="12" t="s">
         <v>13</v>
       </c>
@@ -5359,7 +5434,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="14" t="s">
         <v>5</v>
       </c>
@@ -5385,7 +5460,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="12" t="s">
         <v>63</v>
       </c>
@@ -5411,7 +5486,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="14" t="s">
         <v>52</v>
       </c>
@@ -5437,7 +5512,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="12" t="s">
         <v>52</v>
       </c>
@@ -5463,7 +5538,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="14" t="s">
         <v>12</v>
       </c>
@@ -5489,7 +5564,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="12" t="s">
         <v>6</v>
       </c>
@@ -5515,7 +5590,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="14" t="s">
         <v>52</v>
       </c>
@@ -5541,7 +5616,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="12" t="s">
         <v>5</v>
       </c>
@@ -5567,7 +5642,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="14" t="s">
         <v>76</v>
       </c>
@@ -5593,7 +5668,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="12" t="s">
         <v>52</v>
       </c>
@@ -5619,7 +5694,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="14" t="s">
         <v>52</v>
       </c>
@@ -5645,7 +5720,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="12" t="s">
         <v>52</v>
       </c>
@@ -5671,7 +5746,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="14" t="s">
         <v>52</v>
       </c>
@@ -5697,7 +5772,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="12" t="s">
         <v>52</v>
       </c>
@@ -5723,7 +5798,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="14" t="s">
         <v>7</v>
       </c>
@@ -5749,7 +5824,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="12" t="s">
         <v>7</v>
       </c>
@@ -5775,7 +5850,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="14" t="s">
         <v>52</v>
       </c>
@@ -5801,7 +5876,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="12" t="s">
         <v>52</v>
       </c>
@@ -5827,7 +5902,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="14" t="s">
         <v>52</v>
       </c>
@@ -5853,7 +5928,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="12" t="s">
         <v>52</v>
       </c>
@@ -5879,7 +5954,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="14" t="s">
         <v>52</v>
       </c>
@@ -5905,7 +5980,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="12" t="s">
         <v>86</v>
       </c>
@@ -5931,7 +6006,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="14" t="s">
         <v>86</v>
       </c>
@@ -5957,7 +6032,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="12" t="s">
         <v>135</v>
       </c>
@@ -5983,7 +6058,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="14" t="s">
         <v>5</v>
       </c>
@@ -6009,7 +6084,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="12" t="s">
         <v>6</v>
       </c>
@@ -6035,7 +6110,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="14" t="s">
         <v>86</v>
       </c>
@@ -6061,7 +6136,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="12" t="s">
         <v>86</v>
       </c>
@@ -6087,7 +6162,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="14" t="s">
         <v>86</v>
       </c>
@@ -6113,7 +6188,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="12" t="s">
         <v>86</v>
       </c>
@@ -6139,7 +6214,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="14" t="s">
         <v>5</v>
       </c>
@@ -6165,7 +6240,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="12" t="s">
         <v>66</v>
       </c>
@@ -6191,7 +6266,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="14" t="s">
         <v>66</v>
       </c>
@@ -6217,7 +6292,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="12" t="s">
         <v>5</v>
       </c>
@@ -6243,7 +6318,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="14" t="s">
         <v>5</v>
       </c>
@@ -6269,7 +6344,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="12" t="s">
         <v>5</v>
       </c>
@@ -6295,7 +6370,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="14" t="s">
         <v>63</v>
       </c>
@@ -6321,7 +6396,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="12" t="s">
         <v>6</v>
       </c>
@@ -6347,7 +6422,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="14" t="s">
         <v>52</v>
       </c>
@@ -6373,7 +6448,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="12" t="s">
         <v>86</v>
       </c>
@@ -6399,7 +6474,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="14" t="s">
         <v>6</v>
       </c>
@@ -6425,7 +6500,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="12" t="s">
         <v>86</v>
       </c>
@@ -6451,7 +6526,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" s="14" t="s">
         <v>63</v>
       </c>
@@ -6477,7 +6552,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="12" t="s">
         <v>175</v>
       </c>
@@ -6503,7 +6578,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" s="14" t="s">
         <v>6</v>
       </c>
@@ -6529,7 +6604,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="12" t="s">
         <v>6</v>
       </c>
@@ -6555,7 +6630,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" s="14" t="s">
         <v>6</v>
       </c>
@@ -6581,7 +6656,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" s="12" t="s">
         <v>6</v>
       </c>
@@ -6607,7 +6682,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" s="14" t="s">
         <v>6</v>
       </c>
@@ -6633,7 +6708,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" s="12" t="s">
         <v>6</v>
       </c>
@@ -6659,7 +6734,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" s="14" t="s">
         <v>97</v>
       </c>
@@ -6685,7 +6760,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" s="12" t="s">
         <v>5</v>
       </c>
@@ -6711,7 +6786,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" s="14" t="s">
         <v>7</v>
       </c>
@@ -6737,7 +6812,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" s="12" t="s">
         <v>5</v>
       </c>
@@ -6763,7 +6838,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" s="14" t="s">
         <v>5</v>
       </c>
@@ -6789,7 +6864,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" s="12" t="s">
         <v>5</v>
       </c>
@@ -6815,7 +6890,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" s="14" t="s">
         <v>5</v>
       </c>
@@ -6841,7 +6916,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" s="12" t="s">
         <v>5</v>
       </c>
@@ -6867,7 +6942,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" s="14" t="s">
         <v>5</v>
       </c>
@@ -6893,7 +6968,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" s="12" t="s">
         <v>5</v>
       </c>
@@ -6919,7 +6994,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" s="14" t="s">
         <v>5</v>
       </c>
@@ -6945,7 +7020,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" s="12" t="s">
         <v>52</v>
       </c>
@@ -6971,7 +7046,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" s="14" t="s">
         <v>9</v>
       </c>
@@ -6997,7 +7072,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" s="12" t="s">
         <v>76</v>
       </c>
@@ -7023,7 +7098,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" s="14" t="s">
         <v>212</v>
       </c>
@@ -7049,7 +7124,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" s="12" t="s">
         <v>52</v>
       </c>
@@ -7075,7 +7150,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" s="14" t="s">
         <v>86</v>
       </c>
@@ -7101,7 +7176,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" s="12" t="s">
         <v>5</v>
       </c>
@@ -7127,7 +7202,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" s="14" t="s">
         <v>5</v>
       </c>
@@ -7153,7 +7228,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" s="12" t="s">
         <v>76</v>
       </c>
@@ -7179,7 +7254,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" s="14" t="s">
         <v>14</v>
       </c>
@@ -7205,7 +7280,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" s="12" t="s">
         <v>5</v>
       </c>
@@ -7231,7 +7306,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" s="14" t="s">
         <v>7</v>
       </c>
@@ -7257,7 +7332,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" s="12" t="s">
         <v>52</v>
       </c>
@@ -7283,7 +7358,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" s="14" t="s">
         <v>9</v>
       </c>
@@ -7309,7 +7384,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" s="12" t="s">
         <v>7</v>
       </c>
@@ -7335,7 +7410,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" s="14" t="s">
         <v>86</v>
       </c>
@@ -7361,7 +7436,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" s="12" t="s">
         <v>233</v>
       </c>
@@ -7387,7 +7462,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" s="14" t="s">
         <v>236</v>
       </c>
@@ -7413,7 +7488,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" s="12" t="s">
         <v>63</v>
       </c>
@@ -7439,7 +7514,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" s="14" t="s">
         <v>63</v>
       </c>
@@ -7465,7 +7540,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" s="12" t="s">
         <v>63</v>
       </c>
@@ -7491,7 +7566,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" s="14" t="s">
         <v>7</v>
       </c>
@@ -7517,7 +7592,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" s="12" t="s">
         <v>66</v>
       </c>
@@ -7543,7 +7618,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" s="14" t="s">
         <v>66</v>
       </c>
@@ -7569,7 +7644,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" s="12" t="s">
         <v>9</v>
       </c>
@@ -7595,7 +7670,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" s="14" t="s">
         <v>76</v>
       </c>
@@ -7621,7 +7696,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" s="12" t="s">
         <v>76</v>
       </c>
@@ -7647,7 +7722,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" s="14" t="s">
         <v>76</v>
       </c>
@@ -7673,7 +7748,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" s="12" t="s">
         <v>6</v>
       </c>
@@ -7699,7 +7774,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" s="14" t="s">
         <v>6</v>
       </c>
@@ -7725,7 +7800,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" s="12" t="s">
         <v>252</v>
       </c>
@@ -7751,7 +7826,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" s="14" t="s">
         <v>5</v>
       </c>
@@ -7777,7 +7852,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141" s="12" t="s">
         <v>7</v>
       </c>
@@ -7803,7 +7878,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142" s="14" t="s">
         <v>7</v>
       </c>
@@ -7829,7 +7904,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143" s="12" t="s">
         <v>7</v>
       </c>
@@ -7855,7 +7930,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144" s="14" t="s">
         <v>7</v>
       </c>
@@ -7881,7 +7956,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145" s="12" t="s">
         <v>6</v>
       </c>
@@ -7907,7 +7982,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146" s="14" t="s">
         <v>6</v>
       </c>
@@ -7933,7 +8008,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147" s="12" t="s">
         <v>6</v>
       </c>
@@ -7959,7 +8034,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A148" s="14" t="s">
         <v>97</v>
       </c>
@@ -7985,7 +8060,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A149" s="12" t="s">
         <v>7</v>
       </c>
@@ -8011,7 +8086,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A150" s="14" t="s">
         <v>5</v>
       </c>
@@ -8037,7 +8112,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A151" s="12" t="s">
         <v>212</v>
       </c>
@@ -8063,7 +8138,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A152" s="14" t="s">
         <v>86</v>
       </c>
@@ -8089,7 +8164,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A153" s="12" t="s">
         <v>13</v>
       </c>
@@ -8115,7 +8190,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A154" s="14" t="s">
         <v>268</v>
       </c>
@@ -8141,7 +8216,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A155" s="12" t="s">
         <v>270</v>
       </c>
@@ -8167,7 +8242,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A156" s="14" t="s">
         <v>8</v>
       </c>
@@ -8193,7 +8268,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A157" s="12" t="s">
         <v>5</v>
       </c>
@@ -8219,7 +8294,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A158" s="14" t="s">
         <v>5</v>
       </c>
@@ -8245,7 +8320,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A159" s="12" t="s">
         <v>5</v>
       </c>
@@ -8271,7 +8346,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A160" s="14" t="s">
         <v>5</v>
       </c>
@@ -8297,7 +8372,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A161" s="12" t="s">
         <v>5</v>
       </c>
@@ -8323,7 +8398,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A162" s="14" t="s">
         <v>278</v>
       </c>
@@ -8349,7 +8424,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A163" s="12" t="s">
         <v>79</v>
       </c>
@@ -8375,7 +8450,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A164" s="14" t="s">
         <v>175</v>
       </c>
@@ -8401,7 +8476,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A165" s="12" t="s">
         <v>282</v>
       </c>
@@ -8427,7 +8502,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A166" s="14" t="s">
         <v>284</v>
       </c>
@@ -8453,7 +8528,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A167" s="12" t="s">
         <v>5</v>
       </c>
@@ -8479,7 +8554,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A168" s="14" t="s">
         <v>11</v>
       </c>
@@ -8505,7 +8580,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A169" s="12" t="s">
         <v>52</v>
       </c>
@@ -8531,7 +8606,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A170" s="14" t="s">
         <v>7</v>
       </c>
@@ -8557,7 +8632,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A171" s="12" t="s">
         <v>14</v>
       </c>
@@ -8583,7 +8658,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A172" s="14" t="s">
         <v>7</v>
       </c>
@@ -8609,7 +8684,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A173" s="12" t="s">
         <v>7</v>
       </c>
@@ -8635,7 +8710,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A174" s="14" t="s">
         <v>7</v>
       </c>
@@ -8661,7 +8736,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A175" s="12" t="s">
         <v>52</v>
       </c>
@@ -8687,7 +8762,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A176" s="14" t="s">
         <v>302</v>
       </c>
@@ -8713,7 +8788,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A177" s="12" t="s">
         <v>86</v>
       </c>
@@ -8739,7 +8814,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A178" s="14" t="s">
         <v>86</v>
       </c>
@@ -8765,7 +8840,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A179" s="12" t="s">
         <v>66</v>
       </c>
@@ -8791,7 +8866,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A180" s="14" t="s">
         <v>5</v>
       </c>
@@ -8817,7 +8892,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A181" s="12" t="s">
         <v>63</v>
       </c>
@@ -8843,7 +8918,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A182" s="14" t="s">
         <v>6</v>
       </c>
@@ -8869,7 +8944,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A183" s="12" t="s">
         <v>6</v>
       </c>
@@ -8895,7 +8970,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A184" s="14" t="s">
         <v>6</v>
       </c>
@@ -8921,7 +8996,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A185" s="12" t="s">
         <v>63</v>
       </c>
@@ -8947,7 +9022,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A186" s="14" t="s">
         <v>63</v>
       </c>
@@ -8973,7 +9048,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A187" s="12" t="s">
         <v>63</v>
       </c>
@@ -8999,7 +9074,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A188" s="14" t="s">
         <v>7</v>
       </c>
@@ -9025,7 +9100,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A189" s="12" t="s">
         <v>7</v>
       </c>
@@ -9051,7 +9126,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A190" s="14" t="s">
         <v>7</v>
       </c>
@@ -9077,7 +9152,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A191" s="12" t="s">
         <v>7</v>
       </c>
@@ -9103,7 +9178,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A192" s="14" t="s">
         <v>7</v>
       </c>
@@ -9129,7 +9204,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A193" s="12" t="s">
         <v>6</v>
       </c>
@@ -9155,7 +9230,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A194" s="14" t="s">
         <v>302</v>
       </c>
@@ -9181,7 +9256,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A195" s="12" t="s">
         <v>14</v>
       </c>
@@ -9207,7 +9282,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A196" s="14" t="s">
         <v>7</v>
       </c>
@@ -9233,7 +9308,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A197" s="12" t="s">
         <v>5</v>
       </c>
@@ -9259,7 +9334,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A198" s="14" t="s">
         <v>6</v>
       </c>
@@ -9285,7 +9360,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A199" s="12" t="s">
         <v>5</v>
       </c>
@@ -9311,7 +9386,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A200" s="14" t="s">
         <v>5</v>
       </c>
@@ -9337,7 +9412,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A201" s="12" t="s">
         <v>5</v>
       </c>
@@ -9363,7 +9438,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A202" s="14" t="s">
         <v>5</v>
       </c>
@@ -9389,7 +9464,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A203" s="12" t="s">
         <v>13</v>
       </c>
@@ -9415,7 +9490,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A204" s="14" t="s">
         <v>66</v>
       </c>
@@ -9441,7 +9516,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A205" s="12" t="s">
         <v>175</v>
       </c>
@@ -9467,7 +9542,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A206" s="14" t="s">
         <v>6</v>
       </c>
@@ -9493,7 +9568,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A207" s="12" t="s">
         <v>52</v>
       </c>
@@ -9519,7 +9594,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A208" s="14" t="s">
         <v>236</v>
       </c>
@@ -9545,7 +9620,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A209" s="12" t="s">
         <v>52</v>
       </c>
@@ -9571,7 +9646,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A210" s="14" t="s">
         <v>5</v>
       </c>
@@ -9597,7 +9672,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A211" s="12" t="s">
         <v>7</v>
       </c>
@@ -9623,7 +9698,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A212" s="14" t="s">
         <v>7</v>
       </c>
@@ -9649,7 +9724,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A213" s="12" t="s">
         <v>5</v>
       </c>
@@ -9675,7 +9750,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A214" s="14" t="s">
         <v>368</v>
       </c>
@@ -9701,7 +9776,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A215" s="12" t="s">
         <v>79</v>
       </c>
@@ -9727,7 +9802,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A216" s="14" t="s">
         <v>14</v>
       </c>
@@ -9753,7 +9828,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A217" s="12" t="s">
         <v>63</v>
       </c>
@@ -9779,7 +9854,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A218" s="14" t="s">
         <v>9</v>
       </c>
@@ -9805,7 +9880,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A219" s="12" t="s">
         <v>6</v>
       </c>
@@ -9831,7 +9906,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A220" s="14" t="s">
         <v>5</v>
       </c>
@@ -9857,7 +9932,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A221" s="12" t="s">
         <v>5</v>
       </c>
@@ -9883,7 +9958,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A222" s="14" t="s">
         <v>5</v>
       </c>
@@ -9909,7 +9984,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A223" s="12" t="s">
         <v>86</v>
       </c>
@@ -9935,7 +10010,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A224" s="14" t="s">
         <v>66</v>
       </c>
@@ -9961,7 +10036,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="225" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A225" s="12" t="s">
         <v>9</v>
       </c>
@@ -9987,7 +10062,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="226" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A226" s="14" t="s">
         <v>86</v>
       </c>
@@ -10013,7 +10088,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="227" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A227" s="12" t="s">
         <v>8</v>
       </c>
@@ -10039,7 +10114,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="228" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A228" s="14" t="s">
         <v>39</v>
       </c>
@@ -10065,7 +10140,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="229" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A229" s="12" t="s">
         <v>5</v>
       </c>
@@ -10091,7 +10166,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="230" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A230" s="14" t="s">
         <v>8</v>
       </c>
@@ -10117,7 +10192,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="231" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A231" s="12" t="s">
         <v>86</v>
       </c>
@@ -10143,7 +10218,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="232" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A232" s="14" t="s">
         <v>86</v>
       </c>
@@ -10169,7 +10244,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="233" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A233" s="12" t="s">
         <v>86</v>
       </c>
@@ -10195,7 +10270,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="234" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A234" s="14" t="s">
         <v>6</v>
       </c>
@@ -10221,7 +10296,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="235" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A235" s="12" t="s">
         <v>6</v>
       </c>
@@ -10247,7 +10322,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="236" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A236" s="14" t="s">
         <v>6</v>
       </c>
@@ -10273,7 +10348,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="237" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A237" s="12" t="s">
         <v>6</v>
       </c>
@@ -10299,7 +10374,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="238" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A238" s="14" t="s">
         <v>6</v>
       </c>
@@ -10325,7 +10400,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="239" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A239" s="12" t="s">
         <v>6</v>
       </c>
@@ -10351,7 +10426,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="240" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A240" s="14" t="s">
         <v>97</v>
       </c>
@@ -10377,7 +10452,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="241" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A241" s="12" t="s">
         <v>7</v>
       </c>
@@ -10403,7 +10478,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="242" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A242" s="14" t="s">
         <v>252</v>
       </c>
@@ -10429,7 +10504,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="243" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A243" s="12" t="s">
         <v>63</v>
       </c>
@@ -10455,7 +10530,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="244" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A244" s="14" t="s">
         <v>63</v>
       </c>
@@ -10481,7 +10556,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="245" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A245" s="12" t="s">
         <v>63</v>
       </c>
@@ -10507,7 +10582,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="246" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A246" s="14" t="s">
         <v>63</v>
       </c>
@@ -10533,7 +10608,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="247" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A247" s="12" t="s">
         <v>5</v>
       </c>
@@ -10559,7 +10634,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="248" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A248" s="14" t="s">
         <v>14</v>
       </c>
@@ -10585,7 +10660,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="249" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A249" s="12" t="s">
         <v>7</v>
       </c>
@@ -10611,7 +10686,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="250" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A250" s="14" t="s">
         <v>7</v>
       </c>
@@ -10637,7 +10712,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="251" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A251" s="12" t="s">
         <v>11</v>
       </c>
@@ -10663,7 +10738,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="252" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A252" s="14" t="s">
         <v>6</v>
       </c>
@@ -10689,7 +10764,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="253" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A253" s="12" t="s">
         <v>6</v>
       </c>
@@ -10715,7 +10790,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="254" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A254" s="14" t="s">
         <v>6</v>
       </c>
@@ -10741,7 +10816,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="255" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A255" s="12" t="s">
         <v>6</v>
       </c>
@@ -10767,7 +10842,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="256" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A256" s="14" t="s">
         <v>86</v>
       </c>
@@ -10793,7 +10868,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="257" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A257" s="12" t="s">
         <v>5</v>
       </c>
@@ -10819,7 +10894,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="258" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A258" s="14" t="s">
         <v>5</v>
       </c>
@@ -10845,7 +10920,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="259" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A259" s="12" t="s">
         <v>63</v>
       </c>
@@ -10871,7 +10946,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="260" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A260" s="14" t="s">
         <v>63</v>
       </c>
@@ -10897,7 +10972,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="261" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A261" s="12" t="s">
         <v>66</v>
       </c>
@@ -10923,7 +10998,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="262" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A262" s="14" t="s">
         <v>76</v>
       </c>
@@ -10949,7 +11024,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="263" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A263" s="12" t="s">
         <v>6</v>
       </c>
@@ -10975,7 +11050,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="264" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A264" s="14" t="s">
         <v>6</v>
       </c>
@@ -11001,7 +11076,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="265" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A265" s="12" t="s">
         <v>5</v>
       </c>
@@ -11027,7 +11102,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="266" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A266" s="14" t="s">
         <v>5</v>
       </c>
@@ -11053,7 +11128,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="267" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A267" s="12" t="s">
         <v>5</v>
       </c>
@@ -11079,7 +11154,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="268" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A268" s="14" t="s">
         <v>5</v>
       </c>
@@ -11105,7 +11180,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="269" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A269" s="12" t="s">
         <v>5</v>
       </c>
@@ -11131,7 +11206,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="270" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A270" s="14" t="s">
         <v>5</v>
       </c>
@@ -11157,7 +11232,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="271" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A271" s="12" t="s">
         <v>5</v>
       </c>
@@ -11183,7 +11258,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="272" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A272" s="14" t="s">
         <v>5</v>
       </c>
@@ -11209,7 +11284,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="273" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A273" s="12" t="s">
         <v>66</v>
       </c>
@@ -11235,7 +11310,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="274" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A274" s="14" t="s">
         <v>11</v>
       </c>
@@ -11261,7 +11336,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="275" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A275" s="12" t="s">
         <v>11</v>
       </c>
@@ -11287,7 +11362,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="276" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A276" s="14" t="s">
         <v>9</v>
       </c>
@@ -11313,7 +11388,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="277" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A277" s="12" t="s">
         <v>52</v>
       </c>
@@ -11339,7 +11414,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="278" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A278" s="14" t="s">
         <v>52</v>
       </c>
@@ -11365,7 +11440,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="279" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A279" s="12" t="s">
         <v>52</v>
       </c>
@@ -11391,7 +11466,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="280" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A280" s="14" t="s">
         <v>52</v>
       </c>
@@ -11417,7 +11492,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="281" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A281" s="12" t="s">
         <v>52</v>
       </c>
@@ -11443,7 +11518,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="282" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A282" s="14" t="s">
         <v>52</v>
       </c>
@@ -11469,7 +11544,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="283" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A283" s="12" t="s">
         <v>52</v>
       </c>
@@ -11495,7 +11570,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="284" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A284" s="14" t="s">
         <v>52</v>
       </c>
@@ -11521,7 +11596,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="285" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A285" s="12" t="s">
         <v>52</v>
       </c>
@@ -11547,7 +11622,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="286" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A286" s="14" t="s">
         <v>52</v>
       </c>
@@ -11573,7 +11648,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="287" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A287" s="12" t="s">
         <v>52</v>
       </c>
@@ -11599,7 +11674,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="288" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A288" s="14" t="s">
         <v>5</v>
       </c>
@@ -11625,7 +11700,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="289" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A289" s="12" t="s">
         <v>66</v>
       </c>
@@ -11651,7 +11726,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="290" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A290" s="14" t="s">
         <v>368</v>
       </c>
@@ -11677,7 +11752,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="291" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A291" s="12" t="s">
         <v>5</v>
       </c>
@@ -11703,7 +11778,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="292" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A292" s="14" t="s">
         <v>5</v>
       </c>
@@ -11729,7 +11804,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="293" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A293" s="12" t="s">
         <v>66</v>
       </c>
@@ -11755,7 +11830,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="294" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A294" s="14" t="s">
         <v>11</v>
       </c>
@@ -11781,7 +11856,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="295" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A295" s="12" t="s">
         <v>11</v>
       </c>
@@ -11807,7 +11882,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="296" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A296" s="14" t="s">
         <v>11</v>
       </c>
@@ -11833,7 +11908,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="297" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A297" s="12" t="s">
         <v>11</v>
       </c>
@@ -11859,7 +11934,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="298" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A298" s="14" t="s">
         <v>66</v>
       </c>
@@ -11885,7 +11960,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="299" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A299" s="12" t="s">
         <v>66</v>
       </c>
@@ -11911,7 +11986,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="300" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A300" s="14" t="s">
         <v>66</v>
       </c>
@@ -11937,7 +12012,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="301" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A301" s="12" t="s">
         <v>66</v>
       </c>
@@ -11963,7 +12038,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="302" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A302" s="14" t="s">
         <v>66</v>
       </c>
@@ -11989,7 +12064,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="303" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A303" s="12" t="s">
         <v>66</v>
       </c>
@@ -12015,7 +12090,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="304" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A304" s="14" t="s">
         <v>175</v>
       </c>
@@ -12041,7 +12116,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="305" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A305" s="12" t="s">
         <v>86</v>
       </c>
@@ -12067,7 +12142,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="306" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A306" s="14" t="s">
         <v>5</v>
       </c>
@@ -12093,7 +12168,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="307" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A307" s="12" t="s">
         <v>5</v>
       </c>
@@ -12119,7 +12194,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="308" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A308" s="14" t="s">
         <v>5</v>
       </c>
@@ -12145,7 +12220,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="309" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A309" s="12" t="s">
         <v>5</v>
       </c>
@@ -12171,7 +12246,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="310" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A310" s="14" t="s">
         <v>5</v>
       </c>
@@ -12197,7 +12272,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="311" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A311" s="12" t="s">
         <v>86</v>
       </c>
@@ -12223,7 +12298,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="312" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A312" s="14" t="s">
         <v>86</v>
       </c>
@@ -12249,7 +12324,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="313" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A313" s="12" t="s">
         <v>86</v>
       </c>
@@ -12275,7 +12350,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="314" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A314" s="14" t="s">
         <v>66</v>
       </c>
@@ -12301,7 +12376,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="315" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A315" s="12" t="s">
         <v>66</v>
       </c>
@@ -12327,7 +12402,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="316" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A316" s="14" t="s">
         <v>66</v>
       </c>
@@ -12353,7 +12428,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="317" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A317" s="12" t="s">
         <v>66</v>
       </c>
@@ -12379,7 +12454,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="318" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A318" s="14" t="s">
         <v>11</v>
       </c>
@@ -12405,7 +12480,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="319" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A319" s="12" t="s">
         <v>76</v>
       </c>
@@ -12431,7 +12506,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="320" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A320" s="14" t="s">
         <v>6</v>
       </c>
@@ -12457,7 +12532,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="321" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A321" s="12" t="s">
         <v>6</v>
       </c>
@@ -12483,7 +12558,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="322" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A322" s="14" t="s">
         <v>5</v>
       </c>
@@ -12509,7 +12584,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="323" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A323" s="12" t="s">
         <v>8</v>
       </c>
@@ -12535,7 +12610,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="324" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A324" s="14" t="s">
         <v>8</v>
       </c>
@@ -12561,7 +12636,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="325" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A325" s="12" t="s">
         <v>8</v>
       </c>
@@ -12587,7 +12662,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="326" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A326" s="14" t="s">
         <v>8</v>
       </c>
@@ -12613,7 +12688,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="327" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A327" s="12" t="s">
         <v>8</v>
       </c>
@@ -12639,7 +12714,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="328" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A328" s="14" t="s">
         <v>8</v>
       </c>
@@ -12665,7 +12740,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="329" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A329" s="12" t="s">
         <v>8</v>
       </c>
@@ -12691,7 +12766,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="330" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A330" s="14" t="s">
         <v>8</v>
       </c>
@@ -12717,7 +12792,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="331" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A331" s="12" t="s">
         <v>9</v>
       </c>
@@ -12743,7 +12818,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="332" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A332" s="14" t="s">
         <v>9</v>
       </c>
@@ -12769,7 +12844,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="333" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A333" s="12" t="s">
         <v>6</v>
       </c>
@@ -12795,7 +12870,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="334" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A334" s="14" t="s">
         <v>252</v>
       </c>
@@ -12821,7 +12896,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="335" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A335" s="12" t="s">
         <v>5</v>
       </c>
@@ -12847,7 +12922,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="336" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A336" s="14" t="s">
         <v>5</v>
       </c>
@@ -12873,7 +12948,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="337" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A337" s="12" t="s">
         <v>86</v>
       </c>
@@ -12899,7 +12974,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="338" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A338" s="14" t="s">
         <v>7</v>
       </c>
@@ -12925,7 +13000,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="339" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A339" s="12" t="s">
         <v>7</v>
       </c>
@@ -12951,7 +13026,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="340" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A340" s="14" t="s">
         <v>86</v>
       </c>
@@ -12977,7 +13052,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="341" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A341" s="12" t="s">
         <v>86</v>
       </c>
@@ -13003,7 +13078,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="342" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A342" s="14" t="s">
         <v>7</v>
       </c>
@@ -13029,7 +13104,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="343" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A343" s="12" t="s">
         <v>97</v>
       </c>
@@ -13055,7 +13130,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="344" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A344" s="14" t="s">
         <v>86</v>
       </c>
@@ -13081,7 +13156,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="345" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A345" s="12" t="s">
         <v>86</v>
       </c>
@@ -13107,7 +13182,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="346" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A346" s="14" t="s">
         <v>86</v>
       </c>
@@ -13133,7 +13208,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="347" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A347" s="12" t="s">
         <v>86</v>
       </c>
@@ -13159,7 +13234,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="348" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A348" s="14" t="s">
         <v>86</v>
       </c>
@@ -13185,7 +13260,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="349" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A349" s="12" t="s">
         <v>66</v>
       </c>
@@ -13211,7 +13286,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="350" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A350" s="14" t="s">
         <v>66</v>
       </c>
@@ -13237,7 +13312,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="351" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A351" s="12" t="s">
         <v>14</v>
       </c>
@@ -13263,7 +13338,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="352" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A352" s="14" t="s">
         <v>14</v>
       </c>
@@ -13289,7 +13364,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="353" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A353" s="12" t="s">
         <v>14</v>
       </c>
@@ -13315,7 +13390,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="354" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A354" s="14" t="s">
         <v>5</v>
       </c>
@@ -13341,7 +13416,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="355" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A355" s="12" t="s">
         <v>12</v>
       </c>
@@ -13367,7 +13442,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="356" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A356" s="14" t="s">
         <v>5</v>
       </c>
@@ -13393,7 +13468,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="357" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A357" s="12" t="s">
         <v>5</v>
       </c>
@@ -13419,7 +13494,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="358" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A358" s="14" t="s">
         <v>5</v>
       </c>
@@ -13445,7 +13520,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="359" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A359" s="12" t="s">
         <v>5</v>
       </c>
@@ -13471,7 +13546,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="360" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A360" s="14" t="s">
         <v>5</v>
       </c>
@@ -13497,7 +13572,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="361" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A361" s="12" t="s">
         <v>5</v>
       </c>
@@ -13523,7 +13598,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="362" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A362" s="14" t="s">
         <v>5</v>
       </c>
@@ -13549,7 +13624,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="363" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A363" s="12" t="s">
         <v>5</v>
       </c>
@@ -13575,7 +13650,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="364" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A364" s="14" t="s">
         <v>5</v>
       </c>
@@ -13601,7 +13676,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="365" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A365" s="12" t="s">
         <v>13</v>
       </c>
@@ -13627,7 +13702,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="366" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A366" s="14" t="s">
         <v>13</v>
       </c>
@@ -13653,7 +13728,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="367" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A367" s="12" t="s">
         <v>284</v>
       </c>
@@ -13679,7 +13754,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="368" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A368" s="14" t="s">
         <v>284</v>
       </c>
@@ -13705,7 +13780,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="369" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A369" s="12" t="s">
         <v>13</v>
       </c>
@@ -13731,7 +13806,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="370" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A370" s="14" t="s">
         <v>5</v>
       </c>
@@ -13757,7 +13832,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="371" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A371" s="12" t="s">
         <v>5</v>
       </c>
@@ -13783,7 +13858,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="372" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A372" s="14" t="s">
         <v>5</v>
       </c>
@@ -13809,7 +13884,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="373" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A373" s="12" t="s">
         <v>5</v>
       </c>
@@ -13835,7 +13910,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="374" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A374" s="14" t="s">
         <v>5</v>
       </c>
@@ -13861,7 +13936,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="375" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A375" s="12" t="s">
         <v>5</v>
       </c>
@@ -13887,7 +13962,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="376" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A376" s="14" t="s">
         <v>5</v>
       </c>
@@ -13913,7 +13988,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="377" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A377" s="12" t="s">
         <v>5</v>
       </c>
@@ -13939,7 +14014,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="378" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A378" s="14" t="s">
         <v>5</v>
       </c>
@@ -13965,7 +14040,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="379" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A379" s="12" t="s">
         <v>5</v>
       </c>
@@ -13991,7 +14066,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="380" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A380" s="14" t="s">
         <v>5</v>
       </c>
@@ -14017,7 +14092,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="381" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A381" s="12" t="s">
         <v>7</v>
       </c>
@@ -14043,7 +14118,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="382" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A382" s="14" t="s">
         <v>66</v>
       </c>
@@ -14069,7 +14144,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="383" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A383" s="12" t="s">
         <v>66</v>
       </c>
@@ -14095,7 +14170,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="384" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A384" s="14" t="s">
         <v>66</v>
       </c>
@@ -14121,7 +14196,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="385" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A385" s="12" t="s">
         <v>66</v>
       </c>
@@ -14147,7 +14222,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="386" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A386" s="14" t="s">
         <v>66</v>
       </c>
@@ -14173,7 +14248,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="387" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A387" s="12" t="s">
         <v>66</v>
       </c>
@@ -14199,7 +14274,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="388" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A388" s="14" t="s">
         <v>66</v>
       </c>
@@ -14225,7 +14300,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="389" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A389" s="12" t="s">
         <v>66</v>
       </c>
@@ -14251,7 +14326,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="390" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A390" s="14" t="s">
         <v>11</v>
       </c>
@@ -14277,7 +14352,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="391" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A391" s="12" t="s">
         <v>11</v>
       </c>
@@ -14303,7 +14378,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="392" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A392" s="14" t="s">
         <v>11</v>
       </c>
@@ -14329,7 +14404,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="393" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A393" s="12" t="s">
         <v>11</v>
       </c>
@@ -14355,7 +14430,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="394" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A394" s="14" t="s">
         <v>11</v>
       </c>
@@ -14381,7 +14456,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="395" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A395" s="12" t="s">
         <v>11</v>
       </c>
@@ -14407,7 +14482,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="396" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A396" s="14" t="s">
         <v>11</v>
       </c>
@@ -14433,7 +14508,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="397" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A397" s="12" t="s">
         <v>9</v>
       </c>
@@ -14459,7 +14534,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="398" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A398" s="14" t="s">
         <v>76</v>
       </c>
@@ -14485,7 +14560,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="399" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A399" s="12" t="s">
         <v>76</v>
       </c>
@@ -14511,7 +14586,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="400" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A400" s="14" t="s">
         <v>76</v>
       </c>
@@ -14537,7 +14612,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="401" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A401" s="12" t="s">
         <v>6</v>
       </c>
@@ -14563,7 +14638,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="402" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A402" s="14" t="s">
         <v>52</v>
       </c>
@@ -14589,7 +14664,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="403" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A403" s="12" t="s">
         <v>52</v>
       </c>
@@ -14615,7 +14690,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="404" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A404" s="14" t="s">
         <v>97</v>
       </c>
@@ -14641,7 +14716,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="405" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A405" s="12" t="s">
         <v>7</v>
       </c>
@@ -14667,7 +14742,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="406" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A406" s="14" t="s">
         <v>66</v>
       </c>
@@ -14693,7 +14768,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="407" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A407" s="12" t="s">
         <v>5</v>
       </c>
@@ -14719,7 +14794,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="408" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A408" s="14" t="s">
         <v>212</v>
       </c>
@@ -14745,7 +14820,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="409" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A409" s="12" t="s">
         <v>5</v>
       </c>
@@ -14771,7 +14846,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="410" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A410" s="14" t="s">
         <v>282</v>
       </c>
@@ -14797,7 +14872,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="411" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A411" s="12" t="s">
         <v>302</v>
       </c>
@@ -14823,7 +14898,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="412" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A412" s="14" t="s">
         <v>302</v>
       </c>
@@ -14849,7 +14924,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="413" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A413" s="12" t="s">
         <v>7</v>
       </c>
@@ -14875,7 +14950,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="414" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A414" s="14" t="s">
         <v>66</v>
       </c>
@@ -14901,7 +14976,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="415" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A415" s="12" t="s">
         <v>11</v>
       </c>
@@ -14927,7 +15002,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="416" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A416" s="14" t="s">
         <v>52</v>
       </c>
@@ -14953,7 +15028,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="417" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A417" s="12" t="s">
         <v>66</v>
       </c>
@@ -14979,7 +15054,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="418" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A418" s="14" t="s">
         <v>5</v>
       </c>
@@ -15005,7 +15080,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="419" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A419" s="12" t="s">
         <v>5</v>
       </c>
@@ -15031,7 +15106,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="420" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A420" s="14" t="s">
         <v>5</v>
       </c>
@@ -15057,7 +15132,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="421" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A421" s="12" t="s">
         <v>76</v>
       </c>
@@ -15083,7 +15158,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="422" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A422" s="14" t="s">
         <v>86</v>
       </c>
@@ -15109,7 +15184,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="423" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A423" s="12" t="s">
         <v>86</v>
       </c>
@@ -15135,7 +15210,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="424" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A424" s="14" t="s">
         <v>5</v>
       </c>
@@ -15161,7 +15236,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="425" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A425" s="12" t="s">
         <v>5</v>
       </c>
@@ -15187,7 +15262,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="426" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A426" s="14" t="s">
         <v>5</v>
       </c>
@@ -15213,7 +15288,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="427" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A427" s="12" t="s">
         <v>5</v>
       </c>
@@ -15239,7 +15314,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="428" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A428" s="14" t="s">
         <v>5</v>
       </c>
@@ -15265,7 +15340,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="429" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A429" s="12" t="s">
         <v>7</v>
       </c>
@@ -15291,7 +15366,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="430" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A430" s="14" t="s">
         <v>6</v>
       </c>
@@ -15317,7 +15392,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="431" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A431" s="12" t="s">
         <v>6</v>
       </c>
@@ -15343,7 +15418,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="432" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A432" s="14" t="s">
         <v>86</v>
       </c>
@@ -15369,7 +15444,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="433" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A433" s="12" t="s">
         <v>14</v>
       </c>
@@ -15395,7 +15470,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="434" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A434" s="14" t="s">
         <v>8</v>
       </c>
@@ -15421,7 +15496,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="435" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A435" s="12" t="s">
         <v>8</v>
       </c>
@@ -15447,7 +15522,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="436" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A436" s="14" t="s">
         <v>66</v>
       </c>
@@ -15473,7 +15548,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="437" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A437" s="12" t="s">
         <v>7</v>
       </c>
@@ -15499,7 +15574,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="438" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A438" s="14" t="s">
         <v>175</v>
       </c>
@@ -15525,7 +15600,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="439" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A439" s="12" t="s">
         <v>175</v>
       </c>
@@ -15551,7 +15626,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="440" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A440" s="14" t="s">
         <v>14</v>
       </c>
@@ -15577,7 +15652,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="441" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A441" s="12" t="s">
         <v>76</v>
       </c>
@@ -15603,7 +15678,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="442" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A442" s="14" t="s">
         <v>52</v>
       </c>
@@ -15629,7 +15704,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="443" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A443" s="12" t="s">
         <v>7</v>
       </c>
@@ -15655,7 +15730,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="444" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A444" s="14" t="s">
         <v>7</v>
       </c>
@@ -15681,7 +15756,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="445" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A445" s="12" t="s">
         <v>66</v>
       </c>
@@ -15707,7 +15782,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="446" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A446" s="14" t="s">
         <v>11</v>
       </c>
@@ -15733,7 +15808,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="447" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A447" s="12" t="s">
         <v>5</v>
       </c>
@@ -15759,7 +15834,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="448" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A448" s="14" t="s">
         <v>52</v>
       </c>
@@ -15785,7 +15860,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="449" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A449" s="12" t="s">
         <v>52</v>
       </c>
@@ -15811,7 +15886,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="450" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A450" s="14" t="s">
         <v>667</v>
       </c>
@@ -15837,7 +15912,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="451" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A451" s="12" t="s">
         <v>86</v>
       </c>
@@ -15863,7 +15938,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="452" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A452" s="14" t="s">
         <v>86</v>
       </c>
@@ -15889,7 +15964,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="453" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A453" s="12" t="s">
         <v>86</v>
       </c>
@@ -15915,7 +15990,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="454" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A454" s="14" t="s">
         <v>7</v>
       </c>
@@ -15941,7 +16016,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="455" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A455" s="12" t="s">
         <v>7</v>
       </c>
@@ -15967,7 +16042,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="456" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A456" s="14" t="s">
         <v>7</v>
       </c>
@@ -15993,7 +16068,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="457" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A457" s="12" t="s">
         <v>11</v>
       </c>
@@ -16019,7 +16094,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="458" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A458" s="14" t="s">
         <v>97</v>
       </c>
@@ -16045,7 +16120,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="459" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A459" s="12" t="s">
         <v>7</v>
       </c>
@@ -16071,7 +16146,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="460" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A460" s="14" t="s">
         <v>175</v>
       </c>
@@ -16097,7 +16172,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="461" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A461" s="12" t="s">
         <v>63</v>
       </c>
@@ -16123,7 +16198,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="462" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A462" s="14" t="s">
         <v>63</v>
       </c>
@@ -16149,7 +16224,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="463" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A463" s="12" t="s">
         <v>76</v>
       </c>
@@ -16175,7 +16250,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="464" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A464" s="14" t="s">
         <v>86</v>
       </c>
@@ -16201,7 +16276,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="465" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A465" s="12" t="s">
         <v>5</v>
       </c>
@@ -16227,7 +16302,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="466" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A466" s="14" t="s">
         <v>5</v>
       </c>
@@ -16253,7 +16328,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="467" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A467" s="12" t="s">
         <v>7</v>
       </c>
@@ -16279,7 +16354,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="468" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A468" s="14" t="s">
         <v>6</v>
       </c>
@@ -16305,7 +16380,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="469" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A469" s="12" t="s">
         <v>268</v>
       </c>
@@ -16331,7 +16406,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="470" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A470" s="14" t="s">
         <v>5</v>
       </c>
@@ -16357,7 +16432,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="471" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A471" s="12" t="s">
         <v>5</v>
       </c>
@@ -16383,7 +16458,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="472" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A472" s="14" t="s">
         <v>5</v>
       </c>
@@ -16409,7 +16484,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="473" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A473" s="12" t="s">
         <v>86</v>
       </c>
@@ -16435,7 +16510,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="474" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A474" s="14" t="s">
         <v>6</v>
       </c>
@@ -16461,7 +16536,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="475" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A475" s="12" t="s">
         <v>6</v>
       </c>
@@ -16487,7 +16562,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="476" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A476" s="14" t="s">
         <v>6</v>
       </c>
@@ -16513,7 +16588,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="477" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A477" s="12" t="s">
         <v>6</v>
       </c>
@@ -16539,7 +16614,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="478" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A478" s="14" t="s">
         <v>6</v>
       </c>
@@ -16565,7 +16640,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="479" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A479" s="12" t="s">
         <v>52</v>
       </c>
@@ -16591,7 +16666,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="480" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A480" s="14" t="s">
         <v>52</v>
       </c>
@@ -16617,7 +16692,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="481" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A481" s="12" t="s">
         <v>7</v>
       </c>
@@ -16643,7 +16718,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="482" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A482" s="14" t="s">
         <v>14</v>
       </c>
@@ -16669,7 +16744,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="483" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A483" s="12" t="s">
         <v>5</v>
       </c>
@@ -16695,7 +16770,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="484" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A484" s="14" t="s">
         <v>86</v>
       </c>
@@ -16721,7 +16796,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="485" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A485" s="12" t="s">
         <v>86</v>
       </c>
@@ -16747,7 +16822,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="486" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A486" s="14" t="s">
         <v>9</v>
       </c>
@@ -16773,7 +16848,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="487" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A487" s="12" t="s">
         <v>52</v>
       </c>
@@ -16799,7 +16874,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="488" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A488" s="14" t="s">
         <v>5</v>
       </c>
@@ -16825,7 +16900,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="489" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A489" s="12" t="s">
         <v>8</v>
       </c>
@@ -16851,7 +16926,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="490" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A490" s="14" t="s">
         <v>5</v>
       </c>
@@ -16877,7 +16952,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="491" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A491" s="12" t="s">
         <v>5</v>
       </c>
@@ -16903,7 +16978,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="492" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A492" s="14" t="s">
         <v>233</v>
       </c>
@@ -16929,7 +17004,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="493" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A493" s="12" t="s">
         <v>11</v>
       </c>
@@ -16955,7 +17030,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="494" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A494" s="14" t="s">
         <v>66</v>
       </c>
@@ -16981,7 +17056,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="495" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A495" s="12" t="s">
         <v>252</v>
       </c>
@@ -17007,7 +17082,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="496" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A496" s="14" t="s">
         <v>10</v>
       </c>
@@ -17033,7 +17108,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="497" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A497" s="12" t="s">
         <v>5</v>
       </c>
@@ -17059,7 +17134,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="498" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A498" s="14" t="s">
         <v>5</v>
       </c>
@@ -17085,7 +17160,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="499" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A499" s="12" t="s">
         <v>7</v>
       </c>
@@ -17111,7 +17186,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="500" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A500" s="14" t="s">
         <v>7</v>
       </c>
@@ -17137,7 +17212,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="501" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A501" s="12" t="s">
         <v>6</v>
       </c>
@@ -17163,7 +17238,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="502" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A502" s="14" t="s">
         <v>6</v>
       </c>
@@ -17189,7 +17264,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="503" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A503" s="12" t="s">
         <v>6</v>
       </c>
@@ -17215,7 +17290,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="504" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A504" s="14" t="s">
         <v>52</v>
       </c>
@@ -17241,7 +17316,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="505" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A505" s="12" t="s">
         <v>52</v>
       </c>
@@ -17267,7 +17342,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="506" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A506" s="14" t="s">
         <v>52</v>
       </c>
@@ -17293,7 +17368,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="507" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A507" s="12" t="s">
         <v>52</v>
       </c>
@@ -17319,7 +17394,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="508" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A508" s="14" t="s">
         <v>52</v>
       </c>
@@ -17345,7 +17420,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="509" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A509" s="12" t="s">
         <v>5</v>
       </c>
@@ -17371,7 +17446,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="510" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A510" s="14" t="s">
         <v>86</v>
       </c>
@@ -17397,7 +17472,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="511" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A511" s="12" t="s">
         <v>14</v>
       </c>
@@ -17423,7 +17498,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="512" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A512" s="14" t="s">
         <v>13</v>
       </c>
@@ -17449,7 +17524,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="513" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A513" s="12" t="s">
         <v>270</v>
       </c>
@@ -17475,7 +17550,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="514" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A514" s="14" t="s">
         <v>5</v>
       </c>
@@ -17501,7 +17576,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="515" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A515" s="12" t="s">
         <v>5</v>
       </c>
@@ -17527,7 +17602,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="516" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A516" s="14" t="s">
         <v>749</v>
       </c>
@@ -17553,7 +17628,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="517" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A517" s="12" t="s">
         <v>66</v>
       </c>
@@ -17579,7 +17654,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="518" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A518" s="14" t="s">
         <v>9</v>
       </c>
@@ -17605,7 +17680,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="519" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A519" s="12" t="s">
         <v>6</v>
       </c>
@@ -17631,7 +17706,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="520" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A520" s="14" t="s">
         <v>52</v>
       </c>
@@ -17657,7 +17732,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="521" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A521" s="12" t="s">
         <v>212</v>
       </c>
@@ -17683,7 +17758,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="522" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A522" s="14" t="s">
         <v>5</v>
       </c>
@@ -17709,7 +17784,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="523" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A523" s="12" t="s">
         <v>86</v>
       </c>
@@ -17735,7 +17810,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="524" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A524" s="14" t="s">
         <v>66</v>
       </c>
@@ -17761,7 +17836,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="525" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A525" s="12" t="s">
         <v>5</v>
       </c>
@@ -17787,7 +17862,7 @@
         <v>767</v>
       </c>
     </row>
-    <row r="526" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A526" s="14" t="s">
         <v>66</v>
       </c>
@@ -17813,7 +17888,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="527" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A527" s="12" t="s">
         <v>6</v>
       </c>
@@ -17839,7 +17914,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="528" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A528" s="14" t="s">
         <v>5</v>
       </c>
@@ -17865,7 +17940,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="529" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A529" s="12" t="s">
         <v>5</v>
       </c>
@@ -17891,7 +17966,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="530" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A530" s="14" t="s">
         <v>66</v>
       </c>
@@ -17917,7 +17992,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="531" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A531" s="12" t="s">
         <v>6</v>
       </c>
@@ -17943,7 +18018,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="532" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A532" s="14" t="s">
         <v>282</v>
       </c>
@@ -17969,7 +18044,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="533" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A533" s="12" t="s">
         <v>86</v>
       </c>
@@ -17995,7 +18070,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="534" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A534" s="14" t="s">
         <v>7</v>
       </c>
@@ -18021,7 +18096,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="535" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A535" s="12" t="s">
         <v>7</v>
       </c>
@@ -18047,7 +18122,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="536" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A536" s="14" t="s">
         <v>7</v>
       </c>
@@ -18073,7 +18148,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="537" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A537" s="12" t="s">
         <v>7</v>
       </c>
@@ -18099,7 +18174,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="538" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A538" s="14" t="s">
         <v>9</v>
       </c>
@@ -18125,7 +18200,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="539" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A539" s="12" t="s">
         <v>789</v>
       </c>
@@ -18151,7 +18226,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="540" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A540" s="14" t="s">
         <v>63</v>
       </c>
@@ -18177,7 +18252,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="541" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A541" s="12" t="s">
         <v>7</v>
       </c>
@@ -18203,7 +18278,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="542" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A542" s="14" t="s">
         <v>7</v>
       </c>
@@ -18229,7 +18304,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="543" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A543" s="12" t="s">
         <v>7</v>
       </c>
@@ -18255,7 +18330,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="544" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A544" s="14" t="s">
         <v>7</v>
       </c>
@@ -18281,7 +18356,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="545" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A545" s="12" t="s">
         <v>7</v>
       </c>
@@ -18307,7 +18382,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="546" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A546" s="14" t="s">
         <v>7</v>
       </c>
@@ -18333,7 +18408,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="547" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A547" s="12" t="s">
         <v>6</v>
       </c>
@@ -18359,7 +18434,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="548" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A548" s="14" t="s">
         <v>5</v>
       </c>
@@ -18385,7 +18460,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="549" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A549" s="12" t="s">
         <v>7</v>
       </c>
@@ -18411,7 +18486,7 @@
         <v>805</v>
       </c>
     </row>
-    <row r="550" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A550" s="14" t="s">
         <v>7</v>
       </c>
@@ -18437,7 +18512,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="551" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A551" s="12" t="s">
         <v>7</v>
       </c>
@@ -18463,7 +18538,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="552" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A552" s="14" t="s">
         <v>282</v>
       </c>
@@ -18489,7 +18564,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="553" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A553" s="12" t="s">
         <v>11</v>
       </c>
@@ -18515,7 +18590,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="554" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A554" s="14" t="s">
         <v>6</v>
       </c>
@@ -18541,7 +18616,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="555" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A555" s="12" t="s">
         <v>6</v>
       </c>
@@ -18567,7 +18642,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="556" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A556" s="14" t="s">
         <v>6</v>
       </c>
@@ -18593,7 +18668,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="557" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A557" s="12" t="s">
         <v>6</v>
       </c>
@@ -18619,7 +18694,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="558" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A558" s="14" t="s">
         <v>6</v>
       </c>
@@ -18645,7 +18720,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="559" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A559" s="12" t="s">
         <v>6</v>
       </c>
@@ -18671,7 +18746,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="560" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A560" s="14" t="s">
         <v>79</v>
       </c>
@@ -18697,7 +18772,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="561" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A561" s="12" t="s">
         <v>5</v>
       </c>
@@ -18723,7 +18798,7 @@
         <v>820</v>
       </c>
     </row>
-    <row r="562" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A562" s="14" t="s">
         <v>9</v>
       </c>
@@ -18749,7 +18824,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="563" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A563" s="12" t="s">
         <v>76</v>
       </c>
@@ -18775,7 +18850,7 @@
         <v>822</v>
       </c>
     </row>
-    <row r="564" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A564" s="14" t="s">
         <v>6</v>
       </c>
@@ -18801,7 +18876,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="565" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A565" s="12" t="s">
         <v>14</v>
       </c>
@@ -18827,7 +18902,7 @@
         <v>826</v>
       </c>
     </row>
-    <row r="566" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A566" s="14" t="s">
         <v>7</v>
       </c>
@@ -18853,7 +18928,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="567" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A567" s="12" t="s">
         <v>6</v>
       </c>
@@ -18879,7 +18954,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="568" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A568" s="14" t="s">
         <v>6</v>
       </c>
@@ -18905,7 +18980,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="569" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A569" s="12" t="s">
         <v>6</v>
       </c>
@@ -18931,7 +19006,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="570" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A570" s="14" t="s">
         <v>6</v>
       </c>
@@ -18957,7 +19032,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="571" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A571" s="12" t="s">
         <v>6</v>
       </c>
@@ -18983,7 +19058,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="572" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A572" s="14" t="s">
         <v>6</v>
       </c>
@@ -19009,7 +19084,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="573" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A573" s="12" t="s">
         <v>6</v>
       </c>
@@ -19035,7 +19110,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="574" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A574" s="14" t="s">
         <v>6</v>
       </c>
@@ -19061,7 +19136,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="575" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A575" s="12" t="s">
         <v>6</v>
       </c>
@@ -19087,7 +19162,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="576" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A576" s="14" t="s">
         <v>6</v>
       </c>
@@ -19113,7 +19188,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="577" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A577" s="12" t="s">
         <v>6</v>
       </c>
@@ -19139,7 +19214,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="578" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A578" s="14" t="s">
         <v>10</v>
       </c>
@@ -19165,7 +19240,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="579" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A579" s="12" t="s">
         <v>8</v>
       </c>
@@ -19191,7 +19266,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="580" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A580" s="14" t="s">
         <v>5</v>
       </c>
@@ -19217,7 +19292,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="581" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A581" s="12" t="s">
         <v>39</v>
       </c>
@@ -19243,7 +19318,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="582" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A582" s="14" t="s">
         <v>39</v>
       </c>
@@ -19269,7 +19344,7 @@
         <v>839</v>
       </c>
     </row>
-    <row r="583" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A583" s="12" t="s">
         <v>11</v>
       </c>
@@ -19295,7 +19370,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="584" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A584" s="14" t="s">
         <v>9</v>
       </c>
@@ -19321,7 +19396,7 @@
         <v>841</v>
       </c>
     </row>
-    <row r="585" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A585" s="12" t="s">
         <v>97</v>
       </c>
@@ -19347,7 +19422,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="586" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A586" s="14" t="s">
         <v>79</v>
       </c>
@@ -19373,7 +19448,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="587" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A587" s="12" t="s">
         <v>86</v>
       </c>
@@ -19399,7 +19474,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="588" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A588" s="14" t="s">
         <v>86</v>
       </c>
@@ -19425,7 +19500,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="589" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A589" s="12" t="s">
         <v>7</v>
       </c>
@@ -19451,7 +19526,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="590" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A590" s="14" t="s">
         <v>6</v>
       </c>
@@ -19477,7 +19552,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="591" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A591" s="12" t="s">
         <v>86</v>
       </c>
@@ -19503,7 +19578,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="592" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A592" s="14" t="s">
         <v>66</v>
       </c>
@@ -19529,7 +19604,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="593" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A593" s="12" t="s">
         <v>6</v>
       </c>
@@ -19555,7 +19630,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="594" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A594" s="14" t="s">
         <v>52</v>
       </c>
@@ -19581,7 +19656,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="595" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A595" s="12" t="s">
         <v>7</v>
       </c>
@@ -19607,7 +19682,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="596" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A596" s="14" t="s">
         <v>5</v>
       </c>
@@ -19633,7 +19708,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="597" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A597" s="12" t="s">
         <v>63</v>
       </c>
@@ -19659,7 +19734,7 @@
         <v>857</v>
       </c>
     </row>
-    <row r="598" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A598" s="14" t="s">
         <v>63</v>
       </c>
@@ -19685,7 +19760,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="599" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A599" s="12" t="s">
         <v>63</v>
       </c>
@@ -19711,7 +19786,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="600" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A600" s="14" t="s">
         <v>66</v>
       </c>
@@ -19737,7 +19812,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="601" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A601" s="12" t="s">
         <v>6</v>
       </c>
@@ -19763,7 +19838,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="602" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A602" s="14" t="s">
         <v>52</v>
       </c>
@@ -19789,7 +19864,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="603" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A603" s="12" t="s">
         <v>5</v>
       </c>
@@ -19815,7 +19890,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="604" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A604" s="14" t="s">
         <v>5</v>
       </c>
@@ -19841,7 +19916,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="605" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A605" s="12" t="s">
         <v>5</v>
       </c>
@@ -19867,7 +19942,7 @@
         <v>870</v>
       </c>
     </row>
-    <row r="606" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A606" s="14" t="s">
         <v>7</v>
       </c>
@@ -19893,7 +19968,7 @@
         <v>872</v>
       </c>
     </row>
-    <row r="607" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A607" s="12" t="s">
         <v>52</v>
       </c>
@@ -19919,7 +19994,7 @@
         <v>874</v>
       </c>
     </row>
-    <row r="608" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A608" s="14" t="s">
         <v>52</v>
       </c>
@@ -19945,7 +20020,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="609" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A609" s="12" t="s">
         <v>52</v>
       </c>
@@ -19971,7 +20046,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="610" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A610" s="14" t="s">
         <v>52</v>
       </c>
@@ -19997,7 +20072,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="611" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A611" s="12" t="s">
         <v>52</v>
       </c>
@@ -20023,7 +20098,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="612" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A612" s="14" t="s">
         <v>52</v>
       </c>
@@ -20049,7 +20124,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="613" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A613" s="12" t="s">
         <v>52</v>
       </c>
@@ -20075,7 +20150,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="614" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A614" s="14" t="s">
         <v>52</v>
       </c>
@@ -20101,7 +20176,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="615" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A615" s="12" t="s">
         <v>52</v>
       </c>
@@ -20127,7 +20202,7 @@
         <v>878</v>
       </c>
     </row>
-    <row r="616" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A616" s="14" t="s">
         <v>14</v>
       </c>
@@ -20153,7 +20228,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="617" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A617" s="12" t="s">
         <v>52</v>
       </c>
@@ -20179,7 +20254,7 @@
         <v>882</v>
       </c>
     </row>
-    <row r="618" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A618" s="14" t="s">
         <v>7</v>
       </c>
@@ -20205,7 +20280,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="619" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A619" s="12" t="s">
         <v>7</v>
       </c>
@@ -20231,7 +20306,7 @@
         <v>885</v>
       </c>
     </row>
-    <row r="620" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A620" s="14" t="s">
         <v>7</v>
       </c>
@@ -20257,7 +20332,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="621" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A621" s="12" t="s">
         <v>5</v>
       </c>
@@ -20283,7 +20358,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="622" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A622" s="14" t="s">
         <v>5</v>
       </c>
@@ -20309,7 +20384,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="623" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A623" s="12" t="s">
         <v>5</v>
       </c>
@@ -20335,7 +20410,7 @@
         <v>888</v>
       </c>
     </row>
-    <row r="624" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A624" s="14" t="s">
         <v>5</v>
       </c>
@@ -20361,7 +20436,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="625" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A625" s="12" t="s">
         <v>5</v>
       </c>
@@ -20387,7 +20462,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="626" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A626" s="14" t="s">
         <v>63</v>
       </c>
@@ -20413,7 +20488,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="627" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="627" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A627" s="12" t="s">
         <v>86</v>
       </c>
@@ -20439,7 +20514,7 @@
         <v>893</v>
       </c>
     </row>
-    <row r="628" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A628" s="14" t="s">
         <v>86</v>
       </c>
@@ -20465,7 +20540,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="629" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A629" s="12" t="s">
         <v>86</v>
       </c>
@@ -20491,7 +20566,7 @@
         <v>895</v>
       </c>
     </row>
-    <row r="630" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A630" s="14" t="s">
         <v>11</v>
       </c>
@@ -20517,7 +20592,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="631" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="631" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A631" s="12" t="s">
         <v>9</v>
       </c>
@@ -20543,7 +20618,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="632" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="632" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A632" s="14" t="s">
         <v>5</v>
       </c>
@@ -20569,7 +20644,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="633" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="633" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A633" s="12" t="s">
         <v>5</v>
       </c>
@@ -20595,7 +20670,7 @@
         <v>898</v>
       </c>
     </row>
-    <row r="634" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A634" s="14" t="s">
         <v>86</v>
       </c>
@@ -20621,7 +20696,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="635" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="635" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A635" s="12" t="s">
         <v>14</v>
       </c>
@@ -20647,7 +20722,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="636" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="636" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A636" s="14" t="s">
         <v>12</v>
       </c>
@@ -20673,7 +20748,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="637" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="637" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A637" s="12" t="s">
         <v>5</v>
       </c>
@@ -20699,7 +20774,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="638" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="638" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A638" s="14" t="s">
         <v>76</v>
       </c>
@@ -20725,7 +20800,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="639" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="639" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A639" s="12" t="s">
         <v>76</v>
       </c>
@@ -20751,7 +20826,7 @@
         <v>904</v>
       </c>
     </row>
-    <row r="640" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A640" s="14" t="s">
         <v>76</v>
       </c>
@@ -20777,7 +20852,7 @@
         <v>906</v>
       </c>
     </row>
-    <row r="641" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="641" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A641" s="12" t="s">
         <v>6</v>
       </c>
@@ -20803,7 +20878,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="642" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A642" s="14" t="s">
         <v>6</v>
       </c>
@@ -20829,7 +20904,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="643" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="643" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A643" s="12" t="s">
         <v>6</v>
       </c>
@@ -20855,7 +20930,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="644" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="644" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A644" s="14" t="s">
         <v>6</v>
       </c>
@@ -20881,7 +20956,7 @@
         <v>913</v>
       </c>
     </row>
-    <row r="645" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="645" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A645" s="12" t="s">
         <v>6</v>
       </c>
@@ -20907,7 +20982,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="646" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="646" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A646" s="14" t="s">
         <v>52</v>
       </c>
@@ -20927,13 +21002,13 @@
         <v>16</v>
       </c>
       <c r="G646" s="20">
-        <v>44</v>
+        <v>93</v>
       </c>
       <c r="H646" s="21" t="s">
         <v>916</v>
       </c>
     </row>
-    <row r="647" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="647" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A647" s="12" t="s">
         <v>7</v>
       </c>
@@ -20953,13 +21028,13 @@
         <v>16</v>
       </c>
       <c r="G647" s="17">
-        <v>132</v>
+        <v>83</v>
       </c>
       <c r="H647" s="18" t="s">
         <v>917</v>
       </c>
     </row>
-    <row r="648" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="648" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A648" s="14" t="s">
         <v>7</v>
       </c>
@@ -20985,7 +21060,7 @@
         <v>918</v>
       </c>
     </row>
-    <row r="649" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="649" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A649" s="12" t="s">
         <v>789</v>
       </c>
@@ -21011,7 +21086,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="650" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="650" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A650" s="14" t="s">
         <v>282</v>
       </c>
@@ -21037,7 +21112,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="651" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="651" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A651" s="12" t="s">
         <v>282</v>
       </c>
@@ -21061,6 +21136,864 @@
       </c>
       <c r="H651" s="18" t="s">
         <v>923</v>
+      </c>
+    </row>
+    <row r="652" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A652" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="B652" s="15">
+        <v>45232</v>
+      </c>
+      <c r="C652" s="15">
+        <v>45274</v>
+      </c>
+      <c r="D652" s="15">
+        <v>45275</v>
+      </c>
+      <c r="E652" s="19" t="s">
+        <v>924</v>
+      </c>
+      <c r="F652" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G652" s="20">
+        <v>1</v>
+      </c>
+      <c r="H652" s="21" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="653" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A653" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B653" s="13">
+        <v>45232</v>
+      </c>
+      <c r="C653" s="13">
+        <v>45274</v>
+      </c>
+      <c r="D653" s="13">
+        <v>45276</v>
+      </c>
+      <c r="E653" s="16" t="s">
+        <v>924</v>
+      </c>
+      <c r="F653" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G653" s="17">
+        <v>1</v>
+      </c>
+      <c r="H653" s="18" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="654" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A654" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="B654" s="15">
+        <v>45232</v>
+      </c>
+      <c r="C654" s="15">
+        <v>45274</v>
+      </c>
+      <c r="D654" s="15">
+        <v>45277</v>
+      </c>
+      <c r="E654" s="19" t="s">
+        <v>924</v>
+      </c>
+      <c r="F654" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G654" s="20">
+        <v>1</v>
+      </c>
+      <c r="H654" s="21" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="655" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A655" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B655" s="13">
+        <v>45232</v>
+      </c>
+      <c r="C655" s="13">
+        <v>45274</v>
+      </c>
+      <c r="D655" s="13">
+        <v>45278</v>
+      </c>
+      <c r="E655" s="16" t="s">
+        <v>924</v>
+      </c>
+      <c r="F655" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G655" s="17">
+        <v>1</v>
+      </c>
+      <c r="H655" s="18" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="656" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A656" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="B656" s="15">
+        <v>45232</v>
+      </c>
+      <c r="C656" s="15">
+        <v>45274</v>
+      </c>
+      <c r="D656" s="15">
+        <v>45279</v>
+      </c>
+      <c r="E656" s="19" t="s">
+        <v>924</v>
+      </c>
+      <c r="F656" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G656" s="20">
+        <v>1</v>
+      </c>
+      <c r="H656" s="21" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="657" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A657" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B657" s="13">
+        <v>45232</v>
+      </c>
+      <c r="C657" s="13">
+        <v>45274</v>
+      </c>
+      <c r="D657" s="13">
+        <v>45280</v>
+      </c>
+      <c r="E657" s="16" t="s">
+        <v>924</v>
+      </c>
+      <c r="F657" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G657" s="17">
+        <v>1</v>
+      </c>
+      <c r="H657" s="18" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="658" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A658" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="B658" s="15">
+        <v>45232</v>
+      </c>
+      <c r="C658" s="15">
+        <v>45274</v>
+      </c>
+      <c r="D658" s="15">
+        <v>45281</v>
+      </c>
+      <c r="E658" s="19" t="s">
+        <v>924</v>
+      </c>
+      <c r="F658" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G658" s="20">
+        <v>1</v>
+      </c>
+      <c r="H658" s="21" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="659" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A659" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B659" s="13">
+        <v>45232</v>
+      </c>
+      <c r="C659" s="13">
+        <v>45274</v>
+      </c>
+      <c r="D659" s="13">
+        <v>45282</v>
+      </c>
+      <c r="E659" s="16" t="s">
+        <v>924</v>
+      </c>
+      <c r="F659" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G659" s="17">
+        <v>1</v>
+      </c>
+      <c r="H659" s="18" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="660" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A660" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="B660" s="15">
+        <v>45232</v>
+      </c>
+      <c r="C660" s="15">
+        <v>45274</v>
+      </c>
+      <c r="D660" s="15">
+        <v>45283</v>
+      </c>
+      <c r="E660" s="19" t="s">
+        <v>924</v>
+      </c>
+      <c r="F660" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G660" s="20">
+        <v>1</v>
+      </c>
+      <c r="H660" s="21" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="661" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A661" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B661" s="13">
+        <v>45232</v>
+      </c>
+      <c r="C661" s="13">
+        <v>45274</v>
+      </c>
+      <c r="D661" s="13">
+        <v>45284</v>
+      </c>
+      <c r="E661" s="16" t="s">
+        <v>924</v>
+      </c>
+      <c r="F661" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G661" s="17">
+        <v>1</v>
+      </c>
+      <c r="H661" s="18" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="662" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A662" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="B662" s="15">
+        <v>45232</v>
+      </c>
+      <c r="C662" s="15">
+        <v>45274</v>
+      </c>
+      <c r="D662" s="15">
+        <v>45285</v>
+      </c>
+      <c r="E662" s="19" t="s">
+        <v>924</v>
+      </c>
+      <c r="F662" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G662" s="20">
+        <v>1</v>
+      </c>
+      <c r="H662" s="21" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="663" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A663" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B663" s="13">
+        <v>45232</v>
+      </c>
+      <c r="C663" s="13">
+        <v>45274</v>
+      </c>
+      <c r="D663" s="13">
+        <v>45290</v>
+      </c>
+      <c r="E663" s="16" t="s">
+        <v>924</v>
+      </c>
+      <c r="F663" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G663" s="17">
+        <v>3</v>
+      </c>
+      <c r="H663" s="18" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="664" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A664" s="14" t="s">
+        <v>926</v>
+      </c>
+      <c r="B664" s="15">
+        <v>45231</v>
+      </c>
+      <c r="C664" s="15">
+        <v>45274</v>
+      </c>
+      <c r="D664" s="15">
+        <v>45292</v>
+      </c>
+      <c r="E664" s="19" t="s">
+        <v>927</v>
+      </c>
+      <c r="F664" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G664" s="20">
+        <v>142</v>
+      </c>
+      <c r="H664" s="21" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="665" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A665" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B665" s="13">
+        <v>45245</v>
+      </c>
+      <c r="C665" s="13">
+        <v>45274</v>
+      </c>
+      <c r="D665" s="13">
+        <v>45307</v>
+      </c>
+      <c r="E665" s="16" t="s">
+        <v>929</v>
+      </c>
+      <c r="F665" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G665" s="17">
+        <v>58</v>
+      </c>
+      <c r="H665" s="18" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="666" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A666" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="B666" s="15">
+        <v>45245</v>
+      </c>
+      <c r="C666" s="15">
+        <v>45274</v>
+      </c>
+      <c r="D666" s="15">
+        <v>45307</v>
+      </c>
+      <c r="E666" s="19" t="s">
+        <v>929</v>
+      </c>
+      <c r="F666" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G666" s="20">
+        <v>7</v>
+      </c>
+      <c r="H666" s="21" t="s">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="667" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A667" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="B667" s="13">
+        <v>45239</v>
+      </c>
+      <c r="C667" s="13">
+        <v>45274</v>
+      </c>
+      <c r="D667" s="13">
+        <v>45299</v>
+      </c>
+      <c r="E667" s="16" t="s">
+        <v>654</v>
+      </c>
+      <c r="F667" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G667" s="17">
+        <v>23</v>
+      </c>
+      <c r="H667" s="18" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="668" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A668" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="B668" s="15">
+        <v>45236</v>
+      </c>
+      <c r="C668" s="15">
+        <v>45275</v>
+      </c>
+      <c r="D668" s="15">
+        <v>45306</v>
+      </c>
+      <c r="E668" s="19" t="s">
+        <v>932</v>
+      </c>
+      <c r="F668" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G668" s="20">
+        <v>29</v>
+      </c>
+      <c r="H668" s="21" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="669" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A669" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B669" s="13">
+        <v>45236</v>
+      </c>
+      <c r="C669" s="13">
+        <v>45275</v>
+      </c>
+      <c r="D669" s="13">
+        <v>45296</v>
+      </c>
+      <c r="E669" s="16" t="s">
+        <v>934</v>
+      </c>
+      <c r="F669" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G669" s="17">
+        <v>85</v>
+      </c>
+      <c r="H669" s="18" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="670" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A670" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B670" s="15">
+        <v>45236</v>
+      </c>
+      <c r="C670" s="15">
+        <v>45275</v>
+      </c>
+      <c r="D670" s="15">
+        <v>45296</v>
+      </c>
+      <c r="E670" s="19" t="s">
+        <v>934</v>
+      </c>
+      <c r="F670" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G670" s="20">
+        <v>1</v>
+      </c>
+      <c r="H670" s="21" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="671" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A671" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B671" s="13">
+        <v>45236</v>
+      </c>
+      <c r="C671" s="13">
+        <v>45275</v>
+      </c>
+      <c r="D671" s="13">
+        <v>45296</v>
+      </c>
+      <c r="E671" s="16" t="s">
+        <v>934</v>
+      </c>
+      <c r="F671" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G671" s="17">
+        <v>1</v>
+      </c>
+      <c r="H671" s="18" t="s">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="672" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A672" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B672" s="15">
+        <v>45236</v>
+      </c>
+      <c r="C672" s="15">
+        <v>45275</v>
+      </c>
+      <c r="D672" s="15">
+        <v>45296</v>
+      </c>
+      <c r="E672" s="19" t="s">
+        <v>934</v>
+      </c>
+      <c r="F672" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G672" s="20">
+        <v>1</v>
+      </c>
+      <c r="H672" s="21" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="673" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A673" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B673" s="13">
+        <v>45238</v>
+      </c>
+      <c r="C673" s="13">
+        <v>45278</v>
+      </c>
+      <c r="D673" s="13">
+        <v>45299</v>
+      </c>
+      <c r="E673" s="16" t="s">
+        <v>939</v>
+      </c>
+      <c r="F673" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G673" s="17">
+        <v>75</v>
+      </c>
+      <c r="H673" s="18" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="674" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A674" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="B674" s="15">
+        <v>45238</v>
+      </c>
+      <c r="C674" s="15">
+        <v>45278</v>
+      </c>
+      <c r="D674" s="15">
+        <v>45299</v>
+      </c>
+      <c r="E674" s="19" t="s">
+        <v>939</v>
+      </c>
+      <c r="F674" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G674" s="20">
+        <v>1</v>
+      </c>
+      <c r="H674" s="21" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="675" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A675" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B675" s="13">
+        <v>45238</v>
+      </c>
+      <c r="C675" s="13">
+        <v>45278</v>
+      </c>
+      <c r="D675" s="13">
+        <v>45299</v>
+      </c>
+      <c r="E675" s="16" t="s">
+        <v>939</v>
+      </c>
+      <c r="F675" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G675" s="17">
+        <v>1</v>
+      </c>
+      <c r="H675" s="18" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="676" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A676" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="B676" s="15">
+        <v>45238</v>
+      </c>
+      <c r="C676" s="15">
+        <v>45278</v>
+      </c>
+      <c r="D676" s="15">
+        <v>45299</v>
+      </c>
+      <c r="E676" s="19" t="s">
+        <v>939</v>
+      </c>
+      <c r="F676" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G676" s="20">
+        <v>1</v>
+      </c>
+      <c r="H676" s="21" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="677" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A677" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B677" s="13">
+        <v>45233</v>
+      </c>
+      <c r="C677" s="13">
+        <v>45278</v>
+      </c>
+      <c r="D677" s="13">
+        <v>45291</v>
+      </c>
+      <c r="E677" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="F677" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G677" s="17">
+        <v>73</v>
+      </c>
+      <c r="H677" s="18" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="678" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A678" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="B678" s="15">
+        <v>45233</v>
+      </c>
+      <c r="C678" s="15">
+        <v>45278</v>
+      </c>
+      <c r="D678" s="15">
+        <v>45291</v>
+      </c>
+      <c r="E678" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="F678" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G678" s="20">
+        <v>1</v>
+      </c>
+      <c r="H678" s="21" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="679" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A679" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B679" s="13">
+        <v>45233</v>
+      </c>
+      <c r="C679" s="13">
+        <v>45278</v>
+      </c>
+      <c r="D679" s="13">
+        <v>45291</v>
+      </c>
+      <c r="E679" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="F679" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G679" s="17">
+        <v>1</v>
+      </c>
+      <c r="H679" s="18" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="680" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A680" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="B680" s="15">
+        <v>45233</v>
+      </c>
+      <c r="C680" s="15">
+        <v>45278</v>
+      </c>
+      <c r="D680" s="15">
+        <v>45291</v>
+      </c>
+      <c r="E680" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="F680" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G680" s="20">
+        <v>1</v>
+      </c>
+      <c r="H680" s="21" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="681" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A681" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B681" s="13">
+        <v>45239</v>
+      </c>
+      <c r="C681" s="13">
+        <v>45278</v>
+      </c>
+      <c r="D681" s="13">
+        <v>45317</v>
+      </c>
+      <c r="E681" s="16" t="s">
+        <v>945</v>
+      </c>
+      <c r="F681" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G681" s="17">
+        <v>32</v>
+      </c>
+      <c r="H681" s="18" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="682" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A682" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B682" s="15">
+        <v>45239</v>
+      </c>
+      <c r="C682" s="15">
+        <v>45278</v>
+      </c>
+      <c r="D682" s="15">
+        <v>45303</v>
+      </c>
+      <c r="E682" s="19" t="s">
+        <v>945</v>
+      </c>
+      <c r="F682" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G682" s="20">
+        <v>1</v>
+      </c>
+      <c r="H682" s="21" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="683" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A683" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B683" s="13">
+        <v>45239</v>
+      </c>
+      <c r="C683" s="13">
+        <v>45278</v>
+      </c>
+      <c r="D683" s="13">
+        <v>45317</v>
+      </c>
+      <c r="E683" s="16" t="s">
+        <v>945</v>
+      </c>
+      <c r="F683" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G683" s="17">
+        <v>3</v>
+      </c>
+      <c r="H683" s="18" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="684" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A684" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="B684" s="15">
+        <v>45239</v>
+      </c>
+      <c r="C684" s="15">
+        <v>45278</v>
+      </c>
+      <c r="D684" s="15">
+        <v>45299</v>
+      </c>
+      <c r="E684" s="19" t="s">
+        <v>947</v>
+      </c>
+      <c r="F684" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="G684" s="20">
+        <v>130</v>
+      </c>
+      <c r="H684" s="21" t="s">
+        <v>948</v>
       </c>
     </row>
   </sheetData>
@@ -21073,8 +22006,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Unknown Document Type" ma:contentTypeID="0x010104" ma:contentTypeVersion="0" ma:contentTypeDescription="" ma:contentTypeScope="" ma:versionID="05d83ceaa0bbd2e3bc716e6e66bd857a">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b3d69fe45253d5ff147bb69036b756a7">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010024A56C947B344C46A18F0D79B93D8399" ma:contentTypeVersion="0" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7fad6a7f847b37b99d8a9e27cc7330ef">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6834f8c0c0eabdc6c42b2f987c760c09">
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
@@ -21096,8 +22029,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type" ma:readOnly="true"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="3" ma:displayName="Title"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -21202,13 +22135,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ACBADEC5-19FA-4C96-BDB7-7E865E63669C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BFC921AE-4ACD-44BF-84F7-87C6CD843C9F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6C6D04E-1A93-400F-B2C0-35619BAB5383}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4BB077E5-4586-4B29-90FD-4FD1D75EC0D0}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FE0E8F8F-B4D9-4546-8D3B-F512BDDDF4A5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C48C9B3-7993-434D-B169-FDF7C9C657E0}"/>
 </file>
--- a/data/warn-scraper/cache/ca/warn_report1.xlsx
+++ b/data/warn-scraper/cache/ca/warn_report1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BVang\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C49BA018-AE1D-4AF2-ADEA-272DDCD68F87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B88755DC-6D58-4745-A690-029384D0274A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
   <sheets>
     <sheet name="Index" sheetId="3" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2751" uniqueCount="950">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2763" uniqueCount="955">
   <si>
     <t>County/Parish</t>
   </si>
@@ -2951,6 +2951,21 @@
     <t>14700 W. Schulte Road  Tracy CA 95377</t>
   </si>
   <si>
+    <t>Talis Biomedical Corporation</t>
+  </si>
+  <si>
+    <t>1100 Island Drive Suite 100  Redwood City CA 94065</t>
+  </si>
+  <si>
+    <t>One Tuna Lane  San Diego CA 92101</t>
+  </si>
+  <si>
+    <t>Knox Attorney Service, Inc.</t>
+  </si>
+  <si>
+    <t>P1 1155 N. P1 St., Suite 100  San Jose CA 95112</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">WARN REPORT - </t>
     </r>
@@ -2962,7 +2977,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>07/01/23 to 12/18/23</t>
+      <t>07/01/23 to 12/20/23</t>
     </r>
     <r>
       <rPr>
@@ -2982,7 +2997,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>A detailed WARN summary by county and filtered according to received date. Table Spans cells A2 through H684.</t>
+      <t>A detailed WARN summary by county and filtered according to received date. Table Spans cells A2 through H687.</t>
     </r>
   </si>
 </sst>
@@ -3288,8 +3303,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFF0F0F0"/>
+          <bgColor rgb="FFF0F0F0"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -3329,8 +3344,8 @@
       <numFmt numFmtId="165" formatCode="[$-10436]#,##0;\(#,##0\)"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFF0F0F0"/>
+          <bgColor rgb="FFF0F0F0"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -3369,8 +3384,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFF0F0F0"/>
+          <bgColor rgb="FFF0F0F0"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -3409,8 +3424,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFF0F0F0"/>
+          <bgColor rgb="FFF0F0F0"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -3450,8 +3465,8 @@
       <numFmt numFmtId="164" formatCode="[$-10409]mm/dd/yyyy"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFF0F0F0"/>
+          <bgColor rgb="FFF0F0F0"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -3491,8 +3506,8 @@
       <numFmt numFmtId="164" formatCode="[$-10409]mm/dd/yyyy"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFF0F0F0"/>
+          <bgColor rgb="FFF0F0F0"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -3532,8 +3547,8 @@
       <numFmt numFmtId="164" formatCode="[$-10409]mm/dd/yyyy"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFF0F0F0"/>
+          <bgColor rgb="FFF0F0F0"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -3572,8 +3587,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFF0F0F0"/>
+          <bgColor rgb="FFF0F0F0"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -3765,8 +3780,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:H684" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
-  <autoFilter ref="A2:H684" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:H687" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
+  <autoFilter ref="A2:H687" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -4150,7 +4165,7 @@
       </c>
       <c r="B3" s="5">
         <f>SUM('Detailed WARN Report '!G:G)</f>
-        <v>36205</v>
+        <v>36397</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -4185,7 +4200,7 @@
       </c>
       <c r="B7" s="5">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Permanent")</f>
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -4217,20 +4232,20 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:H684"/>
+  <dimension ref="A1:H687"/>
   <sheetFormatPr defaultColWidth="26" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="4" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="59.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="63.28515625" style="1" customWidth="1"/>
     <col min="6" max="6" width="21.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="58.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="63" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="117" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>949</v>
+        <v>954</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -4238,7 +4253,7 @@
       <c r="G1" s="6"/>
       <c r="H1" s="6"/>
     </row>
-    <row r="2" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
         <v>0</v>
       </c>
@@ -21994,6 +22009,84 @@
       </c>
       <c r="H684" s="21" t="s">
         <v>948</v>
+      </c>
+    </row>
+    <row r="685" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A685" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="B685" s="13">
+        <v>45244</v>
+      </c>
+      <c r="C685" s="13">
+        <v>45280</v>
+      </c>
+      <c r="D685" s="13">
+        <v>45305</v>
+      </c>
+      <c r="E685" s="16" t="s">
+        <v>949</v>
+      </c>
+      <c r="F685" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G685" s="17">
+        <v>103</v>
+      </c>
+      <c r="H685" s="18" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="686" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A686" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B686" s="15">
+        <v>45243</v>
+      </c>
+      <c r="C686" s="15">
+        <v>45280</v>
+      </c>
+      <c r="D686" s="15">
+        <v>45303</v>
+      </c>
+      <c r="E686" s="19" t="s">
+        <v>296</v>
+      </c>
+      <c r="F686" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G686" s="20">
+        <v>4</v>
+      </c>
+      <c r="H686" s="21" t="s">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="687" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A687" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B687" s="13">
+        <v>45245</v>
+      </c>
+      <c r="C687" s="13">
+        <v>45280</v>
+      </c>
+      <c r="D687" s="13">
+        <v>45306</v>
+      </c>
+      <c r="E687" s="16" t="s">
+        <v>952</v>
+      </c>
+      <c r="F687" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G687" s="17">
+        <v>85</v>
+      </c>
+      <c r="H687" s="18" t="s">
+        <v>953</v>
       </c>
     </row>
   </sheetData>
@@ -22006,8 +22099,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010024A56C947B344C46A18F0D79B93D8399" ma:contentTypeVersion="0" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7fad6a7f847b37b99d8a9e27cc7330ef">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6834f8c0c0eabdc6c42b2f987c760c09">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Unknown Document Type" ma:contentTypeID="0x010104" ma:contentTypeVersion="0" ma:contentTypeDescription="" ma:contentTypeScope="" ma:versionID="05d83ceaa0bbd2e3bc716e6e66bd857a">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b3d69fe45253d5ff147bb69036b756a7">
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
@@ -22029,8 +22122,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type" ma:readOnly="true"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="3" ma:displayName="Title"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -22135,13 +22228,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BFC921AE-4ACD-44BF-84F7-87C6CD843C9F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE073E07-F3E7-42A4-84A1-A3D57141FBD2}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4BB077E5-4586-4B29-90FD-4FD1D75EC0D0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64BC2BAC-5B33-432A-920B-0D9898CF0092}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C48C9B3-7993-434D-B169-FDF7C9C657E0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66C4B2B8-03F8-4672-99EC-6FFAC505985D}"/>
 </file>
--- a/data/warn-scraper/cache/ca/warn_report1.xlsx
+++ b/data/warn-scraper/cache/ca/warn_report1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BVang\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B88755DC-6D58-4745-A690-029384D0274A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34FED68E-1FAA-4256-97A0-E1334EA87D13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2763" uniqueCount="955">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2807" uniqueCount="963">
   <si>
     <t>County/Parish</t>
   </si>
@@ -2966,6 +2966,30 @@
     <t>P1 1155 N. P1 St., Suite 100  San Jose CA 95112</t>
   </si>
   <si>
+    <t>NextGen Healthcare, Inc.</t>
+  </si>
+  <si>
+    <t>18111 Von Karman Ave. Suite 600  Irvine CA 92612</t>
+  </si>
+  <si>
+    <t>Western Digital</t>
+  </si>
+  <si>
+    <t>3355 Michelson Drive  Irvine CA 92612</t>
+  </si>
+  <si>
+    <t>Renesas Electronics Corporation</t>
+  </si>
+  <si>
+    <t>1001 Murphy Ranch Road  Milpitas CA 95035</t>
+  </si>
+  <si>
+    <t>6024 Silver Creek Valley Road  San Jose CA 95138</t>
+  </si>
+  <si>
+    <t>2200 S McDowell Blvd Ext  Petaluma CA 94954</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">WARN REPORT - </t>
     </r>
@@ -2977,7 +3001,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>07/01/23 to 12/20/23</t>
+      <t>07/01/23 to 12/25/23</t>
     </r>
     <r>
       <rPr>
@@ -2997,7 +3021,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>A detailed WARN summary by county and filtered according to received date. Table Spans cells A2 through H687.</t>
+      <t>A detailed WARN summary by county and filtered according to received date. Table Spans cells A2 through H698.</t>
     </r>
   </si>
 </sst>
@@ -3303,8 +3327,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF0F0F0"/>
-          <bgColor rgb="FFF0F0F0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -3344,8 +3368,8 @@
       <numFmt numFmtId="165" formatCode="[$-10436]#,##0;\(#,##0\)"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF0F0F0"/>
-          <bgColor rgb="FFF0F0F0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -3384,8 +3408,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF0F0F0"/>
-          <bgColor rgb="FFF0F0F0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -3424,8 +3448,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF0F0F0"/>
-          <bgColor rgb="FFF0F0F0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -3465,8 +3489,8 @@
       <numFmt numFmtId="164" formatCode="[$-10409]mm/dd/yyyy"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF0F0F0"/>
-          <bgColor rgb="FFF0F0F0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -3506,8 +3530,8 @@
       <numFmt numFmtId="164" formatCode="[$-10409]mm/dd/yyyy"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF0F0F0"/>
-          <bgColor rgb="FFF0F0F0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -3547,8 +3571,8 @@
       <numFmt numFmtId="164" formatCode="[$-10409]mm/dd/yyyy"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF0F0F0"/>
-          <bgColor rgb="FFF0F0F0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -3587,8 +3611,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF0F0F0"/>
-          <bgColor rgb="FFF0F0F0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -3780,8 +3804,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:H687" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
-  <autoFilter ref="A2:H687" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:H698" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
+  <autoFilter ref="A2:H698" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -4165,7 +4189,7 @@
       </c>
       <c r="B3" s="5">
         <f>SUM('Detailed WARN Report '!G:G)</f>
-        <v>36397</v>
+        <v>36684</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -4174,7 +4198,7 @@
       </c>
       <c r="B4" s="5">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Permanent")</f>
-        <v>458</v>
+        <v>469</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -4232,7 +4256,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:H687"/>
+  <dimension ref="A1:H698"/>
   <sheetFormatPr defaultColWidth="26" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.85546875" bestFit="1" customWidth="1"/>
@@ -4245,7 +4269,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="117" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>954</v>
+        <v>962</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -20029,7 +20053,7 @@
         <v>16</v>
       </c>
       <c r="G608" s="20">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H608" s="21" t="s">
         <v>876</v>
@@ -20055,7 +20079,7 @@
         <v>16</v>
       </c>
       <c r="G609" s="17">
-        <v>1</v>
+        <v>73</v>
       </c>
       <c r="H609" s="18" t="s">
         <v>876</v>
@@ -20081,7 +20105,7 @@
         <v>16</v>
       </c>
       <c r="G610" s="20">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H610" s="21" t="s">
         <v>876</v>
@@ -20107,7 +20131,7 @@
         <v>16</v>
       </c>
       <c r="G611" s="17">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H611" s="18" t="s">
         <v>876</v>
@@ -20185,7 +20209,7 @@
         <v>16</v>
       </c>
       <c r="G614" s="20">
-        <v>103</v>
+        <v>2</v>
       </c>
       <c r="H614" s="21" t="s">
         <v>876</v>
@@ -20196,51 +20220,51 @@
         <v>52</v>
       </c>
       <c r="B615" s="13">
-        <v>45236</v>
+        <v>45237</v>
       </c>
       <c r="C615" s="13">
         <v>45267</v>
       </c>
       <c r="D615" s="13">
-        <v>45296</v>
+        <v>45260</v>
       </c>
       <c r="E615" s="16" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="F615" s="16" t="s">
         <v>16</v>
       </c>
       <c r="G615" s="17">
-        <v>155</v>
+        <v>1</v>
       </c>
       <c r="H615" s="18" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
     </row>
     <row r="616" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A616" s="14" t="s">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="B616" s="15">
-        <v>45233</v>
+        <v>45237</v>
       </c>
       <c r="C616" s="15">
-        <v>45271</v>
+        <v>45267</v>
       </c>
       <c r="D616" s="15">
-        <v>45296</v>
+        <v>45270</v>
       </c>
       <c r="E616" s="19" t="s">
-        <v>879</v>
+        <v>875</v>
       </c>
       <c r="F616" s="19" t="s">
         <v>16</v>
       </c>
       <c r="G616" s="20">
-        <v>141</v>
+        <v>1</v>
       </c>
       <c r="H616" s="21" t="s">
-        <v>880</v>
+        <v>876</v>
       </c>
     </row>
     <row r="617" spans="1:8" x14ac:dyDescent="0.25">
@@ -20248,82 +20272,82 @@
         <v>52</v>
       </c>
       <c r="B617" s="13">
-        <v>45232</v>
+        <v>45237</v>
       </c>
       <c r="C617" s="13">
-        <v>45271</v>
+        <v>45267</v>
       </c>
       <c r="D617" s="13">
-        <v>45292</v>
+        <v>45443</v>
       </c>
       <c r="E617" s="16" t="s">
-        <v>881</v>
+        <v>875</v>
       </c>
       <c r="F617" s="16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G617" s="17">
-        <v>71</v>
+        <v>2</v>
       </c>
       <c r="H617" s="18" t="s">
-        <v>882</v>
+        <v>876</v>
       </c>
     </row>
     <row r="618" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A618" s="14" t="s">
-        <v>7</v>
+        <v>52</v>
       </c>
       <c r="B618" s="15">
-        <v>45233</v>
+        <v>45237</v>
       </c>
       <c r="C618" s="15">
-        <v>45271</v>
+        <v>45267</v>
       </c>
       <c r="D618" s="15">
-        <v>45303</v>
+        <v>45474</v>
       </c>
       <c r="E618" s="19" t="s">
-        <v>883</v>
+        <v>875</v>
       </c>
       <c r="F618" s="19" t="s">
         <v>16</v>
       </c>
       <c r="G618" s="20">
-        <v>109</v>
+        <v>6</v>
       </c>
       <c r="H618" s="21" t="s">
-        <v>884</v>
+        <v>876</v>
       </c>
     </row>
     <row r="619" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A619" s="12" t="s">
-        <v>7</v>
+        <v>52</v>
       </c>
       <c r="B619" s="13">
-        <v>45233</v>
+        <v>45236</v>
       </c>
       <c r="C619" s="13">
-        <v>45271</v>
+        <v>45267</v>
       </c>
       <c r="D619" s="13">
-        <v>45303</v>
+        <v>45296</v>
       </c>
       <c r="E619" s="16" t="s">
-        <v>883</v>
+        <v>877</v>
       </c>
       <c r="F619" s="16" t="s">
         <v>16</v>
       </c>
       <c r="G619" s="17">
-        <v>1</v>
+        <v>155</v>
       </c>
       <c r="H619" s="18" t="s">
-        <v>885</v>
+        <v>878</v>
       </c>
     </row>
     <row r="620" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A620" s="14" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B620" s="15">
         <v>45233</v>
@@ -20332,114 +20356,114 @@
         <v>45271</v>
       </c>
       <c r="D620" s="15">
-        <v>45303</v>
+        <v>45296</v>
       </c>
       <c r="E620" s="19" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
       <c r="F620" s="19" t="s">
         <v>16</v>
       </c>
       <c r="G620" s="20">
-        <v>1</v>
+        <v>141</v>
       </c>
       <c r="H620" s="21" t="s">
-        <v>886</v>
+        <v>880</v>
       </c>
     </row>
     <row r="621" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A621" s="12" t="s">
-        <v>5</v>
+        <v>52</v>
       </c>
       <c r="B621" s="13">
-        <v>45236</v>
+        <v>45232</v>
       </c>
       <c r="C621" s="13">
-        <v>45272</v>
+        <v>45271</v>
       </c>
       <c r="D621" s="13">
-        <v>45295</v>
+        <v>45292</v>
       </c>
       <c r="E621" s="16" t="s">
-        <v>464</v>
+        <v>881</v>
       </c>
       <c r="F621" s="16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G621" s="17">
-        <v>26</v>
+        <v>71</v>
       </c>
       <c r="H621" s="18" t="s">
-        <v>466</v>
+        <v>882</v>
       </c>
     </row>
     <row r="622" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A622" s="14" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B622" s="15">
-        <v>45236</v>
+        <v>45233</v>
       </c>
       <c r="C622" s="15">
-        <v>45272</v>
+        <v>45271</v>
       </c>
       <c r="D622" s="15">
-        <v>45295</v>
+        <v>45303</v>
       </c>
       <c r="E622" s="19" t="s">
-        <v>467</v>
+        <v>883</v>
       </c>
       <c r="F622" s="19" t="s">
         <v>16</v>
       </c>
       <c r="G622" s="20">
-        <v>22</v>
+        <v>109</v>
       </c>
       <c r="H622" s="21" t="s">
-        <v>468</v>
+        <v>884</v>
       </c>
     </row>
     <row r="623" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A623" s="12" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B623" s="13">
-        <v>45236</v>
+        <v>45233</v>
       </c>
       <c r="C623" s="13">
-        <v>45272</v>
+        <v>45271</v>
       </c>
       <c r="D623" s="13">
-        <v>45295</v>
+        <v>45303</v>
       </c>
       <c r="E623" s="16" t="s">
-        <v>887</v>
+        <v>883</v>
       </c>
       <c r="F623" s="16" t="s">
         <v>16</v>
       </c>
       <c r="G623" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H623" s="18" t="s">
-        <v>888</v>
+        <v>885</v>
       </c>
     </row>
     <row r="624" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A624" s="14" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B624" s="15">
-        <v>45236</v>
+        <v>45233</v>
       </c>
       <c r="C624" s="15">
-        <v>45272</v>
+        <v>45271</v>
       </c>
       <c r="D624" s="15">
-        <v>45295</v>
+        <v>45303</v>
       </c>
       <c r="E624" s="19" t="s">
-        <v>464</v>
+        <v>883</v>
       </c>
       <c r="F624" s="19" t="s">
         <v>16</v>
@@ -20448,7 +20472,7 @@
         <v>1</v>
       </c>
       <c r="H624" s="21" t="s">
-        <v>889</v>
+        <v>886</v>
       </c>
     </row>
     <row r="625" spans="1:8" x14ac:dyDescent="0.25">
@@ -20471,15 +20495,15 @@
         <v>16</v>
       </c>
       <c r="G625" s="17">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="H625" s="18" t="s">
-        <v>890</v>
+        <v>466</v>
       </c>
     </row>
     <row r="626" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A626" s="14" t="s">
-        <v>63</v>
+        <v>5</v>
       </c>
       <c r="B626" s="15">
         <v>45236</v>
@@ -20491,21 +20515,21 @@
         <v>45295</v>
       </c>
       <c r="E626" s="19" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="F626" s="19" t="s">
         <v>16</v>
       </c>
       <c r="G626" s="20">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="H626" s="21" t="s">
-        <v>891</v>
+        <v>468</v>
       </c>
     </row>
     <row r="627" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A627" s="12" t="s">
-        <v>86</v>
+        <v>5</v>
       </c>
       <c r="B627" s="13">
         <v>45236</v>
@@ -20517,21 +20541,21 @@
         <v>45295</v>
       </c>
       <c r="E627" s="16" t="s">
-        <v>892</v>
+        <v>887</v>
       </c>
       <c r="F627" s="16" t="s">
         <v>16</v>
       </c>
       <c r="G627" s="17">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H627" s="18" t="s">
-        <v>893</v>
+        <v>888</v>
       </c>
     </row>
     <row r="628" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A628" s="14" t="s">
-        <v>86</v>
+        <v>5</v>
       </c>
       <c r="B628" s="15">
         <v>45236</v>
@@ -20543,21 +20567,21 @@
         <v>45295</v>
       </c>
       <c r="E628" s="19" t="s">
-        <v>478</v>
+        <v>464</v>
       </c>
       <c r="F628" s="19" t="s">
         <v>16</v>
       </c>
       <c r="G628" s="20">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H628" s="21" t="s">
-        <v>479</v>
+        <v>889</v>
       </c>
     </row>
     <row r="629" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A629" s="12" t="s">
-        <v>86</v>
+        <v>5</v>
       </c>
       <c r="B629" s="13">
         <v>45236</v>
@@ -20569,21 +20593,21 @@
         <v>45295</v>
       </c>
       <c r="E629" s="16" t="s">
-        <v>894</v>
+        <v>464</v>
       </c>
       <c r="F629" s="16" t="s">
         <v>16</v>
       </c>
       <c r="G629" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H629" s="18" t="s">
-        <v>895</v>
+        <v>890</v>
       </c>
     </row>
     <row r="630" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A630" s="14" t="s">
-        <v>11</v>
+        <v>63</v>
       </c>
       <c r="B630" s="15">
         <v>45236</v>
@@ -20601,41 +20625,41 @@
         <v>16</v>
       </c>
       <c r="G630" s="20">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H630" s="21" t="s">
-        <v>896</v>
+        <v>891</v>
       </c>
     </row>
     <row r="631" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A631" s="12" t="s">
-        <v>9</v>
+        <v>86</v>
       </c>
       <c r="B631" s="13">
-        <v>45233</v>
+        <v>45236</v>
       </c>
       <c r="C631" s="13">
         <v>45272</v>
       </c>
       <c r="D631" s="13">
-        <v>45291</v>
+        <v>45295</v>
       </c>
       <c r="E631" s="16" t="s">
-        <v>51</v>
+        <v>892</v>
       </c>
       <c r="F631" s="16" t="s">
         <v>16</v>
       </c>
       <c r="G631" s="17">
-        <v>235</v>
+        <v>4</v>
       </c>
       <c r="H631" s="18" t="s">
-        <v>230</v>
+        <v>893</v>
       </c>
     </row>
     <row r="632" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A632" s="14" t="s">
-        <v>5</v>
+        <v>86</v>
       </c>
       <c r="B632" s="15">
         <v>45236</v>
@@ -20647,21 +20671,21 @@
         <v>45295</v>
       </c>
       <c r="E632" s="19" t="s">
-        <v>464</v>
+        <v>478</v>
       </c>
       <c r="F632" s="19" t="s">
         <v>16</v>
       </c>
       <c r="G632" s="20">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H632" s="21" t="s">
-        <v>897</v>
+        <v>479</v>
       </c>
     </row>
     <row r="633" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A633" s="12" t="s">
-        <v>5</v>
+        <v>86</v>
       </c>
       <c r="B633" s="13">
         <v>45236</v>
@@ -20673,27 +20697,27 @@
         <v>45295</v>
       </c>
       <c r="E633" s="16" t="s">
-        <v>464</v>
+        <v>894</v>
       </c>
       <c r="F633" s="16" t="s">
         <v>16</v>
       </c>
       <c r="G633" s="17">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="H633" s="18" t="s">
-        <v>898</v>
+        <v>895</v>
       </c>
     </row>
     <row r="634" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A634" s="14" t="s">
-        <v>86</v>
+        <v>11</v>
       </c>
       <c r="B634" s="15">
         <v>45236</v>
       </c>
       <c r="C634" s="15">
-        <v>45273</v>
+        <v>45272</v>
       </c>
       <c r="D634" s="15">
         <v>45295</v>
@@ -20705,62 +20729,62 @@
         <v>16</v>
       </c>
       <c r="G634" s="20">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="H634" s="21" t="s">
-        <v>465</v>
+        <v>896</v>
       </c>
     </row>
     <row r="635" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A635" s="12" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B635" s="13">
-        <v>45236</v>
+        <v>45233</v>
       </c>
       <c r="C635" s="13">
-        <v>45273</v>
+        <v>45272</v>
       </c>
       <c r="D635" s="13">
-        <v>45295</v>
+        <v>45291</v>
       </c>
       <c r="E635" s="16" t="s">
-        <v>464</v>
+        <v>51</v>
       </c>
       <c r="F635" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G635" s="17">
-        <v>1</v>
+        <v>235</v>
       </c>
       <c r="H635" s="18" t="s">
-        <v>899</v>
+        <v>230</v>
       </c>
     </row>
     <row r="636" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A636" s="14" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B636" s="15">
-        <v>45243</v>
+        <v>45236</v>
       </c>
       <c r="C636" s="15">
-        <v>45273</v>
+        <v>45272</v>
       </c>
       <c r="D636" s="15">
-        <v>45303</v>
+        <v>45295</v>
       </c>
       <c r="E636" s="19" t="s">
-        <v>900</v>
+        <v>464</v>
       </c>
       <c r="F636" s="19" t="s">
         <v>16</v>
       </c>
       <c r="G636" s="20">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="H636" s="21" t="s">
-        <v>901</v>
+        <v>897</v>
       </c>
     </row>
     <row r="637" spans="1:8" x14ac:dyDescent="0.25">
@@ -20771,27 +20795,27 @@
         <v>45236</v>
       </c>
       <c r="C637" s="13">
-        <v>45273</v>
+        <v>45272</v>
       </c>
       <c r="D637" s="13">
-        <v>45310</v>
+        <v>45295</v>
       </c>
       <c r="E637" s="16" t="s">
-        <v>902</v>
+        <v>464</v>
       </c>
       <c r="F637" s="16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G637" s="17">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="H637" s="18" t="s">
-        <v>38</v>
+        <v>898</v>
       </c>
     </row>
     <row r="638" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A638" s="14" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="B638" s="15">
         <v>45236</v>
@@ -20809,15 +20833,15 @@
         <v>16</v>
       </c>
       <c r="G638" s="20">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="H638" s="21" t="s">
-        <v>483</v>
+        <v>465</v>
       </c>
     </row>
     <row r="639" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A639" s="12" t="s">
-        <v>76</v>
+        <v>14</v>
       </c>
       <c r="B639" s="13">
         <v>45236</v>
@@ -20829,47 +20853,47 @@
         <v>45295</v>
       </c>
       <c r="E639" s="16" t="s">
-        <v>903</v>
+        <v>464</v>
       </c>
       <c r="F639" s="16" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G639" s="17">
         <v>1</v>
       </c>
       <c r="H639" s="18" t="s">
-        <v>904</v>
+        <v>899</v>
       </c>
     </row>
     <row r="640" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A640" s="14" t="s">
-        <v>76</v>
+        <v>12</v>
       </c>
       <c r="B640" s="15">
-        <v>45238</v>
+        <v>45243</v>
       </c>
       <c r="C640" s="15">
         <v>45273</v>
       </c>
       <c r="D640" s="15">
-        <v>45306</v>
+        <v>45303</v>
       </c>
       <c r="E640" s="19" t="s">
-        <v>905</v>
+        <v>900</v>
       </c>
       <c r="F640" s="19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G640" s="20">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="H640" s="21" t="s">
-        <v>906</v>
+        <v>901</v>
       </c>
     </row>
     <row r="641" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A641" s="12" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B641" s="13">
         <v>45236</v>
@@ -20878,24 +20902,24 @@
         <v>45273</v>
       </c>
       <c r="D641" s="13">
-        <v>45295</v>
+        <v>45310</v>
       </c>
       <c r="E641" s="16" t="s">
-        <v>907</v>
+        <v>902</v>
       </c>
       <c r="F641" s="16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G641" s="17">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="H641" s="18" t="s">
-        <v>908</v>
+        <v>38</v>
       </c>
     </row>
     <row r="642" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A642" s="14" t="s">
-        <v>6</v>
+        <v>76</v>
       </c>
       <c r="B642" s="15">
         <v>45236</v>
@@ -20907,21 +20931,21 @@
         <v>45295</v>
       </c>
       <c r="E642" s="19" t="s">
-        <v>909</v>
+        <v>464</v>
       </c>
       <c r="F642" s="19" t="s">
         <v>16</v>
       </c>
       <c r="G642" s="20">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H642" s="21" t="s">
-        <v>910</v>
+        <v>483</v>
       </c>
     </row>
     <row r="643" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A643" s="12" t="s">
-        <v>6</v>
+        <v>76</v>
       </c>
       <c r="B643" s="13">
         <v>45236</v>
@@ -20933,21 +20957,21 @@
         <v>45295</v>
       </c>
       <c r="E643" s="16" t="s">
-        <v>911</v>
+        <v>903</v>
       </c>
       <c r="F643" s="16" t="s">
         <v>16</v>
       </c>
       <c r="G643" s="17">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H643" s="18" t="s">
-        <v>486</v>
+        <v>904</v>
       </c>
     </row>
     <row r="644" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A644" s="14" t="s">
-        <v>6</v>
+        <v>76</v>
       </c>
       <c r="B644" s="15">
         <v>45238</v>
@@ -20956,19 +20980,19 @@
         <v>45273</v>
       </c>
       <c r="D644" s="15">
-        <v>45298</v>
+        <v>45306</v>
       </c>
       <c r="E644" s="19" t="s">
-        <v>912</v>
+        <v>905</v>
       </c>
       <c r="F644" s="19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G644" s="20">
-        <v>140</v>
+        <v>51</v>
       </c>
       <c r="H644" s="21" t="s">
-        <v>913</v>
+        <v>906</v>
       </c>
     </row>
     <row r="645" spans="1:8" x14ac:dyDescent="0.25">
@@ -20976,134 +21000,134 @@
         <v>6</v>
       </c>
       <c r="B645" s="13">
-        <v>45238</v>
+        <v>45236</v>
       </c>
       <c r="C645" s="13">
         <v>45273</v>
       </c>
       <c r="D645" s="13">
-        <v>45328</v>
+        <v>45295</v>
       </c>
       <c r="E645" s="16" t="s">
-        <v>912</v>
+        <v>907</v>
       </c>
       <c r="F645" s="16" t="s">
         <v>16</v>
       </c>
       <c r="G645" s="17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H645" s="18" t="s">
-        <v>914</v>
+        <v>908</v>
       </c>
     </row>
     <row r="646" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A646" s="14" t="s">
-        <v>52</v>
+        <v>6</v>
       </c>
       <c r="B646" s="15">
-        <v>45231</v>
+        <v>45236</v>
       </c>
       <c r="C646" s="15">
         <v>45273</v>
       </c>
       <c r="D646" s="15">
-        <v>45278</v>
+        <v>45295</v>
       </c>
       <c r="E646" s="19" t="s">
-        <v>915</v>
+        <v>909</v>
       </c>
       <c r="F646" s="19" t="s">
         <v>16</v>
       </c>
       <c r="G646" s="20">
-        <v>93</v>
+        <v>1</v>
       </c>
       <c r="H646" s="21" t="s">
-        <v>916</v>
+        <v>910</v>
       </c>
     </row>
     <row r="647" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A647" s="12" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B647" s="13">
-        <v>45231</v>
+        <v>45236</v>
       </c>
       <c r="C647" s="13">
         <v>45273</v>
       </c>
       <c r="D647" s="13">
-        <v>45278</v>
+        <v>45295</v>
       </c>
       <c r="E647" s="16" t="s">
-        <v>915</v>
+        <v>911</v>
       </c>
       <c r="F647" s="16" t="s">
         <v>16</v>
       </c>
       <c r="G647" s="17">
-        <v>83</v>
+        <v>5</v>
       </c>
       <c r="H647" s="18" t="s">
-        <v>917</v>
+        <v>486</v>
       </c>
     </row>
     <row r="648" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A648" s="14" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B648" s="15">
-        <v>45239</v>
+        <v>45238</v>
       </c>
       <c r="C648" s="15">
         <v>45273</v>
       </c>
       <c r="D648" s="15">
-        <v>45299</v>
+        <v>45298</v>
       </c>
       <c r="E648" s="19" t="s">
-        <v>305</v>
+        <v>912</v>
       </c>
       <c r="F648" s="19" t="s">
         <v>16</v>
       </c>
       <c r="G648" s="20">
-        <v>87</v>
+        <v>140</v>
       </c>
       <c r="H648" s="21" t="s">
-        <v>918</v>
+        <v>913</v>
       </c>
     </row>
     <row r="649" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A649" s="12" t="s">
-        <v>789</v>
+        <v>6</v>
       </c>
       <c r="B649" s="13">
-        <v>45243</v>
+        <v>45238</v>
       </c>
       <c r="C649" s="13">
         <v>45273</v>
       </c>
       <c r="D649" s="13">
-        <v>45303</v>
+        <v>45328</v>
       </c>
       <c r="E649" s="16" t="s">
-        <v>919</v>
+        <v>912</v>
       </c>
       <c r="F649" s="16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G649" s="17">
         <v>7</v>
       </c>
       <c r="H649" s="18" t="s">
-        <v>920</v>
+        <v>914</v>
       </c>
     </row>
     <row r="650" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A650" s="14" t="s">
-        <v>282</v>
+        <v>52</v>
       </c>
       <c r="B650" s="15">
         <v>45231</v>
@@ -21112,24 +21136,24 @@
         <v>45273</v>
       </c>
       <c r="D650" s="15">
-        <v>45291</v>
+        <v>45278</v>
       </c>
       <c r="E650" s="19" t="s">
-        <v>921</v>
+        <v>915</v>
       </c>
       <c r="F650" s="19" t="s">
         <v>16</v>
       </c>
       <c r="G650" s="20">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="H650" s="21" t="s">
-        <v>922</v>
+        <v>916</v>
       </c>
     </row>
     <row r="651" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A651" s="12" t="s">
-        <v>282</v>
+        <v>7</v>
       </c>
       <c r="B651" s="13">
         <v>45231</v>
@@ -21138,114 +21162,114 @@
         <v>45273</v>
       </c>
       <c r="D651" s="13">
-        <v>45291</v>
+        <v>45278</v>
       </c>
       <c r="E651" s="16" t="s">
-        <v>921</v>
+        <v>915</v>
       </c>
       <c r="F651" s="16" t="s">
         <v>16</v>
       </c>
       <c r="G651" s="17">
-        <v>1</v>
+        <v>83</v>
       </c>
       <c r="H651" s="18" t="s">
-        <v>923</v>
+        <v>917</v>
       </c>
     </row>
     <row r="652" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A652" s="14" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B652" s="15">
-        <v>45232</v>
+        <v>45239</v>
       </c>
       <c r="C652" s="15">
-        <v>45274</v>
+        <v>45273</v>
       </c>
       <c r="D652" s="15">
-        <v>45275</v>
+        <v>45299</v>
       </c>
       <c r="E652" s="19" t="s">
-        <v>924</v>
+        <v>305</v>
       </c>
       <c r="F652" s="19" t="s">
         <v>16</v>
       </c>
       <c r="G652" s="20">
-        <v>1</v>
+        <v>87</v>
       </c>
       <c r="H652" s="21" t="s">
-        <v>925</v>
+        <v>918</v>
       </c>
     </row>
     <row r="653" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A653" s="12" t="s">
-        <v>5</v>
+        <v>789</v>
       </c>
       <c r="B653" s="13">
-        <v>45232</v>
+        <v>45243</v>
       </c>
       <c r="C653" s="13">
-        <v>45274</v>
+        <v>45273</v>
       </c>
       <c r="D653" s="13">
-        <v>45276</v>
+        <v>45303</v>
       </c>
       <c r="E653" s="16" t="s">
-        <v>924</v>
+        <v>919</v>
       </c>
       <c r="F653" s="16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G653" s="17">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H653" s="18" t="s">
-        <v>925</v>
+        <v>920</v>
       </c>
     </row>
     <row r="654" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A654" s="14" t="s">
-        <v>5</v>
+        <v>282</v>
       </c>
       <c r="B654" s="15">
-        <v>45232</v>
+        <v>45231</v>
       </c>
       <c r="C654" s="15">
-        <v>45274</v>
+        <v>45273</v>
       </c>
       <c r="D654" s="15">
-        <v>45277</v>
+        <v>45291</v>
       </c>
       <c r="E654" s="19" t="s">
-        <v>924</v>
+        <v>921</v>
       </c>
       <c r="F654" s="19" t="s">
         <v>16</v>
       </c>
       <c r="G654" s="20">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="H654" s="21" t="s">
-        <v>925</v>
+        <v>922</v>
       </c>
     </row>
     <row r="655" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A655" s="12" t="s">
-        <v>5</v>
+        <v>282</v>
       </c>
       <c r="B655" s="13">
-        <v>45232</v>
+        <v>45231</v>
       </c>
       <c r="C655" s="13">
-        <v>45274</v>
+        <v>45273</v>
       </c>
       <c r="D655" s="13">
-        <v>45278</v>
+        <v>45291</v>
       </c>
       <c r="E655" s="16" t="s">
-        <v>924</v>
+        <v>921</v>
       </c>
       <c r="F655" s="16" t="s">
         <v>16</v>
@@ -21254,7 +21278,7 @@
         <v>1</v>
       </c>
       <c r="H655" s="18" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
     </row>
     <row r="656" spans="1:8" x14ac:dyDescent="0.25">
@@ -21268,7 +21292,7 @@
         <v>45274</v>
       </c>
       <c r="D656" s="15">
-        <v>45279</v>
+        <v>45275</v>
       </c>
       <c r="E656" s="19" t="s">
         <v>924</v>
@@ -21294,7 +21318,7 @@
         <v>45274</v>
       </c>
       <c r="D657" s="13">
-        <v>45280</v>
+        <v>45276</v>
       </c>
       <c r="E657" s="16" t="s">
         <v>924</v>
@@ -21320,7 +21344,7 @@
         <v>45274</v>
       </c>
       <c r="D658" s="15">
-        <v>45281</v>
+        <v>45277</v>
       </c>
       <c r="E658" s="19" t="s">
         <v>924</v>
@@ -21346,7 +21370,7 @@
         <v>45274</v>
       </c>
       <c r="D659" s="13">
-        <v>45282</v>
+        <v>45278</v>
       </c>
       <c r="E659" s="16" t="s">
         <v>924</v>
@@ -21372,7 +21396,7 @@
         <v>45274</v>
       </c>
       <c r="D660" s="15">
-        <v>45283</v>
+        <v>45279</v>
       </c>
       <c r="E660" s="19" t="s">
         <v>924</v>
@@ -21398,7 +21422,7 @@
         <v>45274</v>
       </c>
       <c r="D661" s="13">
-        <v>45284</v>
+        <v>45280</v>
       </c>
       <c r="E661" s="16" t="s">
         <v>924</v>
@@ -21424,7 +21448,7 @@
         <v>45274</v>
       </c>
       <c r="D662" s="15">
-        <v>45285</v>
+        <v>45281</v>
       </c>
       <c r="E662" s="19" t="s">
         <v>924</v>
@@ -21450,7 +21474,7 @@
         <v>45274</v>
       </c>
       <c r="D663" s="13">
-        <v>45290</v>
+        <v>45282</v>
       </c>
       <c r="E663" s="16" t="s">
         <v>924</v>
@@ -21459,7 +21483,7 @@
         <v>16</v>
       </c>
       <c r="G663" s="17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H663" s="18" t="s">
         <v>925</v>
@@ -21467,215 +21491,215 @@
     </row>
     <row r="664" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A664" s="14" t="s">
-        <v>926</v>
+        <v>5</v>
       </c>
       <c r="B664" s="15">
-        <v>45231</v>
+        <v>45232</v>
       </c>
       <c r="C664" s="15">
         <v>45274</v>
       </c>
       <c r="D664" s="15">
-        <v>45292</v>
+        <v>45283</v>
       </c>
       <c r="E664" s="19" t="s">
-        <v>927</v>
+        <v>924</v>
       </c>
       <c r="F664" s="19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G664" s="20">
-        <v>142</v>
+        <v>1</v>
       </c>
       <c r="H664" s="21" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
     </row>
     <row r="665" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A665" s="12" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B665" s="13">
-        <v>45245</v>
+        <v>45232</v>
       </c>
       <c r="C665" s="13">
         <v>45274</v>
       </c>
       <c r="D665" s="13">
-        <v>45307</v>
+        <v>45284</v>
       </c>
       <c r="E665" s="16" t="s">
-        <v>929</v>
+        <v>924</v>
       </c>
       <c r="F665" s="16" t="s">
         <v>16</v>
       </c>
       <c r="G665" s="17">
-        <v>58</v>
+        <v>1</v>
       </c>
       <c r="H665" s="18" t="s">
-        <v>930</v>
+        <v>925</v>
       </c>
     </row>
     <row r="666" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A666" s="14" t="s">
-        <v>66</v>
+        <v>5</v>
       </c>
       <c r="B666" s="15">
-        <v>45245</v>
+        <v>45232</v>
       </c>
       <c r="C666" s="15">
         <v>45274</v>
       </c>
       <c r="D666" s="15">
-        <v>45307</v>
+        <v>45285</v>
       </c>
       <c r="E666" s="19" t="s">
-        <v>929</v>
+        <v>924</v>
       </c>
       <c r="F666" s="19" t="s">
         <v>16</v>
       </c>
       <c r="G666" s="20">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H666" s="21" t="s">
-        <v>931</v>
+        <v>925</v>
       </c>
     </row>
     <row r="667" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A667" s="12" t="s">
-        <v>76</v>
+        <v>5</v>
       </c>
       <c r="B667" s="13">
-        <v>45239</v>
+        <v>45232</v>
       </c>
       <c r="C667" s="13">
         <v>45274</v>
       </c>
       <c r="D667" s="13">
-        <v>45299</v>
+        <v>45290</v>
       </c>
       <c r="E667" s="16" t="s">
-        <v>654</v>
+        <v>924</v>
       </c>
       <c r="F667" s="16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G667" s="17">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="H667" s="18" t="s">
-        <v>655</v>
+        <v>925</v>
       </c>
     </row>
     <row r="668" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A668" s="14" t="s">
-        <v>5</v>
+        <v>926</v>
       </c>
       <c r="B668" s="15">
-        <v>45236</v>
+        <v>45231</v>
       </c>
       <c r="C668" s="15">
-        <v>45275</v>
+        <v>45274</v>
       </c>
       <c r="D668" s="15">
-        <v>45306</v>
+        <v>45292</v>
       </c>
       <c r="E668" s="19" t="s">
-        <v>932</v>
+        <v>927</v>
       </c>
       <c r="F668" s="19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G668" s="20">
-        <v>29</v>
+        <v>142</v>
       </c>
       <c r="H668" s="21" t="s">
-        <v>933</v>
+        <v>928</v>
       </c>
     </row>
     <row r="669" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A669" s="12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B669" s="13">
-        <v>45236</v>
+        <v>45245</v>
       </c>
       <c r="C669" s="13">
-        <v>45275</v>
+        <v>45274</v>
       </c>
       <c r="D669" s="13">
-        <v>45296</v>
+        <v>45307</v>
       </c>
       <c r="E669" s="16" t="s">
-        <v>934</v>
+        <v>929</v>
       </c>
       <c r="F669" s="16" t="s">
         <v>16</v>
       </c>
       <c r="G669" s="17">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="H669" s="18" t="s">
-        <v>935</v>
+        <v>930</v>
       </c>
     </row>
     <row r="670" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A670" s="14" t="s">
-        <v>6</v>
+        <v>66</v>
       </c>
       <c r="B670" s="15">
-        <v>45236</v>
+        <v>45245</v>
       </c>
       <c r="C670" s="15">
-        <v>45275</v>
+        <v>45274</v>
       </c>
       <c r="D670" s="15">
-        <v>45296</v>
+        <v>45307</v>
       </c>
       <c r="E670" s="19" t="s">
-        <v>934</v>
+        <v>929</v>
       </c>
       <c r="F670" s="19" t="s">
         <v>16</v>
       </c>
       <c r="G670" s="20">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H670" s="21" t="s">
-        <v>936</v>
+        <v>931</v>
       </c>
     </row>
     <row r="671" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A671" s="12" t="s">
-        <v>6</v>
+        <v>76</v>
       </c>
       <c r="B671" s="13">
-        <v>45236</v>
+        <v>45239</v>
       </c>
       <c r="C671" s="13">
-        <v>45275</v>
+        <v>45274</v>
       </c>
       <c r="D671" s="13">
-        <v>45296</v>
+        <v>45299</v>
       </c>
       <c r="E671" s="16" t="s">
-        <v>934</v>
+        <v>654</v>
       </c>
       <c r="F671" s="16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G671" s="17">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="H671" s="18" t="s">
-        <v>937</v>
+        <v>655</v>
       </c>
     </row>
     <row r="672" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A672" s="14" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B672" s="15">
         <v>45236</v>
@@ -21684,62 +21708,62 @@
         <v>45275</v>
       </c>
       <c r="D672" s="15">
-        <v>45296</v>
+        <v>45306</v>
       </c>
       <c r="E672" s="19" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="F672" s="19" t="s">
         <v>16</v>
       </c>
       <c r="G672" s="20">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="H672" s="21" t="s">
-        <v>938</v>
+        <v>933</v>
       </c>
     </row>
     <row r="673" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A673" s="12" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B673" s="13">
-        <v>45238</v>
+        <v>45236</v>
       </c>
       <c r="C673" s="13">
-        <v>45278</v>
+        <v>45275</v>
       </c>
       <c r="D673" s="13">
-        <v>45299</v>
+        <v>45296</v>
       </c>
       <c r="E673" s="16" t="s">
-        <v>939</v>
+        <v>934</v>
       </c>
       <c r="F673" s="16" t="s">
         <v>16</v>
       </c>
       <c r="G673" s="17">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="H673" s="18" t="s">
-        <v>940</v>
+        <v>935</v>
       </c>
     </row>
     <row r="674" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A674" s="14" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B674" s="15">
-        <v>45238</v>
+        <v>45236</v>
       </c>
       <c r="C674" s="15">
-        <v>45278</v>
+        <v>45275</v>
       </c>
       <c r="D674" s="15">
-        <v>45299</v>
+        <v>45296</v>
       </c>
       <c r="E674" s="19" t="s">
-        <v>939</v>
+        <v>934</v>
       </c>
       <c r="F674" s="19" t="s">
         <v>16</v>
@@ -21748,24 +21772,24 @@
         <v>1</v>
       </c>
       <c r="H674" s="21" t="s">
-        <v>941</v>
+        <v>936</v>
       </c>
     </row>
     <row r="675" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A675" s="12" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B675" s="13">
-        <v>45238</v>
+        <v>45236</v>
       </c>
       <c r="C675" s="13">
-        <v>45278</v>
+        <v>45275</v>
       </c>
       <c r="D675" s="13">
-        <v>45299</v>
+        <v>45296</v>
       </c>
       <c r="E675" s="16" t="s">
-        <v>939</v>
+        <v>934</v>
       </c>
       <c r="F675" s="16" t="s">
         <v>16</v>
@@ -21774,24 +21798,24 @@
         <v>1</v>
       </c>
       <c r="H675" s="18" t="s">
-        <v>942</v>
+        <v>937</v>
       </c>
     </row>
     <row r="676" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A676" s="14" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B676" s="15">
-        <v>45238</v>
+        <v>45236</v>
       </c>
       <c r="C676" s="15">
-        <v>45278</v>
+        <v>45275</v>
       </c>
       <c r="D676" s="15">
-        <v>45299</v>
+        <v>45296</v>
       </c>
       <c r="E676" s="19" t="s">
-        <v>939</v>
+        <v>934</v>
       </c>
       <c r="F676" s="19" t="s">
         <v>16</v>
@@ -21800,50 +21824,50 @@
         <v>1</v>
       </c>
       <c r="H676" s="21" t="s">
-        <v>943</v>
+        <v>938</v>
       </c>
     </row>
     <row r="677" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A677" s="12" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B677" s="13">
-        <v>45233</v>
+        <v>45238</v>
       </c>
       <c r="C677" s="13">
         <v>45278</v>
       </c>
       <c r="D677" s="13">
-        <v>45291</v>
+        <v>45299</v>
       </c>
       <c r="E677" s="16" t="s">
-        <v>51</v>
+        <v>939</v>
       </c>
       <c r="F677" s="16" t="s">
         <v>16</v>
       </c>
       <c r="G677" s="17">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="H677" s="18" t="s">
-        <v>255</v>
+        <v>940</v>
       </c>
     </row>
     <row r="678" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A678" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B678" s="15">
-        <v>45233</v>
+        <v>45238</v>
       </c>
       <c r="C678" s="15">
         <v>45278</v>
       </c>
       <c r="D678" s="15">
-        <v>45291</v>
+        <v>45299</v>
       </c>
       <c r="E678" s="19" t="s">
-        <v>51</v>
+        <v>939</v>
       </c>
       <c r="F678" s="19" t="s">
         <v>16</v>
@@ -21852,24 +21876,24 @@
         <v>1</v>
       </c>
       <c r="H678" s="21" t="s">
-        <v>944</v>
+        <v>941</v>
       </c>
     </row>
     <row r="679" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A679" s="12" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B679" s="13">
-        <v>45233</v>
+        <v>45238</v>
       </c>
       <c r="C679" s="13">
         <v>45278</v>
       </c>
       <c r="D679" s="13">
-        <v>45291</v>
+        <v>45299</v>
       </c>
       <c r="E679" s="16" t="s">
-        <v>51</v>
+        <v>939</v>
       </c>
       <c r="F679" s="16" t="s">
         <v>16</v>
@@ -21878,24 +21902,24 @@
         <v>1</v>
       </c>
       <c r="H679" s="18" t="s">
-        <v>258</v>
+        <v>942</v>
       </c>
     </row>
     <row r="680" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A680" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B680" s="15">
-        <v>45233</v>
+        <v>45238</v>
       </c>
       <c r="C680" s="15">
         <v>45278</v>
       </c>
       <c r="D680" s="15">
-        <v>45291</v>
+        <v>45299</v>
       </c>
       <c r="E680" s="19" t="s">
-        <v>51</v>
+        <v>939</v>
       </c>
       <c r="F680" s="19" t="s">
         <v>16</v>
@@ -21904,7 +21928,7 @@
         <v>1</v>
       </c>
       <c r="H680" s="21" t="s">
-        <v>257</v>
+        <v>943</v>
       </c>
     </row>
     <row r="681" spans="1:8" x14ac:dyDescent="0.25">
@@ -21912,42 +21936,42 @@
         <v>7</v>
       </c>
       <c r="B681" s="13">
-        <v>45239</v>
+        <v>45233</v>
       </c>
       <c r="C681" s="13">
         <v>45278</v>
       </c>
       <c r="D681" s="13">
-        <v>45317</v>
+        <v>45291</v>
       </c>
       <c r="E681" s="16" t="s">
-        <v>945</v>
+        <v>51</v>
       </c>
       <c r="F681" s="16" t="s">
         <v>16</v>
       </c>
       <c r="G681" s="17">
-        <v>32</v>
+        <v>73</v>
       </c>
       <c r="H681" s="18" t="s">
-        <v>946</v>
+        <v>255</v>
       </c>
     </row>
     <row r="682" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A682" s="14" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B682" s="15">
-        <v>45239</v>
+        <v>45233</v>
       </c>
       <c r="C682" s="15">
         <v>45278</v>
       </c>
       <c r="D682" s="15">
-        <v>45303</v>
+        <v>45291</v>
       </c>
       <c r="E682" s="19" t="s">
-        <v>945</v>
+        <v>51</v>
       </c>
       <c r="F682" s="19" t="s">
         <v>16</v>
@@ -21956,85 +21980,85 @@
         <v>1</v>
       </c>
       <c r="H682" s="21" t="s">
-        <v>734</v>
+        <v>944</v>
       </c>
     </row>
     <row r="683" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A683" s="12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B683" s="13">
-        <v>45239</v>
+        <v>45233</v>
       </c>
       <c r="C683" s="13">
         <v>45278</v>
       </c>
       <c r="D683" s="13">
-        <v>45317</v>
+        <v>45291</v>
       </c>
       <c r="E683" s="16" t="s">
-        <v>945</v>
+        <v>51</v>
       </c>
       <c r="F683" s="16" t="s">
         <v>16</v>
       </c>
       <c r="G683" s="17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H683" s="18" t="s">
-        <v>736</v>
+        <v>258</v>
       </c>
     </row>
     <row r="684" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A684" s="14" t="s">
-        <v>97</v>
+        <v>7</v>
       </c>
       <c r="B684" s="15">
-        <v>45239</v>
+        <v>45233</v>
       </c>
       <c r="C684" s="15">
         <v>45278</v>
       </c>
       <c r="D684" s="15">
-        <v>45299</v>
+        <v>45291</v>
       </c>
       <c r="E684" s="19" t="s">
-        <v>947</v>
+        <v>51</v>
       </c>
       <c r="F684" s="19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G684" s="20">
-        <v>130</v>
+        <v>1</v>
       </c>
       <c r="H684" s="21" t="s">
-        <v>948</v>
+        <v>257</v>
       </c>
     </row>
     <row r="685" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A685" s="12" t="s">
-        <v>63</v>
+        <v>7</v>
       </c>
       <c r="B685" s="13">
-        <v>45244</v>
+        <v>45239</v>
       </c>
       <c r="C685" s="13">
-        <v>45280</v>
+        <v>45278</v>
       </c>
       <c r="D685" s="13">
-        <v>45305</v>
+        <v>45317</v>
       </c>
       <c r="E685" s="16" t="s">
-        <v>949</v>
+        <v>945</v>
       </c>
       <c r="F685" s="16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G685" s="17">
-        <v>103</v>
+        <v>32</v>
       </c>
       <c r="H685" s="18" t="s">
-        <v>950</v>
+        <v>946</v>
       </c>
     </row>
     <row r="686" spans="1:8" x14ac:dyDescent="0.25">
@@ -22042,51 +22066,337 @@
         <v>6</v>
       </c>
       <c r="B686" s="15">
-        <v>45243</v>
+        <v>45239</v>
       </c>
       <c r="C686" s="15">
-        <v>45280</v>
+        <v>45278</v>
       </c>
       <c r="D686" s="15">
         <v>45303</v>
       </c>
       <c r="E686" s="19" t="s">
-        <v>296</v>
+        <v>945</v>
       </c>
       <c r="F686" s="19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G686" s="20">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H686" s="21" t="s">
-        <v>951</v>
+        <v>734</v>
       </c>
     </row>
     <row r="687" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A687" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B687" s="13">
+        <v>45239</v>
+      </c>
+      <c r="C687" s="13">
+        <v>45278</v>
+      </c>
+      <c r="D687" s="13">
+        <v>45317</v>
+      </c>
+      <c r="E687" s="16" t="s">
+        <v>945</v>
+      </c>
+      <c r="F687" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G687" s="17">
+        <v>3</v>
+      </c>
+      <c r="H687" s="18" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="688" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A688" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="B688" s="15">
+        <v>45239</v>
+      </c>
+      <c r="C688" s="15">
+        <v>45278</v>
+      </c>
+      <c r="D688" s="15">
+        <v>45299</v>
+      </c>
+      <c r="E688" s="19" t="s">
+        <v>947</v>
+      </c>
+      <c r="F688" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="G688" s="20">
+        <v>130</v>
+      </c>
+      <c r="H688" s="21" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="689" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A689" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="B689" s="13">
+        <v>45244</v>
+      </c>
+      <c r="C689" s="13">
+        <v>45280</v>
+      </c>
+      <c r="D689" s="13">
+        <v>45305</v>
+      </c>
+      <c r="E689" s="16" t="s">
+        <v>949</v>
+      </c>
+      <c r="F689" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G689" s="17">
+        <v>103</v>
+      </c>
+      <c r="H689" s="18" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="690" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A690" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B690" s="15">
+        <v>45243</v>
+      </c>
+      <c r="C690" s="15">
+        <v>45280</v>
+      </c>
+      <c r="D690" s="15">
+        <v>45303</v>
+      </c>
+      <c r="E690" s="19" t="s">
+        <v>296</v>
+      </c>
+      <c r="F690" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G690" s="20">
+        <v>4</v>
+      </c>
+      <c r="H690" s="21" t="s">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="691" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A691" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="B687" s="13">
+      <c r="B691" s="13">
         <v>45245</v>
       </c>
-      <c r="C687" s="13">
+      <c r="C691" s="13">
         <v>45280</v>
       </c>
-      <c r="D687" s="13">
+      <c r="D691" s="13">
         <v>45306</v>
       </c>
-      <c r="E687" s="16" t="s">
+      <c r="E691" s="16" t="s">
         <v>952</v>
       </c>
-      <c r="F687" s="16" t="s">
+      <c r="F691" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="G687" s="17">
+      <c r="G691" s="17">
         <v>85</v>
       </c>
-      <c r="H687" s="18" t="s">
+      <c r="H691" s="18" t="s">
         <v>953</v>
+      </c>
+    </row>
+    <row r="692" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A692" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="B692" s="15">
+        <v>45245</v>
+      </c>
+      <c r="C692" s="15">
+        <v>45281</v>
+      </c>
+      <c r="D692" s="15">
+        <v>45307</v>
+      </c>
+      <c r="E692" s="19" t="s">
+        <v>954</v>
+      </c>
+      <c r="F692" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G692" s="20">
+        <v>56</v>
+      </c>
+      <c r="H692" s="21" t="s">
+        <v>955</v>
+      </c>
+    </row>
+    <row r="693" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A693" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="B693" s="13">
+        <v>45245</v>
+      </c>
+      <c r="C693" s="13">
+        <v>45281</v>
+      </c>
+      <c r="D693" s="13">
+        <v>45323</v>
+      </c>
+      <c r="E693" s="16" t="s">
+        <v>954</v>
+      </c>
+      <c r="F693" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G693" s="17">
+        <v>2</v>
+      </c>
+      <c r="H693" s="18" t="s">
+        <v>955</v>
+      </c>
+    </row>
+    <row r="694" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A694" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="B694" s="15">
+        <v>45245</v>
+      </c>
+      <c r="C694" s="15">
+        <v>45281</v>
+      </c>
+      <c r="D694" s="15">
+        <v>45352</v>
+      </c>
+      <c r="E694" s="19" t="s">
+        <v>954</v>
+      </c>
+      <c r="F694" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G694" s="20">
+        <v>45</v>
+      </c>
+      <c r="H694" s="21" t="s">
+        <v>955</v>
+      </c>
+    </row>
+    <row r="695" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A695" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="B695" s="13">
+        <v>45245</v>
+      </c>
+      <c r="C695" s="13">
+        <v>45281</v>
+      </c>
+      <c r="D695" s="13">
+        <v>45310</v>
+      </c>
+      <c r="E695" s="16" t="s">
+        <v>956</v>
+      </c>
+      <c r="F695" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G695" s="17">
+        <v>57</v>
+      </c>
+      <c r="H695" s="18" t="s">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="696" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A696" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="B696" s="15">
+        <v>45245</v>
+      </c>
+      <c r="C696" s="15">
+        <v>45282</v>
+      </c>
+      <c r="D696" s="15">
+        <v>45261</v>
+      </c>
+      <c r="E696" s="19" t="s">
+        <v>958</v>
+      </c>
+      <c r="F696" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G696" s="20">
+        <v>50</v>
+      </c>
+      <c r="H696" s="21" t="s">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="697" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A697" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B697" s="13">
+        <v>45245</v>
+      </c>
+      <c r="C697" s="13">
+        <v>45282</v>
+      </c>
+      <c r="D697" s="13">
+        <v>45261</v>
+      </c>
+      <c r="E697" s="16" t="s">
+        <v>958</v>
+      </c>
+      <c r="F697" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G697" s="17">
+        <v>15</v>
+      </c>
+      <c r="H697" s="18" t="s">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="698" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A698" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="B698" s="15">
+        <v>45245</v>
+      </c>
+      <c r="C698" s="15">
+        <v>45282</v>
+      </c>
+      <c r="D698" s="15">
+        <v>45323</v>
+      </c>
+      <c r="E698" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="F698" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G698" s="20">
+        <v>74</v>
+      </c>
+      <c r="H698" s="21" t="s">
+        <v>961</v>
       </c>
     </row>
   </sheetData>
@@ -22228,13 +22538,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE073E07-F3E7-42A4-84A1-A3D57141FBD2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8DB43AC9-8DB6-4E14-954F-CE630D1075EA}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64BC2BAC-5B33-432A-920B-0D9898CF0092}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A88990FD-088B-45B9-8751-4C56F8338E29}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66C4B2B8-03F8-4672-99EC-6FFAC505985D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{110ED65F-5BD8-4447-9020-646F355DDC41}"/>
 </file>
--- a/data/warn-scraper/cache/ca/warn_report1.xlsx
+++ b/data/warn-scraper/cache/ca/warn_report1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\WSB-CO\Communications Unit\Website Management\WARN (Worker Adjustment and Retraining Notification) Updates\2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{611F7AF5-66EE-40D7-A09B-E62FEA6B3D8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B19C4A40-FD45-4BE7-84C2-DB789B34E002}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="624" yWindow="684" windowWidth="21600" windowHeight="11436" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2839" uniqueCount="973">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2899" uniqueCount="991">
   <si>
     <t>County/Parish</t>
   </si>
@@ -3020,6 +3020,60 @@
     <t>900 North Pacific Coast Hwy.  El Segundo CA 90245</t>
   </si>
   <si>
+    <t>Pennymac</t>
+  </si>
+  <si>
+    <t>251 S. Lake Avenue  Pasadena CA 91101</t>
+  </si>
+  <si>
+    <t>3013 Douglas Blvd.  Roseville CA 95661</t>
+  </si>
+  <si>
+    <t>Blue Shield of California</t>
+  </si>
+  <si>
+    <t>601 12th Street  Oakland CA 94607</t>
+  </si>
+  <si>
+    <t>El Dorado County</t>
+  </si>
+  <si>
+    <t>4205 Town Center Blvd., Building B  El Dorado Hills CA 95762</t>
+  </si>
+  <si>
+    <t>4203 Town Center Blvd., Building C  El Dorado Hills CA 95762</t>
+  </si>
+  <si>
+    <t>3840 Kilroy Airport Way  Long Beach CA 90806</t>
+  </si>
+  <si>
+    <t>6300 Canoga Avenue  Los Angeles CA 91367</t>
+  </si>
+  <si>
+    <t>3300 Zinfandel Drive, Building A  Rancho Cordova CA 95670</t>
+  </si>
+  <si>
+    <t>10834 International Drive, Building A  Rancho Cordova CA 95670</t>
+  </si>
+  <si>
+    <t>3131 Camino Del Rio North, Ste. #1300  San Diego CA 92108</t>
+  </si>
+  <si>
+    <t>3201 Reynolds Ranch Parkway  Lodi CA 95240</t>
+  </si>
+  <si>
+    <t>4700 Bechelli Lane  Redding CA 96002</t>
+  </si>
+  <si>
+    <t>29903 Agoura Road  Agoura Hills CA 91301</t>
+  </si>
+  <si>
+    <t>3143 Townsgate Road  Westlake Village CA 91361</t>
+  </si>
+  <si>
+    <t>6101 Condor Drive  Moorpark CA 93021</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">WARN REPORT - </t>
     </r>
@@ -3031,7 +3085,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>07/01/23 to 12/27/23</t>
+      <t>07/01/23 to 01/01/24</t>
     </r>
     <r>
       <rPr>
@@ -3051,7 +3105,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>A detailed WARN summary by county and filtered according to received date. Table Spans cells A2 through H706.</t>
+      <t>A detailed WARN summary by county and filtered according to received date. Table Spans cells A2 through H721.</t>
     </r>
   </si>
 </sst>
@@ -3834,8 +3888,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:H706" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
-  <autoFilter ref="A2:H706" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:H721" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
+  <autoFilter ref="A2:H721" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -4219,7 +4273,7 @@
       </c>
       <c r="B3" s="5">
         <f>SUM('Detailed WARN Report '!G:G)</f>
-        <v>36910</v>
+        <v>37159</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -4228,7 +4282,7 @@
       </c>
       <c r="B4" s="5">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Permanent")</f>
-        <v>477</v>
+        <v>492</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -4286,7 +4340,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:H706"/>
+  <dimension ref="A1:H721"/>
   <sheetFormatPr defaultColWidth="26" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.88671875" bestFit="1" customWidth="1"/>
@@ -4299,7 +4353,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="99.6" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
-        <v>972</v>
+        <v>990</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -22635,6 +22689,396 @@
       </c>
       <c r="H706" s="21" t="s">
         <v>971</v>
+      </c>
+    </row>
+    <row r="707" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A707" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B707" s="13">
+        <v>45245</v>
+      </c>
+      <c r="C707" s="13">
+        <v>45289</v>
+      </c>
+      <c r="D707" s="13">
+        <v>45271</v>
+      </c>
+      <c r="E707" s="14" t="s">
+        <v>972</v>
+      </c>
+      <c r="F707" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G707" s="15">
+        <v>18</v>
+      </c>
+      <c r="H707" s="16" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="708" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A708" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="B708" s="18">
+        <v>45245</v>
+      </c>
+      <c r="C708" s="18">
+        <v>45289</v>
+      </c>
+      <c r="D708" s="18">
+        <v>45307</v>
+      </c>
+      <c r="E708" s="19" t="s">
+        <v>972</v>
+      </c>
+      <c r="F708" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G708" s="20">
+        <v>2</v>
+      </c>
+      <c r="H708" s="21" t="s">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="709" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A709" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="B709" s="13">
+        <v>45257</v>
+      </c>
+      <c r="C709" s="13">
+        <v>45289</v>
+      </c>
+      <c r="D709" s="13">
+        <v>45322</v>
+      </c>
+      <c r="E709" s="14" t="s">
+        <v>975</v>
+      </c>
+      <c r="F709" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G709" s="15">
+        <v>49</v>
+      </c>
+      <c r="H709" s="16" t="s">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="710" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A710" s="17" t="s">
+        <v>977</v>
+      </c>
+      <c r="B710" s="18">
+        <v>45257</v>
+      </c>
+      <c r="C710" s="18">
+        <v>45289</v>
+      </c>
+      <c r="D710" s="18">
+        <v>45322</v>
+      </c>
+      <c r="E710" s="19" t="s">
+        <v>975</v>
+      </c>
+      <c r="F710" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G710" s="20">
+        <v>31</v>
+      </c>
+      <c r="H710" s="21" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="711" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A711" s="12" t="s">
+        <v>977</v>
+      </c>
+      <c r="B711" s="13">
+        <v>45257</v>
+      </c>
+      <c r="C711" s="13">
+        <v>45289</v>
+      </c>
+      <c r="D711" s="13">
+        <v>45322</v>
+      </c>
+      <c r="E711" s="14" t="s">
+        <v>975</v>
+      </c>
+      <c r="F711" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G711" s="15">
+        <v>16</v>
+      </c>
+      <c r="H711" s="16" t="s">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="712" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A712" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="B712" s="18">
+        <v>45257</v>
+      </c>
+      <c r="C712" s="18">
+        <v>45289</v>
+      </c>
+      <c r="D712" s="18">
+        <v>45322</v>
+      </c>
+      <c r="E712" s="19" t="s">
+        <v>975</v>
+      </c>
+      <c r="F712" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G712" s="20">
+        <v>19</v>
+      </c>
+      <c r="H712" s="21" t="s">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="713" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A713" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B713" s="13">
+        <v>45257</v>
+      </c>
+      <c r="C713" s="13">
+        <v>45289</v>
+      </c>
+      <c r="D713" s="13">
+        <v>45322</v>
+      </c>
+      <c r="E713" s="14" t="s">
+        <v>975</v>
+      </c>
+      <c r="F713" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G713" s="15">
+        <v>13</v>
+      </c>
+      <c r="H713" s="16" t="s">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="714" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A714" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="B714" s="18">
+        <v>45257</v>
+      </c>
+      <c r="C714" s="18">
+        <v>45289</v>
+      </c>
+      <c r="D714" s="18">
+        <v>45322</v>
+      </c>
+      <c r="E714" s="19" t="s">
+        <v>975</v>
+      </c>
+      <c r="F714" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G714" s="20">
+        <v>16</v>
+      </c>
+      <c r="H714" s="21" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="715" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A715" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B715" s="13">
+        <v>45257</v>
+      </c>
+      <c r="C715" s="13">
+        <v>45289</v>
+      </c>
+      <c r="D715" s="13">
+        <v>45322</v>
+      </c>
+      <c r="E715" s="14" t="s">
+        <v>975</v>
+      </c>
+      <c r="F715" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G715" s="15">
+        <v>4</v>
+      </c>
+      <c r="H715" s="16" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="716" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A716" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B716" s="18">
+        <v>45257</v>
+      </c>
+      <c r="C716" s="18">
+        <v>45289</v>
+      </c>
+      <c r="D716" s="18">
+        <v>45322</v>
+      </c>
+      <c r="E716" s="19" t="s">
+        <v>975</v>
+      </c>
+      <c r="F716" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G716" s="20">
+        <v>3</v>
+      </c>
+      <c r="H716" s="21" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="717" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A717" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="B717" s="13">
+        <v>45257</v>
+      </c>
+      <c r="C717" s="13">
+        <v>45289</v>
+      </c>
+      <c r="D717" s="13">
+        <v>45322</v>
+      </c>
+      <c r="E717" s="14" t="s">
+        <v>975</v>
+      </c>
+      <c r="F717" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G717" s="15">
+        <v>13</v>
+      </c>
+      <c r="H717" s="16" t="s">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="718" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A718" s="17" t="s">
+        <v>233</v>
+      </c>
+      <c r="B718" s="18">
+        <v>45257</v>
+      </c>
+      <c r="C718" s="18">
+        <v>45289</v>
+      </c>
+      <c r="D718" s="18">
+        <v>45322</v>
+      </c>
+      <c r="E718" s="19" t="s">
+        <v>975</v>
+      </c>
+      <c r="F718" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G718" s="20">
+        <v>1</v>
+      </c>
+      <c r="H718" s="21" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="719" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A719" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B719" s="13">
+        <v>45245</v>
+      </c>
+      <c r="C719" s="13">
+        <v>45289</v>
+      </c>
+      <c r="D719" s="13">
+        <v>45307</v>
+      </c>
+      <c r="E719" s="14" t="s">
+        <v>972</v>
+      </c>
+      <c r="F719" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G719" s="15">
+        <v>51</v>
+      </c>
+      <c r="H719" s="16" t="s">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="720" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A720" s="17" t="s">
+        <v>282</v>
+      </c>
+      <c r="B720" s="18">
+        <v>45245</v>
+      </c>
+      <c r="C720" s="18">
+        <v>45289</v>
+      </c>
+      <c r="D720" s="18">
+        <v>45307</v>
+      </c>
+      <c r="E720" s="19" t="s">
+        <v>972</v>
+      </c>
+      <c r="F720" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G720" s="20">
+        <v>3</v>
+      </c>
+      <c r="H720" s="21" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="721" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A721" s="12" t="s">
+        <v>282</v>
+      </c>
+      <c r="B721" s="13">
+        <v>45245</v>
+      </c>
+      <c r="C721" s="13">
+        <v>45289</v>
+      </c>
+      <c r="D721" s="13">
+        <v>45262</v>
+      </c>
+      <c r="E721" s="14" t="s">
+        <v>972</v>
+      </c>
+      <c r="F721" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G721" s="15">
+        <v>10</v>
+      </c>
+      <c r="H721" s="16" t="s">
+        <v>989</v>
       </c>
     </row>
   </sheetData>
@@ -22776,13 +23220,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3D8398F3-4A10-4D19-A836-661787A73574}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3260B06F-6200-4EDF-8E00-C9F99A8C1C21}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0D695893-9FC7-4C26-8D9B-12853F5D8565}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9CA19DD6-7D65-4F58-80FA-781BC2B53BA2}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5CE692DD-D77A-4297-B7F9-433D9EF1A9F9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{95396435-26CE-409C-B176-81CB8B767237}"/>
 </file>
--- a/data/warn-scraper/cache/ca/warn_report1.xlsx
+++ b/data/warn-scraper/cache/ca/warn_report1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\WSB-CO\Communications Unit\Website Management\WARN (Worker Adjustment and Retraining Notification) Updates\2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B19C4A40-FD45-4BE7-84C2-DB789B34E002}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5E03E6E-9122-41C9-9376-108B06CDD612}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="624" yWindow="684" windowWidth="21600" windowHeight="11436" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2899" uniqueCount="991">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2947" uniqueCount="1010">
   <si>
     <t>County/Parish</t>
   </si>
@@ -3074,6 +3074,63 @@
     <t>6101 Condor Drive  Moorpark CA 93021</t>
   </si>
   <si>
+    <t>Bandier West Hollywood LLC</t>
+  </si>
+  <si>
+    <t>8101 Melrose Ave  Los Angeles CA 90046</t>
+  </si>
+  <si>
+    <t>Lance Camper Mfg. Corp</t>
+  </si>
+  <si>
+    <t>43120 Venture Street  Lancaster CA 93535</t>
+  </si>
+  <si>
+    <t>GE United Technologies LLC</t>
+  </si>
+  <si>
+    <t>3019 Vail Avenue  Los Angeles CA 90040</t>
+  </si>
+  <si>
+    <t>EchoPark Automotive Long Beach</t>
+  </si>
+  <si>
+    <t>2998 Cherry Ave  Signal Hill CA 90755</t>
+  </si>
+  <si>
+    <t>GE United Technologies II Inc.</t>
+  </si>
+  <si>
+    <t>170 West Hill Place  Brisbane CA 94005</t>
+  </si>
+  <si>
+    <t>Broadcom Inc.</t>
+  </si>
+  <si>
+    <t>3401 Hillview Ave  Palo Alto CA 94304</t>
+  </si>
+  <si>
+    <t>Lendlease Americas Inc.</t>
+  </si>
+  <si>
+    <t>1212 Bordeaux Drive  Sunnyvale CA 94089</t>
+  </si>
+  <si>
+    <t>1375 Geneva Dr  Sunnyvale CA 94089</t>
+  </si>
+  <si>
+    <t>215 Bordeaux Drive  Sunnyvale CA 94089</t>
+  </si>
+  <si>
+    <t>111 Sutter Street  San Francisco CA 94104</t>
+  </si>
+  <si>
+    <t>Kinecta Federal Credit Union</t>
+  </si>
+  <si>
+    <t>2100 Park Place  El Segundo CA 90245</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">WARN REPORT - </t>
     </r>
@@ -3085,7 +3142,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>07/01/23 to 01/01/24</t>
+      <t>07/01/23 to 01/03/24</t>
     </r>
     <r>
       <rPr>
@@ -3105,7 +3162,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>A detailed WARN summary by county and filtered according to received date. Table Spans cells A2 through H721.</t>
+      <t>A detailed WARN summary by county and filtered according to received date. Table Spans cells A2 through H733.</t>
     </r>
   </si>
 </sst>
@@ -3888,8 +3945,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:H721" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
-  <autoFilter ref="A2:H721" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:H733" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
+  <autoFilter ref="A2:H733" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -4273,7 +4330,7 @@
       </c>
       <c r="B3" s="5">
         <f>SUM('Detailed WARN Report '!G:G)</f>
-        <v>37159</v>
+        <v>39110</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -4282,7 +4339,7 @@
       </c>
       <c r="B4" s="5">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Permanent")</f>
-        <v>492</v>
+        <v>500</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -4308,7 +4365,7 @@
       </c>
       <c r="B7" s="5">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Permanent")</f>
-        <v>196</v>
+        <v>200</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -4340,7 +4397,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:H721"/>
+  <dimension ref="A1:H733"/>
   <sheetFormatPr defaultColWidth="26" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.88671875" bestFit="1" customWidth="1"/>
@@ -4353,7 +4410,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="99.6" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
-        <v>990</v>
+        <v>1009</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -23079,6 +23136,318 @@
       </c>
       <c r="H721" s="16" t="s">
         <v>989</v>
+      </c>
+    </row>
+    <row r="722" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A722" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="B722" s="18">
+        <v>45252</v>
+      </c>
+      <c r="C722" s="18">
+        <v>45294</v>
+      </c>
+      <c r="D722" s="18">
+        <v>45252</v>
+      </c>
+      <c r="E722" s="19" t="s">
+        <v>990</v>
+      </c>
+      <c r="F722" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G722" s="20">
+        <v>7</v>
+      </c>
+      <c r="H722" s="21" t="s">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="723" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A723" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B723" s="13">
+        <v>45250</v>
+      </c>
+      <c r="C723" s="13">
+        <v>45294</v>
+      </c>
+      <c r="D723" s="13">
+        <v>45313</v>
+      </c>
+      <c r="E723" s="14" t="s">
+        <v>992</v>
+      </c>
+      <c r="F723" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G723" s="15">
+        <v>123</v>
+      </c>
+      <c r="H723" s="16" t="s">
+        <v>993</v>
+      </c>
+    </row>
+    <row r="724" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A724" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="B724" s="18">
+        <v>45251</v>
+      </c>
+      <c r="C724" s="18">
+        <v>45294</v>
+      </c>
+      <c r="D724" s="18">
+        <v>45251</v>
+      </c>
+      <c r="E724" s="19" t="s">
+        <v>994</v>
+      </c>
+      <c r="F724" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G724" s="20">
+        <v>188</v>
+      </c>
+      <c r="H724" s="21" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="725" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A725" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B725" s="13">
+        <v>45294</v>
+      </c>
+      <c r="C725" s="13">
+        <v>45294</v>
+      </c>
+      <c r="D725" s="13">
+        <v>45159</v>
+      </c>
+      <c r="E725" s="14" t="s">
+        <v>996</v>
+      </c>
+      <c r="F725" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="G725" s="15">
+        <v>32</v>
+      </c>
+      <c r="H725" s="16" t="s">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="726" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A726" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="B726" s="18">
+        <v>45251</v>
+      </c>
+      <c r="C726" s="18">
+        <v>45294</v>
+      </c>
+      <c r="D726" s="18">
+        <v>45251</v>
+      </c>
+      <c r="E726" s="19" t="s">
+        <v>998</v>
+      </c>
+      <c r="F726" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G726" s="20">
+        <v>60</v>
+      </c>
+      <c r="H726" s="21" t="s">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="727" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A727" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B727" s="13">
+        <v>45257</v>
+      </c>
+      <c r="C727" s="13">
+        <v>45294</v>
+      </c>
+      <c r="D727" s="13">
+        <v>45317</v>
+      </c>
+      <c r="E727" s="14" t="s">
+        <v>1000</v>
+      </c>
+      <c r="F727" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G727" s="15">
+        <v>1267</v>
+      </c>
+      <c r="H727" s="16" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="728" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A728" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="B728" s="18">
+        <v>45238</v>
+      </c>
+      <c r="C728" s="18">
+        <v>45294</v>
+      </c>
+      <c r="D728" s="18">
+        <v>45299</v>
+      </c>
+      <c r="E728" s="19" t="s">
+        <v>1002</v>
+      </c>
+      <c r="F728" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G728" s="20">
+        <v>13</v>
+      </c>
+      <c r="H728" s="21" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="729" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A729" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B729" s="13">
+        <v>45238</v>
+      </c>
+      <c r="C729" s="13">
+        <v>45294</v>
+      </c>
+      <c r="D729" s="13">
+        <v>45299</v>
+      </c>
+      <c r="E729" s="14" t="s">
+        <v>1002</v>
+      </c>
+      <c r="F729" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G729" s="15">
+        <v>16</v>
+      </c>
+      <c r="H729" s="16" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="730" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A730" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="B730" s="18">
+        <v>45238</v>
+      </c>
+      <c r="C730" s="18">
+        <v>45294</v>
+      </c>
+      <c r="D730" s="18">
+        <v>45299</v>
+      </c>
+      <c r="E730" s="19" t="s">
+        <v>1002</v>
+      </c>
+      <c r="F730" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G730" s="20">
+        <v>27</v>
+      </c>
+      <c r="H730" s="21" t="s">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="731" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A731" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="B731" s="13">
+        <v>45250</v>
+      </c>
+      <c r="C731" s="13">
+        <v>45294</v>
+      </c>
+      <c r="D731" s="13">
+        <v>45282</v>
+      </c>
+      <c r="E731" s="14" t="s">
+        <v>473</v>
+      </c>
+      <c r="F731" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G731" s="15">
+        <v>2</v>
+      </c>
+      <c r="H731" s="16" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="732" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A732" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="B732" s="18">
+        <v>45238</v>
+      </c>
+      <c r="C732" s="18">
+        <v>45294</v>
+      </c>
+      <c r="D732" s="18">
+        <v>45299</v>
+      </c>
+      <c r="E732" s="19" t="s">
+        <v>1002</v>
+      </c>
+      <c r="F732" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G732" s="20">
+        <v>1</v>
+      </c>
+      <c r="H732" s="21" t="s">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="733" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A733" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B733" s="13">
+        <v>45236</v>
+      </c>
+      <c r="C733" s="13">
+        <v>45294</v>
+      </c>
+      <c r="D733" s="13">
+        <v>45236</v>
+      </c>
+      <c r="E733" s="14" t="s">
+        <v>1007</v>
+      </c>
+      <c r="F733" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G733" s="15">
+        <v>215</v>
+      </c>
+      <c r="H733" s="16" t="s">
+        <v>1008</v>
       </c>
     </row>
   </sheetData>
@@ -23220,13 +23589,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3260B06F-6200-4EDF-8E00-C9F99A8C1C21}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4E135FBB-2159-4D7B-A8AA-9F5074125779}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9CA19DD6-7D65-4F58-80FA-781BC2B53BA2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D51CEB9B-D7FE-44C7-98C0-B646A59C90F1}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{95396435-26CE-409C-B176-81CB8B767237}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DF1AB221-4C7A-4E1E-A33F-C19D8FF69A56}"/>
 </file>
--- a/data/warn-scraper/cache/ca/warn_report1.xlsx
+++ b/data/warn-scraper/cache/ca/warn_report1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\WSB-CO\Communications Unit\Website Management\WARN (Worker Adjustment and Retraining Notification) Updates\2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5E03E6E-9122-41C9-9376-108B06CDD612}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65C867DA-0EAD-41D4-B092-351E5CBE2C33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="624" yWindow="684" windowWidth="21600" windowHeight="11436" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2947" uniqueCount="1010">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2983" uniqueCount="1020">
   <si>
     <t>County/Parish</t>
   </si>
@@ -3131,6 +3131,36 @@
     <t>2100 Park Place  El Segundo CA 90245</t>
   </si>
   <si>
+    <t>HMI</t>
+  </si>
+  <si>
+    <t>6611-B Preston Avenue  Livermore CA 94551</t>
+  </si>
+  <si>
+    <t>Herbalife International of America, Inc</t>
+  </si>
+  <si>
+    <t>Quality Fabrication Inc.</t>
+  </si>
+  <si>
+    <t>9631 Irondale Avenue  Chatsworth CA 91311</t>
+  </si>
+  <si>
+    <t>1225 Park Center Drive  Vista CA 92081</t>
+  </si>
+  <si>
+    <t>1330 30th St, Suite G  San Diego CA 92154</t>
+  </si>
+  <si>
+    <t>8090 Arjons Dr  San Diego CA 92126</t>
+  </si>
+  <si>
+    <t>Dairy Farmers of America, Inc.</t>
+  </si>
+  <si>
+    <t>4375 N Ventura Ave.  Ventura CA 93001</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">WARN REPORT - </t>
     </r>
@@ -3142,7 +3172,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>07/01/23 to 01/03/24</t>
+      <t>07/01/23 to 01/08/24</t>
     </r>
     <r>
       <rPr>
@@ -3162,7 +3192,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>A detailed WARN summary by county and filtered according to received date. Table Spans cells A2 through H733.</t>
+      <t>A detailed WARN summary by county and filtered according to received date. Table Spans cells A2 through H742.</t>
     </r>
   </si>
 </sst>
@@ -3468,8 +3498,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF0F0F0"/>
-          <bgColor rgb="FFF0F0F0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -3509,8 +3539,8 @@
       <numFmt numFmtId="165" formatCode="[$-10436]#,##0;\(#,##0\)"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF0F0F0"/>
-          <bgColor rgb="FFF0F0F0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -3549,8 +3579,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF0F0F0"/>
-          <bgColor rgb="FFF0F0F0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -3589,8 +3619,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF0F0F0"/>
-          <bgColor rgb="FFF0F0F0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -3630,8 +3660,8 @@
       <numFmt numFmtId="164" formatCode="[$-10409]mm/dd/yyyy"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF0F0F0"/>
-          <bgColor rgb="FFF0F0F0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -3671,8 +3701,8 @@
       <numFmt numFmtId="164" formatCode="[$-10409]mm/dd/yyyy"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF0F0F0"/>
-          <bgColor rgb="FFF0F0F0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -3712,8 +3742,8 @@
       <numFmt numFmtId="164" formatCode="[$-10409]mm/dd/yyyy"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF0F0F0"/>
-          <bgColor rgb="FFF0F0F0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -3752,8 +3782,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF0F0F0"/>
-          <bgColor rgb="FFF0F0F0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -3945,8 +3975,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:H733" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
-  <autoFilter ref="A2:H733" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:H742" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
+  <autoFilter ref="A2:H742" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -4330,7 +4360,7 @@
       </c>
       <c r="B3" s="5">
         <f>SUM('Detailed WARN Report '!G:G)</f>
-        <v>39110</v>
+        <v>39420</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -4339,7 +4369,7 @@
       </c>
       <c r="B4" s="5">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Permanent")</f>
-        <v>500</v>
+        <v>506</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -4365,7 +4395,7 @@
       </c>
       <c r="B7" s="5">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Permanent")</f>
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -4397,7 +4427,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:H733"/>
+  <dimension ref="A1:H742"/>
   <sheetFormatPr defaultColWidth="26" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.88671875" bestFit="1" customWidth="1"/>
@@ -4410,7 +4440,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="99.6" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
-        <v>1009</v>
+        <v>1019</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -23448,6 +23478,240 @@
       </c>
       <c r="H733" s="16" t="s">
         <v>1008</v>
+      </c>
+    </row>
+    <row r="734" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A734" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="B734" s="18">
+        <v>45258</v>
+      </c>
+      <c r="C734" s="18">
+        <v>45299</v>
+      </c>
+      <c r="D734" s="18">
+        <v>45320</v>
+      </c>
+      <c r="E734" s="19" t="s">
+        <v>1009</v>
+      </c>
+      <c r="F734" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G734" s="20">
+        <v>16</v>
+      </c>
+      <c r="H734" s="21" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="735" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A735" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B735" s="13">
+        <v>45250</v>
+      </c>
+      <c r="C735" s="13">
+        <v>45299</v>
+      </c>
+      <c r="D735" s="13">
+        <v>45310</v>
+      </c>
+      <c r="E735" s="14" t="s">
+        <v>1011</v>
+      </c>
+      <c r="F735" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G735" s="15">
+        <v>12</v>
+      </c>
+      <c r="H735" s="16" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="736" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A736" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="B736" s="18">
+        <v>45246</v>
+      </c>
+      <c r="C736" s="18">
+        <v>45299</v>
+      </c>
+      <c r="D736" s="18">
+        <v>45307</v>
+      </c>
+      <c r="E736" s="19" t="s">
+        <v>1012</v>
+      </c>
+      <c r="F736" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G736" s="20">
+        <v>55</v>
+      </c>
+      <c r="H736" s="21" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="737" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A737" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B737" s="13">
+        <v>45244</v>
+      </c>
+      <c r="C737" s="13">
+        <v>45299</v>
+      </c>
+      <c r="D737" s="13">
+        <v>45304</v>
+      </c>
+      <c r="E737" s="14" t="s">
+        <v>362</v>
+      </c>
+      <c r="F737" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G737" s="15">
+        <v>15</v>
+      </c>
+      <c r="H737" s="16" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="738" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A738" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B738" s="18">
+        <v>45244</v>
+      </c>
+      <c r="C738" s="18">
+        <v>45299</v>
+      </c>
+      <c r="D738" s="18">
+        <v>45304</v>
+      </c>
+      <c r="E738" s="19" t="s">
+        <v>362</v>
+      </c>
+      <c r="F738" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G738" s="20">
+        <v>10</v>
+      </c>
+      <c r="H738" s="21" t="s">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="739" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A739" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B739" s="13">
+        <v>45244</v>
+      </c>
+      <c r="C739" s="13">
+        <v>45299</v>
+      </c>
+      <c r="D739" s="13">
+        <v>45304</v>
+      </c>
+      <c r="E739" s="14" t="s">
+        <v>362</v>
+      </c>
+      <c r="F739" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G739" s="15">
+        <v>37</v>
+      </c>
+      <c r="H739" s="16" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="740" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A740" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="B740" s="18">
+        <v>45250</v>
+      </c>
+      <c r="C740" s="18">
+        <v>45299</v>
+      </c>
+      <c r="D740" s="18">
+        <v>45310</v>
+      </c>
+      <c r="E740" s="19" t="s">
+        <v>1011</v>
+      </c>
+      <c r="F740" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G740" s="20">
+        <v>34</v>
+      </c>
+      <c r="H740" s="21" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="741" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A741" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B741" s="13">
+        <v>45250</v>
+      </c>
+      <c r="C741" s="13">
+        <v>45299</v>
+      </c>
+      <c r="D741" s="13">
+        <v>45310</v>
+      </c>
+      <c r="E741" s="14" t="s">
+        <v>1011</v>
+      </c>
+      <c r="F741" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G741" s="15">
+        <v>63</v>
+      </c>
+      <c r="H741" s="16" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="742" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A742" s="17" t="s">
+        <v>282</v>
+      </c>
+      <c r="B742" s="18">
+        <v>45257</v>
+      </c>
+      <c r="C742" s="18">
+        <v>45299</v>
+      </c>
+      <c r="D742" s="18">
+        <v>45317</v>
+      </c>
+      <c r="E742" s="19" t="s">
+        <v>1017</v>
+      </c>
+      <c r="F742" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G742" s="20">
+        <v>68</v>
+      </c>
+      <c r="H742" s="21" t="s">
+        <v>1018</v>
       </c>
     </row>
   </sheetData>
@@ -23589,13 +23853,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4E135FBB-2159-4D7B-A8AA-9F5074125779}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB5E6FAF-9212-47EB-AA96-8FAD3CEA4811}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D51CEB9B-D7FE-44C7-98C0-B646A59C90F1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{986EF954-FF59-4703-8D36-A3B07C745CB5}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DF1AB221-4C7A-4E1E-A33F-C19D8FF69A56}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{52C42FDA-BF24-451C-B714-3A4193EBD578}"/>
 </file>
--- a/data/warn-scraper/cache/ca/warn_report1.xlsx
+++ b/data/warn-scraper/cache/ca/warn_report1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\WSB-CO\Communications Unit\Website Management\WARN (Worker Adjustment and Retraining Notification) Updates\2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65C867DA-0EAD-41D4-B092-351E5CBE2C33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD344A71-BB25-41AE-B7BD-0189826D85F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="624" yWindow="684" windowWidth="21600" windowHeight="11436" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2983" uniqueCount="1020">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2991" uniqueCount="1024">
   <si>
     <t>County/Parish</t>
   </si>
@@ -3161,6 +3161,18 @@
     <t>4375 N Ventura Ave.  Ventura CA 93001</t>
   </si>
   <si>
+    <t>Vans HQ</t>
+  </si>
+  <si>
+    <t>1588 South Coast Dr.  Costa Mesa CA 92626</t>
+  </si>
+  <si>
+    <t>Block, Inc.</t>
+  </si>
+  <si>
+    <t>760 Market Street  San Francisco CA 94102</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">WARN REPORT - </t>
     </r>
@@ -3172,7 +3184,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>07/01/23 to 01/08/24</t>
+      <t>07/01/23 to 01/10/24</t>
     </r>
     <r>
       <rPr>
@@ -3192,7 +3204,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>A detailed WARN summary by county and filtered according to received date. Table Spans cells A2 through H742.</t>
+      <t>A detailed WARN summary by county and filtered according to received date. Table Spans cells A2 through H744.</t>
     </r>
   </si>
 </sst>
@@ -3498,8 +3510,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFF0F0F0"/>
+          <bgColor rgb="FFF0F0F0"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -3539,8 +3551,8 @@
       <numFmt numFmtId="165" formatCode="[$-10436]#,##0;\(#,##0\)"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFF0F0F0"/>
+          <bgColor rgb="FFF0F0F0"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -3579,8 +3591,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFF0F0F0"/>
+          <bgColor rgb="FFF0F0F0"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -3619,8 +3631,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFF0F0F0"/>
+          <bgColor rgb="FFF0F0F0"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -3660,8 +3672,8 @@
       <numFmt numFmtId="164" formatCode="[$-10409]mm/dd/yyyy"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFF0F0F0"/>
+          <bgColor rgb="FFF0F0F0"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -3701,8 +3713,8 @@
       <numFmt numFmtId="164" formatCode="[$-10409]mm/dd/yyyy"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFF0F0F0"/>
+          <bgColor rgb="FFF0F0F0"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -3742,8 +3754,8 @@
       <numFmt numFmtId="164" formatCode="[$-10409]mm/dd/yyyy"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFF0F0F0"/>
+          <bgColor rgb="FFF0F0F0"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -3782,8 +3794,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFF0F0F0"/>
+          <bgColor rgb="FFF0F0F0"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -3975,8 +3987,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:H742" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
-  <autoFilter ref="A2:H742" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:H744" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
+  <autoFilter ref="A2:H744" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -4360,7 +4372,7 @@
       </c>
       <c r="B3" s="5">
         <f>SUM('Detailed WARN Report '!G:G)</f>
-        <v>39420</v>
+        <v>39513</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -4369,7 +4381,7 @@
       </c>
       <c r="B4" s="5">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Permanent")</f>
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -4427,7 +4439,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:H742"/>
+  <dimension ref="A1:H744"/>
   <sheetFormatPr defaultColWidth="26" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.88671875" bestFit="1" customWidth="1"/>
@@ -4440,7 +4452,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="99.6" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
-        <v>1019</v>
+        <v>1023</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -23712,6 +23724,58 @@
       </c>
       <c r="H742" s="21" t="s">
         <v>1018</v>
+      </c>
+    </row>
+    <row r="743" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A743" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="B743" s="13">
+        <v>45259</v>
+      </c>
+      <c r="C743" s="13">
+        <v>45301</v>
+      </c>
+      <c r="D743" s="13">
+        <v>45321</v>
+      </c>
+      <c r="E743" s="14" t="s">
+        <v>1019</v>
+      </c>
+      <c r="F743" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G743" s="15">
+        <v>42</v>
+      </c>
+      <c r="H743" s="16" t="s">
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="744" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A744" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="B744" s="18">
+        <v>45257</v>
+      </c>
+      <c r="C744" s="18">
+        <v>45301</v>
+      </c>
+      <c r="D744" s="18">
+        <v>45320</v>
+      </c>
+      <c r="E744" s="19" t="s">
+        <v>1021</v>
+      </c>
+      <c r="F744" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G744" s="20">
+        <v>51</v>
+      </c>
+      <c r="H744" s="21" t="s">
+        <v>1022</v>
       </c>
     </row>
   </sheetData>
@@ -23853,13 +23917,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB5E6FAF-9212-47EB-AA96-8FAD3CEA4811}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B21B906-A2C0-480D-94FB-848A55BFE3B5}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{986EF954-FF59-4703-8D36-A3B07C745CB5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C10B65A7-2E20-4B2D-A9D0-4BAA98C41699}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{52C42FDA-BF24-451C-B714-3A4193EBD578}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3CF1BCCA-D56F-4E47-B870-F12FA7E4F26E}"/>
 </file>
--- a/data/warn-scraper/cache/ca/warn_report1.xlsx
+++ b/data/warn-scraper/cache/ca/warn_report1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\WSB-CO\Communications Unit\Website Management\WARN (Worker Adjustment and Retraining Notification) Updates\2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD344A71-BB25-41AE-B7BD-0189826D85F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9416FEB8-4B20-4E88-A05E-F337701C095B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="624" yWindow="684" windowWidth="21600" windowHeight="11436" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2991" uniqueCount="1024">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3039" uniqueCount="1043">
   <si>
     <t>County/Parish</t>
   </si>
@@ -3173,6 +3173,63 @@
     <t>760 Market Street  San Francisco CA 94102</t>
   </si>
   <si>
+    <t>Chart Inc.</t>
+  </si>
+  <si>
+    <t>46441 Landing Parkway  Fremont CA 94538</t>
+  </si>
+  <si>
+    <t>Personalis, Inc.</t>
+  </si>
+  <si>
+    <t>6660 Dumbarton Circle  Fremont CA 94555</t>
+  </si>
+  <si>
+    <t>Lonza Biologics, Inc.</t>
+  </si>
+  <si>
+    <t>1978 W. Winton Avenue  Hayward CA 94545</t>
+  </si>
+  <si>
+    <t>Knauf Insulation Inc.</t>
+  </si>
+  <si>
+    <t>3100 Ashby Road  Shasta Lake CA 96019</t>
+  </si>
+  <si>
+    <t>1310 Cantu-Galleano Ranch Rd  Mira Loma CA 91752</t>
+  </si>
+  <si>
+    <t>Crystal Geyser Water Company</t>
+  </si>
+  <si>
+    <t>501 Washington St  Calistoga CA 94515</t>
+  </si>
+  <si>
+    <t>Matheson Trucking, Inc.</t>
+  </si>
+  <si>
+    <t>9785 Goethe Road  Sacramento CA 95827</t>
+  </si>
+  <si>
+    <t>5853 Citation Way  Sacramento CA 95837</t>
+  </si>
+  <si>
+    <t>C&amp;E GP Specialists, Inc.</t>
+  </si>
+  <si>
+    <t>15970 Bernardo Center Drive  San Diego CA 92127</t>
+  </si>
+  <si>
+    <t>Ruan Transport Corporation</t>
+  </si>
+  <si>
+    <t>830 W. Glenwood St.  Turlock CA 95380</t>
+  </si>
+  <si>
+    <t>754 S Blackstone St.  Tulare CA 93274</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">WARN REPORT - </t>
     </r>
@@ -3184,7 +3241,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>07/01/23 to 01/10/24</t>
+      <t>07/01/23 to 01/15/24</t>
     </r>
     <r>
       <rPr>
@@ -3204,7 +3261,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>A detailed WARN summary by county and filtered according to received date. Table Spans cells A2 through H744.</t>
+      <t>A detailed WARN summary by county and filtered according to received date. Table Spans cells A2 through H756.</t>
     </r>
   </si>
 </sst>
@@ -3987,8 +4044,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:H744" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
-  <autoFilter ref="A2:H744" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:H756" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
+  <autoFilter ref="A2:H756" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -4372,7 +4429,7 @@
       </c>
       <c r="B3" s="5">
         <f>SUM('Detailed WARN Report '!G:G)</f>
-        <v>39513</v>
+        <v>40326</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -4381,7 +4438,7 @@
       </c>
       <c r="B4" s="5">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Permanent")</f>
-        <v>508</v>
+        <v>512</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -4390,7 +4447,7 @@
       </c>
       <c r="B5" s="5">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Temporary")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
@@ -4407,7 +4464,7 @@
       </c>
       <c r="B7" s="5">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Permanent")</f>
-        <v>203</v>
+        <v>210</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -4439,7 +4496,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:H744"/>
+  <dimension ref="A1:H756"/>
   <sheetFormatPr defaultColWidth="26" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.88671875" bestFit="1" customWidth="1"/>
@@ -4452,7 +4509,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="99.6" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
-        <v>1023</v>
+        <v>1042</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -23776,6 +23833,318 @@
       </c>
       <c r="H744" s="21" t="s">
         <v>1022</v>
+      </c>
+    </row>
+    <row r="745" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A745" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="B745" s="13">
+        <v>45258</v>
+      </c>
+      <c r="C745" s="13">
+        <v>45302</v>
+      </c>
+      <c r="D745" s="13">
+        <v>45350</v>
+      </c>
+      <c r="E745" s="14" t="s">
+        <v>1023</v>
+      </c>
+      <c r="F745" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="G745" s="15">
+        <v>8</v>
+      </c>
+      <c r="H745" s="16" t="s">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="746" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A746" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="B746" s="18">
+        <v>45261</v>
+      </c>
+      <c r="C746" s="18">
+        <v>45302</v>
+      </c>
+      <c r="D746" s="18">
+        <v>45321</v>
+      </c>
+      <c r="E746" s="19" t="s">
+        <v>1025</v>
+      </c>
+      <c r="F746" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G746" s="20">
+        <v>62</v>
+      </c>
+      <c r="H746" s="21" t="s">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="747" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A747" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="B747" s="13">
+        <v>45260</v>
+      </c>
+      <c r="C747" s="13">
+        <v>45302</v>
+      </c>
+      <c r="D747" s="13">
+        <v>45324</v>
+      </c>
+      <c r="E747" s="14" t="s">
+        <v>1027</v>
+      </c>
+      <c r="F747" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="G747" s="15">
+        <v>218</v>
+      </c>
+      <c r="H747" s="16" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="748" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A748" s="17" t="s">
+        <v>233</v>
+      </c>
+      <c r="B748" s="18">
+        <v>45252</v>
+      </c>
+      <c r="C748" s="18">
+        <v>45302</v>
+      </c>
+      <c r="D748" s="18">
+        <v>45320</v>
+      </c>
+      <c r="E748" s="19" t="s">
+        <v>1029</v>
+      </c>
+      <c r="F748" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="G748" s="20">
+        <v>97</v>
+      </c>
+      <c r="H748" s="21" t="s">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="749" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A749" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="B749" s="13">
+        <v>45266</v>
+      </c>
+      <c r="C749" s="13">
+        <v>45302</v>
+      </c>
+      <c r="D749" s="13">
+        <v>45265</v>
+      </c>
+      <c r="E749" s="14" t="s">
+        <v>473</v>
+      </c>
+      <c r="F749" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G749" s="15">
+        <v>9</v>
+      </c>
+      <c r="H749" s="16" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="750" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A750" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B750" s="18">
+        <v>45266</v>
+      </c>
+      <c r="C750" s="18">
+        <v>45302</v>
+      </c>
+      <c r="D750" s="18">
+        <v>45326</v>
+      </c>
+      <c r="E750" s="19" t="s">
+        <v>473</v>
+      </c>
+      <c r="F750" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G750" s="20">
+        <v>139</v>
+      </c>
+      <c r="H750" s="21" t="s">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="751" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A751" s="12" t="s">
+        <v>667</v>
+      </c>
+      <c r="B751" s="13">
+        <v>45260</v>
+      </c>
+      <c r="C751" s="13">
+        <v>45302</v>
+      </c>
+      <c r="D751" s="13">
+        <v>45322</v>
+      </c>
+      <c r="E751" s="14" t="s">
+        <v>1032</v>
+      </c>
+      <c r="F751" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G751" s="15">
+        <v>28</v>
+      </c>
+      <c r="H751" s="16" t="s">
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="752" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A752" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="B752" s="18">
+        <v>45261</v>
+      </c>
+      <c r="C752" s="18">
+        <v>45303</v>
+      </c>
+      <c r="D752" s="18">
+        <v>45322</v>
+      </c>
+      <c r="E752" s="19" t="s">
+        <v>1034</v>
+      </c>
+      <c r="F752" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G752" s="20">
+        <v>40</v>
+      </c>
+      <c r="H752" s="21" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="753" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A753" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B753" s="13">
+        <v>45261</v>
+      </c>
+      <c r="C753" s="13">
+        <v>45303</v>
+      </c>
+      <c r="D753" s="13">
+        <v>45322</v>
+      </c>
+      <c r="E753" s="14" t="s">
+        <v>574</v>
+      </c>
+      <c r="F753" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="G753" s="15">
+        <v>57</v>
+      </c>
+      <c r="H753" s="16" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="754" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A754" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B754" s="18">
+        <v>45271</v>
+      </c>
+      <c r="C754" s="18">
+        <v>45303</v>
+      </c>
+      <c r="D754" s="18">
+        <v>45296</v>
+      </c>
+      <c r="E754" s="19" t="s">
+        <v>1037</v>
+      </c>
+      <c r="F754" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G754" s="20">
+        <v>16</v>
+      </c>
+      <c r="H754" s="21" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="755" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A755" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B755" s="13">
+        <v>45233</v>
+      </c>
+      <c r="C755" s="13">
+        <v>45303</v>
+      </c>
+      <c r="D755" s="13">
+        <v>45299</v>
+      </c>
+      <c r="E755" s="14" t="s">
+        <v>1039</v>
+      </c>
+      <c r="F755" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="G755" s="15">
+        <v>47</v>
+      </c>
+      <c r="H755" s="16" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="756" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A756" s="17" t="s">
+        <v>175</v>
+      </c>
+      <c r="B756" s="18">
+        <v>45233</v>
+      </c>
+      <c r="C756" s="18">
+        <v>45303</v>
+      </c>
+      <c r="D756" s="18">
+        <v>45299</v>
+      </c>
+      <c r="E756" s="19" t="s">
+        <v>1039</v>
+      </c>
+      <c r="F756" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G756" s="20">
+        <v>92</v>
+      </c>
+      <c r="H756" s="21" t="s">
+        <v>1041</v>
       </c>
     </row>
   </sheetData>
@@ -23917,13 +24286,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B21B906-A2C0-480D-94FB-848A55BFE3B5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5E2F06E2-89BF-4E8C-9278-1C949154A879}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C10B65A7-2E20-4B2D-A9D0-4BAA98C41699}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AE30DBD-8245-4196-8007-9A826A18B4D5}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3CF1BCCA-D56F-4E47-B870-F12FA7E4F26E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{86874075-AEDE-4547-9E09-3FE8ADCD86BA}"/>
 </file>
--- a/data/warn-scraper/cache/ca/warn_report1.xlsx
+++ b/data/warn-scraper/cache/ca/warn_report1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\WSB-CO\Communications Unit\Website Management\WARN (Worker Adjustment and Retraining Notification) Updates\2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9416FEB8-4B20-4E88-A05E-F337701C095B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D26DDD5-E38D-4293-BEB7-141C71CE57B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="624" yWindow="684" windowWidth="21600" windowHeight="11436" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3039" uniqueCount="1043">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3155" uniqueCount="1081">
   <si>
     <t>County/Parish</t>
   </si>
@@ -3230,6 +3230,120 @@
     <t>754 S Blackstone St.  Tulare CA 93274</t>
   </si>
   <si>
+    <t>Dynaflex Prodcuts</t>
+  </si>
+  <si>
+    <t>2253 Saybrook  Los Angeles CA 90040</t>
+  </si>
+  <si>
+    <t>Eclipse Advantage, LLC at Rite Aid</t>
+  </si>
+  <si>
+    <t>2801 W. Avenue H  Lancaster CA 93536</t>
+  </si>
+  <si>
+    <t>Bristol Farms' Newfound Market Irvine Grocery Store</t>
+  </si>
+  <si>
+    <t>700 Spectrum Center Dr.  Irvine CA 92618</t>
+  </si>
+  <si>
+    <t>BILL Operations, LLC</t>
+  </si>
+  <si>
+    <t>6220 America Center Drive, Sute 100  San Jose CA 95002</t>
+  </si>
+  <si>
+    <t>1755 Beamer Street  Woodland CA 95776</t>
+  </si>
+  <si>
+    <t>Country Club Mortgage</t>
+  </si>
+  <si>
+    <t>9499 N. Ft. Washington Road Suite 103  Fresno CA 93730</t>
+  </si>
+  <si>
+    <t>2020 High Street Suite A  Selma CA 93662</t>
+  </si>
+  <si>
+    <t>216 West 7th Street  Hanford CA 93230</t>
+  </si>
+  <si>
+    <t>Spotify USA Inc</t>
+  </si>
+  <si>
+    <t>555 Mateo Street  Los Angeles CA 90013</t>
+  </si>
+  <si>
+    <t>Ace Hotel Group LLC at Ace Hotel Los Angeles</t>
+  </si>
+  <si>
+    <t>929 S. Broadway  Los Angeles CA 90015</t>
+  </si>
+  <si>
+    <t>Valley Processing, a HEXPOL Company</t>
+  </si>
+  <si>
+    <t>491 Wilson Way  City of Industry CA 91745</t>
+  </si>
+  <si>
+    <t>VF Santa Fe Springs Distribution Center</t>
+  </si>
+  <si>
+    <t>15700 Shoemake Avenue  Santa Fe Springs CA 90670</t>
+  </si>
+  <si>
+    <t>E. J. Lauren, LLC</t>
+  </si>
+  <si>
+    <t>2690 Pellissier Place  City of Industry CA 90601</t>
+  </si>
+  <si>
+    <t>SPS Ventures Inc.</t>
+  </si>
+  <si>
+    <t>21420 Needham Ranch Parkway, Building 6  Santa Clarita CA 91321</t>
+  </si>
+  <si>
+    <t>325 Gladys Avenue  Mountain View CA 94043</t>
+  </si>
+  <si>
+    <t>Alsco Inc.</t>
+  </si>
+  <si>
+    <t>705 West Grape Street  San Diego CA 92101</t>
+  </si>
+  <si>
+    <t>425 California Street  San Francisco CA 94104</t>
+  </si>
+  <si>
+    <t>Country Club Mortgage - Hall</t>
+  </si>
+  <si>
+    <t>525 N. Hall Street Suite A-C  Visalia CA 93291</t>
+  </si>
+  <si>
+    <t>Country Club Mortgage - Center</t>
+  </si>
+  <si>
+    <t>700 W. Center Street  Visalia CA 93291</t>
+  </si>
+  <si>
+    <t>217 E. Palm Avenue  Exeter CA 93221</t>
+  </si>
+  <si>
+    <t>Age of Learning, Inc.</t>
+  </si>
+  <si>
+    <t>101 N. Brand Blvd.  Glendale CA 91203</t>
+  </si>
+  <si>
+    <t>QG Printing II, LLC</t>
+  </si>
+  <si>
+    <t>1201 Shore Street  West Sacramento CA 95691</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">WARN REPORT - </t>
     </r>
@@ -3241,7 +3355,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>07/01/23 to 01/15/24</t>
+      <t>07/01/23 to 01/17/24</t>
     </r>
     <r>
       <rPr>
@@ -3261,7 +3375,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>A detailed WARN summary by county and filtered according to received date. Table Spans cells A2 through H756.</t>
+      <t>A detailed WARN summary by county and filtered according to received date. Table Spans cells A2 through H785.</t>
     </r>
   </si>
 </sst>
@@ -4044,8 +4158,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:H756" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
-  <autoFilter ref="A2:H756" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:H785" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
+  <autoFilter ref="A2:H785" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -4429,7 +4543,7 @@
       </c>
       <c r="B3" s="5">
         <f>SUM('Detailed WARN Report '!G:G)</f>
-        <v>40326</v>
+        <v>42423</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -4438,7 +4552,7 @@
       </c>
       <c r="B4" s="5">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Permanent")</f>
-        <v>512</v>
+        <v>523</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -4464,7 +4578,7 @@
       </c>
       <c r="B7" s="5">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Permanent")</f>
-        <v>210</v>
+        <v>228</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -4496,7 +4610,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:H756"/>
+  <dimension ref="A1:H785"/>
   <sheetFormatPr defaultColWidth="26" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.88671875" bestFit="1" customWidth="1"/>
@@ -4509,7 +4623,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="99.6" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
-        <v>1042</v>
+        <v>1080</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -24145,6 +24259,760 @@
       </c>
       <c r="H756" s="21" t="s">
         <v>1041</v>
+      </c>
+    </row>
+    <row r="757" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A757" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B757" s="13">
+        <v>45243</v>
+      </c>
+      <c r="C757" s="13">
+        <v>45307</v>
+      </c>
+      <c r="D757" s="13">
+        <v>45380</v>
+      </c>
+      <c r="E757" s="14" t="s">
+        <v>1042</v>
+      </c>
+      <c r="F757" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="G757" s="15">
+        <v>18</v>
+      </c>
+      <c r="H757" s="16" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="758" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A758" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="B758" s="18">
+        <v>45264</v>
+      </c>
+      <c r="C758" s="18">
+        <v>45307</v>
+      </c>
+      <c r="D758" s="18">
+        <v>45324</v>
+      </c>
+      <c r="E758" s="19" t="s">
+        <v>1044</v>
+      </c>
+      <c r="F758" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G758" s="20">
+        <v>27</v>
+      </c>
+      <c r="H758" s="21" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="759" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A759" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="B759" s="13">
+        <v>45262</v>
+      </c>
+      <c r="C759" s="13">
+        <v>45307</v>
+      </c>
+      <c r="D759" s="13">
+        <v>45322</v>
+      </c>
+      <c r="E759" s="14" t="s">
+        <v>1046</v>
+      </c>
+      <c r="F759" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="G759" s="15">
+        <v>138</v>
+      </c>
+      <c r="H759" s="16" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="760" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A760" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="B760" s="18">
+        <v>45246</v>
+      </c>
+      <c r="C760" s="18">
+        <v>45307</v>
+      </c>
+      <c r="D760" s="18">
+        <v>45306</v>
+      </c>
+      <c r="E760" s="19" t="s">
+        <v>654</v>
+      </c>
+      <c r="F760" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G760" s="20">
+        <v>1</v>
+      </c>
+      <c r="H760" s="21" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="761" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A761" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B761" s="13">
+        <v>45265</v>
+      </c>
+      <c r="C761" s="13">
+        <v>45307</v>
+      </c>
+      <c r="D761" s="13">
+        <v>45327</v>
+      </c>
+      <c r="E761" s="14" t="s">
+        <v>1048</v>
+      </c>
+      <c r="F761" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G761" s="15">
+        <v>156</v>
+      </c>
+      <c r="H761" s="16" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="762" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A762" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="B762" s="18">
+        <v>45265</v>
+      </c>
+      <c r="C762" s="18">
+        <v>45307</v>
+      </c>
+      <c r="D762" s="18">
+        <v>45327</v>
+      </c>
+      <c r="E762" s="19" t="s">
+        <v>1048</v>
+      </c>
+      <c r="F762" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G762" s="20">
+        <v>156</v>
+      </c>
+      <c r="H762" s="21" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="763" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A763" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B763" s="13">
+        <v>45265</v>
+      </c>
+      <c r="C763" s="13">
+        <v>45307</v>
+      </c>
+      <c r="D763" s="13">
+        <v>45327</v>
+      </c>
+      <c r="E763" s="14" t="s">
+        <v>1048</v>
+      </c>
+      <c r="F763" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G763" s="15">
+        <v>156</v>
+      </c>
+      <c r="H763" s="16" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="764" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A764" s="17" t="s">
+        <v>284</v>
+      </c>
+      <c r="B764" s="18">
+        <v>45264</v>
+      </c>
+      <c r="C764" s="18">
+        <v>45307</v>
+      </c>
+      <c r="D764" s="18">
+        <v>45324</v>
+      </c>
+      <c r="E764" s="19" t="s">
+        <v>1044</v>
+      </c>
+      <c r="F764" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G764" s="20">
+        <v>11</v>
+      </c>
+      <c r="H764" s="21" t="s">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="765" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A765" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="B765" s="13">
+        <v>45268</v>
+      </c>
+      <c r="C765" s="13">
+        <v>45308</v>
+      </c>
+      <c r="D765" s="13">
+        <v>45329</v>
+      </c>
+      <c r="E765" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="F765" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G765" s="15">
+        <v>89</v>
+      </c>
+      <c r="H765" s="16" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="766" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A766" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="B766" s="18">
+        <v>45268</v>
+      </c>
+      <c r="C766" s="18">
+        <v>45308</v>
+      </c>
+      <c r="D766" s="18">
+        <v>45328</v>
+      </c>
+      <c r="E766" s="19" t="s">
+        <v>1051</v>
+      </c>
+      <c r="F766" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G766" s="20">
+        <v>24</v>
+      </c>
+      <c r="H766" s="21" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="767" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A767" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B767" s="13">
+        <v>45268</v>
+      </c>
+      <c r="C767" s="13">
+        <v>45308</v>
+      </c>
+      <c r="D767" s="13">
+        <v>45328</v>
+      </c>
+      <c r="E767" s="14" t="s">
+        <v>1051</v>
+      </c>
+      <c r="F767" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="G767" s="15">
+        <v>6</v>
+      </c>
+      <c r="H767" s="16" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="768" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A768" s="17" t="s">
+        <v>135</v>
+      </c>
+      <c r="B768" s="18">
+        <v>45268</v>
+      </c>
+      <c r="C768" s="18">
+        <v>45308</v>
+      </c>
+      <c r="D768" s="18">
+        <v>45328</v>
+      </c>
+      <c r="E768" s="19" t="s">
+        <v>1051</v>
+      </c>
+      <c r="F768" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G768" s="20">
+        <v>3</v>
+      </c>
+      <c r="H768" s="21" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="769" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A769" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B769" s="13">
+        <v>45265</v>
+      </c>
+      <c r="C769" s="13">
+        <v>45308</v>
+      </c>
+      <c r="D769" s="13">
+        <v>45355</v>
+      </c>
+      <c r="E769" s="14" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F769" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G769" s="15">
+        <v>87</v>
+      </c>
+      <c r="H769" s="16" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="770" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A770" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="B770" s="18">
+        <v>45260</v>
+      </c>
+      <c r="C770" s="18">
+        <v>45308</v>
+      </c>
+      <c r="D770" s="18">
+        <v>45322</v>
+      </c>
+      <c r="E770" s="19" t="s">
+        <v>1057</v>
+      </c>
+      <c r="F770" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G770" s="20">
+        <v>169</v>
+      </c>
+      <c r="H770" s="21" t="s">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="771" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A771" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B771" s="13">
+        <v>45265</v>
+      </c>
+      <c r="C771" s="13">
+        <v>45308</v>
+      </c>
+      <c r="D771" s="13">
+        <v>45331</v>
+      </c>
+      <c r="E771" s="14" t="s">
+        <v>1059</v>
+      </c>
+      <c r="F771" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="G771" s="15">
+        <v>60</v>
+      </c>
+      <c r="H771" s="16" t="s">
+        <v>1060</v>
+      </c>
+    </row>
+    <row r="772" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A772" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="B772" s="18">
+        <v>45268</v>
+      </c>
+      <c r="C772" s="18">
+        <v>45308</v>
+      </c>
+      <c r="D772" s="18">
+        <v>45345</v>
+      </c>
+      <c r="E772" s="19" t="s">
+        <v>1061</v>
+      </c>
+      <c r="F772" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G772" s="20">
+        <v>207</v>
+      </c>
+      <c r="H772" s="21" t="s">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="773" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A773" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B773" s="13">
+        <v>45268</v>
+      </c>
+      <c r="C773" s="13">
+        <v>45308</v>
+      </c>
+      <c r="D773" s="13">
+        <v>45373</v>
+      </c>
+      <c r="E773" s="14" t="s">
+        <v>1061</v>
+      </c>
+      <c r="F773" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="G773" s="15">
+        <v>48</v>
+      </c>
+      <c r="H773" s="16" t="s">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="774" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A774" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="B774" s="18">
+        <v>45268</v>
+      </c>
+      <c r="C774" s="18">
+        <v>45308</v>
+      </c>
+      <c r="D774" s="18">
+        <v>45329</v>
+      </c>
+      <c r="E774" s="19" t="s">
+        <v>1063</v>
+      </c>
+      <c r="F774" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G774" s="20">
+        <v>69</v>
+      </c>
+      <c r="H774" s="21" t="s">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="775" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A775" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B775" s="13">
+        <v>45265</v>
+      </c>
+      <c r="C775" s="13">
+        <v>45308</v>
+      </c>
+      <c r="D775" s="13">
+        <v>45325</v>
+      </c>
+      <c r="E775" s="14" t="s">
+        <v>1065</v>
+      </c>
+      <c r="F775" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G775" s="15">
+        <v>162</v>
+      </c>
+      <c r="H775" s="16" t="s">
+        <v>1066</v>
+      </c>
+    </row>
+    <row r="776" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A776" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="B776" s="18">
+        <v>45266</v>
+      </c>
+      <c r="C776" s="18">
+        <v>45308</v>
+      </c>
+      <c r="D776" s="18">
+        <v>45327</v>
+      </c>
+      <c r="E776" s="19" t="s">
+        <v>688</v>
+      </c>
+      <c r="F776" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G776" s="20">
+        <v>51</v>
+      </c>
+      <c r="H776" s="21" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="777" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A777" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B777" s="13">
+        <v>45268</v>
+      </c>
+      <c r="C777" s="13">
+        <v>45308</v>
+      </c>
+      <c r="D777" s="13">
+        <v>45513</v>
+      </c>
+      <c r="E777" s="14" t="s">
+        <v>664</v>
+      </c>
+      <c r="F777" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="G777" s="15">
+        <v>73</v>
+      </c>
+      <c r="H777" s="16" t="s">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="778" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A778" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="B778" s="18">
+        <v>45267</v>
+      </c>
+      <c r="C778" s="18">
+        <v>45308</v>
+      </c>
+      <c r="D778" s="18">
+        <v>45327</v>
+      </c>
+      <c r="E778" s="19" t="s">
+        <v>613</v>
+      </c>
+      <c r="F778" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G778" s="20">
+        <v>13</v>
+      </c>
+      <c r="H778" s="21" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="779" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A779" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B779" s="13">
+        <v>45271</v>
+      </c>
+      <c r="C779" s="13">
+        <v>45308</v>
+      </c>
+      <c r="D779" s="13">
+        <v>45331</v>
+      </c>
+      <c r="E779" s="14" t="s">
+        <v>1068</v>
+      </c>
+      <c r="F779" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="G779" s="15">
+        <v>107</v>
+      </c>
+      <c r="H779" s="16" t="s">
+        <v>1069</v>
+      </c>
+    </row>
+    <row r="780" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A780" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="B780" s="18">
+        <v>45265</v>
+      </c>
+      <c r="C780" s="18">
+        <v>45308</v>
+      </c>
+      <c r="D780" s="18">
+        <v>45355</v>
+      </c>
+      <c r="E780" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="F780" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G780" s="20">
+        <v>44</v>
+      </c>
+      <c r="H780" s="21" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="781" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A781" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="B781" s="13">
+        <v>45268</v>
+      </c>
+      <c r="C781" s="13">
+        <v>45308</v>
+      </c>
+      <c r="D781" s="13">
+        <v>45328</v>
+      </c>
+      <c r="E781" s="14" t="s">
+        <v>1071</v>
+      </c>
+      <c r="F781" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="G781" s="15">
+        <v>28</v>
+      </c>
+      <c r="H781" s="16" t="s">
+        <v>1072</v>
+      </c>
+    </row>
+    <row r="782" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A782" s="17" t="s">
+        <v>175</v>
+      </c>
+      <c r="B782" s="18">
+        <v>45268</v>
+      </c>
+      <c r="C782" s="18">
+        <v>45308</v>
+      </c>
+      <c r="D782" s="18">
+        <v>45328</v>
+      </c>
+      <c r="E782" s="19" t="s">
+        <v>1073</v>
+      </c>
+      <c r="F782" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G782" s="20">
+        <v>41</v>
+      </c>
+      <c r="H782" s="21" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="783" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A783" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="B783" s="13">
+        <v>45268</v>
+      </c>
+      <c r="C783" s="13">
+        <v>45308</v>
+      </c>
+      <c r="D783" s="13">
+        <v>45328</v>
+      </c>
+      <c r="E783" s="14" t="s">
+        <v>1051</v>
+      </c>
+      <c r="F783" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="G783" s="15">
+        <v>3</v>
+      </c>
+      <c r="H783" s="16" t="s">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="784" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A784" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="B784" s="18">
+        <v>45265</v>
+      </c>
+      <c r="C784" s="18">
+        <v>45308</v>
+      </c>
+      <c r="D784" s="18">
+        <v>45327</v>
+      </c>
+      <c r="E784" s="19" t="s">
+        <v>1076</v>
+      </c>
+      <c r="F784" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G784" s="20">
+        <v>94</v>
+      </c>
+      <c r="H784" s="21" t="s">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="785" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A785" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="B785" s="13">
+        <v>45268</v>
+      </c>
+      <c r="C785" s="13">
+        <v>45308</v>
+      </c>
+      <c r="D785" s="13">
+        <v>45344</v>
+      </c>
+      <c r="E785" s="14" t="s">
+        <v>1078</v>
+      </c>
+      <c r="F785" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="G785" s="15">
+        <v>56</v>
+      </c>
+      <c r="H785" s="16" t="s">
+        <v>1079</v>
       </c>
     </row>
   </sheetData>
@@ -24286,13 +25154,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5E2F06E2-89BF-4E8C-9278-1C949154A879}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{423CA0FB-6767-4F4E-A7C3-5ED31844AF5B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AE30DBD-8245-4196-8007-9A826A18B4D5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E9CBA1D7-E3FA-4F4C-B92B-44B9FF68AEC7}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{86874075-AEDE-4547-9E09-3FE8ADCD86BA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57231535-B16D-4B94-8F5C-1DB9D84E3A89}"/>
 </file>
--- a/data/warn-scraper/cache/ca/warn_report1.xlsx
+++ b/data/warn-scraper/cache/ca/warn_report1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\WSB-CO\Communications Unit\Website Management\WARN (Worker Adjustment and Retraining Notification) Updates\2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D26DDD5-E38D-4293-BEB7-141C71CE57B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{720FFD63-5A59-4779-B3A8-A91D567F2586}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="624" yWindow="684" windowWidth="21600" windowHeight="11436" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3155" uniqueCount="1081">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3259" uniqueCount="1121">
   <si>
     <t>County/Parish</t>
   </si>
@@ -3233,9 +3233,6 @@
     <t>Dynaflex Prodcuts</t>
   </si>
   <si>
-    <t>2253 Saybrook  Los Angeles CA 90040</t>
-  </si>
-  <si>
     <t>Eclipse Advantage, LLC at Rite Aid</t>
   </si>
   <si>
@@ -3342,6 +3339,129 @@
   </si>
   <si>
     <t>1201 Shore Street  West Sacramento CA 95691</t>
+  </si>
+  <si>
+    <t>2253 Saybrook  Commerce CA 90040</t>
+  </si>
+  <si>
+    <t>Global Medical Response</t>
+  </si>
+  <si>
+    <t>13992 Catalina St.  San Leandro CA 94577</t>
+  </si>
+  <si>
+    <t>Lifelong Medical Care dba Lifelong Ashby Health Center</t>
+  </si>
+  <si>
+    <t>3075 Adeline Street Suite 280  Berkeley CA 94703</t>
+  </si>
+  <si>
+    <t>DePuy Synthes Products, Inc.</t>
+  </si>
+  <si>
+    <t>47709-47733 Fremont Blvd  Fremont CA 94538</t>
+  </si>
+  <si>
+    <t>Ridgecrest Regional Hospital</t>
+  </si>
+  <si>
+    <t>1081 N. China Lake Blvd.  Ridgecrest CA 93555</t>
+  </si>
+  <si>
+    <t>Wellness Innovation Group Inc. dba Lowell Farms</t>
+  </si>
+  <si>
+    <t>139 Zabala Road  Salinas CA 93908</t>
+  </si>
+  <si>
+    <t>Carbon, Inc.</t>
+  </si>
+  <si>
+    <t>1089 Mills Way  Redwood City CA 94063</t>
+  </si>
+  <si>
+    <t>Quanex Homeshield LLC</t>
+  </si>
+  <si>
+    <t>13611 Santa Ana Ave  Fontana CA 92337</t>
+  </si>
+  <si>
+    <t>AMQ Solutions, LLC</t>
+  </si>
+  <si>
+    <t>12400 Arrow Route  Rancho Cucamonga CA 91739</t>
+  </si>
+  <si>
+    <t>Steelcase Inc.</t>
+  </si>
+  <si>
+    <t>TuSimple, Inc.</t>
+  </si>
+  <si>
+    <t>9191 Towne Centre Drive  San Diego CA 92122</t>
+  </si>
+  <si>
+    <t>Invitae Corporation</t>
+  </si>
+  <si>
+    <t>1400 16th Street  San Francisco CA 94103</t>
+  </si>
+  <si>
+    <t>2350 Qume Drive  San Jose CA 95131</t>
+  </si>
+  <si>
+    <t>Z Global Logistics dba Kelly Toys Holding LLC</t>
+  </si>
+  <si>
+    <t>4811 S. Alameda St.  Los Angeles CA 90058</t>
+  </si>
+  <si>
+    <t>Cruise LLC - Headquarters</t>
+  </si>
+  <si>
+    <t>333 Brannan Street  San Francisco CA 94017</t>
+  </si>
+  <si>
+    <t>Cruise LLC</t>
+  </si>
+  <si>
+    <t>175 Sylvester Rd.  South San Francisco CA 94080</t>
+  </si>
+  <si>
+    <t>840 W California Ave.  Sunnyvale CA 94086</t>
+  </si>
+  <si>
+    <t>1201 Bryant  San Francisco CA 94103</t>
+  </si>
+  <si>
+    <t>Cruise LLC - CC</t>
+  </si>
+  <si>
+    <t>640 Cesar Chavez  San Francisco CA 94124</t>
+  </si>
+  <si>
+    <t>6410 Via Real  Carpinteria CA 93013</t>
+  </si>
+  <si>
+    <t>ACRT Pacific</t>
+  </si>
+  <si>
+    <t>9901 Geary Ave  Santa Fe Springs CA 90670</t>
+  </si>
+  <si>
+    <t>25625 Rye Canyon Rd  Valencia CA 91355</t>
+  </si>
+  <si>
+    <t>12353 Hesperia Rd  Victorville CA 92395</t>
+  </si>
+  <si>
+    <t>TIDAL, a subsidary of Block, Inc.</t>
+  </si>
+  <si>
+    <t>1455 Market Street, Unit 600  San Francisco CA 94103</t>
+  </si>
+  <si>
+    <t>2425 S Blackstone Street  Tulare CA 93274</t>
   </si>
   <si>
     <r>
@@ -3355,7 +3475,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>07/01/23 to 01/17/24</t>
+      <t>07/01/23 to 01/22/24</t>
     </r>
     <r>
       <rPr>
@@ -3375,7 +3495,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>A detailed WARN summary by county and filtered according to received date. Table Spans cells A2 through H785.</t>
+      <t>A detailed WARN summary by county and filtered according to received date. Table Spans cells A2 through H811.</t>
     </r>
   </si>
 </sst>
@@ -3681,8 +3801,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF0F0F0"/>
-          <bgColor rgb="FFF0F0F0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -3722,8 +3842,8 @@
       <numFmt numFmtId="165" formatCode="[$-10436]#,##0;\(#,##0\)"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF0F0F0"/>
-          <bgColor rgb="FFF0F0F0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -3762,8 +3882,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF0F0F0"/>
-          <bgColor rgb="FFF0F0F0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -3802,8 +3922,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF0F0F0"/>
-          <bgColor rgb="FFF0F0F0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -3843,8 +3963,8 @@
       <numFmt numFmtId="164" formatCode="[$-10409]mm/dd/yyyy"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF0F0F0"/>
-          <bgColor rgb="FFF0F0F0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -3884,8 +4004,8 @@
       <numFmt numFmtId="164" formatCode="[$-10409]mm/dd/yyyy"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF0F0F0"/>
-          <bgColor rgb="FFF0F0F0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -3925,8 +4045,8 @@
       <numFmt numFmtId="164" formatCode="[$-10409]mm/dd/yyyy"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF0F0F0"/>
-          <bgColor rgb="FFF0F0F0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -3965,8 +4085,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF0F0F0"/>
-          <bgColor rgb="FFF0F0F0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -4158,8 +4278,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:H785" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
-  <autoFilter ref="A2:H785" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:H811" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
+  <autoFilter ref="A2:H811" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -4543,7 +4663,7 @@
       </c>
       <c r="B3" s="5">
         <f>SUM('Detailed WARN Report '!G:G)</f>
-        <v>42423</v>
+        <v>43859</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -4552,7 +4672,7 @@
       </c>
       <c r="B4" s="5">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Permanent")</f>
-        <v>523</v>
+        <v>541</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -4578,7 +4698,7 @@
       </c>
       <c r="B7" s="5">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Permanent")</f>
-        <v>228</v>
+        <v>236</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -4610,7 +4730,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:H785"/>
+  <dimension ref="A1:H811"/>
   <sheetFormatPr defaultColWidth="26" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.88671875" bestFit="1" customWidth="1"/>
@@ -4623,7 +4743,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="99.6" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
-        <v>1080</v>
+        <v>1120</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -20320,7 +20440,7 @@
         <v>45267</v>
       </c>
       <c r="D605" s="13">
-        <v>45338</v>
+        <v>45369</v>
       </c>
       <c r="E605" s="14" t="s">
         <v>869</v>
@@ -23319,7 +23439,7 @@
         <v>16</v>
       </c>
       <c r="G720" s="20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H720" s="21" t="s">
         <v>988</v>
@@ -23657,7 +23777,7 @@
         <v>16</v>
       </c>
       <c r="G733" s="15">
-        <v>215</v>
+        <v>85</v>
       </c>
       <c r="H733" s="16" t="s">
         <v>1008</v>
@@ -24281,10 +24401,10 @@
         <v>15</v>
       </c>
       <c r="G757" s="15">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H757" s="16" t="s">
-        <v>1043</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="758" spans="1:8" x14ac:dyDescent="0.3">
@@ -24301,7 +24421,7 @@
         <v>45324</v>
       </c>
       <c r="E758" s="19" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="F758" s="19" t="s">
         <v>15</v>
@@ -24310,7 +24430,7 @@
         <v>27</v>
       </c>
       <c r="H758" s="21" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="759" spans="1:8" x14ac:dyDescent="0.3">
@@ -24327,7 +24447,7 @@
         <v>45322</v>
       </c>
       <c r="E759" s="14" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="F759" s="14" t="s">
         <v>15</v>
@@ -24336,7 +24456,7 @@
         <v>138</v>
       </c>
       <c r="H759" s="16" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="760" spans="1:8" x14ac:dyDescent="0.3">
@@ -24379,7 +24499,7 @@
         <v>45327</v>
       </c>
       <c r="E761" s="14" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="F761" s="14" t="s">
         <v>16</v>
@@ -24388,30 +24508,30 @@
         <v>156</v>
       </c>
       <c r="H761" s="16" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="762" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A762" s="17" t="s">
-        <v>7</v>
+        <v>284</v>
       </c>
       <c r="B762" s="18">
-        <v>45265</v>
+        <v>45264</v>
       </c>
       <c r="C762" s="18">
         <v>45307</v>
       </c>
       <c r="D762" s="18">
-        <v>45327</v>
+        <v>45324</v>
       </c>
       <c r="E762" s="19" t="s">
-        <v>1048</v>
+        <v>1043</v>
       </c>
       <c r="F762" s="19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G762" s="20">
-        <v>156</v>
+        <v>11</v>
       </c>
       <c r="H762" s="21" t="s">
         <v>1049</v>
@@ -24419,59 +24539,59 @@
     </row>
     <row r="763" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A763" s="12" t="s">
-        <v>7</v>
+        <v>86</v>
       </c>
       <c r="B763" s="13">
-        <v>45265</v>
+        <v>45268</v>
       </c>
       <c r="C763" s="13">
-        <v>45307</v>
+        <v>45308</v>
       </c>
       <c r="D763" s="13">
-        <v>45327</v>
+        <v>45329</v>
       </c>
       <c r="E763" s="14" t="s">
-        <v>1048</v>
+        <v>146</v>
       </c>
       <c r="F763" s="14" t="s">
         <v>16</v>
       </c>
       <c r="G763" s="15">
-        <v>156</v>
+        <v>89</v>
       </c>
       <c r="H763" s="16" t="s">
-        <v>1049</v>
+        <v>763</v>
       </c>
     </row>
     <row r="764" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A764" s="17" t="s">
-        <v>284</v>
+        <v>13</v>
       </c>
       <c r="B764" s="18">
-        <v>45264</v>
+        <v>45268</v>
       </c>
       <c r="C764" s="18">
-        <v>45307</v>
+        <v>45308</v>
       </c>
       <c r="D764" s="18">
-        <v>45324</v>
+        <v>45328</v>
       </c>
       <c r="E764" s="19" t="s">
-        <v>1044</v>
+        <v>1050</v>
       </c>
       <c r="F764" s="19" t="s">
         <v>15</v>
       </c>
       <c r="G764" s="20">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="H764" s="21" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="765" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A765" s="12" t="s">
-        <v>86</v>
+        <v>13</v>
       </c>
       <c r="B765" s="13">
         <v>45268</v>
@@ -24480,24 +24600,24 @@
         <v>45308</v>
       </c>
       <c r="D765" s="13">
-        <v>45329</v>
+        <v>45328</v>
       </c>
       <c r="E765" s="14" t="s">
-        <v>146</v>
+        <v>1050</v>
       </c>
       <c r="F765" s="14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G765" s="15">
-        <v>89</v>
+        <v>6</v>
       </c>
       <c r="H765" s="16" t="s">
-        <v>763</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="766" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A766" s="17" t="s">
-        <v>13</v>
+        <v>135</v>
       </c>
       <c r="B766" s="18">
         <v>45268</v>
@@ -24509,68 +24629,68 @@
         <v>45328</v>
       </c>
       <c r="E766" s="19" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="F766" s="19" t="s">
         <v>15</v>
       </c>
       <c r="G766" s="20">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="H766" s="21" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="767" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A767" s="12" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B767" s="13">
-        <v>45268</v>
+        <v>45265</v>
       </c>
       <c r="C767" s="13">
         <v>45308</v>
       </c>
       <c r="D767" s="13">
-        <v>45328</v>
+        <v>45355</v>
       </c>
       <c r="E767" s="14" t="s">
-        <v>1051</v>
+        <v>1054</v>
       </c>
       <c r="F767" s="14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G767" s="15">
-        <v>6</v>
+        <v>87</v>
       </c>
       <c r="H767" s="16" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="768" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A768" s="17" t="s">
-        <v>135</v>
+        <v>5</v>
       </c>
       <c r="B768" s="18">
-        <v>45268</v>
+        <v>45260</v>
       </c>
       <c r="C768" s="18">
         <v>45308</v>
       </c>
       <c r="D768" s="18">
-        <v>45328</v>
+        <v>45322</v>
       </c>
       <c r="E768" s="19" t="s">
-        <v>1051</v>
+        <v>1056</v>
       </c>
       <c r="F768" s="19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G768" s="20">
-        <v>3</v>
+        <v>169</v>
       </c>
       <c r="H768" s="21" t="s">
-        <v>1054</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="769" spans="1:8" x14ac:dyDescent="0.3">
@@ -24584,19 +24704,19 @@
         <v>45308</v>
       </c>
       <c r="D769" s="13">
-        <v>45355</v>
+        <v>45331</v>
       </c>
       <c r="E769" s="14" t="s">
-        <v>1055</v>
+        <v>1058</v>
       </c>
       <c r="F769" s="14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G769" s="15">
-        <v>87</v>
+        <v>60</v>
       </c>
       <c r="H769" s="16" t="s">
-        <v>1056</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="770" spans="1:8" x14ac:dyDescent="0.3">
@@ -24604,25 +24724,25 @@
         <v>5</v>
       </c>
       <c r="B770" s="18">
-        <v>45260</v>
+        <v>45268</v>
       </c>
       <c r="C770" s="18">
         <v>45308</v>
       </c>
       <c r="D770" s="18">
-        <v>45322</v>
+        <v>45345</v>
       </c>
       <c r="E770" s="19" t="s">
-        <v>1057</v>
+        <v>1060</v>
       </c>
       <c r="F770" s="19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G770" s="20">
-        <v>169</v>
+        <v>207</v>
       </c>
       <c r="H770" s="21" t="s">
-        <v>1058</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="771" spans="1:8" x14ac:dyDescent="0.3">
@@ -24630,25 +24750,25 @@
         <v>5</v>
       </c>
       <c r="B771" s="13">
-        <v>45265</v>
+        <v>45268</v>
       </c>
       <c r="C771" s="13">
         <v>45308</v>
       </c>
       <c r="D771" s="13">
-        <v>45331</v>
+        <v>45373</v>
       </c>
       <c r="E771" s="14" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="F771" s="14" t="s">
         <v>15</v>
       </c>
       <c r="G771" s="15">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="H771" s="16" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="772" spans="1:8" x14ac:dyDescent="0.3">
@@ -24662,19 +24782,19 @@
         <v>45308</v>
       </c>
       <c r="D772" s="18">
-        <v>45345</v>
+        <v>45329</v>
       </c>
       <c r="E772" s="19" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="F772" s="19" t="s">
         <v>15</v>
       </c>
       <c r="G772" s="20">
-        <v>207</v>
+        <v>69</v>
       </c>
       <c r="H772" s="21" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="773" spans="1:8" x14ac:dyDescent="0.3">
@@ -24682,74 +24802,74 @@
         <v>5</v>
       </c>
       <c r="B773" s="13">
-        <v>45268</v>
+        <v>45265</v>
       </c>
       <c r="C773" s="13">
         <v>45308</v>
       </c>
       <c r="D773" s="13">
-        <v>45373</v>
+        <v>45325</v>
       </c>
       <c r="E773" s="14" t="s">
-        <v>1061</v>
+        <v>1064</v>
       </c>
       <c r="F773" s="14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G773" s="15">
-        <v>48</v>
+        <v>162</v>
       </c>
       <c r="H773" s="16" t="s">
-        <v>1062</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="774" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A774" s="17" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B774" s="18">
-        <v>45268</v>
+        <v>45266</v>
       </c>
       <c r="C774" s="18">
         <v>45308</v>
       </c>
       <c r="D774" s="18">
-        <v>45329</v>
+        <v>45327</v>
       </c>
       <c r="E774" s="19" t="s">
-        <v>1063</v>
+        <v>688</v>
       </c>
       <c r="F774" s="19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G774" s="20">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="H774" s="21" t="s">
-        <v>1064</v>
+        <v>689</v>
       </c>
     </row>
     <row r="775" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A775" s="12" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B775" s="13">
-        <v>45265</v>
+        <v>45268</v>
       </c>
       <c r="C775" s="13">
         <v>45308</v>
       </c>
       <c r="D775" s="13">
-        <v>45325</v>
+        <v>45513</v>
       </c>
       <c r="E775" s="14" t="s">
-        <v>1065</v>
+        <v>664</v>
       </c>
       <c r="F775" s="14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G775" s="15">
-        <v>162</v>
+        <v>73</v>
       </c>
       <c r="H775" s="16" t="s">
         <v>1066</v>
@@ -24757,10 +24877,10 @@
     </row>
     <row r="776" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A776" s="17" t="s">
-        <v>7</v>
+        <v>66</v>
       </c>
       <c r="B776" s="18">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="C776" s="18">
         <v>45308</v>
@@ -24769,120 +24889,120 @@
         <v>45327</v>
       </c>
       <c r="E776" s="19" t="s">
-        <v>688</v>
+        <v>613</v>
       </c>
       <c r="F776" s="19" t="s">
         <v>16</v>
       </c>
       <c r="G776" s="20">
-        <v>51</v>
+        <v>13</v>
       </c>
       <c r="H776" s="21" t="s">
-        <v>689</v>
+        <v>614</v>
       </c>
     </row>
     <row r="777" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A777" s="12" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B777" s="13">
-        <v>45268</v>
+        <v>45271</v>
       </c>
       <c r="C777" s="13">
         <v>45308</v>
       </c>
       <c r="D777" s="13">
-        <v>45513</v>
+        <v>45331</v>
       </c>
       <c r="E777" s="14" t="s">
-        <v>664</v>
+        <v>1067</v>
       </c>
       <c r="F777" s="14" t="s">
         <v>15</v>
       </c>
       <c r="G777" s="15">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="H777" s="16" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="778" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A778" s="17" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="B778" s="18">
-        <v>45267</v>
+        <v>45265</v>
       </c>
       <c r="C778" s="18">
         <v>45308</v>
       </c>
       <c r="D778" s="18">
-        <v>45327</v>
+        <v>45355</v>
       </c>
       <c r="E778" s="19" t="s">
-        <v>613</v>
+        <v>105</v>
       </c>
       <c r="F778" s="19" t="s">
         <v>16</v>
       </c>
       <c r="G778" s="20">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="H778" s="21" t="s">
-        <v>614</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="779" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A779" s="12" t="s">
-        <v>6</v>
+        <v>175</v>
       </c>
       <c r="B779" s="13">
-        <v>45271</v>
+        <v>45268</v>
       </c>
       <c r="C779" s="13">
         <v>45308</v>
       </c>
       <c r="D779" s="13">
-        <v>45331</v>
+        <v>45328</v>
       </c>
       <c r="E779" s="14" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="F779" s="14" t="s">
         <v>15</v>
       </c>
       <c r="G779" s="15">
-        <v>107</v>
+        <v>28</v>
       </c>
       <c r="H779" s="16" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="780" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A780" s="17" t="s">
-        <v>52</v>
+        <v>175</v>
       </c>
       <c r="B780" s="18">
-        <v>45265</v>
+        <v>45268</v>
       </c>
       <c r="C780" s="18">
         <v>45308</v>
       </c>
       <c r="D780" s="18">
-        <v>45355</v>
+        <v>45328</v>
       </c>
       <c r="E780" s="19" t="s">
-        <v>105</v>
+        <v>1072</v>
       </c>
       <c r="F780" s="19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G780" s="20">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="H780" s="21" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="781" spans="1:8" x14ac:dyDescent="0.3">
@@ -24899,47 +25019,47 @@
         <v>45328</v>
       </c>
       <c r="E781" s="14" t="s">
-        <v>1071</v>
+        <v>1050</v>
       </c>
       <c r="F781" s="14" t="s">
         <v>15</v>
       </c>
       <c r="G781" s="15">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="H781" s="16" t="s">
-        <v>1072</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="782" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A782" s="17" t="s">
-        <v>175</v>
+        <v>5</v>
       </c>
       <c r="B782" s="18">
-        <v>45268</v>
+        <v>45265</v>
       </c>
       <c r="C782" s="18">
         <v>45308</v>
       </c>
       <c r="D782" s="18">
-        <v>45328</v>
+        <v>45327</v>
       </c>
       <c r="E782" s="19" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="F782" s="19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G782" s="20">
-        <v>41</v>
+        <v>94</v>
       </c>
       <c r="H782" s="21" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="783" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A783" s="12" t="s">
-        <v>175</v>
+        <v>284</v>
       </c>
       <c r="B783" s="13">
         <v>45268</v>
@@ -24948,71 +25068,747 @@
         <v>45308</v>
       </c>
       <c r="D783" s="13">
-        <v>45328</v>
+        <v>45344</v>
       </c>
       <c r="E783" s="14" t="s">
-        <v>1051</v>
+        <v>1077</v>
       </c>
       <c r="F783" s="14" t="s">
         <v>15</v>
       </c>
       <c r="G783" s="15">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="H783" s="16" t="s">
-        <v>1075</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="784" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A784" s="17" t="s">
-        <v>5</v>
+        <v>86</v>
       </c>
       <c r="B784" s="18">
-        <v>45265</v>
+        <v>45260</v>
       </c>
       <c r="C784" s="18">
-        <v>45308</v>
+        <v>45309</v>
       </c>
       <c r="D784" s="18">
-        <v>45327</v>
+        <v>45323</v>
       </c>
       <c r="E784" s="19" t="s">
-        <v>1076</v>
+        <v>1080</v>
       </c>
       <c r="F784" s="19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G784" s="20">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="H784" s="21" t="s">
-        <v>1077</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="785" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A785" s="12" t="s">
-        <v>284</v>
+        <v>86</v>
       </c>
       <c r="B785" s="13">
-        <v>45268</v>
+        <v>45273</v>
       </c>
       <c r="C785" s="13">
-        <v>45308</v>
+        <v>45309</v>
       </c>
       <c r="D785" s="13">
-        <v>45344</v>
+        <v>45338</v>
       </c>
       <c r="E785" s="14" t="s">
-        <v>1078</v>
+        <v>1082</v>
       </c>
       <c r="F785" s="14" t="s">
         <v>15</v>
       </c>
       <c r="G785" s="15">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H785" s="16" t="s">
-        <v>1079</v>
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="786" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A786" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="B786" s="18">
+        <v>45259</v>
+      </c>
+      <c r="C786" s="18">
+        <v>45309</v>
+      </c>
+      <c r="D786" s="18">
+        <v>45324</v>
+      </c>
+      <c r="E786" s="19" t="s">
+        <v>1084</v>
+      </c>
+      <c r="F786" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G786" s="20">
+        <v>25</v>
+      </c>
+      <c r="H786" s="21" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="787" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A787" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B787" s="13">
+        <v>45273</v>
+      </c>
+      <c r="C787" s="13">
+        <v>45309</v>
+      </c>
+      <c r="D787" s="13">
+        <v>45350</v>
+      </c>
+      <c r="E787" s="14" t="s">
+        <v>1086</v>
+      </c>
+      <c r="F787" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G787" s="15">
+        <v>30</v>
+      </c>
+      <c r="H787" s="16" t="s">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="788" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A788" s="17" t="s">
+        <v>278</v>
+      </c>
+      <c r="B788" s="18">
+        <v>45273</v>
+      </c>
+      <c r="C788" s="18">
+        <v>45309</v>
+      </c>
+      <c r="D788" s="18">
+        <v>45332</v>
+      </c>
+      <c r="E788" s="19" t="s">
+        <v>1088</v>
+      </c>
+      <c r="F788" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G788" s="20">
+        <v>11</v>
+      </c>
+      <c r="H788" s="21" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="789" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A789" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="B789" s="13">
+        <v>45272</v>
+      </c>
+      <c r="C789" s="13">
+        <v>45309</v>
+      </c>
+      <c r="D789" s="13">
+        <v>45337</v>
+      </c>
+      <c r="E789" s="14" t="s">
+        <v>1090</v>
+      </c>
+      <c r="F789" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G789" s="15">
+        <v>60</v>
+      </c>
+      <c r="H789" s="16" t="s">
+        <v>1091</v>
+      </c>
+    </row>
+    <row r="790" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A790" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="B790" s="18">
+        <v>45261</v>
+      </c>
+      <c r="C790" s="18">
+        <v>45309</v>
+      </c>
+      <c r="D790" s="18">
+        <v>45324</v>
+      </c>
+      <c r="E790" s="19" t="s">
+        <v>1092</v>
+      </c>
+      <c r="F790" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G790" s="20">
+        <v>58</v>
+      </c>
+      <c r="H790" s="21" t="s">
+        <v>1093</v>
+      </c>
+    </row>
+    <row r="791" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A791" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="B791" s="13">
+        <v>45271</v>
+      </c>
+      <c r="C791" s="13">
+        <v>45309</v>
+      </c>
+      <c r="D791" s="13">
+        <v>45373</v>
+      </c>
+      <c r="E791" s="14" t="s">
+        <v>1094</v>
+      </c>
+      <c r="F791" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="G791" s="15">
+        <v>37</v>
+      </c>
+      <c r="H791" s="16" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="792" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A792" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="B792" s="18">
+        <v>45271</v>
+      </c>
+      <c r="C792" s="18">
+        <v>45309</v>
+      </c>
+      <c r="D792" s="18">
+        <v>45373</v>
+      </c>
+      <c r="E792" s="19" t="s">
+        <v>1096</v>
+      </c>
+      <c r="F792" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G792" s="20">
+        <v>40</v>
+      </c>
+      <c r="H792" s="21" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="793" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A793" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B793" s="13">
+        <v>45264</v>
+      </c>
+      <c r="C793" s="13">
+        <v>45309</v>
+      </c>
+      <c r="D793" s="13">
+        <v>45323</v>
+      </c>
+      <c r="E793" s="14" t="s">
+        <v>1097</v>
+      </c>
+      <c r="F793" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G793" s="15">
+        <v>95</v>
+      </c>
+      <c r="H793" s="16" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="794" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A794" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="B794" s="18">
+        <v>45273</v>
+      </c>
+      <c r="C794" s="18">
+        <v>45309</v>
+      </c>
+      <c r="D794" s="18">
+        <v>45334</v>
+      </c>
+      <c r="E794" s="19" t="s">
+        <v>1099</v>
+      </c>
+      <c r="F794" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G794" s="20">
+        <v>238</v>
+      </c>
+      <c r="H794" s="21" t="s">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="795" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A795" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B795" s="13">
+        <v>45272</v>
+      </c>
+      <c r="C795" s="13">
+        <v>45309</v>
+      </c>
+      <c r="D795" s="13">
+        <v>45015</v>
+      </c>
+      <c r="E795" s="14" t="s">
+        <v>777</v>
+      </c>
+      <c r="F795" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G795" s="15">
+        <v>111</v>
+      </c>
+      <c r="H795" s="16" t="s">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="796" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A796" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B796" s="13">
+        <v>45275</v>
+      </c>
+      <c r="C796" s="13">
+        <v>45310</v>
+      </c>
+      <c r="D796" s="13">
+        <v>45275</v>
+      </c>
+      <c r="E796" s="14" t="s">
+        <v>1102</v>
+      </c>
+      <c r="F796" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="G796" s="15">
+        <v>8</v>
+      </c>
+      <c r="H796" s="16" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="797" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A797" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="B797" s="18">
+        <v>45274</v>
+      </c>
+      <c r="C797" s="18">
+        <v>45310</v>
+      </c>
+      <c r="D797" s="18">
+        <v>45274</v>
+      </c>
+      <c r="E797" s="19" t="s">
+        <v>1104</v>
+      </c>
+      <c r="F797" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G797" s="20">
+        <v>330</v>
+      </c>
+      <c r="H797" s="21" t="s">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="798" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A798" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="B798" s="13">
+        <v>45274</v>
+      </c>
+      <c r="C798" s="13">
+        <v>45310</v>
+      </c>
+      <c r="D798" s="13">
+        <v>45274</v>
+      </c>
+      <c r="E798" s="14" t="s">
+        <v>1106</v>
+      </c>
+      <c r="F798" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G798" s="15">
+        <v>18</v>
+      </c>
+      <c r="H798" s="16" t="s">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="799" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A799" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="B799" s="18">
+        <v>45274</v>
+      </c>
+      <c r="C799" s="18">
+        <v>45310</v>
+      </c>
+      <c r="D799" s="18">
+        <v>45274</v>
+      </c>
+      <c r="E799" s="19" t="s">
+        <v>1106</v>
+      </c>
+      <c r="F799" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G799" s="20">
+        <v>43</v>
+      </c>
+      <c r="H799" s="21" t="s">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="800" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A800" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B800" s="13">
+        <v>45275</v>
+      </c>
+      <c r="C800" s="13">
+        <v>45310</v>
+      </c>
+      <c r="D800" s="13">
+        <v>45275</v>
+      </c>
+      <c r="E800" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="F800" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G800" s="15">
+        <v>349</v>
+      </c>
+      <c r="H800" s="16" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="801" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A801" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="B801" s="18">
+        <v>45275</v>
+      </c>
+      <c r="C801" s="18">
+        <v>45310</v>
+      </c>
+      <c r="D801" s="18">
+        <v>45275</v>
+      </c>
+      <c r="E801" s="19" t="s">
+        <v>122</v>
+      </c>
+      <c r="F801" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G801" s="20">
+        <v>42</v>
+      </c>
+      <c r="H801" s="21" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="802" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A802" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="B802" s="13">
+        <v>45278</v>
+      </c>
+      <c r="C802" s="13">
+        <v>45310</v>
+      </c>
+      <c r="D802" s="13">
+        <v>45338</v>
+      </c>
+      <c r="E802" s="14" t="s">
+        <v>654</v>
+      </c>
+      <c r="F802" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="G802" s="15">
+        <v>1</v>
+      </c>
+      <c r="H802" s="16" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="803" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A803" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="B803" s="18">
+        <v>45274</v>
+      </c>
+      <c r="C803" s="18">
+        <v>45310</v>
+      </c>
+      <c r="D803" s="18">
+        <v>45274</v>
+      </c>
+      <c r="E803" s="19" t="s">
+        <v>1106</v>
+      </c>
+      <c r="F803" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G803" s="20">
+        <v>121</v>
+      </c>
+      <c r="H803" s="21" t="s">
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="804" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A804" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="B804" s="13">
+        <v>45274</v>
+      </c>
+      <c r="C804" s="13">
+        <v>45310</v>
+      </c>
+      <c r="D804" s="13">
+        <v>45274</v>
+      </c>
+      <c r="E804" s="14" t="s">
+        <v>1110</v>
+      </c>
+      <c r="F804" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G804" s="15">
+        <v>23</v>
+      </c>
+      <c r="H804" s="16" t="s">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="805" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A805" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="B805" s="18">
+        <v>45275</v>
+      </c>
+      <c r="C805" s="18">
+        <v>45310</v>
+      </c>
+      <c r="D805" s="18">
+        <v>45275</v>
+      </c>
+      <c r="E805" s="19" t="s">
+        <v>122</v>
+      </c>
+      <c r="F805" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G805" s="20">
+        <v>42</v>
+      </c>
+      <c r="H805" s="21" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="806" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A806" s="12" t="s">
+        <v>252</v>
+      </c>
+      <c r="B806" s="13">
+        <v>45275</v>
+      </c>
+      <c r="C806" s="13">
+        <v>45310</v>
+      </c>
+      <c r="D806" s="13">
+        <v>45275</v>
+      </c>
+      <c r="E806" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="F806" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G806" s="15">
+        <v>5</v>
+      </c>
+      <c r="H806" s="16" t="s">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="807" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A807" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="B807" s="18">
+        <v>45261</v>
+      </c>
+      <c r="C807" s="18">
+        <v>45313</v>
+      </c>
+      <c r="D807" s="18">
+        <v>45322</v>
+      </c>
+      <c r="E807" s="19" t="s">
+        <v>1113</v>
+      </c>
+      <c r="F807" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G807" s="20">
+        <v>3</v>
+      </c>
+      <c r="H807" s="21" t="s">
+        <v>1114</v>
+      </c>
+    </row>
+    <row r="808" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A808" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B808" s="13">
+        <v>45261</v>
+      </c>
+      <c r="C808" s="13">
+        <v>45313</v>
+      </c>
+      <c r="D808" s="13">
+        <v>45322</v>
+      </c>
+      <c r="E808" s="14" t="s">
+        <v>1113</v>
+      </c>
+      <c r="F808" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G808" s="15">
+        <v>7</v>
+      </c>
+      <c r="H808" s="16" t="s">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="809" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A809" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="B809" s="18">
+        <v>45261</v>
+      </c>
+      <c r="C809" s="18">
+        <v>45313</v>
+      </c>
+      <c r="D809" s="18">
+        <v>45322</v>
+      </c>
+      <c r="E809" s="19" t="s">
+        <v>1113</v>
+      </c>
+      <c r="F809" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G809" s="20">
+        <v>20</v>
+      </c>
+      <c r="H809" s="21" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="810" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A810" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="B810" s="13">
+        <v>45265</v>
+      </c>
+      <c r="C810" s="13">
+        <v>45313</v>
+      </c>
+      <c r="D810" s="13">
+        <v>45327</v>
+      </c>
+      <c r="E810" s="14" t="s">
+        <v>1117</v>
+      </c>
+      <c r="F810" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G810" s="15">
+        <v>1</v>
+      </c>
+      <c r="H810" s="16" t="s">
+        <v>1118</v>
+      </c>
+    </row>
+    <row r="811" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A811" s="17" t="s">
+        <v>175</v>
+      </c>
+      <c r="B811" s="18">
+        <v>45261</v>
+      </c>
+      <c r="C811" s="18">
+        <v>45313</v>
+      </c>
+      <c r="D811" s="18">
+        <v>45322</v>
+      </c>
+      <c r="E811" s="19" t="s">
+        <v>1113</v>
+      </c>
+      <c r="F811" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G811" s="20">
+        <v>24</v>
+      </c>
+      <c r="H811" s="21" t="s">
+        <v>1119</v>
       </c>
     </row>
   </sheetData>
@@ -25154,13 +25950,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{423CA0FB-6767-4F4E-A7C3-5ED31844AF5B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{20F87E56-696F-4646-A3CA-DCB6F81D56A6}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E9CBA1D7-E3FA-4F4C-B92B-44B9FF68AEC7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0521F685-FBB8-4577-A865-B84595628277}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57231535-B16D-4B94-8F5C-1DB9D84E3A89}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D9D3BDC4-C84D-480E-B209-7127014023B2}"/>
 </file>
--- a/data/warn-scraper/cache/ca/warn_report1.xlsx
+++ b/data/warn-scraper/cache/ca/warn_report1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\WSB-CO\Communications Unit\Website Management\WARN (Worker Adjustment and Retraining Notification) Updates\2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{720FFD63-5A59-4779-B3A8-A91D567F2586}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE8F40CE-71BF-4BE4-8262-2F0BDD3836BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="624" yWindow="684" windowWidth="21600" windowHeight="11436" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3259" uniqueCount="1121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3615" uniqueCount="1267">
   <si>
     <t>County/Parish</t>
   </si>
@@ -3464,6 +3464,444 @@
     <t>2425 S Blackstone Street  Tulare CA 93274</t>
   </si>
   <si>
+    <t>Il Fornaio (America) LLC dba Il Fornaio Pasadena Ristorante</t>
+  </si>
+  <si>
+    <t>24 W. Union St.  Pasadena CA 91103</t>
+  </si>
+  <si>
+    <t>DirectBuy Home Improvement, Inc. dba Z Gallerie</t>
+  </si>
+  <si>
+    <t>1182 Roseville Parkway, #130  Roseville CA 95678</t>
+  </si>
+  <si>
+    <t>DirectBuy Home Improvement, Inc. dba Z Gellerie</t>
+  </si>
+  <si>
+    <t>14006 Riverside Drive  Sherman Oaks CA 91423</t>
+  </si>
+  <si>
+    <t>HMSHost located at Admirals Clubs &amp; Lounges at Los Angeles International Airport (LAX)</t>
+  </si>
+  <si>
+    <t>1 World Way  Los Angeles CA 90045</t>
+  </si>
+  <si>
+    <t>Pfizer</t>
+  </si>
+  <si>
+    <t>181 Oyster Point Blvd. South San Francisco Research Facility South San Francisco CA 94080</t>
+  </si>
+  <si>
+    <t>3333 Bear Street, #141  Costa Mesa CA 92626</t>
+  </si>
+  <si>
+    <t>2785 Cabot Drive  Corona CA 92883</t>
+  </si>
+  <si>
+    <t>1006 N. Camino Real  Encinitas CA 92024</t>
+  </si>
+  <si>
+    <t>1325 S Grand Ave  Santa Ana CA 92705</t>
+  </si>
+  <si>
+    <t>1855 W. 139th Street  Gardena CA 90249</t>
+  </si>
+  <si>
+    <t>PacPartners dba Pizza Hut</t>
+  </si>
+  <si>
+    <t>15099 Hesperian Blvd Suite C  San Leandro CA 94578</t>
+  </si>
+  <si>
+    <t>CalPac Pizza II dba Pizza Hut</t>
+  </si>
+  <si>
+    <t>7716 N. 1st Street  Fresno CA 93720</t>
+  </si>
+  <si>
+    <t>4260 N. Blackstone Ave.  Fresno CA 93726</t>
+  </si>
+  <si>
+    <t>CalPac Pizza dba Pizza Hut - 027400</t>
+  </si>
+  <si>
+    <t>1227 Fresno St.  Fresno CA 93706</t>
+  </si>
+  <si>
+    <t>CalPac Pizza dba Pizza Hut - 027401</t>
+  </si>
+  <si>
+    <t>4188 E. Dakota Ave.  Fresno CA 93726</t>
+  </si>
+  <si>
+    <t>CalPac Pizza dba Pizza Hut - 027403</t>
+  </si>
+  <si>
+    <t>6015 N Figarden Dr.  Fresno CA 93722</t>
+  </si>
+  <si>
+    <t>CalPac Pizza dba Pizza Hut - 027406</t>
+  </si>
+  <si>
+    <t>624 South Clovis Ave.  Fresno CA 93727</t>
+  </si>
+  <si>
+    <t>PacPizza dba Pizza Hut</t>
+  </si>
+  <si>
+    <t>3599 Lake Tahoe Blvd  South Lake Tahoe CA 96150</t>
+  </si>
+  <si>
+    <t>CalPac Pizza dba Pizza Hut - 027383</t>
+  </si>
+  <si>
+    <t>4708 Planz Rd.  Bakersfield CA 93309</t>
+  </si>
+  <si>
+    <t>CalPac Pizza dba Pizza Hut - 027385</t>
+  </si>
+  <si>
+    <t>5221-B Stockdale Hwy  Bakersfield CA 93309</t>
+  </si>
+  <si>
+    <t>CalPac Pizza dba Pizza Hut - 027386</t>
+  </si>
+  <si>
+    <t>6300 White Ln Suite O  Bakersfield CA 93309</t>
+  </si>
+  <si>
+    <t>CalPac Pizza dba Pizza Hut - 027398</t>
+  </si>
+  <si>
+    <t>8110 Rosedale Hwy Suite E  Bakersfield CA 93312</t>
+  </si>
+  <si>
+    <t>CalPac Pizza dba Pizza Hut - 027408</t>
+  </si>
+  <si>
+    <t>3351 Panama Ln #300  Bakersfield CA 93313</t>
+  </si>
+  <si>
+    <t>CalPac Pizza dba Pizza Hut - 027384</t>
+  </si>
+  <si>
+    <t>3701 Auburn St.  Bakersfield CA 93306</t>
+  </si>
+  <si>
+    <t>CalPac Pizza dba Pizza Hut</t>
+  </si>
+  <si>
+    <t>633 Cecil Ave.  Delano CA 93215</t>
+  </si>
+  <si>
+    <t>2340 Highway 46  Wasco CA 93280</t>
+  </si>
+  <si>
+    <t>CalPac Pizza II LLC dba Pizza Hut</t>
+  </si>
+  <si>
+    <t>410 N 11th Ave. Suite 107  Hanford CA 93230</t>
+  </si>
+  <si>
+    <t>1029 N. Lemorre Ave.  Lemoore CA 93245</t>
+  </si>
+  <si>
+    <t>Madera County</t>
+  </si>
+  <si>
+    <t>1475 Country Club Drive  Madera CA 93638</t>
+  </si>
+  <si>
+    <t>419 Pacheco Hwy  Los Banos CA 93635</t>
+  </si>
+  <si>
+    <t>580 W. Olive  Merced CA 95348</t>
+  </si>
+  <si>
+    <t>855 Bellevue Rd S105  Atwater CA 95301</t>
+  </si>
+  <si>
+    <t>Pacpizza dba Pizza Hut</t>
+  </si>
+  <si>
+    <t>451 Oro Dam Blvd  Oroville CA 95965</t>
+  </si>
+  <si>
+    <t>875 Northcrest Dr.  Crescent City CA 95531</t>
+  </si>
+  <si>
+    <t>Yuba County</t>
+  </si>
+  <si>
+    <t>1130 North Beale Road  Marysville CA 95901</t>
+  </si>
+  <si>
+    <t>102 South Park Victoria Drive  Milpitas CA 95035</t>
+  </si>
+  <si>
+    <t>464 North Mathilda Avenue  Sunnyvale CA 94086</t>
+  </si>
+  <si>
+    <t>BrightDrop</t>
+  </si>
+  <si>
+    <t>220 Portage Avenue  Palo Alto CA 94306</t>
+  </si>
+  <si>
+    <t>26100 Newport Rd A-14  Menifee CA 92584</t>
+  </si>
+  <si>
+    <t>Southern PacPizza dba Pizza Hut - 029197</t>
+  </si>
+  <si>
+    <t>1860 W. Ramsey St.  Banning CA 92220</t>
+  </si>
+  <si>
+    <t>Southern PacPizza dba Pizza Hut - 029212</t>
+  </si>
+  <si>
+    <t>14577 Palm Drive  Desert Hot Springs CA 92240</t>
+  </si>
+  <si>
+    <t>Southern PacPizza dba Pizza Hut - 029198</t>
+  </si>
+  <si>
+    <t>25795 Stanford St.  Hemet CA 92544</t>
+  </si>
+  <si>
+    <t>Southern PacPizza dba Pizza Hut - 029220</t>
+  </si>
+  <si>
+    <t>81850 Avenue 46  Indio CA 92201</t>
+  </si>
+  <si>
+    <t>Southern PacPizza dba Pizza Hut - 029207</t>
+  </si>
+  <si>
+    <t>1180 S. Palm Canyon Dr.  Palm Springs CA 92264</t>
+  </si>
+  <si>
+    <t>Southern PacPizza dba Pizza Hut - 029208</t>
+  </si>
+  <si>
+    <t>490 N. State St.  San Jacinto CA 92583</t>
+  </si>
+  <si>
+    <t>Southern PacPizza dba Pizza Hut - 029205</t>
+  </si>
+  <si>
+    <t>34401 Date Palm Dr.  Cathedral City CA 92234</t>
+  </si>
+  <si>
+    <t>Southern PacPizza dba Pizza Hut - 029199</t>
+  </si>
+  <si>
+    <t>49954 Harrison St.  Coachella CA 92236</t>
+  </si>
+  <si>
+    <t>Southern PacPizza dba Pizza Hut - 029201</t>
+  </si>
+  <si>
+    <t>31736 Casino Dr.  Lake Elsinore CA 92530</t>
+  </si>
+  <si>
+    <t>Southern PacPizza dba Pizza Hut - 029222</t>
+  </si>
+  <si>
+    <t>30850 Riverside Dr. A3  Lake Elsinore CA 92530</t>
+  </si>
+  <si>
+    <t>Southern PacPizza dba Pizza Hut - 029224</t>
+  </si>
+  <si>
+    <t>25030 Hancock Ave. Suite 106  Murrieta CA 92562</t>
+  </si>
+  <si>
+    <t>Southern PacPizza dba Pizza Hut - 029203</t>
+  </si>
+  <si>
+    <t>1675 N. Perris Blvd Bldg E  Perris CA 92571</t>
+  </si>
+  <si>
+    <t>Southern PacPizza dba Pizza Hut - 029221</t>
+  </si>
+  <si>
+    <t>33195 Hwy 79 South Ste. D  Temecula CA 92592</t>
+  </si>
+  <si>
+    <t>Southern PacPizza dba Pizza Hut - 029232</t>
+  </si>
+  <si>
+    <t>27267 Nicolas Rd. Bldg E-104  Temecula CA 92591</t>
+  </si>
+  <si>
+    <t>9015 Bruceville Road Suite 180  Elk Grove CA 95758</t>
+  </si>
+  <si>
+    <t>PacPizza dba Pizza Hut - 011664</t>
+  </si>
+  <si>
+    <t>604 West El Camino AVe.  Sacramento CA 95833</t>
+  </si>
+  <si>
+    <t>PacPizza dba Pizza Hut - 011753</t>
+  </si>
+  <si>
+    <t>6619 Florin Road  Sacramento CA 95828</t>
+  </si>
+  <si>
+    <t>PacPizza dba Pizza Hut - 011755</t>
+  </si>
+  <si>
+    <t>1100 Fulton Ave.  Sacramento CA 95825</t>
+  </si>
+  <si>
+    <t>PacPizza dba Pizza Hut - 011761</t>
+  </si>
+  <si>
+    <t>5323-A Elkhorn Blvd.  Sacramento CA 95842</t>
+  </si>
+  <si>
+    <t>PacPizza dba Pizza Hut - 014697</t>
+  </si>
+  <si>
+    <t>6400-B Sunrise Blvd  Citrus Heights CA 95610</t>
+  </si>
+  <si>
+    <t>Southern PacPizza dba Pizza Hut - 029211</t>
+  </si>
+  <si>
+    <t>20811 Bear Valley Rd. Suite C  Apply Valley CA 93208</t>
+  </si>
+  <si>
+    <t>Southern PacPizza dba Pizza Hut - 029213</t>
+  </si>
+  <si>
+    <t>481 Armory Road  Barstow CA 92311</t>
+  </si>
+  <si>
+    <t>Southern PacPizza dba Pizza Hut - 029225</t>
+  </si>
+  <si>
+    <t>16455 Main Street  Hesperia CA 92345</t>
+  </si>
+  <si>
+    <t>Southern PacPizza dba Pizza Hut - 029215</t>
+  </si>
+  <si>
+    <t>14582 Palmdale Rd.  Victorville CA 92392</t>
+  </si>
+  <si>
+    <t>Southern PacPizza dba Pizza Hut - 029202</t>
+  </si>
+  <si>
+    <t>12183 Hesperia Rd.  Victorville CA 92392</t>
+  </si>
+  <si>
+    <t>Southern PacPizza dba Pizza Hut - 029210</t>
+  </si>
+  <si>
+    <t>58012 29 Palms Hwy  Yucca Valley CA 92284</t>
+  </si>
+  <si>
+    <t>Southern PacPizza dba Pizza Hut - 029200</t>
+  </si>
+  <si>
+    <t>72526 29 Palms Hwy  Twentynine Palms CA 92277</t>
+  </si>
+  <si>
+    <t>NuVasive, Inc.</t>
+  </si>
+  <si>
+    <t>7475 Lusk Boulevard  San Diego CA 92121</t>
+  </si>
+  <si>
+    <t>Adidas America, Inc.</t>
+  </si>
+  <si>
+    <t>865 Market Street  San Francisco CA 94103</t>
+  </si>
+  <si>
+    <t>4729 N. Pershing Ave. Suite A  Stockton CA 95207</t>
+  </si>
+  <si>
+    <t>920 N. Main  Manteca CA 95336</t>
+  </si>
+  <si>
+    <t>720 West 11st Street  Tracy CA 95376</t>
+  </si>
+  <si>
+    <t>1171 1st Street  Gilroy CA 95020</t>
+  </si>
+  <si>
+    <t>PacPizza dba Pizza Hut - 011728</t>
+  </si>
+  <si>
+    <t>3094 Story Road  San Jose CA 95127</t>
+  </si>
+  <si>
+    <t>PacPizza dba Pizza Hut - 011729</t>
+  </si>
+  <si>
+    <t>5689 Cottle Road  San Jose CA 95123</t>
+  </si>
+  <si>
+    <t>PacPizza dba Pizza Hut - 032516</t>
+  </si>
+  <si>
+    <t>226 W. Alma Ave. Suite 40  San Jose CA 95110</t>
+  </si>
+  <si>
+    <t>PacPizza dba Pizza Hut - 011730</t>
+  </si>
+  <si>
+    <t>3161 Senter Road  San Jose CA 95111</t>
+  </si>
+  <si>
+    <t>1047 W. Orangeburg Ave.  Modesto CA 95350</t>
+  </si>
+  <si>
+    <t>2600 Mitchell Road Suite P  Ceres CA 95307</t>
+  </si>
+  <si>
+    <t>2401 E. Orangeburg Avenue Unit 200  Modesto CA 95355</t>
+  </si>
+  <si>
+    <t>920 Lander Ave.  Turlock CA 95380</t>
+  </si>
+  <si>
+    <t>Southern PacPizza dba Pizza Hut - 029229</t>
+  </si>
+  <si>
+    <t>393 W. Olive Ave.  Porterville CA 93257</t>
+  </si>
+  <si>
+    <t>Southern PacPizza dba Pizza Hut - 029230</t>
+  </si>
+  <si>
+    <t>276 W. Henderson AVe.  Porterville CA 93257</t>
+  </si>
+  <si>
+    <t>Southern PacPizza dba Pizza Hut - 029226</t>
+  </si>
+  <si>
+    <t>416 E. Tulare AVe.  Visalia CA 93277</t>
+  </si>
+  <si>
+    <t>Southern PacPizza dba Pizza Hut - 029228</t>
+  </si>
+  <si>
+    <t>250 S. Akers St.  Visalia CA 93291</t>
+  </si>
+  <si>
+    <t>1304 E. Prosperity AVe.  Tulare CA 93274</t>
+  </si>
+  <si>
+    <t>2175 E. Francisco Blvd, E, Suite B  San Rafael CA 94901</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">WARN REPORT - </t>
     </r>
@@ -3475,7 +3913,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>07/01/23 to 01/22/24</t>
+      <t>07/01/23 to 01/24/24</t>
     </r>
     <r>
       <rPr>
@@ -3495,7 +3933,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>A detailed WARN summary by county and filtered according to received date. Table Spans cells A2 through H811.</t>
+      <t>A detailed WARN summary by county and filtered according to received date. Table Spans cells A2 through H900.</t>
     </r>
   </si>
 </sst>
@@ -4278,8 +4716,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:H811" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
-  <autoFilter ref="A2:H811" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:H900" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
+  <autoFilter ref="A2:H900" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -4663,7 +5101,7 @@
       </c>
       <c r="B3" s="5">
         <f>SUM('Detailed WARN Report '!G:G)</f>
-        <v>43859</v>
+        <v>45200</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -4672,7 +5110,7 @@
       </c>
       <c r="B4" s="5">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Permanent")</f>
-        <v>541</v>
+        <v>627</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -4698,7 +5136,7 @@
       </c>
       <c r="B7" s="5">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Permanent")</f>
-        <v>236</v>
+        <v>239</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -4730,7 +5168,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:H811"/>
+  <dimension ref="A1:H900"/>
   <sheetFormatPr defaultColWidth="26" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.88671875" bestFit="1" customWidth="1"/>
@@ -4743,7 +5181,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="99.6" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
-        <v>1120</v>
+        <v>1266</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -18568,7 +19006,7 @@
         <v>45250</v>
       </c>
       <c r="D533" s="13">
-        <v>45278</v>
+        <v>45306</v>
       </c>
       <c r="E533" s="14" t="s">
         <v>781</v>
@@ -24513,85 +24951,85 @@
     </row>
     <row r="762" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A762" s="17" t="s">
-        <v>284</v>
+        <v>7</v>
       </c>
       <c r="B762" s="18">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="C762" s="18">
         <v>45307</v>
       </c>
       <c r="D762" s="18">
-        <v>45324</v>
+        <v>45327</v>
       </c>
       <c r="E762" s="19" t="s">
-        <v>1043</v>
+        <v>1047</v>
       </c>
       <c r="F762" s="19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G762" s="20">
-        <v>11</v>
+        <v>156</v>
       </c>
       <c r="H762" s="21" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="763" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A763" s="12" t="s">
-        <v>86</v>
+        <v>7</v>
       </c>
       <c r="B763" s="13">
-        <v>45268</v>
+        <v>45265</v>
       </c>
       <c r="C763" s="13">
-        <v>45308</v>
+        <v>45307</v>
       </c>
       <c r="D763" s="13">
-        <v>45329</v>
+        <v>45327</v>
       </c>
       <c r="E763" s="14" t="s">
-        <v>146</v>
+        <v>1047</v>
       </c>
       <c r="F763" s="14" t="s">
         <v>16</v>
       </c>
       <c r="G763" s="15">
-        <v>89</v>
+        <v>156</v>
       </c>
       <c r="H763" s="16" t="s">
-        <v>763</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="764" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A764" s="17" t="s">
-        <v>13</v>
+        <v>284</v>
       </c>
       <c r="B764" s="18">
-        <v>45268</v>
+        <v>45264</v>
       </c>
       <c r="C764" s="18">
-        <v>45308</v>
+        <v>45307</v>
       </c>
       <c r="D764" s="18">
-        <v>45328</v>
+        <v>45324</v>
       </c>
       <c r="E764" s="19" t="s">
-        <v>1050</v>
+        <v>1043</v>
       </c>
       <c r="F764" s="19" t="s">
         <v>15</v>
       </c>
       <c r="G764" s="20">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="H764" s="21" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="765" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A765" s="12" t="s">
-        <v>13</v>
+        <v>86</v>
       </c>
       <c r="B765" s="13">
         <v>45268</v>
@@ -24600,24 +25038,24 @@
         <v>45308</v>
       </c>
       <c r="D765" s="13">
-        <v>45328</v>
+        <v>45329</v>
       </c>
       <c r="E765" s="14" t="s">
-        <v>1050</v>
+        <v>146</v>
       </c>
       <c r="F765" s="14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G765" s="15">
-        <v>6</v>
+        <v>89</v>
       </c>
       <c r="H765" s="16" t="s">
-        <v>1052</v>
+        <v>763</v>
       </c>
     </row>
     <row r="766" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A766" s="17" t="s">
-        <v>135</v>
+        <v>13</v>
       </c>
       <c r="B766" s="18">
         <v>45268</v>
@@ -24635,62 +25073,62 @@
         <v>15</v>
       </c>
       <c r="G766" s="20">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="H766" s="21" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="767" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A767" s="12" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="B767" s="13">
-        <v>45265</v>
+        <v>45268</v>
       </c>
       <c r="C767" s="13">
         <v>45308</v>
       </c>
       <c r="D767" s="13">
-        <v>45355</v>
+        <v>45328</v>
       </c>
       <c r="E767" s="14" t="s">
-        <v>1054</v>
+        <v>1050</v>
       </c>
       <c r="F767" s="14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G767" s="15">
-        <v>87</v>
+        <v>6</v>
       </c>
       <c r="H767" s="16" t="s">
-        <v>1055</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="768" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A768" s="17" t="s">
-        <v>5</v>
+        <v>135</v>
       </c>
       <c r="B768" s="18">
-        <v>45260</v>
+        <v>45268</v>
       </c>
       <c r="C768" s="18">
         <v>45308</v>
       </c>
       <c r="D768" s="18">
-        <v>45322</v>
+        <v>45328</v>
       </c>
       <c r="E768" s="19" t="s">
-        <v>1056</v>
+        <v>1050</v>
       </c>
       <c r="F768" s="19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G768" s="20">
-        <v>169</v>
+        <v>3</v>
       </c>
       <c r="H768" s="21" t="s">
-        <v>1057</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="769" spans="1:8" x14ac:dyDescent="0.3">
@@ -24704,19 +25142,19 @@
         <v>45308</v>
       </c>
       <c r="D769" s="13">
-        <v>45331</v>
+        <v>45355</v>
       </c>
       <c r="E769" s="14" t="s">
-        <v>1058</v>
+        <v>1054</v>
       </c>
       <c r="F769" s="14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G769" s="15">
-        <v>60</v>
+        <v>87</v>
       </c>
       <c r="H769" s="16" t="s">
-        <v>1059</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="770" spans="1:8" x14ac:dyDescent="0.3">
@@ -24724,25 +25162,25 @@
         <v>5</v>
       </c>
       <c r="B770" s="18">
-        <v>45268</v>
+        <v>45260</v>
       </c>
       <c r="C770" s="18">
         <v>45308</v>
       </c>
       <c r="D770" s="18">
-        <v>45345</v>
+        <v>45322</v>
       </c>
       <c r="E770" s="19" t="s">
-        <v>1060</v>
+        <v>1056</v>
       </c>
       <c r="F770" s="19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G770" s="20">
-        <v>207</v>
+        <v>169</v>
       </c>
       <c r="H770" s="21" t="s">
-        <v>1061</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="771" spans="1:8" x14ac:dyDescent="0.3">
@@ -24750,25 +25188,25 @@
         <v>5</v>
       </c>
       <c r="B771" s="13">
-        <v>45268</v>
+        <v>45265</v>
       </c>
       <c r="C771" s="13">
         <v>45308</v>
       </c>
       <c r="D771" s="13">
-        <v>45373</v>
+        <v>45331</v>
       </c>
       <c r="E771" s="14" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="F771" s="14" t="s">
         <v>15</v>
       </c>
       <c r="G771" s="15">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="H771" s="16" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="772" spans="1:8" x14ac:dyDescent="0.3">
@@ -24782,19 +25220,19 @@
         <v>45308</v>
       </c>
       <c r="D772" s="18">
-        <v>45329</v>
+        <v>45345</v>
       </c>
       <c r="E772" s="19" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="F772" s="19" t="s">
         <v>15</v>
       </c>
       <c r="G772" s="20">
-        <v>69</v>
+        <v>207</v>
       </c>
       <c r="H772" s="21" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="773" spans="1:8" x14ac:dyDescent="0.3">
@@ -24802,85 +25240,85 @@
         <v>5</v>
       </c>
       <c r="B773" s="13">
-        <v>45265</v>
+        <v>45268</v>
       </c>
       <c r="C773" s="13">
         <v>45308</v>
       </c>
       <c r="D773" s="13">
-        <v>45325</v>
+        <v>45373</v>
       </c>
       <c r="E773" s="14" t="s">
-        <v>1064</v>
+        <v>1060</v>
       </c>
       <c r="F773" s="14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G773" s="15">
-        <v>162</v>
+        <v>48</v>
       </c>
       <c r="H773" s="16" t="s">
-        <v>1065</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="774" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A774" s="17" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B774" s="18">
-        <v>45266</v>
+        <v>45268</v>
       </c>
       <c r="C774" s="18">
         <v>45308</v>
       </c>
       <c r="D774" s="18">
-        <v>45327</v>
+        <v>45329</v>
       </c>
       <c r="E774" s="19" t="s">
-        <v>688</v>
+        <v>1062</v>
       </c>
       <c r="F774" s="19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G774" s="20">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="H774" s="21" t="s">
-        <v>689</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="775" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A775" s="12" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B775" s="13">
-        <v>45268</v>
+        <v>45265</v>
       </c>
       <c r="C775" s="13">
         <v>45308</v>
       </c>
       <c r="D775" s="13">
-        <v>45513</v>
+        <v>45325</v>
       </c>
       <c r="E775" s="14" t="s">
-        <v>664</v>
+        <v>1064</v>
       </c>
       <c r="F775" s="14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G775" s="15">
-        <v>73</v>
+        <v>162</v>
       </c>
       <c r="H775" s="16" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="776" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A776" s="17" t="s">
-        <v>66</v>
+        <v>7</v>
       </c>
       <c r="B776" s="18">
-        <v>45267</v>
+        <v>45266</v>
       </c>
       <c r="C776" s="18">
         <v>45308</v>
@@ -24889,120 +25327,120 @@
         <v>45327</v>
       </c>
       <c r="E776" s="19" t="s">
-        <v>613</v>
+        <v>688</v>
       </c>
       <c r="F776" s="19" t="s">
         <v>16</v>
       </c>
       <c r="G776" s="20">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="H776" s="21" t="s">
-        <v>614</v>
+        <v>689</v>
       </c>
     </row>
     <row r="777" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A777" s="12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B777" s="13">
-        <v>45271</v>
+        <v>45268</v>
       </c>
       <c r="C777" s="13">
         <v>45308</v>
       </c>
       <c r="D777" s="13">
-        <v>45331</v>
+        <v>45513</v>
       </c>
       <c r="E777" s="14" t="s">
-        <v>1067</v>
+        <v>664</v>
       </c>
       <c r="F777" s="14" t="s">
         <v>15</v>
       </c>
       <c r="G777" s="15">
-        <v>107</v>
+        <v>73</v>
       </c>
       <c r="H777" s="16" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="778" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A778" s="17" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="B778" s="18">
-        <v>45265</v>
+        <v>45267</v>
       </c>
       <c r="C778" s="18">
         <v>45308</v>
       </c>
       <c r="D778" s="18">
-        <v>45355</v>
+        <v>45327</v>
       </c>
       <c r="E778" s="19" t="s">
-        <v>105</v>
+        <v>613</v>
       </c>
       <c r="F778" s="19" t="s">
         <v>16</v>
       </c>
       <c r="G778" s="20">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="H778" s="21" t="s">
-        <v>1069</v>
+        <v>614</v>
       </c>
     </row>
     <row r="779" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A779" s="12" t="s">
-        <v>175</v>
+        <v>6</v>
       </c>
       <c r="B779" s="13">
-        <v>45268</v>
+        <v>45271</v>
       </c>
       <c r="C779" s="13">
         <v>45308</v>
       </c>
       <c r="D779" s="13">
-        <v>45328</v>
+        <v>45331</v>
       </c>
       <c r="E779" s="14" t="s">
-        <v>1070</v>
+        <v>1067</v>
       </c>
       <c r="F779" s="14" t="s">
         <v>15</v>
       </c>
       <c r="G779" s="15">
-        <v>28</v>
+        <v>107</v>
       </c>
       <c r="H779" s="16" t="s">
-        <v>1071</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="780" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A780" s="17" t="s">
-        <v>175</v>
+        <v>52</v>
       </c>
       <c r="B780" s="18">
-        <v>45268</v>
+        <v>45265</v>
       </c>
       <c r="C780" s="18">
         <v>45308</v>
       </c>
       <c r="D780" s="18">
-        <v>45328</v>
+        <v>45355</v>
       </c>
       <c r="E780" s="19" t="s">
-        <v>1072</v>
+        <v>105</v>
       </c>
       <c r="F780" s="19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G780" s="20">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="H780" s="21" t="s">
-        <v>1073</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="781" spans="1:8" x14ac:dyDescent="0.3">
@@ -25019,47 +25457,47 @@
         <v>45328</v>
       </c>
       <c r="E781" s="14" t="s">
-        <v>1050</v>
+        <v>1070</v>
       </c>
       <c r="F781" s="14" t="s">
         <v>15</v>
       </c>
       <c r="G781" s="15">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="H781" s="16" t="s">
-        <v>1074</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="782" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A782" s="17" t="s">
-        <v>5</v>
+        <v>175</v>
       </c>
       <c r="B782" s="18">
-        <v>45265</v>
+        <v>45268</v>
       </c>
       <c r="C782" s="18">
         <v>45308</v>
       </c>
       <c r="D782" s="18">
-        <v>45327</v>
+        <v>45328</v>
       </c>
       <c r="E782" s="19" t="s">
-        <v>1075</v>
+        <v>1072</v>
       </c>
       <c r="F782" s="19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G782" s="20">
-        <v>94</v>
+        <v>41</v>
       </c>
       <c r="H782" s="21" t="s">
-        <v>1076</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="783" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A783" s="12" t="s">
-        <v>284</v>
+        <v>175</v>
       </c>
       <c r="B783" s="13">
         <v>45268</v>
@@ -25068,71 +25506,71 @@
         <v>45308</v>
       </c>
       <c r="D783" s="13">
-        <v>45344</v>
+        <v>45328</v>
       </c>
       <c r="E783" s="14" t="s">
-        <v>1077</v>
+        <v>1050</v>
       </c>
       <c r="F783" s="14" t="s">
         <v>15</v>
       </c>
       <c r="G783" s="15">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="H783" s="16" t="s">
-        <v>1078</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="784" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A784" s="17" t="s">
-        <v>86</v>
+        <v>5</v>
       </c>
       <c r="B784" s="18">
-        <v>45260</v>
+        <v>45265</v>
       </c>
       <c r="C784" s="18">
-        <v>45309</v>
+        <v>45308</v>
       </c>
       <c r="D784" s="18">
-        <v>45323</v>
+        <v>45327</v>
       </c>
       <c r="E784" s="19" t="s">
-        <v>1080</v>
+        <v>1075</v>
       </c>
       <c r="F784" s="19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G784" s="20">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="H784" s="21" t="s">
-        <v>1081</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="785" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A785" s="12" t="s">
-        <v>86</v>
+        <v>284</v>
       </c>
       <c r="B785" s="13">
-        <v>45273</v>
+        <v>45268</v>
       </c>
       <c r="C785" s="13">
-        <v>45309</v>
+        <v>45308</v>
       </c>
       <c r="D785" s="13">
-        <v>45338</v>
+        <v>45344</v>
       </c>
       <c r="E785" s="14" t="s">
-        <v>1082</v>
+        <v>1077</v>
       </c>
       <c r="F785" s="14" t="s">
         <v>15</v>
       </c>
       <c r="G785" s="15">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H785" s="16" t="s">
-        <v>1083</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="786" spans="1:8" x14ac:dyDescent="0.3">
@@ -25140,30 +25578,30 @@
         <v>86</v>
       </c>
       <c r="B786" s="18">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="C786" s="18">
         <v>45309</v>
       </c>
       <c r="D786" s="18">
-        <v>45324</v>
+        <v>45323</v>
       </c>
       <c r="E786" s="19" t="s">
-        <v>1084</v>
+        <v>1080</v>
       </c>
       <c r="F786" s="19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G786" s="20">
-        <v>25</v>
+        <v>84</v>
       </c>
       <c r="H786" s="21" t="s">
-        <v>1085</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="787" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A787" s="12" t="s">
-        <v>8</v>
+        <v>86</v>
       </c>
       <c r="B787" s="13">
         <v>45273</v>
@@ -25172,123 +25610,123 @@
         <v>45309</v>
       </c>
       <c r="D787" s="13">
-        <v>45350</v>
+        <v>45338</v>
       </c>
       <c r="E787" s="14" t="s">
-        <v>1086</v>
+        <v>1082</v>
       </c>
       <c r="F787" s="14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G787" s="15">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="H787" s="16" t="s">
-        <v>1087</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="788" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A788" s="17" t="s">
-        <v>278</v>
+        <v>86</v>
       </c>
       <c r="B788" s="18">
-        <v>45273</v>
+        <v>45259</v>
       </c>
       <c r="C788" s="18">
         <v>45309</v>
       </c>
       <c r="D788" s="18">
-        <v>45332</v>
+        <v>45324</v>
       </c>
       <c r="E788" s="19" t="s">
-        <v>1088</v>
+        <v>1084</v>
       </c>
       <c r="F788" s="19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G788" s="20">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="H788" s="21" t="s">
-        <v>1089</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="789" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A789" s="12" t="s">
-        <v>63</v>
+        <v>8</v>
       </c>
       <c r="B789" s="13">
-        <v>45272</v>
+        <v>45273</v>
       </c>
       <c r="C789" s="13">
         <v>45309</v>
       </c>
       <c r="D789" s="13">
-        <v>45337</v>
+        <v>45350</v>
       </c>
       <c r="E789" s="14" t="s">
-        <v>1090</v>
+        <v>1086</v>
       </c>
       <c r="F789" s="14" t="s">
         <v>16</v>
       </c>
       <c r="G789" s="15">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="H789" s="16" t="s">
-        <v>1091</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="790" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A790" s="17" t="s">
-        <v>76</v>
+        <v>278</v>
       </c>
       <c r="B790" s="18">
-        <v>45261</v>
+        <v>45273</v>
       </c>
       <c r="C790" s="18">
         <v>45309</v>
       </c>
       <c r="D790" s="18">
-        <v>45324</v>
+        <v>45332</v>
       </c>
       <c r="E790" s="19" t="s">
-        <v>1092</v>
+        <v>1088</v>
       </c>
       <c r="F790" s="19" t="s">
         <v>15</v>
       </c>
       <c r="G790" s="20">
-        <v>58</v>
+        <v>11</v>
       </c>
       <c r="H790" s="21" t="s">
-        <v>1093</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="791" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A791" s="12" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="B791" s="13">
-        <v>45271</v>
+        <v>45272</v>
       </c>
       <c r="C791" s="13">
         <v>45309</v>
       </c>
       <c r="D791" s="13">
-        <v>45373</v>
+        <v>45337</v>
       </c>
       <c r="E791" s="14" t="s">
-        <v>1094</v>
+        <v>1090</v>
       </c>
       <c r="F791" s="14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G791" s="15">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="H791" s="16" t="s">
-        <v>1095</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="792" spans="1:8" x14ac:dyDescent="0.3">
@@ -25296,519 +25734,2833 @@
         <v>76</v>
       </c>
       <c r="B792" s="18">
-        <v>45271</v>
+        <v>45261</v>
       </c>
       <c r="C792" s="18">
         <v>45309</v>
       </c>
       <c r="D792" s="18">
-        <v>45373</v>
+        <v>45324</v>
       </c>
       <c r="E792" s="19" t="s">
-        <v>1096</v>
+        <v>1092</v>
       </c>
       <c r="F792" s="19" t="s">
         <v>15</v>
       </c>
       <c r="G792" s="20">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="H792" s="21" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="793" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A793" s="12" t="s">
-        <v>6</v>
+        <v>76</v>
       </c>
       <c r="B793" s="13">
-        <v>45264</v>
+        <v>45271</v>
       </c>
       <c r="C793" s="13">
         <v>45309</v>
       </c>
       <c r="D793" s="13">
-        <v>45323</v>
+        <v>45373</v>
       </c>
       <c r="E793" s="14" t="s">
-        <v>1097</v>
+        <v>1094</v>
       </c>
       <c r="F793" s="14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G793" s="15">
-        <v>95</v>
+        <v>37</v>
       </c>
       <c r="H793" s="16" t="s">
-        <v>1098</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="794" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A794" s="17" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="B794" s="18">
-        <v>45273</v>
+        <v>45271</v>
       </c>
       <c r="C794" s="18">
         <v>45309</v>
       </c>
       <c r="D794" s="18">
-        <v>45334</v>
+        <v>45373</v>
       </c>
       <c r="E794" s="19" t="s">
-        <v>1099</v>
+        <v>1096</v>
       </c>
       <c r="F794" s="19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G794" s="20">
-        <v>238</v>
+        <v>40</v>
       </c>
       <c r="H794" s="21" t="s">
-        <v>1100</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="795" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A795" s="12" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B795" s="13">
-        <v>45272</v>
+        <v>45264</v>
       </c>
       <c r="C795" s="13">
         <v>45309</v>
       </c>
       <c r="D795" s="13">
+        <v>45323</v>
+      </c>
+      <c r="E795" s="14" t="s">
+        <v>1097</v>
+      </c>
+      <c r="F795" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G795" s="15">
+        <v>95</v>
+      </c>
+      <c r="H795" s="16" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="796" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A796" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="B796" s="18">
+        <v>45273</v>
+      </c>
+      <c r="C796" s="18">
+        <v>45309</v>
+      </c>
+      <c r="D796" s="18">
+        <v>45334</v>
+      </c>
+      <c r="E796" s="19" t="s">
+        <v>1099</v>
+      </c>
+      <c r="F796" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G796" s="20">
+        <v>238</v>
+      </c>
+      <c r="H796" s="21" t="s">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="797" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A797" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B797" s="13">
+        <v>45272</v>
+      </c>
+      <c r="C797" s="13">
+        <v>45309</v>
+      </c>
+      <c r="D797" s="13">
         <v>45015</v>
       </c>
-      <c r="E795" s="14" t="s">
+      <c r="E797" s="14" t="s">
         <v>777</v>
       </c>
-      <c r="F795" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="G795" s="15">
+      <c r="F797" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G797" s="15">
         <v>111</v>
       </c>
-      <c r="H795" s="16" t="s">
+      <c r="H797" s="16" t="s">
         <v>1101</v>
       </c>
     </row>
-    <row r="796" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A796" s="12" t="s">
+    <row r="798" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A798" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="B798" s="18">
+        <v>45272</v>
+      </c>
+      <c r="C798" s="18">
+        <v>45309</v>
+      </c>
+      <c r="D798" s="18">
+        <v>45015</v>
+      </c>
+      <c r="E798" s="19" t="s">
+        <v>777</v>
+      </c>
+      <c r="F798" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G798" s="20">
+        <v>111</v>
+      </c>
+      <c r="H798" s="21" t="s">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="799" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A799" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="B796" s="13">
+      <c r="B799" s="13">
         <v>45275</v>
       </c>
-      <c r="C796" s="13">
+      <c r="C799" s="13">
         <v>45310</v>
       </c>
-      <c r="D796" s="13">
+      <c r="D799" s="13">
         <v>45275</v>
       </c>
-      <c r="E796" s="14" t="s">
+      <c r="E799" s="14" t="s">
         <v>1102</v>
       </c>
-      <c r="F796" s="14" t="s">
+      <c r="F799" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G796" s="15">
+      <c r="G799" s="15">
         <v>8</v>
       </c>
-      <c r="H796" s="16" t="s">
+      <c r="H799" s="16" t="s">
         <v>1103</v>
       </c>
     </row>
-    <row r="797" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A797" s="17" t="s">
+    <row r="800" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A800" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="B797" s="18">
+      <c r="B800" s="18">
         <v>45274</v>
       </c>
-      <c r="C797" s="18">
+      <c r="C800" s="18">
         <v>45310</v>
       </c>
-      <c r="D797" s="18">
+      <c r="D800" s="18">
         <v>45274</v>
       </c>
-      <c r="E797" s="19" t="s">
+      <c r="E800" s="19" t="s">
         <v>1104</v>
       </c>
-      <c r="F797" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="G797" s="20">
+      <c r="F800" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G800" s="20">
         <v>330</v>
       </c>
-      <c r="H797" s="21" t="s">
+      <c r="H800" s="21" t="s">
         <v>1105</v>
       </c>
     </row>
-    <row r="798" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A798" s="12" t="s">
+    <row r="801" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A801" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="B798" s="13">
+      <c r="B801" s="13">
         <v>45274</v>
       </c>
-      <c r="C798" s="13">
+      <c r="C801" s="13">
         <v>45310</v>
       </c>
-      <c r="D798" s="13">
+      <c r="D801" s="13">
         <v>45274</v>
       </c>
-      <c r="E798" s="14" t="s">
+      <c r="E801" s="14" t="s">
         <v>1106</v>
       </c>
-      <c r="F798" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="G798" s="15">
+      <c r="F801" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G801" s="15">
         <v>18</v>
       </c>
-      <c r="H798" s="16" t="s">
+      <c r="H801" s="16" t="s">
         <v>1107</v>
       </c>
     </row>
-    <row r="799" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A799" s="17" t="s">
+    <row r="802" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A802" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B799" s="18">
+      <c r="B802" s="18">
         <v>45274</v>
       </c>
-      <c r="C799" s="18">
+      <c r="C802" s="18">
         <v>45310</v>
       </c>
-      <c r="D799" s="18">
+      <c r="D802" s="18">
         <v>45274</v>
       </c>
-      <c r="E799" s="19" t="s">
+      <c r="E802" s="19" t="s">
         <v>1106</v>
       </c>
-      <c r="F799" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="G799" s="20">
+      <c r="F802" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G802" s="20">
         <v>43</v>
       </c>
-      <c r="H799" s="21" t="s">
+      <c r="H802" s="21" t="s">
         <v>1108</v>
       </c>
     </row>
-    <row r="800" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A800" s="12" t="s">
+    <row r="803" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A803" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="B800" s="13">
+      <c r="B803" s="13">
         <v>45275</v>
       </c>
-      <c r="C800" s="13">
+      <c r="C803" s="13">
         <v>45310</v>
       </c>
-      <c r="D800" s="13">
+      <c r="D803" s="13">
         <v>45275</v>
       </c>
-      <c r="E800" s="14" t="s">
+      <c r="E803" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="F800" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="G800" s="15">
+      <c r="F803" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G803" s="15">
         <v>349</v>
       </c>
-      <c r="H800" s="16" t="s">
+      <c r="H803" s="16" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="801" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A801" s="17" t="s">
+    <row r="804" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A804" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B801" s="18">
+      <c r="B804" s="18">
         <v>45275</v>
       </c>
-      <c r="C801" s="18">
+      <c r="C804" s="18">
         <v>45310</v>
       </c>
-      <c r="D801" s="18">
+      <c r="D804" s="18">
         <v>45275</v>
       </c>
-      <c r="E801" s="19" t="s">
+      <c r="E804" s="19" t="s">
         <v>122</v>
       </c>
-      <c r="F801" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="G801" s="20">
+      <c r="F804" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G804" s="20">
         <v>42</v>
       </c>
-      <c r="H801" s="21" t="s">
+      <c r="H804" s="21" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="802" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A802" s="12" t="s">
+    <row r="805" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A805" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="B802" s="13">
+      <c r="B805" s="13">
         <v>45278</v>
       </c>
-      <c r="C802" s="13">
+      <c r="C805" s="13">
         <v>45310</v>
       </c>
-      <c r="D802" s="13">
+      <c r="D805" s="13">
         <v>45338</v>
       </c>
-      <c r="E802" s="14" t="s">
+      <c r="E805" s="14" t="s">
         <v>654</v>
       </c>
-      <c r="F802" s="14" t="s">
+      <c r="F805" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G802" s="15">
+      <c r="G805" s="15">
         <v>1</v>
       </c>
-      <c r="H802" s="16" t="s">
+      <c r="H805" s="16" t="s">
         <v>655</v>
       </c>
     </row>
-    <row r="803" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A803" s="17" t="s">
+    <row r="806" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A806" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="B803" s="18">
+      <c r="B806" s="18">
         <v>45274</v>
       </c>
-      <c r="C803" s="18">
+      <c r="C806" s="18">
         <v>45310</v>
       </c>
-      <c r="D803" s="18">
+      <c r="D806" s="18">
         <v>45274</v>
       </c>
-      <c r="E803" s="19" t="s">
+      <c r="E806" s="19" t="s">
         <v>1106</v>
       </c>
-      <c r="F803" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="G803" s="20">
+      <c r="F806" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G806" s="20">
         <v>121</v>
       </c>
-      <c r="H803" s="21" t="s">
+      <c r="H806" s="21" t="s">
         <v>1109</v>
       </c>
     </row>
-    <row r="804" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A804" s="12" t="s">
+    <row r="807" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A807" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="B804" s="13">
+      <c r="B807" s="13">
         <v>45274</v>
       </c>
-      <c r="C804" s="13">
+      <c r="C807" s="13">
         <v>45310</v>
       </c>
-      <c r="D804" s="13">
+      <c r="D807" s="13">
         <v>45274</v>
       </c>
-      <c r="E804" s="14" t="s">
+      <c r="E807" s="14" t="s">
         <v>1110</v>
       </c>
-      <c r="F804" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="G804" s="15">
+      <c r="F807" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G807" s="15">
         <v>23</v>
       </c>
-      <c r="H804" s="16" t="s">
+      <c r="H807" s="16" t="s">
         <v>1111</v>
       </c>
     </row>
-    <row r="805" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A805" s="17" t="s">
+    <row r="808" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A808" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="B805" s="18">
+      <c r="B808" s="18">
         <v>45275</v>
       </c>
-      <c r="C805" s="18">
+      <c r="C808" s="18">
         <v>45310</v>
       </c>
-      <c r="D805" s="18">
+      <c r="D808" s="18">
         <v>45275</v>
       </c>
-      <c r="E805" s="19" t="s">
+      <c r="E808" s="19" t="s">
         <v>122</v>
       </c>
-      <c r="F805" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="G805" s="20">
+      <c r="F808" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G808" s="20">
         <v>42</v>
       </c>
-      <c r="H805" s="21" t="s">
+      <c r="H808" s="21" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="806" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A806" s="12" t="s">
+    <row r="809" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A809" s="12" t="s">
         <v>252</v>
       </c>
-      <c r="B806" s="13">
+      <c r="B809" s="13">
         <v>45275</v>
       </c>
-      <c r="C806" s="13">
+      <c r="C809" s="13">
         <v>45310</v>
       </c>
-      <c r="D806" s="13">
+      <c r="D809" s="13">
         <v>45275</v>
       </c>
-      <c r="E806" s="14" t="s">
+      <c r="E809" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="F806" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="G806" s="15">
+      <c r="F809" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G809" s="15">
         <v>5</v>
       </c>
-      <c r="H806" s="16" t="s">
+      <c r="H809" s="16" t="s">
         <v>1112</v>
       </c>
     </row>
-    <row r="807" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A807" s="17" t="s">
+    <row r="810" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A810" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="B807" s="18">
+      <c r="B810" s="18">
         <v>45261</v>
       </c>
-      <c r="C807" s="18">
+      <c r="C810" s="18">
         <v>45313</v>
       </c>
-      <c r="D807" s="18">
+      <c r="D810" s="18">
         <v>45322</v>
       </c>
-      <c r="E807" s="19" t="s">
+      <c r="E810" s="19" t="s">
         <v>1113</v>
       </c>
-      <c r="F807" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="G807" s="20">
+      <c r="F810" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G810" s="20">
         <v>3</v>
       </c>
-      <c r="H807" s="21" t="s">
+      <c r="H810" s="21" t="s">
         <v>1114</v>
       </c>
     </row>
-    <row r="808" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A808" s="12" t="s">
+    <row r="811" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A811" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="B808" s="13">
+      <c r="B811" s="13">
         <v>45261</v>
       </c>
-      <c r="C808" s="13">
+      <c r="C811" s="13">
         <v>45313</v>
       </c>
-      <c r="D808" s="13">
+      <c r="D811" s="13">
         <v>45322</v>
       </c>
-      <c r="E808" s="14" t="s">
+      <c r="E811" s="14" t="s">
         <v>1113</v>
       </c>
-      <c r="F808" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="G808" s="15">
+      <c r="F811" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G811" s="15">
         <v>7</v>
       </c>
-      <c r="H808" s="16" t="s">
+      <c r="H811" s="16" t="s">
         <v>1115</v>
       </c>
     </row>
-    <row r="809" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A809" s="17" t="s">
+    <row r="812" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A812" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="B809" s="18">
+      <c r="B812" s="18">
         <v>45261</v>
       </c>
-      <c r="C809" s="18">
+      <c r="C812" s="18">
         <v>45313</v>
       </c>
-      <c r="D809" s="18">
+      <c r="D812" s="18">
         <v>45322</v>
       </c>
-      <c r="E809" s="19" t="s">
+      <c r="E812" s="19" t="s">
         <v>1113</v>
       </c>
-      <c r="F809" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="G809" s="20">
+      <c r="F812" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G812" s="20">
         <v>20</v>
       </c>
-      <c r="H809" s="21" t="s">
+      <c r="H812" s="21" t="s">
         <v>1116</v>
       </c>
     </row>
-    <row r="810" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A810" s="12" t="s">
+    <row r="813" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A813" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="B810" s="13">
+      <c r="B813" s="13">
         <v>45265</v>
       </c>
-      <c r="C810" s="13">
+      <c r="C813" s="13">
         <v>45313</v>
       </c>
-      <c r="D810" s="13">
+      <c r="D813" s="13">
         <v>45327</v>
       </c>
-      <c r="E810" s="14" t="s">
+      <c r="E813" s="14" t="s">
         <v>1117</v>
       </c>
-      <c r="F810" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="G810" s="15">
+      <c r="F813" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G813" s="15">
         <v>1</v>
       </c>
-      <c r="H810" s="16" t="s">
+      <c r="H813" s="16" t="s">
         <v>1118</v>
       </c>
     </row>
-    <row r="811" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A811" s="17" t="s">
+    <row r="814" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A814" s="17" t="s">
         <v>175</v>
       </c>
-      <c r="B811" s="18">
+      <c r="B814" s="18">
         <v>45261</v>
       </c>
-      <c r="C811" s="18">
+      <c r="C814" s="18">
         <v>45313</v>
       </c>
-      <c r="D811" s="18">
+      <c r="D814" s="18">
         <v>45322</v>
       </c>
-      <c r="E811" s="19" t="s">
+      <c r="E814" s="19" t="s">
         <v>1113</v>
       </c>
-      <c r="F811" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="G811" s="20">
+      <c r="F814" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G814" s="20">
         <v>24</v>
       </c>
-      <c r="H811" s="21" t="s">
+      <c r="H814" s="21" t="s">
         <v>1119</v>
+      </c>
+    </row>
+    <row r="815" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A815" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B815" s="13">
+        <v>45275</v>
+      </c>
+      <c r="C815" s="13">
+        <v>45314</v>
+      </c>
+      <c r="D815" s="13">
+        <v>45305</v>
+      </c>
+      <c r="E815" s="14" t="s">
+        <v>1120</v>
+      </c>
+      <c r="F815" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="G815" s="15">
+        <v>65</v>
+      </c>
+      <c r="H815" s="16" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="816" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A816" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="B816" s="18">
+        <v>45272</v>
+      </c>
+      <c r="C816" s="18">
+        <v>45314</v>
+      </c>
+      <c r="D816" s="18">
+        <v>45322</v>
+      </c>
+      <c r="E816" s="19" t="s">
+        <v>1122</v>
+      </c>
+      <c r="F816" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G816" s="20">
+        <v>9</v>
+      </c>
+      <c r="H816" s="21" t="s">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="817" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A817" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B817" s="13">
+        <v>45272</v>
+      </c>
+      <c r="C817" s="13">
+        <v>45314</v>
+      </c>
+      <c r="D817" s="13">
+        <v>45322</v>
+      </c>
+      <c r="E817" s="14" t="s">
+        <v>1124</v>
+      </c>
+      <c r="F817" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G817" s="15">
+        <v>15</v>
+      </c>
+      <c r="H817" s="16" t="s">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="818" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A818" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="B818" s="18">
+        <v>45275</v>
+      </c>
+      <c r="C818" s="18">
+        <v>45314</v>
+      </c>
+      <c r="D818" s="18">
+        <v>45347</v>
+      </c>
+      <c r="E818" s="19" t="s">
+        <v>1126</v>
+      </c>
+      <c r="F818" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G818" s="20">
+        <v>127</v>
+      </c>
+      <c r="H818" s="21" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="819" spans="1:8" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A819" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="B819" s="13">
+        <v>45275</v>
+      </c>
+      <c r="C819" s="13">
+        <v>45314</v>
+      </c>
+      <c r="D819" s="13">
+        <v>45334</v>
+      </c>
+      <c r="E819" s="14" t="s">
+        <v>1128</v>
+      </c>
+      <c r="F819" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G819" s="15">
+        <v>52</v>
+      </c>
+      <c r="H819" s="16" t="s">
+        <v>1129</v>
+      </c>
+    </row>
+    <row r="820" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A820" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="B820" s="18">
+        <v>45272</v>
+      </c>
+      <c r="C820" s="18">
+        <v>45314</v>
+      </c>
+      <c r="D820" s="18">
+        <v>45322</v>
+      </c>
+      <c r="E820" s="19" t="s">
+        <v>1122</v>
+      </c>
+      <c r="F820" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G820" s="20">
+        <v>11</v>
+      </c>
+      <c r="H820" s="21" t="s">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="821" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A821" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B821" s="13">
+        <v>45272</v>
+      </c>
+      <c r="C821" s="13">
+        <v>45314</v>
+      </c>
+      <c r="D821" s="13">
+        <v>45322</v>
+      </c>
+      <c r="E821" s="14" t="s">
+        <v>1122</v>
+      </c>
+      <c r="F821" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G821" s="15">
+        <v>8</v>
+      </c>
+      <c r="H821" s="16" t="s">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="822" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A822" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B822" s="18">
+        <v>45272</v>
+      </c>
+      <c r="C822" s="18">
+        <v>45314</v>
+      </c>
+      <c r="D822" s="18">
+        <v>45322</v>
+      </c>
+      <c r="E822" s="19" t="s">
+        <v>1122</v>
+      </c>
+      <c r="F822" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G822" s="20">
+        <v>9</v>
+      </c>
+      <c r="H822" s="21" t="s">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="823" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A823" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="B823" s="13">
+        <v>45261</v>
+      </c>
+      <c r="C823" s="13">
+        <v>45314</v>
+      </c>
+      <c r="D823" s="13">
+        <v>45322</v>
+      </c>
+      <c r="E823" s="14" t="s">
+        <v>1113</v>
+      </c>
+      <c r="F823" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G823" s="15">
+        <v>4</v>
+      </c>
+      <c r="H823" s="16" t="s">
+        <v>1133</v>
+      </c>
+    </row>
+    <row r="824" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A824" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="B824" s="18">
+        <v>45272</v>
+      </c>
+      <c r="C824" s="18">
+        <v>45314</v>
+      </c>
+      <c r="D824" s="18">
+        <v>45322</v>
+      </c>
+      <c r="E824" s="19" t="s">
+        <v>1122</v>
+      </c>
+      <c r="F824" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G824" s="20">
+        <v>46</v>
+      </c>
+      <c r="H824" s="21" t="s">
+        <v>1134</v>
+      </c>
+    </row>
+    <row r="825" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A825" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="B825" s="13">
+        <v>45274</v>
+      </c>
+      <c r="C825" s="13">
+        <v>45315</v>
+      </c>
+      <c r="D825" s="13">
+        <v>45339</v>
+      </c>
+      <c r="E825" s="14" t="s">
+        <v>1135</v>
+      </c>
+      <c r="F825" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G825" s="15">
+        <v>2</v>
+      </c>
+      <c r="H825" s="16" t="s">
+        <v>1136</v>
+      </c>
+    </row>
+    <row r="826" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A826" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="B826" s="18">
+        <v>45274</v>
+      </c>
+      <c r="C826" s="18">
+        <v>45315</v>
+      </c>
+      <c r="D826" s="18">
+        <v>45337</v>
+      </c>
+      <c r="E826" s="19" t="s">
+        <v>1137</v>
+      </c>
+      <c r="F826" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G826" s="20">
+        <v>4</v>
+      </c>
+      <c r="H826" s="21" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="827" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A827" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B827" s="13">
+        <v>45274</v>
+      </c>
+      <c r="C827" s="13">
+        <v>45315</v>
+      </c>
+      <c r="D827" s="13">
+        <v>45339</v>
+      </c>
+      <c r="E827" s="14" t="s">
+        <v>1137</v>
+      </c>
+      <c r="F827" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G827" s="15">
+        <v>3</v>
+      </c>
+      <c r="H827" s="16" t="s">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="828" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A828" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="B828" s="18">
+        <v>45274</v>
+      </c>
+      <c r="C828" s="18">
+        <v>45315</v>
+      </c>
+      <c r="D828" s="18">
+        <v>45341</v>
+      </c>
+      <c r="E828" s="19" t="s">
+        <v>1140</v>
+      </c>
+      <c r="F828" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G828" s="20">
+        <v>5</v>
+      </c>
+      <c r="H828" s="21" t="s">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="829" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A829" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B829" s="13">
+        <v>45274</v>
+      </c>
+      <c r="C829" s="13">
+        <v>45315</v>
+      </c>
+      <c r="D829" s="13">
+        <v>45335</v>
+      </c>
+      <c r="E829" s="14" t="s">
+        <v>1142</v>
+      </c>
+      <c r="F829" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G829" s="15">
+        <v>5</v>
+      </c>
+      <c r="H829" s="16" t="s">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="830" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A830" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="B830" s="18">
+        <v>45274</v>
+      </c>
+      <c r="C830" s="18">
+        <v>45315</v>
+      </c>
+      <c r="D830" s="18">
+        <v>45337</v>
+      </c>
+      <c r="E830" s="19" t="s">
+        <v>1144</v>
+      </c>
+      <c r="F830" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G830" s="20">
+        <v>5</v>
+      </c>
+      <c r="H830" s="21" t="s">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="831" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A831" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B831" s="13">
+        <v>45274</v>
+      </c>
+      <c r="C831" s="13">
+        <v>45315</v>
+      </c>
+      <c r="D831" s="13">
+        <v>45339</v>
+      </c>
+      <c r="E831" s="14" t="s">
+        <v>1146</v>
+      </c>
+      <c r="F831" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G831" s="15">
+        <v>5</v>
+      </c>
+      <c r="H831" s="16" t="s">
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="832" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A832" s="17" t="s">
+        <v>977</v>
+      </c>
+      <c r="B832" s="18">
+        <v>45274</v>
+      </c>
+      <c r="C832" s="18">
+        <v>45315</v>
+      </c>
+      <c r="D832" s="18">
+        <v>45346</v>
+      </c>
+      <c r="E832" s="19" t="s">
+        <v>1148</v>
+      </c>
+      <c r="F832" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G832" s="20">
+        <v>3</v>
+      </c>
+      <c r="H832" s="21" t="s">
+        <v>1149</v>
+      </c>
+    </row>
+    <row r="833" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A833" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B833" s="13">
+        <v>45274</v>
+      </c>
+      <c r="C833" s="13">
+        <v>45315</v>
+      </c>
+      <c r="D833" s="13">
+        <v>45338</v>
+      </c>
+      <c r="E833" s="14" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F833" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G833" s="15">
+        <v>4</v>
+      </c>
+      <c r="H833" s="16" t="s">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="834" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A834" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="B834" s="18">
+        <v>45274</v>
+      </c>
+      <c r="C834" s="18">
+        <v>45315</v>
+      </c>
+      <c r="D834" s="18">
+        <v>45338</v>
+      </c>
+      <c r="E834" s="19" t="s">
+        <v>1152</v>
+      </c>
+      <c r="F834" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G834" s="20">
+        <v>8</v>
+      </c>
+      <c r="H834" s="21" t="s">
+        <v>1153</v>
+      </c>
+    </row>
+    <row r="835" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A835" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B835" s="13">
+        <v>45274</v>
+      </c>
+      <c r="C835" s="13">
+        <v>45315</v>
+      </c>
+      <c r="D835" s="13">
+        <v>45338</v>
+      </c>
+      <c r="E835" s="14" t="s">
+        <v>1154</v>
+      </c>
+      <c r="F835" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G835" s="15">
+        <v>3</v>
+      </c>
+      <c r="H835" s="16" t="s">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="836" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A836" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="B836" s="18">
+        <v>45274</v>
+      </c>
+      <c r="C836" s="18">
+        <v>45315</v>
+      </c>
+      <c r="D836" s="18">
+        <v>45338</v>
+      </c>
+      <c r="E836" s="19" t="s">
+        <v>1156</v>
+      </c>
+      <c r="F836" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G836" s="20">
+        <v>6</v>
+      </c>
+      <c r="H836" s="21" t="s">
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="837" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A837" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B837" s="13">
+        <v>45274</v>
+      </c>
+      <c r="C837" s="13">
+        <v>45315</v>
+      </c>
+      <c r="D837" s="13">
+        <v>45338</v>
+      </c>
+      <c r="E837" s="14" t="s">
+        <v>1158</v>
+      </c>
+      <c r="F837" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G837" s="15">
+        <v>10</v>
+      </c>
+      <c r="H837" s="16" t="s">
+        <v>1159</v>
+      </c>
+    </row>
+    <row r="838" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A838" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="B838" s="18">
+        <v>45274</v>
+      </c>
+      <c r="C838" s="18">
+        <v>45315</v>
+      </c>
+      <c r="D838" s="18">
+        <v>45338</v>
+      </c>
+      <c r="E838" s="19" t="s">
+        <v>1160</v>
+      </c>
+      <c r="F838" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G838" s="20">
+        <v>7</v>
+      </c>
+      <c r="H838" s="21" t="s">
+        <v>1161</v>
+      </c>
+    </row>
+    <row r="839" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A839" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B839" s="13">
+        <v>45274</v>
+      </c>
+      <c r="C839" s="13">
+        <v>45315</v>
+      </c>
+      <c r="D839" s="13">
+        <v>45337</v>
+      </c>
+      <c r="E839" s="14" t="s">
+        <v>1162</v>
+      </c>
+      <c r="F839" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G839" s="15">
+        <v>5</v>
+      </c>
+      <c r="H839" s="16" t="s">
+        <v>1163</v>
+      </c>
+    </row>
+    <row r="840" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A840" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="B840" s="18">
+        <v>45274</v>
+      </c>
+      <c r="C840" s="18">
+        <v>45315</v>
+      </c>
+      <c r="D840" s="18">
+        <v>45337</v>
+      </c>
+      <c r="E840" s="19" t="s">
+        <v>1162</v>
+      </c>
+      <c r="F840" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G840" s="20">
+        <v>3</v>
+      </c>
+      <c r="H840" s="21" t="s">
+        <v>1164</v>
+      </c>
+    </row>
+    <row r="841" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A841" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="B841" s="13">
+        <v>45274</v>
+      </c>
+      <c r="C841" s="13">
+        <v>45315</v>
+      </c>
+      <c r="D841" s="13">
+        <v>45339</v>
+      </c>
+      <c r="E841" s="14" t="s">
+        <v>1165</v>
+      </c>
+      <c r="F841" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G841" s="15">
+        <v>4</v>
+      </c>
+      <c r="H841" s="16" t="s">
+        <v>1166</v>
+      </c>
+    </row>
+    <row r="842" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A842" s="17" t="s">
+        <v>135</v>
+      </c>
+      <c r="B842" s="18">
+        <v>45274</v>
+      </c>
+      <c r="C842" s="18">
+        <v>45315</v>
+      </c>
+      <c r="D842" s="18">
+        <v>45339</v>
+      </c>
+      <c r="E842" s="19" t="s">
+        <v>1162</v>
+      </c>
+      <c r="F842" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G842" s="20">
+        <v>5</v>
+      </c>
+      <c r="H842" s="21" t="s">
+        <v>1167</v>
+      </c>
+    </row>
+    <row r="843" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A843" s="12" t="s">
+        <v>1168</v>
+      </c>
+      <c r="B843" s="13">
+        <v>45274</v>
+      </c>
+      <c r="C843" s="13">
+        <v>45315</v>
+      </c>
+      <c r="D843" s="13">
+        <v>45335</v>
+      </c>
+      <c r="E843" s="14" t="s">
+        <v>1162</v>
+      </c>
+      <c r="F843" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G843" s="15">
+        <v>6</v>
+      </c>
+      <c r="H843" s="16" t="s">
+        <v>1169</v>
+      </c>
+    </row>
+    <row r="844" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A844" s="17" t="s">
+        <v>926</v>
+      </c>
+      <c r="B844" s="18">
+        <v>45274</v>
+      </c>
+      <c r="C844" s="18">
+        <v>45315</v>
+      </c>
+      <c r="D844" s="18">
+        <v>45338</v>
+      </c>
+      <c r="E844" s="19" t="s">
+        <v>1165</v>
+      </c>
+      <c r="F844" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G844" s="20">
+        <v>5</v>
+      </c>
+      <c r="H844" s="21" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="845" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A845" s="12" t="s">
+        <v>926</v>
+      </c>
+      <c r="B845" s="13">
+        <v>45274</v>
+      </c>
+      <c r="C845" s="13">
+        <v>45315</v>
+      </c>
+      <c r="D845" s="13">
+        <v>45339</v>
+      </c>
+      <c r="E845" s="14" t="s">
+        <v>1162</v>
+      </c>
+      <c r="F845" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G845" s="15">
+        <v>7</v>
+      </c>
+      <c r="H845" s="16" t="s">
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="846" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A846" s="17" t="s">
+        <v>926</v>
+      </c>
+      <c r="B846" s="18">
+        <v>45274</v>
+      </c>
+      <c r="C846" s="18">
+        <v>45315</v>
+      </c>
+      <c r="D846" s="18">
+        <v>45339</v>
+      </c>
+      <c r="E846" s="19" t="s">
+        <v>1162</v>
+      </c>
+      <c r="F846" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G846" s="20">
+        <v>4</v>
+      </c>
+      <c r="H846" s="21" t="s">
+        <v>1172</v>
+      </c>
+    </row>
+    <row r="847" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A847" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="B847" s="13">
+        <v>45274</v>
+      </c>
+      <c r="C847" s="13">
+        <v>45315</v>
+      </c>
+      <c r="D847" s="13">
+        <v>45345</v>
+      </c>
+      <c r="E847" s="14" t="s">
+        <v>1173</v>
+      </c>
+      <c r="F847" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G847" s="15">
+        <v>2</v>
+      </c>
+      <c r="H847" s="16" t="s">
+        <v>1174</v>
+      </c>
+    </row>
+    <row r="848" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A848" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="B848" s="18">
+        <v>45274</v>
+      </c>
+      <c r="C848" s="18">
+        <v>45315</v>
+      </c>
+      <c r="D848" s="18">
+        <v>45347</v>
+      </c>
+      <c r="E848" s="19" t="s">
+        <v>1148</v>
+      </c>
+      <c r="F848" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G848" s="20">
+        <v>4</v>
+      </c>
+      <c r="H848" s="21" t="s">
+        <v>1175</v>
+      </c>
+    </row>
+    <row r="849" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A849" s="12" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B849" s="13">
+        <v>45274</v>
+      </c>
+      <c r="C849" s="13">
+        <v>45315</v>
+      </c>
+      <c r="D849" s="13">
+        <v>45345</v>
+      </c>
+      <c r="E849" s="14" t="s">
+        <v>1148</v>
+      </c>
+      <c r="F849" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G849" s="15">
+        <v>7</v>
+      </c>
+      <c r="H849" s="16" t="s">
+        <v>1177</v>
+      </c>
+    </row>
+    <row r="850" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A850" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="B850" s="18">
+        <v>45274</v>
+      </c>
+      <c r="C850" s="18">
+        <v>45315</v>
+      </c>
+      <c r="D850" s="18">
+        <v>45338</v>
+      </c>
+      <c r="E850" s="19" t="s">
+        <v>1148</v>
+      </c>
+      <c r="F850" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G850" s="20">
+        <v>2</v>
+      </c>
+      <c r="H850" s="21" t="s">
+        <v>1178</v>
+      </c>
+    </row>
+    <row r="851" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A851" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B851" s="13">
+        <v>45274</v>
+      </c>
+      <c r="C851" s="13">
+        <v>45315</v>
+      </c>
+      <c r="D851" s="13">
+        <v>45347</v>
+      </c>
+      <c r="E851" s="14" t="s">
+        <v>1148</v>
+      </c>
+      <c r="F851" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G851" s="15">
+        <v>4</v>
+      </c>
+      <c r="H851" s="16" t="s">
+        <v>1179</v>
+      </c>
+    </row>
+    <row r="852" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A852" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="B852" s="18">
+        <v>45275</v>
+      </c>
+      <c r="C852" s="18">
+        <v>45315</v>
+      </c>
+      <c r="D852" s="18">
+        <v>45275</v>
+      </c>
+      <c r="E852" s="19" t="s">
+        <v>1180</v>
+      </c>
+      <c r="F852" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G852" s="20">
+        <v>6</v>
+      </c>
+      <c r="H852" s="21" t="s">
+        <v>1181</v>
+      </c>
+    </row>
+    <row r="853" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A853" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B853" s="13">
+        <v>45274</v>
+      </c>
+      <c r="C853" s="13">
+        <v>45315</v>
+      </c>
+      <c r="D853" s="13">
+        <v>45337</v>
+      </c>
+      <c r="E853" s="14" t="s">
+        <v>1135</v>
+      </c>
+      <c r="F853" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G853" s="15">
+        <v>8</v>
+      </c>
+      <c r="H853" s="16" t="s">
+        <v>1182</v>
+      </c>
+    </row>
+    <row r="854" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A854" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B854" s="18">
+        <v>45274</v>
+      </c>
+      <c r="C854" s="18">
+        <v>45315</v>
+      </c>
+      <c r="D854" s="18">
+        <v>45338</v>
+      </c>
+      <c r="E854" s="19" t="s">
+        <v>1183</v>
+      </c>
+      <c r="F854" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G854" s="20">
+        <v>5</v>
+      </c>
+      <c r="H854" s="21" t="s">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="855" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A855" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B855" s="13">
+        <v>45274</v>
+      </c>
+      <c r="C855" s="13">
+        <v>45315</v>
+      </c>
+      <c r="D855" s="13">
+        <v>45334</v>
+      </c>
+      <c r="E855" s="14" t="s">
+        <v>1185</v>
+      </c>
+      <c r="F855" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G855" s="15">
+        <v>2</v>
+      </c>
+      <c r="H855" s="16" t="s">
+        <v>1186</v>
+      </c>
+    </row>
+    <row r="856" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A856" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B856" s="18">
+        <v>45274</v>
+      </c>
+      <c r="C856" s="18">
+        <v>45315</v>
+      </c>
+      <c r="D856" s="18">
+        <v>45345</v>
+      </c>
+      <c r="E856" s="19" t="s">
+        <v>1187</v>
+      </c>
+      <c r="F856" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G856" s="20">
+        <v>6</v>
+      </c>
+      <c r="H856" s="21" t="s">
+        <v>1188</v>
+      </c>
+    </row>
+    <row r="857" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A857" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B857" s="13">
+        <v>45274</v>
+      </c>
+      <c r="C857" s="13">
+        <v>45315</v>
+      </c>
+      <c r="D857" s="13">
+        <v>45340</v>
+      </c>
+      <c r="E857" s="14" t="s">
+        <v>1189</v>
+      </c>
+      <c r="F857" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G857" s="15">
+        <v>8</v>
+      </c>
+      <c r="H857" s="16" t="s">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="858" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A858" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B858" s="18">
+        <v>45274</v>
+      </c>
+      <c r="C858" s="18">
+        <v>45315</v>
+      </c>
+      <c r="D858" s="18">
+        <v>45338</v>
+      </c>
+      <c r="E858" s="19" t="s">
+        <v>1191</v>
+      </c>
+      <c r="F858" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G858" s="20">
+        <v>4</v>
+      </c>
+      <c r="H858" s="21" t="s">
+        <v>1192</v>
+      </c>
+    </row>
+    <row r="859" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A859" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B859" s="13">
+        <v>45274</v>
+      </c>
+      <c r="C859" s="13">
+        <v>45315</v>
+      </c>
+      <c r="D859" s="13">
+        <v>45340</v>
+      </c>
+      <c r="E859" s="14" t="s">
+        <v>1193</v>
+      </c>
+      <c r="F859" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G859" s="15">
+        <v>5</v>
+      </c>
+      <c r="H859" s="16" t="s">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="860" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A860" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B860" s="18">
+        <v>45274</v>
+      </c>
+      <c r="C860" s="18">
+        <v>45315</v>
+      </c>
+      <c r="D860" s="18">
+        <v>45340</v>
+      </c>
+      <c r="E860" s="19" t="s">
+        <v>1195</v>
+      </c>
+      <c r="F860" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G860" s="20">
+        <v>6</v>
+      </c>
+      <c r="H860" s="21" t="s">
+        <v>1196</v>
+      </c>
+    </row>
+    <row r="861" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A861" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B861" s="13">
+        <v>45274</v>
+      </c>
+      <c r="C861" s="13">
+        <v>45315</v>
+      </c>
+      <c r="D861" s="13">
+        <v>45334</v>
+      </c>
+      <c r="E861" s="14" t="s">
+        <v>1197</v>
+      </c>
+      <c r="F861" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G861" s="15">
+        <v>1</v>
+      </c>
+      <c r="H861" s="16" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="862" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A862" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B862" s="18">
+        <v>45274</v>
+      </c>
+      <c r="C862" s="18">
+        <v>45315</v>
+      </c>
+      <c r="D862" s="18">
+        <v>45338</v>
+      </c>
+      <c r="E862" s="19" t="s">
+        <v>1199</v>
+      </c>
+      <c r="F862" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G862" s="20">
+        <v>6</v>
+      </c>
+      <c r="H862" s="21" t="s">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="863" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A863" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B863" s="13">
+        <v>45274</v>
+      </c>
+      <c r="C863" s="13">
+        <v>45315</v>
+      </c>
+      <c r="D863" s="13">
+        <v>45337</v>
+      </c>
+      <c r="E863" s="14" t="s">
+        <v>1201</v>
+      </c>
+      <c r="F863" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G863" s="15">
+        <v>5</v>
+      </c>
+      <c r="H863" s="16" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="864" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A864" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B864" s="18">
+        <v>45274</v>
+      </c>
+      <c r="C864" s="18">
+        <v>45315</v>
+      </c>
+      <c r="D864" s="18">
+        <v>45338</v>
+      </c>
+      <c r="E864" s="19" t="s">
+        <v>1203</v>
+      </c>
+      <c r="F864" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G864" s="20">
+        <v>10</v>
+      </c>
+      <c r="H864" s="21" t="s">
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="865" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A865" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B865" s="13">
+        <v>45274</v>
+      </c>
+      <c r="C865" s="13">
+        <v>45315</v>
+      </c>
+      <c r="D865" s="13">
+        <v>45340</v>
+      </c>
+      <c r="E865" s="14" t="s">
+        <v>1205</v>
+      </c>
+      <c r="F865" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G865" s="15">
+        <v>7</v>
+      </c>
+      <c r="H865" s="16" t="s">
+        <v>1206</v>
+      </c>
+    </row>
+    <row r="866" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A866" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B866" s="18">
+        <v>45274</v>
+      </c>
+      <c r="C866" s="18">
+        <v>45315</v>
+      </c>
+      <c r="D866" s="18">
+        <v>45340</v>
+      </c>
+      <c r="E866" s="19" t="s">
+        <v>1207</v>
+      </c>
+      <c r="F866" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G866" s="20">
+        <v>6</v>
+      </c>
+      <c r="H866" s="21" t="s">
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="867" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A867" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B867" s="13">
+        <v>45274</v>
+      </c>
+      <c r="C867" s="13">
+        <v>45315</v>
+      </c>
+      <c r="D867" s="13">
+        <v>45341</v>
+      </c>
+      <c r="E867" s="14" t="s">
+        <v>1209</v>
+      </c>
+      <c r="F867" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G867" s="15">
+        <v>8</v>
+      </c>
+      <c r="H867" s="16" t="s">
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="868" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A868" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="B868" s="18">
+        <v>45274</v>
+      </c>
+      <c r="C868" s="18">
+        <v>45315</v>
+      </c>
+      <c r="D868" s="18">
+        <v>45334</v>
+      </c>
+      <c r="E868" s="19" t="s">
+        <v>1165</v>
+      </c>
+      <c r="F868" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G868" s="20">
+        <v>4</v>
+      </c>
+      <c r="H868" s="21" t="s">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="869" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A869" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B869" s="13">
+        <v>45274</v>
+      </c>
+      <c r="C869" s="13">
+        <v>45315</v>
+      </c>
+      <c r="D869" s="13">
+        <v>45337</v>
+      </c>
+      <c r="E869" s="14" t="s">
+        <v>1212</v>
+      </c>
+      <c r="F869" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G869" s="15">
+        <v>3</v>
+      </c>
+      <c r="H869" s="16" t="s">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="870" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A870" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="B870" s="18">
+        <v>45274</v>
+      </c>
+      <c r="C870" s="18">
+        <v>45315</v>
+      </c>
+      <c r="D870" s="18">
+        <v>45340</v>
+      </c>
+      <c r="E870" s="19" t="s">
+        <v>1214</v>
+      </c>
+      <c r="F870" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G870" s="20">
+        <v>1</v>
+      </c>
+      <c r="H870" s="21" t="s">
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="871" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A871" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B871" s="13">
+        <v>45274</v>
+      </c>
+      <c r="C871" s="13">
+        <v>45315</v>
+      </c>
+      <c r="D871" s="13">
+        <v>45338</v>
+      </c>
+      <c r="E871" s="14" t="s">
+        <v>1216</v>
+      </c>
+      <c r="F871" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G871" s="15">
+        <v>7</v>
+      </c>
+      <c r="H871" s="16" t="s">
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="872" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A872" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="B872" s="18">
+        <v>45274</v>
+      </c>
+      <c r="C872" s="18">
+        <v>45315</v>
+      </c>
+      <c r="D872" s="18">
+        <v>45339</v>
+      </c>
+      <c r="E872" s="19" t="s">
+        <v>1218</v>
+      </c>
+      <c r="F872" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G872" s="20">
+        <v>7</v>
+      </c>
+      <c r="H872" s="21" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="873" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A873" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B873" s="13">
+        <v>45274</v>
+      </c>
+      <c r="C873" s="13">
+        <v>45315</v>
+      </c>
+      <c r="D873" s="13">
+        <v>45347</v>
+      </c>
+      <c r="E873" s="14" t="s">
+        <v>1220</v>
+      </c>
+      <c r="F873" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G873" s="15">
+        <v>4</v>
+      </c>
+      <c r="H873" s="16" t="s">
+        <v>1221</v>
+      </c>
+    </row>
+    <row r="874" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A874" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="B874" s="18">
+        <v>45274</v>
+      </c>
+      <c r="C874" s="18">
+        <v>45315</v>
+      </c>
+      <c r="D874" s="18">
+        <v>45341</v>
+      </c>
+      <c r="E874" s="19" t="s">
+        <v>1222</v>
+      </c>
+      <c r="F874" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G874" s="20">
+        <v>7</v>
+      </c>
+      <c r="H874" s="21" t="s">
+        <v>1223</v>
+      </c>
+    </row>
+    <row r="875" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A875" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="B875" s="13">
+        <v>45274</v>
+      </c>
+      <c r="C875" s="13">
+        <v>45315</v>
+      </c>
+      <c r="D875" s="13">
+        <v>45342</v>
+      </c>
+      <c r="E875" s="14" t="s">
+        <v>1224</v>
+      </c>
+      <c r="F875" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G875" s="15">
+        <v>4</v>
+      </c>
+      <c r="H875" s="16" t="s">
+        <v>1225</v>
+      </c>
+    </row>
+    <row r="876" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A876" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="B876" s="18">
+        <v>45274</v>
+      </c>
+      <c r="C876" s="18">
+        <v>45315</v>
+      </c>
+      <c r="D876" s="18">
+        <v>45338</v>
+      </c>
+      <c r="E876" s="19" t="s">
+        <v>1226</v>
+      </c>
+      <c r="F876" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G876" s="20">
+        <v>10</v>
+      </c>
+      <c r="H876" s="21" t="s">
+        <v>1227</v>
+      </c>
+    </row>
+    <row r="877" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A877" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="B877" s="13">
+        <v>45274</v>
+      </c>
+      <c r="C877" s="13">
+        <v>45315</v>
+      </c>
+      <c r="D877" s="13">
+        <v>45338</v>
+      </c>
+      <c r="E877" s="14" t="s">
+        <v>1228</v>
+      </c>
+      <c r="F877" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G877" s="15">
+        <v>13</v>
+      </c>
+      <c r="H877" s="16" t="s">
+        <v>1229</v>
+      </c>
+    </row>
+    <row r="878" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A878" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="B878" s="18">
+        <v>45274</v>
+      </c>
+      <c r="C878" s="18">
+        <v>45315</v>
+      </c>
+      <c r="D878" s="18">
+        <v>45341</v>
+      </c>
+      <c r="E878" s="19" t="s">
+        <v>1230</v>
+      </c>
+      <c r="F878" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G878" s="20">
+        <v>5</v>
+      </c>
+      <c r="H878" s="21" t="s">
+        <v>1231</v>
+      </c>
+    </row>
+    <row r="879" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A879" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="B879" s="13">
+        <v>45274</v>
+      </c>
+      <c r="C879" s="13">
+        <v>45315</v>
+      </c>
+      <c r="D879" s="13">
+        <v>45337</v>
+      </c>
+      <c r="E879" s="14" t="s">
+        <v>1232</v>
+      </c>
+      <c r="F879" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G879" s="15">
+        <v>3</v>
+      </c>
+      <c r="H879" s="16" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="880" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A880" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="B880" s="18">
+        <v>45274</v>
+      </c>
+      <c r="C880" s="18">
+        <v>45315</v>
+      </c>
+      <c r="D880" s="18">
+        <v>45337</v>
+      </c>
+      <c r="E880" s="19" t="s">
+        <v>1234</v>
+      </c>
+      <c r="F880" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G880" s="20">
+        <v>2</v>
+      </c>
+      <c r="H880" s="21" t="s">
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="881" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A881" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B881" s="13">
+        <v>45294</v>
+      </c>
+      <c r="C881" s="13">
+        <v>45315</v>
+      </c>
+      <c r="D881" s="13">
+        <v>45356</v>
+      </c>
+      <c r="E881" s="14" t="s">
+        <v>1236</v>
+      </c>
+      <c r="F881" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G881" s="15">
+        <v>157</v>
+      </c>
+      <c r="H881" s="16" t="s">
+        <v>1237</v>
+      </c>
+    </row>
+    <row r="882" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A882" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="B882" s="18">
+        <v>45293</v>
+      </c>
+      <c r="C882" s="18">
+        <v>45315</v>
+      </c>
+      <c r="D882" s="18">
+        <v>45353</v>
+      </c>
+      <c r="E882" s="19" t="s">
+        <v>1238</v>
+      </c>
+      <c r="F882" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G882" s="20">
+        <v>28</v>
+      </c>
+      <c r="H882" s="21" t="s">
+        <v>1239</v>
+      </c>
+    </row>
+    <row r="883" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A883" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="B883" s="13">
+        <v>45274</v>
+      </c>
+      <c r="C883" s="13">
+        <v>45315</v>
+      </c>
+      <c r="D883" s="13">
+        <v>45336</v>
+      </c>
+      <c r="E883" s="14" t="s">
+        <v>1148</v>
+      </c>
+      <c r="F883" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G883" s="15">
+        <v>4</v>
+      </c>
+      <c r="H883" s="16" t="s">
+        <v>1240</v>
+      </c>
+    </row>
+    <row r="884" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A884" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="B884" s="18">
+        <v>45274</v>
+      </c>
+      <c r="C884" s="18">
+        <v>45315</v>
+      </c>
+      <c r="D884" s="18">
+        <v>45337</v>
+      </c>
+      <c r="E884" s="19" t="s">
+        <v>1148</v>
+      </c>
+      <c r="F884" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G884" s="20">
+        <v>3</v>
+      </c>
+      <c r="H884" s="21" t="s">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="885" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A885" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="B885" s="13">
+        <v>45274</v>
+      </c>
+      <c r="C885" s="13">
+        <v>45315</v>
+      </c>
+      <c r="D885" s="13">
+        <v>45335</v>
+      </c>
+      <c r="E885" s="14" t="s">
+        <v>1148</v>
+      </c>
+      <c r="F885" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G885" s="15">
+        <v>3</v>
+      </c>
+      <c r="H885" s="16" t="s">
+        <v>1242</v>
+      </c>
+    </row>
+    <row r="886" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A886" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="B886" s="18">
+        <v>45274</v>
+      </c>
+      <c r="C886" s="18">
+        <v>45315</v>
+      </c>
+      <c r="D886" s="18">
+        <v>45346</v>
+      </c>
+      <c r="E886" s="19" t="s">
+        <v>1148</v>
+      </c>
+      <c r="F886" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G886" s="20">
+        <v>4</v>
+      </c>
+      <c r="H886" s="21" t="s">
+        <v>1243</v>
+      </c>
+    </row>
+    <row r="887" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A887" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B887" s="13">
+        <v>45274</v>
+      </c>
+      <c r="C887" s="13">
+        <v>45315</v>
+      </c>
+      <c r="D887" s="13">
+        <v>45345</v>
+      </c>
+      <c r="E887" s="14" t="s">
+        <v>1244</v>
+      </c>
+      <c r="F887" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G887" s="15">
+        <v>4</v>
+      </c>
+      <c r="H887" s="16" t="s">
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="888" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A888" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="B888" s="18">
+        <v>45274</v>
+      </c>
+      <c r="C888" s="18">
+        <v>45315</v>
+      </c>
+      <c r="D888" s="18">
+        <v>45339</v>
+      </c>
+      <c r="E888" s="19" t="s">
+        <v>1246</v>
+      </c>
+      <c r="F888" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G888" s="20">
+        <v>4</v>
+      </c>
+      <c r="H888" s="21" t="s">
+        <v>1247</v>
+      </c>
+    </row>
+    <row r="889" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A889" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B889" s="13">
+        <v>45274</v>
+      </c>
+      <c r="C889" s="13">
+        <v>45315</v>
+      </c>
+      <c r="D889" s="13">
+        <v>45339</v>
+      </c>
+      <c r="E889" s="14" t="s">
+        <v>1248</v>
+      </c>
+      <c r="F889" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G889" s="15">
+        <v>5</v>
+      </c>
+      <c r="H889" s="16" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="890" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A890" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="B890" s="18">
+        <v>45274</v>
+      </c>
+      <c r="C890" s="18">
+        <v>45315</v>
+      </c>
+      <c r="D890" s="18">
+        <v>45338</v>
+      </c>
+      <c r="E890" s="19" t="s">
+        <v>1250</v>
+      </c>
+      <c r="F890" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G890" s="20">
+        <v>3</v>
+      </c>
+      <c r="H890" s="21" t="s">
+        <v>1251</v>
+      </c>
+    </row>
+    <row r="891" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A891" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B891" s="13">
+        <v>45274</v>
+      </c>
+      <c r="C891" s="13">
+        <v>45315</v>
+      </c>
+      <c r="D891" s="13">
+        <v>45337</v>
+      </c>
+      <c r="E891" s="14" t="s">
+        <v>1165</v>
+      </c>
+      <c r="F891" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G891" s="15">
+        <v>6</v>
+      </c>
+      <c r="H891" s="16" t="s">
+        <v>1252</v>
+      </c>
+    </row>
+    <row r="892" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A892" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="B892" s="18">
+        <v>45274</v>
+      </c>
+      <c r="C892" s="18">
+        <v>45315</v>
+      </c>
+      <c r="D892" s="18">
+        <v>45337</v>
+      </c>
+      <c r="E892" s="19" t="s">
+        <v>1148</v>
+      </c>
+      <c r="F892" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G892" s="20">
+        <v>4</v>
+      </c>
+      <c r="H892" s="21" t="s">
+        <v>1253</v>
+      </c>
+    </row>
+    <row r="893" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A893" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B893" s="13">
+        <v>45274</v>
+      </c>
+      <c r="C893" s="13">
+        <v>45315</v>
+      </c>
+      <c r="D893" s="13">
+        <v>45342</v>
+      </c>
+      <c r="E893" s="14" t="s">
+        <v>1148</v>
+      </c>
+      <c r="F893" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G893" s="15">
+        <v>6</v>
+      </c>
+      <c r="H893" s="16" t="s">
+        <v>1254</v>
+      </c>
+    </row>
+    <row r="894" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A894" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="B894" s="18">
+        <v>45274</v>
+      </c>
+      <c r="C894" s="18">
+        <v>45315</v>
+      </c>
+      <c r="D894" s="18">
+        <v>45337</v>
+      </c>
+      <c r="E894" s="19" t="s">
+        <v>1148</v>
+      </c>
+      <c r="F894" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G894" s="20">
+        <v>2</v>
+      </c>
+      <c r="H894" s="21" t="s">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="895" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A895" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="B895" s="13">
+        <v>45274</v>
+      </c>
+      <c r="C895" s="13">
+        <v>45315</v>
+      </c>
+      <c r="D895" s="13">
+        <v>45338</v>
+      </c>
+      <c r="E895" s="14" t="s">
+        <v>1256</v>
+      </c>
+      <c r="F895" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G895" s="15">
+        <v>10</v>
+      </c>
+      <c r="H895" s="16" t="s">
+        <v>1257</v>
+      </c>
+    </row>
+    <row r="896" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A896" s="17" t="s">
+        <v>175</v>
+      </c>
+      <c r="B896" s="18">
+        <v>45274</v>
+      </c>
+      <c r="C896" s="18">
+        <v>45315</v>
+      </c>
+      <c r="D896" s="18">
+        <v>45338</v>
+      </c>
+      <c r="E896" s="19" t="s">
+        <v>1258</v>
+      </c>
+      <c r="F896" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G896" s="20">
+        <v>6</v>
+      </c>
+      <c r="H896" s="21" t="s">
+        <v>1259</v>
+      </c>
+    </row>
+    <row r="897" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A897" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="B897" s="13">
+        <v>45274</v>
+      </c>
+      <c r="C897" s="13">
+        <v>45315</v>
+      </c>
+      <c r="D897" s="13">
+        <v>45339</v>
+      </c>
+      <c r="E897" s="14" t="s">
+        <v>1260</v>
+      </c>
+      <c r="F897" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G897" s="15">
+        <v>4</v>
+      </c>
+      <c r="H897" s="16" t="s">
+        <v>1261</v>
+      </c>
+    </row>
+    <row r="898" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A898" s="17" t="s">
+        <v>175</v>
+      </c>
+      <c r="B898" s="18">
+        <v>45274</v>
+      </c>
+      <c r="C898" s="18">
+        <v>45315</v>
+      </c>
+      <c r="D898" s="18">
+        <v>45339</v>
+      </c>
+      <c r="E898" s="19" t="s">
+        <v>1262</v>
+      </c>
+      <c r="F898" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G898" s="20">
+        <v>8</v>
+      </c>
+      <c r="H898" s="21" t="s">
+        <v>1263</v>
+      </c>
+    </row>
+    <row r="899" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A899" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="B899" s="13">
+        <v>45274</v>
+      </c>
+      <c r="C899" s="13">
+        <v>45315</v>
+      </c>
+      <c r="D899" s="13">
+        <v>45338</v>
+      </c>
+      <c r="E899" s="14" t="s">
+        <v>1162</v>
+      </c>
+      <c r="F899" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G899" s="15">
+        <v>5</v>
+      </c>
+      <c r="H899" s="16" t="s">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="900" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A900" s="17" t="s">
+        <v>302</v>
+      </c>
+      <c r="B900" s="18">
+        <v>45272</v>
+      </c>
+      <c r="C900" s="18">
+        <v>45315</v>
+      </c>
+      <c r="D900" s="18">
+        <v>45322</v>
+      </c>
+      <c r="E900" s="19" t="s">
+        <v>1122</v>
+      </c>
+      <c r="F900" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G900" s="20">
+        <v>15</v>
+      </c>
+      <c r="H900" s="21" t="s">
+        <v>1265</v>
       </c>
     </row>
   </sheetData>
@@ -25950,13 +28702,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{20F87E56-696F-4646-A3CA-DCB6F81D56A6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DDD99E44-A383-42F6-A86C-6B941219F0C2}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0521F685-FBB8-4577-A865-B84595628277}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF8AD181-1AAA-4CD9-9C56-6F3DF38D6B53}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D9D3BDC4-C84D-480E-B209-7127014023B2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{296C2C31-135D-4B5F-9800-666FD012220B}"/>
 </file>
--- a/data/warn-scraper/cache/ca/warn_report1.xlsx
+++ b/data/warn-scraper/cache/ca/warn_report1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\WSB-CO\BPAC\Policy &amp; Program Communications Group\Communications Unit\Website Management\WARN (Worker Adjustment and Retraining Notification) Updates\2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F5CA17E-10E8-456E-9BCA-570FF2567496}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5181BFE7-EB8E-4D2E-921E-6C084F61D2C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="624" yWindow="684" windowWidth="21600" windowHeight="11436" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4303" uniqueCount="1539">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4379" uniqueCount="1549">
   <si>
     <t>County/Parish</t>
   </si>
@@ -4376,12 +4376,6 @@
     <t>6417 Selma Ave.  Los Angeles CA 90028</t>
   </si>
   <si>
-    <t>2763 Saint Louis Avenue  Signal Hill CA 90755</t>
-  </si>
-  <si>
-    <t>2301 E. Anaheim Street  Wilmington CA 90744</t>
-  </si>
-  <si>
     <t>126 E Oris St.  Compton CA 90222</t>
   </si>
   <si>
@@ -4716,6 +4710,42 @@
   </si>
   <si>
     <t>3043 Townsgate Road  Westlake Village CA 91361</t>
+  </si>
+  <si>
+    <t>2763 Saint Louis Ave  Signal Hill CA 90755</t>
+  </si>
+  <si>
+    <t>Pixelberry Studios</t>
+  </si>
+  <si>
+    <t>4940 El Camino Real, Suite 150  Los Altos CA 94022</t>
+  </si>
+  <si>
+    <t>Google US-MTV-RLS1</t>
+  </si>
+  <si>
+    <t>100 Mayfield Ave  Mountain View CA 94043</t>
+  </si>
+  <si>
+    <t>Google US-MTV-RLS2</t>
+  </si>
+  <si>
+    <t>250 Mayfield Ave  Mountain View CA 94043</t>
+  </si>
+  <si>
+    <t>5600 Argosy Circe Suite 100  Huntington Beach CA 92649</t>
+  </si>
+  <si>
+    <t>DHL Supply Chain</t>
+  </si>
+  <si>
+    <t>1089 East Mill Street  San Bernardino CA 92408</t>
+  </si>
+  <si>
+    <t>Pure Storage, Inc.</t>
+  </si>
+  <si>
+    <t>2555 Augustine Drive  Santa Clara CA 95054</t>
   </si>
   <si>
     <r>
@@ -4729,7 +4759,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>07/01/23 to 02/05/24</t>
+      <t>07/01/23 to 02/07/24</t>
     </r>
     <r>
       <rPr>
@@ -4749,7 +4779,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>A detailed WARN summary by county and filtered according to received date. Table Spans cells A2 through H1072.</t>
+      <t>A detailed WARN summary by county and filtered according to received date. Table Spans cells A2 through H1091.</t>
     </r>
   </si>
 </sst>
@@ -5063,8 +5093,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFF0F0F0"/>
+          <bgColor rgb="FFF0F0F0"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -5104,8 +5134,8 @@
       <numFmt numFmtId="165" formatCode="[$-10436]#,##0;\(#,##0\)"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFF0F0F0"/>
+          <bgColor rgb="FFF0F0F0"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -5144,8 +5174,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFF0F0F0"/>
+          <bgColor rgb="FFF0F0F0"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -5184,8 +5214,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFF0F0F0"/>
+          <bgColor rgb="FFF0F0F0"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -5225,8 +5255,8 @@
       <numFmt numFmtId="164" formatCode="[$-10409]mm/dd/yyyy"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFF0F0F0"/>
+          <bgColor rgb="FFF0F0F0"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -5266,8 +5296,8 @@
       <numFmt numFmtId="164" formatCode="[$-10409]mm/dd/yyyy"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFF0F0F0"/>
+          <bgColor rgb="FFF0F0F0"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -5307,8 +5337,8 @@
       <numFmt numFmtId="164" formatCode="[$-10409]mm/dd/yyyy"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFF0F0F0"/>
+          <bgColor rgb="FFF0F0F0"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -5347,8 +5377,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFF0F0F0"/>
+          <bgColor rgb="FFF0F0F0"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -5540,8 +5570,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:H1072" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
-  <autoFilter ref="A2:H1072" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:H1091" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
+  <autoFilter ref="A2:H1091" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -5925,7 +5955,7 @@
       </c>
       <c r="B3" s="5">
         <f>SUM('Detailed WARN Report '!G:G)</f>
-        <v>55616</v>
+        <v>56349</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -5934,7 +5964,7 @@
       </c>
       <c r="B4" s="5">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Permanent")</f>
-        <v>749</v>
+        <v>768</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -5992,7 +6022,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:H1072"/>
+  <dimension ref="A1:H1091"/>
   <sheetFormatPr defaultColWidth="26" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.88671875" bestFit="1" customWidth="1"/>
@@ -6007,7 +6037,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="99.6" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
-        <v>1538</v>
+        <v>1548</v>
       </c>
       <c r="D1" s="12"/>
       <c r="E1" s="6"/>
@@ -17599,7 +17629,7 @@
         <v>45351</v>
       </c>
       <c r="E447" s="17" t="s">
-        <v>1440</v>
+        <v>1438</v>
       </c>
       <c r="F447" s="17" t="s">
         <v>15</v>
@@ -17608,7 +17638,7 @@
         <v>48</v>
       </c>
       <c r="H447" s="19" t="s">
-        <v>1441</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="448" spans="1:8" x14ac:dyDescent="0.3">
@@ -27173,7 +27203,7 @@
         <v>15</v>
       </c>
       <c r="G815" s="18">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="H815" s="19" t="s">
         <v>1118</v>
@@ -31870,7 +31900,7 @@
         <v>45322</v>
       </c>
       <c r="D996" s="21">
-        <v>45366</v>
+        <v>45369</v>
       </c>
       <c r="E996" s="22" t="s">
         <v>1388</v>
@@ -31879,10 +31909,10 @@
         <v>15</v>
       </c>
       <c r="G996" s="23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H996" s="24" t="s">
-        <v>1424</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="997" spans="1:8" x14ac:dyDescent="0.3">
@@ -31890,30 +31920,30 @@
         <v>5</v>
       </c>
       <c r="B997" s="16">
-        <v>45308</v>
+        <v>45310</v>
       </c>
       <c r="C997" s="16">
         <v>45322</v>
       </c>
       <c r="D997" s="16">
-        <v>45366</v>
+        <v>45309</v>
       </c>
       <c r="E997" s="17" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="F997" s="17" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G997" s="18">
-        <v>1</v>
+        <v>86</v>
       </c>
       <c r="H997" s="19" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="998" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A998" s="20" t="s">
-        <v>5</v>
+        <v>62</v>
       </c>
       <c r="B998" s="21">
         <v>45310</v>
@@ -31931,62 +31961,62 @@
         <v>16</v>
       </c>
       <c r="G998" s="23">
-        <v>86</v>
+        <v>55</v>
       </c>
       <c r="H998" s="24" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="999" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A999" s="15" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B999" s="16">
-        <v>45310</v>
+        <v>45315</v>
       </c>
       <c r="C999" s="16">
         <v>45322</v>
       </c>
       <c r="D999" s="16">
-        <v>45309</v>
+        <v>45380</v>
       </c>
       <c r="E999" s="17" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
       <c r="F999" s="17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G999" s="18">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="H999" s="19" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="1000" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1000" s="20" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="B1000" s="21">
-        <v>45315</v>
+        <v>45308</v>
       </c>
       <c r="C1000" s="21">
         <v>45322</v>
       </c>
       <c r="D1000" s="21">
-        <v>45380</v>
+        <v>45370</v>
       </c>
       <c r="E1000" s="22" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="F1000" s="22" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G1000" s="23">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="H1000" s="24" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="1001" spans="1:8" x14ac:dyDescent="0.3">
@@ -32003,16 +32033,16 @@
         <v>45370</v>
       </c>
       <c r="E1001" s="17" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="F1001" s="17" t="s">
         <v>16</v>
       </c>
       <c r="G1001" s="18">
-        <v>86</v>
+        <v>52</v>
       </c>
       <c r="H1001" s="19" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="1002" spans="1:8" x14ac:dyDescent="0.3">
@@ -32020,56 +32050,56 @@
         <v>11</v>
       </c>
       <c r="B1002" s="21">
-        <v>45308</v>
+        <v>45310</v>
       </c>
       <c r="C1002" s="21">
         <v>45322</v>
       </c>
       <c r="D1002" s="21">
-        <v>45370</v>
+        <v>45373</v>
       </c>
       <c r="E1002" s="22" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="F1002" s="22" t="s">
         <v>16</v>
       </c>
       <c r="G1002" s="23">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="H1002" s="24" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="1003" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1003" s="15" t="s">
-        <v>11</v>
+        <v>85</v>
       </c>
       <c r="B1003" s="16">
-        <v>45310</v>
+        <v>45307</v>
       </c>
       <c r="C1003" s="16">
         <v>45322</v>
       </c>
       <c r="D1003" s="16">
-        <v>45373</v>
+        <v>45369</v>
       </c>
       <c r="E1003" s="17" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="F1003" s="17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G1003" s="18">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="H1003" s="19" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="1004" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1004" s="20" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="B1004" s="21">
         <v>45307</v>
@@ -32087,15 +32117,15 @@
         <v>15</v>
       </c>
       <c r="G1004" s="23">
-        <v>11</v>
+        <v>64</v>
       </c>
       <c r="H1004" s="24" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="1005" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1005" s="15" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="B1005" s="16">
         <v>45307</v>
@@ -32113,10 +32143,10 @@
         <v>15</v>
       </c>
       <c r="G1005" s="18">
-        <v>64</v>
+        <v>3</v>
       </c>
       <c r="H1005" s="19" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="1006" spans="1:8" x14ac:dyDescent="0.3">
@@ -32124,25 +32154,25 @@
         <v>75</v>
       </c>
       <c r="B1006" s="21">
-        <v>45307</v>
+        <v>45308</v>
       </c>
       <c r="C1006" s="21">
         <v>45322</v>
       </c>
       <c r="D1006" s="21">
-        <v>45369</v>
+        <v>45370</v>
       </c>
       <c r="E1006" s="22" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="F1006" s="22" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G1006" s="23">
-        <v>3</v>
+        <v>49</v>
       </c>
       <c r="H1006" s="24" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="1007" spans="1:8" x14ac:dyDescent="0.3">
@@ -32159,42 +32189,42 @@
         <v>45370</v>
       </c>
       <c r="E1007" s="17" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="F1007" s="17" t="s">
         <v>16</v>
       </c>
       <c r="G1007" s="18">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="H1007" s="19" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="1008" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1008" s="20" t="s">
-        <v>75</v>
+        <v>6</v>
       </c>
       <c r="B1008" s="21">
-        <v>45308</v>
+        <v>45307</v>
       </c>
       <c r="C1008" s="21">
         <v>45322</v>
       </c>
       <c r="D1008" s="21">
-        <v>45370</v>
+        <v>45369</v>
       </c>
       <c r="E1008" s="22" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
       <c r="F1008" s="22" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G1008" s="23">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="H1008" s="24" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="1009" spans="1:8" x14ac:dyDescent="0.3">
@@ -32202,91 +32232,91 @@
         <v>6</v>
       </c>
       <c r="B1009" s="16">
-        <v>45307</v>
+        <v>45316</v>
       </c>
       <c r="C1009" s="16">
         <v>45322</v>
       </c>
       <c r="D1009" s="16">
-        <v>45369</v>
+        <v>45379</v>
       </c>
       <c r="E1009" s="17" t="s">
-        <v>1394</v>
+        <v>1397</v>
       </c>
       <c r="F1009" s="17" t="s">
         <v>15</v>
       </c>
       <c r="G1009" s="18">
-        <v>6</v>
+        <v>83</v>
       </c>
       <c r="H1009" s="19" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="1010" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1010" s="20" t="s">
-        <v>6</v>
+        <v>281</v>
       </c>
       <c r="B1010" s="21">
-        <v>45316</v>
+        <v>45308</v>
       </c>
       <c r="C1010" s="21">
         <v>45322</v>
       </c>
       <c r="D1010" s="21">
-        <v>45379</v>
+        <v>45292</v>
       </c>
       <c r="E1010" s="22" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="F1010" s="22" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G1010" s="23">
-        <v>83</v>
+        <v>5</v>
       </c>
       <c r="H1010" s="24" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="1011" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1011" s="15" t="s">
-        <v>281</v>
+        <v>65</v>
       </c>
       <c r="B1011" s="16">
-        <v>45308</v>
+        <v>45310</v>
       </c>
       <c r="C1011" s="16">
-        <v>45322</v>
+        <v>45323</v>
       </c>
       <c r="D1011" s="16">
-        <v>45292</v>
+        <v>45375</v>
       </c>
       <c r="E1011" s="17" t="s">
-        <v>1398</v>
+        <v>1440</v>
       </c>
       <c r="F1011" s="17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G1011" s="18">
-        <v>5</v>
+        <v>160</v>
       </c>
       <c r="H1011" s="19" t="s">
-        <v>1439</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="1012" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1012" s="20" t="s">
-        <v>65</v>
+        <v>5</v>
       </c>
       <c r="B1012" s="21">
-        <v>45310</v>
+        <v>45315</v>
       </c>
       <c r="C1012" s="21">
         <v>45323</v>
       </c>
       <c r="D1012" s="21">
-        <v>45375</v>
+        <v>45376</v>
       </c>
       <c r="E1012" s="22" t="s">
         <v>1442</v>
@@ -32295,7 +32325,7 @@
         <v>15</v>
       </c>
       <c r="G1012" s="23">
-        <v>160</v>
+        <v>72</v>
       </c>
       <c r="H1012" s="24" t="s">
         <v>1443</v>
@@ -32306,13 +32336,13 @@
         <v>5</v>
       </c>
       <c r="B1013" s="16">
-        <v>45315</v>
+        <v>45313</v>
       </c>
       <c r="C1013" s="16">
         <v>45323</v>
       </c>
       <c r="D1013" s="16">
-        <v>45376</v>
+        <v>45382</v>
       </c>
       <c r="E1013" s="17" t="s">
         <v>1444</v>
@@ -32321,41 +32351,41 @@
         <v>15</v>
       </c>
       <c r="G1013" s="18">
-        <v>72</v>
+        <v>15</v>
       </c>
       <c r="H1013" s="19" t="s">
         <v>1445</v>
       </c>
     </row>
-    <row r="1014" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1014" spans="1:8" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1014" s="20" t="s">
         <v>5</v>
       </c>
       <c r="B1014" s="21">
-        <v>45313</v>
+        <v>45314</v>
       </c>
       <c r="C1014" s="21">
         <v>45323</v>
       </c>
       <c r="D1014" s="21">
-        <v>45382</v>
+        <v>45317</v>
       </c>
       <c r="E1014" s="22" t="s">
         <v>1446</v>
       </c>
       <c r="F1014" s="22" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G1014" s="23">
-        <v>15</v>
+        <v>58</v>
       </c>
       <c r="H1014" s="24" t="s">
         <v>1447</v>
       </c>
     </row>
-    <row r="1015" spans="1:8" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="1015" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1015" s="15" t="s">
-        <v>5</v>
+        <v>1448</v>
       </c>
       <c r="B1015" s="16">
         <v>45314</v>
@@ -32364,42 +32394,42 @@
         <v>45323</v>
       </c>
       <c r="D1015" s="16">
-        <v>45317</v>
+        <v>45310</v>
       </c>
       <c r="E1015" s="17" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="F1015" s="17" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G1015" s="18">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="H1015" s="19" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="1016" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1016" s="20" t="s">
-        <v>1450</v>
+        <v>62</v>
       </c>
       <c r="B1016" s="21">
-        <v>45314</v>
+        <v>45299</v>
       </c>
       <c r="C1016" s="21">
         <v>45323</v>
       </c>
       <c r="D1016" s="21">
-        <v>45310</v>
+        <v>45359</v>
       </c>
       <c r="E1016" s="22" t="s">
         <v>1451</v>
       </c>
       <c r="F1016" s="22" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G1016" s="23">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H1016" s="24" t="s">
         <v>1452</v>
@@ -32407,16 +32437,16 @@
     </row>
     <row r="1017" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1017" s="15" t="s">
-        <v>62</v>
+        <v>7</v>
       </c>
       <c r="B1017" s="16">
-        <v>45299</v>
+        <v>45310</v>
       </c>
       <c r="C1017" s="16">
         <v>45323</v>
       </c>
       <c r="D1017" s="16">
-        <v>45359</v>
+        <v>45373</v>
       </c>
       <c r="E1017" s="17" t="s">
         <v>1453</v>
@@ -32425,7 +32455,7 @@
         <v>16</v>
       </c>
       <c r="G1017" s="18">
-        <v>63</v>
+        <v>1</v>
       </c>
       <c r="H1017" s="19" t="s">
         <v>1454</v>
@@ -32442,7 +32472,7 @@
         <v>45323</v>
       </c>
       <c r="D1018" s="21">
-        <v>45373</v>
+        <v>45370</v>
       </c>
       <c r="E1018" s="22" t="s">
         <v>1455</v>
@@ -32451,7 +32481,7 @@
         <v>16</v>
       </c>
       <c r="G1018" s="23">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="H1018" s="24" t="s">
         <v>1456</v>
@@ -32459,25 +32489,25 @@
     </row>
     <row r="1019" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1019" s="15" t="s">
-        <v>7</v>
+        <v>85</v>
       </c>
       <c r="B1019" s="16">
-        <v>45310</v>
+        <v>45311</v>
       </c>
       <c r="C1019" s="16">
         <v>45323</v>
       </c>
       <c r="D1019" s="16">
-        <v>45370</v>
+        <v>45375</v>
       </c>
       <c r="E1019" s="17" t="s">
         <v>1457</v>
       </c>
       <c r="F1019" s="17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G1019" s="18">
-        <v>72</v>
+        <v>115</v>
       </c>
       <c r="H1019" s="19" t="s">
         <v>1458</v>
@@ -32485,25 +32515,25 @@
     </row>
     <row r="1020" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1020" s="20" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="B1020" s="21">
-        <v>45311</v>
+        <v>45313</v>
       </c>
       <c r="C1020" s="21">
         <v>45323</v>
       </c>
       <c r="D1020" s="21">
-        <v>45375</v>
+        <v>45379</v>
       </c>
       <c r="E1020" s="22" t="s">
         <v>1459</v>
       </c>
       <c r="F1020" s="22" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G1020" s="23">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="H1020" s="24" t="s">
         <v>1460</v>
@@ -32511,16 +32541,16 @@
     </row>
     <row r="1021" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1021" s="15" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="B1021" s="16">
-        <v>45313</v>
+        <v>45308</v>
       </c>
       <c r="C1021" s="16">
         <v>45323</v>
       </c>
       <c r="D1021" s="16">
-        <v>45379</v>
+        <v>45383</v>
       </c>
       <c r="E1021" s="17" t="s">
         <v>1461</v>
@@ -32529,7 +32559,7 @@
         <v>16</v>
       </c>
       <c r="G1021" s="18">
-        <v>117</v>
+        <v>14</v>
       </c>
       <c r="H1021" s="19" t="s">
         <v>1462</v>
@@ -32537,16 +32567,16 @@
     </row>
     <row r="1022" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1022" s="20" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="B1022" s="21">
-        <v>45308</v>
+        <v>45314</v>
       </c>
       <c r="C1022" s="21">
         <v>45323</v>
       </c>
       <c r="D1022" s="21">
-        <v>45383</v>
+        <v>45315</v>
       </c>
       <c r="E1022" s="22" t="s">
         <v>1463</v>
@@ -32555,7 +32585,7 @@
         <v>16</v>
       </c>
       <c r="G1022" s="23">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H1022" s="24" t="s">
         <v>1464</v>
@@ -32563,7 +32593,7 @@
     </row>
     <row r="1023" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1023" s="15" t="s">
-        <v>51</v>
+        <v>7</v>
       </c>
       <c r="B1023" s="16">
         <v>45314</v>
@@ -32575,16 +32605,16 @@
         <v>45315</v>
       </c>
       <c r="E1023" s="17" t="s">
+        <v>1463</v>
+      </c>
+      <c r="F1023" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1023" s="18">
+        <v>261</v>
+      </c>
+      <c r="H1023" s="19" t="s">
         <v>1465</v>
-      </c>
-      <c r="F1023" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1023" s="18">
-        <v>20</v>
-      </c>
-      <c r="H1023" s="19" t="s">
-        <v>1466</v>
       </c>
     </row>
     <row r="1024" spans="1:8" x14ac:dyDescent="0.3">
@@ -32592,22 +32622,22 @@
         <v>7</v>
       </c>
       <c r="B1024" s="21">
-        <v>45314</v>
+        <v>45293</v>
       </c>
       <c r="C1024" s="21">
         <v>45323</v>
       </c>
       <c r="D1024" s="21">
-        <v>45315</v>
+        <v>45355</v>
       </c>
       <c r="E1024" s="22" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
       <c r="F1024" s="22" t="s">
-        <v>16</v>
+        <v>98</v>
       </c>
       <c r="G1024" s="23">
-        <v>261</v>
+        <v>73</v>
       </c>
       <c r="H1024" s="24" t="s">
         <v>1467</v>
@@ -32615,77 +32645,77 @@
     </row>
     <row r="1025" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1025" s="15" t="s">
-        <v>7</v>
+        <v>211</v>
       </c>
       <c r="B1025" s="16">
-        <v>45293</v>
+        <v>45317</v>
       </c>
       <c r="C1025" s="16">
         <v>45323</v>
       </c>
       <c r="D1025" s="16">
-        <v>45355</v>
+        <v>45380</v>
       </c>
       <c r="E1025" s="17" t="s">
-        <v>1468</v>
+        <v>758</v>
       </c>
       <c r="F1025" s="17" t="s">
-        <v>98</v>
+        <v>16</v>
       </c>
       <c r="G1025" s="18">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="H1025" s="19" t="s">
-        <v>1469</v>
-      </c>
-    </row>
-    <row r="1026" spans="1:8" x14ac:dyDescent="0.3">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="1026" spans="1:8" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1026" s="20" t="s">
-        <v>211</v>
+        <v>10</v>
       </c>
       <c r="B1026" s="21">
-        <v>45317</v>
+        <v>45306</v>
       </c>
       <c r="C1026" s="21">
         <v>45323</v>
       </c>
       <c r="D1026" s="21">
-        <v>45380</v>
+        <v>45366</v>
       </c>
       <c r="E1026" s="22" t="s">
-        <v>758</v>
+        <v>1468</v>
       </c>
       <c r="F1026" s="22" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G1026" s="23">
-        <v>59</v>
+        <v>168</v>
       </c>
       <c r="H1026" s="24" t="s">
-        <v>759</v>
-      </c>
-    </row>
-    <row r="1027" spans="1:8" ht="20.399999999999999" x14ac:dyDescent="0.3">
+        <v>1469</v>
+      </c>
+    </row>
+    <row r="1027" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1027" s="15" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B1027" s="16">
-        <v>45306</v>
+        <v>45314</v>
       </c>
       <c r="C1027" s="16">
-        <v>45323</v>
+        <v>45324</v>
       </c>
       <c r="D1027" s="16">
-        <v>45366</v>
+        <v>45379</v>
       </c>
       <c r="E1027" s="17" t="s">
         <v>1470</v>
       </c>
       <c r="F1027" s="17" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G1027" s="18">
-        <v>168</v>
+        <v>83</v>
       </c>
       <c r="H1027" s="19" t="s">
         <v>1471</v>
@@ -32696,25 +32726,25 @@
         <v>5</v>
       </c>
       <c r="B1028" s="21">
-        <v>45314</v>
+        <v>45320</v>
       </c>
       <c r="C1028" s="21">
         <v>45324</v>
       </c>
       <c r="D1028" s="21">
-        <v>45379</v>
+        <v>45380</v>
       </c>
       <c r="E1028" s="22" t="s">
-        <v>1472</v>
+        <v>899</v>
       </c>
       <c r="F1028" s="22" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G1028" s="23">
-        <v>83</v>
+        <v>4</v>
       </c>
       <c r="H1028" s="24" t="s">
-        <v>1473</v>
+        <v>37</v>
       </c>
     </row>
     <row r="1029" spans="1:8" x14ac:dyDescent="0.3">
@@ -32722,25 +32752,25 @@
         <v>5</v>
       </c>
       <c r="B1029" s="16">
-        <v>45320</v>
+        <v>45321</v>
       </c>
       <c r="C1029" s="16">
         <v>45324</v>
       </c>
       <c r="D1029" s="16">
-        <v>45380</v>
+        <v>45387</v>
       </c>
       <c r="E1029" s="17" t="s">
-        <v>899</v>
+        <v>1472</v>
       </c>
       <c r="F1029" s="17" t="s">
         <v>16</v>
       </c>
       <c r="G1029" s="18">
-        <v>4</v>
+        <v>260</v>
       </c>
       <c r="H1029" s="19" t="s">
-        <v>37</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="1030" spans="1:8" x14ac:dyDescent="0.3">
@@ -32748,13 +32778,13 @@
         <v>5</v>
       </c>
       <c r="B1030" s="21">
-        <v>45321</v>
+        <v>45316</v>
       </c>
       <c r="C1030" s="21">
         <v>45324</v>
       </c>
       <c r="D1030" s="21">
-        <v>45387</v>
+        <v>45381</v>
       </c>
       <c r="E1030" s="22" t="s">
         <v>1474</v>
@@ -32763,7 +32793,7 @@
         <v>16</v>
       </c>
       <c r="G1030" s="23">
-        <v>260</v>
+        <v>49</v>
       </c>
       <c r="H1030" s="24" t="s">
         <v>1475</v>
@@ -32771,16 +32801,16 @@
     </row>
     <row r="1031" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1031" s="15" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B1031" s="16">
-        <v>45316</v>
+        <v>45321</v>
       </c>
       <c r="C1031" s="16">
         <v>45324</v>
       </c>
       <c r="D1031" s="16">
-        <v>45381</v>
+        <v>45321</v>
       </c>
       <c r="E1031" s="17" t="s">
         <v>1476</v>
@@ -32789,7 +32819,7 @@
         <v>16</v>
       </c>
       <c r="G1031" s="18">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="H1031" s="19" t="s">
         <v>1477</v>
@@ -32797,28 +32827,28 @@
     </row>
     <row r="1032" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1032" s="20" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B1032" s="21">
-        <v>45321</v>
+        <v>45316</v>
       </c>
       <c r="C1032" s="21">
         <v>45324</v>
       </c>
       <c r="D1032" s="21">
-        <v>45321</v>
+        <v>45381</v>
       </c>
       <c r="E1032" s="22" t="s">
+        <v>1474</v>
+      </c>
+      <c r="F1032" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1032" s="23">
+        <v>79</v>
+      </c>
+      <c r="H1032" s="24" t="s">
         <v>1478</v>
-      </c>
-      <c r="F1032" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1032" s="23">
-        <v>7</v>
-      </c>
-      <c r="H1032" s="24" t="s">
-        <v>1479</v>
       </c>
     </row>
     <row r="1033" spans="1:8" x14ac:dyDescent="0.3">
@@ -32835,16 +32865,16 @@
         <v>45381</v>
       </c>
       <c r="E1033" s="17" t="s">
-        <v>1476</v>
+        <v>1474</v>
       </c>
       <c r="F1033" s="17" t="s">
         <v>16</v>
       </c>
       <c r="G1033" s="18">
-        <v>79</v>
+        <v>130</v>
       </c>
       <c r="H1033" s="19" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="1034" spans="1:8" x14ac:dyDescent="0.3">
@@ -32852,22 +32882,22 @@
         <v>5</v>
       </c>
       <c r="B1034" s="21">
-        <v>45316</v>
+        <v>45322</v>
       </c>
       <c r="C1034" s="21">
         <v>45324</v>
       </c>
       <c r="D1034" s="21">
-        <v>45381</v>
+        <v>45383</v>
       </c>
       <c r="E1034" s="22" t="s">
-        <v>1476</v>
+        <v>1480</v>
       </c>
       <c r="F1034" s="22" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G1034" s="23">
-        <v>130</v>
+        <v>39</v>
       </c>
       <c r="H1034" s="24" t="s">
         <v>1481</v>
@@ -32875,16 +32905,16 @@
     </row>
     <row r="1035" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1035" s="15" t="s">
-        <v>5</v>
+        <v>235</v>
       </c>
       <c r="B1035" s="16">
-        <v>45322</v>
+        <v>45315</v>
       </c>
       <c r="C1035" s="16">
         <v>45324</v>
       </c>
       <c r="D1035" s="16">
-        <v>45383</v>
+        <v>45382</v>
       </c>
       <c r="E1035" s="17" t="s">
         <v>1482</v>
@@ -32893,7 +32923,7 @@
         <v>15</v>
       </c>
       <c r="G1035" s="18">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="H1035" s="19" t="s">
         <v>1483</v>
@@ -32901,25 +32931,25 @@
     </row>
     <row r="1036" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1036" s="20" t="s">
-        <v>235</v>
+        <v>1484</v>
       </c>
       <c r="B1036" s="21">
-        <v>45315</v>
+        <v>45322</v>
       </c>
       <c r="C1036" s="21">
         <v>45324</v>
       </c>
       <c r="D1036" s="21">
-        <v>45382</v>
+        <v>45387</v>
       </c>
       <c r="E1036" s="22" t="s">
-        <v>1484</v>
+        <v>1367</v>
       </c>
       <c r="F1036" s="22" t="s">
         <v>15</v>
       </c>
       <c r="G1036" s="23">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H1036" s="24" t="s">
         <v>1485</v>
@@ -32927,51 +32957,51 @@
     </row>
     <row r="1037" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1037" s="15" t="s">
-        <v>1486</v>
+        <v>62</v>
       </c>
       <c r="B1037" s="16">
-        <v>45322</v>
+        <v>45316</v>
       </c>
       <c r="C1037" s="16">
         <v>45324</v>
       </c>
       <c r="D1037" s="16">
-        <v>45387</v>
+        <v>45381</v>
       </c>
       <c r="E1037" s="17" t="s">
-        <v>1367</v>
+        <v>1474</v>
       </c>
       <c r="F1037" s="17" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G1037" s="18">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="H1037" s="19" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="1038" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1038" s="20" t="s">
-        <v>62</v>
+        <v>7</v>
       </c>
       <c r="B1038" s="21">
-        <v>45316</v>
+        <v>45323</v>
       </c>
       <c r="C1038" s="21">
         <v>45324</v>
       </c>
       <c r="D1038" s="21">
-        <v>45381</v>
+        <v>45324</v>
       </c>
       <c r="E1038" s="22" t="s">
-        <v>1476</v>
+        <v>1487</v>
       </c>
       <c r="F1038" s="22" t="s">
         <v>16</v>
       </c>
       <c r="G1038" s="23">
-        <v>76</v>
+        <v>48</v>
       </c>
       <c r="H1038" s="24" t="s">
         <v>1488</v>
@@ -32997,7 +33027,7 @@
         <v>16</v>
       </c>
       <c r="G1039" s="18">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="H1039" s="19" t="s">
         <v>1490</v>
@@ -33023,7 +33053,7 @@
         <v>16</v>
       </c>
       <c r="G1040" s="23">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H1040" s="24" t="s">
         <v>1492</v>
@@ -33049,7 +33079,7 @@
         <v>16</v>
       </c>
       <c r="G1041" s="18">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H1041" s="19" t="s">
         <v>1494</v>
@@ -33057,16 +33087,16 @@
     </row>
     <row r="1042" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1042" s="20" t="s">
-        <v>7</v>
+        <v>65</v>
       </c>
       <c r="B1042" s="21">
-        <v>45323</v>
+        <v>45320</v>
       </c>
       <c r="C1042" s="21">
         <v>45324</v>
       </c>
       <c r="D1042" s="21">
-        <v>45324</v>
+        <v>45380</v>
       </c>
       <c r="E1042" s="22" t="s">
         <v>1495</v>
@@ -33075,7 +33105,7 @@
         <v>16</v>
       </c>
       <c r="G1042" s="23">
-        <v>6</v>
+        <v>125</v>
       </c>
       <c r="H1042" s="24" t="s">
         <v>1496</v>
@@ -33086,48 +33116,48 @@
         <v>65</v>
       </c>
       <c r="B1043" s="16">
-        <v>45320</v>
+        <v>45316</v>
       </c>
       <c r="C1043" s="16">
         <v>45324</v>
       </c>
       <c r="D1043" s="16">
-        <v>45380</v>
+        <v>45381</v>
       </c>
       <c r="E1043" s="17" t="s">
+        <v>1474</v>
+      </c>
+      <c r="F1043" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1043" s="18">
+        <v>479</v>
+      </c>
+      <c r="H1043" s="19" t="s">
         <v>1497</v>
-      </c>
-      <c r="F1043" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1043" s="18">
-        <v>125</v>
-      </c>
-      <c r="H1043" s="19" t="s">
-        <v>1498</v>
       </c>
     </row>
     <row r="1044" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1044" s="20" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="B1044" s="21">
-        <v>45316</v>
+        <v>45320</v>
       </c>
       <c r="C1044" s="21">
         <v>45324</v>
       </c>
       <c r="D1044" s="21">
-        <v>45381</v>
+        <v>45380</v>
       </c>
       <c r="E1044" s="22" t="s">
-        <v>1476</v>
+        <v>1498</v>
       </c>
       <c r="F1044" s="22" t="s">
         <v>16</v>
       </c>
       <c r="G1044" s="23">
-        <v>479</v>
+        <v>425</v>
       </c>
       <c r="H1044" s="24" t="s">
         <v>1499</v>
@@ -33135,25 +33165,25 @@
     </row>
     <row r="1045" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1045" s="15" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B1045" s="16">
-        <v>45320</v>
+        <v>45323</v>
       </c>
       <c r="C1045" s="16">
         <v>45324</v>
       </c>
       <c r="D1045" s="16">
-        <v>45380</v>
+        <v>45443</v>
       </c>
       <c r="E1045" s="17" t="s">
         <v>1500</v>
       </c>
       <c r="F1045" s="17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G1045" s="18">
-        <v>425</v>
+        <v>8</v>
       </c>
       <c r="H1045" s="19" t="s">
         <v>1501</v>
@@ -33161,16 +33191,16 @@
     </row>
     <row r="1046" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1046" s="20" t="s">
-        <v>9</v>
+        <v>75</v>
       </c>
       <c r="B1046" s="21">
-        <v>45323</v>
+        <v>45322</v>
       </c>
       <c r="C1046" s="21">
         <v>45324</v>
       </c>
       <c r="D1046" s="21">
-        <v>45443</v>
+        <v>45382</v>
       </c>
       <c r="E1046" s="22" t="s">
         <v>1502</v>
@@ -33179,7 +33209,7 @@
         <v>15</v>
       </c>
       <c r="G1046" s="23">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="H1046" s="24" t="s">
         <v>1503</v>
@@ -33190,22 +33220,22 @@
         <v>75</v>
       </c>
       <c r="B1047" s="16">
-        <v>45322</v>
+        <v>45309</v>
       </c>
       <c r="C1047" s="16">
         <v>45324</v>
       </c>
       <c r="D1047" s="16">
-        <v>45382</v>
+        <v>45372</v>
       </c>
       <c r="E1047" s="17" t="s">
         <v>1504</v>
       </c>
       <c r="F1047" s="17" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G1047" s="18">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="H1047" s="19" t="s">
         <v>1505</v>
@@ -33213,28 +33243,28 @@
     </row>
     <row r="1048" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1048" s="20" t="s">
-        <v>75</v>
+        <v>6</v>
       </c>
       <c r="B1048" s="21">
-        <v>45309</v>
+        <v>45316</v>
       </c>
       <c r="C1048" s="21">
         <v>45324</v>
       </c>
       <c r="D1048" s="21">
-        <v>45372</v>
+        <v>45377</v>
       </c>
       <c r="E1048" s="22" t="s">
         <v>1506</v>
       </c>
       <c r="F1048" s="22" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G1048" s="23">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="H1048" s="24" t="s">
-        <v>1507</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="1049" spans="1:8" x14ac:dyDescent="0.3">
@@ -33251,16 +33281,16 @@
         <v>45377</v>
       </c>
       <c r="E1049" s="17" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="F1049" s="17" t="s">
         <v>16</v>
       </c>
       <c r="G1049" s="18">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="H1049" s="19" t="s">
-        <v>1338</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="1050" spans="1:8" x14ac:dyDescent="0.3">
@@ -33277,16 +33307,16 @@
         <v>45377</v>
       </c>
       <c r="E1050" s="22" t="s">
+        <v>1508</v>
+      </c>
+      <c r="F1050" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1050" s="23">
+        <v>8</v>
+      </c>
+      <c r="H1050" s="24" t="s">
         <v>1509</v>
-      </c>
-      <c r="F1050" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1050" s="23">
-        <v>9</v>
-      </c>
-      <c r="H1050" s="24" t="s">
-        <v>1340</v>
       </c>
     </row>
     <row r="1051" spans="1:8" x14ac:dyDescent="0.3">
@@ -33309,10 +33339,10 @@
         <v>16</v>
       </c>
       <c r="G1051" s="18">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H1051" s="19" t="s">
-        <v>1511</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="1052" spans="1:8" x14ac:dyDescent="0.3">
@@ -33329,16 +33359,16 @@
         <v>45377</v>
       </c>
       <c r="E1052" s="22" t="s">
+        <v>1511</v>
+      </c>
+      <c r="F1052" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1052" s="23">
+        <v>12</v>
+      </c>
+      <c r="H1052" s="24" t="s">
         <v>1512</v>
-      </c>
-      <c r="F1052" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1052" s="23">
-        <v>1</v>
-      </c>
-      <c r="H1052" s="24" t="s">
-        <v>1342</v>
       </c>
     </row>
     <row r="1053" spans="1:8" x14ac:dyDescent="0.3">
@@ -33361,7 +33391,7 @@
         <v>16</v>
       </c>
       <c r="G1053" s="18">
-        <v>12</v>
+        <v>70</v>
       </c>
       <c r="H1053" s="19" t="s">
         <v>1514</v>
@@ -33372,77 +33402,77 @@
         <v>6</v>
       </c>
       <c r="B1054" s="21">
-        <v>45316</v>
+        <v>45309</v>
       </c>
       <c r="C1054" s="21">
         <v>45324</v>
       </c>
       <c r="D1054" s="21">
-        <v>45377</v>
+        <v>45362</v>
       </c>
       <c r="E1054" s="22" t="s">
-        <v>1515</v>
+        <v>1504</v>
       </c>
       <c r="F1054" s="22" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G1054" s="23">
-        <v>70</v>
+        <v>7</v>
       </c>
       <c r="H1054" s="24" t="s">
-        <v>1516</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="1055" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1055" s="15" t="s">
-        <v>6</v>
+        <v>251</v>
       </c>
       <c r="B1055" s="16">
-        <v>45309</v>
+        <v>45322</v>
       </c>
       <c r="C1055" s="16">
         <v>45324</v>
       </c>
       <c r="D1055" s="16">
-        <v>45362</v>
+        <v>45382</v>
       </c>
       <c r="E1055" s="17" t="s">
-        <v>1506</v>
+        <v>500</v>
       </c>
       <c r="F1055" s="17" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G1055" s="18">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="H1055" s="19" t="s">
-        <v>1507</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="1056" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1056" s="20" t="s">
-        <v>251</v>
+        <v>5</v>
       </c>
       <c r="B1056" s="21">
-        <v>45322</v>
+        <v>45314</v>
       </c>
       <c r="C1056" s="21">
         <v>45324</v>
       </c>
       <c r="D1056" s="21">
-        <v>45382</v>
+        <v>45376</v>
       </c>
       <c r="E1056" s="22" t="s">
-        <v>500</v>
+        <v>54</v>
       </c>
       <c r="F1056" s="22" t="s">
         <v>16</v>
       </c>
       <c r="G1056" s="23">
-        <v>16</v>
+        <v>91</v>
       </c>
       <c r="H1056" s="24" t="s">
-        <v>1517</v>
+        <v>55</v>
       </c>
     </row>
     <row r="1057" spans="1:8" x14ac:dyDescent="0.3">
@@ -33465,7 +33495,7 @@
         <v>16</v>
       </c>
       <c r="G1057" s="18">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="H1057" s="19" t="s">
         <v>55</v>
@@ -33473,7 +33503,7 @@
     </row>
     <row r="1058" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1058" s="20" t="s">
-        <v>5</v>
+        <v>283</v>
       </c>
       <c r="B1058" s="21">
         <v>45314</v>
@@ -33482,97 +33512,97 @@
         <v>45324</v>
       </c>
       <c r="D1058" s="21">
-        <v>45376</v>
+        <v>45355</v>
       </c>
       <c r="E1058" s="22" t="s">
-        <v>54</v>
+        <v>1516</v>
       </c>
       <c r="F1058" s="22" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G1058" s="23">
-        <v>20</v>
+        <v>241</v>
       </c>
       <c r="H1058" s="24" t="s">
-        <v>55</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="1059" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1059" s="15" t="s">
-        <v>283</v>
+        <v>301</v>
       </c>
       <c r="B1059" s="16">
-        <v>45314</v>
+        <v>45316</v>
       </c>
       <c r="C1059" s="16">
         <v>45324</v>
       </c>
       <c r="D1059" s="16">
-        <v>45355</v>
+        <v>45381</v>
       </c>
       <c r="E1059" s="17" t="s">
+        <v>1474</v>
+      </c>
+      <c r="F1059" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1059" s="18">
+        <v>86</v>
+      </c>
+      <c r="H1059" s="19" t="s">
         <v>1518</v>
-      </c>
-      <c r="F1059" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="G1059" s="18">
-        <v>241</v>
-      </c>
-      <c r="H1059" s="19" t="s">
-        <v>1519</v>
       </c>
     </row>
     <row r="1060" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1060" s="20" t="s">
-        <v>301</v>
+        <v>14</v>
       </c>
       <c r="B1060" s="21">
-        <v>45316</v>
+        <v>45327</v>
       </c>
       <c r="C1060" s="21">
-        <v>45324</v>
+        <v>45327</v>
       </c>
       <c r="D1060" s="21">
-        <v>45381</v>
+        <v>45408</v>
       </c>
       <c r="E1060" s="22" t="s">
-        <v>1476</v>
+        <v>293</v>
       </c>
       <c r="F1060" s="22" t="s">
         <v>16</v>
       </c>
       <c r="G1060" s="23">
-        <v>86</v>
+        <v>6</v>
       </c>
       <c r="H1060" s="24" t="s">
-        <v>1520</v>
+        <v>294</v>
       </c>
     </row>
     <row r="1061" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1061" s="15" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="B1061" s="16">
-        <v>45327</v>
+        <v>45323</v>
       </c>
       <c r="C1061" s="16">
         <v>45327</v>
       </c>
       <c r="D1061" s="16">
-        <v>45408</v>
+        <v>45394</v>
       </c>
       <c r="E1061" s="17" t="s">
-        <v>293</v>
+        <v>1519</v>
       </c>
       <c r="F1061" s="17" t="s">
         <v>16</v>
       </c>
       <c r="G1061" s="18">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="H1061" s="19" t="s">
-        <v>294</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="1062" spans="1:8" x14ac:dyDescent="0.3">
@@ -33580,13 +33610,13 @@
         <v>5</v>
       </c>
       <c r="B1062" s="21">
-        <v>45323</v>
+        <v>45327</v>
       </c>
       <c r="C1062" s="21">
         <v>45327</v>
       </c>
       <c r="D1062" s="21">
-        <v>45394</v>
+        <v>45328</v>
       </c>
       <c r="E1062" s="22" t="s">
         <v>1521</v>
@@ -33595,7 +33625,7 @@
         <v>16</v>
       </c>
       <c r="G1062" s="23">
-        <v>60</v>
+        <v>122</v>
       </c>
       <c r="H1062" s="24" t="s">
         <v>1522</v>
@@ -33603,7 +33633,7 @@
     </row>
     <row r="1063" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1063" s="15" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B1063" s="16">
         <v>45327</v>
@@ -33615,39 +33645,39 @@
         <v>45328</v>
       </c>
       <c r="E1063" s="17" t="s">
+        <v>1521</v>
+      </c>
+      <c r="F1063" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1063" s="18">
+        <v>52</v>
+      </c>
+      <c r="H1063" s="19" t="s">
         <v>1523</v>
-      </c>
-      <c r="F1063" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1063" s="18">
-        <v>122</v>
-      </c>
-      <c r="H1063" s="19" t="s">
-        <v>1524</v>
       </c>
     </row>
     <row r="1064" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1064" s="20" t="s">
-        <v>7</v>
+        <v>62</v>
       </c>
       <c r="B1064" s="21">
-        <v>45327</v>
+        <v>45323</v>
       </c>
       <c r="C1064" s="21">
         <v>45327</v>
       </c>
       <c r="D1064" s="21">
-        <v>45328</v>
+        <v>45382</v>
       </c>
       <c r="E1064" s="22" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
       <c r="F1064" s="22" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G1064" s="23">
-        <v>52</v>
+        <v>92</v>
       </c>
       <c r="H1064" s="24" t="s">
         <v>1525</v>
@@ -33655,7 +33685,7 @@
     </row>
     <row r="1065" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1065" s="15" t="s">
-        <v>62</v>
+        <v>6</v>
       </c>
       <c r="B1065" s="16">
         <v>45323</v>
@@ -33670,18 +33700,18 @@
         <v>1526</v>
       </c>
       <c r="F1065" s="17" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G1065" s="18">
-        <v>92</v>
+        <v>4</v>
       </c>
       <c r="H1065" s="19" t="s">
-        <v>1527</v>
+        <v>848</v>
       </c>
     </row>
     <row r="1066" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1066" s="20" t="s">
-        <v>6</v>
+        <v>51</v>
       </c>
       <c r="B1066" s="21">
         <v>45323</v>
@@ -33690,19 +33720,19 @@
         <v>45327</v>
       </c>
       <c r="D1066" s="21">
-        <v>45382</v>
+        <v>45405</v>
       </c>
       <c r="E1066" s="22" t="s">
+        <v>1527</v>
+      </c>
+      <c r="F1066" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1066" s="23">
+        <v>51</v>
+      </c>
+      <c r="H1066" s="24" t="s">
         <v>1528</v>
-      </c>
-      <c r="F1066" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1066" s="23">
-        <v>4</v>
-      </c>
-      <c r="H1066" s="24" t="s">
-        <v>848</v>
       </c>
     </row>
     <row r="1067" spans="1:8" x14ac:dyDescent="0.3">
@@ -33716,7 +33746,7 @@
         <v>45327</v>
       </c>
       <c r="D1067" s="16">
-        <v>45405</v>
+        <v>45386</v>
       </c>
       <c r="E1067" s="17" t="s">
         <v>1529</v>
@@ -33725,7 +33755,7 @@
         <v>16</v>
       </c>
       <c r="G1067" s="18">
-        <v>51</v>
+        <v>83</v>
       </c>
       <c r="H1067" s="19" t="s">
         <v>1530</v>
@@ -33736,65 +33766,65 @@
         <v>51</v>
       </c>
       <c r="B1068" s="21">
-        <v>45323</v>
+        <v>45324</v>
       </c>
       <c r="C1068" s="21">
         <v>45327</v>
       </c>
       <c r="D1068" s="21">
-        <v>45386</v>
+        <v>45324</v>
       </c>
       <c r="E1068" s="22" t="s">
-        <v>1531</v>
+        <v>753</v>
       </c>
       <c r="F1068" s="22" t="s">
         <v>16</v>
       </c>
       <c r="G1068" s="23">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="H1068" s="24" t="s">
-        <v>1532</v>
+        <v>754</v>
       </c>
     </row>
     <row r="1069" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1069" s="15" t="s">
-        <v>51</v>
+        <v>7</v>
       </c>
       <c r="B1069" s="16">
-        <v>45324</v>
+        <v>45321</v>
       </c>
       <c r="C1069" s="16">
         <v>45327</v>
       </c>
       <c r="D1069" s="16">
-        <v>45324</v>
+        <v>45381</v>
       </c>
       <c r="E1069" s="17" t="s">
-        <v>753</v>
+        <v>1531</v>
       </c>
       <c r="F1069" s="17" t="s">
         <v>16</v>
       </c>
       <c r="G1069" s="18">
-        <v>99</v>
+        <v>311</v>
       </c>
       <c r="H1069" s="19" t="s">
-        <v>754</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="1070" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1070" s="20" t="s">
-        <v>7</v>
+        <v>78</v>
       </c>
       <c r="B1070" s="21">
-        <v>45321</v>
+        <v>45323</v>
       </c>
       <c r="C1070" s="21">
         <v>45327</v>
       </c>
       <c r="D1070" s="21">
-        <v>45381</v>
+        <v>45383</v>
       </c>
       <c r="E1070" s="22" t="s">
         <v>1533</v>
@@ -33803,7 +33833,7 @@
         <v>16</v>
       </c>
       <c r="G1070" s="23">
-        <v>311</v>
+        <v>43</v>
       </c>
       <c r="H1070" s="24" t="s">
         <v>1534</v>
@@ -33811,7 +33841,7 @@
     </row>
     <row r="1071" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1071" s="15" t="s">
-        <v>78</v>
+        <v>281</v>
       </c>
       <c r="B1071" s="16">
         <v>45323</v>
@@ -33820,45 +33850,539 @@
         <v>45327</v>
       </c>
       <c r="D1071" s="16">
-        <v>45383</v>
+        <v>45295</v>
       </c>
       <c r="E1071" s="17" t="s">
+        <v>969</v>
+      </c>
+      <c r="F1071" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1071" s="18">
+        <v>1</v>
+      </c>
+      <c r="H1071" s="19" t="s">
         <v>1535</v>
-      </c>
-      <c r="F1071" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1071" s="18">
-        <v>43</v>
-      </c>
-      <c r="H1071" s="19" t="s">
-        <v>1536</v>
       </c>
     </row>
     <row r="1072" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1072" s="20" t="s">
-        <v>281</v>
+        <v>7</v>
       </c>
       <c r="B1072" s="21">
+        <v>45307</v>
+      </c>
+      <c r="C1072" s="21">
+        <v>45328</v>
+      </c>
+      <c r="D1072" s="21">
+        <v>45366</v>
+      </c>
+      <c r="E1072" s="22" t="s">
+        <v>1537</v>
+      </c>
+      <c r="F1072" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1072" s="23">
+        <v>120</v>
+      </c>
+      <c r="H1072" s="24" t="s">
+        <v>1538</v>
+      </c>
+    </row>
+    <row r="1073" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1073" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1073" s="16">
+        <v>45313</v>
+      </c>
+      <c r="C1073" s="16">
+        <v>45328</v>
+      </c>
+      <c r="D1073" s="16">
+        <v>45355</v>
+      </c>
+      <c r="E1073" s="17" t="s">
+        <v>1539</v>
+      </c>
+      <c r="F1073" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1073" s="18">
+        <v>57</v>
+      </c>
+      <c r="H1073" s="19" t="s">
+        <v>1540</v>
+      </c>
+    </row>
+    <row r="1074" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1074" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1074" s="21">
+        <v>45313</v>
+      </c>
+      <c r="C1074" s="21">
+        <v>45328</v>
+      </c>
+      <c r="D1074" s="21">
+        <v>45355</v>
+      </c>
+      <c r="E1074" s="22" t="s">
+        <v>1541</v>
+      </c>
+      <c r="F1074" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1074" s="23">
+        <v>16</v>
+      </c>
+      <c r="H1074" s="24" t="s">
+        <v>1542</v>
+      </c>
+    </row>
+    <row r="1075" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1075" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1075" s="16">
         <v>45323</v>
       </c>
-      <c r="C1072" s="21">
+      <c r="C1075" s="16">
+        <v>45328</v>
+      </c>
+      <c r="D1075" s="16">
+        <v>45296</v>
+      </c>
+      <c r="E1075" s="17" t="s">
+        <v>472</v>
+      </c>
+      <c r="F1075" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1075" s="18">
+        <v>1</v>
+      </c>
+      <c r="H1075" s="19" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="1076" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1076" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1076" s="21">
+        <v>45323</v>
+      </c>
+      <c r="C1076" s="21">
+        <v>45328</v>
+      </c>
+      <c r="D1076" s="21">
+        <v>45315</v>
+      </c>
+      <c r="E1076" s="22" t="s">
+        <v>472</v>
+      </c>
+      <c r="F1076" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1076" s="23">
+        <v>1</v>
+      </c>
+      <c r="H1076" s="24" t="s">
+        <v>1543</v>
+      </c>
+    </row>
+    <row r="1077" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1077" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1077" s="16">
+        <v>45323</v>
+      </c>
+      <c r="C1077" s="16">
+        <v>45328</v>
+      </c>
+      <c r="D1077" s="16">
+        <v>45317</v>
+      </c>
+      <c r="E1077" s="17" t="s">
+        <v>472</v>
+      </c>
+      <c r="F1077" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1077" s="18">
+        <v>4</v>
+      </c>
+      <c r="H1077" s="19" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="1078" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1078" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1078" s="21">
+        <v>45323</v>
+      </c>
+      <c r="C1078" s="21">
+        <v>45328</v>
+      </c>
+      <c r="D1078" s="21">
+        <v>45322</v>
+      </c>
+      <c r="E1078" s="22" t="s">
+        <v>472</v>
+      </c>
+      <c r="F1078" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1078" s="23">
+        <v>1</v>
+      </c>
+      <c r="H1078" s="24" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="1079" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1079" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1079" s="16">
+        <v>45323</v>
+      </c>
+      <c r="C1079" s="16">
+        <v>45328</v>
+      </c>
+      <c r="D1079" s="16">
+        <v>45338</v>
+      </c>
+      <c r="E1079" s="17" t="s">
+        <v>472</v>
+      </c>
+      <c r="F1079" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1079" s="18">
+        <v>6</v>
+      </c>
+      <c r="H1079" s="19" t="s">
+        <v>1543</v>
+      </c>
+    </row>
+    <row r="1080" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1080" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1080" s="21">
+        <v>45323</v>
+      </c>
+      <c r="C1080" s="21">
+        <v>45328</v>
+      </c>
+      <c r="D1080" s="21">
+        <v>45352</v>
+      </c>
+      <c r="E1080" s="22" t="s">
+        <v>472</v>
+      </c>
+      <c r="F1080" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1080" s="23">
+        <v>6</v>
+      </c>
+      <c r="H1080" s="24" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="1081" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1081" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1081" s="16">
+        <v>45323</v>
+      </c>
+      <c r="C1081" s="16">
+        <v>45328</v>
+      </c>
+      <c r="D1081" s="16">
+        <v>45359</v>
+      </c>
+      <c r="E1081" s="17" t="s">
+        <v>472</v>
+      </c>
+      <c r="F1081" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1081" s="18">
+        <v>1</v>
+      </c>
+      <c r="H1081" s="19" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="1082" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1082" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1082" s="21">
+        <v>45323</v>
+      </c>
+      <c r="C1082" s="21">
+        <v>45328</v>
+      </c>
+      <c r="D1082" s="21">
+        <v>45366</v>
+      </c>
+      <c r="E1082" s="22" t="s">
+        <v>472</v>
+      </c>
+      <c r="F1082" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1082" s="23">
+        <v>2</v>
+      </c>
+      <c r="H1082" s="24" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="1083" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1083" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1083" s="16">
+        <v>45323</v>
+      </c>
+      <c r="C1083" s="16">
+        <v>45328</v>
+      </c>
+      <c r="D1083" s="16">
+        <v>45373</v>
+      </c>
+      <c r="E1083" s="17" t="s">
+        <v>472</v>
+      </c>
+      <c r="F1083" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1083" s="18">
+        <v>1</v>
+      </c>
+      <c r="H1083" s="19" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="1084" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1084" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1084" s="21">
+        <v>45323</v>
+      </c>
+      <c r="C1084" s="21">
+        <v>45328</v>
+      </c>
+      <c r="D1084" s="21">
+        <v>45380</v>
+      </c>
+      <c r="E1084" s="22" t="s">
+        <v>472</v>
+      </c>
+      <c r="F1084" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1084" s="23">
+        <v>84</v>
+      </c>
+      <c r="H1084" s="24" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="1085" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1085" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1085" s="16">
+        <v>45323</v>
+      </c>
+      <c r="C1085" s="16">
+        <v>45328</v>
+      </c>
+      <c r="D1085" s="16">
+        <v>45387</v>
+      </c>
+      <c r="E1085" s="17" t="s">
+        <v>472</v>
+      </c>
+      <c r="F1085" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1085" s="18">
+        <v>1</v>
+      </c>
+      <c r="H1085" s="19" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="1086" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1086" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1086" s="21">
+        <v>45323</v>
+      </c>
+      <c r="C1086" s="21">
+        <v>45328</v>
+      </c>
+      <c r="D1086" s="21">
+        <v>45408</v>
+      </c>
+      <c r="E1086" s="22" t="s">
+        <v>472</v>
+      </c>
+      <c r="F1086" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1086" s="23">
+        <v>20</v>
+      </c>
+      <c r="H1086" s="24" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="1087" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1087" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1087" s="16">
+        <v>45323</v>
+      </c>
+      <c r="C1087" s="16">
+        <v>45328</v>
+      </c>
+      <c r="D1087" s="16">
+        <v>45380</v>
+      </c>
+      <c r="E1087" s="17" t="s">
+        <v>472</v>
+      </c>
+      <c r="F1087" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1087" s="18">
+        <v>1</v>
+      </c>
+      <c r="H1087" s="19" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="1088" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1088" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1088" s="21">
+        <v>45323</v>
+      </c>
+      <c r="C1088" s="21">
+        <v>45328</v>
+      </c>
+      <c r="D1088" s="21">
         <v>45327</v>
       </c>
-      <c r="D1072" s="21">
-        <v>45295</v>
-      </c>
-      <c r="E1072" s="22" t="s">
-        <v>969</v>
-      </c>
-      <c r="F1072" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1072" s="23">
-        <v>1</v>
-      </c>
-      <c r="H1072" s="24" t="s">
-        <v>1537</v>
+      <c r="E1088" s="22" t="s">
+        <v>472</v>
+      </c>
+      <c r="F1088" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1088" s="23">
+        <v>89</v>
+      </c>
+      <c r="H1088" s="24" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="1089" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1089" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1089" s="16">
+        <v>45323</v>
+      </c>
+      <c r="C1089" s="16">
+        <v>45328</v>
+      </c>
+      <c r="D1089" s="16">
+        <v>45408</v>
+      </c>
+      <c r="E1089" s="17" t="s">
+        <v>472</v>
+      </c>
+      <c r="F1089" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1089" s="18">
+        <v>246</v>
+      </c>
+      <c r="H1089" s="19" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="1090" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1090" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="B1090" s="21">
+        <v>45307</v>
+      </c>
+      <c r="C1090" s="21">
+        <v>45328</v>
+      </c>
+      <c r="D1090" s="21">
+        <v>45367</v>
+      </c>
+      <c r="E1090" s="22" t="s">
+        <v>1544</v>
+      </c>
+      <c r="F1090" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1090" s="23">
+        <v>13</v>
+      </c>
+      <c r="H1090" s="24" t="s">
+        <v>1545</v>
+      </c>
+    </row>
+    <row r="1091" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1091" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1091" s="16">
+        <v>45329</v>
+      </c>
+      <c r="C1091" s="16">
+        <v>45329</v>
+      </c>
+      <c r="D1091" s="16">
+        <v>45390</v>
+      </c>
+      <c r="E1091" s="17" t="s">
+        <v>1546</v>
+      </c>
+      <c r="F1091" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1091" s="18">
+        <v>81</v>
+      </c>
+      <c r="H1091" s="19" t="s">
+        <v>1547</v>
       </c>
     </row>
   </sheetData>
@@ -34000,13 +34524,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B48BC392-FD1B-469F-B84B-ED6D437FF036}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7D4BC4E0-AE6C-401F-993E-3930E78928FF}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C5E4FE0-8E74-4E56-B28C-A255DF853189}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3EA462EE-355B-45D6-9DFB-5F0C91A6ABAB}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{95CB3ACB-6411-42F1-A3CE-81FC8B20A9AA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7AFD4378-0F47-4AF4-847A-43A902618409}"/>
 </file>
--- a/data/warn-scraper/cache/ca/warn_report1.xlsx
+++ b/data/warn-scraper/cache/ca/warn_report1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BVang\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{604C5774-F3BF-4FE9-9D9B-AE5F7CBDB02F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5337F169-F50A-44C4-8327-CBB11931B357}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4451" uniqueCount="1572">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4499" uniqueCount="1591">
   <si>
     <t>County/Parish</t>
   </si>
@@ -4769,24 +4769,6 @@
     <t>Brookfield Properties (USA II) LLC</t>
   </si>
   <si>
-    <t>110 E 9th Street  Los Angeles CA 90079</t>
-  </si>
-  <si>
-    <t>333 S Grand Ave  Los Angeles CA 90071</t>
-  </si>
-  <si>
-    <t>333 S Hope  Los Angeles CA 90071</t>
-  </si>
-  <si>
-    <t>601 S Figueora Street  Los Angeles CA 90017</t>
-  </si>
-  <si>
-    <t>777 S Figueora Street  Los Angeles CA 90017</t>
-  </si>
-  <si>
-    <t>4640 Admiralty Way  Marina Del Rey CA 90292</t>
-  </si>
-  <si>
     <t>Grammarly, Inc.</t>
   </si>
   <si>
@@ -4815,6 +4797,81 @@
   </si>
   <si>
     <t>6080 Center Drive  Los Angeles CA 90045</t>
+  </si>
+  <si>
+    <t>110 E 9th Street, Suite A200  Los Angeles CA 90079</t>
+  </si>
+  <si>
+    <t>333 S Grand Ave, Suite 300  Los Angeles CA 90071</t>
+  </si>
+  <si>
+    <t>333 S Hope Street, Suite C-100  Los Angeles CA 90071</t>
+  </si>
+  <si>
+    <t>601 S Figueora Street, Suite 1450  Los Angeles CA 90017</t>
+  </si>
+  <si>
+    <t>777 S Figueora Street, Suite 375  Los Angeles CA 90017</t>
+  </si>
+  <si>
+    <t>4640 Admiralty Way, Suite 402  Marina Del Rey CA 90292</t>
+  </si>
+  <si>
+    <t>333 S. Grand Ave, Suite 1525  Los Angeles CA 90071</t>
+  </si>
+  <si>
+    <t>415 Natoma Street  San Francisco CA 94103</t>
+  </si>
+  <si>
+    <t>1 Post Street, Suite 450  San Francisco CA 94104</t>
+  </si>
+  <si>
+    <t>545 San Antonio Road, Suite 314  Mountain View CA 94040</t>
+  </si>
+  <si>
+    <t>Zwift, Inc.</t>
+  </si>
+  <si>
+    <t>111 W. Ocean Blvd.  Long Beach CA 90802</t>
+  </si>
+  <si>
+    <t>Gibson Overseas, Inc.</t>
+  </si>
+  <si>
+    <t>7776 Tippecanoe Ave  San Bernardino CA 92410</t>
+  </si>
+  <si>
+    <t>Aurora Solar Inc.</t>
+  </si>
+  <si>
+    <t>153 Kearny Street, 5th Floor  San Francisco CA 94108</t>
+  </si>
+  <si>
+    <t>Riot Games</t>
+  </si>
+  <si>
+    <t>12333 W Olympic Blvd.  Los Angeles CA 90064</t>
+  </si>
+  <si>
+    <t>900 Middlefield Road  Redwood City CA 94063</t>
+  </si>
+  <si>
+    <t>Universal Intermodal Services, Inc.</t>
+  </si>
+  <si>
+    <t>15033 Slover Ave  Fontana CA 92337</t>
+  </si>
+  <si>
+    <t>Nordson Corporation</t>
+  </si>
+  <si>
+    <t>2765 Loker Avenue West  Carlsbad CA 92010</t>
+  </si>
+  <si>
+    <t>Maplebear Inc. dba Instacart</t>
+  </si>
+  <si>
+    <t>50 Beale Street, #600  San Francisco CA 94107</t>
   </si>
   <si>
     <r>
@@ -4828,7 +4885,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>07/01/23 to 02/12/24</t>
+      <t>07/01/23 to 02/14/24</t>
     </r>
     <r>
       <rPr>
@@ -4848,7 +4905,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>A detailed WARN summary by county and filtered according to received date. Table Spans cells A2 through H1109.</t>
+      <t>A detailed WARN summary by county and filtered according to received date. Table Spans cells A2 through H1121.</t>
     </r>
   </si>
 </sst>
@@ -5639,8 +5696,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:H1109" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
-  <autoFilter ref="A2:H1109" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:H1121" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
+  <autoFilter ref="A2:H1121" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -6024,7 +6081,7 @@
       </c>
       <c r="B3" s="5">
         <f>SUM('Detailed WARN Report '!G:G)</f>
-        <v>57287</v>
+        <v>58084</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -6033,7 +6090,7 @@
       </c>
       <c r="B4" s="5">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Permanent")</f>
-        <v>780</v>
+        <v>791</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -6059,7 +6116,7 @@
       </c>
       <c r="B7" s="5">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Permanent")</f>
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -6091,7 +6148,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:H1109"/>
+  <dimension ref="A1:H1121"/>
   <sheetFormatPr defaultColWidth="26" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.85546875" bestFit="1" customWidth="1"/>
@@ -6106,7 +6163,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="117" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>1571</v>
+        <v>1590</v>
       </c>
       <c r="D1" s="12"/>
       <c r="E1" s="6"/>
@@ -32654,7 +32711,7 @@
         <v>16</v>
       </c>
       <c r="G1022" s="23">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H1022" s="24" t="s">
         <v>1456</v>
@@ -34604,10 +34661,10 @@
         <v>16</v>
       </c>
       <c r="G1097" s="18">
-        <v>100</v>
+        <v>19</v>
       </c>
       <c r="H1097" s="19" t="s">
-        <v>1555</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="1098" spans="1:8" x14ac:dyDescent="0.25">
@@ -34630,10 +34687,10 @@
         <v>16</v>
       </c>
       <c r="G1098" s="23">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H1098" s="24" t="s">
-        <v>1556</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="1099" spans="1:8" x14ac:dyDescent="0.25">
@@ -34656,10 +34713,10 @@
         <v>16</v>
       </c>
       <c r="G1099" s="18">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="H1099" s="19" t="s">
-        <v>1557</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="1100" spans="1:8" x14ac:dyDescent="0.25">
@@ -34682,10 +34739,10 @@
         <v>16</v>
       </c>
       <c r="G1100" s="23">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="H1100" s="24" t="s">
-        <v>1558</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="1101" spans="1:8" x14ac:dyDescent="0.25">
@@ -34708,10 +34765,10 @@
         <v>16</v>
       </c>
       <c r="G1101" s="18">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H1101" s="19" t="s">
-        <v>1559</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="1102" spans="1:8" x14ac:dyDescent="0.25">
@@ -34734,140 +34791,140 @@
         <v>16</v>
       </c>
       <c r="G1102" s="23">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H1102" s="24" t="s">
-        <v>1560</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="1103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1103" s="15" t="s">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="B1103" s="16">
-        <v>45329</v>
+        <v>45316</v>
       </c>
       <c r="C1103" s="16">
         <v>45330</v>
       </c>
       <c r="D1103" s="16">
-        <v>45390</v>
+        <v>45383</v>
       </c>
       <c r="E1103" s="17" t="s">
-        <v>1561</v>
+        <v>1554</v>
       </c>
       <c r="F1103" s="17" t="s">
         <v>16</v>
       </c>
       <c r="G1103" s="18">
-        <v>82</v>
+        <v>29</v>
       </c>
       <c r="H1103" s="19" t="s">
-        <v>1562</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="1104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1104" s="20" t="s">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="B1104" s="21">
-        <v>45331</v>
+        <v>45316</v>
       </c>
       <c r="C1104" s="21">
-        <v>45331</v>
+        <v>45330</v>
       </c>
       <c r="D1104" s="21">
-        <v>45408</v>
+        <v>45383</v>
       </c>
       <c r="E1104" s="22" t="s">
-        <v>1563</v>
+        <v>1554</v>
       </c>
       <c r="F1104" s="22" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G1104" s="23">
-        <v>55</v>
+        <v>2</v>
       </c>
       <c r="H1104" s="24" t="s">
-        <v>1564</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="1105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1105" s="15" t="s">
-        <v>281</v>
+        <v>51</v>
       </c>
       <c r="B1105" s="16">
+        <v>45316</v>
+      </c>
+      <c r="C1105" s="16">
         <v>45330</v>
       </c>
-      <c r="C1105" s="16">
-        <v>45331</v>
-      </c>
       <c r="D1105" s="16">
-        <v>45420</v>
+        <v>45383</v>
       </c>
       <c r="E1105" s="17" t="s">
-        <v>1565</v>
+        <v>1554</v>
       </c>
       <c r="F1105" s="17" t="s">
         <v>16</v>
       </c>
       <c r="G1105" s="18">
-        <v>55</v>
+        <v>3</v>
       </c>
       <c r="H1105" s="19" t="s">
-        <v>1566</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="1106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1106" s="20" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B1106" s="21">
-        <v>45329</v>
+        <v>45316</v>
       </c>
       <c r="C1106" s="21">
-        <v>45331</v>
+        <v>45330</v>
       </c>
       <c r="D1106" s="21">
-        <v>45389</v>
+        <v>45383</v>
       </c>
       <c r="E1106" s="22" t="s">
-        <v>1567</v>
+        <v>1554</v>
       </c>
       <c r="F1106" s="22" t="s">
         <v>16</v>
       </c>
       <c r="G1106" s="23">
-        <v>521</v>
+        <v>1</v>
       </c>
       <c r="H1106" s="24" t="s">
-        <v>1568</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="1107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1107" s="15" t="s">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="B1107" s="16">
-        <v>45334</v>
+        <v>45329</v>
       </c>
       <c r="C1107" s="16">
-        <v>45334</v>
+        <v>45330</v>
       </c>
       <c r="D1107" s="16">
-        <v>45394</v>
+        <v>45390</v>
       </c>
       <c r="E1107" s="17" t="s">
-        <v>1569</v>
+        <v>1555</v>
       </c>
       <c r="F1107" s="17" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G1107" s="18">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H1107" s="19" t="s">
-        <v>1570</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="1108" spans="1:8" x14ac:dyDescent="0.25">
@@ -34875,51 +34932,363 @@
         <v>5</v>
       </c>
       <c r="B1108" s="21">
-        <v>45334</v>
+        <v>45331</v>
       </c>
       <c r="C1108" s="21">
-        <v>45334</v>
+        <v>45331</v>
       </c>
       <c r="D1108" s="21">
-        <v>45396</v>
+        <v>45408</v>
       </c>
       <c r="E1108" s="22" t="s">
-        <v>631</v>
+        <v>1557</v>
       </c>
       <c r="F1108" s="22" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G1108" s="23">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="H1108" s="24" t="s">
-        <v>632</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="1109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1109" s="15" t="s">
+        <v>281</v>
+      </c>
+      <c r="B1109" s="16">
+        <v>45330</v>
+      </c>
+      <c r="C1109" s="16">
+        <v>45331</v>
+      </c>
+      <c r="D1109" s="16">
+        <v>45420</v>
+      </c>
+      <c r="E1109" s="17" t="s">
+        <v>1559</v>
+      </c>
+      <c r="F1109" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1109" s="18">
+        <v>55</v>
+      </c>
+      <c r="H1109" s="19" t="s">
+        <v>1560</v>
+      </c>
+    </row>
+    <row r="1110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1110" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="B1109" s="16">
+      <c r="B1110" s="21">
+        <v>45329</v>
+      </c>
+      <c r="C1110" s="21">
+        <v>45331</v>
+      </c>
+      <c r="D1110" s="21">
+        <v>45389</v>
+      </c>
+      <c r="E1110" s="22" t="s">
+        <v>1561</v>
+      </c>
+      <c r="F1110" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1110" s="23">
+        <v>521</v>
+      </c>
+      <c r="H1110" s="24" t="s">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="1111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1111" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1111" s="16">
         <v>45334</v>
       </c>
-      <c r="C1109" s="16">
+      <c r="C1111" s="16">
         <v>45334</v>
       </c>
-      <c r="D1109" s="16">
+      <c r="D1111" s="16">
+        <v>45394</v>
+      </c>
+      <c r="E1111" s="17" t="s">
+        <v>1563</v>
+      </c>
+      <c r="F1111" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1111" s="18">
+        <v>84</v>
+      </c>
+      <c r="H1111" s="19" t="s">
+        <v>1564</v>
+      </c>
+    </row>
+    <row r="1112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1112" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1112" s="21">
+        <v>45334</v>
+      </c>
+      <c r="C1112" s="21">
+        <v>45334</v>
+      </c>
+      <c r="D1112" s="21">
         <v>45396</v>
       </c>
-      <c r="E1109" s="17" t="s">
+      <c r="E1112" s="22" t="s">
         <v>631</v>
       </c>
-      <c r="F1109" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1109" s="18">
+      <c r="F1112" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1112" s="23">
+        <v>32</v>
+      </c>
+      <c r="H1112" s="24" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="1113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1113" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1113" s="16">
+        <v>45334</v>
+      </c>
+      <c r="C1113" s="16">
+        <v>45334</v>
+      </c>
+      <c r="D1113" s="16">
+        <v>45396</v>
+      </c>
+      <c r="E1113" s="17" t="s">
+        <v>631</v>
+      </c>
+      <c r="F1113" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1113" s="18">
         <v>24</v>
       </c>
-      <c r="H1109" s="19" t="s">
+      <c r="H1113" s="19" t="s">
         <v>633</v>
+      </c>
+    </row>
+    <row r="1114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1114" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1114" s="21">
+        <v>45328</v>
+      </c>
+      <c r="C1114" s="21">
+        <v>45335</v>
+      </c>
+      <c r="D1114" s="21">
+        <v>45389</v>
+      </c>
+      <c r="E1114" s="22" t="s">
+        <v>1575</v>
+      </c>
+      <c r="F1114" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1114" s="23">
+        <v>76</v>
+      </c>
+      <c r="H1114" s="24" t="s">
+        <v>1576</v>
+      </c>
+    </row>
+    <row r="1115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1115" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="B1115" s="16">
+        <v>45331</v>
+      </c>
+      <c r="C1115" s="16">
+        <v>45335</v>
+      </c>
+      <c r="D1115" s="16">
+        <v>45412</v>
+      </c>
+      <c r="E1115" s="17" t="s">
+        <v>1577</v>
+      </c>
+      <c r="F1115" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1115" s="18">
+        <v>44</v>
+      </c>
+      <c r="H1115" s="19" t="s">
+        <v>1578</v>
+      </c>
+    </row>
+    <row r="1116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1116" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1116" s="21">
+        <v>45334</v>
+      </c>
+      <c r="C1116" s="21">
+        <v>45335</v>
+      </c>
+      <c r="D1116" s="21">
+        <v>45322</v>
+      </c>
+      <c r="E1116" s="22" t="s">
+        <v>1579</v>
+      </c>
+      <c r="F1116" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1116" s="23">
+        <v>115</v>
+      </c>
+      <c r="H1116" s="24" t="s">
+        <v>1580</v>
+      </c>
+    </row>
+    <row r="1117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1117" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1117" s="16">
+        <v>45313</v>
+      </c>
+      <c r="C1117" s="16">
+        <v>45336</v>
+      </c>
+      <c r="D1117" s="16">
+        <v>45376</v>
+      </c>
+      <c r="E1117" s="17" t="s">
+        <v>1581</v>
+      </c>
+      <c r="F1117" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1117" s="18">
+        <v>330</v>
+      </c>
+      <c r="H1117" s="19" t="s">
+        <v>1582</v>
+      </c>
+    </row>
+    <row r="1118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1118" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="B1118" s="21">
+        <v>45313</v>
+      </c>
+      <c r="C1118" s="21">
+        <v>45336</v>
+      </c>
+      <c r="D1118" s="21">
+        <v>45376</v>
+      </c>
+      <c r="E1118" s="22" t="s">
+        <v>1581</v>
+      </c>
+      <c r="F1118" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1118" s="23">
+        <v>6</v>
+      </c>
+      <c r="H1118" s="24" t="s">
+        <v>1583</v>
+      </c>
+    </row>
+    <row r="1119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1119" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="B1119" s="16">
+        <v>45335</v>
+      </c>
+      <c r="C1119" s="16">
+        <v>45336</v>
+      </c>
+      <c r="D1119" s="16">
+        <v>45401</v>
+      </c>
+      <c r="E1119" s="17" t="s">
+        <v>1584</v>
+      </c>
+      <c r="F1119" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1119" s="18">
+        <v>42</v>
+      </c>
+      <c r="H1119" s="19" t="s">
+        <v>1585</v>
+      </c>
+    </row>
+    <row r="1120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1120" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1120" s="21">
+        <v>45335</v>
+      </c>
+      <c r="C1120" s="21">
+        <v>45336</v>
+      </c>
+      <c r="D1120" s="21">
+        <v>45408</v>
+      </c>
+      <c r="E1120" s="22" t="s">
+        <v>1586</v>
+      </c>
+      <c r="F1120" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1120" s="23">
+        <v>69</v>
+      </c>
+      <c r="H1120" s="24" t="s">
+        <v>1587</v>
+      </c>
+    </row>
+    <row r="1121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1121" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1121" s="16">
+        <v>45335</v>
+      </c>
+      <c r="C1121" s="16">
+        <v>45336</v>
+      </c>
+      <c r="D1121" s="16">
+        <v>45338</v>
+      </c>
+      <c r="E1121" s="17" t="s">
+        <v>1588</v>
+      </c>
+      <c r="F1121" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1121" s="18">
+        <v>105</v>
+      </c>
+      <c r="H1121" s="19" t="s">
+        <v>1589</v>
       </c>
     </row>
   </sheetData>
@@ -35061,13 +35430,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{017870F2-8C84-4C3D-AC0F-CF778F92642E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D3EFAB4-461E-43EF-9A6D-C1275BD66554}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9C8B01A8-9EDE-4ED1-ADD4-CA3CFA990214}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4EF12D60-5154-4EEC-973E-0431B903931B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{95CE815D-9513-411B-BAAC-0AC61B9ECC65}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6897395A-9A41-4B46-9C37-13B25014997A}"/>
 </file>
--- a/data/warn-scraper/cache/ca/warn_report1.xlsx
+++ b/data/warn-scraper/cache/ca/warn_report1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\WSB-CO\BPAC\Policy &amp; Program Communications Group\Communications Unit\Website Management\5. WARN (Worker Adjustment and Retraining Notification) Updates\2023\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\WSB-CO\BPAC\Policy &amp; Program Communications Group\Communications Unit\Website Management\5. WARN (Worker Adjustment and Retraining Notification) Updates\2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4E7F943-5D00-4AF1-A756-D7A2C1265504}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D62CFFE-50BA-4271-96EF-3734F538F94C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33405" yWindow="3210" windowWidth="15405" windowHeight="11430" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
+    <workbookView xWindow="39945" yWindow="3330" windowWidth="15405" windowHeight="11430" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
   <sheets>
     <sheet name="Index" sheetId="3" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4867" uniqueCount="1686">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4915" uniqueCount="1705">
   <si>
     <t>County/Parish</t>
   </si>
@@ -5159,6 +5159,63 @@
     <t>1305 Tommydon Street  Stockton CA 95210</t>
   </si>
   <si>
+    <t>BuzzFeed Media Enterprises, Inc.</t>
+  </si>
+  <si>
+    <t>1135 N Mansfield Ave  Los Angeles CA 90038</t>
+  </si>
+  <si>
+    <t>Balfour Beatty US Civils</t>
+  </si>
+  <si>
+    <t>2121 S El Camino Real Ste 1000  San Mateo CA 94403</t>
+  </si>
+  <si>
+    <t>Moondoggies, Inc dba The Dog</t>
+  </si>
+  <si>
+    <t>4479 Everts Street  San Diego CA 92109</t>
+  </si>
+  <si>
+    <t>Delta Dental Plan of California</t>
+  </si>
+  <si>
+    <t>11185 International Drive  Rancho Cordova CA 95670</t>
+  </si>
+  <si>
+    <t>Gruma Corp dba Mission Foods</t>
+  </si>
+  <si>
+    <t>11559 Jersey Blvd  Rancho Cucamonga CA 91730</t>
+  </si>
+  <si>
+    <t>Levi Strauss &amp; Co.</t>
+  </si>
+  <si>
+    <t>1155 Battery Street  San Francisco CA 94111</t>
+  </si>
+  <si>
+    <t>Walters &amp; Wolf Precast</t>
+  </si>
+  <si>
+    <t>41777 Boyce Road  Fremont CA 94538</t>
+  </si>
+  <si>
+    <t>2753 E. Eastland Center Drive, Ste 5555  West Covina CA 91791</t>
+  </si>
+  <si>
+    <t>Orion Strategic Solutions LLC</t>
+  </si>
+  <si>
+    <t>5702 Bauer Road  San Diego CA 92145</t>
+  </si>
+  <si>
+    <t>St. Vincent de Paul High School</t>
+  </si>
+  <si>
+    <t>849 Keokuk Street  Petaluma CA 94952</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">WARN REPORT - </t>
     </r>
@@ -5170,7 +5227,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>07/01/23 to 02/28/24</t>
+      <t>07/01/23 to 03/04/24</t>
     </r>
     <r>
       <rPr>
@@ -5190,7 +5247,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>A detailed WARN summary by county and filtered according to received date. Table Spans cells A2 through H1213.</t>
+      <t>A detailed WARN summary by county and filtered according to received date. Table Spans cells A2 through H1225.</t>
     </r>
   </si>
 </sst>
@@ -5504,8 +5561,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF0F0F0"/>
-          <bgColor rgb="FFF0F0F0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -5545,8 +5602,8 @@
       <numFmt numFmtId="165" formatCode="[$-10436]#,##0;\(#,##0\)"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF0F0F0"/>
-          <bgColor rgb="FFF0F0F0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -5585,8 +5642,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF0F0F0"/>
-          <bgColor rgb="FFF0F0F0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -5625,8 +5682,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF0F0F0"/>
-          <bgColor rgb="FFF0F0F0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -5666,8 +5723,8 @@
       <numFmt numFmtId="164" formatCode="[$-10409]mm/dd/yyyy"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF0F0F0"/>
-          <bgColor rgb="FFF0F0F0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -5707,8 +5764,8 @@
       <numFmt numFmtId="164" formatCode="[$-10409]mm/dd/yyyy"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF0F0F0"/>
-          <bgColor rgb="FFF0F0F0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -5748,8 +5805,8 @@
       <numFmt numFmtId="164" formatCode="[$-10409]mm/dd/yyyy"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF0F0F0"/>
-          <bgColor rgb="FFF0F0F0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -5788,8 +5845,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF0F0F0"/>
-          <bgColor rgb="FFF0F0F0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -5981,8 +6038,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:H1213" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
-  <autoFilter ref="A2:H1213" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:H1225" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
+  <autoFilter ref="A2:H1225" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -6366,7 +6423,7 @@
       </c>
       <c r="B3" s="5">
         <f>SUM('Detailed WARN Report '!G:G)</f>
-        <v>61747</v>
+        <v>62810</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -6375,7 +6432,7 @@
       </c>
       <c r="B4" s="5">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Permanent")</f>
-        <v>875</v>
+        <v>883</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -6401,7 +6458,7 @@
       </c>
       <c r="B7" s="5">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Permanent")</f>
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -6433,7 +6490,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:H1213"/>
+  <dimension ref="A1:H1225"/>
   <sheetFormatPr defaultColWidth="26" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.88671875" bestFit="1" customWidth="1"/>
@@ -6448,7 +6505,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="99.6" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
-        <v>1685</v>
+        <v>1704</v>
       </c>
       <c r="D1" s="12"/>
       <c r="E1" s="6"/>
@@ -37966,6 +38023,318 @@
       </c>
       <c r="H1213" s="19" t="s">
         <v>1684</v>
+      </c>
+    </row>
+    <row r="1214" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1214" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1214" s="21">
+        <v>45350</v>
+      </c>
+      <c r="C1214" s="21">
+        <v>45351</v>
+      </c>
+      <c r="D1214" s="21">
+        <v>45411</v>
+      </c>
+      <c r="E1214" s="22" t="s">
+        <v>1685</v>
+      </c>
+      <c r="F1214" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1214" s="23">
+        <v>59</v>
+      </c>
+      <c r="H1214" s="24" t="s">
+        <v>1686</v>
+      </c>
+    </row>
+    <row r="1215" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1215" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="B1215" s="16">
+        <v>45348</v>
+      </c>
+      <c r="C1215" s="16">
+        <v>45351</v>
+      </c>
+      <c r="D1215" s="16">
+        <v>45408</v>
+      </c>
+      <c r="E1215" s="17" t="s">
+        <v>1687</v>
+      </c>
+      <c r="F1215" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1215" s="18">
+        <v>222</v>
+      </c>
+      <c r="H1215" s="19" t="s">
+        <v>1688</v>
+      </c>
+    </row>
+    <row r="1216" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1216" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1216" s="21">
+        <v>45349</v>
+      </c>
+      <c r="C1216" s="21">
+        <v>45351</v>
+      </c>
+      <c r="D1216" s="21">
+        <v>45410</v>
+      </c>
+      <c r="E1216" s="22" t="s">
+        <v>1689</v>
+      </c>
+      <c r="F1216" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1216" s="23">
+        <v>5</v>
+      </c>
+      <c r="H1216" s="24" t="s">
+        <v>1690</v>
+      </c>
+    </row>
+    <row r="1217" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1217" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1217" s="16">
+        <v>45350</v>
+      </c>
+      <c r="C1217" s="16">
+        <v>45352</v>
+      </c>
+      <c r="D1217" s="16">
+        <v>45401</v>
+      </c>
+      <c r="E1217" s="17" t="s">
+        <v>1599</v>
+      </c>
+      <c r="F1217" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1217" s="18">
+        <v>1</v>
+      </c>
+      <c r="H1217" s="19" t="s">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="1218" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1218" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1218" s="21">
+        <v>45351</v>
+      </c>
+      <c r="C1218" s="21">
+        <v>45352</v>
+      </c>
+      <c r="D1218" s="21">
+        <v>45429</v>
+      </c>
+      <c r="E1218" s="22" t="s">
+        <v>1691</v>
+      </c>
+      <c r="F1218" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1218" s="23">
+        <v>137</v>
+      </c>
+      <c r="H1218" s="24" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="1219" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1219" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="B1219" s="16">
+        <v>45350</v>
+      </c>
+      <c r="C1219" s="16">
+        <v>45352</v>
+      </c>
+      <c r="D1219" s="16">
+        <v>45410</v>
+      </c>
+      <c r="E1219" s="17" t="s">
+        <v>1693</v>
+      </c>
+      <c r="F1219" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1219" s="18">
+        <v>93</v>
+      </c>
+      <c r="H1219" s="19" t="s">
+        <v>1694</v>
+      </c>
+    </row>
+    <row r="1220" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1220" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1220" s="21">
+        <v>45350</v>
+      </c>
+      <c r="C1220" s="21">
+        <v>45352</v>
+      </c>
+      <c r="D1220" s="21">
+        <v>45409</v>
+      </c>
+      <c r="E1220" s="22" t="s">
+        <v>1695</v>
+      </c>
+      <c r="F1220" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1220" s="23">
+        <v>146</v>
+      </c>
+      <c r="H1220" s="24" t="s">
+        <v>1696</v>
+      </c>
+    </row>
+    <row r="1221" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1221" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="B1221" s="16">
+        <v>45352</v>
+      </c>
+      <c r="C1221" s="16">
+        <v>45355</v>
+      </c>
+      <c r="D1221" s="16">
+        <v>45412</v>
+      </c>
+      <c r="E1221" s="17" t="s">
+        <v>1697</v>
+      </c>
+      <c r="F1221" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1221" s="18">
+        <v>86</v>
+      </c>
+      <c r="H1221" s="19" t="s">
+        <v>1698</v>
+      </c>
+    </row>
+    <row r="1222" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1222" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1222" s="21">
+        <v>45350</v>
+      </c>
+      <c r="C1222" s="21">
+        <v>45355</v>
+      </c>
+      <c r="D1222" s="21">
+        <v>45443</v>
+      </c>
+      <c r="E1222" s="22" t="s">
+        <v>1371</v>
+      </c>
+      <c r="F1222" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1222" s="23">
+        <v>233</v>
+      </c>
+      <c r="H1222" s="24" t="s">
+        <v>1699</v>
+      </c>
+    </row>
+    <row r="1223" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1223" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1223" s="16">
+        <v>45352</v>
+      </c>
+      <c r="C1223" s="16">
+        <v>45355</v>
+      </c>
+      <c r="D1223" s="16">
+        <v>45412</v>
+      </c>
+      <c r="E1223" s="17" t="s">
+        <v>929</v>
+      </c>
+      <c r="F1223" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1223" s="18">
+        <v>3</v>
+      </c>
+      <c r="H1223" s="19" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="1224" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1224" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1224" s="21">
+        <v>45351</v>
+      </c>
+      <c r="C1224" s="21">
+        <v>45355</v>
+      </c>
+      <c r="D1224" s="21">
+        <v>45412</v>
+      </c>
+      <c r="E1224" s="22" t="s">
+        <v>1700</v>
+      </c>
+      <c r="F1224" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1224" s="23">
+        <v>10</v>
+      </c>
+      <c r="H1224" s="24" t="s">
+        <v>1701</v>
+      </c>
+    </row>
+    <row r="1225" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1225" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1225" s="16">
+        <v>45352</v>
+      </c>
+      <c r="C1225" s="16">
+        <v>45355</v>
+      </c>
+      <c r="D1225" s="16">
+        <v>45413</v>
+      </c>
+      <c r="E1225" s="17" t="s">
+        <v>1702</v>
+      </c>
+      <c r="F1225" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1225" s="18">
+        <v>68</v>
+      </c>
+      <c r="H1225" s="19" t="s">
+        <v>1703</v>
       </c>
     </row>
   </sheetData>
@@ -38107,13 +38476,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{489FE0E0-4017-46F5-8264-135FE418F5E4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2143B1E1-FA5C-43D0-B2B3-CA52DC42C6EF}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4E78C94-674F-41D9-AD38-00FE96B8B688}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EC5166C0-5FC5-4E52-B2CA-6AB57DDD6CD1}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6FCA5E0-A946-47FF-8667-5C37E4CAFE2E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF2C2602-A604-412A-B955-AC3B63C9FDA5}"/>
 </file>
--- a/data/warn-scraper/cache/ca/warn_report1.xlsx
+++ b/data/warn-scraper/cache/ca/warn_report1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\WSB-CO\BPAC\Policy &amp; Program Communications Group\Communications Unit\Website Management\5. WARN (Worker Adjustment and Retraining Notification) Updates\2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90088427-008A-40F5-961E-BA5FB3BC2804}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1539F0F0-2B4E-4DB4-AC6B-CF90A61F0501}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="39945" yWindow="3330" windowWidth="15405" windowHeight="11430" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
+    <workbookView xWindow="39675" yWindow="2325" windowWidth="15405" windowHeight="11430" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
   <sheets>
     <sheet name="Index" sheetId="3" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5023" uniqueCount="1744">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5035" uniqueCount="1746">
   <si>
     <t>County/Parish</t>
   </si>
@@ -5333,6 +5333,12 @@
     <t>1515 W 190th Street, Ste 275  Gardena CA 90248</t>
   </si>
   <si>
+    <t>Kett Engineering Corporation</t>
+  </si>
+  <si>
+    <t>5201 Great America Parkway, Suite 320, #3221  Santa Clara CA 95054</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">WARN REPORT - </t>
     </r>
@@ -5344,7 +5350,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>07/01/23 to 03/11/24</t>
+      <t>07/01/23 to 03/13/24</t>
     </r>
     <r>
       <rPr>
@@ -5364,7 +5370,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>A detailed WARN summary by county and filtered according to received date. Table Spans cells A2 through H1252.</t>
+      <t>A detailed WARN summary by county and filtered according to received date. Table Spans cells A2 through H1255.</t>
     </r>
   </si>
 </sst>
@@ -5678,8 +5684,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFF0F0F0"/>
+          <bgColor rgb="FFF0F0F0"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -5719,8 +5725,8 @@
       <numFmt numFmtId="165" formatCode="[$-10436]#,##0;\(#,##0\)"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFF0F0F0"/>
+          <bgColor rgb="FFF0F0F0"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -5759,8 +5765,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFF0F0F0"/>
+          <bgColor rgb="FFF0F0F0"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -5799,8 +5805,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFF0F0F0"/>
+          <bgColor rgb="FFF0F0F0"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -5840,8 +5846,8 @@
       <numFmt numFmtId="164" formatCode="[$-10409]mm/dd/yyyy"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFF0F0F0"/>
+          <bgColor rgb="FFF0F0F0"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -5881,8 +5887,8 @@
       <numFmt numFmtId="164" formatCode="[$-10409]mm/dd/yyyy"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFF0F0F0"/>
+          <bgColor rgb="FFF0F0F0"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -5922,8 +5928,8 @@
       <numFmt numFmtId="164" formatCode="[$-10409]mm/dd/yyyy"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFF0F0F0"/>
+          <bgColor rgb="FFF0F0F0"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -5962,8 +5968,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFF0F0F0"/>
+          <bgColor rgb="FFF0F0F0"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -6155,8 +6161,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:H1252" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
-  <autoFilter ref="A2:H1252" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:H1255" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
+  <autoFilter ref="A2:H1255" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -6540,7 +6546,7 @@
       </c>
       <c r="B3" s="5">
         <f>SUM('Detailed WARN Report '!G:G)</f>
-        <v>64871</v>
+        <v>65117</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -6549,7 +6555,7 @@
       </c>
       <c r="B4" s="5">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Permanent")</f>
-        <v>898</v>
+        <v>901</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -6607,7 +6613,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:H1252"/>
+  <dimension ref="A1:H1255"/>
   <sheetFormatPr defaultColWidth="26" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.88671875" bestFit="1" customWidth="1"/>
@@ -6622,7 +6628,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="99.6" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
-        <v>1743</v>
+        <v>1745</v>
       </c>
       <c r="D1" s="12"/>
       <c r="E1" s="6"/>
@@ -39154,6 +39160,84 @@
       </c>
       <c r="H1252" s="24" t="s">
         <v>1742</v>
+      </c>
+    </row>
+    <row r="1253" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1253" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1253" s="16">
+        <v>45362</v>
+      </c>
+      <c r="C1253" s="16">
+        <v>45363</v>
+      </c>
+      <c r="D1253" s="16">
+        <v>45426</v>
+      </c>
+      <c r="E1253" s="17" t="s">
+        <v>1743</v>
+      </c>
+      <c r="F1253" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1253" s="18">
+        <v>180</v>
+      </c>
+      <c r="H1253" s="19" t="s">
+        <v>1744</v>
+      </c>
+    </row>
+    <row r="1254" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1254" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1254" s="21">
+        <v>45352</v>
+      </c>
+      <c r="C1254" s="21">
+        <v>45364</v>
+      </c>
+      <c r="D1254" s="21">
+        <v>45417</v>
+      </c>
+      <c r="E1254" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1254" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1254" s="23">
+        <v>4</v>
+      </c>
+      <c r="H1254" s="24" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1255" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1255" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1255" s="16">
+        <v>45364</v>
+      </c>
+      <c r="C1255" s="16">
+        <v>45364</v>
+      </c>
+      <c r="D1255" s="16">
+        <v>45425</v>
+      </c>
+      <c r="E1255" s="17" t="s">
+        <v>929</v>
+      </c>
+      <c r="F1255" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1255" s="18">
+        <v>62</v>
+      </c>
+      <c r="H1255" s="19" t="s">
+        <v>930</v>
       </c>
     </row>
   </sheetData>
@@ -39295,13 +39379,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E0B8FB51-B098-43E0-A487-C18ABD58D49B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C87510FC-8C99-48AD-87AB-8602A216C518}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B791B9EE-5832-4464-904F-9E13CB938FB3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{31833EF0-F092-4116-B243-AA1E078425BC}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5E14D654-C8BE-4BB5-B904-64974860AA77}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F07E73E6-F064-4AA6-8776-1DACED7CFA2C}"/>
 </file>
--- a/data/warn-scraper/cache/ca/warn_report1.xlsx
+++ b/data/warn-scraper/cache/ca/warn_report1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\WSB-CO\BPAC\Policy &amp; Program Communications Group\Communications Unit\Website Management\5. WARN (Worker Adjustment and Retraining Notification) Updates\2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1539F0F0-2B4E-4DB4-AC6B-CF90A61F0501}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B9F1AE6-55A6-4AD3-83E3-F40C4F075BB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="39675" yWindow="2325" windowWidth="15405" windowHeight="11430" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5035" uniqueCount="1746">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5071" uniqueCount="1760">
   <si>
     <t>County/Parish</t>
   </si>
@@ -5339,6 +5339,48 @@
     <t>5201 Great America Parkway, Suite 320, #3221  Santa Clara CA 95054</t>
   </si>
   <si>
+    <t>PKL Services Inc</t>
+  </si>
+  <si>
+    <t>VMFAT-101, Hanger 3, Bldg. 9500, MCAS  Miramar CA 92145</t>
+  </si>
+  <si>
+    <t>Watermark Services IV, LLC</t>
+  </si>
+  <si>
+    <t>2750 Geary Blvd  San Francisco CA 94118</t>
+  </si>
+  <si>
+    <t>Shadow Holdings, LLC dba Bright Innovation Labs</t>
+  </si>
+  <si>
+    <t>26455 Ruether Ave  Santa Clarita CA 91350</t>
+  </si>
+  <si>
+    <t>Bristol Myers Squibb</t>
+  </si>
+  <si>
+    <t>3545 Cray Court  San Diego CA 92121</t>
+  </si>
+  <si>
+    <t>Scripps Health</t>
+  </si>
+  <si>
+    <t>10790 Rancho Bernardo Road  San Diego CA 92127</t>
+  </si>
+  <si>
+    <t>435 H Street  Chula Vista CA 91910</t>
+  </si>
+  <si>
+    <t>4080 Douglas Blvd  Granite Bay CA 95746</t>
+  </si>
+  <si>
+    <t>The Hills Hotel</t>
+  </si>
+  <si>
+    <t>25205 La Paz Road  Laguna Hills CA 92653</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">WARN REPORT - </t>
     </r>
@@ -5350,7 +5392,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>07/01/23 to 03/13/24</t>
+      <t>07/01/23 to 03/18/24</t>
     </r>
     <r>
       <rPr>
@@ -5370,7 +5412,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>A detailed WARN summary by county and filtered according to received date. Table Spans cells A2 through H1255.</t>
+      <t>A detailed WARN summary by county and filtered according to received date. Table Spans cells A2 through H1264.</t>
     </r>
   </si>
 </sst>
@@ -5684,8 +5726,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF0F0F0"/>
-          <bgColor rgb="FFF0F0F0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -5725,8 +5767,8 @@
       <numFmt numFmtId="165" formatCode="[$-10436]#,##0;\(#,##0\)"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF0F0F0"/>
-          <bgColor rgb="FFF0F0F0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -5765,8 +5807,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF0F0F0"/>
-          <bgColor rgb="FFF0F0F0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -5805,8 +5847,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF0F0F0"/>
-          <bgColor rgb="FFF0F0F0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -5846,8 +5888,8 @@
       <numFmt numFmtId="164" formatCode="[$-10409]mm/dd/yyyy"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF0F0F0"/>
-          <bgColor rgb="FFF0F0F0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -5887,8 +5929,8 @@
       <numFmt numFmtId="164" formatCode="[$-10409]mm/dd/yyyy"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF0F0F0"/>
-          <bgColor rgb="FFF0F0F0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -5928,8 +5970,8 @@
       <numFmt numFmtId="164" formatCode="[$-10409]mm/dd/yyyy"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF0F0F0"/>
-          <bgColor rgb="FFF0F0F0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -5968,8 +6010,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF0F0F0"/>
-          <bgColor rgb="FFF0F0F0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -6161,8 +6203,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:H1255" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
-  <autoFilter ref="A2:H1255" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:H1264" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
+  <autoFilter ref="A2:H1264" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -6546,7 +6588,7 @@
       </c>
       <c r="B3" s="5">
         <f>SUM('Detailed WARN Report '!G:G)</f>
-        <v>65117</v>
+        <v>65812</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -6555,7 +6597,7 @@
       </c>
       <c r="B4" s="5">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Permanent")</f>
-        <v>901</v>
+        <v>909</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -6581,7 +6623,7 @@
       </c>
       <c r="B7" s="5">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Permanent")</f>
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -6613,7 +6655,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:H1255"/>
+  <dimension ref="A1:H1264"/>
   <sheetFormatPr defaultColWidth="26" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.88671875" bestFit="1" customWidth="1"/>
@@ -6628,7 +6670,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="99.6" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
-        <v>1745</v>
+        <v>1759</v>
       </c>
       <c r="D1" s="12"/>
       <c r="E1" s="6"/>
@@ -30010,7 +30052,7 @@
         <v>1262</v>
       </c>
     </row>
-    <row r="901" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="901" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A901" s="15" t="s">
         <v>5</v>
       </c>
@@ -39238,6 +39280,240 @@
       </c>
       <c r="H1255" s="19" t="s">
         <v>930</v>
+      </c>
+    </row>
+    <row r="1256" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1256" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1256" s="21">
+        <v>45351</v>
+      </c>
+      <c r="C1256" s="21">
+        <v>45365</v>
+      </c>
+      <c r="D1256" s="21">
+        <v>45412</v>
+      </c>
+      <c r="E1256" s="22" t="s">
+        <v>1745</v>
+      </c>
+      <c r="F1256" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1256" s="23">
+        <v>89</v>
+      </c>
+      <c r="H1256" s="24" t="s">
+        <v>1746</v>
+      </c>
+    </row>
+    <row r="1257" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1257" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1257" s="16">
+        <v>45352</v>
+      </c>
+      <c r="C1257" s="16">
+        <v>45365</v>
+      </c>
+      <c r="D1257" s="16">
+        <v>45412</v>
+      </c>
+      <c r="E1257" s="17" t="s">
+        <v>1747</v>
+      </c>
+      <c r="F1257" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1257" s="18">
+        <v>41</v>
+      </c>
+      <c r="H1257" s="19" t="s">
+        <v>1748</v>
+      </c>
+    </row>
+    <row r="1258" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1258" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1258" s="21">
+        <v>45355</v>
+      </c>
+      <c r="C1258" s="21">
+        <v>45366</v>
+      </c>
+      <c r="D1258" s="21">
+        <v>45429</v>
+      </c>
+      <c r="E1258" s="22" t="s">
+        <v>1749</v>
+      </c>
+      <c r="F1258" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1258" s="23">
+        <v>8</v>
+      </c>
+      <c r="H1258" s="24" t="s">
+        <v>1750</v>
+      </c>
+    </row>
+    <row r="1259" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1259" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1259" s="16">
+        <v>45365</v>
+      </c>
+      <c r="C1259" s="16">
+        <v>45366</v>
+      </c>
+      <c r="D1259" s="16">
+        <v>45404</v>
+      </c>
+      <c r="E1259" s="17" t="s">
+        <v>1751</v>
+      </c>
+      <c r="F1259" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1259" s="18">
+        <v>252</v>
+      </c>
+      <c r="H1259" s="19" t="s">
+        <v>1752</v>
+      </c>
+    </row>
+    <row r="1260" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1260" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1260" s="21">
+        <v>45365</v>
+      </c>
+      <c r="C1260" s="21">
+        <v>45366</v>
+      </c>
+      <c r="D1260" s="21">
+        <v>45425</v>
+      </c>
+      <c r="E1260" s="22" t="s">
+        <v>1753</v>
+      </c>
+      <c r="F1260" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1260" s="23">
+        <v>13</v>
+      </c>
+      <c r="H1260" s="24" t="s">
+        <v>1754</v>
+      </c>
+    </row>
+    <row r="1261" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1261" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1261" s="16">
+        <v>45365</v>
+      </c>
+      <c r="C1261" s="16">
+        <v>45366</v>
+      </c>
+      <c r="D1261" s="16">
+        <v>45466</v>
+      </c>
+      <c r="E1261" s="17" t="s">
+        <v>1753</v>
+      </c>
+      <c r="F1261" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1261" s="18">
+        <v>134</v>
+      </c>
+      <c r="H1261" s="19" t="s">
+        <v>1755</v>
+      </c>
+    </row>
+    <row r="1262" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1262" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1262" s="21">
+        <v>45365</v>
+      </c>
+      <c r="C1262" s="21">
+        <v>45369</v>
+      </c>
+      <c r="D1262" s="21">
+        <v>45457</v>
+      </c>
+      <c r="E1262" s="22" t="s">
+        <v>1371</v>
+      </c>
+      <c r="F1262" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1262" s="23">
+        <v>79</v>
+      </c>
+      <c r="H1262" s="24" t="s">
+        <v>1756</v>
+      </c>
+    </row>
+    <row r="1263" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1263" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1263" s="16">
+        <v>45366</v>
+      </c>
+      <c r="C1263" s="16">
+        <v>45369</v>
+      </c>
+      <c r="D1263" s="16">
+        <v>45429</v>
+      </c>
+      <c r="E1263" s="17" t="s">
+        <v>1757</v>
+      </c>
+      <c r="F1263" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1263" s="18">
+        <v>73</v>
+      </c>
+      <c r="H1263" s="19" t="s">
+        <v>1758</v>
+      </c>
+    </row>
+    <row r="1264" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1264" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1264" s="21">
+        <v>45366</v>
+      </c>
+      <c r="C1264" s="21">
+        <v>45369</v>
+      </c>
+      <c r="D1264" s="21">
+        <v>45366</v>
+      </c>
+      <c r="E1264" s="22" t="s">
+        <v>1094</v>
+      </c>
+      <c r="F1264" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1264" s="23">
+        <v>6</v>
+      </c>
+      <c r="H1264" s="24" t="s">
+        <v>1095</v>
       </c>
     </row>
   </sheetData>
@@ -39379,13 +39655,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C87510FC-8C99-48AD-87AB-8602A216C518}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{720AA53D-F131-4DFA-8DC6-452A5B121959}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{31833EF0-F092-4116-B243-AA1E078425BC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{685088B4-4029-49C3-9FC5-5C80D3122F5F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F07E73E6-F064-4AA6-8776-1DACED7CFA2C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A59EE633-2677-4A79-B575-F0331E61247D}"/>
 </file>
--- a/data/warn-scraper/cache/ca/warn_report1.xlsx
+++ b/data/warn-scraper/cache/ca/warn_report1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\WSB-CO\BPAC\Policy &amp; Program Communications Group\Communications Unit\Website Management\5. WARN (Worker Adjustment and Retraining Notification) Updates\2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B9F1AE6-55A6-4AD3-83E3-F40C4F075BB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63789D15-4ABA-403A-A3A8-B626CA6CFFFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="39675" yWindow="2325" windowWidth="15405" windowHeight="11430" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5071" uniqueCount="1760">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5103" uniqueCount="1770">
   <si>
     <t>County/Parish</t>
   </si>
@@ -5381,6 +5381,36 @@
     <t>25205 La Paz Road  Laguna Hills CA 92653</t>
   </si>
   <si>
+    <t>Fashion Institute of Design &amp; Merchandising</t>
+  </si>
+  <si>
+    <t>Abbott Laboratories</t>
+  </si>
+  <si>
+    <t>2302 Courage Dr  Fairfield CA 94533</t>
+  </si>
+  <si>
+    <t>Northrop Grumman</t>
+  </si>
+  <si>
+    <t>1 Space Park Dr.  Redondo Beach CA 90278</t>
+  </si>
+  <si>
+    <t>1 Space Park Drive  Manhattan Beach CA 90266</t>
+  </si>
+  <si>
+    <t>500 North Douglas  El Segundo CA 90245</t>
+  </si>
+  <si>
+    <t>815 Hornet Way  El Segundo CA 90245</t>
+  </si>
+  <si>
+    <t>400 Continental Drive  El Segundo CA 90245</t>
+  </si>
+  <si>
+    <t>1100 W. Hollyvale St.  Azusa CA 91702</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">WARN REPORT - </t>
     </r>
@@ -5392,7 +5422,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>07/01/23 to 03/18/24</t>
+      <t>07/01/23 to 03/20/24</t>
     </r>
     <r>
       <rPr>
@@ -5412,7 +5442,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>A detailed WARN summary by county and filtered according to received date. Table Spans cells A2 through H1264.</t>
+      <t>A detailed WARN summary by county and filtered according to received date. Table Spans cells A2 through H1272.</t>
     </r>
   </si>
 </sst>
@@ -5726,8 +5756,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFF0F0F0"/>
+          <bgColor rgb="FFF0F0F0"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -5767,8 +5797,8 @@
       <numFmt numFmtId="165" formatCode="[$-10436]#,##0;\(#,##0\)"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFF0F0F0"/>
+          <bgColor rgb="FFF0F0F0"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -5807,8 +5837,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFF0F0F0"/>
+          <bgColor rgb="FFF0F0F0"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -5847,8 +5877,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFF0F0F0"/>
+          <bgColor rgb="FFF0F0F0"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -5888,8 +5918,8 @@
       <numFmt numFmtId="164" formatCode="[$-10409]mm/dd/yyyy"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFF0F0F0"/>
+          <bgColor rgb="FFF0F0F0"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -5929,8 +5959,8 @@
       <numFmt numFmtId="164" formatCode="[$-10409]mm/dd/yyyy"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFF0F0F0"/>
+          <bgColor rgb="FFF0F0F0"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -5970,8 +6000,8 @@
       <numFmt numFmtId="164" formatCode="[$-10409]mm/dd/yyyy"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFF0F0F0"/>
+          <bgColor rgb="FFF0F0F0"/>
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -6010,8 +6040,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFF0F0F0"/>
+          <bgColor rgb="FFF0F0F0"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
@@ -6203,8 +6233,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:H1264" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
-  <autoFilter ref="A2:H1264" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:H1272" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
+  <autoFilter ref="A2:H1272" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -6588,7 +6618,7 @@
       </c>
       <c r="B3" s="5">
         <f>SUM('Detailed WARN Report '!G:G)</f>
-        <v>65812</v>
+        <v>67171</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -6597,7 +6627,7 @@
       </c>
       <c r="B4" s="5">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Permanent")</f>
-        <v>909</v>
+        <v>916</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -6623,7 +6653,7 @@
       </c>
       <c r="B7" s="5">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Permanent")</f>
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -6655,7 +6685,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:H1264"/>
+  <dimension ref="A1:H1272"/>
   <sheetFormatPr defaultColWidth="26" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.88671875" bestFit="1" customWidth="1"/>
@@ -6670,7 +6700,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="99.6" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
-        <v>1759</v>
+        <v>1769</v>
       </c>
       <c r="D1" s="12"/>
       <c r="E1" s="6"/>
@@ -22367,7 +22397,7 @@
         <v>45267</v>
       </c>
       <c r="D605" s="16">
-        <v>45369</v>
+        <v>45412</v>
       </c>
       <c r="E605" s="17" t="s">
         <v>866</v>
@@ -39514,6 +39544,214 @@
       </c>
       <c r="H1264" s="24" t="s">
         <v>1095</v>
+      </c>
+    </row>
+    <row r="1265" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1265" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1265" s="16">
+        <v>45369</v>
+      </c>
+      <c r="C1265" s="16">
+        <v>45371</v>
+      </c>
+      <c r="D1265" s="16">
+        <v>45460</v>
+      </c>
+      <c r="E1265" s="17" t="s">
+        <v>1759</v>
+      </c>
+      <c r="F1265" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1265" s="18">
+        <v>95</v>
+      </c>
+      <c r="H1265" s="19" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="1266" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1266" s="20" t="s">
+        <v>211</v>
+      </c>
+      <c r="B1266" s="21">
+        <v>45370</v>
+      </c>
+      <c r="C1266" s="21">
+        <v>45371</v>
+      </c>
+      <c r="D1266" s="21">
+        <v>45430</v>
+      </c>
+      <c r="E1266" s="22" t="s">
+        <v>1760</v>
+      </c>
+      <c r="F1266" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1266" s="23">
+        <v>195</v>
+      </c>
+      <c r="H1266" s="24" t="s">
+        <v>1761</v>
+      </c>
+    </row>
+    <row r="1267" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1267" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1267" s="16">
+        <v>45355</v>
+      </c>
+      <c r="C1267" s="16">
+        <v>45371</v>
+      </c>
+      <c r="D1267" s="16">
+        <v>45411</v>
+      </c>
+      <c r="E1267" s="17" t="s">
+        <v>1762</v>
+      </c>
+      <c r="F1267" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1267" s="18">
+        <v>731</v>
+      </c>
+      <c r="H1267" s="19" t="s">
+        <v>1763</v>
+      </c>
+    </row>
+    <row r="1268" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1268" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1268" s="21">
+        <v>45355</v>
+      </c>
+      <c r="C1268" s="21">
+        <v>45371</v>
+      </c>
+      <c r="D1268" s="21">
+        <v>45411</v>
+      </c>
+      <c r="E1268" s="22" t="s">
+        <v>1762</v>
+      </c>
+      <c r="F1268" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1268" s="23">
+        <v>227</v>
+      </c>
+      <c r="H1268" s="24" t="s">
+        <v>1764</v>
+      </c>
+    </row>
+    <row r="1269" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1269" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1269" s="16">
+        <v>45355</v>
+      </c>
+      <c r="C1269" s="16">
+        <v>45371</v>
+      </c>
+      <c r="D1269" s="16">
+        <v>45411</v>
+      </c>
+      <c r="E1269" s="17" t="s">
+        <v>1762</v>
+      </c>
+      <c r="F1269" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1269" s="18">
+        <v>3</v>
+      </c>
+      <c r="H1269" s="19" t="s">
+        <v>1765</v>
+      </c>
+    </row>
+    <row r="1270" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1270" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1270" s="21">
+        <v>45355</v>
+      </c>
+      <c r="C1270" s="21">
+        <v>45371</v>
+      </c>
+      <c r="D1270" s="21">
+        <v>45411</v>
+      </c>
+      <c r="E1270" s="22" t="s">
+        <v>1762</v>
+      </c>
+      <c r="F1270" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1270" s="23">
+        <v>2</v>
+      </c>
+      <c r="H1270" s="24" t="s">
+        <v>1766</v>
+      </c>
+    </row>
+    <row r="1271" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1271" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1271" s="16">
+        <v>45355</v>
+      </c>
+      <c r="C1271" s="16">
+        <v>45371</v>
+      </c>
+      <c r="D1271" s="16">
+        <v>45411</v>
+      </c>
+      <c r="E1271" s="17" t="s">
+        <v>1762</v>
+      </c>
+      <c r="F1271" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1271" s="18">
+        <v>1</v>
+      </c>
+      <c r="H1271" s="19" t="s">
+        <v>1767</v>
+      </c>
+    </row>
+    <row r="1272" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1272" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1272" s="21">
+        <v>45355</v>
+      </c>
+      <c r="C1272" s="21">
+        <v>45371</v>
+      </c>
+      <c r="D1272" s="21">
+        <v>45411</v>
+      </c>
+      <c r="E1272" s="22" t="s">
+        <v>1762</v>
+      </c>
+      <c r="F1272" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1272" s="23">
+        <v>105</v>
+      </c>
+      <c r="H1272" s="24" t="s">
+        <v>1768</v>
       </c>
     </row>
   </sheetData>
@@ -39655,13 +39893,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{720AA53D-F131-4DFA-8DC6-452A5B121959}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{98DB9D66-E85F-460D-9A0B-2307F99CFF85}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{685088B4-4029-49C3-9FC5-5C80D3122F5F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3AD512D1-4D5D-4D79-A3E1-7E6D140EEF93}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A59EE633-2677-4A79-B575-F0331E61247D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7A9FB6AF-F5B1-45F4-B4E3-57121A94FDFD}"/>
 </file>
--- a/data/warn-scraper/cache/ca/warn_report1.xlsx
+++ b/data/warn-scraper/cache/ca/warn_report1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\entshare3\JS-Data\WSB-CO\BPAC\Policy &amp; Program Communications Group\Communications Unit\Website Management\5. WARN (Worker Adjustment and Retraining Notification) Updates\2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02339EE4-6F07-4B53-91F6-EA9EB3E47952}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EFC2745D-5A94-4E77-83CB-F46229CF52D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="751" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="751" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
   <sheets>
     <sheet name="Index" sheetId="3" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3841" uniqueCount="1087">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3861" uniqueCount="1091">
   <si>
     <t>County/Parish</t>
   </si>
@@ -3320,8 +3320,83 @@
     <t>2004 E. Park Place, Unit K  El Segundo CA 90245</t>
   </si>
   <si>
+    <t>Owens Valley Career Development Center</t>
+  </si>
+  <si>
+    <t>37190 Jose Basin Road  Auberry CA 93602</t>
+  </si>
+  <si>
+    <t>ACLU of Southern California</t>
+  </si>
+  <si>
+    <t>1313 W 8th Street, #200  Los Angeles CA 90017</t>
+  </si>
+  <si>
+    <t>Draegers Supermarkets</t>
+  </si>
+  <si>
+    <t>222 E. Fourth St.  San Mateo CA 94401</t>
+  </si>
+  <si>
+    <t>IGM Biosciences, Inc.</t>
+  </si>
+  <si>
+    <t>325 East Middlefield Road  Mountain View CA 94043</t>
+  </si>
+  <si>
+    <t>5918 Stoneridge Mall Road  Pleasanton CA 94588</t>
+  </si>
+  <si>
+    <t>1115 Dublin Canyon Road  Pleasanton CA 94588</t>
+  </si>
+  <si>
+    <t>Columbus Manufacturing, Inc., a wholly-owned subsidiary of the Hormel Foods Corporation</t>
+  </si>
+  <si>
+    <t>30977 San Antonio Street  Hayward CA 94544</t>
+  </si>
+  <si>
+    <t>22001 Ventura Blvd  Woodland Hills CA 91364</t>
+  </si>
+  <si>
+    <t>Placer Labs Inc.</t>
+  </si>
+  <si>
+    <t>440 N. Barranca Ave #1277  Covina CA 91723</t>
+  </si>
+  <si>
+    <t>Medical Manufacturing Technologies / Interface Catheter Solutions</t>
+  </si>
+  <si>
+    <t>27752 El Lazo Road  Laguna Niguel CA 92677</t>
+  </si>
+  <si>
+    <t>Ortho Organizers Inc.</t>
+  </si>
+  <si>
+    <t>1822 Aston Avenue  Carlsbad CA 92008</t>
+  </si>
+  <si>
+    <t>Aurora Solar Inc.</t>
+  </si>
+  <si>
+    <t>153 Kearny St., 5th Floor  San Francisco CA 94108</t>
+  </si>
+  <si>
+    <t>Renesas Electronics Corporation</t>
+  </si>
+  <si>
+    <t>6024 Silver Creek Valley Road  San Jose CA 95138</t>
+  </si>
+  <si>
+    <t>1001 Murphy Ranch Road  Milpitas CA 95035</t>
+  </si>
+  <si>
+    <t>6200 Franklin Boulevard  Sacramento CA 95824</t>
+  </si>
+  <si>
     <r>
-      <t xml:space="preserve">WARN REPORT - 01/01/2023 - 01/15/2025
+      <t xml:space="preserve">WARN REPORT - 01/01/2023 - 01/20/2025
 </t>
     </r>
     <r>
@@ -3335,69 +3410,6 @@
     </r>
   </si>
   <si>
-    <t>Owens Valley Career Development Center</t>
-  </si>
-  <si>
-    <t>37190 Jose Basin Road  Auberry CA 93602</t>
-  </si>
-  <si>
-    <t>ACLU of Southern California</t>
-  </si>
-  <si>
-    <t>1313 W 8th Street, #200  Los Angeles CA 90017</t>
-  </si>
-  <si>
-    <t>Draegers Supermarkets</t>
-  </si>
-  <si>
-    <t>222 E. Fourth St.  San Mateo CA 94401</t>
-  </si>
-  <si>
-    <t>IGM Biosciences, Inc.</t>
-  </si>
-  <si>
-    <t>325 East Middlefield Road  Mountain View CA 94043</t>
-  </si>
-  <si>
-    <t>5918 Stoneridge Mall Road  Pleasanton CA 94588</t>
-  </si>
-  <si>
-    <t>1115 Dublin Canyon Road  Pleasanton CA 94588</t>
-  </si>
-  <si>
-    <t>Columbus Manufacturing, Inc., a wholly-owned subsidiary of the Hormel Foods Corporation</t>
-  </si>
-  <si>
-    <t>30977 San Antonio Street  Hayward CA 94544</t>
-  </si>
-  <si>
-    <t>22001 Ventura Blvd  Woodland Hills CA 91364</t>
-  </si>
-  <si>
-    <t>Placer Labs Inc.</t>
-  </si>
-  <si>
-    <t>440 N. Barranca Ave #1277  Covina CA 91723</t>
-  </si>
-  <si>
-    <t>Medical Manufacturing Technologies / Interface Catheter Solutions</t>
-  </si>
-  <si>
-    <t>27752 El Lazo Road  Laguna Niguel CA 92677</t>
-  </si>
-  <si>
-    <t>Ortho Organizers Inc.</t>
-  </si>
-  <si>
-    <t>1822 Aston Avenue  Carlsbad CA 92008</t>
-  </si>
-  <si>
-    <t>Aurora Solar Inc.</t>
-  </si>
-  <si>
-    <t>153 Kearny St., 5th Floor  San Francisco CA 94108</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">WARN REPORT - </t>
     </r>
@@ -3409,7 +3421,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>07/01/24 to 01/15/2025</t>
+      <t>07/01/24 to 01/20/2025</t>
     </r>
     <r>
       <rPr>
@@ -3429,7 +3441,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I756.</t>
+      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I760.</t>
     </r>
   </si>
 </sst>
@@ -4656,8 +4668,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I756" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
-  <autoFilter ref="A2:I756" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I760" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
+  <autoFilter ref="A2:I760" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -5011,37 +5023,37 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D341DFFF-02D2-4572-95F5-BB3221952133}">
   <dimension ref="A1:A6"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="74" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1" ht="135" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="21" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:1" ht="21" x14ac:dyDescent="0.35">
       <c r="A2" s="12" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
         <v>33</v>
       </c>
@@ -5060,18 +5072,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1832896D-8AFB-4FFC-957E-910308F3BC0C}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.453125" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.453125" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.42578125" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="76.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
         <v>20</v>
       </c>
@@ -5079,25 +5091,25 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B3" s="11">
         <f>SUM('Detailed WARN Report '!G:G)</f>
-        <v>42349</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+        <v>42517</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B4" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Permanent")</f>
-        <v>393</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>14</v>
       </c>
@@ -5106,7 +5118,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>15</v>
       </c>
@@ -5114,16 +5126,16 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B7" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Permanent")</f>
-        <v>331</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>17</v>
       </c>
@@ -5132,7 +5144,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>18</v>
       </c>
@@ -5153,26 +5165,26 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
   <dimension ref="A1:I766"/>
-  <sheetFormatPr defaultColWidth="102.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="102.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.7265625" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.7109375" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.81640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.453125" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="62.26953125" style="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.26953125" style="3" customWidth="1"/>
-    <col min="7" max="7" width="9.81640625" style="3" customWidth="1"/>
-    <col min="8" max="8" width="57.7265625" style="3" customWidth="1"/>
-    <col min="9" max="9" width="51.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.85546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.42578125" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="62.28515625" style="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.28515625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="9.85546875" style="3" customWidth="1"/>
+    <col min="8" max="8" width="57.7109375" style="3" customWidth="1"/>
+    <col min="9" max="9" width="51.85546875" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="100" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" ht="102" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
-        <v>1086</v>
+        <v>1090</v>
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:9" ht="24" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A2" s="29" t="s">
         <v>0</v>
       </c>
@@ -5201,7 +5213,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="26" t="s">
         <v>5</v>
       </c>
@@ -5230,7 +5242,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="26" t="s">
         <v>21</v>
       </c>
@@ -5259,7 +5271,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="26" t="s">
         <v>7</v>
       </c>
@@ -5288,7 +5300,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="26" t="s">
         <v>5</v>
       </c>
@@ -5317,7 +5329,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="26" t="s">
         <v>6</v>
       </c>
@@ -5346,7 +5358,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="26" t="s">
         <v>6</v>
       </c>
@@ -5375,7 +5387,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="26" t="s">
         <v>49</v>
       </c>
@@ -5404,7 +5416,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="26" t="s">
         <v>23</v>
       </c>
@@ -5433,7 +5445,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="26" t="s">
         <v>22</v>
       </c>
@@ -5462,7 +5474,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="26" t="s">
         <v>22</v>
       </c>
@@ -5491,7 +5503,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="26" t="s">
         <v>5</v>
       </c>
@@ -5520,7 +5532,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="26" t="s">
         <v>21</v>
       </c>
@@ -5549,7 +5561,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="26" t="s">
         <v>6</v>
       </c>
@@ -5578,7 +5590,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="26" t="s">
         <v>62</v>
       </c>
@@ -5607,7 +5619,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="26" t="s">
         <v>6</v>
       </c>
@@ -5636,7 +5648,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="26" t="s">
         <v>6</v>
       </c>
@@ -5665,7 +5677,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="26" t="s">
         <v>67</v>
       </c>
@@ -5694,7 +5706,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="26" t="s">
         <v>22</v>
       </c>
@@ -5723,7 +5735,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="26" t="s">
         <v>6</v>
       </c>
@@ -5752,7 +5764,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="26" t="s">
         <v>6</v>
       </c>
@@ -5781,7 +5793,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="26" t="s">
         <v>5</v>
       </c>
@@ -5810,7 +5822,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="26" t="s">
         <v>5</v>
       </c>
@@ -5839,7 +5851,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="26" t="s">
         <v>79</v>
       </c>
@@ -5868,7 +5880,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="26" t="s">
         <v>21</v>
       </c>
@@ -5897,7 +5909,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="26" t="s">
         <v>84</v>
       </c>
@@ -5926,7 +5938,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="26" t="s">
         <v>86</v>
       </c>
@@ -5955,7 +5967,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="26" t="s">
         <v>22</v>
       </c>
@@ -5984,7 +5996,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="26" t="s">
         <v>5</v>
       </c>
@@ -6013,7 +6025,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="26" t="s">
         <v>5</v>
       </c>
@@ -6042,7 +6054,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="26" t="s">
         <v>5</v>
       </c>
@@ -6071,7 +6083,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="26" t="s">
         <v>23</v>
       </c>
@@ -6100,7 +6112,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="26" t="s">
         <v>23</v>
       </c>
@@ -6129,7 +6141,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="26" t="s">
         <v>5</v>
       </c>
@@ -6158,7 +6170,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="26" t="s">
         <v>5</v>
       </c>
@@ -6187,7 +6199,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="26" t="s">
         <v>5</v>
       </c>
@@ -6216,7 +6228,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="26" t="s">
         <v>5</v>
       </c>
@@ -6245,7 +6257,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="26" t="s">
         <v>5</v>
       </c>
@@ -6274,7 +6286,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="26" t="s">
         <v>5</v>
       </c>
@@ -6303,7 +6315,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="26" t="s">
         <v>5</v>
       </c>
@@ -6332,7 +6344,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="26" t="s">
         <v>5</v>
       </c>
@@ -6361,7 +6373,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="26" t="s">
         <v>21</v>
       </c>
@@ -6390,7 +6402,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="26" t="s">
         <v>106</v>
       </c>
@@ -6419,7 +6431,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="26" t="s">
         <v>106</v>
       </c>
@@ -6448,7 +6460,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="26" t="s">
         <v>22</v>
       </c>
@@ -6477,7 +6489,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="26" t="s">
         <v>22</v>
       </c>
@@ -6506,7 +6518,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="26" t="s">
         <v>22</v>
       </c>
@@ -6535,7 +6547,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="26" t="s">
         <v>22</v>
       </c>
@@ -6564,7 +6576,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="26" t="s">
         <v>114</v>
       </c>
@@ -6593,7 +6605,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="26" t="s">
         <v>5</v>
       </c>
@@ -6622,7 +6634,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="26" t="s">
         <v>5</v>
       </c>
@@ -6651,7 +6663,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="26" t="s">
         <v>5</v>
       </c>
@@ -6680,7 +6692,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="26" t="s">
         <v>79</v>
       </c>
@@ -6709,7 +6721,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="26" t="s">
         <v>79</v>
       </c>
@@ -6738,7 +6750,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="26" t="s">
         <v>5</v>
       </c>
@@ -6767,7 +6779,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="26" t="s">
         <v>5</v>
       </c>
@@ -6796,7 +6808,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="26" t="s">
         <v>5</v>
       </c>
@@ -6825,7 +6837,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="26" t="s">
         <v>84</v>
       </c>
@@ -6854,7 +6866,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="26" t="s">
         <v>5</v>
       </c>
@@ -6883,7 +6895,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="26" t="s">
         <v>23</v>
       </c>
@@ -6912,7 +6924,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="26" t="s">
         <v>23</v>
       </c>
@@ -6941,7 +6953,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="26" t="s">
         <v>23</v>
       </c>
@@ -6970,7 +6982,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="26" t="s">
         <v>23</v>
       </c>
@@ -6999,7 +7011,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="26" t="s">
         <v>49</v>
       </c>
@@ -7028,7 +7040,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="26" t="s">
         <v>139</v>
       </c>
@@ -7057,7 +7069,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="26" t="s">
         <v>139</v>
       </c>
@@ -7086,7 +7098,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="26" t="s">
         <v>142</v>
       </c>
@@ -7115,7 +7127,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="26" t="s">
         <v>144</v>
       </c>
@@ -7144,7 +7156,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="26" t="s">
         <v>144</v>
       </c>
@@ -7173,7 +7185,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="26" t="s">
         <v>144</v>
       </c>
@@ -7202,7 +7214,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="26" t="s">
         <v>144</v>
       </c>
@@ -7231,7 +7243,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="26" t="s">
         <v>144</v>
       </c>
@@ -7260,7 +7272,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="26" t="s">
         <v>144</v>
       </c>
@@ -7289,7 +7301,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="26" t="s">
         <v>23</v>
       </c>
@@ -7318,7 +7330,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="26" t="s">
         <v>21</v>
       </c>
@@ -7347,7 +7359,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="26" t="s">
         <v>155</v>
       </c>
@@ -7376,7 +7388,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="26" t="s">
         <v>23</v>
       </c>
@@ -7405,7 +7417,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="26" t="s">
         <v>23</v>
       </c>
@@ -7434,7 +7446,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="26" t="s">
         <v>79</v>
       </c>
@@ -7463,7 +7475,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="26" t="s">
         <v>5</v>
       </c>
@@ -7492,7 +7504,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="26" t="s">
         <v>21</v>
       </c>
@@ -7521,7 +7533,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="26" t="s">
         <v>165</v>
       </c>
@@ -7550,7 +7562,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="26" t="s">
         <v>22</v>
       </c>
@@ -7579,7 +7591,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="26" t="s">
         <v>6</v>
       </c>
@@ -7608,7 +7620,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="26" t="s">
         <v>62</v>
       </c>
@@ -7637,7 +7649,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="26" t="s">
         <v>84</v>
       </c>
@@ -7666,7 +7678,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="26" t="s">
         <v>62</v>
       </c>
@@ -7695,7 +7707,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="26" t="s">
         <v>21</v>
       </c>
@@ -7724,7 +7736,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="26" t="s">
         <v>114</v>
       </c>
@@ -7753,7 +7765,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="26" t="s">
         <v>79</v>
       </c>
@@ -7782,7 +7794,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="26" t="s">
         <v>79</v>
       </c>
@@ -7811,7 +7823,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" s="26" t="s">
         <v>7</v>
       </c>
@@ -7840,7 +7852,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="26" t="s">
         <v>5</v>
       </c>
@@ -7869,7 +7881,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" s="26" t="s">
         <v>5</v>
       </c>
@@ -7898,7 +7910,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="26" t="s">
         <v>5</v>
       </c>
@@ -7927,7 +7939,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" s="26" t="s">
         <v>5</v>
       </c>
@@ -7956,7 +7968,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" s="26" t="s">
         <v>5</v>
       </c>
@@ -7985,7 +7997,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" s="26" t="s">
         <v>5</v>
       </c>
@@ -8014,7 +8026,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" s="26" t="s">
         <v>5</v>
       </c>
@@ -8043,7 +8055,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" s="26" t="s">
         <v>86</v>
       </c>
@@ -8072,7 +8084,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" s="26" t="s">
         <v>62</v>
       </c>
@@ -8101,7 +8113,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" s="26" t="s">
         <v>62</v>
       </c>
@@ -8130,7 +8142,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" s="26" t="s">
         <v>62</v>
       </c>
@@ -8159,7 +8171,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" s="26" t="s">
         <v>62</v>
       </c>
@@ -8188,7 +8200,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" s="26" t="s">
         <v>165</v>
       </c>
@@ -8217,7 +8229,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" s="26" t="s">
         <v>6</v>
       </c>
@@ -8246,7 +8258,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" s="26" t="s">
         <v>6</v>
       </c>
@@ -8275,7 +8287,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" s="26" t="s">
         <v>84</v>
       </c>
@@ -8304,7 +8316,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" s="26" t="s">
         <v>6</v>
       </c>
@@ -8333,7 +8345,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" s="26" t="s">
         <v>6</v>
       </c>
@@ -8362,7 +8374,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" s="26" t="s">
         <v>84</v>
       </c>
@@ -8391,7 +8403,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" s="26" t="s">
         <v>21</v>
       </c>
@@ -8420,7 +8432,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" s="26" t="s">
         <v>5</v>
       </c>
@@ -8449,7 +8461,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" s="26" t="s">
         <v>84</v>
       </c>
@@ -8478,7 +8490,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" s="26" t="s">
         <v>21</v>
       </c>
@@ -8507,7 +8519,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" s="26" t="s">
         <v>242</v>
       </c>
@@ -8536,7 +8548,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" s="26" t="s">
         <v>22</v>
       </c>
@@ -8565,7 +8577,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" s="26" t="s">
         <v>5</v>
       </c>
@@ -8594,7 +8606,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" s="26" t="s">
         <v>23</v>
       </c>
@@ -8623,7 +8635,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" s="26" t="s">
         <v>5</v>
       </c>
@@ -8652,7 +8664,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" s="26" t="s">
         <v>22</v>
       </c>
@@ -8681,7 +8693,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" s="26" t="s">
         <v>114</v>
       </c>
@@ -8710,7 +8722,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" s="26" t="s">
         <v>84</v>
       </c>
@@ -8739,7 +8751,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" s="26" t="s">
         <v>247</v>
       </c>
@@ -8768,7 +8780,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" s="32" t="s">
         <v>5</v>
       </c>
@@ -8797,7 +8809,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" s="32" t="s">
         <v>86</v>
       </c>
@@ -8826,7 +8838,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" s="32" t="s">
         <v>62</v>
       </c>
@@ -8855,7 +8867,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" s="32" t="s">
         <v>165</v>
       </c>
@@ -8884,7 +8896,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" s="32" t="s">
         <v>22</v>
       </c>
@@ -8913,7 +8925,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" s="33" t="s">
         <v>6</v>
       </c>
@@ -8942,7 +8954,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" s="39" t="s">
         <v>114</v>
       </c>
@@ -8971,7 +8983,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" s="39" t="s">
         <v>5</v>
       </c>
@@ -9000,7 +9012,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" s="39" t="s">
         <v>5</v>
       </c>
@@ -9029,7 +9041,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" s="39" t="s">
         <v>5</v>
       </c>
@@ -9058,7 +9070,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" s="39" t="s">
         <v>21</v>
       </c>
@@ -9087,7 +9099,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" s="39" t="s">
         <v>23</v>
       </c>
@@ -9116,7 +9128,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" s="39" t="s">
         <v>23</v>
       </c>
@@ -9145,7 +9157,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" s="39" t="s">
         <v>6</v>
       </c>
@@ -9174,7 +9186,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" s="39" t="s">
         <v>79</v>
       </c>
@@ -9203,7 +9215,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" s="39" t="s">
         <v>84</v>
       </c>
@@ -9232,7 +9244,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" s="39" t="s">
         <v>6</v>
       </c>
@@ -9261,7 +9273,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" s="39" t="s">
         <v>62</v>
       </c>
@@ -9290,7 +9302,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" s="39" t="s">
         <v>289</v>
       </c>
@@ -9319,7 +9331,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" s="39" t="s">
         <v>292</v>
       </c>
@@ -9348,7 +9360,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" s="39" t="s">
         <v>5</v>
       </c>
@@ -9377,7 +9389,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" s="39" t="s">
         <v>86</v>
       </c>
@@ -9406,7 +9418,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" s="39" t="s">
         <v>289</v>
       </c>
@@ -9435,7 +9447,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" s="39" t="s">
         <v>5</v>
       </c>
@@ -9464,7 +9476,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" s="39" t="s">
         <v>21</v>
       </c>
@@ -9493,7 +9505,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" s="39" t="s">
         <v>79</v>
       </c>
@@ -9522,7 +9534,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" s="39" t="s">
         <v>79</v>
       </c>
@@ -9551,7 +9563,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" s="39" t="s">
         <v>79</v>
       </c>
@@ -9580,7 +9592,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" s="39" t="s">
         <v>5</v>
       </c>
@@ -9609,7 +9621,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" s="39" t="s">
         <v>247</v>
       </c>
@@ -9638,7 +9650,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" s="39" t="s">
         <v>23</v>
       </c>
@@ -9667,7 +9679,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" s="39" t="s">
         <v>5</v>
       </c>
@@ -9696,7 +9708,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" s="39" t="s">
         <v>5</v>
       </c>
@@ -9725,7 +9737,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" s="39" t="s">
         <v>5</v>
       </c>
@@ -9754,7 +9766,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" s="39" t="s">
         <v>5</v>
       </c>
@@ -9783,7 +9795,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161" s="39" t="s">
         <v>5</v>
       </c>
@@ -9812,7 +9824,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162" s="39" t="s">
         <v>84</v>
       </c>
@@ -9841,7 +9853,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" s="39" t="s">
         <v>86</v>
       </c>
@@ -9870,7 +9882,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" s="39" t="s">
         <v>62</v>
       </c>
@@ -9899,7 +9911,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165" s="39" t="s">
         <v>292</v>
       </c>
@@ -9928,7 +9940,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166" s="39" t="s">
         <v>5</v>
       </c>
@@ -9957,7 +9969,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167" s="39" t="s">
         <v>21</v>
       </c>
@@ -9986,7 +9998,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168" s="39" t="s">
         <v>62</v>
       </c>
@@ -10015,7 +10027,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169" s="39" t="s">
         <v>62</v>
       </c>
@@ -10044,7 +10056,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170" s="39" t="s">
         <v>62</v>
       </c>
@@ -10073,7 +10085,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171" s="39" t="s">
         <v>62</v>
       </c>
@@ -10102,7 +10114,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" s="39" t="s">
         <v>6</v>
       </c>
@@ -10131,7 +10143,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" s="39" t="s">
         <v>5</v>
       </c>
@@ -10160,7 +10172,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" s="39" t="s">
         <v>5</v>
       </c>
@@ -10189,7 +10201,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" s="39" t="s">
         <v>5</v>
       </c>
@@ -10218,7 +10230,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176" s="39" t="s">
         <v>5</v>
       </c>
@@ -10247,7 +10259,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177" s="39" t="s">
         <v>5</v>
       </c>
@@ -10276,7 +10288,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178" s="39" t="s">
         <v>139</v>
       </c>
@@ -10305,7 +10317,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179" s="39" t="s">
         <v>344</v>
       </c>
@@ -10334,7 +10346,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180" s="39" t="s">
         <v>155</v>
       </c>
@@ -10363,7 +10375,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181" s="39" t="s">
         <v>22</v>
       </c>
@@ -10392,7 +10404,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182" s="39" t="s">
         <v>22</v>
       </c>
@@ -10421,7 +10433,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A183" s="39" t="s">
         <v>6</v>
       </c>
@@ -10450,7 +10462,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184" s="39" t="s">
         <v>352</v>
       </c>
@@ -10479,7 +10491,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A185" s="39" t="s">
         <v>352</v>
       </c>
@@ -10508,7 +10520,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A186" s="39" t="s">
         <v>144</v>
       </c>
@@ -10537,7 +10549,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A187" s="39" t="s">
         <v>23</v>
       </c>
@@ -10566,7 +10578,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A188" s="39" t="s">
         <v>5</v>
       </c>
@@ -10595,7 +10607,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A189" s="39" t="s">
         <v>21</v>
       </c>
@@ -10624,7 +10636,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A190" s="39" t="s">
         <v>21</v>
       </c>
@@ -10653,7 +10665,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A191" s="39" t="s">
         <v>84</v>
       </c>
@@ -10682,7 +10694,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A192" s="39" t="s">
         <v>62</v>
       </c>
@@ -10711,7 +10723,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A193" s="39" t="s">
         <v>22</v>
       </c>
@@ -10740,7 +10752,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A194" s="39" t="s">
         <v>22</v>
       </c>
@@ -10769,7 +10781,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A195" s="39" t="s">
         <v>6</v>
       </c>
@@ -10798,7 +10810,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A196" s="39" t="s">
         <v>289</v>
       </c>
@@ -10827,7 +10839,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A197" s="39" t="s">
         <v>22</v>
       </c>
@@ -10856,7 +10868,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A198" s="39" t="s">
         <v>23</v>
       </c>
@@ -10885,7 +10897,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A199" s="39" t="s">
         <v>5</v>
       </c>
@@ -10914,7 +10926,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A200" s="39" t="s">
         <v>21</v>
       </c>
@@ -10943,7 +10955,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A201" s="39" t="s">
         <v>6</v>
       </c>
@@ -10972,7 +10984,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A202" s="39" t="s">
         <v>6</v>
       </c>
@@ -11001,7 +11013,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A203" s="39" t="s">
         <v>6</v>
       </c>
@@ -11030,7 +11042,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A204" s="39" t="s">
         <v>383</v>
       </c>
@@ -11059,7 +11071,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A205" s="39" t="s">
         <v>5</v>
       </c>
@@ -11088,7 +11100,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A206" s="26" t="s">
         <v>22</v>
       </c>
@@ -11117,7 +11129,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A207" s="26" t="s">
         <v>6</v>
       </c>
@@ -11146,7 +11158,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A208" s="26" t="s">
         <v>84</v>
       </c>
@@ -11175,7 +11187,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209" s="26" t="s">
         <v>62</v>
       </c>
@@ -11204,7 +11216,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210" s="26" t="s">
         <v>106</v>
       </c>
@@ -11233,7 +11245,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211" s="26" t="s">
         <v>22</v>
       </c>
@@ -11262,7 +11274,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212" s="26" t="s">
         <v>5</v>
       </c>
@@ -11291,7 +11303,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" s="26" t="s">
         <v>5</v>
       </c>
@@ -11320,7 +11332,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214" s="26" t="s">
         <v>21</v>
       </c>
@@ -11349,7 +11361,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215" s="26" t="s">
         <v>21</v>
       </c>
@@ -11378,7 +11390,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A216" s="26" t="s">
         <v>23</v>
       </c>
@@ -11407,7 +11419,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217" s="26" t="s">
         <v>165</v>
       </c>
@@ -11436,7 +11448,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218" s="26" t="s">
         <v>22</v>
       </c>
@@ -11465,7 +11477,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A219" s="26" t="s">
         <v>22</v>
       </c>
@@ -11494,7 +11506,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220" s="26" t="s">
         <v>22</v>
       </c>
@@ -11523,7 +11535,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221" s="26" t="s">
         <v>247</v>
       </c>
@@ -11552,7 +11564,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A222" s="26" t="s">
         <v>84</v>
       </c>
@@ -11581,7 +11593,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223" s="49" t="s">
         <v>84</v>
       </c>
@@ -11610,7 +11622,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224" s="49" t="s">
         <v>62</v>
       </c>
@@ -11639,7 +11651,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A225" s="49" t="s">
         <v>62</v>
       </c>
@@ -11668,7 +11680,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A226" s="49" t="s">
         <v>62</v>
       </c>
@@ -11697,7 +11709,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A227" s="49" t="s">
         <v>415</v>
       </c>
@@ -11726,7 +11738,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A228" s="49" t="s">
         <v>23</v>
       </c>
@@ -11755,7 +11767,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A229" s="49" t="s">
         <v>21</v>
       </c>
@@ -11784,7 +11796,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A230" s="49" t="s">
         <v>5</v>
       </c>
@@ -11813,7 +11825,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A231" s="49" t="s">
         <v>23</v>
       </c>
@@ -11842,7 +11854,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A232" s="49" t="s">
         <v>23</v>
       </c>
@@ -11871,7 +11883,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A233" s="49" t="s">
         <v>23</v>
       </c>
@@ -11900,7 +11912,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A234" s="49" t="s">
         <v>23</v>
       </c>
@@ -11929,7 +11941,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A235" s="49" t="s">
         <v>23</v>
       </c>
@@ -11958,7 +11970,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A236" s="49" t="s">
         <v>79</v>
       </c>
@@ -11987,7 +11999,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A237" s="49" t="s">
         <v>5</v>
       </c>
@@ -12016,7 +12028,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A238" s="49" t="s">
         <v>5</v>
       </c>
@@ -12045,7 +12057,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A239" s="49" t="s">
         <v>5</v>
       </c>
@@ -12074,7 +12086,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A240" s="49" t="s">
         <v>5</v>
       </c>
@@ -12103,7 +12115,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A241" s="49" t="s">
         <v>5</v>
       </c>
@@ -12132,7 +12144,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A242" s="49" t="s">
         <v>21</v>
       </c>
@@ -12161,7 +12173,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A243" s="49" t="s">
         <v>106</v>
       </c>
@@ -12190,7 +12202,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A244" s="49" t="s">
         <v>106</v>
       </c>
@@ -12219,7 +12231,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A245" s="49" t="s">
         <v>165</v>
       </c>
@@ -12248,7 +12260,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A246" s="49" t="s">
         <v>165</v>
       </c>
@@ -12277,7 +12289,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A247" s="49" t="s">
         <v>86</v>
       </c>
@@ -12306,7 +12318,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A248" s="49" t="s">
         <v>144</v>
       </c>
@@ -12335,7 +12347,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A249" s="49" t="s">
         <v>5</v>
       </c>
@@ -12364,7 +12376,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A250" s="49" t="s">
         <v>5</v>
       </c>
@@ -12393,7 +12405,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A251" s="49" t="s">
         <v>5</v>
       </c>
@@ -12422,7 +12434,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A252" s="49" t="s">
         <v>62</v>
       </c>
@@ -12451,7 +12463,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A253" s="49" t="s">
         <v>79</v>
       </c>
@@ -12480,7 +12492,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A254" s="49" t="s">
         <v>292</v>
       </c>
@@ -12509,7 +12521,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A255" s="49" t="s">
         <v>5</v>
       </c>
@@ -12538,7 +12550,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A256" s="49" t="s">
         <v>5</v>
       </c>
@@ -12567,7 +12579,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A257" s="49" t="s">
         <v>5</v>
       </c>
@@ -12596,7 +12608,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A258" s="49" t="s">
         <v>5</v>
       </c>
@@ -12625,7 +12637,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A259" s="49" t="s">
         <v>6</v>
       </c>
@@ -12654,7 +12666,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A260" s="49" t="s">
         <v>453</v>
       </c>
@@ -12683,7 +12695,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A261" s="49" t="s">
         <v>292</v>
       </c>
@@ -12712,7 +12724,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A262" s="49" t="s">
         <v>453</v>
       </c>
@@ -12741,7 +12753,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A263" s="49" t="s">
         <v>23</v>
       </c>
@@ -12770,7 +12782,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A264" s="49" t="s">
         <v>5</v>
       </c>
@@ -12799,7 +12811,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A265" s="49" t="s">
         <v>5</v>
       </c>
@@ -12828,7 +12840,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A266" s="49" t="s">
         <v>5</v>
       </c>
@@ -12857,7 +12869,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A267" s="49" t="s">
         <v>62</v>
       </c>
@@ -12886,7 +12898,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A268" s="49" t="s">
         <v>106</v>
       </c>
@@ -12915,7 +12927,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A269" s="49" t="s">
         <v>22</v>
       </c>
@@ -12944,7 +12956,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A270" s="49" t="s">
         <v>144</v>
       </c>
@@ -12973,7 +12985,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A271" s="49" t="s">
         <v>5</v>
       </c>
@@ -13002,7 +13014,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A272" s="49" t="s">
         <v>5</v>
       </c>
@@ -13031,7 +13043,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A273" s="49" t="s">
         <v>21</v>
       </c>
@@ -13060,7 +13072,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A274" s="49" t="s">
         <v>106</v>
       </c>
@@ -13089,7 +13101,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A275" s="49" t="s">
         <v>6</v>
       </c>
@@ -13118,7 +13130,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A276" s="49" t="s">
         <v>62</v>
       </c>
@@ -13147,7 +13159,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A277" s="49" t="s">
         <v>62</v>
       </c>
@@ -13176,7 +13188,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A278" s="49" t="s">
         <v>242</v>
       </c>
@@ -13205,7 +13217,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A279" s="49" t="s">
         <v>292</v>
       </c>
@@ -13234,7 +13246,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A280" s="49" t="s">
         <v>482</v>
       </c>
@@ -13263,7 +13275,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A281" s="49" t="s">
         <v>247</v>
       </c>
@@ -13292,7 +13304,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A282" s="49" t="s">
         <v>23</v>
       </c>
@@ -13321,7 +13333,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A283" s="49" t="s">
         <v>487</v>
       </c>
@@ -13350,7 +13362,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A284" s="49" t="s">
         <v>487</v>
       </c>
@@ -13379,7 +13391,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A285" s="49" t="s">
         <v>5</v>
       </c>
@@ -13408,7 +13420,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A286" s="49" t="s">
         <v>5</v>
       </c>
@@ -13437,7 +13449,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A287" s="49" t="s">
         <v>5</v>
       </c>
@@ -13466,7 +13478,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A288" s="49" t="s">
         <v>165</v>
       </c>
@@ -13495,7 +13507,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A289" s="49" t="s">
         <v>114</v>
       </c>
@@ -13524,7 +13536,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A290" s="49" t="s">
         <v>62</v>
       </c>
@@ -13553,7 +13565,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A291" s="49" t="s">
         <v>21</v>
       </c>
@@ -13582,7 +13594,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A292" s="49" t="s">
         <v>247</v>
       </c>
@@ -13611,7 +13623,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A293" s="49" t="s">
         <v>144</v>
       </c>
@@ -13640,7 +13652,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A294" s="49" t="s">
         <v>5</v>
       </c>
@@ -13669,7 +13681,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A295" s="49" t="s">
         <v>21</v>
       </c>
@@ -13698,7 +13710,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A296" s="49" t="s">
         <v>21</v>
       </c>
@@ -13727,7 +13739,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A297" s="49" t="s">
         <v>144</v>
       </c>
@@ -13756,7 +13768,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A298" s="49" t="s">
         <v>144</v>
       </c>
@@ -13785,7 +13797,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A299" s="49" t="s">
         <v>23</v>
       </c>
@@ -13814,7 +13826,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A300" s="49" t="s">
         <v>23</v>
       </c>
@@ -13843,7 +13855,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A301" s="49" t="s">
         <v>23</v>
       </c>
@@ -13872,7 +13884,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A302" s="49" t="s">
         <v>79</v>
       </c>
@@ -13901,7 +13913,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="303" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A303" s="49" t="s">
         <v>5</v>
       </c>
@@ -13930,7 +13942,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="304" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A304" s="49" t="s">
         <v>5</v>
       </c>
@@ -13959,7 +13971,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="305" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A305" s="49" t="s">
         <v>22</v>
       </c>
@@ -13988,7 +14000,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="306" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A306" s="49" t="s">
         <v>482</v>
       </c>
@@ -14017,7 +14029,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="307" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A307" s="49" t="s">
         <v>106</v>
       </c>
@@ -14046,7 +14058,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="308" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A308" s="49" t="s">
         <v>6</v>
       </c>
@@ -14075,7 +14087,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="309" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A309" s="49" t="s">
         <v>6</v>
       </c>
@@ -14104,7 +14116,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="310" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A310" s="49" t="s">
         <v>5</v>
       </c>
@@ -14133,7 +14145,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="311" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A311" s="49" t="s">
         <v>247</v>
       </c>
@@ -14162,7 +14174,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="312" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A312" s="49" t="s">
         <v>5</v>
       </c>
@@ -14191,7 +14203,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="313" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A313" s="49" t="s">
         <v>5</v>
       </c>
@@ -14220,7 +14232,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="314" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A314" s="49" t="s">
         <v>5</v>
       </c>
@@ -14249,7 +14261,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="315" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A315" s="49" t="s">
         <v>5</v>
       </c>
@@ -14278,7 +14290,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="316" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A316" s="49" t="s">
         <v>5</v>
       </c>
@@ -14307,7 +14319,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="317" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A317" s="49" t="s">
         <v>5</v>
       </c>
@@ -14336,7 +14348,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="318" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A318" s="49" t="s">
         <v>5</v>
       </c>
@@ -14365,7 +14377,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="319" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A319" s="49" t="s">
         <v>5</v>
       </c>
@@ -14394,7 +14406,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="320" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A320" s="49" t="s">
         <v>5</v>
       </c>
@@ -14423,7 +14435,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="321" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A321" s="49" t="s">
         <v>5</v>
       </c>
@@ -14452,7 +14464,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="322" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A322" s="49" t="s">
         <v>5</v>
       </c>
@@ -14481,7 +14493,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="323" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A323" s="49" t="s">
         <v>5</v>
       </c>
@@ -14510,7 +14522,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="324" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A324" s="49" t="s">
         <v>62</v>
       </c>
@@ -14539,7 +14551,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="325" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A325" s="49" t="s">
         <v>62</v>
       </c>
@@ -14568,7 +14580,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="326" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A326" s="49" t="s">
         <v>84</v>
       </c>
@@ -14597,7 +14609,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="327" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A327" s="49" t="s">
         <v>84</v>
       </c>
@@ -14626,7 +14638,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="328" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A328" s="49" t="s">
         <v>62</v>
       </c>
@@ -14655,7 +14667,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="329" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A329" s="49" t="s">
         <v>62</v>
       </c>
@@ -14684,7 +14696,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="330" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A330" s="49" t="s">
         <v>62</v>
       </c>
@@ -14713,7 +14725,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="331" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A331" s="49" t="s">
         <v>62</v>
       </c>
@@ -14742,7 +14754,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="332" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A332" s="49" t="s">
         <v>62</v>
       </c>
@@ -14771,7 +14783,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="333" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A333" s="49" t="s">
         <v>165</v>
       </c>
@@ -14800,7 +14812,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="334" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A334" s="49" t="s">
         <v>62</v>
       </c>
@@ -14829,7 +14841,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="335" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A335" s="49" t="s">
         <v>5</v>
       </c>
@@ -14858,7 +14870,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="336" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A336" s="49" t="s">
         <v>5</v>
       </c>
@@ -14887,7 +14899,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="337" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A337" s="49" t="s">
         <v>106</v>
       </c>
@@ -14916,7 +14928,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="338" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A338" s="49" t="s">
         <v>106</v>
       </c>
@@ -14945,7 +14957,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="339" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A339" s="49" t="s">
         <v>106</v>
       </c>
@@ -14974,7 +14986,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="340" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A340" s="49" t="s">
         <v>106</v>
       </c>
@@ -15003,7 +15015,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="341" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A341" s="49" t="s">
         <v>22</v>
       </c>
@@ -15032,7 +15044,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="342" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A342" s="49" t="s">
         <v>79</v>
       </c>
@@ -15061,7 +15073,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="343" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A343" s="49" t="s">
         <v>62</v>
       </c>
@@ -15090,7 +15102,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="344" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A344" s="49" t="s">
         <v>62</v>
       </c>
@@ -15119,7 +15131,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="345" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A345" s="49" t="s">
         <v>62</v>
       </c>
@@ -15148,7 +15160,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="346" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A346" s="49" t="s">
         <v>62</v>
       </c>
@@ -15177,7 +15189,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="347" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A347" s="49" t="s">
         <v>62</v>
       </c>
@@ -15206,7 +15218,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="348" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A348" s="49" t="s">
         <v>142</v>
       </c>
@@ -15235,7 +15247,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="349" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A349" s="49" t="s">
         <v>23</v>
       </c>
@@ -15264,7 +15276,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="350" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A350" s="49" t="s">
         <v>144</v>
       </c>
@@ -15293,7 +15305,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="351" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A351" s="49" t="s">
         <v>21</v>
       </c>
@@ -15322,7 +15334,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="352" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A352" s="49" t="s">
         <v>23</v>
       </c>
@@ -15351,7 +15363,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="353" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A353" s="49" t="s">
         <v>5</v>
       </c>
@@ -15380,7 +15392,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="354" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A354" s="49" t="s">
         <v>5</v>
       </c>
@@ -15409,7 +15421,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="355" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A355" s="49" t="s">
         <v>5</v>
       </c>
@@ -15438,7 +15450,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="356" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A356" s="49" t="s">
         <v>5</v>
       </c>
@@ -15467,7 +15479,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="357" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A357" s="49" t="s">
         <v>21</v>
       </c>
@@ -15496,7 +15508,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="358" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A358" s="49" t="s">
         <v>165</v>
       </c>
@@ -15525,7 +15537,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="359" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A359" s="49" t="s">
         <v>6</v>
       </c>
@@ -15554,7 +15566,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="360" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A360" s="49" t="s">
         <v>84</v>
       </c>
@@ -15583,7 +15595,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="361" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A361" s="49" t="s">
         <v>86</v>
       </c>
@@ -15612,7 +15624,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="362" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A362" s="49" t="s">
         <v>62</v>
       </c>
@@ -15641,7 +15653,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="363" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A363" s="49" t="s">
         <v>144</v>
       </c>
@@ -15670,7 +15682,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="364" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A364" s="49" t="s">
         <v>5</v>
       </c>
@@ -15699,7 +15711,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="365" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A365" s="49" t="s">
         <v>5</v>
       </c>
@@ -15728,7 +15740,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="366" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A366" s="49" t="s">
         <v>289</v>
       </c>
@@ -15757,7 +15769,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="367" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A367" s="49" t="s">
         <v>383</v>
       </c>
@@ -15786,7 +15798,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="368" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A368" s="49" t="s">
         <v>23</v>
       </c>
@@ -15815,7 +15827,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="369" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A369" s="49" t="s">
         <v>62</v>
       </c>
@@ -15844,7 +15856,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="370" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A370" s="49" t="s">
         <v>62</v>
       </c>
@@ -15873,7 +15885,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="371" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A371" s="49" t="s">
         <v>106</v>
       </c>
@@ -15902,7 +15914,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="372" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A372" s="49" t="s">
         <v>114</v>
       </c>
@@ -15931,7 +15943,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="373" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A373" s="49" t="s">
         <v>247</v>
       </c>
@@ -15960,7 +15972,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="374" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A374" s="49" t="s">
         <v>247</v>
       </c>
@@ -15989,7 +16001,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="375" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A375" s="49" t="s">
         <v>247</v>
       </c>
@@ -16018,7 +16030,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="376" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A376" s="49" t="s">
         <v>23</v>
       </c>
@@ -16047,7 +16059,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="377" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A377" s="49" t="s">
         <v>23</v>
       </c>
@@ -16076,7 +16088,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="378" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A378" s="49" t="s">
         <v>62</v>
       </c>
@@ -16105,7 +16117,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="379" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A379" s="49" t="s">
         <v>62</v>
       </c>
@@ -16134,7 +16146,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="380" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A380" s="49" t="s">
         <v>62</v>
       </c>
@@ -16163,7 +16175,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="381" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A381" s="49" t="s">
         <v>144</v>
       </c>
@@ -16192,7 +16204,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="382" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A382" s="49" t="s">
         <v>5</v>
       </c>
@@ -16221,7 +16233,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="383" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A383" s="49" t="s">
         <v>86</v>
       </c>
@@ -16250,7 +16262,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="384" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A384" s="49" t="s">
         <v>62</v>
       </c>
@@ -16279,7 +16291,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="385" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A385" s="49" t="s">
         <v>106</v>
       </c>
@@ -16308,7 +16320,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="386" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A386" s="49" t="s">
         <v>106</v>
       </c>
@@ -16337,7 +16349,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="387" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A387" s="49" t="s">
         <v>5</v>
       </c>
@@ -16366,7 +16378,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="388" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A388" s="49" t="s">
         <v>86</v>
       </c>
@@ -16395,7 +16407,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="389" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A389" s="49" t="s">
         <v>22</v>
       </c>
@@ -16424,7 +16436,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="390" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A390" s="49" t="s">
         <v>22</v>
       </c>
@@ -16453,7 +16465,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="391" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A391" s="49" t="s">
         <v>84</v>
       </c>
@@ -16482,7 +16494,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="392" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A392" s="49" t="s">
         <v>114</v>
       </c>
@@ -16511,7 +16523,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="393" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A393" s="49" t="s">
         <v>5</v>
       </c>
@@ -16540,7 +16552,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="394" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A394" s="49" t="s">
         <v>5</v>
       </c>
@@ -16569,7 +16581,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="395" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A395" s="49" t="s">
         <v>247</v>
       </c>
@@ -16598,7 +16610,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="396" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A396" s="49" t="s">
         <v>23</v>
       </c>
@@ -16627,7 +16639,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="397" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A397" s="49" t="s">
         <v>79</v>
       </c>
@@ -16656,7 +16668,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="398" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A398" s="49" t="s">
         <v>487</v>
       </c>
@@ -16685,7 +16697,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="399" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A399" s="49" t="s">
         <v>5</v>
       </c>
@@ -16714,7 +16726,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="400" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A400" s="49" t="s">
         <v>5</v>
       </c>
@@ -16743,7 +16755,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="401" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A401" s="49" t="s">
         <v>344</v>
       </c>
@@ -16772,7 +16784,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="402" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A402" s="49" t="s">
         <v>642</v>
       </c>
@@ -16801,7 +16813,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="403" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A403" s="49" t="s">
         <v>644</v>
       </c>
@@ -16830,7 +16842,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="404" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A404" s="49" t="s">
         <v>646</v>
       </c>
@@ -16859,7 +16871,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="405" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A405" s="49" t="s">
         <v>648</v>
       </c>
@@ -16888,7 +16900,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="406" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A406" s="49" t="s">
         <v>650</v>
       </c>
@@ -16917,7 +16929,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="407" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A407" s="49" t="s">
         <v>652</v>
       </c>
@@ -16946,7 +16958,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="408" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A408" s="49" t="s">
         <v>155</v>
       </c>
@@ -16975,7 +16987,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="409" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A409" s="49" t="s">
         <v>165</v>
       </c>
@@ -17004,7 +17016,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="410" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A410" s="49" t="s">
         <v>22</v>
       </c>
@@ -17033,7 +17045,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="411" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A411" s="49" t="s">
         <v>62</v>
       </c>
@@ -17062,7 +17074,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="412" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A412" s="49" t="s">
         <v>5</v>
       </c>
@@ -17091,7 +17103,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="413" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A413" s="49" t="s">
         <v>289</v>
       </c>
@@ -17120,7 +17132,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="414" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A414" s="49" t="s">
         <v>289</v>
       </c>
@@ -17149,7 +17161,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="415" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A415" s="49" t="s">
         <v>5</v>
       </c>
@@ -17178,7 +17190,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="416" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A416" s="49" t="s">
         <v>5</v>
       </c>
@@ -17207,7 +17219,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="417" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A417" s="49" t="s">
         <v>84</v>
       </c>
@@ -17236,7 +17248,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="418" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A418" s="49" t="s">
         <v>86</v>
       </c>
@@ -17265,7 +17277,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="419" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A419" s="49" t="s">
         <v>114</v>
       </c>
@@ -17294,7 +17306,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="420" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A420" s="49" t="s">
         <v>5</v>
       </c>
@@ -17323,7 +17335,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="421" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A421" s="49" t="s">
         <v>139</v>
       </c>
@@ -17352,7 +17364,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="422" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A422" s="49" t="s">
         <v>23</v>
       </c>
@@ -17381,7 +17393,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="423" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A423" s="49" t="s">
         <v>5</v>
       </c>
@@ -17410,7 +17422,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="424" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A424" s="49" t="s">
         <v>5</v>
       </c>
@@ -17439,7 +17451,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="425" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A425" s="49" t="s">
         <v>5</v>
       </c>
@@ -17468,7 +17480,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="426" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A426" s="49" t="s">
         <v>5</v>
       </c>
@@ -17497,7 +17509,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="427" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A427" s="49" t="s">
         <v>22</v>
       </c>
@@ -17526,7 +17538,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="428" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A428" s="49" t="s">
         <v>5</v>
       </c>
@@ -17555,7 +17567,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="429" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A429" s="49" t="s">
         <v>62</v>
       </c>
@@ -17584,7 +17596,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="430" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A430" s="49" t="s">
         <v>5</v>
       </c>
@@ -17613,7 +17625,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="431" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A431" s="49" t="s">
         <v>289</v>
       </c>
@@ -17642,7 +17654,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="432" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A432" s="49" t="s">
         <v>5</v>
       </c>
@@ -17671,7 +17683,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="433" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A433" s="49" t="s">
         <v>5</v>
       </c>
@@ -17700,7 +17712,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="434" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A434" s="49" t="s">
         <v>86</v>
       </c>
@@ -17729,7 +17741,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="435" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A435" s="49" t="s">
         <v>62</v>
       </c>
@@ -17758,7 +17770,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="436" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A436" s="49" t="s">
         <v>22</v>
       </c>
@@ -17787,7 +17799,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="437" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A437" s="49" t="s">
         <v>22</v>
       </c>
@@ -17816,7 +17828,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="438" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A438" s="49" t="s">
         <v>84</v>
       </c>
@@ -17845,7 +17857,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="439" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A439" s="49" t="s">
         <v>62</v>
       </c>
@@ -17874,7 +17886,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="440" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A440" s="49" t="s">
         <v>5</v>
       </c>
@@ -17903,7 +17915,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="441" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A441" s="49" t="s">
         <v>86</v>
       </c>
@@ -17932,7 +17944,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="442" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A442" s="49" t="s">
         <v>62</v>
       </c>
@@ -17961,7 +17973,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="443" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A443" s="49" t="s">
         <v>5</v>
       </c>
@@ -17990,7 +18002,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="444" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A444" s="49" t="s">
         <v>5</v>
       </c>
@@ -18019,7 +18031,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="445" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A445" s="49" t="s">
         <v>292</v>
       </c>
@@ -18048,7 +18060,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="446" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A446" s="49" t="s">
         <v>5</v>
       </c>
@@ -18077,7 +18089,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="447" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A447" s="49" t="s">
         <v>5</v>
       </c>
@@ -18106,7 +18118,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="448" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A448" s="49" t="s">
         <v>5</v>
       </c>
@@ -18135,7 +18147,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="449" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A449" s="49" t="s">
         <v>5</v>
       </c>
@@ -18164,7 +18176,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="450" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A450" s="49" t="s">
         <v>21</v>
       </c>
@@ -18193,7 +18205,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="451" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A451" s="49" t="s">
         <v>21</v>
       </c>
@@ -18222,7 +18234,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="452" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A452" s="49" t="s">
         <v>21</v>
       </c>
@@ -18251,7 +18263,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="453" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A453" s="49" t="s">
         <v>21</v>
       </c>
@@ -18280,7 +18292,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="454" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A454" s="49" t="s">
         <v>22</v>
       </c>
@@ -18309,7 +18321,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="455" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A455" s="49" t="s">
         <v>22</v>
       </c>
@@ -18338,7 +18350,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="456" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A456" s="49" t="s">
         <v>6</v>
       </c>
@@ -18367,7 +18379,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="457" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A457" s="49" t="s">
         <v>6</v>
       </c>
@@ -18396,7 +18408,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="458" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A458" s="49" t="s">
         <v>6</v>
       </c>
@@ -18425,7 +18437,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="459" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A459" s="49" t="s">
         <v>165</v>
       </c>
@@ -18454,7 +18466,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="460" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A460" s="49" t="s">
         <v>62</v>
       </c>
@@ -18483,7 +18495,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="461" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A461" s="49" t="s">
         <v>23</v>
       </c>
@@ -18512,7 +18524,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="462" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A462" s="49" t="s">
         <v>23</v>
       </c>
@@ -18541,7 +18553,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="463" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A463" s="49" t="s">
         <v>23</v>
       </c>
@@ -18570,7 +18582,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="464" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A464" s="49" t="s">
         <v>23</v>
       </c>
@@ -18599,7 +18611,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="465" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A465" s="49" t="s">
         <v>646</v>
       </c>
@@ -18628,7 +18640,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="466" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A466" s="49" t="s">
         <v>79</v>
       </c>
@@ -18657,7 +18669,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="467" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A467" s="49" t="s">
         <v>7</v>
       </c>
@@ -18686,7 +18698,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="468" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A468" s="49" t="s">
         <v>7</v>
       </c>
@@ -18715,7 +18727,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="469" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A469" s="49" t="s">
         <v>7</v>
       </c>
@@ -18744,7 +18756,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="470" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A470" s="49" t="s">
         <v>7</v>
       </c>
@@ -18773,7 +18785,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="471" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A471" s="49" t="s">
         <v>745</v>
       </c>
@@ -18802,7 +18814,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="472" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A472" s="49" t="s">
         <v>745</v>
       </c>
@@ -18831,7 +18843,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="473" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A473" s="49" t="s">
         <v>292</v>
       </c>
@@ -18860,7 +18872,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="474" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A474" s="49" t="s">
         <v>292</v>
       </c>
@@ -18889,7 +18901,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="475" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A475" s="49" t="s">
         <v>292</v>
       </c>
@@ -18918,7 +18930,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="476" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A476" s="49" t="s">
         <v>292</v>
       </c>
@@ -18947,7 +18959,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="477" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A477" s="49" t="s">
         <v>292</v>
       </c>
@@ -18976,7 +18988,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="478" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A478" s="49" t="s">
         <v>292</v>
       </c>
@@ -19005,7 +19017,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="479" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A479" s="49" t="s">
         <v>754</v>
       </c>
@@ -19034,7 +19046,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="480" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A480" s="49" t="s">
         <v>5</v>
       </c>
@@ -19063,7 +19075,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="481" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A481" s="49" t="s">
         <v>5</v>
       </c>
@@ -19092,7 +19104,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="482" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="482" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A482" s="49" t="s">
         <v>5</v>
       </c>
@@ -19121,7 +19133,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="483" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A483" s="49" t="s">
         <v>5</v>
       </c>
@@ -19150,7 +19162,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="484" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="484" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A484" s="49" t="s">
         <v>5</v>
       </c>
@@ -19179,7 +19191,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="485" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="485" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A485" s="49" t="s">
         <v>5</v>
       </c>
@@ -19208,7 +19220,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="486" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A486" s="49" t="s">
         <v>5</v>
       </c>
@@ -19237,7 +19249,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="487" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A487" s="49" t="s">
         <v>5</v>
       </c>
@@ -19266,7 +19278,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="488" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A488" s="49" t="s">
         <v>5</v>
       </c>
@@ -19295,7 +19307,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="489" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A489" s="49" t="s">
         <v>5</v>
       </c>
@@ -19324,7 +19336,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="490" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A490" s="49" t="s">
         <v>5</v>
       </c>
@@ -19353,7 +19365,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="491" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A491" s="49" t="s">
         <v>5</v>
       </c>
@@ -19382,7 +19394,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="492" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="492" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A492" s="49" t="s">
         <v>5</v>
       </c>
@@ -19411,7 +19423,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="493" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="493" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A493" s="49" t="s">
         <v>5</v>
       </c>
@@ -19440,7 +19452,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="494" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="494" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A494" s="49" t="s">
         <v>5</v>
       </c>
@@ -19469,7 +19481,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="495" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A495" s="49" t="s">
         <v>5</v>
       </c>
@@ -19498,7 +19510,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="496" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A496" s="49" t="s">
         <v>5</v>
       </c>
@@ -19527,7 +19539,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="497" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="497" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A497" s="49" t="s">
         <v>5</v>
       </c>
@@ -19556,7 +19568,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="498" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="498" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A498" s="49" t="s">
         <v>5</v>
       </c>
@@ -19585,7 +19597,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="499" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="499" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A499" s="49" t="s">
         <v>5</v>
       </c>
@@ -19614,7 +19626,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="500" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="500" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A500" s="49" t="s">
         <v>5</v>
       </c>
@@ -19643,7 +19655,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="501" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="501" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A501" s="49" t="s">
         <v>5</v>
       </c>
@@ -19672,7 +19684,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="502" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="502" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A502" s="49" t="s">
         <v>5</v>
       </c>
@@ -19701,7 +19713,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="503" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A503" s="49" t="s">
         <v>5</v>
       </c>
@@ -19730,7 +19742,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="504" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="504" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A504" s="49" t="s">
         <v>5</v>
       </c>
@@ -19759,7 +19771,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="505" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="505" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A505" s="49" t="s">
         <v>5</v>
       </c>
@@ -19788,7 +19800,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="506" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="506" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A506" s="49" t="s">
         <v>5</v>
       </c>
@@ -19817,7 +19829,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="507" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="507" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A507" s="49" t="s">
         <v>5</v>
       </c>
@@ -19846,7 +19858,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="508" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="508" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A508" s="49" t="s">
         <v>5</v>
       </c>
@@ -19875,7 +19887,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="509" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="509" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A509" s="49" t="s">
         <v>5</v>
       </c>
@@ -19904,7 +19916,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="510" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="510" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A510" s="49" t="s">
         <v>5</v>
       </c>
@@ -19933,7 +19945,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="511" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A511" s="49" t="s">
         <v>5</v>
       </c>
@@ -19962,7 +19974,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="512" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="512" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A512" s="49" t="s">
         <v>5</v>
       </c>
@@ -19991,7 +20003,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="513" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="513" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A513" s="49" t="s">
         <v>5</v>
       </c>
@@ -20020,7 +20032,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="514" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="514" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A514" s="49" t="s">
         <v>5</v>
       </c>
@@ -20049,7 +20061,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="515" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="515" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A515" s="49" t="s">
         <v>5</v>
       </c>
@@ -20078,7 +20090,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="516" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="516" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A516" s="49" t="s">
         <v>344</v>
       </c>
@@ -20107,7 +20119,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="517" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A517" s="49" t="s">
         <v>21</v>
       </c>
@@ -20136,7 +20148,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="518" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="518" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A518" s="49" t="s">
         <v>21</v>
       </c>
@@ -20165,7 +20177,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="519" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A519" s="49" t="s">
         <v>21</v>
       </c>
@@ -20194,7 +20206,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="520" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="520" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A520" s="49" t="s">
         <v>21</v>
       </c>
@@ -20223,7 +20235,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="521" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="521" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A521" s="49" t="s">
         <v>21</v>
       </c>
@@ -20252,7 +20264,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="522" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="522" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A522" s="49" t="s">
         <v>21</v>
       </c>
@@ -20281,7 +20293,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="523" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="523" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A523" s="49" t="s">
         <v>21</v>
       </c>
@@ -20310,7 +20322,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="524" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A524" s="49" t="s">
         <v>21</v>
       </c>
@@ -20339,7 +20351,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="525" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="525" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A525" s="49" t="s">
         <v>21</v>
       </c>
@@ -20368,7 +20380,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="526" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="526" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A526" s="49" t="s">
         <v>21</v>
       </c>
@@ -20397,7 +20409,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="527" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="527" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A527" s="49" t="s">
         <v>21</v>
       </c>
@@ -20426,7 +20438,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="528" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="528" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A528" s="49" t="s">
         <v>21</v>
       </c>
@@ -20455,7 +20467,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="529" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="529" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A529" s="49" t="s">
         <v>106</v>
       </c>
@@ -20484,7 +20496,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="530" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="530" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A530" s="49" t="s">
         <v>106</v>
       </c>
@@ -20513,7 +20525,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="531" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="531" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A531" s="49" t="s">
         <v>106</v>
       </c>
@@ -20542,7 +20554,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="532" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="532" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A532" s="49" t="s">
         <v>106</v>
       </c>
@@ -20571,7 +20583,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="533" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="533" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A533" s="49" t="s">
         <v>106</v>
       </c>
@@ -20600,7 +20612,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="534" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="534" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A534" s="49" t="s">
         <v>106</v>
       </c>
@@ -20629,7 +20641,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="535" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="535" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A535" s="49" t="s">
         <v>106</v>
       </c>
@@ -20658,7 +20670,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="536" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="536" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A536" s="49" t="s">
         <v>106</v>
       </c>
@@ -20687,7 +20699,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="537" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="537" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A537" s="49" t="s">
         <v>106</v>
       </c>
@@ -20716,7 +20728,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="538" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="538" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A538" s="49" t="s">
         <v>106</v>
       </c>
@@ -20745,7 +20757,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="539" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="539" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A539" s="49" t="s">
         <v>165</v>
       </c>
@@ -20774,7 +20786,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="540" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="540" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A540" s="49" t="s">
         <v>165</v>
       </c>
@@ -20803,7 +20815,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="541" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="541" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A541" s="49" t="s">
         <v>165</v>
       </c>
@@ -20832,7 +20844,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="542" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="542" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A542" s="49" t="s">
         <v>165</v>
       </c>
@@ -20861,7 +20873,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="543" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="543" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A543" s="49" t="s">
         <v>165</v>
       </c>
@@ -20890,7 +20902,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="544" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="544" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A544" s="49" t="s">
         <v>165</v>
       </c>
@@ -20919,7 +20931,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="545" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="545" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A545" s="49" t="s">
         <v>22</v>
       </c>
@@ -20948,7 +20960,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="546" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="546" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A546" s="49" t="s">
         <v>22</v>
       </c>
@@ -20977,7 +20989,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="547" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="547" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A547" s="49" t="s">
         <v>22</v>
       </c>
@@ -21006,7 +21018,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="548" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="548" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A548" s="49" t="s">
         <v>22</v>
       </c>
@@ -21035,7 +21047,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="549" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="549" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A549" s="49" t="s">
         <v>22</v>
       </c>
@@ -21064,7 +21076,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="550" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="550" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A550" s="49" t="s">
         <v>22</v>
       </c>
@@ -21093,7 +21105,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="551" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="551" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A551" s="49" t="s">
         <v>22</v>
       </c>
@@ -21122,7 +21134,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="552" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="552" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A552" s="49" t="s">
         <v>22</v>
       </c>
@@ -21151,7 +21163,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="553" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="553" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A553" s="49" t="s">
         <v>22</v>
       </c>
@@ -21180,7 +21192,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="554" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="554" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A554" s="49" t="s">
         <v>22</v>
       </c>
@@ -21209,7 +21221,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="555" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="555" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A555" s="49" t="s">
         <v>22</v>
       </c>
@@ -21238,7 +21250,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="556" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="556" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A556" s="49" t="s">
         <v>22</v>
       </c>
@@ -21267,7 +21279,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="557" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="557" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A557" s="49" t="s">
         <v>22</v>
       </c>
@@ -21296,7 +21308,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="558" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="558" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A558" s="49" t="s">
         <v>6</v>
       </c>
@@ -21325,7 +21337,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="559" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="559" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A559" s="49" t="s">
         <v>6</v>
       </c>
@@ -21354,7 +21366,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="560" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="560" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A560" s="49" t="s">
         <v>6</v>
       </c>
@@ -21383,7 +21395,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="561" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="561" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A561" s="49" t="s">
         <v>6</v>
       </c>
@@ -21412,7 +21424,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="562" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="562" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A562" s="49" t="s">
         <v>6</v>
       </c>
@@ -21441,7 +21453,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="563" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="563" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A563" s="49" t="s">
         <v>6</v>
       </c>
@@ -21470,7 +21482,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="564" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="564" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A564" s="49" t="s">
         <v>6</v>
       </c>
@@ -21499,7 +21511,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="565" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="565" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A565" s="49" t="s">
         <v>6</v>
       </c>
@@ -21528,7 +21540,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="566" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="566" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A566" s="49" t="s">
         <v>6</v>
       </c>
@@ -21557,7 +21569,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="567" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="567" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A567" s="49" t="s">
         <v>6</v>
       </c>
@@ -21586,7 +21598,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="568" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="568" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A568" s="49" t="s">
         <v>6</v>
       </c>
@@ -21615,7 +21627,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="569" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="569" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A569" s="49" t="s">
         <v>6</v>
       </c>
@@ -21644,7 +21656,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="570" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="570" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A570" s="49" t="s">
         <v>6</v>
       </c>
@@ -21673,7 +21685,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="571" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="571" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A571" s="49" t="s">
         <v>114</v>
       </c>
@@ -21702,7 +21714,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="572" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="572" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A572" s="49" t="s">
         <v>114</v>
       </c>
@@ -21731,7 +21743,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="573" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="573" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A573" s="49" t="s">
         <v>114</v>
       </c>
@@ -21760,7 +21772,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="574" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="574" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A574" s="49" t="s">
         <v>114</v>
       </c>
@@ -21789,7 +21801,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="575" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="575" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A575" s="49" t="s">
         <v>142</v>
       </c>
@@ -21818,7 +21830,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="576" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="576" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A576" s="49" t="s">
         <v>142</v>
       </c>
@@ -21847,7 +21859,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="577" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="577" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A577" s="49" t="s">
         <v>142</v>
       </c>
@@ -21876,7 +21888,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="578" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="578" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A578" s="49" t="s">
         <v>86</v>
       </c>
@@ -21905,7 +21917,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="579" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="579" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A579" s="49" t="s">
         <v>854</v>
       </c>
@@ -21934,7 +21946,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="580" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="580" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A580" s="49" t="s">
         <v>854</v>
       </c>
@@ -21963,7 +21975,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="581" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="581" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A581" s="49" t="s">
         <v>62</v>
       </c>
@@ -21992,7 +22004,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="582" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="582" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A582" s="49" t="s">
         <v>62</v>
       </c>
@@ -22021,7 +22033,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="583" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="583" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A583" s="49" t="s">
         <v>62</v>
       </c>
@@ -22050,7 +22062,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="584" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="584" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A584" s="49" t="s">
         <v>62</v>
       </c>
@@ -22079,7 +22091,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="585" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="585" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A585" s="49" t="s">
         <v>62</v>
       </c>
@@ -22108,7 +22120,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="586" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="586" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A586" s="49" t="s">
         <v>861</v>
       </c>
@@ -22137,7 +22149,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="587" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="587" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A587" s="49" t="s">
         <v>144</v>
       </c>
@@ -22166,7 +22178,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="588" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="588" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A588" s="49" t="s">
         <v>144</v>
       </c>
@@ -22195,7 +22207,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="589" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="589" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A589" s="49" t="s">
         <v>289</v>
       </c>
@@ -22224,7 +22236,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="590" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="590" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A590" s="49" t="s">
         <v>247</v>
       </c>
@@ -22253,7 +22265,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="591" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="591" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A591" s="49" t="s">
         <v>247</v>
       </c>
@@ -22282,7 +22294,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="592" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="592" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A592" s="49" t="s">
         <v>383</v>
       </c>
@@ -22311,7 +22323,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="593" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="593" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A593" s="49" t="s">
         <v>23</v>
       </c>
@@ -22340,7 +22352,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="594" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="594" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A594" s="49" t="s">
         <v>292</v>
       </c>
@@ -22369,7 +22381,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="595" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="595" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A595" s="49" t="s">
         <v>754</v>
       </c>
@@ -22398,7 +22410,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="596" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="596" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A596" s="49" t="s">
         <v>5</v>
       </c>
@@ -22427,7 +22439,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="597" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="597" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A597" s="49" t="s">
         <v>5</v>
       </c>
@@ -22456,7 +22468,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="598" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="598" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A598" s="49" t="s">
         <v>5</v>
       </c>
@@ -22485,7 +22497,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="599" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="599" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A599" s="49" t="s">
         <v>5</v>
       </c>
@@ -22514,7 +22526,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="600" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="600" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A600" s="49" t="s">
         <v>21</v>
       </c>
@@ -22543,7 +22555,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="601" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="601" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A601" s="49" t="s">
         <v>21</v>
       </c>
@@ -22572,7 +22584,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="602" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="602" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A602" s="49" t="s">
         <v>21</v>
       </c>
@@ -22601,7 +22613,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="603" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="603" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A603" s="49" t="s">
         <v>22</v>
       </c>
@@ -22630,7 +22642,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="604" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="604" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A604" s="49" t="s">
         <v>6</v>
       </c>
@@ -22659,7 +22671,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="605" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="605" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A605" s="49" t="s">
         <v>6</v>
       </c>
@@ -22688,7 +22700,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="606" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="606" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A606" s="49" t="s">
         <v>854</v>
       </c>
@@ -22717,7 +22729,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="607" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="607" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A607" s="49" t="s">
         <v>62</v>
       </c>
@@ -22746,7 +22758,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="608" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="608" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A608" s="49" t="s">
         <v>247</v>
       </c>
@@ -22775,7 +22787,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="609" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="609" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A609" s="49" t="s">
         <v>5</v>
       </c>
@@ -22804,7 +22816,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="610" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="610" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A610" s="49" t="s">
         <v>21</v>
       </c>
@@ -22833,7 +22845,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="611" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="611" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A611" s="49" t="s">
         <v>84</v>
       </c>
@@ -22862,7 +22874,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="612" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="612" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A612" s="49" t="s">
         <v>84</v>
       </c>
@@ -22891,7 +22903,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="613" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="613" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A613" s="49" t="s">
         <v>84</v>
       </c>
@@ -22920,7 +22932,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="614" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="614" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A614" s="49" t="s">
         <v>142</v>
       </c>
@@ -22949,7 +22961,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="615" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="615" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A615" s="49" t="s">
         <v>5</v>
       </c>
@@ -22978,7 +22990,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="616" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="616" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A616" s="49" t="s">
         <v>86</v>
       </c>
@@ -23007,7 +23019,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="617" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="617" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A617" s="49" t="s">
         <v>62</v>
       </c>
@@ -23036,7 +23048,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="618" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="618" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A618" s="49" t="s">
         <v>62</v>
       </c>
@@ -23065,7 +23077,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="619" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="619" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A619" s="49" t="s">
         <v>21</v>
       </c>
@@ -23094,7 +23106,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="620" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="620" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A620" s="49" t="s">
         <v>84</v>
       </c>
@@ -23123,7 +23135,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="621" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="621" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A621" s="49" t="s">
         <v>142</v>
       </c>
@@ -23152,7 +23164,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="622" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="622" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A622" s="49" t="s">
         <v>5</v>
       </c>
@@ -23181,7 +23193,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="623" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="623" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A623" s="49" t="s">
         <v>84</v>
       </c>
@@ -23210,7 +23222,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="624" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="624" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A624" s="49" t="s">
         <v>86</v>
       </c>
@@ -23239,7 +23251,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="625" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="625" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A625" s="49" t="s">
         <v>21</v>
       </c>
@@ -23268,7 +23280,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="626" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="626" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A626" s="49" t="s">
         <v>21</v>
       </c>
@@ -23297,7 +23309,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="627" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="627" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A627" s="49" t="s">
         <v>21</v>
       </c>
@@ -23326,7 +23338,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="628" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="628" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A628" s="49" t="s">
         <v>22</v>
       </c>
@@ -23355,7 +23367,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="629" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="629" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A629" s="49" t="s">
         <v>22</v>
       </c>
@@ -23384,7 +23396,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="630" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="630" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A630" s="49" t="s">
         <v>5</v>
       </c>
@@ -23413,7 +23425,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="631" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="631" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A631" s="49" t="s">
         <v>5</v>
       </c>
@@ -23442,7 +23454,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="632" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="632" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A632" s="49" t="s">
         <v>5</v>
       </c>
@@ -23471,7 +23483,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="633" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="633" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A633" s="49" t="s">
         <v>79</v>
       </c>
@@ -23500,7 +23512,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="634" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="634" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A634" s="49" t="s">
         <v>79</v>
       </c>
@@ -23529,7 +23541,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="635" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="635" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A635" s="49" t="s">
         <v>5</v>
       </c>
@@ -23558,7 +23570,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="636" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="636" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A636" s="49" t="s">
         <v>5</v>
       </c>
@@ -23587,7 +23599,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="637" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="637" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A637" s="49" t="s">
         <v>5</v>
       </c>
@@ -23616,7 +23628,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="638" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="638" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A638" s="49" t="s">
         <v>5</v>
       </c>
@@ -23645,7 +23657,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="639" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="639" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A639" s="49" t="s">
         <v>21</v>
       </c>
@@ -23674,7 +23686,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="640" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="640" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A640" s="49" t="s">
         <v>6</v>
       </c>
@@ -23703,7 +23715,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="641" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="641" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A641" s="49" t="s">
         <v>62</v>
       </c>
@@ -23732,7 +23744,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="642" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="642" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A642" s="49" t="s">
         <v>62</v>
       </c>
@@ -23761,7 +23773,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="643" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="643" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A643" s="49" t="s">
         <v>5</v>
       </c>
@@ -23790,7 +23802,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="644" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="644" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A644" s="49" t="s">
         <v>22</v>
       </c>
@@ -23819,7 +23831,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="645" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="645" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A645" s="49" t="s">
         <v>62</v>
       </c>
@@ -23848,7 +23860,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="646" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="646" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A646" s="49" t="s">
         <v>22</v>
       </c>
@@ -23877,7 +23889,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="647" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="647" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A647" s="49" t="s">
         <v>23</v>
       </c>
@@ -23906,7 +23918,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="648" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="648" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A648" s="49" t="s">
         <v>5</v>
       </c>
@@ -23935,7 +23947,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="649" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="649" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A649" s="49" t="s">
         <v>21</v>
       </c>
@@ -23964,7 +23976,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="650" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="650" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A650" s="49" t="s">
         <v>79</v>
       </c>
@@ -23993,7 +24005,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="651" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="651" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A651" s="49" t="s">
         <v>292</v>
       </c>
@@ -24022,7 +24034,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="652" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="652" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A652" s="49" t="s">
         <v>5</v>
       </c>
@@ -24051,7 +24063,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="653" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="653" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A653" s="49" t="s">
         <v>6</v>
       </c>
@@ -24080,7 +24092,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="654" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="654" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A654" s="49" t="s">
         <v>5</v>
       </c>
@@ -24109,7 +24121,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="655" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="655" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A655" s="49" t="s">
         <v>21</v>
       </c>
@@ -24138,7 +24150,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="656" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="656" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A656" s="49" t="s">
         <v>21</v>
       </c>
@@ -24167,7 +24179,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="657" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="657" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A657" s="49" t="s">
         <v>84</v>
       </c>
@@ -24196,7 +24208,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="658" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="658" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A658" s="49" t="s">
         <v>84</v>
       </c>
@@ -24225,7 +24237,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="659" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="659" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A659" s="49" t="s">
         <v>292</v>
       </c>
@@ -24254,7 +24266,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="660" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="660" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A660" s="49" t="s">
         <v>646</v>
       </c>
@@ -24283,7 +24295,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="661" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="661" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A661" s="49" t="s">
         <v>23</v>
       </c>
@@ -24312,7 +24324,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="662" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="662" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A662" s="49" t="s">
         <v>106</v>
       </c>
@@ -24341,7 +24353,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="663" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="663" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A663" s="49" t="s">
         <v>22</v>
       </c>
@@ -24370,7 +24382,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="664" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="664" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A664" s="49" t="s">
         <v>114</v>
       </c>
@@ -24399,7 +24411,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="665" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="665" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A665" s="49" t="s">
         <v>453</v>
       </c>
@@ -24428,7 +24440,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="666" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="666" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A666" s="49" t="s">
         <v>22</v>
       </c>
@@ -24457,7 +24469,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="667" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="667" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A667" s="49" t="s">
         <v>247</v>
       </c>
@@ -24486,7 +24498,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="668" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="668" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A668" s="49" t="s">
         <v>292</v>
       </c>
@@ -24515,7 +24527,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="669" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="669" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A669" s="49" t="s">
         <v>5</v>
       </c>
@@ -24544,7 +24556,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="670" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="670" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A670" s="49" t="s">
         <v>5</v>
       </c>
@@ -24573,7 +24585,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="671" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="671" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A671" s="49" t="s">
         <v>5</v>
       </c>
@@ -24602,7 +24614,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="672" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="672" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A672" s="49" t="s">
         <v>21</v>
       </c>
@@ -24631,7 +24643,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="673" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="673" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A673" s="49" t="s">
         <v>21</v>
       </c>
@@ -24660,7 +24672,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="674" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="674" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A674" s="49" t="s">
         <v>6</v>
       </c>
@@ -24689,7 +24701,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="675" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="675" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A675" s="49" t="s">
         <v>79</v>
       </c>
@@ -24718,7 +24730,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="676" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="676" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A676" s="49" t="s">
         <v>292</v>
       </c>
@@ -24747,7 +24759,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="677" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="677" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A677" s="49" t="s">
         <v>292</v>
       </c>
@@ -24776,7 +24788,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="678" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="678" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A678" s="49" t="s">
         <v>106</v>
       </c>
@@ -24805,7 +24817,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="679" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="679" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A679" s="49" t="s">
         <v>106</v>
       </c>
@@ -24834,7 +24846,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="680" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="680" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A680" s="49" t="s">
         <v>106</v>
       </c>
@@ -24863,7 +24875,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="681" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="681" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A681" s="49" t="s">
         <v>106</v>
       </c>
@@ -24892,7 +24904,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="682" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="682" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A682" s="49" t="s">
         <v>5</v>
       </c>
@@ -24921,7 +24933,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="683" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="683" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A683" s="49" t="s">
         <v>5</v>
       </c>
@@ -24950,7 +24962,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="684" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="684" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A684" s="49" t="s">
         <v>84</v>
       </c>
@@ -24979,7 +24991,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="685" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="685" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A685" s="49" t="s">
         <v>79</v>
       </c>
@@ -25008,7 +25020,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="686" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="686" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A686" s="49" t="s">
         <v>5</v>
       </c>
@@ -25037,7 +25049,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="687" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="687" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A687" s="49" t="s">
         <v>22</v>
       </c>
@@ -25066,7 +25078,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="688" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="688" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A688" s="49" t="s">
         <v>5</v>
       </c>
@@ -25095,7 +25107,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="689" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="689" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A689" s="49" t="s">
         <v>5</v>
       </c>
@@ -25124,7 +25136,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="690" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="690" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A690" s="49" t="s">
         <v>21</v>
       </c>
@@ -25153,7 +25165,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="691" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="691" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A691" s="49" t="s">
         <v>5</v>
       </c>
@@ -25182,7 +25194,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="692" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="692" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A692" s="49" t="s">
         <v>5</v>
       </c>
@@ -25211,7 +25223,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="693" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="693" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A693" s="49" t="s">
         <v>62</v>
       </c>
@@ -25240,7 +25252,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="694" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="694" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A694" s="49" t="s">
         <v>62</v>
       </c>
@@ -25269,7 +25281,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="695" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="695" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A695" s="49" t="s">
         <v>62</v>
       </c>
@@ -25298,7 +25310,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="696" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="696" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A696" s="49" t="s">
         <v>62</v>
       </c>
@@ -25327,7 +25339,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="697" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="697" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A697" s="49" t="s">
         <v>62</v>
       </c>
@@ -25356,7 +25368,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="698" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="698" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A698" s="49" t="s">
         <v>84</v>
       </c>
@@ -25385,7 +25397,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="699" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="699" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A699" s="49" t="s">
         <v>23</v>
       </c>
@@ -25414,7 +25426,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="700" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="700" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A700" s="49" t="s">
         <v>5</v>
       </c>
@@ -25443,7 +25455,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="701" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="701" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A701" s="49" t="s">
         <v>482</v>
       </c>
@@ -25472,7 +25484,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="702" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="702" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A702" s="49" t="s">
         <v>5</v>
       </c>
@@ -25501,7 +25513,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="703" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="703" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A703" s="49" t="s">
         <v>5</v>
       </c>
@@ -25530,7 +25542,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="704" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="704" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A704" s="49" t="s">
         <v>5</v>
       </c>
@@ -25559,7 +25571,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="705" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="705" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A705" s="49" t="s">
         <v>5</v>
       </c>
@@ -25588,7 +25600,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="706" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="706" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A706" s="49" t="s">
         <v>5</v>
       </c>
@@ -25617,7 +25629,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="707" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="707" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A707" s="49" t="s">
         <v>861</v>
       </c>
@@ -25646,7 +25658,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="708" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="708" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A708" s="49" t="s">
         <v>861</v>
       </c>
@@ -25675,7 +25687,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="709" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="709" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A709" s="49" t="s">
         <v>861</v>
       </c>
@@ -25704,7 +25716,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="710" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="710" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A710" s="49" t="s">
         <v>292</v>
       </c>
@@ -25733,7 +25745,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="711" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="711" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A711" s="49" t="s">
         <v>292</v>
       </c>
@@ -25762,7 +25774,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="712" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="712" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A712" s="49" t="s">
         <v>5</v>
       </c>
@@ -25791,7 +25803,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="713" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="713" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A713" s="49" t="s">
         <v>5</v>
       </c>
@@ -25820,7 +25832,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="714" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="714" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A714" s="49" t="s">
         <v>62</v>
       </c>
@@ -25849,7 +25861,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="715" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="715" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A715" s="49" t="s">
         <v>5</v>
       </c>
@@ -25878,7 +25890,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="716" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="716" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A716" s="49" t="s">
         <v>861</v>
       </c>
@@ -25907,7 +25919,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="717" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="717" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A717" s="49" t="s">
         <v>22</v>
       </c>
@@ -25936,7 +25948,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="718" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="718" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A718" s="49" t="s">
         <v>86</v>
       </c>
@@ -25965,7 +25977,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="719" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="719" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A719" s="49" t="s">
         <v>23</v>
       </c>
@@ -25994,7 +26006,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="720" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="720" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A720" s="49" t="s">
         <v>5</v>
       </c>
@@ -26023,7 +26035,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="721" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="721" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A721" s="49" t="s">
         <v>165</v>
       </c>
@@ -26052,7 +26064,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="722" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="722" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A722" s="49" t="s">
         <v>6</v>
       </c>
@@ -26081,7 +26093,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="723" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="723" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A723" s="49" t="s">
         <v>5</v>
       </c>
@@ -26110,7 +26122,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="724" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="724" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A724" s="49" t="s">
         <v>21</v>
       </c>
@@ -26139,7 +26151,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="725" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="725" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A725" s="49" t="s">
         <v>21</v>
       </c>
@@ -26168,7 +26180,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="726" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="726" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A726" s="49" t="s">
         <v>21</v>
       </c>
@@ -26197,7 +26209,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="727" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="727" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A727" s="49" t="s">
         <v>22</v>
       </c>
@@ -26226,7 +26238,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="728" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="728" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A728" s="49" t="s">
         <v>62</v>
       </c>
@@ -26255,7 +26267,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="729" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="729" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A729" s="49" t="s">
         <v>23</v>
       </c>
@@ -26284,7 +26296,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="730" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="730" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A730" s="49" t="s">
         <v>5</v>
       </c>
@@ -26313,7 +26325,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="731" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="731" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A731" s="49" t="s">
         <v>6</v>
       </c>
@@ -26342,7 +26354,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="732" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="732" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A732" s="49" t="s">
         <v>62</v>
       </c>
@@ -26371,7 +26383,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="733" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="733" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A733" s="49" t="s">
         <v>21</v>
       </c>
@@ -26400,7 +26412,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="734" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="734" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A734" s="49" t="s">
         <v>23</v>
       </c>
@@ -26429,7 +26441,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="735" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="735" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A735" s="49" t="s">
         <v>5</v>
       </c>
@@ -26458,7 +26470,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="736" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="736" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A736" s="49" t="s">
         <v>5</v>
       </c>
@@ -26487,7 +26499,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="737" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="737" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A737" s="49" t="s">
         <v>21</v>
       </c>
@@ -26516,7 +26528,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="738" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="738" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A738" s="49" t="s">
         <v>21</v>
       </c>
@@ -26545,7 +26557,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="739" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="739" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A739" s="49" t="s">
         <v>165</v>
       </c>
@@ -26574,7 +26586,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="740" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="740" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A740" s="49" t="s">
         <v>165</v>
       </c>
@@ -26603,7 +26615,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="741" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="741" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A741" s="49" t="s">
         <v>62</v>
       </c>
@@ -26632,7 +26644,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="742" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="742" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A742" s="49" t="s">
         <v>352</v>
       </c>
@@ -26661,7 +26673,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="743" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="743" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A743" s="49" t="s">
         <v>5</v>
       </c>
@@ -26690,7 +26702,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="744" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="744" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A744" s="49" t="s">
         <v>7</v>
       </c>
@@ -26704,7 +26716,7 @@
         <v>45758</v>
       </c>
       <c r="E744" s="49" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F744" s="49" t="s">
         <v>9</v>
@@ -26713,13 +26725,13 @@
         <v>4</v>
       </c>
       <c r="H744" s="51" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="I744" s="26" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="745" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="745" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A745" s="49" t="s">
         <v>5</v>
       </c>
@@ -26733,22 +26745,22 @@
         <v>45667</v>
       </c>
       <c r="E745" s="49" t="s">
+        <v>1066</v>
+      </c>
+      <c r="F745" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="G745" s="51">
+        <v>8</v>
+      </c>
+      <c r="H745" s="51" t="s">
         <v>1067</v>
-      </c>
-      <c r="F745" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="G745" s="51">
-        <v>8</v>
-      </c>
-      <c r="H745" s="51" t="s">
-        <v>1068</v>
       </c>
       <c r="I745" s="26" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="746" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="746" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A746" s="49" t="s">
         <v>86</v>
       </c>
@@ -26762,7 +26774,7 @@
         <v>45726</v>
       </c>
       <c r="E746" s="49" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="F746" s="49" t="s">
         <v>8</v>
@@ -26771,13 +26783,13 @@
         <v>71</v>
       </c>
       <c r="H746" s="51" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="I746" s="26" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="747" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="747" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A747" s="49" t="s">
         <v>62</v>
       </c>
@@ -26791,7 +26803,7 @@
         <v>45726</v>
       </c>
       <c r="E747" s="49" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="F747" s="49" t="s">
         <v>9</v>
@@ -26800,13 +26812,13 @@
         <v>100</v>
       </c>
       <c r="H747" s="51" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="I747" s="26" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="748" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="748" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A748" s="49" t="s">
         <v>23</v>
       </c>
@@ -26829,13 +26841,13 @@
         <v>18</v>
       </c>
       <c r="H748" s="51" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="I748" s="26" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="749" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="749" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A749" s="49" t="s">
         <v>23</v>
       </c>
@@ -26858,13 +26870,13 @@
         <v>138</v>
       </c>
       <c r="H749" s="51" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="I749" s="26" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="750" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="750" spans="1:9" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A750" s="49" t="s">
         <v>23</v>
       </c>
@@ -26878,7 +26890,7 @@
         <v>45731</v>
       </c>
       <c r="E750" s="49" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="F750" s="49" t="s">
         <v>9</v>
@@ -26887,13 +26899,13 @@
         <v>125</v>
       </c>
       <c r="H750" s="51" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="I750" s="26" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="751" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="751" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A751" s="49" t="s">
         <v>5</v>
       </c>
@@ -26916,13 +26928,13 @@
         <v>10</v>
       </c>
       <c r="H751" s="51" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="I751" s="26" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="752" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="752" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A752" s="49" t="s">
         <v>5</v>
       </c>
@@ -26936,7 +26948,7 @@
         <v>45732</v>
       </c>
       <c r="E752" s="49" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="F752" s="49" t="s">
         <v>9</v>
@@ -26945,13 +26957,13 @@
         <v>34</v>
       </c>
       <c r="H752" s="51" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="I752" s="26" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="753" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="753" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A753" s="49" t="s">
         <v>62</v>
       </c>
@@ -26980,7 +26992,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="754" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="754" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A754" s="49" t="s">
         <v>21</v>
       </c>
@@ -26994,7 +27006,7 @@
         <v>45733</v>
       </c>
       <c r="E754" s="49" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="F754" s="49" t="s">
         <v>8</v>
@@ -27003,13 +27015,13 @@
         <v>15</v>
       </c>
       <c r="H754" s="51" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="I754" s="26" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="755" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="755" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A755" s="49" t="s">
         <v>6</v>
       </c>
@@ -27023,7 +27035,7 @@
         <v>45748</v>
       </c>
       <c r="E755" s="49" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="F755" s="49" t="s">
         <v>8</v>
@@ -27032,13 +27044,13 @@
         <v>69</v>
       </c>
       <c r="H755" s="51" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="I755" s="26" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="756" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="756" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A756" s="49" t="s">
         <v>84</v>
       </c>
@@ -27052,7 +27064,7 @@
         <v>45667</v>
       </c>
       <c r="E756" s="49" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="F756" s="49" t="s">
         <v>9</v>
@@ -27061,57 +27073,129 @@
         <v>58</v>
       </c>
       <c r="H756" s="51" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="I756" s="26" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="757" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A757" s="49"/>
-      <c r="B757" s="50"/>
-      <c r="C757" s="50"/>
-      <c r="D757" s="50"/>
-      <c r="E757" s="49"/>
-      <c r="F757" s="49"/>
-      <c r="G757" s="51"/>
-      <c r="H757" s="51"/>
-      <c r="I757" s="26"/>
-    </row>
-    <row r="758" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A758" s="49"/>
-      <c r="B758" s="50"/>
-      <c r="C758" s="50"/>
-      <c r="D758" s="50"/>
-      <c r="E758" s="49"/>
-      <c r="F758" s="49"/>
-      <c r="G758" s="51"/>
-      <c r="H758" s="51"/>
-      <c r="I758" s="26"/>
-    </row>
-    <row r="759" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A759" s="49"/>
-      <c r="B759" s="50"/>
-      <c r="C759" s="50"/>
-      <c r="D759" s="50"/>
-      <c r="E759" s="49"/>
-      <c r="F759" s="49"/>
-      <c r="G759" s="51"/>
-      <c r="H759" s="51"/>
-      <c r="I759" s="26"/>
-    </row>
-    <row r="760" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A760" s="49"/>
-      <c r="B760" s="50"/>
-      <c r="C760" s="50"/>
-      <c r="D760" s="50"/>
-      <c r="E760" s="49"/>
-      <c r="F760" s="49"/>
-      <c r="G760" s="51"/>
-      <c r="H760" s="51"/>
-      <c r="I760" s="26"/>
-    </row>
-    <row r="761" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="757" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A757" s="49" t="s">
+        <v>62</v>
+      </c>
+      <c r="B757" s="50">
+        <v>45673</v>
+      </c>
+      <c r="C757" s="50">
+        <v>45673</v>
+      </c>
+      <c r="D757" s="50">
+        <v>45678</v>
+      </c>
+      <c r="E757" s="49" t="s">
+        <v>1085</v>
+      </c>
+      <c r="F757" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="G757" s="51">
+        <v>47</v>
+      </c>
+      <c r="H757" s="51" t="s">
+        <v>1086</v>
+      </c>
+      <c r="I757" s="26" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="758" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A758" s="49" t="s">
+        <v>62</v>
+      </c>
+      <c r="B758" s="50">
+        <v>45673</v>
+      </c>
+      <c r="C758" s="50">
+        <v>45673</v>
+      </c>
+      <c r="D758" s="50">
+        <v>45678</v>
+      </c>
+      <c r="E758" s="49" t="s">
+        <v>1085</v>
+      </c>
+      <c r="F758" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="G758" s="51">
+        <v>21</v>
+      </c>
+      <c r="H758" s="51" t="s">
+        <v>1087</v>
+      </c>
+      <c r="I758" s="26" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="759" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A759" s="49" t="s">
+        <v>165</v>
+      </c>
+      <c r="B759" s="50">
+        <v>45673</v>
+      </c>
+      <c r="C759" s="50">
+        <v>45673</v>
+      </c>
+      <c r="D759" s="50">
+        <v>45787</v>
+      </c>
+      <c r="E759" s="49" t="s">
+        <v>1049</v>
+      </c>
+      <c r="F759" s="49" t="s">
+        <v>8</v>
+      </c>
+      <c r="G759" s="51">
+        <v>79</v>
+      </c>
+      <c r="H759" s="51" t="s">
+        <v>1088</v>
+      </c>
+      <c r="I759" s="26" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="760" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A760" s="49" t="s">
+        <v>5</v>
+      </c>
+      <c r="B760" s="50">
+        <v>45673</v>
+      </c>
+      <c r="C760" s="50">
+        <v>45674</v>
+      </c>
+      <c r="D760" s="50">
+        <v>45733</v>
+      </c>
+      <c r="E760" s="49" t="s">
+        <v>993</v>
+      </c>
+      <c r="F760" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="G760" s="51">
+        <v>21</v>
+      </c>
+      <c r="H760" s="51" t="s">
+        <v>994</v>
+      </c>
+      <c r="I760" s="26" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="761" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A761" s="49"/>
       <c r="B761" s="50"/>
       <c r="C761" s="50"/>
@@ -27122,7 +27206,7 @@
       <c r="H761" s="51"/>
       <c r="I761" s="26"/>
     </row>
-    <row r="762" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="762" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A762" s="49"/>
       <c r="B762" s="50"/>
       <c r="C762" s="50"/>
@@ -27133,7 +27217,7 @@
       <c r="H762" s="51"/>
       <c r="I762" s="26"/>
     </row>
-    <row r="763" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="763" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A763" s="49"/>
       <c r="B763" s="50"/>
       <c r="C763" s="50"/>
@@ -27144,7 +27228,7 @@
       <c r="H763" s="51"/>
       <c r="I763" s="26"/>
     </row>
-    <row r="764" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="764" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A764" s="49"/>
       <c r="B764" s="50"/>
       <c r="C764" s="50"/>
@@ -27155,7 +27239,7 @@
       <c r="H764" s="51"/>
       <c r="I764" s="26"/>
     </row>
-    <row r="765" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="765" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A765" s="49"/>
       <c r="B765" s="50"/>
       <c r="C765" s="50"/>
@@ -27166,7 +27250,7 @@
       <c r="H765" s="51"/>
       <c r="I765" s="26"/>
     </row>
-    <row r="766" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="766" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A766" s="49"/>
       <c r="B766" s="50"/>
       <c r="C766" s="50"/>
@@ -27191,7 +27275,7 @@
           <x14:formula1>
             <xm:f>'Industry List'!$A$1:$A$22</xm:f>
           </x14:formula1>
-          <xm:sqref>I3:I756</xm:sqref>
+          <xm:sqref>I3:I760</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -27202,18 +27286,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CC03875-3DF4-4258-8762-7FFE2A7D620D}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.7265625" style="22" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.7109375" style="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="95" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="97.5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="15" t="s">
         <v>20</v>
       </c>
@@ -27221,7 +27305,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="s">
         <v>24</v>
       </c>
@@ -27230,7 +27314,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
         <v>13</v>
       </c>
@@ -27239,7 +27323,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
         <v>14</v>
       </c>
@@ -27248,7 +27332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="17" t="s">
         <v>15</v>
       </c>
@@ -27257,7 +27341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="17" t="s">
         <v>16</v>
       </c>
@@ -27266,7 +27350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
         <v>17</v>
       </c>
@@ -27275,7 +27359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>18</v>
       </c>
@@ -27298,25 +27382,25 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EE76718-798E-45ED-8CA1-01AA760CE5F1}">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.453125" style="18" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.1796875" style="18" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.26953125" style="18" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="31.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="34.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" style="18" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.28515625" style="18" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="34.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="108.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" ht="110.25" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
-        <v>1064</v>
+        <v>1089</v>
       </c>
       <c r="E1"/>
     </row>
-    <row r="2" spans="1:8" ht="24" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A2" s="19" t="s">
         <v>0</v>
       </c>
@@ -27342,7 +27426,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -27379,117 +27463,117 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E81B0C9-EE0D-4672-99B4-ACA7D2D31E92}">
   <dimension ref="A1:A22"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="67.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="67.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>194</v>
       </c>

--- a/data/warn-scraper/cache/ca/warn_report1.xlsx
+++ b/data/warn-scraper/cache/ca/warn_report1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\entshare3\JS-Data\WSB-CO\BPAC\Policy &amp; Program Communications Group\Communications Unit\Website Management\5. WARN (Worker Adjustment and Retraining Notification) Updates\2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EFC2745D-5A94-4E77-83CB-F46229CF52D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96C56D35-4CE0-4CFB-8AB2-65948F060E30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="751" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="751" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
   <sheets>
     <sheet name="Index" sheetId="3" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3861" uniqueCount="1091">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3921" uniqueCount="1104">
   <si>
     <t>County/Parish</t>
   </si>
@@ -3396,7 +3396,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">WARN REPORT - 01/01/2023 - 01/20/2025
+      <t xml:space="preserve">WARN REPORT - 01/01/2023 - 01/22/2025
 </t>
     </r>
     <r>
@@ -3410,6 +3410,45 @@
     </r>
   </si>
   <si>
+    <t>Del Monte Foods, Inc.</t>
+  </si>
+  <si>
+    <t>10652 Jackson Avenue  Hanford CA 93230</t>
+  </si>
+  <si>
+    <t>Fast Ride Moto, LLC</t>
+  </si>
+  <si>
+    <t>6919 North Avenue  Lemon Grove CA 91945</t>
+  </si>
+  <si>
+    <t>Quanex Homeshield LLC</t>
+  </si>
+  <si>
+    <t>3640 Ramos Drive, Suite #120  West Sacramento CA 95691</t>
+  </si>
+  <si>
+    <t>1438 Webster Street  Oakland CA 94612</t>
+  </si>
+  <si>
+    <t>5820 Owens Drive  Pleasanton CA 94588</t>
+  </si>
+  <si>
+    <t>10949 Pendleton Street  Sun Valley CA 91352</t>
+  </si>
+  <si>
+    <t>4733 W. Sunset Blvd  Los Angeles CA 90027</t>
+  </si>
+  <si>
+    <t>1840 California Avenue  Corona CA 92881</t>
+  </si>
+  <si>
+    <t>1900 S. Norfolk Street  San Mateo CA 94403</t>
+  </si>
+  <si>
+    <t>276 International Circle  San Jose CA 95119</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">WARN REPORT - </t>
     </r>
@@ -3421,7 +3460,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>07/01/24 to 01/20/2025</t>
+      <t>07/01/24 to 01/22/2025</t>
     </r>
     <r>
       <rPr>
@@ -3441,7 +3480,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I760.</t>
+      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I772.</t>
     </r>
   </si>
 </sst>
@@ -4668,8 +4707,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I760" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
-  <autoFilter ref="A2:I760" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I772" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
+  <autoFilter ref="A2:I772" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -5023,37 +5062,37 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D341DFFF-02D2-4572-95F5-BB3221952133}">
   <dimension ref="A1:A6"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="74" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="135" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A1" s="10" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="21" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:1" ht="21" x14ac:dyDescent="0.5">
       <c r="A2" s="12" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" s="13" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" s="13" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" s="13" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A6" s="13" t="s">
         <v>33</v>
       </c>
@@ -5072,18 +5111,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1832896D-8AFB-4FFC-957E-910308F3BC0C}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="28.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.453125" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.453125" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="76.5" x14ac:dyDescent="0.35">
       <c r="A1" s="10" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="14" t="s">
         <v>20</v>
       </c>
@@ -5091,25 +5130,25 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B3" s="11">
         <f>SUM('Detailed WARN Report '!G:G)</f>
-        <v>42517</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>42998</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B4" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Permanent")</f>
-        <v>396</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>14</v>
       </c>
@@ -5118,7 +5157,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>15</v>
       </c>
@@ -5126,16 +5165,16 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B7" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Permanent")</f>
-        <v>332</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>17</v>
       </c>
@@ -5144,7 +5183,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>18</v>
       </c>
@@ -5164,27 +5203,27 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:I766"/>
-  <sheetFormatPr defaultColWidth="102.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:I778"/>
+  <sheetFormatPr defaultColWidth="102.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="28.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.7265625" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.85546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.42578125" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="62.28515625" style="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.28515625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="9.85546875" style="3" customWidth="1"/>
-    <col min="8" max="8" width="57.7109375" style="3" customWidth="1"/>
-    <col min="9" max="9" width="51.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.81640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.453125" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="62.26953125" style="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.26953125" style="3" customWidth="1"/>
+    <col min="7" max="7" width="9.81640625" style="3" customWidth="1"/>
+    <col min="8" max="8" width="57.7265625" style="3" customWidth="1"/>
+    <col min="9" max="9" width="51.81640625" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="102" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="100" x14ac:dyDescent="0.35">
       <c r="A1" s="16" t="s">
-        <v>1090</v>
+        <v>1103</v>
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:9" ht="24.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="24" x14ac:dyDescent="0.35">
       <c r="A2" s="29" t="s">
         <v>0</v>
       </c>
@@ -5213,7 +5252,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" s="26" t="s">
         <v>5</v>
       </c>
@@ -5242,7 +5281,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" s="26" t="s">
         <v>21</v>
       </c>
@@ -5271,7 +5310,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" s="26" t="s">
         <v>7</v>
       </c>
@@ -5300,7 +5339,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" s="26" t="s">
         <v>5</v>
       </c>
@@ -5329,7 +5368,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" s="26" t="s">
         <v>6</v>
       </c>
@@ -5358,7 +5397,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" s="26" t="s">
         <v>6</v>
       </c>
@@ -5387,7 +5426,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" s="26" t="s">
         <v>49</v>
       </c>
@@ -5416,7 +5455,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" s="26" t="s">
         <v>23</v>
       </c>
@@ -5445,7 +5484,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" s="26" t="s">
         <v>22</v>
       </c>
@@ -5474,7 +5513,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" s="26" t="s">
         <v>22</v>
       </c>
@@ -5503,7 +5542,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" s="26" t="s">
         <v>5</v>
       </c>
@@ -5532,7 +5571,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" s="26" t="s">
         <v>21</v>
       </c>
@@ -5561,7 +5600,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" s="26" t="s">
         <v>6</v>
       </c>
@@ -5590,7 +5629,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" s="26" t="s">
         <v>62</v>
       </c>
@@ -5619,7 +5658,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" s="26" t="s">
         <v>6</v>
       </c>
@@ -5648,7 +5687,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" s="26" t="s">
         <v>6</v>
       </c>
@@ -5677,7 +5716,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" s="26" t="s">
         <v>67</v>
       </c>
@@ -5706,7 +5745,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" s="26" t="s">
         <v>22</v>
       </c>
@@ -5735,7 +5774,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" s="26" t="s">
         <v>6</v>
       </c>
@@ -5764,7 +5803,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" s="26" t="s">
         <v>6</v>
       </c>
@@ -5793,7 +5832,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" s="26" t="s">
         <v>5</v>
       </c>
@@ -5822,7 +5861,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" s="26" t="s">
         <v>5</v>
       </c>
@@ -5851,7 +5890,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" s="26" t="s">
         <v>79</v>
       </c>
@@ -5880,7 +5919,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" s="26" t="s">
         <v>21</v>
       </c>
@@ -5909,7 +5948,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" s="26" t="s">
         <v>84</v>
       </c>
@@ -5938,7 +5977,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" s="26" t="s">
         <v>86</v>
       </c>
@@ -5967,7 +6006,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" s="26" t="s">
         <v>22</v>
       </c>
@@ -5996,7 +6035,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" s="26" t="s">
         <v>5</v>
       </c>
@@ -6025,7 +6064,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" s="26" t="s">
         <v>5</v>
       </c>
@@ -6054,7 +6093,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32" s="26" t="s">
         <v>5</v>
       </c>
@@ -6083,7 +6122,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" s="26" t="s">
         <v>23</v>
       </c>
@@ -6112,7 +6151,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34" s="26" t="s">
         <v>23</v>
       </c>
@@ -6141,7 +6180,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35" s="26" t="s">
         <v>5</v>
       </c>
@@ -6170,7 +6209,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36" s="26" t="s">
         <v>5</v>
       </c>
@@ -6199,7 +6238,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37" s="26" t="s">
         <v>5</v>
       </c>
@@ -6228,7 +6267,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38" s="26" t="s">
         <v>5</v>
       </c>
@@ -6257,7 +6296,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39" s="26" t="s">
         <v>5</v>
       </c>
@@ -6286,7 +6325,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40" s="26" t="s">
         <v>5</v>
       </c>
@@ -6315,7 +6354,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A41" s="26" t="s">
         <v>5</v>
       </c>
@@ -6344,7 +6383,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42" s="26" t="s">
         <v>5</v>
       </c>
@@ -6373,7 +6412,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A43" s="26" t="s">
         <v>21</v>
       </c>
@@ -6402,7 +6441,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A44" s="26" t="s">
         <v>106</v>
       </c>
@@ -6431,7 +6470,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A45" s="26" t="s">
         <v>106</v>
       </c>
@@ -6460,7 +6499,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A46" s="26" t="s">
         <v>22</v>
       </c>
@@ -6489,7 +6528,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A47" s="26" t="s">
         <v>22</v>
       </c>
@@ -6518,7 +6557,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A48" s="26" t="s">
         <v>22</v>
       </c>
@@ -6547,7 +6586,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A49" s="26" t="s">
         <v>22</v>
       </c>
@@ -6576,7 +6615,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A50" s="26" t="s">
         <v>114</v>
       </c>
@@ -6605,7 +6644,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A51" s="26" t="s">
         <v>5</v>
       </c>
@@ -6634,7 +6673,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A52" s="26" t="s">
         <v>5</v>
       </c>
@@ -6663,7 +6702,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A53" s="26" t="s">
         <v>5</v>
       </c>
@@ -6692,7 +6731,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A54" s="26" t="s">
         <v>79</v>
       </c>
@@ -6721,7 +6760,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A55" s="26" t="s">
         <v>79</v>
       </c>
@@ -6750,7 +6789,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A56" s="26" t="s">
         <v>5</v>
       </c>
@@ -6779,7 +6818,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A57" s="26" t="s">
         <v>5</v>
       </c>
@@ -6808,7 +6847,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A58" s="26" t="s">
         <v>5</v>
       </c>
@@ -6837,7 +6876,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A59" s="26" t="s">
         <v>84</v>
       </c>
@@ -6866,7 +6905,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A60" s="26" t="s">
         <v>5</v>
       </c>
@@ -6895,7 +6934,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A61" s="26" t="s">
         <v>23</v>
       </c>
@@ -6924,7 +6963,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A62" s="26" t="s">
         <v>23</v>
       </c>
@@ -6953,7 +6992,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A63" s="26" t="s">
         <v>23</v>
       </c>
@@ -6982,7 +7021,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A64" s="26" t="s">
         <v>23</v>
       </c>
@@ -7011,7 +7050,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A65" s="26" t="s">
         <v>49</v>
       </c>
@@ -7040,7 +7079,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A66" s="26" t="s">
         <v>139</v>
       </c>
@@ -7069,7 +7108,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A67" s="26" t="s">
         <v>139</v>
       </c>
@@ -7098,7 +7137,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A68" s="26" t="s">
         <v>142</v>
       </c>
@@ -7127,7 +7166,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A69" s="26" t="s">
         <v>144</v>
       </c>
@@ -7156,7 +7195,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A70" s="26" t="s">
         <v>144</v>
       </c>
@@ -7185,7 +7224,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A71" s="26" t="s">
         <v>144</v>
       </c>
@@ -7214,7 +7253,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A72" s="26" t="s">
         <v>144</v>
       </c>
@@ -7243,7 +7282,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A73" s="26" t="s">
         <v>144</v>
       </c>
@@ -7272,7 +7311,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A74" s="26" t="s">
         <v>144</v>
       </c>
@@ -7301,7 +7340,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A75" s="26" t="s">
         <v>23</v>
       </c>
@@ -7330,7 +7369,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A76" s="26" t="s">
         <v>21</v>
       </c>
@@ -7359,7 +7398,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A77" s="26" t="s">
         <v>155</v>
       </c>
@@ -7388,7 +7427,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A78" s="26" t="s">
         <v>23</v>
       </c>
@@ -7417,7 +7456,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A79" s="26" t="s">
         <v>23</v>
       </c>
@@ -7446,7 +7485,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A80" s="26" t="s">
         <v>79</v>
       </c>
@@ -7475,7 +7514,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A81" s="26" t="s">
         <v>5</v>
       </c>
@@ -7504,7 +7543,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A82" s="26" t="s">
         <v>21</v>
       </c>
@@ -7533,7 +7572,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A83" s="26" t="s">
         <v>165</v>
       </c>
@@ -7562,7 +7601,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A84" s="26" t="s">
         <v>22</v>
       </c>
@@ -7591,7 +7630,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A85" s="26" t="s">
         <v>6</v>
       </c>
@@ -7620,7 +7659,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A86" s="26" t="s">
         <v>62</v>
       </c>
@@ -7649,7 +7688,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A87" s="26" t="s">
         <v>84</v>
       </c>
@@ -7678,7 +7717,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A88" s="26" t="s">
         <v>62</v>
       </c>
@@ -7707,7 +7746,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A89" s="26" t="s">
         <v>21</v>
       </c>
@@ -7736,7 +7775,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A90" s="26" t="s">
         <v>114</v>
       </c>
@@ -7765,7 +7804,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A91" s="26" t="s">
         <v>79</v>
       </c>
@@ -7794,7 +7833,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A92" s="26" t="s">
         <v>79</v>
       </c>
@@ -7823,7 +7862,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A93" s="26" t="s">
         <v>7</v>
       </c>
@@ -7852,7 +7891,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A94" s="26" t="s">
         <v>5</v>
       </c>
@@ -7881,7 +7920,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A95" s="26" t="s">
         <v>5</v>
       </c>
@@ -7910,7 +7949,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A96" s="26" t="s">
         <v>5</v>
       </c>
@@ -7939,7 +7978,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A97" s="26" t="s">
         <v>5</v>
       </c>
@@ -7968,7 +8007,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A98" s="26" t="s">
         <v>5</v>
       </c>
@@ -7997,7 +8036,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A99" s="26" t="s">
         <v>5</v>
       </c>
@@ -8026,7 +8065,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A100" s="26" t="s">
         <v>5</v>
       </c>
@@ -8055,7 +8094,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A101" s="26" t="s">
         <v>86</v>
       </c>
@@ -8084,7 +8123,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A102" s="26" t="s">
         <v>62</v>
       </c>
@@ -8113,7 +8152,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A103" s="26" t="s">
         <v>62</v>
       </c>
@@ -8142,7 +8181,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A104" s="26" t="s">
         <v>62</v>
       </c>
@@ -8171,7 +8210,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A105" s="26" t="s">
         <v>62</v>
       </c>
@@ -8200,7 +8239,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A106" s="26" t="s">
         <v>165</v>
       </c>
@@ -8229,7 +8268,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A107" s="26" t="s">
         <v>6</v>
       </c>
@@ -8258,7 +8297,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A108" s="26" t="s">
         <v>6</v>
       </c>
@@ -8287,7 +8326,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A109" s="26" t="s">
         <v>84</v>
       </c>
@@ -8316,7 +8355,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A110" s="26" t="s">
         <v>6</v>
       </c>
@@ -8345,7 +8384,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A111" s="26" t="s">
         <v>6</v>
       </c>
@@ -8374,7 +8413,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A112" s="26" t="s">
         <v>84</v>
       </c>
@@ -8403,7 +8442,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A113" s="26" t="s">
         <v>21</v>
       </c>
@@ -8432,7 +8471,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A114" s="26" t="s">
         <v>5</v>
       </c>
@@ -8461,7 +8500,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A115" s="26" t="s">
         <v>84</v>
       </c>
@@ -8490,7 +8529,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A116" s="26" t="s">
         <v>21</v>
       </c>
@@ -8519,7 +8558,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A117" s="26" t="s">
         <v>242</v>
       </c>
@@ -8548,7 +8587,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A118" s="26" t="s">
         <v>22</v>
       </c>
@@ -8577,7 +8616,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A119" s="26" t="s">
         <v>5</v>
       </c>
@@ -8606,7 +8645,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A120" s="26" t="s">
         <v>23</v>
       </c>
@@ -8635,7 +8674,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A121" s="26" t="s">
         <v>5</v>
       </c>
@@ -8664,7 +8703,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A122" s="26" t="s">
         <v>22</v>
       </c>
@@ -8693,7 +8732,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A123" s="26" t="s">
         <v>114</v>
       </c>
@@ -8722,7 +8761,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A124" s="26" t="s">
         <v>84</v>
       </c>
@@ -8751,7 +8790,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A125" s="26" t="s">
         <v>247</v>
       </c>
@@ -8780,7 +8819,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A126" s="32" t="s">
         <v>5</v>
       </c>
@@ -8809,7 +8848,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A127" s="32" t="s">
         <v>86</v>
       </c>
@@ -8838,7 +8877,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A128" s="32" t="s">
         <v>62</v>
       </c>
@@ -8867,7 +8906,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A129" s="32" t="s">
         <v>165</v>
       </c>
@@ -8896,7 +8935,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A130" s="32" t="s">
         <v>22</v>
       </c>
@@ -8925,7 +8964,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A131" s="33" t="s">
         <v>6</v>
       </c>
@@ -8954,7 +8993,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A132" s="39" t="s">
         <v>114</v>
       </c>
@@ -8983,7 +9022,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A133" s="39" t="s">
         <v>5</v>
       </c>
@@ -9012,7 +9051,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A134" s="39" t="s">
         <v>5</v>
       </c>
@@ -9041,7 +9080,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A135" s="39" t="s">
         <v>5</v>
       </c>
@@ -9070,7 +9109,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A136" s="39" t="s">
         <v>21</v>
       </c>
@@ -9099,7 +9138,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A137" s="39" t="s">
         <v>23</v>
       </c>
@@ -9128,7 +9167,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A138" s="39" t="s">
         <v>23</v>
       </c>
@@ -9157,7 +9196,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A139" s="39" t="s">
         <v>6</v>
       </c>
@@ -9186,7 +9225,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A140" s="39" t="s">
         <v>79</v>
       </c>
@@ -9215,7 +9254,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A141" s="39" t="s">
         <v>84</v>
       </c>
@@ -9244,7 +9283,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A142" s="39" t="s">
         <v>6</v>
       </c>
@@ -9273,7 +9312,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A143" s="39" t="s">
         <v>62</v>
       </c>
@@ -9302,7 +9341,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A144" s="39" t="s">
         <v>289</v>
       </c>
@@ -9331,7 +9370,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A145" s="39" t="s">
         <v>292</v>
       </c>
@@ -9360,7 +9399,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A146" s="39" t="s">
         <v>5</v>
       </c>
@@ -9389,7 +9428,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A147" s="39" t="s">
         <v>86</v>
       </c>
@@ -9418,7 +9457,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A148" s="39" t="s">
         <v>289</v>
       </c>
@@ -9447,7 +9486,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A149" s="39" t="s">
         <v>5</v>
       </c>
@@ -9476,7 +9515,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A150" s="39" t="s">
         <v>21</v>
       </c>
@@ -9505,7 +9544,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A151" s="39" t="s">
         <v>79</v>
       </c>
@@ -9534,7 +9573,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A152" s="39" t="s">
         <v>79</v>
       </c>
@@ -9563,7 +9602,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A153" s="39" t="s">
         <v>79</v>
       </c>
@@ -9592,7 +9631,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A154" s="39" t="s">
         <v>5</v>
       </c>
@@ -9621,7 +9660,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A155" s="39" t="s">
         <v>247</v>
       </c>
@@ -9650,7 +9689,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A156" s="39" t="s">
         <v>23</v>
       </c>
@@ -9679,7 +9718,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A157" s="39" t="s">
         <v>5</v>
       </c>
@@ -9708,7 +9747,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A158" s="39" t="s">
         <v>5</v>
       </c>
@@ -9737,7 +9776,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A159" s="39" t="s">
         <v>5</v>
       </c>
@@ -9766,7 +9805,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A160" s="39" t="s">
         <v>5</v>
       </c>
@@ -9795,7 +9834,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A161" s="39" t="s">
         <v>5</v>
       </c>
@@ -9824,7 +9863,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A162" s="39" t="s">
         <v>84</v>
       </c>
@@ -9853,7 +9892,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A163" s="39" t="s">
         <v>86</v>
       </c>
@@ -9882,7 +9921,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A164" s="39" t="s">
         <v>62</v>
       </c>
@@ -9911,7 +9950,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A165" s="39" t="s">
         <v>292</v>
       </c>
@@ -9940,7 +9979,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A166" s="39" t="s">
         <v>5</v>
       </c>
@@ -9969,7 +10008,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A167" s="39" t="s">
         <v>21</v>
       </c>
@@ -9998,7 +10037,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A168" s="39" t="s">
         <v>62</v>
       </c>
@@ -10027,7 +10066,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A169" s="39" t="s">
         <v>62</v>
       </c>
@@ -10056,7 +10095,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A170" s="39" t="s">
         <v>62</v>
       </c>
@@ -10085,7 +10124,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A171" s="39" t="s">
         <v>62</v>
       </c>
@@ -10114,7 +10153,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A172" s="39" t="s">
         <v>6</v>
       </c>
@@ -10143,7 +10182,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A173" s="39" t="s">
         <v>5</v>
       </c>
@@ -10172,7 +10211,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A174" s="39" t="s">
         <v>5</v>
       </c>
@@ -10201,7 +10240,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A175" s="39" t="s">
         <v>5</v>
       </c>
@@ -10230,7 +10269,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A176" s="39" t="s">
         <v>5</v>
       </c>
@@ -10259,7 +10298,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A177" s="39" t="s">
         <v>5</v>
       </c>
@@ -10288,7 +10327,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A178" s="39" t="s">
         <v>139</v>
       </c>
@@ -10317,7 +10356,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A179" s="39" t="s">
         <v>344</v>
       </c>
@@ -10346,7 +10385,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A180" s="39" t="s">
         <v>155</v>
       </c>
@@ -10375,7 +10414,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A181" s="39" t="s">
         <v>22</v>
       </c>
@@ -10404,7 +10443,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A182" s="39" t="s">
         <v>22</v>
       </c>
@@ -10433,7 +10472,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A183" s="39" t="s">
         <v>6</v>
       </c>
@@ -10462,7 +10501,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A184" s="39" t="s">
         <v>352</v>
       </c>
@@ -10491,7 +10530,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A185" s="39" t="s">
         <v>352</v>
       </c>
@@ -10520,7 +10559,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A186" s="39" t="s">
         <v>144</v>
       </c>
@@ -10549,7 +10588,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A187" s="39" t="s">
         <v>23</v>
       </c>
@@ -10578,7 +10617,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A188" s="39" t="s">
         <v>5</v>
       </c>
@@ -10607,7 +10646,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A189" s="39" t="s">
         <v>21</v>
       </c>
@@ -10636,7 +10675,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A190" s="39" t="s">
         <v>21</v>
       </c>
@@ -10665,7 +10704,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A191" s="39" t="s">
         <v>84</v>
       </c>
@@ -10694,7 +10733,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A192" s="39" t="s">
         <v>62</v>
       </c>
@@ -10723,7 +10762,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A193" s="39" t="s">
         <v>22</v>
       </c>
@@ -10752,7 +10791,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A194" s="39" t="s">
         <v>22</v>
       </c>
@@ -10781,7 +10820,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A195" s="39" t="s">
         <v>6</v>
       </c>
@@ -10810,7 +10849,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A196" s="39" t="s">
         <v>289</v>
       </c>
@@ -10839,7 +10878,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A197" s="39" t="s">
         <v>22</v>
       </c>
@@ -10868,7 +10907,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A198" s="39" t="s">
         <v>23</v>
       </c>
@@ -10897,7 +10936,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A199" s="39" t="s">
         <v>5</v>
       </c>
@@ -10926,7 +10965,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A200" s="39" t="s">
         <v>21</v>
       </c>
@@ -10955,7 +10994,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A201" s="39" t="s">
         <v>6</v>
       </c>
@@ -10984,7 +11023,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A202" s="39" t="s">
         <v>6</v>
       </c>
@@ -11013,7 +11052,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A203" s="39" t="s">
         <v>6</v>
       </c>
@@ -11042,7 +11081,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A204" s="39" t="s">
         <v>383</v>
       </c>
@@ -11071,7 +11110,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A205" s="39" t="s">
         <v>5</v>
       </c>
@@ -11100,7 +11139,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A206" s="26" t="s">
         <v>22</v>
       </c>
@@ -11129,7 +11168,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A207" s="26" t="s">
         <v>6</v>
       </c>
@@ -11158,7 +11197,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A208" s="26" t="s">
         <v>84</v>
       </c>
@@ -11187,7 +11226,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A209" s="26" t="s">
         <v>62</v>
       </c>
@@ -11216,7 +11255,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A210" s="26" t="s">
         <v>106</v>
       </c>
@@ -11245,7 +11284,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A211" s="26" t="s">
         <v>22</v>
       </c>
@@ -11274,7 +11313,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A212" s="26" t="s">
         <v>5</v>
       </c>
@@ -11303,7 +11342,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A213" s="26" t="s">
         <v>5</v>
       </c>
@@ -11332,7 +11371,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A214" s="26" t="s">
         <v>21</v>
       </c>
@@ -11361,7 +11400,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A215" s="26" t="s">
         <v>21</v>
       </c>
@@ -11390,7 +11429,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A216" s="26" t="s">
         <v>23</v>
       </c>
@@ -11419,7 +11458,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A217" s="26" t="s">
         <v>165</v>
       </c>
@@ -11448,7 +11487,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A218" s="26" t="s">
         <v>22</v>
       </c>
@@ -11477,7 +11516,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A219" s="26" t="s">
         <v>22</v>
       </c>
@@ -11506,7 +11545,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A220" s="26" t="s">
         <v>22</v>
       </c>
@@ -11535,7 +11574,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A221" s="26" t="s">
         <v>247</v>
       </c>
@@ -11564,7 +11603,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A222" s="26" t="s">
         <v>84</v>
       </c>
@@ -11593,7 +11632,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A223" s="49" t="s">
         <v>84</v>
       </c>
@@ -11622,7 +11661,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A224" s="49" t="s">
         <v>62</v>
       </c>
@@ -11651,7 +11690,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A225" s="49" t="s">
         <v>62</v>
       </c>
@@ -11680,7 +11719,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A226" s="49" t="s">
         <v>62</v>
       </c>
@@ -11709,7 +11748,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A227" s="49" t="s">
         <v>415</v>
       </c>
@@ -11738,7 +11777,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A228" s="49" t="s">
         <v>23</v>
       </c>
@@ -11767,7 +11806,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A229" s="49" t="s">
         <v>21</v>
       </c>
@@ -11796,7 +11835,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A230" s="49" t="s">
         <v>5</v>
       </c>
@@ -11825,7 +11864,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A231" s="49" t="s">
         <v>23</v>
       </c>
@@ -11854,7 +11893,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A232" s="49" t="s">
         <v>23</v>
       </c>
@@ -11883,7 +11922,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A233" s="49" t="s">
         <v>23</v>
       </c>
@@ -11912,7 +11951,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A234" s="49" t="s">
         <v>23</v>
       </c>
@@ -11941,7 +11980,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A235" s="49" t="s">
         <v>23</v>
       </c>
@@ -11970,7 +12009,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A236" s="49" t="s">
         <v>79</v>
       </c>
@@ -11999,7 +12038,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A237" s="49" t="s">
         <v>5</v>
       </c>
@@ -12028,7 +12067,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A238" s="49" t="s">
         <v>5</v>
       </c>
@@ -12057,7 +12096,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A239" s="49" t="s">
         <v>5</v>
       </c>
@@ -12086,7 +12125,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A240" s="49" t="s">
         <v>5</v>
       </c>
@@ -12115,7 +12154,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A241" s="49" t="s">
         <v>5</v>
       </c>
@@ -12144,7 +12183,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A242" s="49" t="s">
         <v>21</v>
       </c>
@@ -12173,7 +12212,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A243" s="49" t="s">
         <v>106</v>
       </c>
@@ -12202,7 +12241,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A244" s="49" t="s">
         <v>106</v>
       </c>
@@ -12231,7 +12270,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A245" s="49" t="s">
         <v>165</v>
       </c>
@@ -12260,7 +12299,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A246" s="49" t="s">
         <v>165</v>
       </c>
@@ -12289,7 +12328,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A247" s="49" t="s">
         <v>86</v>
       </c>
@@ -12318,7 +12357,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A248" s="49" t="s">
         <v>144</v>
       </c>
@@ -12347,7 +12386,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A249" s="49" t="s">
         <v>5</v>
       </c>
@@ -12376,7 +12415,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A250" s="49" t="s">
         <v>5</v>
       </c>
@@ -12405,7 +12444,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A251" s="49" t="s">
         <v>5</v>
       </c>
@@ -12434,7 +12473,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A252" s="49" t="s">
         <v>62</v>
       </c>
@@ -12463,7 +12502,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A253" s="49" t="s">
         <v>79</v>
       </c>
@@ -12492,7 +12531,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A254" s="49" t="s">
         <v>292</v>
       </c>
@@ -12521,7 +12560,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A255" s="49" t="s">
         <v>5</v>
       </c>
@@ -12550,7 +12589,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A256" s="49" t="s">
         <v>5</v>
       </c>
@@ -12579,7 +12618,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A257" s="49" t="s">
         <v>5</v>
       </c>
@@ -12608,7 +12647,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A258" s="49" t="s">
         <v>5</v>
       </c>
@@ -12637,7 +12676,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A259" s="49" t="s">
         <v>6</v>
       </c>
@@ -12666,7 +12705,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A260" s="49" t="s">
         <v>453</v>
       </c>
@@ -12695,7 +12734,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A261" s="49" t="s">
         <v>292</v>
       </c>
@@ -12724,7 +12763,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A262" s="49" t="s">
         <v>453</v>
       </c>
@@ -12753,7 +12792,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A263" s="49" t="s">
         <v>23</v>
       </c>
@@ -12782,7 +12821,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A264" s="49" t="s">
         <v>5</v>
       </c>
@@ -12811,7 +12850,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A265" s="49" t="s">
         <v>5</v>
       </c>
@@ -12840,7 +12879,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A266" s="49" t="s">
         <v>5</v>
       </c>
@@ -12869,7 +12908,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A267" s="49" t="s">
         <v>62</v>
       </c>
@@ -12898,7 +12937,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A268" s="49" t="s">
         <v>106</v>
       </c>
@@ -12927,7 +12966,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A269" s="49" t="s">
         <v>22</v>
       </c>
@@ -12956,7 +12995,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A270" s="49" t="s">
         <v>144</v>
       </c>
@@ -12985,7 +13024,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A271" s="49" t="s">
         <v>5</v>
       </c>
@@ -13014,7 +13053,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A272" s="49" t="s">
         <v>5</v>
       </c>
@@ -13043,7 +13082,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A273" s="49" t="s">
         <v>21</v>
       </c>
@@ -13072,7 +13111,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A274" s="49" t="s">
         <v>106</v>
       </c>
@@ -13101,7 +13140,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A275" s="49" t="s">
         <v>6</v>
       </c>
@@ -13130,7 +13169,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A276" s="49" t="s">
         <v>62</v>
       </c>
@@ -13159,7 +13198,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A277" s="49" t="s">
         <v>62</v>
       </c>
@@ -13188,7 +13227,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A278" s="49" t="s">
         <v>242</v>
       </c>
@@ -13217,7 +13256,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A279" s="49" t="s">
         <v>292</v>
       </c>
@@ -13246,7 +13285,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A280" s="49" t="s">
         <v>482</v>
       </c>
@@ -13275,7 +13314,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A281" s="49" t="s">
         <v>247</v>
       </c>
@@ -13304,7 +13343,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A282" s="49" t="s">
         <v>23</v>
       </c>
@@ -13333,7 +13372,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A283" s="49" t="s">
         <v>487</v>
       </c>
@@ -13362,7 +13401,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A284" s="49" t="s">
         <v>487</v>
       </c>
@@ -13391,7 +13430,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A285" s="49" t="s">
         <v>5</v>
       </c>
@@ -13420,7 +13459,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A286" s="49" t="s">
         <v>5</v>
       </c>
@@ -13449,7 +13488,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A287" s="49" t="s">
         <v>5</v>
       </c>
@@ -13478,7 +13517,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A288" s="49" t="s">
         <v>165</v>
       </c>
@@ -13507,7 +13546,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A289" s="49" t="s">
         <v>114</v>
       </c>
@@ -13536,7 +13575,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A290" s="49" t="s">
         <v>62</v>
       </c>
@@ -13565,7 +13604,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A291" s="49" t="s">
         <v>21</v>
       </c>
@@ -13594,7 +13633,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A292" s="49" t="s">
         <v>247</v>
       </c>
@@ -13623,7 +13662,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A293" s="49" t="s">
         <v>144</v>
       </c>
@@ -13652,7 +13691,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A294" s="49" t="s">
         <v>5</v>
       </c>
@@ -13681,7 +13720,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A295" s="49" t="s">
         <v>21</v>
       </c>
@@ -13710,7 +13749,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A296" s="49" t="s">
         <v>21</v>
       </c>
@@ -13739,7 +13778,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A297" s="49" t="s">
         <v>144</v>
       </c>
@@ -13768,7 +13807,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A298" s="49" t="s">
         <v>144</v>
       </c>
@@ -13797,7 +13836,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A299" s="49" t="s">
         <v>23</v>
       </c>
@@ -13826,7 +13865,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A300" s="49" t="s">
         <v>23</v>
       </c>
@@ -13855,7 +13894,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A301" s="49" t="s">
         <v>23</v>
       </c>
@@ -13884,7 +13923,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A302" s="49" t="s">
         <v>79</v>
       </c>
@@ -13913,7 +13952,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="303" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A303" s="49" t="s">
         <v>5</v>
       </c>
@@ -13942,7 +13981,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="304" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A304" s="49" t="s">
         <v>5</v>
       </c>
@@ -13971,7 +14010,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="305" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A305" s="49" t="s">
         <v>22</v>
       </c>
@@ -14000,7 +14039,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="306" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A306" s="49" t="s">
         <v>482</v>
       </c>
@@ -14029,7 +14068,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="307" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A307" s="49" t="s">
         <v>106</v>
       </c>
@@ -14058,7 +14097,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="308" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A308" s="49" t="s">
         <v>6</v>
       </c>
@@ -14087,7 +14126,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="309" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A309" s="49" t="s">
         <v>6</v>
       </c>
@@ -14116,7 +14155,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="310" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A310" s="49" t="s">
         <v>5</v>
       </c>
@@ -14145,7 +14184,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="311" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A311" s="49" t="s">
         <v>247</v>
       </c>
@@ -14174,7 +14213,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="312" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A312" s="49" t="s">
         <v>5</v>
       </c>
@@ -14203,7 +14242,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="313" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A313" s="49" t="s">
         <v>5</v>
       </c>
@@ -14232,7 +14271,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="314" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A314" s="49" t="s">
         <v>5</v>
       </c>
@@ -14261,7 +14300,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="315" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A315" s="49" t="s">
         <v>5</v>
       </c>
@@ -14290,7 +14329,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="316" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A316" s="49" t="s">
         <v>5</v>
       </c>
@@ -14319,7 +14358,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="317" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A317" s="49" t="s">
         <v>5</v>
       </c>
@@ -14348,7 +14387,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="318" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A318" s="49" t="s">
         <v>5</v>
       </c>
@@ -14377,7 +14416,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="319" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A319" s="49" t="s">
         <v>5</v>
       </c>
@@ -14406,7 +14445,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="320" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A320" s="49" t="s">
         <v>5</v>
       </c>
@@ -14435,7 +14474,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="321" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A321" s="49" t="s">
         <v>5</v>
       </c>
@@ -14464,7 +14503,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="322" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A322" s="49" t="s">
         <v>5</v>
       </c>
@@ -14493,7 +14532,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="323" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A323" s="49" t="s">
         <v>5</v>
       </c>
@@ -14522,7 +14561,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="324" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A324" s="49" t="s">
         <v>62</v>
       </c>
@@ -14551,7 +14590,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="325" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A325" s="49" t="s">
         <v>62</v>
       </c>
@@ -14580,7 +14619,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="326" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A326" s="49" t="s">
         <v>84</v>
       </c>
@@ -14609,7 +14648,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="327" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A327" s="49" t="s">
         <v>84</v>
       </c>
@@ -14638,7 +14677,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="328" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A328" s="49" t="s">
         <v>62</v>
       </c>
@@ -14667,7 +14706,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="329" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A329" s="49" t="s">
         <v>62</v>
       </c>
@@ -14696,7 +14735,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="330" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A330" s="49" t="s">
         <v>62</v>
       </c>
@@ -14725,7 +14764,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="331" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A331" s="49" t="s">
         <v>62</v>
       </c>
@@ -14754,7 +14793,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="332" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A332" s="49" t="s">
         <v>62</v>
       </c>
@@ -14783,7 +14822,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="333" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A333" s="49" t="s">
         <v>165</v>
       </c>
@@ -14812,7 +14851,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="334" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A334" s="49" t="s">
         <v>62</v>
       </c>
@@ -14841,7 +14880,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="335" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A335" s="49" t="s">
         <v>5</v>
       </c>
@@ -14870,7 +14909,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="336" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A336" s="49" t="s">
         <v>5</v>
       </c>
@@ -14899,7 +14938,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="337" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A337" s="49" t="s">
         <v>106</v>
       </c>
@@ -14928,7 +14967,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="338" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A338" s="49" t="s">
         <v>106</v>
       </c>
@@ -14957,7 +14996,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="339" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A339" s="49" t="s">
         <v>106</v>
       </c>
@@ -14986,7 +15025,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="340" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A340" s="49" t="s">
         <v>106</v>
       </c>
@@ -15015,7 +15054,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="341" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A341" s="49" t="s">
         <v>22</v>
       </c>
@@ -15044,7 +15083,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="342" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A342" s="49" t="s">
         <v>79</v>
       </c>
@@ -15073,7 +15112,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="343" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A343" s="49" t="s">
         <v>62</v>
       </c>
@@ -15102,7 +15141,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="344" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A344" s="49" t="s">
         <v>62</v>
       </c>
@@ -15131,7 +15170,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="345" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A345" s="49" t="s">
         <v>62</v>
       </c>
@@ -15160,7 +15199,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="346" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A346" s="49" t="s">
         <v>62</v>
       </c>
@@ -15189,7 +15228,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="347" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A347" s="49" t="s">
         <v>62</v>
       </c>
@@ -15218,7 +15257,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="348" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A348" s="49" t="s">
         <v>142</v>
       </c>
@@ -15247,7 +15286,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="349" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A349" s="49" t="s">
         <v>23</v>
       </c>
@@ -15276,7 +15315,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="350" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A350" s="49" t="s">
         <v>144</v>
       </c>
@@ -15305,7 +15344,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="351" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A351" s="49" t="s">
         <v>21</v>
       </c>
@@ -15334,7 +15373,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="352" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A352" s="49" t="s">
         <v>23</v>
       </c>
@@ -15363,7 +15402,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="353" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A353" s="49" t="s">
         <v>5</v>
       </c>
@@ -15392,7 +15431,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="354" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A354" s="49" t="s">
         <v>5</v>
       </c>
@@ -15421,7 +15460,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="355" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A355" s="49" t="s">
         <v>5</v>
       </c>
@@ -15450,7 +15489,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="356" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A356" s="49" t="s">
         <v>5</v>
       </c>
@@ -15479,7 +15518,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="357" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A357" s="49" t="s">
         <v>21</v>
       </c>
@@ -15508,7 +15547,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="358" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A358" s="49" t="s">
         <v>165</v>
       </c>
@@ -15537,7 +15576,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="359" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A359" s="49" t="s">
         <v>6</v>
       </c>
@@ -15566,7 +15605,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="360" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A360" s="49" t="s">
         <v>84</v>
       </c>
@@ -15595,7 +15634,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="361" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A361" s="49" t="s">
         <v>86</v>
       </c>
@@ -15624,7 +15663,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="362" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A362" s="49" t="s">
         <v>62</v>
       </c>
@@ -15653,7 +15692,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="363" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A363" s="49" t="s">
         <v>144</v>
       </c>
@@ -15682,7 +15721,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="364" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A364" s="49" t="s">
         <v>5</v>
       </c>
@@ -15711,7 +15750,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="365" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A365" s="49" t="s">
         <v>5</v>
       </c>
@@ -15740,7 +15779,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="366" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A366" s="49" t="s">
         <v>289</v>
       </c>
@@ -15769,7 +15808,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="367" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A367" s="49" t="s">
         <v>383</v>
       </c>
@@ -15798,7 +15837,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="368" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A368" s="49" t="s">
         <v>23</v>
       </c>
@@ -15827,7 +15866,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="369" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A369" s="49" t="s">
         <v>62</v>
       </c>
@@ -15856,7 +15895,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="370" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A370" s="49" t="s">
         <v>62</v>
       </c>
@@ -15885,7 +15924,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="371" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A371" s="49" t="s">
         <v>106</v>
       </c>
@@ -15914,7 +15953,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="372" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A372" s="49" t="s">
         <v>114</v>
       </c>
@@ -15943,7 +15982,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="373" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A373" s="49" t="s">
         <v>247</v>
       </c>
@@ -15972,7 +16011,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="374" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A374" s="49" t="s">
         <v>247</v>
       </c>
@@ -16001,7 +16040,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="375" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A375" s="49" t="s">
         <v>247</v>
       </c>
@@ -16030,7 +16069,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="376" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A376" s="49" t="s">
         <v>23</v>
       </c>
@@ -16059,7 +16098,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="377" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A377" s="49" t="s">
         <v>23</v>
       </c>
@@ -16088,7 +16127,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="378" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A378" s="49" t="s">
         <v>62</v>
       </c>
@@ -16117,7 +16156,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="379" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A379" s="49" t="s">
         <v>62</v>
       </c>
@@ -16146,7 +16185,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="380" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A380" s="49" t="s">
         <v>62</v>
       </c>
@@ -16175,7 +16214,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="381" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A381" s="49" t="s">
         <v>144</v>
       </c>
@@ -16204,7 +16243,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="382" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A382" s="49" t="s">
         <v>5</v>
       </c>
@@ -16233,7 +16272,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="383" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A383" s="49" t="s">
         <v>86</v>
       </c>
@@ -16262,7 +16301,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="384" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A384" s="49" t="s">
         <v>62</v>
       </c>
@@ -16291,7 +16330,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="385" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A385" s="49" t="s">
         <v>106</v>
       </c>
@@ -16320,7 +16359,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="386" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A386" s="49" t="s">
         <v>106</v>
       </c>
@@ -16349,7 +16388,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="387" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A387" s="49" t="s">
         <v>5</v>
       </c>
@@ -16378,7 +16417,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="388" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A388" s="49" t="s">
         <v>86</v>
       </c>
@@ -16407,7 +16446,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="389" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A389" s="49" t="s">
         <v>22</v>
       </c>
@@ -16436,7 +16475,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="390" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A390" s="49" t="s">
         <v>22</v>
       </c>
@@ -16465,7 +16504,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="391" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A391" s="49" t="s">
         <v>84</v>
       </c>
@@ -16494,7 +16533,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="392" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A392" s="49" t="s">
         <v>114</v>
       </c>
@@ -16523,7 +16562,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="393" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A393" s="49" t="s">
         <v>5</v>
       </c>
@@ -16552,7 +16591,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="394" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A394" s="49" t="s">
         <v>5</v>
       </c>
@@ -16581,7 +16620,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="395" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A395" s="49" t="s">
         <v>247</v>
       </c>
@@ -16610,7 +16649,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="396" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A396" s="49" t="s">
         <v>23</v>
       </c>
@@ -16639,7 +16678,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="397" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A397" s="49" t="s">
         <v>79</v>
       </c>
@@ -16668,7 +16707,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="398" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A398" s="49" t="s">
         <v>487</v>
       </c>
@@ -16697,7 +16736,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="399" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A399" s="49" t="s">
         <v>5</v>
       </c>
@@ -16726,7 +16765,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="400" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A400" s="49" t="s">
         <v>5</v>
       </c>
@@ -16755,7 +16794,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="401" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A401" s="49" t="s">
         <v>344</v>
       </c>
@@ -16784,7 +16823,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="402" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A402" s="49" t="s">
         <v>642</v>
       </c>
@@ -16813,7 +16852,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="403" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A403" s="49" t="s">
         <v>644</v>
       </c>
@@ -16842,7 +16881,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="404" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A404" s="49" t="s">
         <v>646</v>
       </c>
@@ -16871,7 +16910,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="405" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A405" s="49" t="s">
         <v>648</v>
       </c>
@@ -16900,7 +16939,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="406" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A406" s="49" t="s">
         <v>650</v>
       </c>
@@ -16929,7 +16968,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="407" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A407" s="49" t="s">
         <v>652</v>
       </c>
@@ -16958,7 +16997,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="408" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A408" s="49" t="s">
         <v>155</v>
       </c>
@@ -16987,7 +17026,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="409" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A409" s="49" t="s">
         <v>165</v>
       </c>
@@ -17016,7 +17055,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="410" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A410" s="49" t="s">
         <v>22</v>
       </c>
@@ -17045,7 +17084,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="411" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A411" s="49" t="s">
         <v>62</v>
       </c>
@@ -17074,7 +17113,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="412" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A412" s="49" t="s">
         <v>5</v>
       </c>
@@ -17103,7 +17142,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="413" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A413" s="49" t="s">
         <v>289</v>
       </c>
@@ -17132,7 +17171,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="414" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A414" s="49" t="s">
         <v>289</v>
       </c>
@@ -17161,7 +17200,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="415" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A415" s="49" t="s">
         <v>5</v>
       </c>
@@ -17190,7 +17229,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="416" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A416" s="49" t="s">
         <v>5</v>
       </c>
@@ -17219,7 +17258,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="417" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A417" s="49" t="s">
         <v>84</v>
       </c>
@@ -17248,7 +17287,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="418" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A418" s="49" t="s">
         <v>86</v>
       </c>
@@ -17277,7 +17316,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="419" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A419" s="49" t="s">
         <v>114</v>
       </c>
@@ -17306,7 +17345,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="420" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A420" s="49" t="s">
         <v>5</v>
       </c>
@@ -17335,7 +17374,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="421" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A421" s="49" t="s">
         <v>139</v>
       </c>
@@ -17364,7 +17403,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="422" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A422" s="49" t="s">
         <v>23</v>
       </c>
@@ -17393,7 +17432,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="423" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A423" s="49" t="s">
         <v>5</v>
       </c>
@@ -17422,7 +17461,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="424" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A424" s="49" t="s">
         <v>5</v>
       </c>
@@ -17451,7 +17490,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="425" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A425" s="49" t="s">
         <v>5</v>
       </c>
@@ -17480,7 +17519,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="426" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A426" s="49" t="s">
         <v>5</v>
       </c>
@@ -17509,7 +17548,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="427" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A427" s="49" t="s">
         <v>22</v>
       </c>
@@ -17538,7 +17577,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="428" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A428" s="49" t="s">
         <v>5</v>
       </c>
@@ -17567,7 +17606,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="429" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A429" s="49" t="s">
         <v>62</v>
       </c>
@@ -17596,7 +17635,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="430" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A430" s="49" t="s">
         <v>5</v>
       </c>
@@ -17625,7 +17664,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="431" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A431" s="49" t="s">
         <v>289</v>
       </c>
@@ -17654,7 +17693,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="432" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A432" s="49" t="s">
         <v>5</v>
       </c>
@@ -17683,7 +17722,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="433" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A433" s="49" t="s">
         <v>5</v>
       </c>
@@ -17712,7 +17751,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="434" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A434" s="49" t="s">
         <v>86</v>
       </c>
@@ -17741,7 +17780,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="435" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A435" s="49" t="s">
         <v>62</v>
       </c>
@@ -17770,7 +17809,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="436" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A436" s="49" t="s">
         <v>22</v>
       </c>
@@ -17799,7 +17838,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="437" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A437" s="49" t="s">
         <v>22</v>
       </c>
@@ -17828,7 +17867,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="438" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A438" s="49" t="s">
         <v>84</v>
       </c>
@@ -17857,7 +17896,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="439" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A439" s="49" t="s">
         <v>62</v>
       </c>
@@ -17886,7 +17925,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="440" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A440" s="49" t="s">
         <v>5</v>
       </c>
@@ -17915,7 +17954,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="441" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A441" s="49" t="s">
         <v>86</v>
       </c>
@@ -17944,7 +17983,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="442" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A442" s="49" t="s">
         <v>62</v>
       </c>
@@ -17973,7 +18012,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="443" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A443" s="49" t="s">
         <v>5</v>
       </c>
@@ -18002,7 +18041,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="444" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A444" s="49" t="s">
         <v>5</v>
       </c>
@@ -18031,7 +18070,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="445" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A445" s="49" t="s">
         <v>292</v>
       </c>
@@ -18060,7 +18099,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="446" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A446" s="49" t="s">
         <v>5</v>
       </c>
@@ -18089,7 +18128,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="447" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A447" s="49" t="s">
         <v>5</v>
       </c>
@@ -18118,7 +18157,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="448" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A448" s="49" t="s">
         <v>5</v>
       </c>
@@ -18147,7 +18186,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="449" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A449" s="49" t="s">
         <v>5</v>
       </c>
@@ -18176,7 +18215,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="450" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A450" s="49" t="s">
         <v>21</v>
       </c>
@@ -18205,7 +18244,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="451" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A451" s="49" t="s">
         <v>21</v>
       </c>
@@ -18234,7 +18273,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="452" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A452" s="49" t="s">
         <v>21</v>
       </c>
@@ -18263,7 +18302,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="453" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A453" s="49" t="s">
         <v>21</v>
       </c>
@@ -18292,7 +18331,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="454" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A454" s="49" t="s">
         <v>22</v>
       </c>
@@ -18321,7 +18360,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="455" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A455" s="49" t="s">
         <v>22</v>
       </c>
@@ -18350,7 +18389,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="456" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A456" s="49" t="s">
         <v>6</v>
       </c>
@@ -18379,7 +18418,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="457" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A457" s="49" t="s">
         <v>6</v>
       </c>
@@ -18408,7 +18447,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="458" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A458" s="49" t="s">
         <v>6</v>
       </c>
@@ -18437,7 +18476,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="459" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A459" s="49" t="s">
         <v>165</v>
       </c>
@@ -18466,7 +18505,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="460" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A460" s="49" t="s">
         <v>62</v>
       </c>
@@ -18495,7 +18534,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="461" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A461" s="49" t="s">
         <v>23</v>
       </c>
@@ -18524,7 +18563,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="462" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A462" s="49" t="s">
         <v>23</v>
       </c>
@@ -18553,7 +18592,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="463" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A463" s="49" t="s">
         <v>23</v>
       </c>
@@ -18582,7 +18621,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="464" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A464" s="49" t="s">
         <v>23</v>
       </c>
@@ -18611,7 +18650,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="465" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A465" s="49" t="s">
         <v>646</v>
       </c>
@@ -18640,7 +18679,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="466" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A466" s="49" t="s">
         <v>79</v>
       </c>
@@ -18669,7 +18708,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="467" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A467" s="49" t="s">
         <v>7</v>
       </c>
@@ -18698,7 +18737,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="468" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A468" s="49" t="s">
         <v>7</v>
       </c>
@@ -18727,7 +18766,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="469" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A469" s="49" t="s">
         <v>7</v>
       </c>
@@ -18756,7 +18795,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="470" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A470" s="49" t="s">
         <v>7</v>
       </c>
@@ -18785,7 +18824,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="471" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A471" s="49" t="s">
         <v>745</v>
       </c>
@@ -18814,7 +18853,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="472" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A472" s="49" t="s">
         <v>745</v>
       </c>
@@ -18843,7 +18882,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="473" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A473" s="49" t="s">
         <v>292</v>
       </c>
@@ -18872,7 +18911,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="474" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A474" s="49" t="s">
         <v>292</v>
       </c>
@@ -18901,7 +18940,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="475" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A475" s="49" t="s">
         <v>292</v>
       </c>
@@ -18930,7 +18969,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="476" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A476" s="49" t="s">
         <v>292</v>
       </c>
@@ -18959,7 +18998,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="477" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A477" s="49" t="s">
         <v>292</v>
       </c>
@@ -18988,7 +19027,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="478" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A478" s="49" t="s">
         <v>292</v>
       </c>
@@ -19017,7 +19056,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="479" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A479" s="49" t="s">
         <v>754</v>
       </c>
@@ -19046,7 +19085,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="480" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A480" s="49" t="s">
         <v>5</v>
       </c>
@@ -19075,7 +19114,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="481" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A481" s="49" t="s">
         <v>5</v>
       </c>
@@ -19104,7 +19143,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="482" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A482" s="49" t="s">
         <v>5</v>
       </c>
@@ -19133,7 +19172,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="483" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A483" s="49" t="s">
         <v>5</v>
       </c>
@@ -19162,7 +19201,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="484" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A484" s="49" t="s">
         <v>5</v>
       </c>
@@ -19191,7 +19230,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="485" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A485" s="49" t="s">
         <v>5</v>
       </c>
@@ -19220,7 +19259,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="486" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A486" s="49" t="s">
         <v>5</v>
       </c>
@@ -19249,7 +19288,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="487" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A487" s="49" t="s">
         <v>5</v>
       </c>
@@ -19278,7 +19317,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="488" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A488" s="49" t="s">
         <v>5</v>
       </c>
@@ -19307,7 +19346,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="489" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A489" s="49" t="s">
         <v>5</v>
       </c>
@@ -19336,7 +19375,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="490" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A490" s="49" t="s">
         <v>5</v>
       </c>
@@ -19365,7 +19404,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="491" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A491" s="49" t="s">
         <v>5</v>
       </c>
@@ -19394,7 +19433,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="492" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A492" s="49" t="s">
         <v>5</v>
       </c>
@@ -19423,7 +19462,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="493" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A493" s="49" t="s">
         <v>5</v>
       </c>
@@ -19452,7 +19491,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="494" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A494" s="49" t="s">
         <v>5</v>
       </c>
@@ -19481,7 +19520,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="495" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A495" s="49" t="s">
         <v>5</v>
       </c>
@@ -19510,7 +19549,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="496" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A496" s="49" t="s">
         <v>5</v>
       </c>
@@ -19539,7 +19578,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="497" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A497" s="49" t="s">
         <v>5</v>
       </c>
@@ -19568,7 +19607,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="498" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A498" s="49" t="s">
         <v>5</v>
       </c>
@@ -19597,7 +19636,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="499" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A499" s="49" t="s">
         <v>5</v>
       </c>
@@ -19626,7 +19665,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="500" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A500" s="49" t="s">
         <v>5</v>
       </c>
@@ -19655,7 +19694,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="501" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A501" s="49" t="s">
         <v>5</v>
       </c>
@@ -19684,7 +19723,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="502" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A502" s="49" t="s">
         <v>5</v>
       </c>
@@ -19713,7 +19752,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="503" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A503" s="49" t="s">
         <v>5</v>
       </c>
@@ -19742,7 +19781,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="504" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A504" s="49" t="s">
         <v>5</v>
       </c>
@@ -19771,7 +19810,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="505" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A505" s="49" t="s">
         <v>5</v>
       </c>
@@ -19800,7 +19839,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="506" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A506" s="49" t="s">
         <v>5</v>
       </c>
@@ -19829,7 +19868,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="507" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A507" s="49" t="s">
         <v>5</v>
       </c>
@@ -19858,7 +19897,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="508" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A508" s="49" t="s">
         <v>5</v>
       </c>
@@ -19887,7 +19926,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="509" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A509" s="49" t="s">
         <v>5</v>
       </c>
@@ -19916,7 +19955,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="510" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A510" s="49" t="s">
         <v>5</v>
       </c>
@@ -19945,7 +19984,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="511" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A511" s="49" t="s">
         <v>5</v>
       </c>
@@ -19974,7 +20013,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="512" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A512" s="49" t="s">
         <v>5</v>
       </c>
@@ -20003,7 +20042,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="513" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A513" s="49" t="s">
         <v>5</v>
       </c>
@@ -20032,7 +20071,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="514" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A514" s="49" t="s">
         <v>5</v>
       </c>
@@ -20061,7 +20100,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="515" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A515" s="49" t="s">
         <v>5</v>
       </c>
@@ -20090,7 +20129,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="516" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A516" s="49" t="s">
         <v>344</v>
       </c>
@@ -20119,7 +20158,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="517" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A517" s="49" t="s">
         <v>21</v>
       </c>
@@ -20148,7 +20187,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="518" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A518" s="49" t="s">
         <v>21</v>
       </c>
@@ -20177,7 +20216,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="519" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A519" s="49" t="s">
         <v>21</v>
       </c>
@@ -20206,7 +20245,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="520" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A520" s="49" t="s">
         <v>21</v>
       </c>
@@ -20235,7 +20274,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="521" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A521" s="49" t="s">
         <v>21</v>
       </c>
@@ -20264,7 +20303,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="522" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A522" s="49" t="s">
         <v>21</v>
       </c>
@@ -20293,7 +20332,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="523" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A523" s="49" t="s">
         <v>21</v>
       </c>
@@ -20322,7 +20361,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="524" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A524" s="49" t="s">
         <v>21</v>
       </c>
@@ -20351,7 +20390,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="525" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A525" s="49" t="s">
         <v>21</v>
       </c>
@@ -20380,7 +20419,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="526" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A526" s="49" t="s">
         <v>21</v>
       </c>
@@ -20409,7 +20448,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="527" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A527" s="49" t="s">
         <v>21</v>
       </c>
@@ -20438,7 +20477,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="528" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A528" s="49" t="s">
         <v>21</v>
       </c>
@@ -20467,7 +20506,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="529" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A529" s="49" t="s">
         <v>106</v>
       </c>
@@ -20496,7 +20535,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="530" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A530" s="49" t="s">
         <v>106</v>
       </c>
@@ -20525,7 +20564,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="531" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A531" s="49" t="s">
         <v>106</v>
       </c>
@@ -20554,7 +20593,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="532" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A532" s="49" t="s">
         <v>106</v>
       </c>
@@ -20583,7 +20622,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="533" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A533" s="49" t="s">
         <v>106</v>
       </c>
@@ -20612,7 +20651,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="534" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A534" s="49" t="s">
         <v>106</v>
       </c>
@@ -20641,7 +20680,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="535" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A535" s="49" t="s">
         <v>106</v>
       </c>
@@ -20670,7 +20709,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="536" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A536" s="49" t="s">
         <v>106</v>
       </c>
@@ -20699,7 +20738,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="537" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A537" s="49" t="s">
         <v>106</v>
       </c>
@@ -20728,7 +20767,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="538" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A538" s="49" t="s">
         <v>106</v>
       </c>
@@ -20757,7 +20796,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="539" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A539" s="49" t="s">
         <v>165</v>
       </c>
@@ -20786,7 +20825,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="540" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A540" s="49" t="s">
         <v>165</v>
       </c>
@@ -20815,7 +20854,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="541" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A541" s="49" t="s">
         <v>165</v>
       </c>
@@ -20844,7 +20883,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="542" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A542" s="49" t="s">
         <v>165</v>
       </c>
@@ -20873,7 +20912,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="543" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A543" s="49" t="s">
         <v>165</v>
       </c>
@@ -20902,7 +20941,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="544" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A544" s="49" t="s">
         <v>165</v>
       </c>
@@ -20931,7 +20970,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="545" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A545" s="49" t="s">
         <v>22</v>
       </c>
@@ -20960,7 +20999,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="546" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A546" s="49" t="s">
         <v>22</v>
       </c>
@@ -20989,7 +21028,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="547" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A547" s="49" t="s">
         <v>22</v>
       </c>
@@ -21018,7 +21057,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="548" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A548" s="49" t="s">
         <v>22</v>
       </c>
@@ -21047,7 +21086,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="549" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A549" s="49" t="s">
         <v>22</v>
       </c>
@@ -21076,7 +21115,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="550" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A550" s="49" t="s">
         <v>22</v>
       </c>
@@ -21105,7 +21144,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="551" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A551" s="49" t="s">
         <v>22</v>
       </c>
@@ -21134,7 +21173,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="552" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A552" s="49" t="s">
         <v>22</v>
       </c>
@@ -21163,7 +21202,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="553" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A553" s="49" t="s">
         <v>22</v>
       </c>
@@ -21192,7 +21231,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="554" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A554" s="49" t="s">
         <v>22</v>
       </c>
@@ -21221,7 +21260,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="555" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A555" s="49" t="s">
         <v>22</v>
       </c>
@@ -21250,7 +21289,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="556" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A556" s="49" t="s">
         <v>22</v>
       </c>
@@ -21279,7 +21318,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="557" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A557" s="49" t="s">
         <v>22</v>
       </c>
@@ -21308,7 +21347,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="558" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A558" s="49" t="s">
         <v>6</v>
       </c>
@@ -21337,7 +21376,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="559" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A559" s="49" t="s">
         <v>6</v>
       </c>
@@ -21366,7 +21405,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="560" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A560" s="49" t="s">
         <v>6</v>
       </c>
@@ -21395,7 +21434,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="561" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A561" s="49" t="s">
         <v>6</v>
       </c>
@@ -21424,7 +21463,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="562" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A562" s="49" t="s">
         <v>6</v>
       </c>
@@ -21453,7 +21492,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="563" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A563" s="49" t="s">
         <v>6</v>
       </c>
@@ -21482,7 +21521,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="564" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A564" s="49" t="s">
         <v>6</v>
       </c>
@@ -21511,7 +21550,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="565" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A565" s="49" t="s">
         <v>6</v>
       </c>
@@ -21540,7 +21579,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="566" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A566" s="49" t="s">
         <v>6</v>
       </c>
@@ -21569,7 +21608,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="567" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A567" s="49" t="s">
         <v>6</v>
       </c>
@@ -21598,7 +21637,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="568" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A568" s="49" t="s">
         <v>6</v>
       </c>
@@ -21627,7 +21666,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="569" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A569" s="49" t="s">
         <v>6</v>
       </c>
@@ -21656,7 +21695,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="570" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A570" s="49" t="s">
         <v>6</v>
       </c>
@@ -21685,7 +21724,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="571" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A571" s="49" t="s">
         <v>114</v>
       </c>
@@ -21714,7 +21753,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="572" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A572" s="49" t="s">
         <v>114</v>
       </c>
@@ -21743,7 +21782,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="573" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A573" s="49" t="s">
         <v>114</v>
       </c>
@@ -21772,7 +21811,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="574" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A574" s="49" t="s">
         <v>114</v>
       </c>
@@ -21801,7 +21840,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="575" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A575" s="49" t="s">
         <v>142</v>
       </c>
@@ -21830,7 +21869,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="576" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A576" s="49" t="s">
         <v>142</v>
       </c>
@@ -21859,7 +21898,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="577" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A577" s="49" t="s">
         <v>142</v>
       </c>
@@ -21888,7 +21927,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="578" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A578" s="49" t="s">
         <v>86</v>
       </c>
@@ -21917,7 +21956,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="579" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A579" s="49" t="s">
         <v>854</v>
       </c>
@@ -21946,7 +21985,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="580" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A580" s="49" t="s">
         <v>854</v>
       </c>
@@ -21975,7 +22014,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="581" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A581" s="49" t="s">
         <v>62</v>
       </c>
@@ -22004,7 +22043,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="582" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A582" s="49" t="s">
         <v>62</v>
       </c>
@@ -22033,7 +22072,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="583" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A583" s="49" t="s">
         <v>62</v>
       </c>
@@ -22062,7 +22101,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="584" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A584" s="49" t="s">
         <v>62</v>
       </c>
@@ -22091,7 +22130,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="585" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A585" s="49" t="s">
         <v>62</v>
       </c>
@@ -22120,7 +22159,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="586" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A586" s="49" t="s">
         <v>861</v>
       </c>
@@ -22149,7 +22188,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="587" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A587" s="49" t="s">
         <v>144</v>
       </c>
@@ -22178,7 +22217,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="588" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A588" s="49" t="s">
         <v>144</v>
       </c>
@@ -22207,7 +22246,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="589" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A589" s="49" t="s">
         <v>289</v>
       </c>
@@ -22236,7 +22275,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="590" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A590" s="49" t="s">
         <v>247</v>
       </c>
@@ -22265,7 +22304,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="591" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A591" s="49" t="s">
         <v>247</v>
       </c>
@@ -22294,7 +22333,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="592" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A592" s="49" t="s">
         <v>383</v>
       </c>
@@ -22323,7 +22362,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="593" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A593" s="49" t="s">
         <v>23</v>
       </c>
@@ -22352,7 +22391,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="594" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A594" s="49" t="s">
         <v>292</v>
       </c>
@@ -22381,7 +22420,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="595" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A595" s="49" t="s">
         <v>754</v>
       </c>
@@ -22410,7 +22449,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="596" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A596" s="49" t="s">
         <v>5</v>
       </c>
@@ -22439,7 +22478,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="597" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A597" s="49" t="s">
         <v>5</v>
       </c>
@@ -22468,7 +22507,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="598" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A598" s="49" t="s">
         <v>5</v>
       </c>
@@ -22497,7 +22536,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="599" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A599" s="49" t="s">
         <v>5</v>
       </c>
@@ -22526,7 +22565,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="600" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A600" s="49" t="s">
         <v>21</v>
       </c>
@@ -22555,7 +22594,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="601" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A601" s="49" t="s">
         <v>21</v>
       </c>
@@ -22584,7 +22623,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="602" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A602" s="49" t="s">
         <v>21</v>
       </c>
@@ -22613,7 +22652,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="603" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A603" s="49" t="s">
         <v>22</v>
       </c>
@@ -22642,7 +22681,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="604" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A604" s="49" t="s">
         <v>6</v>
       </c>
@@ -22671,7 +22710,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="605" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A605" s="49" t="s">
         <v>6</v>
       </c>
@@ -22700,7 +22739,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="606" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A606" s="49" t="s">
         <v>854</v>
       </c>
@@ -22729,7 +22768,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="607" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A607" s="49" t="s">
         <v>62</v>
       </c>
@@ -22758,7 +22797,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="608" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A608" s="49" t="s">
         <v>247</v>
       </c>
@@ -22787,7 +22826,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="609" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A609" s="49" t="s">
         <v>5</v>
       </c>
@@ -22816,7 +22855,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="610" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A610" s="49" t="s">
         <v>21</v>
       </c>
@@ -22845,7 +22884,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="611" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A611" s="49" t="s">
         <v>84</v>
       </c>
@@ -22874,7 +22913,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="612" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A612" s="49" t="s">
         <v>84</v>
       </c>
@@ -22903,7 +22942,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="613" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A613" s="49" t="s">
         <v>84</v>
       </c>
@@ -22932,7 +22971,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="614" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A614" s="49" t="s">
         <v>142</v>
       </c>
@@ -22961,7 +23000,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="615" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A615" s="49" t="s">
         <v>5</v>
       </c>
@@ -22990,7 +23029,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="616" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A616" s="49" t="s">
         <v>86</v>
       </c>
@@ -23019,7 +23058,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="617" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A617" s="49" t="s">
         <v>62</v>
       </c>
@@ -23048,7 +23087,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="618" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A618" s="49" t="s">
         <v>62</v>
       </c>
@@ -23077,7 +23116,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="619" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A619" s="49" t="s">
         <v>21</v>
       </c>
@@ -23106,7 +23145,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="620" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A620" s="49" t="s">
         <v>84</v>
       </c>
@@ -23135,7 +23174,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="621" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A621" s="49" t="s">
         <v>142</v>
       </c>
@@ -23164,7 +23203,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="622" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A622" s="49" t="s">
         <v>5</v>
       </c>
@@ -23193,7 +23232,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="623" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A623" s="49" t="s">
         <v>84</v>
       </c>
@@ -23222,7 +23261,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="624" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A624" s="49" t="s">
         <v>86</v>
       </c>
@@ -23251,7 +23290,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="625" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A625" s="49" t="s">
         <v>21</v>
       </c>
@@ -23280,7 +23319,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="626" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A626" s="49" t="s">
         <v>21</v>
       </c>
@@ -23309,7 +23348,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="627" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A627" s="49" t="s">
         <v>21</v>
       </c>
@@ -23338,7 +23377,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="628" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A628" s="49" t="s">
         <v>22</v>
       </c>
@@ -23367,7 +23406,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="629" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A629" s="49" t="s">
         <v>22</v>
       </c>
@@ -23396,7 +23435,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="630" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A630" s="49" t="s">
         <v>5</v>
       </c>
@@ -23425,7 +23464,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="631" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A631" s="49" t="s">
         <v>5</v>
       </c>
@@ -23454,7 +23493,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="632" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A632" s="49" t="s">
         <v>5</v>
       </c>
@@ -23483,7 +23522,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="633" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A633" s="49" t="s">
         <v>79</v>
       </c>
@@ -23512,7 +23551,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="634" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A634" s="49" t="s">
         <v>79</v>
       </c>
@@ -23541,7 +23580,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="635" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A635" s="49" t="s">
         <v>5</v>
       </c>
@@ -23570,7 +23609,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="636" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A636" s="49" t="s">
         <v>5</v>
       </c>
@@ -23599,7 +23638,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="637" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A637" s="49" t="s">
         <v>5</v>
       </c>
@@ -23628,7 +23667,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="638" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A638" s="49" t="s">
         <v>5</v>
       </c>
@@ -23657,7 +23696,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="639" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A639" s="49" t="s">
         <v>21</v>
       </c>
@@ -23686,7 +23725,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="640" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A640" s="49" t="s">
         <v>6</v>
       </c>
@@ -23715,7 +23754,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="641" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A641" s="49" t="s">
         <v>62</v>
       </c>
@@ -23744,7 +23783,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="642" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A642" s="49" t="s">
         <v>62</v>
       </c>
@@ -23773,7 +23812,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="643" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A643" s="49" t="s">
         <v>5</v>
       </c>
@@ -23802,7 +23841,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="644" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A644" s="49" t="s">
         <v>22</v>
       </c>
@@ -23831,7 +23870,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="645" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A645" s="49" t="s">
         <v>62</v>
       </c>
@@ -23860,7 +23899,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="646" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A646" s="49" t="s">
         <v>22</v>
       </c>
@@ -23889,7 +23928,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="647" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A647" s="49" t="s">
         <v>23</v>
       </c>
@@ -23918,7 +23957,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="648" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A648" s="49" t="s">
         <v>5</v>
       </c>
@@ -23947,7 +23986,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="649" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A649" s="49" t="s">
         <v>21</v>
       </c>
@@ -23976,7 +24015,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="650" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A650" s="49" t="s">
         <v>79</v>
       </c>
@@ -24005,7 +24044,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="651" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A651" s="49" t="s">
         <v>292</v>
       </c>
@@ -24034,7 +24073,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="652" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A652" s="49" t="s">
         <v>5</v>
       </c>
@@ -24063,7 +24102,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="653" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A653" s="49" t="s">
         <v>6</v>
       </c>
@@ -24092,7 +24131,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="654" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A654" s="49" t="s">
         <v>5</v>
       </c>
@@ -24121,7 +24160,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="655" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A655" s="49" t="s">
         <v>21</v>
       </c>
@@ -24150,7 +24189,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="656" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A656" s="49" t="s">
         <v>21</v>
       </c>
@@ -24179,7 +24218,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="657" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A657" s="49" t="s">
         <v>84</v>
       </c>
@@ -24208,7 +24247,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="658" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A658" s="49" t="s">
         <v>84</v>
       </c>
@@ -24237,7 +24276,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="659" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A659" s="49" t="s">
         <v>292</v>
       </c>
@@ -24266,7 +24305,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="660" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A660" s="49" t="s">
         <v>646</v>
       </c>
@@ -24295,7 +24334,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="661" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A661" s="49" t="s">
         <v>23</v>
       </c>
@@ -24324,7 +24363,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="662" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A662" s="49" t="s">
         <v>106</v>
       </c>
@@ -24353,7 +24392,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="663" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A663" s="49" t="s">
         <v>22</v>
       </c>
@@ -24382,7 +24421,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="664" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A664" s="49" t="s">
         <v>114</v>
       </c>
@@ -24411,7 +24450,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="665" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A665" s="49" t="s">
         <v>453</v>
       </c>
@@ -24440,7 +24479,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="666" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A666" s="49" t="s">
         <v>22</v>
       </c>
@@ -24469,7 +24508,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="667" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A667" s="49" t="s">
         <v>247</v>
       </c>
@@ -24498,7 +24537,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="668" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A668" s="49" t="s">
         <v>292</v>
       </c>
@@ -24527,7 +24566,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="669" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A669" s="49" t="s">
         <v>5</v>
       </c>
@@ -24556,7 +24595,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="670" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A670" s="49" t="s">
         <v>5</v>
       </c>
@@ -24585,7 +24624,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="671" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A671" s="49" t="s">
         <v>5</v>
       </c>
@@ -24614,7 +24653,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="672" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A672" s="49" t="s">
         <v>21</v>
       </c>
@@ -24643,7 +24682,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="673" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A673" s="49" t="s">
         <v>21</v>
       </c>
@@ -24672,7 +24711,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="674" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A674" s="49" t="s">
         <v>6</v>
       </c>
@@ -24701,7 +24740,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="675" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A675" s="49" t="s">
         <v>79</v>
       </c>
@@ -24730,7 +24769,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="676" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A676" s="49" t="s">
         <v>292</v>
       </c>
@@ -24759,7 +24798,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="677" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A677" s="49" t="s">
         <v>292</v>
       </c>
@@ -24788,7 +24827,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="678" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A678" s="49" t="s">
         <v>106</v>
       </c>
@@ -24817,7 +24856,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="679" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A679" s="49" t="s">
         <v>106</v>
       </c>
@@ -24846,7 +24885,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="680" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A680" s="49" t="s">
         <v>106</v>
       </c>
@@ -24875,7 +24914,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="681" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A681" s="49" t="s">
         <v>106</v>
       </c>
@@ -24904,7 +24943,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="682" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A682" s="49" t="s">
         <v>5</v>
       </c>
@@ -24933,7 +24972,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="683" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A683" s="49" t="s">
         <v>5</v>
       </c>
@@ -24962,7 +25001,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="684" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A684" s="49" t="s">
         <v>84</v>
       </c>
@@ -24991,7 +25030,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="685" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A685" s="49" t="s">
         <v>79</v>
       </c>
@@ -25020,7 +25059,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="686" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A686" s="49" t="s">
         <v>5</v>
       </c>
@@ -25049,7 +25088,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="687" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A687" s="49" t="s">
         <v>22</v>
       </c>
@@ -25078,7 +25117,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="688" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A688" s="49" t="s">
         <v>5</v>
       </c>
@@ -25107,7 +25146,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="689" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A689" s="49" t="s">
         <v>5</v>
       </c>
@@ -25136,7 +25175,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="690" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A690" s="49" t="s">
         <v>21</v>
       </c>
@@ -25165,7 +25204,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="691" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A691" s="49" t="s">
         <v>5</v>
       </c>
@@ -25194,7 +25233,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="692" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A692" s="49" t="s">
         <v>5</v>
       </c>
@@ -25223,7 +25262,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="693" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A693" s="49" t="s">
         <v>62</v>
       </c>
@@ -25252,7 +25291,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="694" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A694" s="49" t="s">
         <v>62</v>
       </c>
@@ -25281,7 +25320,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="695" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A695" s="49" t="s">
         <v>62</v>
       </c>
@@ -25310,7 +25349,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="696" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A696" s="49" t="s">
         <v>62</v>
       </c>
@@ -25339,7 +25378,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="697" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A697" s="49" t="s">
         <v>62</v>
       </c>
@@ -25368,7 +25407,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="698" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A698" s="49" t="s">
         <v>84</v>
       </c>
@@ -25397,7 +25436,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="699" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A699" s="49" t="s">
         <v>23</v>
       </c>
@@ -25426,7 +25465,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="700" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A700" s="49" t="s">
         <v>5</v>
       </c>
@@ -25455,7 +25494,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="701" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A701" s="49" t="s">
         <v>482</v>
       </c>
@@ -25484,7 +25523,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="702" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A702" s="49" t="s">
         <v>5</v>
       </c>
@@ -25513,7 +25552,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="703" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A703" s="49" t="s">
         <v>5</v>
       </c>
@@ -25542,7 +25581,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="704" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A704" s="49" t="s">
         <v>5</v>
       </c>
@@ -25571,7 +25610,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="705" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A705" s="49" t="s">
         <v>5</v>
       </c>
@@ -25600,7 +25639,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="706" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A706" s="49" t="s">
         <v>5</v>
       </c>
@@ -25629,7 +25668,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="707" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A707" s="49" t="s">
         <v>861</v>
       </c>
@@ -25658,7 +25697,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="708" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A708" s="49" t="s">
         <v>861</v>
       </c>
@@ -25687,7 +25726,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="709" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A709" s="49" t="s">
         <v>861</v>
       </c>
@@ -25716,7 +25755,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="710" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A710" s="49" t="s">
         <v>292</v>
       </c>
@@ -25745,7 +25784,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="711" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A711" s="49" t="s">
         <v>292</v>
       </c>
@@ -25774,7 +25813,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="712" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A712" s="49" t="s">
         <v>5</v>
       </c>
@@ -25803,7 +25842,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="713" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A713" s="49" t="s">
         <v>5</v>
       </c>
@@ -25832,7 +25871,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="714" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A714" s="49" t="s">
         <v>62</v>
       </c>
@@ -25861,7 +25900,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="715" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A715" s="49" t="s">
         <v>5</v>
       </c>
@@ -25890,7 +25929,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="716" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A716" s="49" t="s">
         <v>861</v>
       </c>
@@ -25919,7 +25958,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="717" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A717" s="49" t="s">
         <v>22</v>
       </c>
@@ -25948,7 +25987,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="718" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A718" s="49" t="s">
         <v>86</v>
       </c>
@@ -25977,7 +26016,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="719" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A719" s="49" t="s">
         <v>23</v>
       </c>
@@ -26006,7 +26045,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="720" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A720" s="49" t="s">
         <v>5</v>
       </c>
@@ -26035,7 +26074,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="721" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A721" s="49" t="s">
         <v>165</v>
       </c>
@@ -26064,7 +26103,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="722" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A722" s="49" t="s">
         <v>6</v>
       </c>
@@ -26093,7 +26132,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="723" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A723" s="49" t="s">
         <v>5</v>
       </c>
@@ -26122,7 +26161,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="724" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A724" s="49" t="s">
         <v>21</v>
       </c>
@@ -26151,7 +26190,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="725" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A725" s="49" t="s">
         <v>21</v>
       </c>
@@ -26180,7 +26219,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="726" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A726" s="49" t="s">
         <v>21</v>
       </c>
@@ -26209,7 +26248,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="727" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A727" s="49" t="s">
         <v>22</v>
       </c>
@@ -26238,7 +26277,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="728" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A728" s="49" t="s">
         <v>62</v>
       </c>
@@ -26267,7 +26306,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="729" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A729" s="49" t="s">
         <v>23</v>
       </c>
@@ -26296,7 +26335,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="730" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A730" s="49" t="s">
         <v>5</v>
       </c>
@@ -26325,7 +26364,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="731" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A731" s="49" t="s">
         <v>6</v>
       </c>
@@ -26354,7 +26393,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="732" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A732" s="49" t="s">
         <v>62</v>
       </c>
@@ -26383,7 +26422,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="733" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A733" s="49" t="s">
         <v>21</v>
       </c>
@@ -26412,7 +26451,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="734" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A734" s="49" t="s">
         <v>23</v>
       </c>
@@ -26441,7 +26480,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="735" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A735" s="49" t="s">
         <v>5</v>
       </c>
@@ -26470,7 +26509,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="736" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A736" s="49" t="s">
         <v>5</v>
       </c>
@@ -26499,7 +26538,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="737" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A737" s="49" t="s">
         <v>21</v>
       </c>
@@ -26528,7 +26567,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="738" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A738" s="49" t="s">
         <v>21</v>
       </c>
@@ -26557,7 +26596,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="739" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A739" s="49" t="s">
         <v>165</v>
       </c>
@@ -26586,7 +26625,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="740" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A740" s="49" t="s">
         <v>165</v>
       </c>
@@ -26615,7 +26654,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="741" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A741" s="49" t="s">
         <v>62</v>
       </c>
@@ -26644,7 +26683,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="742" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A742" s="49" t="s">
         <v>352</v>
       </c>
@@ -26673,7 +26712,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="743" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A743" s="49" t="s">
         <v>5</v>
       </c>
@@ -26702,7 +26741,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="744" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A744" s="49" t="s">
         <v>7</v>
       </c>
@@ -26731,7 +26770,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="745" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A745" s="49" t="s">
         <v>5</v>
       </c>
@@ -26760,7 +26799,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="746" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A746" s="49" t="s">
         <v>86</v>
       </c>
@@ -26789,7 +26828,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="747" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A747" s="49" t="s">
         <v>62</v>
       </c>
@@ -26818,7 +26857,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="748" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A748" s="49" t="s">
         <v>23</v>
       </c>
@@ -26847,7 +26886,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="749" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A749" s="49" t="s">
         <v>23</v>
       </c>
@@ -26876,7 +26915,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="750" spans="1:9" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A750" s="49" t="s">
         <v>23</v>
       </c>
@@ -26905,7 +26944,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="751" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A751" s="49" t="s">
         <v>5</v>
       </c>
@@ -26934,7 +26973,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="752" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A752" s="49" t="s">
         <v>5</v>
       </c>
@@ -26963,7 +27002,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="753" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A753" s="49" t="s">
         <v>62</v>
       </c>
@@ -26992,7 +27031,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="754" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A754" s="49" t="s">
         <v>21</v>
       </c>
@@ -27021,7 +27060,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="755" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A755" s="49" t="s">
         <v>6</v>
       </c>
@@ -27050,7 +27089,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="756" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A756" s="49" t="s">
         <v>84</v>
       </c>
@@ -27079,7 +27118,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="757" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A757" s="49" t="s">
         <v>62</v>
       </c>
@@ -27108,7 +27147,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="758" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A758" s="49" t="s">
         <v>62</v>
       </c>
@@ -27137,7 +27176,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="759" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A759" s="49" t="s">
         <v>165</v>
       </c>
@@ -27166,7 +27205,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="760" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A760" s="49" t="s">
         <v>5</v>
       </c>
@@ -27195,71 +27234,419 @@
         <v>186</v>
       </c>
     </row>
-    <row r="761" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A761" s="49"/>
-      <c r="B761" s="50"/>
-      <c r="C761" s="50"/>
-      <c r="D761" s="50"/>
-      <c r="E761" s="49"/>
-      <c r="F761" s="49"/>
-      <c r="G761" s="51"/>
-      <c r="H761" s="51"/>
-      <c r="I761" s="26"/>
-    </row>
-    <row r="762" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A762" s="49"/>
-      <c r="B762" s="50"/>
-      <c r="C762" s="50"/>
-      <c r="D762" s="50"/>
-      <c r="E762" s="49"/>
-      <c r="F762" s="49"/>
-      <c r="G762" s="51"/>
-      <c r="H762" s="51"/>
-      <c r="I762" s="26"/>
-    </row>
-    <row r="763" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A763" s="49"/>
-      <c r="B763" s="50"/>
-      <c r="C763" s="50"/>
-      <c r="D763" s="50"/>
-      <c r="E763" s="49"/>
-      <c r="F763" s="49"/>
-      <c r="G763" s="51"/>
-      <c r="H763" s="51"/>
-      <c r="I763" s="26"/>
-    </row>
-    <row r="764" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A764" s="49"/>
-      <c r="B764" s="50"/>
-      <c r="C764" s="50"/>
-      <c r="D764" s="50"/>
-      <c r="E764" s="49"/>
-      <c r="F764" s="49"/>
-      <c r="G764" s="51"/>
-      <c r="H764" s="51"/>
-      <c r="I764" s="26"/>
-    </row>
-    <row r="765" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A765" s="49"/>
-      <c r="B765" s="50"/>
-      <c r="C765" s="50"/>
-      <c r="D765" s="50"/>
-      <c r="E765" s="49"/>
-      <c r="F765" s="49"/>
-      <c r="G765" s="51"/>
-      <c r="H765" s="51"/>
-      <c r="I765" s="26"/>
-    </row>
-    <row r="766" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A766" s="49"/>
-      <c r="B766" s="50"/>
-      <c r="C766" s="50"/>
-      <c r="D766" s="50"/>
-      <c r="E766" s="49"/>
-      <c r="F766" s="49"/>
-      <c r="G766" s="51"/>
-      <c r="H766" s="51"/>
-      <c r="I766" s="26"/>
+    <row r="761" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A761" s="49" t="s">
+        <v>754</v>
+      </c>
+      <c r="B761" s="50">
+        <v>45678</v>
+      </c>
+      <c r="C761" s="50">
+        <v>45678</v>
+      </c>
+      <c r="D761" s="50">
+        <v>45744</v>
+      </c>
+      <c r="E761" s="49" t="s">
+        <v>1090</v>
+      </c>
+      <c r="F761" s="49" t="s">
+        <v>8</v>
+      </c>
+      <c r="G761" s="51">
+        <v>378</v>
+      </c>
+      <c r="H761" s="51" t="s">
+        <v>1091</v>
+      </c>
+      <c r="I761" s="26" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="762" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A762" s="49" t="s">
+        <v>6</v>
+      </c>
+      <c r="B762" s="50">
+        <v>45673</v>
+      </c>
+      <c r="C762" s="50">
+        <v>45678</v>
+      </c>
+      <c r="D762" s="50">
+        <v>45673</v>
+      </c>
+      <c r="E762" s="49" t="s">
+        <v>1092</v>
+      </c>
+      <c r="F762" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="G762" s="51">
+        <v>1</v>
+      </c>
+      <c r="H762" s="51" t="s">
+        <v>1093</v>
+      </c>
+      <c r="I762" s="26" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="763" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A763" s="49" t="s">
+        <v>383</v>
+      </c>
+      <c r="B763" s="50">
+        <v>45677</v>
+      </c>
+      <c r="C763" s="50">
+        <v>45678</v>
+      </c>
+      <c r="D763" s="50">
+        <v>45737</v>
+      </c>
+      <c r="E763" s="49" t="s">
+        <v>1094</v>
+      </c>
+      <c r="F763" s="49" t="s">
+        <v>8</v>
+      </c>
+      <c r="G763" s="51">
+        <v>50</v>
+      </c>
+      <c r="H763" s="51" t="s">
+        <v>1095</v>
+      </c>
+      <c r="I763" s="26" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="764" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A764" s="49" t="s">
+        <v>23</v>
+      </c>
+      <c r="B764" s="50">
+        <v>45678</v>
+      </c>
+      <c r="C764" s="50">
+        <v>45679</v>
+      </c>
+      <c r="D764" s="50">
+        <v>45738</v>
+      </c>
+      <c r="E764" s="49" t="s">
+        <v>373</v>
+      </c>
+      <c r="F764" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="G764" s="51">
+        <v>15</v>
+      </c>
+      <c r="H764" s="51" t="s">
+        <v>426</v>
+      </c>
+      <c r="I764" s="26" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="765" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A765" s="49" t="s">
+        <v>23</v>
+      </c>
+      <c r="B765" s="50">
+        <v>45678</v>
+      </c>
+      <c r="C765" s="50">
+        <v>45679</v>
+      </c>
+      <c r="D765" s="50">
+        <v>45738</v>
+      </c>
+      <c r="E765" s="49" t="s">
+        <v>373</v>
+      </c>
+      <c r="F765" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="G765" s="51">
+        <v>11</v>
+      </c>
+      <c r="H765" s="51" t="s">
+        <v>1096</v>
+      </c>
+      <c r="I765" s="26" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="766" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A766" s="49" t="s">
+        <v>23</v>
+      </c>
+      <c r="B766" s="50">
+        <v>45678</v>
+      </c>
+      <c r="C766" s="50">
+        <v>45679</v>
+      </c>
+      <c r="D766" s="50">
+        <v>45738</v>
+      </c>
+      <c r="E766" s="49" t="s">
+        <v>373</v>
+      </c>
+      <c r="F766" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="G766" s="51">
+        <v>1</v>
+      </c>
+      <c r="H766" s="51" t="s">
+        <v>427</v>
+      </c>
+      <c r="I766" s="26" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="767" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A767" s="49" t="s">
+        <v>23</v>
+      </c>
+      <c r="B767" s="50">
+        <v>45678</v>
+      </c>
+      <c r="C767" s="50">
+        <v>45679</v>
+      </c>
+      <c r="D767" s="50">
+        <v>45738</v>
+      </c>
+      <c r="E767" s="49" t="s">
+        <v>373</v>
+      </c>
+      <c r="F767" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="G767" s="51">
+        <v>2</v>
+      </c>
+      <c r="H767" s="51" t="s">
+        <v>1097</v>
+      </c>
+      <c r="I767" s="26" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="768" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A768" s="49" t="s">
+        <v>5</v>
+      </c>
+      <c r="B768" s="50">
+        <v>45678</v>
+      </c>
+      <c r="C768" s="50">
+        <v>45679</v>
+      </c>
+      <c r="D768" s="50">
+        <v>45738</v>
+      </c>
+      <c r="E768" s="49" t="s">
+        <v>373</v>
+      </c>
+      <c r="F768" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="G768" s="51">
+        <v>19</v>
+      </c>
+      <c r="H768" s="51" t="s">
+        <v>1098</v>
+      </c>
+      <c r="I768" s="26" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="769" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A769" s="49" t="s">
+        <v>5</v>
+      </c>
+      <c r="B769" s="50">
+        <v>45678</v>
+      </c>
+      <c r="C769" s="50">
+        <v>45679</v>
+      </c>
+      <c r="D769" s="50">
+        <v>45738</v>
+      </c>
+      <c r="E769" s="49" t="s">
+        <v>373</v>
+      </c>
+      <c r="F769" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="G769" s="51">
+        <v>1</v>
+      </c>
+      <c r="H769" s="51" t="s">
+        <v>1099</v>
+      </c>
+      <c r="I769" s="26" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="770" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A770" s="49" t="s">
+        <v>106</v>
+      </c>
+      <c r="B770" s="50">
+        <v>45678</v>
+      </c>
+      <c r="C770" s="50">
+        <v>45679</v>
+      </c>
+      <c r="D770" s="50">
+        <v>45738</v>
+      </c>
+      <c r="E770" s="49" t="s">
+        <v>373</v>
+      </c>
+      <c r="F770" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="G770" s="51">
+        <v>1</v>
+      </c>
+      <c r="H770" s="51" t="s">
+        <v>1100</v>
+      </c>
+      <c r="I770" s="26" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="771" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A771" s="49" t="s">
+        <v>86</v>
+      </c>
+      <c r="B771" s="50">
+        <v>45678</v>
+      </c>
+      <c r="C771" s="50">
+        <v>45679</v>
+      </c>
+      <c r="D771" s="50">
+        <v>45738</v>
+      </c>
+      <c r="E771" s="49" t="s">
+        <v>373</v>
+      </c>
+      <c r="F771" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="G771" s="51">
+        <v>1</v>
+      </c>
+      <c r="H771" s="51" t="s">
+        <v>1101</v>
+      </c>
+      <c r="I771" s="26" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="772" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A772" s="49" t="s">
+        <v>62</v>
+      </c>
+      <c r="B772" s="50">
+        <v>45678</v>
+      </c>
+      <c r="C772" s="50">
+        <v>45679</v>
+      </c>
+      <c r="D772" s="50">
+        <v>45738</v>
+      </c>
+      <c r="E772" s="49" t="s">
+        <v>373</v>
+      </c>
+      <c r="F772" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="G772" s="51">
+        <v>1</v>
+      </c>
+      <c r="H772" s="51" t="s">
+        <v>1102</v>
+      </c>
+      <c r="I772" s="26" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="773" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A773" s="49"/>
+      <c r="B773" s="50"/>
+      <c r="C773" s="50"/>
+      <c r="D773" s="50"/>
+      <c r="E773" s="49"/>
+      <c r="F773" s="49"/>
+      <c r="G773" s="51"/>
+      <c r="H773" s="51"/>
+      <c r="I773" s="26"/>
+    </row>
+    <row r="774" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A774" s="49"/>
+      <c r="B774" s="50"/>
+      <c r="C774" s="50"/>
+      <c r="D774" s="50"/>
+      <c r="E774" s="49"/>
+      <c r="F774" s="49"/>
+      <c r="G774" s="51"/>
+      <c r="H774" s="51"/>
+      <c r="I774" s="26"/>
+    </row>
+    <row r="775" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A775" s="49"/>
+      <c r="B775" s="50"/>
+      <c r="C775" s="50"/>
+      <c r="D775" s="50"/>
+      <c r="E775" s="49"/>
+      <c r="F775" s="49"/>
+      <c r="G775" s="51"/>
+      <c r="H775" s="51"/>
+      <c r="I775" s="26"/>
+    </row>
+    <row r="776" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A776" s="49"/>
+      <c r="B776" s="50"/>
+      <c r="C776" s="50"/>
+      <c r="D776" s="50"/>
+      <c r="E776" s="49"/>
+      <c r="F776" s="49"/>
+      <c r="G776" s="51"/>
+      <c r="H776" s="51"/>
+      <c r="I776" s="26"/>
+    </row>
+    <row r="777" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A777" s="49"/>
+      <c r="B777" s="50"/>
+      <c r="C777" s="50"/>
+      <c r="D777" s="50"/>
+      <c r="E777" s="49"/>
+      <c r="F777" s="49"/>
+      <c r="G777" s="51"/>
+      <c r="H777" s="51"/>
+      <c r="I777" s="26"/>
+    </row>
+    <row r="778" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A778" s="49"/>
+      <c r="B778" s="50"/>
+      <c r="C778" s="50"/>
+      <c r="D778" s="50"/>
+      <c r="E778" s="49"/>
+      <c r="F778" s="49"/>
+      <c r="G778" s="51"/>
+      <c r="H778" s="51"/>
+      <c r="I778" s="26"/>
     </row>
   </sheetData>
   <phoneticPr fontId="10" type="noConversion"/>
@@ -27275,7 +27662,7 @@
           <x14:formula1>
             <xm:f>'Industry List'!$A$1:$A$22</xm:f>
           </x14:formula1>
-          <xm:sqref>I3:I760</xm:sqref>
+          <xm:sqref>I3:I772</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -27286,18 +27673,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CC03875-3DF4-4258-8762-7FFE2A7D620D}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="28.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.7109375" style="22" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.7265625" style="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="97.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="95" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="15" t="s">
         <v>20</v>
       </c>
@@ -27305,7 +27692,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="17" t="s">
         <v>24</v>
       </c>
@@ -27314,7 +27701,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="17" t="s">
         <v>13</v>
       </c>
@@ -27323,7 +27710,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="17" t="s">
         <v>14</v>
       </c>
@@ -27332,7 +27719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="17" t="s">
         <v>15</v>
       </c>
@@ -27341,7 +27728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="17" t="s">
         <v>16</v>
       </c>
@@ -27350,7 +27737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="17" t="s">
         <v>17</v>
       </c>
@@ -27359,7 +27746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="17" t="s">
         <v>18</v>
       </c>
@@ -27382,25 +27769,25 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EE76718-798E-45ED-8CA1-01AA760CE5F1}">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="26.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.42578125" style="18" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" style="18" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.28515625" style="18" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="31.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="34.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.453125" style="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.1796875" style="18" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.26953125" style="18" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="34.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="110.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="108.5" x14ac:dyDescent="0.35">
       <c r="A1" s="25" t="s">
         <v>1089</v>
       </c>
       <c r="E1"/>
     </row>
-    <row r="2" spans="1:8" ht="24.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="24" x14ac:dyDescent="0.35">
       <c r="A2" s="19" t="s">
         <v>0</v>
       </c>
@@ -27426,7 +27813,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -27463,117 +27850,117 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E81B0C9-EE0D-4672-99B4-ACA7D2D31E92}">
   <dimension ref="A1:A22"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="67.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="67.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>194</v>
       </c>

--- a/data/warn-scraper/cache/ca/warn_report1.xlsx
+++ b/data/warn-scraper/cache/ca/warn_report1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\entshare3\JS-Data\WSB-CO\BPAC\Policy &amp; Program Communications Group\Communications Unit\Website Management\5. WARN (Worker Adjustment and Retraining Notification) Updates\2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96C56D35-4CE0-4CFB-8AB2-65948F060E30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EA1BB0E-C985-4B61-8CE3-4D1AE83D45DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="751" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="751" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
   <sheets>
     <sheet name="Index" sheetId="3" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3921" uniqueCount="1104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3946" uniqueCount="1112">
   <si>
     <t>County/Parish</t>
   </si>
@@ -3395,8 +3395,47 @@
     <t>6200 Franklin Boulevard  Sacramento CA 95824</t>
   </si>
   <si>
+    <t>Del Monte Foods, Inc.</t>
+  </si>
+  <si>
+    <t>10652 Jackson Avenue  Hanford CA 93230</t>
+  </si>
+  <si>
+    <t>Fast Ride Moto, LLC</t>
+  </si>
+  <si>
+    <t>6919 North Avenue  Lemon Grove CA 91945</t>
+  </si>
+  <si>
+    <t>Quanex Homeshield LLC</t>
+  </si>
+  <si>
+    <t>3640 Ramos Drive, Suite #120  West Sacramento CA 95691</t>
+  </si>
+  <si>
+    <t>1438 Webster Street  Oakland CA 94612</t>
+  </si>
+  <si>
+    <t>5820 Owens Drive  Pleasanton CA 94588</t>
+  </si>
+  <si>
+    <t>10949 Pendleton Street  Sun Valley CA 91352</t>
+  </si>
+  <si>
+    <t>4733 W. Sunset Blvd  Los Angeles CA 90027</t>
+  </si>
+  <si>
+    <t>1840 California Avenue  Corona CA 92881</t>
+  </si>
+  <si>
+    <t>1900 S. Norfolk Street  San Mateo CA 94403</t>
+  </si>
+  <si>
+    <t>276 International Circle  San Jose CA 95119</t>
+  </si>
+  <si>
     <r>
-      <t xml:space="preserve">WARN REPORT - 01/01/2023 - 01/22/2025
+      <t xml:space="preserve">WARN REPORT - 01/01/2023 - 01/27/2025
 </t>
     </r>
     <r>
@@ -3410,43 +3449,28 @@
     </r>
   </si>
   <si>
-    <t>Del Monte Foods, Inc.</t>
-  </si>
-  <si>
-    <t>10652 Jackson Avenue  Hanford CA 93230</t>
-  </si>
-  <si>
-    <t>Fast Ride Moto, LLC</t>
-  </si>
-  <si>
-    <t>6919 North Avenue  Lemon Grove CA 91945</t>
-  </si>
-  <si>
-    <t>Quanex Homeshield LLC</t>
-  </si>
-  <si>
-    <t>3640 Ramos Drive, Suite #120  West Sacramento CA 95691</t>
-  </si>
-  <si>
-    <t>1438 Webster Street  Oakland CA 94612</t>
-  </si>
-  <si>
-    <t>5820 Owens Drive  Pleasanton CA 94588</t>
-  </si>
-  <si>
-    <t>10949 Pendleton Street  Sun Valley CA 91352</t>
-  </si>
-  <si>
-    <t>4733 W. Sunset Blvd  Los Angeles CA 90027</t>
-  </si>
-  <si>
-    <t>1840 California Avenue  Corona CA 92881</t>
-  </si>
-  <si>
-    <t>1900 S. Norfolk Street  San Mateo CA 94403</t>
-  </si>
-  <si>
-    <t>276 International Circle  San Jose CA 95119</t>
+    <t>Evergreen Recycling, Inc</t>
+  </si>
+  <si>
+    <t>875 Michigan Avenue  Riverside CA 92507</t>
+  </si>
+  <si>
+    <t>Universal Logistics Intermodal Inc.</t>
+  </si>
+  <si>
+    <t>15033 Slover Avenue  Fontana CA 92337</t>
+  </si>
+  <si>
+    <t>Pasadena Park Healthcare &amp; Wellness Center</t>
+  </si>
+  <si>
+    <t>2585 E. Washington Blvd  Pasadena CA 91107</t>
+  </si>
+  <si>
+    <t>Joann Stores Support Center, Inc.</t>
+  </si>
+  <si>
+    <t>2500 N. Plaza Drive  Visalia CA 93291</t>
   </si>
   <si>
     <r>
@@ -3460,7 +3484,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>07/01/24 to 01/22/2025</t>
+      <t>07/01/24 to 01/27/2025</t>
     </r>
     <r>
       <rPr>
@@ -3480,7 +3504,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I772.</t>
+      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I777.</t>
     </r>
   </si>
 </sst>
@@ -4707,8 +4731,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I772" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
-  <autoFilter ref="A2:I772" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I777" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
+  <autoFilter ref="A2:I777" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -5136,7 +5160,7 @@
       </c>
       <c r="B3" s="11">
         <f>SUM('Detailed WARN Report '!G:G)</f>
-        <v>42998</v>
+        <v>43469</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
@@ -5145,7 +5169,7 @@
       </c>
       <c r="B4" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Permanent")</f>
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
@@ -5171,7 +5195,7 @@
       </c>
       <c r="B7" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Permanent")</f>
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
@@ -5203,7 +5227,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:I778"/>
+  <dimension ref="A1:I783"/>
   <sheetFormatPr defaultColWidth="102.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="28.7265625" style="3" bestFit="1" customWidth="1"/>
@@ -5219,11 +5243,11 @@
   <sheetData>
     <row r="1" spans="1:9" ht="100" x14ac:dyDescent="0.35">
       <c r="A1" s="16" t="s">
-        <v>1103</v>
+        <v>1111</v>
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:9" ht="24" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" ht="35.5" x14ac:dyDescent="0.35">
       <c r="A2" s="29" t="s">
         <v>0</v>
       </c>
@@ -23910,7 +23934,7 @@
         <v>45623</v>
       </c>
       <c r="D646" s="50">
-        <v>45684</v>
+        <v>45698</v>
       </c>
       <c r="E646" s="49" t="s">
         <v>916</v>
@@ -27248,7 +27272,7 @@
         <v>45744</v>
       </c>
       <c r="E761" s="49" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="F761" s="49" t="s">
         <v>8</v>
@@ -27257,7 +27281,7 @@
         <v>378</v>
       </c>
       <c r="H761" s="51" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="I761" s="26" t="s">
         <v>177</v>
@@ -27277,7 +27301,7 @@
         <v>45673</v>
       </c>
       <c r="E762" s="49" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="F762" s="49" t="s">
         <v>9</v>
@@ -27286,7 +27310,7 @@
         <v>1</v>
       </c>
       <c r="H762" s="51" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="I762" s="26" t="s">
         <v>179</v>
@@ -27306,7 +27330,7 @@
         <v>45737</v>
       </c>
       <c r="E763" s="49" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="F763" s="49" t="s">
         <v>8</v>
@@ -27315,7 +27339,7 @@
         <v>50</v>
       </c>
       <c r="H763" s="51" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="I763" s="26" t="s">
         <v>177</v>
@@ -27373,7 +27397,7 @@
         <v>11</v>
       </c>
       <c r="H765" s="51" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="I765" s="26" t="s">
         <v>188</v>
@@ -27431,7 +27455,7 @@
         <v>2</v>
       </c>
       <c r="H767" s="51" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="I767" s="26" t="s">
         <v>188</v>
@@ -27460,7 +27484,7 @@
         <v>19</v>
       </c>
       <c r="H768" s="51" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="I768" s="26" t="s">
         <v>188</v>
@@ -27489,7 +27513,7 @@
         <v>1</v>
       </c>
       <c r="H769" s="51" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="I769" s="26" t="s">
         <v>188</v>
@@ -27518,7 +27542,7 @@
         <v>1</v>
       </c>
       <c r="H770" s="51" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="I770" s="26" t="s">
         <v>188</v>
@@ -27547,7 +27571,7 @@
         <v>1</v>
       </c>
       <c r="H771" s="51" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="I771" s="26" t="s">
         <v>188</v>
@@ -27576,66 +27600,156 @@
         <v>1</v>
       </c>
       <c r="H772" s="51" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="I772" s="26" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="773" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A773" s="49"/>
-      <c r="B773" s="50"/>
-      <c r="C773" s="50"/>
-      <c r="D773" s="50"/>
-      <c r="E773" s="49"/>
-      <c r="F773" s="49"/>
-      <c r="G773" s="51"/>
-      <c r="H773" s="51"/>
-      <c r="I773" s="26"/>
+      <c r="A773" s="49" t="s">
+        <v>79</v>
+      </c>
+      <c r="B773" s="50">
+        <v>45680</v>
+      </c>
+      <c r="C773" s="50">
+        <v>45680</v>
+      </c>
+      <c r="D773" s="50">
+        <v>45740</v>
+      </c>
+      <c r="E773" s="49" t="s">
+        <v>201</v>
+      </c>
+      <c r="F773" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="G773" s="51">
+        <v>8</v>
+      </c>
+      <c r="H773" s="51" t="s">
+        <v>306</v>
+      </c>
+      <c r="I773" s="26" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="774" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A774" s="49"/>
-      <c r="B774" s="50"/>
-      <c r="C774" s="50"/>
-      <c r="D774" s="50"/>
-      <c r="E774" s="49"/>
-      <c r="F774" s="49"/>
-      <c r="G774" s="51"/>
-      <c r="H774" s="51"/>
-      <c r="I774" s="26"/>
+      <c r="A774" s="49" t="s">
+        <v>106</v>
+      </c>
+      <c r="B774" s="50">
+        <v>45679</v>
+      </c>
+      <c r="C774" s="50">
+        <v>45680</v>
+      </c>
+      <c r="D774" s="50">
+        <v>45740</v>
+      </c>
+      <c r="E774" s="49" t="s">
+        <v>1103</v>
+      </c>
+      <c r="F774" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="G774" s="51">
+        <v>57</v>
+      </c>
+      <c r="H774" s="51" t="s">
+        <v>1104</v>
+      </c>
+      <c r="I774" s="26" t="s">
+        <v>186</v>
+      </c>
     </row>
     <row r="775" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A775" s="49"/>
-      <c r="B775" s="50"/>
-      <c r="C775" s="50"/>
-      <c r="D775" s="50"/>
-      <c r="E775" s="49"/>
-      <c r="F775" s="49"/>
-      <c r="G775" s="51"/>
-      <c r="H775" s="51"/>
-      <c r="I775" s="26"/>
+      <c r="A775" s="49" t="s">
+        <v>22</v>
+      </c>
+      <c r="B775" s="50">
+        <v>45678</v>
+      </c>
+      <c r="C775" s="50">
+        <v>45680</v>
+      </c>
+      <c r="D775" s="50">
+        <v>45738</v>
+      </c>
+      <c r="E775" s="49" t="s">
+        <v>1105</v>
+      </c>
+      <c r="F775" s="49" t="s">
+        <v>8</v>
+      </c>
+      <c r="G775" s="51">
+        <v>46</v>
+      </c>
+      <c r="H775" s="51" t="s">
+        <v>1106</v>
+      </c>
+      <c r="I775" s="26" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="776" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A776" s="49"/>
-      <c r="B776" s="50"/>
-      <c r="C776" s="50"/>
-      <c r="D776" s="50"/>
-      <c r="E776" s="49"/>
-      <c r="F776" s="49"/>
-      <c r="G776" s="51"/>
-      <c r="H776" s="51"/>
-      <c r="I776" s="26"/>
+      <c r="A776" s="49" t="s">
+        <v>5</v>
+      </c>
+      <c r="B776" s="50">
+        <v>45684</v>
+      </c>
+      <c r="C776" s="50">
+        <v>45684</v>
+      </c>
+      <c r="D776" s="50">
+        <v>45672</v>
+      </c>
+      <c r="E776" s="49" t="s">
+        <v>1107</v>
+      </c>
+      <c r="F776" s="49" t="s">
+        <v>129</v>
+      </c>
+      <c r="G776" s="51">
+        <v>151</v>
+      </c>
+      <c r="H776" s="51" t="s">
+        <v>1108</v>
+      </c>
+      <c r="I776" s="26" t="s">
+        <v>188</v>
+      </c>
     </row>
     <row r="777" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A777" s="49"/>
-      <c r="B777" s="50"/>
-      <c r="C777" s="50"/>
-      <c r="D777" s="50"/>
-      <c r="E777" s="49"/>
-      <c r="F777" s="49"/>
-      <c r="G777" s="51"/>
-      <c r="H777" s="51"/>
-      <c r="I777" s="26"/>
+      <c r="A777" s="49" t="s">
+        <v>453</v>
+      </c>
+      <c r="B777" s="50">
+        <v>45681</v>
+      </c>
+      <c r="C777" s="50">
+        <v>45684</v>
+      </c>
+      <c r="D777" s="50">
+        <v>45747</v>
+      </c>
+      <c r="E777" s="49" t="s">
+        <v>1109</v>
+      </c>
+      <c r="F777" s="49" t="s">
+        <v>8</v>
+      </c>
+      <c r="G777" s="51">
+        <v>209</v>
+      </c>
+      <c r="H777" s="51" t="s">
+        <v>1110</v>
+      </c>
+      <c r="I777" s="26" t="s">
+        <v>179</v>
+      </c>
     </row>
     <row r="778" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A778" s="49"/>
@@ -27647,6 +27761,61 @@
       <c r="G778" s="51"/>
       <c r="H778" s="51"/>
       <c r="I778" s="26"/>
+    </row>
+    <row r="779" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A779" s="49"/>
+      <c r="B779" s="50"/>
+      <c r="C779" s="50"/>
+      <c r="D779" s="50"/>
+      <c r="E779" s="49"/>
+      <c r="F779" s="49"/>
+      <c r="G779" s="51"/>
+      <c r="H779" s="51"/>
+      <c r="I779" s="26"/>
+    </row>
+    <row r="780" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A780" s="49"/>
+      <c r="B780" s="50"/>
+      <c r="C780" s="50"/>
+      <c r="D780" s="50"/>
+      <c r="E780" s="49"/>
+      <c r="F780" s="49"/>
+      <c r="G780" s="51"/>
+      <c r="H780" s="51"/>
+      <c r="I780" s="26"/>
+    </row>
+    <row r="781" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A781" s="49"/>
+      <c r="B781" s="50"/>
+      <c r="C781" s="50"/>
+      <c r="D781" s="50"/>
+      <c r="E781" s="49"/>
+      <c r="F781" s="49"/>
+      <c r="G781" s="51"/>
+      <c r="H781" s="51"/>
+      <c r="I781" s="26"/>
+    </row>
+    <row r="782" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A782" s="49"/>
+      <c r="B782" s="50"/>
+      <c r="C782" s="50"/>
+      <c r="D782" s="50"/>
+      <c r="E782" s="49"/>
+      <c r="F782" s="49"/>
+      <c r="G782" s="51"/>
+      <c r="H782" s="51"/>
+      <c r="I782" s="26"/>
+    </row>
+    <row r="783" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A783" s="49"/>
+      <c r="B783" s="50"/>
+      <c r="C783" s="50"/>
+      <c r="D783" s="50"/>
+      <c r="E783" s="49"/>
+      <c r="F783" s="49"/>
+      <c r="G783" s="51"/>
+      <c r="H783" s="51"/>
+      <c r="I783" s="26"/>
     </row>
   </sheetData>
   <phoneticPr fontId="10" type="noConversion"/>
@@ -27662,7 +27831,7 @@
           <x14:formula1>
             <xm:f>'Industry List'!$A$1:$A$22</xm:f>
           </x14:formula1>
-          <xm:sqref>I3:I772</xm:sqref>
+          <xm:sqref>I3:I777</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -27783,7 +27952,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="108.5" x14ac:dyDescent="0.35">
       <c r="A1" s="25" t="s">
-        <v>1089</v>
+        <v>1102</v>
       </c>
       <c r="E1"/>
     </row>

--- a/data/warn-scraper/cache/ca/warn_report1.xlsx
+++ b/data/warn-scraper/cache/ca/warn_report1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\entshare3\JS-Data\WSB-CO\BPAC\Policy &amp; Program Communications Group\Communications Unit\Website Management\5. WARN (Worker Adjustment and Retraining Notification) Updates\2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EA1BB0E-C985-4B61-8CE3-4D1AE83D45DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1C19437-C4AF-405C-BC50-8677CAF8634D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="751" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="751" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
   <sheets>
     <sheet name="Index" sheetId="3" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3946" uniqueCount="1112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4006" uniqueCount="1128">
   <si>
     <t>County/Parish</t>
   </si>
@@ -3434,8 +3434,32 @@
     <t>276 International Circle  San Jose CA 95119</t>
   </si>
   <si>
+    <t>Evergreen Recycling, Inc</t>
+  </si>
+  <si>
+    <t>875 Michigan Avenue  Riverside CA 92507</t>
+  </si>
+  <si>
+    <t>Universal Logistics Intermodal Inc.</t>
+  </si>
+  <si>
+    <t>15033 Slover Avenue  Fontana CA 92337</t>
+  </si>
+  <si>
+    <t>Pasadena Park Healthcare &amp; Wellness Center</t>
+  </si>
+  <si>
+    <t>2585 E. Washington Blvd  Pasadena CA 91107</t>
+  </si>
+  <si>
+    <t>Joann Stores Support Center, Inc.</t>
+  </si>
+  <si>
+    <t>2500 N. Plaza Drive  Visalia CA 93291</t>
+  </si>
+  <si>
     <r>
-      <t xml:space="preserve">WARN REPORT - 01/01/2023 - 01/27/2025
+      <t xml:space="preserve">WARN REPORT - 01/01/2023 - 01/29/2025
 </t>
     </r>
     <r>
@@ -3449,28 +3473,52 @@
     </r>
   </si>
   <si>
-    <t>Evergreen Recycling, Inc</t>
-  </si>
-  <si>
-    <t>875 Michigan Avenue  Riverside CA 92507</t>
-  </si>
-  <si>
-    <t>Universal Logistics Intermodal Inc.</t>
-  </si>
-  <si>
-    <t>15033 Slover Avenue  Fontana CA 92337</t>
-  </si>
-  <si>
-    <t>Pasadena Park Healthcare &amp; Wellness Center</t>
-  </si>
-  <si>
-    <t>2585 E. Washington Blvd  Pasadena CA 91107</t>
-  </si>
-  <si>
-    <t>Joann Stores Support Center, Inc.</t>
-  </si>
-  <si>
-    <t>2500 N. Plaza Drive  Visalia CA 93291</t>
+    <t>Prime MSO, LLC</t>
+  </si>
+  <si>
+    <t>5353 Balboa Blvd., Suite 300  Encino CA 91316</t>
+  </si>
+  <si>
+    <t>9920 Jefferson Blvd.  Culver City CA 90232</t>
+  </si>
+  <si>
+    <t>2040 E. Mariposa Avenue  El Segundo CA 90245</t>
+  </si>
+  <si>
+    <t>LEGOLAND</t>
+  </si>
+  <si>
+    <t>1 LEGOLAND Drive  Carlsbad CA 92008</t>
+  </si>
+  <si>
+    <t>Foster Farms</t>
+  </si>
+  <si>
+    <t>500 F Street  Turlock CA 95380</t>
+  </si>
+  <si>
+    <t>550 C Street  Turlock CA 95380</t>
+  </si>
+  <si>
+    <t>3600 W. Main Street  Turlock CA 95380</t>
+  </si>
+  <si>
+    <t>Pregis</t>
+  </si>
+  <si>
+    <t>159 N. San Antonio Avenue  Pomona CA 91767</t>
+  </si>
+  <si>
+    <t>Quantumscape Battery Inc.</t>
+  </si>
+  <si>
+    <t>1730 Technology Drive  San Jose CA 95110</t>
+  </si>
+  <si>
+    <t>InvenSense Inc.</t>
+  </si>
+  <si>
+    <t>1745 Technology Drive Suite #200 San Jose CA 95110</t>
   </si>
   <si>
     <r>
@@ -3484,7 +3532,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>07/01/24 to 01/27/2025</t>
+      <t>07/01/24 to 01/29/2025</t>
     </r>
     <r>
       <rPr>
@@ -3504,7 +3552,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I777.</t>
+      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I789.</t>
     </r>
   </si>
 </sst>
@@ -4731,8 +4779,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I777" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
-  <autoFilter ref="A2:I777" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I789" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
+  <autoFilter ref="A2:I789" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -5086,37 +5134,37 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D341DFFF-02D2-4572-95F5-BB3221952133}">
   <dimension ref="A1:A6"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="74" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1" ht="135" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="21" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:1" ht="21" x14ac:dyDescent="0.35">
       <c r="A2" s="12" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
         <v>33</v>
       </c>
@@ -5135,18 +5183,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1832896D-8AFB-4FFC-957E-910308F3BC0C}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.453125" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.453125" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.42578125" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="76.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
         <v>20</v>
       </c>
@@ -5154,25 +5202,25 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B3" s="11">
         <f>SUM('Detailed WARN Report '!G:G)</f>
-        <v>43469</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+        <v>44276</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B4" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Permanent")</f>
-        <v>408</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>14</v>
       </c>
@@ -5181,7 +5229,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>15</v>
       </c>
@@ -5189,16 +5237,16 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B7" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Permanent")</f>
-        <v>336</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>17</v>
       </c>
@@ -5207,7 +5255,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>18</v>
       </c>
@@ -5227,27 +5275,27 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:I783"/>
-  <sheetFormatPr defaultColWidth="102.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:I795"/>
+  <sheetFormatPr defaultColWidth="102.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.7265625" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.7109375" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.81640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.453125" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="62.26953125" style="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.26953125" style="3" customWidth="1"/>
-    <col min="7" max="7" width="9.81640625" style="3" customWidth="1"/>
-    <col min="8" max="8" width="57.7265625" style="3" customWidth="1"/>
-    <col min="9" max="9" width="51.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.85546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.42578125" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="62.28515625" style="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.28515625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="9.85546875" style="3" customWidth="1"/>
+    <col min="8" max="8" width="57.7109375" style="3" customWidth="1"/>
+    <col min="9" max="9" width="51.85546875" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="100" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" ht="102" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
-        <v>1111</v>
+        <v>1127</v>
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:9" ht="35.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A2" s="29" t="s">
         <v>0</v>
       </c>
@@ -5276,7 +5324,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="26" t="s">
         <v>5</v>
       </c>
@@ -5305,7 +5353,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="26" t="s">
         <v>21</v>
       </c>
@@ -5334,7 +5382,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="26" t="s">
         <v>7</v>
       </c>
@@ -5363,7 +5411,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="26" t="s">
         <v>5</v>
       </c>
@@ -5392,7 +5440,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="26" t="s">
         <v>6</v>
       </c>
@@ -5421,7 +5469,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="26" t="s">
         <v>6</v>
       </c>
@@ -5450,7 +5498,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="26" t="s">
         <v>49</v>
       </c>
@@ -5479,7 +5527,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="26" t="s">
         <v>23</v>
       </c>
@@ -5508,7 +5556,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="26" t="s">
         <v>22</v>
       </c>
@@ -5537,7 +5585,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="26" t="s">
         <v>22</v>
       </c>
@@ -5566,7 +5614,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="26" t="s">
         <v>5</v>
       </c>
@@ -5595,7 +5643,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="26" t="s">
         <v>21</v>
       </c>
@@ -5624,7 +5672,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="26" t="s">
         <v>6</v>
       </c>
@@ -5653,7 +5701,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="26" t="s">
         <v>62</v>
       </c>
@@ -5682,7 +5730,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="26" t="s">
         <v>6</v>
       </c>
@@ -5711,7 +5759,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="26" t="s">
         <v>6</v>
       </c>
@@ -5740,7 +5788,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="26" t="s">
         <v>67</v>
       </c>
@@ -5769,7 +5817,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="26" t="s">
         <v>22</v>
       </c>
@@ -5798,7 +5846,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="26" t="s">
         <v>6</v>
       </c>
@@ -5827,7 +5875,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="26" t="s">
         <v>6</v>
       </c>
@@ -5856,7 +5904,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="26" t="s">
         <v>5</v>
       </c>
@@ -5885,7 +5933,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="26" t="s">
         <v>5</v>
       </c>
@@ -5914,7 +5962,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="26" t="s">
         <v>79</v>
       </c>
@@ -5943,7 +5991,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="26" t="s">
         <v>21</v>
       </c>
@@ -5972,7 +6020,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="26" t="s">
         <v>84</v>
       </c>
@@ -6001,7 +6049,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="26" t="s">
         <v>86</v>
       </c>
@@ -6030,7 +6078,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="26" t="s">
         <v>22</v>
       </c>
@@ -6059,7 +6107,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="26" t="s">
         <v>5</v>
       </c>
@@ -6088,7 +6136,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="26" t="s">
         <v>5</v>
       </c>
@@ -6117,7 +6165,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="26" t="s">
         <v>5</v>
       </c>
@@ -6146,7 +6194,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="26" t="s">
         <v>23</v>
       </c>
@@ -6175,7 +6223,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="26" t="s">
         <v>23</v>
       </c>
@@ -6204,7 +6252,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="26" t="s">
         <v>5</v>
       </c>
@@ -6233,7 +6281,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="26" t="s">
         <v>5</v>
       </c>
@@ -6262,7 +6310,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="26" t="s">
         <v>5</v>
       </c>
@@ -6291,7 +6339,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="26" t="s">
         <v>5</v>
       </c>
@@ -6320,7 +6368,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="26" t="s">
         <v>5</v>
       </c>
@@ -6349,7 +6397,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="26" t="s">
         <v>5</v>
       </c>
@@ -6378,7 +6426,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="26" t="s">
         <v>5</v>
       </c>
@@ -6407,7 +6455,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="26" t="s">
         <v>5</v>
       </c>
@@ -6436,7 +6484,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="26" t="s">
         <v>21</v>
       </c>
@@ -6465,7 +6513,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="26" t="s">
         <v>106</v>
       </c>
@@ -6494,7 +6542,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="26" t="s">
         <v>106</v>
       </c>
@@ -6523,7 +6571,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="26" t="s">
         <v>22</v>
       </c>
@@ -6552,7 +6600,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="26" t="s">
         <v>22</v>
       </c>
@@ -6581,7 +6629,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="26" t="s">
         <v>22</v>
       </c>
@@ -6610,7 +6658,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="26" t="s">
         <v>22</v>
       </c>
@@ -6639,7 +6687,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="26" t="s">
         <v>114</v>
       </c>
@@ -6668,7 +6716,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="26" t="s">
         <v>5</v>
       </c>
@@ -6697,7 +6745,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="26" t="s">
         <v>5</v>
       </c>
@@ -6726,7 +6774,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="26" t="s">
         <v>5</v>
       </c>
@@ -6755,7 +6803,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="26" t="s">
         <v>79</v>
       </c>
@@ -6784,7 +6832,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="26" t="s">
         <v>79</v>
       </c>
@@ -6813,7 +6861,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="26" t="s">
         <v>5</v>
       </c>
@@ -6842,7 +6890,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="26" t="s">
         <v>5</v>
       </c>
@@ -6871,7 +6919,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="26" t="s">
         <v>5</v>
       </c>
@@ -6900,7 +6948,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="26" t="s">
         <v>84</v>
       </c>
@@ -6929,7 +6977,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="26" t="s">
         <v>5</v>
       </c>
@@ -6958,7 +7006,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="26" t="s">
         <v>23</v>
       </c>
@@ -6987,7 +7035,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="26" t="s">
         <v>23</v>
       </c>
@@ -7016,7 +7064,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="26" t="s">
         <v>23</v>
       </c>
@@ -7045,7 +7093,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="26" t="s">
         <v>23</v>
       </c>
@@ -7074,7 +7122,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="26" t="s">
         <v>49</v>
       </c>
@@ -7103,7 +7151,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="26" t="s">
         <v>139</v>
       </c>
@@ -7132,7 +7180,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="26" t="s">
         <v>139</v>
       </c>
@@ -7161,7 +7209,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="26" t="s">
         <v>142</v>
       </c>
@@ -7190,7 +7238,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="26" t="s">
         <v>144</v>
       </c>
@@ -7219,7 +7267,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="26" t="s">
         <v>144</v>
       </c>
@@ -7248,7 +7296,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="26" t="s">
         <v>144</v>
       </c>
@@ -7277,7 +7325,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="26" t="s">
         <v>144</v>
       </c>
@@ -7306,7 +7354,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="26" t="s">
         <v>144</v>
       </c>
@@ -7335,7 +7383,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="26" t="s">
         <v>144</v>
       </c>
@@ -7364,7 +7412,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="26" t="s">
         <v>23</v>
       </c>
@@ -7393,7 +7441,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="26" t="s">
         <v>21</v>
       </c>
@@ -7422,7 +7470,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="26" t="s">
         <v>155</v>
       </c>
@@ -7451,7 +7499,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="26" t="s">
         <v>23</v>
       </c>
@@ -7480,7 +7528,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="26" t="s">
         <v>23</v>
       </c>
@@ -7509,7 +7557,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="26" t="s">
         <v>79</v>
       </c>
@@ -7538,7 +7586,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="26" t="s">
         <v>5</v>
       </c>
@@ -7567,7 +7615,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="26" t="s">
         <v>21</v>
       </c>
@@ -7596,7 +7644,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="26" t="s">
         <v>165</v>
       </c>
@@ -7625,7 +7673,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="26" t="s">
         <v>22</v>
       </c>
@@ -7654,7 +7702,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="26" t="s">
         <v>6</v>
       </c>
@@ -7683,7 +7731,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="26" t="s">
         <v>62</v>
       </c>
@@ -7712,7 +7760,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="26" t="s">
         <v>84</v>
       </c>
@@ -7741,7 +7789,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="26" t="s">
         <v>62</v>
       </c>
@@ -7770,7 +7818,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="26" t="s">
         <v>21</v>
       </c>
@@ -7799,7 +7847,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="26" t="s">
         <v>114</v>
       </c>
@@ -7828,7 +7876,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="26" t="s">
         <v>79</v>
       </c>
@@ -7857,7 +7905,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="26" t="s">
         <v>79</v>
       </c>
@@ -7886,7 +7934,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" s="26" t="s">
         <v>7</v>
       </c>
@@ -7915,7 +7963,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="26" t="s">
         <v>5</v>
       </c>
@@ -7944,7 +7992,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" s="26" t="s">
         <v>5</v>
       </c>
@@ -7973,7 +8021,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="26" t="s">
         <v>5</v>
       </c>
@@ -8002,7 +8050,7 @@
         <v>187</v>
       </c>
     </